--- a/010_開発プロセス標準/Nablarchを使用したシステム開発における標準WBS.xlsx
+++ b/010_開発プロセス標準/Nablarchを使用したシステム開発における標準WBS.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650A631E-9E7D-4FB2-97FF-4C102CFCFAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B476C759-000E-42D5-975E-D55A089344D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="14" r:id="rId1"/>
@@ -16,11 +16,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2. WBS'!$A$2:$E$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'1. 概要'!$A$1:$AI$70</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'1. 概要'!$A$1:$AI$110</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'2. WBS'!$A$1:$K$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">目次!$A$1:$AI$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">目次!$A$1:$AI$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'1. 概要'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'2. WBS'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="427">
   <si>
     <t xml:space="preserve">データベース論理設計
 </t>
@@ -2971,52 +2971,6 @@
 標</t>
     <rPh sb="2" eb="3">
       <t>シルベ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">画面イメージはHTMLで作成すること。PG・UTI工程において、JSP自動生成ツールを使用することで、HTML→JSP変換の作業負荷を軽減できる。
-JSP自動生成ツールの詳細は、Nablarch Toolboxの下記ドキュメントを参照。
-・JSP自動生成ツール
-</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>コウテイ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ヘンカン</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>サギョウ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>フカ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>ケイゲン</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="106" eb="108">
-      <t>カキ</t>
-    </rPh>
-    <rPh sb="115" eb="117">
-      <t>サンショウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -3623,26 +3577,6 @@
       <t>タンタイ</t>
     </rPh>
     <rPh sb="93" eb="95">
-      <t>ヒョウジュン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">プログラミング・単体テストガイド
-マスタデータ投入ツール
-JSP自動生成ツール
-SQL自動生成ツール
-HTMLチェックツール
-JSP静的解析ツール
-Java静的解析ツール
-使用不許可APIチェックツール
-リクエスト単体データ作成ツール
-単体テスト標準
-</t>
-    <rPh sb="118" eb="120">
-      <t>タンタイ</t>
-    </rPh>
-    <rPh sb="123" eb="125">
       <t>ヒョウジュン</t>
     </rPh>
     <phoneticPr fontId="3"/>
@@ -4699,6 +4633,331 @@
       <t>ハン</t>
     </rPh>
     <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>1.4. Nablarch6を使用する場合の記載の読み替えについて</t>
+    <rPh sb="15" eb="17">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Nablarch6はJakarta EE 10前提のフレームワークである。</t>
+    <rPh sb="23" eb="25">
+      <t>ゼンテイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>省略名</t>
+  </si>
+  <si>
+    <t>JSF</t>
+  </si>
+  <si>
+    <t>JASPIC</t>
+  </si>
+  <si>
+    <t>JACC</t>
+  </si>
+  <si>
+    <t>JMS</t>
+  </si>
+  <si>
+    <t>JPA</t>
+  </si>
+  <si>
+    <t>JTA</t>
+  </si>
+  <si>
+    <t>JBatch</t>
+  </si>
+  <si>
+    <t>JCA</t>
+  </si>
+  <si>
+    <t>JAF</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t>EJB</t>
+  </si>
+  <si>
+    <t>JAXB</t>
+  </si>
+  <si>
+    <t>JSON-B</t>
+  </si>
+  <si>
+    <t>JSON-P</t>
+  </si>
+  <si>
+    <t>JSP</t>
+  </si>
+  <si>
+    <t>JAX-WS</t>
+  </si>
+  <si>
+    <t>JAX-RS</t>
+  </si>
+  <si>
+    <t>JSTL</t>
+  </si>
+  <si>
+    <t>CDI</t>
+  </si>
+  <si>
+    <t>Jakarta EE仕様</t>
+    <rPh sb="10" eb="12">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>特に断りがない限り、本書に登場する省略名は、以下のようにJakarta EEの仕様を指すものとする。</t>
+    <rPh sb="39" eb="41">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>JAX-RS BeanValidationハンドラ</t>
+  </si>
+  <si>
+    <t>JAX-RSアダプタ</t>
+  </si>
+  <si>
+    <t>Jakarta RESTful Web Servicesアダプタ</t>
+  </si>
+  <si>
+    <t>JAX-RSサポート</t>
+  </si>
+  <si>
+    <t>Jakarta RESTful Web Servicesサポート</t>
+  </si>
+  <si>
+    <t>JAX-RSレスポンスハンドラ</t>
+  </si>
+  <si>
+    <t>Jakarta RESTful Web Servicesレスポンスハンドラ</t>
+  </si>
+  <si>
+    <t>JSPカスタムタグ</t>
+  </si>
+  <si>
+    <t>Jakarta Server Pagesカスタムタグ</t>
+  </si>
+  <si>
+    <t>JSP静的解析ツール</t>
+  </si>
+  <si>
+    <t>Jakarta Server Pages静的解析ツール</t>
+  </si>
+  <si>
+    <t>JSR352に準拠したバッチアプリケーション</t>
+  </si>
+  <si>
+    <t>Jakarta Batchに準拠したバッチアプリケーション</t>
+  </si>
+  <si>
+    <t>Jakarta RESTful Web Servcies Bean Validationハンドラ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Jakarta Faces</t>
+  </si>
+  <si>
+    <t>Jakarta Authentication</t>
+  </si>
+  <si>
+    <t>Jakarta Authorization</t>
+  </si>
+  <si>
+    <t>Jakarta Messaging</t>
+  </si>
+  <si>
+    <t>Jakarta Persistence</t>
+  </si>
+  <si>
+    <t>Jakarta Transactions</t>
+  </si>
+  <si>
+    <t>Jakarta Batch</t>
+  </si>
+  <si>
+    <t>Jakarta Connectors</t>
+  </si>
+  <si>
+    <t>Jakarta Activation</t>
+  </si>
+  <si>
+    <t>Jakarta Expression Language</t>
+  </si>
+  <si>
+    <t>Jakarta Enterprise Beans</t>
+  </si>
+  <si>
+    <t>Jakarta XML Binding</t>
+  </si>
+  <si>
+    <t>Jakarta JSON Binding</t>
+  </si>
+  <si>
+    <t>Jakarta JSON Processing</t>
+  </si>
+  <si>
+    <t>Jakarta Server Pages</t>
+  </si>
+  <si>
+    <t>Jakarta XML Web Services</t>
+  </si>
+  <si>
+    <t>Jakarta RESTful Web Services</t>
+  </si>
+  <si>
+    <t>Jakarta Standard Tag Library</t>
+  </si>
+  <si>
+    <t>Jakarta Contexts and Dependency Injection</t>
+  </si>
+  <si>
+    <t>1.4. Nablarch6を使用する場合の記載の読み替えについて</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>特に断りがない限り、本書に登場するNablarch5までの機能名・Fintanコンテンツ名は、</t>
+    <rPh sb="0" eb="1">
+      <t>トク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コトワ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カギ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ホンショ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>トウジョウ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>キノウメイ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下のようにNablarch6からの機能名・Fintanコンテンツ名を指すものとする。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Nablarch5までの機能名・Fintanコンテンツ名</t>
+    <rPh sb="12" eb="15">
+      <t>キノウメイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Nablarch6からの機能名・Fintanコンテンツ名</t>
+    <rPh sb="12" eb="15">
+      <t>キノウメイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>JSPコーディング規約</t>
+    <rPh sb="9" eb="11">
+      <t>キヤク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Jakarta Server Pagesコーディング規約</t>
+    <rPh sb="26" eb="28">
+      <t>キヤク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>画面イメージはHTMLで作成すること。</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">プログラミング・単体テストガイド
+マスタデータ投入ツール
+SQL自動生成ツール
+HTMLチェックツール
+JSP静的解析ツール
+Java静的解析ツール
+使用不許可APIチェックツール
+リクエスト単体データ作成ツール
+単体テスト標準
+</t>
+    <rPh sb="107" eb="109">
+      <t>タンタイ</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>ヒョウジュン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Nablarch6がJakarta EE 10前提となることに伴い、いくつかの機能名が変更された。</t>
+    <rPh sb="23" eb="25">
+      <t>ゼンテイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>トモナ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>またFintanで提供されるコンテンツもNablarch6前提となることで、コンテンツ名が一部変更された。</t>
+    <rPh sb="29" eb="31">
+      <t>ゼンテイ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -5134,7 +5393,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5300,87 +5559,6 @@
     <xf numFmtId="31" fontId="9" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -5489,11 +5667,86 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -5504,17 +5757,14 @@
     <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -5543,6 +5793,15 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5551,6 +5810,26 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -5609,8 +5888,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7953375" y="285750"/>
-          <a:ext cx="1400175" cy="590550"/>
+          <a:off x="7334250" y="285750"/>
+          <a:ext cx="1276350" cy="590550"/>
           <a:chOff x="591" y="61"/>
           <a:chExt cx="147" cy="62"/>
         </a:xfrm>
@@ -5927,8 +6206,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1035740" y="2776331"/>
-          <a:ext cx="6527524" cy="2745684"/>
+          <a:off x="969065" y="2776331"/>
+          <a:ext cx="5994124" cy="2745684"/>
           <a:chOff x="121" y="113"/>
           <a:chExt cx="729" cy="300"/>
         </a:xfrm>
@@ -6779,55 +7058,55 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S513"/>
-  <sheetFormatPr defaultColWidth="6.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="6.6328125" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="6.625" style="13"/>
+    <col min="1" max="16384" width="6.6328125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="14"/>
       <c r="C1" s="15"/>
     </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
     </row>
-    <row r="3" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="4" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="6" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="8" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="10" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="11" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="12" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="13" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="15" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="16" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="17" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="18" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="19" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="20" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="21" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="22" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F22" s="17"/>
       <c r="H22" s="17"/>
     </row>
-    <row r="23" spans="6:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="6:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
       <c r="J23" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="24" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="24" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F24" s="17"/>
       <c r="G24" s="17"/>
       <c r="H24" s="17"/>
     </row>
-    <row r="25" spans="6:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="6:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F25" s="17"/>
       <c r="G25" s="17"/>
       <c r="H25" s="17"/>
@@ -6838,42 +7117,42 @@
       <c r="J25" s="64"/>
       <c r="K25" s="64"/>
     </row>
-    <row r="26" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
       <c r="H26" s="17"/>
     </row>
-    <row r="27" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
     </row>
-    <row r="28" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F28" s="18"/>
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
     </row>
-    <row r="29" spans="6:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="6:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F29" s="17"/>
       <c r="H29" s="17"/>
     </row>
-    <row r="30" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F30" s="17"/>
       <c r="G30" s="19"/>
       <c r="H30" s="17"/>
     </row>
-    <row r="31" spans="6:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="6:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F31" s="17"/>
       <c r="G31" s="19"/>
       <c r="H31" s="17"/>
     </row>
-    <row r="32" spans="6:11" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="6:11" ht="19" x14ac:dyDescent="0.3">
       <c r="F32" s="17"/>
       <c r="G32" s="19"/>
       <c r="H32" s="17"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="6:19" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="6:19" ht="19" x14ac:dyDescent="0.3">
       <c r="F33" s="17"/>
       <c r="H33" s="17"/>
       <c r="J33" s="21"/>
@@ -6883,7 +7162,7 @@
       <c r="O33" s="21"/>
       <c r="P33" s="21"/>
     </row>
-    <row r="34" spans="6:19" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="6:19" ht="19" x14ac:dyDescent="0.3">
       <c r="F34" s="17"/>
       <c r="H34" s="17"/>
       <c r="J34" s="20"/>
@@ -6896,515 +7175,515 @@
       <c r="R34" s="23"/>
       <c r="S34" s="23"/>
     </row>
-    <row r="35" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O35" s="21"/>
       <c r="P35" s="21"/>
       <c r="Q35" s="23"/>
       <c r="R35" s="23"/>
       <c r="S35" s="23"/>
     </row>
-    <row r="36" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O36" s="24"/>
       <c r="P36" s="23"/>
       <c r="Q36" s="24"/>
       <c r="R36" s="23"/>
       <c r="S36" s="24"/>
     </row>
-    <row r="37" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O37" s="25"/>
       <c r="P37" s="25"/>
       <c r="Q37" s="25"/>
       <c r="R37" s="26"/>
       <c r="S37" s="25"/>
     </row>
-    <row r="38" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O38" s="25"/>
       <c r="P38" s="25"/>
       <c r="Q38" s="26"/>
       <c r="R38" s="26"/>
       <c r="S38" s="26"/>
     </row>
-    <row r="39" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O39" s="25"/>
       <c r="P39" s="25"/>
       <c r="Q39" s="26"/>
       <c r="R39" s="26"/>
       <c r="S39" s="26"/>
     </row>
-    <row r="40" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="46" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="47" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I25:K25"/>
@@ -7424,164 +7703,164 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN34"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="11" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="3.625" style="30"/>
+    <col min="1" max="16384" width="3.6328125" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="98" t="s">
-        <v>281</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="107" t="s">
+    <row r="1" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="71" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="80" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="116" t="s">
-        <v>293</v>
-      </c>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="118"/>
-      <c r="AA1" s="98" t="s">
-        <v>282</v>
-      </c>
-      <c r="AB1" s="100"/>
-      <c r="AC1" s="125" t="str">
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="89" t="s">
+        <v>291</v>
+      </c>
+      <c r="T1" s="90"/>
+      <c r="U1" s="90"/>
+      <c r="V1" s="90"/>
+      <c r="W1" s="90"/>
+      <c r="X1" s="90"/>
+      <c r="Y1" s="90"/>
+      <c r="Z1" s="91"/>
+      <c r="AA1" s="71" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="98" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="126"/>
-      <c r="AE1" s="126"/>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="92">
+      <c r="AD1" s="99"/>
+      <c r="AE1" s="99"/>
+      <c r="AF1" s="100"/>
+      <c r="AG1" s="65">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="93"/>
-      <c r="AI1" s="94"/>
+      <c r="AH1" s="66"/>
+      <c r="AI1" s="67"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
       <c r="AN1" s="3"/>
     </row>
-    <row r="2" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="98" t="s">
-        <v>283</v>
-      </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="110"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="120"/>
-      <c r="Y2" s="120"/>
-      <c r="Z2" s="121"/>
-      <c r="AA2" s="98" t="s">
-        <v>284</v>
-      </c>
-      <c r="AB2" s="100"/>
-      <c r="AC2" s="104" t="str">
+    <row r="2" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="85"/>
+      <c r="S2" s="92"/>
+      <c r="T2" s="93"/>
+      <c r="U2" s="93"/>
+      <c r="V2" s="93"/>
+      <c r="W2" s="93"/>
+      <c r="X2" s="93"/>
+      <c r="Y2" s="93"/>
+      <c r="Z2" s="94"/>
+      <c r="AA2" s="71" t="s">
+        <v>282</v>
+      </c>
+      <c r="AB2" s="73"/>
+      <c r="AC2" s="77" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="105"/>
-      <c r="AE2" s="105"/>
-      <c r="AF2" s="106"/>
-      <c r="AG2" s="92">
+      <c r="AD2" s="78"/>
+      <c r="AE2" s="78"/>
+      <c r="AF2" s="79"/>
+      <c r="AG2" s="65">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44455</v>
       </c>
-      <c r="AH2" s="93"/>
-      <c r="AI2" s="94"/>
+      <c r="AH2" s="66"/>
+      <c r="AI2" s="67"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
     </row>
-    <row r="3" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="98" t="s">
-        <v>285</v>
-      </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="113"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
-      <c r="R3" s="115"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="123"/>
-      <c r="U3" s="123"/>
-      <c r="V3" s="123"/>
-      <c r="W3" s="123"/>
-      <c r="X3" s="123"/>
-      <c r="Y3" s="123"/>
-      <c r="Z3" s="124"/>
-      <c r="AA3" s="98"/>
-      <c r="AB3" s="100"/>
-      <c r="AC3" s="125"/>
-      <c r="AD3" s="126"/>
-      <c r="AE3" s="126"/>
-      <c r="AF3" s="127"/>
-      <c r="AG3" s="92"/>
-      <c r="AH3" s="93"/>
-      <c r="AI3" s="94"/>
+    <row r="3" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="71" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="75"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="87"/>
+      <c r="Q3" s="87"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="95"/>
+      <c r="T3" s="96"/>
+      <c r="U3" s="96"/>
+      <c r="V3" s="96"/>
+      <c r="W3" s="96"/>
+      <c r="X3" s="96"/>
+      <c r="Y3" s="96"/>
+      <c r="Z3" s="97"/>
+      <c r="AA3" s="71"/>
+      <c r="AB3" s="73"/>
+      <c r="AC3" s="98"/>
+      <c r="AD3" s="99"/>
+      <c r="AE3" s="99"/>
+      <c r="AF3" s="100"/>
+      <c r="AG3" s="65"/>
+      <c r="AH3" s="66"/>
+      <c r="AI3" s="67"/>
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
       <c r="AM3" s="2"/>
       <c r="AN3" s="2"/>
     </row>
-    <row r="5" spans="1:40" s="4" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" s="4" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N5" s="5" t="s">
         <v>183</v>
       </c>
@@ -7595,7 +7874,7 @@
       <c r="AH5" s="6"/>
       <c r="AI5" s="6"/>
     </row>
-    <row r="6" spans="1:40" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N6" s="5"/>
       <c r="AA6" s="6"/>
       <c r="AB6" s="6"/>
@@ -7607,1066 +7886,1222 @@
       <c r="AH6" s="6"/>
       <c r="AI6" s="6"/>
     </row>
-    <row r="7" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>286</v>
-      </c>
-      <c r="B7" s="95" t="s">
+        <v>284</v>
+      </c>
+      <c r="B7" s="68" t="s">
         <v>186</v>
       </c>
-      <c r="C7" s="96"/>
-      <c r="D7" s="95" t="s">
+      <c r="C7" s="69"/>
+      <c r="D7" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="E7" s="97"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="95" t="s">
+      <c r="E7" s="70"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="68" t="s">
         <v>188</v>
       </c>
-      <c r="H7" s="97"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="95" t="s">
-        <v>287</v>
-      </c>
-      <c r="K7" s="97"/>
-      <c r="L7" s="97"/>
-      <c r="M7" s="97"/>
-      <c r="N7" s="97"/>
-      <c r="O7" s="97"/>
-      <c r="P7" s="96"/>
-      <c r="Q7" s="95" t="s">
+      <c r="H7" s="70"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="69"/>
+      <c r="Q7" s="68" t="s">
         <v>189</v>
       </c>
-      <c r="R7" s="97"/>
-      <c r="S7" s="97"/>
-      <c r="T7" s="97"/>
-      <c r="U7" s="97"/>
-      <c r="V7" s="97"/>
-      <c r="W7" s="97"/>
-      <c r="X7" s="97"/>
-      <c r="Y7" s="97"/>
-      <c r="Z7" s="97"/>
-      <c r="AA7" s="97"/>
-      <c r="AB7" s="97"/>
-      <c r="AC7" s="97"/>
-      <c r="AD7" s="97"/>
-      <c r="AE7" s="96"/>
-      <c r="AF7" s="95" t="s">
+      <c r="R7" s="70"/>
+      <c r="S7" s="70"/>
+      <c r="T7" s="70"/>
+      <c r="U7" s="70"/>
+      <c r="V7" s="70"/>
+      <c r="W7" s="70"/>
+      <c r="X7" s="70"/>
+      <c r="Y7" s="70"/>
+      <c r="Z7" s="70"/>
+      <c r="AA7" s="70"/>
+      <c r="AB7" s="70"/>
+      <c r="AC7" s="70"/>
+      <c r="AD7" s="70"/>
+      <c r="AE7" s="69"/>
+      <c r="AF7" s="68" t="s">
         <v>190</v>
       </c>
-      <c r="AG7" s="97"/>
-      <c r="AH7" s="97"/>
-      <c r="AI7" s="96"/>
-    </row>
-    <row r="8" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="AG7" s="70"/>
+      <c r="AH7" s="70"/>
+      <c r="AI7" s="69"/>
+    </row>
+    <row r="8" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="113" t="s">
+        <v>286</v>
+      </c>
+      <c r="C8" s="114"/>
+      <c r="D8" s="115">
+        <v>43336</v>
+      </c>
+      <c r="E8" s="116"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="118" t="s">
+        <v>287</v>
+      </c>
+      <c r="H8" s="119"/>
+      <c r="I8" s="120"/>
+      <c r="J8" s="121" t="s">
         <v>288</v>
       </c>
-      <c r="C8" s="79"/>
-      <c r="D8" s="80">
-        <v>43336</v>
-      </c>
-      <c r="E8" s="81"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="83" t="s">
+      <c r="K8" s="122"/>
+      <c r="L8" s="122"/>
+      <c r="M8" s="122"/>
+      <c r="N8" s="122"/>
+      <c r="O8" s="122"/>
+      <c r="P8" s="123"/>
+      <c r="Q8" s="124" t="s">
         <v>289</v>
       </c>
-      <c r="H8" s="84"/>
-      <c r="I8" s="85"/>
-      <c r="J8" s="86" t="s">
+      <c r="R8" s="125"/>
+      <c r="S8" s="125"/>
+      <c r="T8" s="125"/>
+      <c r="U8" s="125"/>
+      <c r="V8" s="125"/>
+      <c r="W8" s="125"/>
+      <c r="X8" s="125"/>
+      <c r="Y8" s="125"/>
+      <c r="Z8" s="125"/>
+      <c r="AA8" s="125"/>
+      <c r="AB8" s="125"/>
+      <c r="AC8" s="125"/>
+      <c r="AD8" s="125"/>
+      <c r="AE8" s="126"/>
+      <c r="AF8" s="121" t="s">
         <v>290</v>
       </c>
-      <c r="K8" s="87"/>
-      <c r="L8" s="87"/>
-      <c r="M8" s="87"/>
-      <c r="N8" s="87"/>
-      <c r="O8" s="87"/>
-      <c r="P8" s="88"/>
-      <c r="Q8" s="89" t="s">
-        <v>291</v>
-      </c>
-      <c r="R8" s="90"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="90"/>
-      <c r="U8" s="90"/>
-      <c r="V8" s="90"/>
-      <c r="W8" s="90"/>
-      <c r="X8" s="90"/>
-      <c r="Y8" s="90"/>
-      <c r="Z8" s="90"/>
-      <c r="AA8" s="90"/>
-      <c r="AB8" s="90"/>
-      <c r="AC8" s="90"/>
-      <c r="AD8" s="90"/>
-      <c r="AE8" s="91"/>
-      <c r="AF8" s="86" t="s">
-        <v>292</v>
-      </c>
-      <c r="AG8" s="87"/>
-      <c r="AH8" s="87"/>
-      <c r="AI8" s="88"/>
-    </row>
-    <row r="9" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AG8" s="122"/>
+      <c r="AH8" s="122"/>
+      <c r="AI8" s="123"/>
+    </row>
+    <row r="9" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="29">
         <v>2</v>
       </c>
-      <c r="B9" s="65" t="s">
-        <v>357</v>
-      </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="67">
+      <c r="B9" s="101" t="s">
+        <v>355</v>
+      </c>
+      <c r="C9" s="102"/>
+      <c r="D9" s="103">
         <v>43896</v>
       </c>
-      <c r="E9" s="68"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="67" t="s">
-        <v>339</v>
-      </c>
-      <c r="H9" s="70"/>
-      <c r="I9" s="66"/>
-      <c r="J9" s="71" t="s">
-        <v>340</v>
-      </c>
-      <c r="K9" s="72"/>
-      <c r="L9" s="72"/>
-      <c r="M9" s="72"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="72"/>
-      <c r="P9" s="73"/>
-      <c r="Q9" s="74" t="s">
-        <v>355</v>
-      </c>
-      <c r="R9" s="75"/>
-      <c r="S9" s="75"/>
-      <c r="T9" s="75"/>
-      <c r="U9" s="75"/>
-      <c r="V9" s="75"/>
-      <c r="W9" s="75"/>
-      <c r="X9" s="75"/>
-      <c r="Y9" s="75"/>
-      <c r="Z9" s="75"/>
-      <c r="AA9" s="75"/>
-      <c r="AB9" s="75"/>
-      <c r="AC9" s="75"/>
-      <c r="AD9" s="75"/>
-      <c r="AE9" s="76"/>
-      <c r="AF9" s="71" t="s">
-        <v>292</v>
-      </c>
-      <c r="AG9" s="72"/>
-      <c r="AH9" s="72"/>
-      <c r="AI9" s="73"/>
-    </row>
-    <row r="10" spans="1:40" s="9" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E9" s="104"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="103" t="s">
+        <v>337</v>
+      </c>
+      <c r="H9" s="106"/>
+      <c r="I9" s="102"/>
+      <c r="J9" s="107" t="s">
+        <v>338</v>
+      </c>
+      <c r="K9" s="108"/>
+      <c r="L9" s="108"/>
+      <c r="M9" s="108"/>
+      <c r="N9" s="108"/>
+      <c r="O9" s="108"/>
+      <c r="P9" s="109"/>
+      <c r="Q9" s="110" t="s">
+        <v>353</v>
+      </c>
+      <c r="R9" s="111"/>
+      <c r="S9" s="111"/>
+      <c r="T9" s="111"/>
+      <c r="U9" s="111"/>
+      <c r="V9" s="111"/>
+      <c r="W9" s="111"/>
+      <c r="X9" s="111"/>
+      <c r="Y9" s="111"/>
+      <c r="Z9" s="111"/>
+      <c r="AA9" s="111"/>
+      <c r="AB9" s="111"/>
+      <c r="AC9" s="111"/>
+      <c r="AD9" s="111"/>
+      <c r="AE9" s="112"/>
+      <c r="AF9" s="107" t="s">
+        <v>290</v>
+      </c>
+      <c r="AG9" s="108"/>
+      <c r="AH9" s="108"/>
+      <c r="AI9" s="109"/>
+    </row>
+    <row r="10" spans="1:40" s="9" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="29">
         <v>3</v>
       </c>
-      <c r="B10" s="65" t="s">
-        <v>358</v>
-      </c>
-      <c r="C10" s="66"/>
-      <c r="D10" s="67">
+      <c r="B10" s="101" t="s">
+        <v>356</v>
+      </c>
+      <c r="C10" s="102"/>
+      <c r="D10" s="103">
         <v>44455</v>
       </c>
-      <c r="E10" s="68"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="67" t="s">
-        <v>339</v>
-      </c>
-      <c r="H10" s="70"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="71" t="s">
-        <v>340</v>
-      </c>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="73"/>
-      <c r="Q10" s="74" t="s">
-        <v>359</v>
-      </c>
-      <c r="R10" s="75"/>
-      <c r="S10" s="75"/>
-      <c r="T10" s="75"/>
-      <c r="U10" s="75"/>
-      <c r="V10" s="75"/>
-      <c r="W10" s="75"/>
-      <c r="X10" s="75"/>
-      <c r="Y10" s="75"/>
-      <c r="Z10" s="75"/>
-      <c r="AA10" s="75"/>
-      <c r="AB10" s="75"/>
-      <c r="AC10" s="75"/>
-      <c r="AD10" s="75"/>
-      <c r="AE10" s="76"/>
-      <c r="AF10" s="71" t="s">
-        <v>292</v>
-      </c>
-      <c r="AG10" s="72"/>
-      <c r="AH10" s="72"/>
-      <c r="AI10" s="73"/>
-    </row>
-    <row r="11" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E10" s="104"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="103" t="s">
+        <v>337</v>
+      </c>
+      <c r="H10" s="106"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="107" t="s">
+        <v>338</v>
+      </c>
+      <c r="K10" s="108"/>
+      <c r="L10" s="108"/>
+      <c r="M10" s="108"/>
+      <c r="N10" s="108"/>
+      <c r="O10" s="108"/>
+      <c r="P10" s="109"/>
+      <c r="Q10" s="110" t="s">
+        <v>357</v>
+      </c>
+      <c r="R10" s="111"/>
+      <c r="S10" s="111"/>
+      <c r="T10" s="111"/>
+      <c r="U10" s="111"/>
+      <c r="V10" s="111"/>
+      <c r="W10" s="111"/>
+      <c r="X10" s="111"/>
+      <c r="Y10" s="111"/>
+      <c r="Z10" s="111"/>
+      <c r="AA10" s="111"/>
+      <c r="AB10" s="111"/>
+      <c r="AC10" s="111"/>
+      <c r="AD10" s="111"/>
+      <c r="AE10" s="112"/>
+      <c r="AF10" s="107" t="s">
+        <v>290</v>
+      </c>
+      <c r="AG10" s="108"/>
+      <c r="AH10" s="108"/>
+      <c r="AI10" s="109"/>
+    </row>
+    <row r="11" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="29"/>
-      <c r="B11" s="65"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="73"/>
-      <c r="Q11" s="74"/>
-      <c r="R11" s="75"/>
-      <c r="S11" s="75"/>
-      <c r="T11" s="75"/>
-      <c r="U11" s="75"/>
-      <c r="V11" s="75"/>
-      <c r="W11" s="75"/>
-      <c r="X11" s="75"/>
-      <c r="Y11" s="75"/>
-      <c r="Z11" s="75"/>
-      <c r="AA11" s="75"/>
-      <c r="AB11" s="75"/>
-      <c r="AC11" s="75"/>
-      <c r="AD11" s="75"/>
-      <c r="AE11" s="76"/>
-      <c r="AF11" s="71"/>
-      <c r="AG11" s="72"/>
-      <c r="AH11" s="72"/>
-      <c r="AI11" s="73"/>
-    </row>
-    <row r="12" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="101"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="107"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="108"/>
+      <c r="M11" s="108"/>
+      <c r="N11" s="108"/>
+      <c r="O11" s="108"/>
+      <c r="P11" s="109"/>
+      <c r="Q11" s="110"/>
+      <c r="R11" s="111"/>
+      <c r="S11" s="111"/>
+      <c r="T11" s="111"/>
+      <c r="U11" s="111"/>
+      <c r="V11" s="111"/>
+      <c r="W11" s="111"/>
+      <c r="X11" s="111"/>
+      <c r="Y11" s="111"/>
+      <c r="Z11" s="111"/>
+      <c r="AA11" s="111"/>
+      <c r="AB11" s="111"/>
+      <c r="AC11" s="111"/>
+      <c r="AD11" s="111"/>
+      <c r="AE11" s="112"/>
+      <c r="AF11" s="107"/>
+      <c r="AG11" s="108"/>
+      <c r="AH11" s="108"/>
+      <c r="AI11" s="109"/>
+    </row>
+    <row r="12" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="29"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="66"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="P12" s="73"/>
-      <c r="Q12" s="74"/>
-      <c r="R12" s="75"/>
-      <c r="S12" s="75"/>
-      <c r="T12" s="75"/>
-      <c r="U12" s="75"/>
-      <c r="V12" s="75"/>
-      <c r="W12" s="75"/>
-      <c r="X12" s="75"/>
-      <c r="Y12" s="75"/>
-      <c r="Z12" s="75"/>
-      <c r="AA12" s="75"/>
-      <c r="AB12" s="75"/>
-      <c r="AC12" s="75"/>
-      <c r="AD12" s="75"/>
-      <c r="AE12" s="76"/>
-      <c r="AF12" s="71"/>
-      <c r="AG12" s="72"/>
-      <c r="AH12" s="72"/>
-      <c r="AI12" s="73"/>
-    </row>
-    <row r="13" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="101"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="106"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="107"/>
+      <c r="K12" s="108"/>
+      <c r="L12" s="108"/>
+      <c r="M12" s="108"/>
+      <c r="N12" s="108"/>
+      <c r="O12" s="108"/>
+      <c r="P12" s="109"/>
+      <c r="Q12" s="110"/>
+      <c r="R12" s="111"/>
+      <c r="S12" s="111"/>
+      <c r="T12" s="111"/>
+      <c r="U12" s="111"/>
+      <c r="V12" s="111"/>
+      <c r="W12" s="111"/>
+      <c r="X12" s="111"/>
+      <c r="Y12" s="111"/>
+      <c r="Z12" s="111"/>
+      <c r="AA12" s="111"/>
+      <c r="AB12" s="111"/>
+      <c r="AC12" s="111"/>
+      <c r="AD12" s="111"/>
+      <c r="AE12" s="112"/>
+      <c r="AF12" s="107"/>
+      <c r="AG12" s="108"/>
+      <c r="AH12" s="108"/>
+      <c r="AI12" s="109"/>
+    </row>
+    <row r="13" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="29"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="72"/>
-      <c r="M13" s="72"/>
-      <c r="N13" s="72"/>
-      <c r="O13" s="72"/>
-      <c r="P13" s="73"/>
-      <c r="Q13" s="74"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="75"/>
-      <c r="U13" s="75"/>
-      <c r="V13" s="75"/>
-      <c r="W13" s="75"/>
-      <c r="X13" s="75"/>
-      <c r="Y13" s="75"/>
-      <c r="Z13" s="75"/>
-      <c r="AA13" s="75"/>
-      <c r="AB13" s="75"/>
-      <c r="AC13" s="75"/>
-      <c r="AD13" s="75"/>
-      <c r="AE13" s="76"/>
-      <c r="AF13" s="71"/>
-      <c r="AG13" s="72"/>
-      <c r="AH13" s="72"/>
-      <c r="AI13" s="73"/>
-    </row>
-    <row r="14" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="101"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="107"/>
+      <c r="K13" s="108"/>
+      <c r="L13" s="108"/>
+      <c r="M13" s="108"/>
+      <c r="N13" s="108"/>
+      <c r="O13" s="108"/>
+      <c r="P13" s="109"/>
+      <c r="Q13" s="110"/>
+      <c r="R13" s="111"/>
+      <c r="S13" s="111"/>
+      <c r="T13" s="111"/>
+      <c r="U13" s="111"/>
+      <c r="V13" s="111"/>
+      <c r="W13" s="111"/>
+      <c r="X13" s="111"/>
+      <c r="Y13" s="111"/>
+      <c r="Z13" s="111"/>
+      <c r="AA13" s="111"/>
+      <c r="AB13" s="111"/>
+      <c r="AC13" s="111"/>
+      <c r="AD13" s="111"/>
+      <c r="AE13" s="112"/>
+      <c r="AF13" s="107"/>
+      <c r="AG13" s="108"/>
+      <c r="AH13" s="108"/>
+      <c r="AI13" s="109"/>
+    </row>
+    <row r="14" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="29"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="72"/>
-      <c r="M14" s="72"/>
-      <c r="N14" s="72"/>
-      <c r="O14" s="72"/>
-      <c r="P14" s="73"/>
-      <c r="Q14" s="74"/>
-      <c r="R14" s="75"/>
-      <c r="S14" s="75"/>
-      <c r="T14" s="75"/>
-      <c r="U14" s="75"/>
-      <c r="V14" s="75"/>
-      <c r="W14" s="75"/>
-      <c r="X14" s="75"/>
-      <c r="Y14" s="75"/>
-      <c r="Z14" s="75"/>
-      <c r="AA14" s="75"/>
-      <c r="AB14" s="75"/>
-      <c r="AC14" s="75"/>
-      <c r="AD14" s="75"/>
-      <c r="AE14" s="76"/>
-      <c r="AF14" s="71"/>
-      <c r="AG14" s="72"/>
-      <c r="AH14" s="72"/>
-      <c r="AI14" s="73"/>
-    </row>
-    <row r="15" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="101"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="106"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="107"/>
+      <c r="K14" s="108"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="108"/>
+      <c r="N14" s="108"/>
+      <c r="O14" s="108"/>
+      <c r="P14" s="109"/>
+      <c r="Q14" s="110"/>
+      <c r="R14" s="111"/>
+      <c r="S14" s="111"/>
+      <c r="T14" s="111"/>
+      <c r="U14" s="111"/>
+      <c r="V14" s="111"/>
+      <c r="W14" s="111"/>
+      <c r="X14" s="111"/>
+      <c r="Y14" s="111"/>
+      <c r="Z14" s="111"/>
+      <c r="AA14" s="111"/>
+      <c r="AB14" s="111"/>
+      <c r="AC14" s="111"/>
+      <c r="AD14" s="111"/>
+      <c r="AE14" s="112"/>
+      <c r="AF14" s="107"/>
+      <c r="AG14" s="108"/>
+      <c r="AH14" s="108"/>
+      <c r="AI14" s="109"/>
+    </row>
+    <row r="15" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="29"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="72"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="72"/>
-      <c r="P15" s="73"/>
-      <c r="Q15" s="74"/>
-      <c r="R15" s="75"/>
-      <c r="S15" s="75"/>
-      <c r="T15" s="75"/>
-      <c r="U15" s="75"/>
-      <c r="V15" s="75"/>
-      <c r="W15" s="75"/>
-      <c r="X15" s="75"/>
-      <c r="Y15" s="75"/>
-      <c r="Z15" s="75"/>
-      <c r="AA15" s="75"/>
-      <c r="AB15" s="75"/>
-      <c r="AC15" s="75"/>
-      <c r="AD15" s="75"/>
-      <c r="AE15" s="76"/>
-      <c r="AF15" s="71"/>
-      <c r="AG15" s="72"/>
-      <c r="AH15" s="72"/>
-      <c r="AI15" s="73"/>
-    </row>
-    <row r="16" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="101"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="101"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="107"/>
+      <c r="K15" s="108"/>
+      <c r="L15" s="108"/>
+      <c r="M15" s="108"/>
+      <c r="N15" s="108"/>
+      <c r="O15" s="108"/>
+      <c r="P15" s="109"/>
+      <c r="Q15" s="110"/>
+      <c r="R15" s="111"/>
+      <c r="S15" s="111"/>
+      <c r="T15" s="111"/>
+      <c r="U15" s="111"/>
+      <c r="V15" s="111"/>
+      <c r="W15" s="111"/>
+      <c r="X15" s="111"/>
+      <c r="Y15" s="111"/>
+      <c r="Z15" s="111"/>
+      <c r="AA15" s="111"/>
+      <c r="AB15" s="111"/>
+      <c r="AC15" s="111"/>
+      <c r="AD15" s="111"/>
+      <c r="AE15" s="112"/>
+      <c r="AF15" s="107"/>
+      <c r="AG15" s="108"/>
+      <c r="AH15" s="108"/>
+      <c r="AI15" s="109"/>
+    </row>
+    <row r="16" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="29"/>
-      <c r="B16" s="65"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="72"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="72"/>
-      <c r="N16" s="72"/>
-      <c r="O16" s="72"/>
-      <c r="P16" s="73"/>
-      <c r="Q16" s="74"/>
-      <c r="R16" s="75"/>
-      <c r="S16" s="75"/>
-      <c r="T16" s="75"/>
-      <c r="U16" s="75"/>
-      <c r="V16" s="75"/>
-      <c r="W16" s="75"/>
-      <c r="X16" s="75"/>
-      <c r="Y16" s="75"/>
-      <c r="Z16" s="75"/>
-      <c r="AA16" s="75"/>
-      <c r="AB16" s="75"/>
-      <c r="AC16" s="75"/>
-      <c r="AD16" s="75"/>
-      <c r="AE16" s="76"/>
-      <c r="AF16" s="71"/>
-      <c r="AG16" s="72"/>
-      <c r="AH16" s="72"/>
-      <c r="AI16" s="73"/>
-    </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="101"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="104"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="101"/>
+      <c r="H16" s="106"/>
+      <c r="I16" s="102"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="108"/>
+      <c r="O16" s="108"/>
+      <c r="P16" s="109"/>
+      <c r="Q16" s="110"/>
+      <c r="R16" s="111"/>
+      <c r="S16" s="111"/>
+      <c r="T16" s="111"/>
+      <c r="U16" s="111"/>
+      <c r="V16" s="111"/>
+      <c r="W16" s="111"/>
+      <c r="X16" s="111"/>
+      <c r="Y16" s="111"/>
+      <c r="Z16" s="111"/>
+      <c r="AA16" s="111"/>
+      <c r="AB16" s="111"/>
+      <c r="AC16" s="111"/>
+      <c r="AD16" s="111"/>
+      <c r="AE16" s="112"/>
+      <c r="AF16" s="107"/>
+      <c r="AG16" s="108"/>
+      <c r="AH16" s="108"/>
+      <c r="AI16" s="109"/>
+    </row>
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="29"/>
-      <c r="B17" s="65"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="72"/>
-      <c r="L17" s="72"/>
-      <c r="M17" s="72"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="72"/>
-      <c r="P17" s="73"/>
-      <c r="Q17" s="74"/>
-      <c r="R17" s="75"/>
-      <c r="S17" s="75"/>
-      <c r="T17" s="75"/>
-      <c r="U17" s="75"/>
-      <c r="V17" s="75"/>
-      <c r="W17" s="75"/>
-      <c r="X17" s="75"/>
-      <c r="Y17" s="75"/>
-      <c r="Z17" s="75"/>
-      <c r="AA17" s="75"/>
-      <c r="AB17" s="75"/>
-      <c r="AC17" s="75"/>
-      <c r="AD17" s="75"/>
-      <c r="AE17" s="76"/>
-      <c r="AF17" s="71"/>
-      <c r="AG17" s="72"/>
-      <c r="AH17" s="72"/>
-      <c r="AI17" s="73"/>
-    </row>
-    <row r="18" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="101"/>
+      <c r="C17" s="102"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="101"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="107"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="108"/>
+      <c r="M17" s="108"/>
+      <c r="N17" s="108"/>
+      <c r="O17" s="108"/>
+      <c r="P17" s="109"/>
+      <c r="Q17" s="110"/>
+      <c r="R17" s="111"/>
+      <c r="S17" s="111"/>
+      <c r="T17" s="111"/>
+      <c r="U17" s="111"/>
+      <c r="V17" s="111"/>
+      <c r="W17" s="111"/>
+      <c r="X17" s="111"/>
+      <c r="Y17" s="111"/>
+      <c r="Z17" s="111"/>
+      <c r="AA17" s="111"/>
+      <c r="AB17" s="111"/>
+      <c r="AC17" s="111"/>
+      <c r="AD17" s="111"/>
+      <c r="AE17" s="112"/>
+      <c r="AF17" s="107"/>
+      <c r="AG17" s="108"/>
+      <c r="AH17" s="108"/>
+      <c r="AI17" s="109"/>
+    </row>
+    <row r="18" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="29"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="72"/>
-      <c r="L18" s="72"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="72"/>
-      <c r="O18" s="72"/>
-      <c r="P18" s="73"/>
-      <c r="Q18" s="74"/>
-      <c r="R18" s="75"/>
-      <c r="S18" s="75"/>
-      <c r="T18" s="75"/>
-      <c r="U18" s="75"/>
-      <c r="V18" s="75"/>
-      <c r="W18" s="75"/>
-      <c r="X18" s="75"/>
-      <c r="Y18" s="75"/>
-      <c r="Z18" s="75"/>
-      <c r="AA18" s="75"/>
-      <c r="AB18" s="75"/>
-      <c r="AC18" s="75"/>
-      <c r="AD18" s="75"/>
-      <c r="AE18" s="76"/>
-      <c r="AF18" s="71"/>
-      <c r="AG18" s="72"/>
-      <c r="AH18" s="72"/>
-      <c r="AI18" s="73"/>
-    </row>
-    <row r="19" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="101"/>
+      <c r="C18" s="102"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="101"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="102"/>
+      <c r="J18" s="107"/>
+      <c r="K18" s="108"/>
+      <c r="L18" s="108"/>
+      <c r="M18" s="108"/>
+      <c r="N18" s="108"/>
+      <c r="O18" s="108"/>
+      <c r="P18" s="109"/>
+      <c r="Q18" s="110"/>
+      <c r="R18" s="111"/>
+      <c r="S18" s="111"/>
+      <c r="T18" s="111"/>
+      <c r="U18" s="111"/>
+      <c r="V18" s="111"/>
+      <c r="W18" s="111"/>
+      <c r="X18" s="111"/>
+      <c r="Y18" s="111"/>
+      <c r="Z18" s="111"/>
+      <c r="AA18" s="111"/>
+      <c r="AB18" s="111"/>
+      <c r="AC18" s="111"/>
+      <c r="AD18" s="111"/>
+      <c r="AE18" s="112"/>
+      <c r="AF18" s="107"/>
+      <c r="AG18" s="108"/>
+      <c r="AH18" s="108"/>
+      <c r="AI18" s="109"/>
+    </row>
+    <row r="19" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="29"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="72"/>
-      <c r="L19" s="72"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="72"/>
-      <c r="O19" s="72"/>
-      <c r="P19" s="73"/>
-      <c r="Q19" s="74"/>
-      <c r="R19" s="75"/>
-      <c r="S19" s="75"/>
-      <c r="T19" s="75"/>
-      <c r="U19" s="75"/>
-      <c r="V19" s="75"/>
-      <c r="W19" s="75"/>
-      <c r="X19" s="75"/>
-      <c r="Y19" s="75"/>
-      <c r="Z19" s="75"/>
-      <c r="AA19" s="75"/>
-      <c r="AB19" s="75"/>
-      <c r="AC19" s="75"/>
-      <c r="AD19" s="75"/>
-      <c r="AE19" s="76"/>
-      <c r="AF19" s="71"/>
-      <c r="AG19" s="72"/>
-      <c r="AH19" s="72"/>
-      <c r="AI19" s="73"/>
-    </row>
-    <row r="20" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="101"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="101"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="107"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="108"/>
+      <c r="M19" s="108"/>
+      <c r="N19" s="108"/>
+      <c r="O19" s="108"/>
+      <c r="P19" s="109"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="111"/>
+      <c r="S19" s="111"/>
+      <c r="T19" s="111"/>
+      <c r="U19" s="111"/>
+      <c r="V19" s="111"/>
+      <c r="W19" s="111"/>
+      <c r="X19" s="111"/>
+      <c r="Y19" s="111"/>
+      <c r="Z19" s="111"/>
+      <c r="AA19" s="111"/>
+      <c r="AB19" s="111"/>
+      <c r="AC19" s="111"/>
+      <c r="AD19" s="111"/>
+      <c r="AE19" s="112"/>
+      <c r="AF19" s="107"/>
+      <c r="AG19" s="108"/>
+      <c r="AH19" s="108"/>
+      <c r="AI19" s="109"/>
+    </row>
+    <row r="20" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="29"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="66"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="72"/>
-      <c r="L20" s="72"/>
-      <c r="M20" s="72"/>
-      <c r="N20" s="72"/>
-      <c r="O20" s="72"/>
-      <c r="P20" s="73"/>
-      <c r="Q20" s="74"/>
-      <c r="R20" s="75"/>
-      <c r="S20" s="75"/>
-      <c r="T20" s="75"/>
-      <c r="U20" s="75"/>
-      <c r="V20" s="75"/>
-      <c r="W20" s="75"/>
-      <c r="X20" s="75"/>
-      <c r="Y20" s="75"/>
-      <c r="Z20" s="75"/>
-      <c r="AA20" s="75"/>
-      <c r="AB20" s="75"/>
-      <c r="AC20" s="75"/>
-      <c r="AD20" s="75"/>
-      <c r="AE20" s="76"/>
-      <c r="AF20" s="71"/>
-      <c r="AG20" s="72"/>
-      <c r="AH20" s="72"/>
-      <c r="AI20" s="73"/>
-    </row>
-    <row r="21" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="101"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="103"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="101"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="107"/>
+      <c r="K20" s="108"/>
+      <c r="L20" s="108"/>
+      <c r="M20" s="108"/>
+      <c r="N20" s="108"/>
+      <c r="O20" s="108"/>
+      <c r="P20" s="109"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="111"/>
+      <c r="S20" s="111"/>
+      <c r="T20" s="111"/>
+      <c r="U20" s="111"/>
+      <c r="V20" s="111"/>
+      <c r="W20" s="111"/>
+      <c r="X20" s="111"/>
+      <c r="Y20" s="111"/>
+      <c r="Z20" s="111"/>
+      <c r="AA20" s="111"/>
+      <c r="AB20" s="111"/>
+      <c r="AC20" s="111"/>
+      <c r="AD20" s="111"/>
+      <c r="AE20" s="112"/>
+      <c r="AF20" s="107"/>
+      <c r="AG20" s="108"/>
+      <c r="AH20" s="108"/>
+      <c r="AI20" s="109"/>
+    </row>
+    <row r="21" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="29"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="72"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="72"/>
-      <c r="P21" s="73"/>
-      <c r="Q21" s="74"/>
-      <c r="R21" s="75"/>
-      <c r="S21" s="75"/>
-      <c r="T21" s="75"/>
-      <c r="U21" s="75"/>
-      <c r="V21" s="75"/>
-      <c r="W21" s="75"/>
-      <c r="X21" s="75"/>
-      <c r="Y21" s="75"/>
-      <c r="Z21" s="75"/>
-      <c r="AA21" s="75"/>
-      <c r="AB21" s="75"/>
-      <c r="AC21" s="75"/>
-      <c r="AD21" s="75"/>
-      <c r="AE21" s="76"/>
-      <c r="AF21" s="71"/>
-      <c r="AG21" s="72"/>
-      <c r="AH21" s="72"/>
-      <c r="AI21" s="73"/>
-    </row>
-    <row r="22" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="101"/>
+      <c r="C21" s="102"/>
+      <c r="D21" s="103"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="102"/>
+      <c r="J21" s="107"/>
+      <c r="K21" s="108"/>
+      <c r="L21" s="108"/>
+      <c r="M21" s="108"/>
+      <c r="N21" s="108"/>
+      <c r="O21" s="108"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="110"/>
+      <c r="R21" s="111"/>
+      <c r="S21" s="111"/>
+      <c r="T21" s="111"/>
+      <c r="U21" s="111"/>
+      <c r="V21" s="111"/>
+      <c r="W21" s="111"/>
+      <c r="X21" s="111"/>
+      <c r="Y21" s="111"/>
+      <c r="Z21" s="111"/>
+      <c r="AA21" s="111"/>
+      <c r="AB21" s="111"/>
+      <c r="AC21" s="111"/>
+      <c r="AD21" s="111"/>
+      <c r="AE21" s="112"/>
+      <c r="AF21" s="107"/>
+      <c r="AG21" s="108"/>
+      <c r="AH21" s="108"/>
+      <c r="AI21" s="109"/>
+    </row>
+    <row r="22" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="29"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="72"/>
-      <c r="P22" s="73"/>
-      <c r="Q22" s="74"/>
-      <c r="R22" s="75"/>
-      <c r="S22" s="75"/>
-      <c r="T22" s="75"/>
-      <c r="U22" s="75"/>
-      <c r="V22" s="75"/>
-      <c r="W22" s="75"/>
-      <c r="X22" s="75"/>
-      <c r="Y22" s="75"/>
-      <c r="Z22" s="75"/>
-      <c r="AA22" s="75"/>
-      <c r="AB22" s="75"/>
-      <c r="AC22" s="75"/>
-      <c r="AD22" s="75"/>
-      <c r="AE22" s="76"/>
-      <c r="AF22" s="71"/>
-      <c r="AG22" s="72"/>
-      <c r="AH22" s="72"/>
-      <c r="AI22" s="73"/>
-    </row>
-    <row r="23" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="101"/>
+      <c r="C22" s="102"/>
+      <c r="D22" s="103"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="101"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="102"/>
+      <c r="J22" s="107"/>
+      <c r="K22" s="108"/>
+      <c r="L22" s="108"/>
+      <c r="M22" s="108"/>
+      <c r="N22" s="108"/>
+      <c r="O22" s="108"/>
+      <c r="P22" s="109"/>
+      <c r="Q22" s="110"/>
+      <c r="R22" s="111"/>
+      <c r="S22" s="111"/>
+      <c r="T22" s="111"/>
+      <c r="U22" s="111"/>
+      <c r="V22" s="111"/>
+      <c r="W22" s="111"/>
+      <c r="X22" s="111"/>
+      <c r="Y22" s="111"/>
+      <c r="Z22" s="111"/>
+      <c r="AA22" s="111"/>
+      <c r="AB22" s="111"/>
+      <c r="AC22" s="111"/>
+      <c r="AD22" s="111"/>
+      <c r="AE22" s="112"/>
+      <c r="AF22" s="107"/>
+      <c r="AG22" s="108"/>
+      <c r="AH22" s="108"/>
+      <c r="AI22" s="109"/>
+    </row>
+    <row r="23" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="29"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="71"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="72"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="72"/>
-      <c r="P23" s="73"/>
-      <c r="Q23" s="74"/>
-      <c r="R23" s="75"/>
-      <c r="S23" s="75"/>
-      <c r="T23" s="75"/>
-      <c r="U23" s="75"/>
-      <c r="V23" s="75"/>
-      <c r="W23" s="75"/>
-      <c r="X23" s="75"/>
-      <c r="Y23" s="75"/>
-      <c r="Z23" s="75"/>
-      <c r="AA23" s="75"/>
-      <c r="AB23" s="75"/>
-      <c r="AC23" s="75"/>
-      <c r="AD23" s="75"/>
-      <c r="AE23" s="76"/>
-      <c r="AF23" s="71"/>
-      <c r="AG23" s="72"/>
-      <c r="AH23" s="72"/>
-      <c r="AI23" s="73"/>
-    </row>
-    <row r="24" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="101"/>
+      <c r="C23" s="102"/>
+      <c r="D23" s="103"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="101"/>
+      <c r="H23" s="106"/>
+      <c r="I23" s="102"/>
+      <c r="J23" s="107"/>
+      <c r="K23" s="108"/>
+      <c r="L23" s="108"/>
+      <c r="M23" s="108"/>
+      <c r="N23" s="108"/>
+      <c r="O23" s="108"/>
+      <c r="P23" s="109"/>
+      <c r="Q23" s="110"/>
+      <c r="R23" s="111"/>
+      <c r="S23" s="111"/>
+      <c r="T23" s="111"/>
+      <c r="U23" s="111"/>
+      <c r="V23" s="111"/>
+      <c r="W23" s="111"/>
+      <c r="X23" s="111"/>
+      <c r="Y23" s="111"/>
+      <c r="Z23" s="111"/>
+      <c r="AA23" s="111"/>
+      <c r="AB23" s="111"/>
+      <c r="AC23" s="111"/>
+      <c r="AD23" s="111"/>
+      <c r="AE23" s="112"/>
+      <c r="AF23" s="107"/>
+      <c r="AG23" s="108"/>
+      <c r="AH23" s="108"/>
+      <c r="AI23" s="109"/>
+    </row>
+    <row r="24" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="29"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="66"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="66"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="72"/>
-      <c r="N24" s="72"/>
-      <c r="O24" s="72"/>
-      <c r="P24" s="73"/>
-      <c r="Q24" s="74"/>
-      <c r="R24" s="75"/>
-      <c r="S24" s="75"/>
-      <c r="T24" s="75"/>
-      <c r="U24" s="75"/>
-      <c r="V24" s="75"/>
-      <c r="W24" s="75"/>
-      <c r="X24" s="75"/>
-      <c r="Y24" s="75"/>
-      <c r="Z24" s="75"/>
-      <c r="AA24" s="75"/>
-      <c r="AB24" s="75"/>
-      <c r="AC24" s="75"/>
-      <c r="AD24" s="75"/>
-      <c r="AE24" s="76"/>
-      <c r="AF24" s="71"/>
-      <c r="AG24" s="72"/>
-      <c r="AH24" s="72"/>
-      <c r="AI24" s="73"/>
-    </row>
-    <row r="25" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="101"/>
+      <c r="C24" s="102"/>
+      <c r="D24" s="103"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="106"/>
+      <c r="I24" s="102"/>
+      <c r="J24" s="107"/>
+      <c r="K24" s="108"/>
+      <c r="L24" s="108"/>
+      <c r="M24" s="108"/>
+      <c r="N24" s="108"/>
+      <c r="O24" s="108"/>
+      <c r="P24" s="109"/>
+      <c r="Q24" s="110"/>
+      <c r="R24" s="111"/>
+      <c r="S24" s="111"/>
+      <c r="T24" s="111"/>
+      <c r="U24" s="111"/>
+      <c r="V24" s="111"/>
+      <c r="W24" s="111"/>
+      <c r="X24" s="111"/>
+      <c r="Y24" s="111"/>
+      <c r="Z24" s="111"/>
+      <c r="AA24" s="111"/>
+      <c r="AB24" s="111"/>
+      <c r="AC24" s="111"/>
+      <c r="AD24" s="111"/>
+      <c r="AE24" s="112"/>
+      <c r="AF24" s="107"/>
+      <c r="AG24" s="108"/>
+      <c r="AH24" s="108"/>
+      <c r="AI24" s="109"/>
+    </row>
+    <row r="25" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="29"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="66"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="72"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="72"/>
-      <c r="P25" s="73"/>
-      <c r="Q25" s="74"/>
-      <c r="R25" s="75"/>
-      <c r="S25" s="75"/>
-      <c r="T25" s="75"/>
-      <c r="U25" s="75"/>
-      <c r="V25" s="75"/>
-      <c r="W25" s="75"/>
-      <c r="X25" s="75"/>
-      <c r="Y25" s="75"/>
-      <c r="Z25" s="75"/>
-      <c r="AA25" s="75"/>
-      <c r="AB25" s="75"/>
-      <c r="AC25" s="75"/>
-      <c r="AD25" s="75"/>
-      <c r="AE25" s="76"/>
-      <c r="AF25" s="71"/>
-      <c r="AG25" s="72"/>
-      <c r="AH25" s="72"/>
-      <c r="AI25" s="73"/>
-    </row>
-    <row r="26" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="101"/>
+      <c r="C25" s="102"/>
+      <c r="D25" s="103"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="101"/>
+      <c r="H25" s="106"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="107"/>
+      <c r="K25" s="108"/>
+      <c r="L25" s="108"/>
+      <c r="M25" s="108"/>
+      <c r="N25" s="108"/>
+      <c r="O25" s="108"/>
+      <c r="P25" s="109"/>
+      <c r="Q25" s="110"/>
+      <c r="R25" s="111"/>
+      <c r="S25" s="111"/>
+      <c r="T25" s="111"/>
+      <c r="U25" s="111"/>
+      <c r="V25" s="111"/>
+      <c r="W25" s="111"/>
+      <c r="X25" s="111"/>
+      <c r="Y25" s="111"/>
+      <c r="Z25" s="111"/>
+      <c r="AA25" s="111"/>
+      <c r="AB25" s="111"/>
+      <c r="AC25" s="111"/>
+      <c r="AD25" s="111"/>
+      <c r="AE25" s="112"/>
+      <c r="AF25" s="107"/>
+      <c r="AG25" s="108"/>
+      <c r="AH25" s="108"/>
+      <c r="AI25" s="109"/>
+    </row>
+    <row r="26" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="29"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="72"/>
-      <c r="M26" s="72"/>
-      <c r="N26" s="72"/>
-      <c r="O26" s="72"/>
-      <c r="P26" s="73"/>
-      <c r="Q26" s="74"/>
-      <c r="R26" s="75"/>
-      <c r="S26" s="75"/>
-      <c r="T26" s="75"/>
-      <c r="U26" s="75"/>
-      <c r="V26" s="75"/>
-      <c r="W26" s="75"/>
-      <c r="X26" s="75"/>
-      <c r="Y26" s="75"/>
-      <c r="Z26" s="75"/>
-      <c r="AA26" s="75"/>
-      <c r="AB26" s="75"/>
-      <c r="AC26" s="75"/>
-      <c r="AD26" s="75"/>
-      <c r="AE26" s="76"/>
-      <c r="AF26" s="71"/>
-      <c r="AG26" s="72"/>
-      <c r="AH26" s="72"/>
-      <c r="AI26" s="73"/>
-    </row>
-    <row r="27" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="101"/>
+      <c r="C26" s="102"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="101"/>
+      <c r="H26" s="106"/>
+      <c r="I26" s="102"/>
+      <c r="J26" s="107"/>
+      <c r="K26" s="108"/>
+      <c r="L26" s="108"/>
+      <c r="M26" s="108"/>
+      <c r="N26" s="108"/>
+      <c r="O26" s="108"/>
+      <c r="P26" s="109"/>
+      <c r="Q26" s="110"/>
+      <c r="R26" s="111"/>
+      <c r="S26" s="111"/>
+      <c r="T26" s="111"/>
+      <c r="U26" s="111"/>
+      <c r="V26" s="111"/>
+      <c r="W26" s="111"/>
+      <c r="X26" s="111"/>
+      <c r="Y26" s="111"/>
+      <c r="Z26" s="111"/>
+      <c r="AA26" s="111"/>
+      <c r="AB26" s="111"/>
+      <c r="AC26" s="111"/>
+      <c r="AD26" s="111"/>
+      <c r="AE26" s="112"/>
+      <c r="AF26" s="107"/>
+      <c r="AG26" s="108"/>
+      <c r="AH26" s="108"/>
+      <c r="AI26" s="109"/>
+    </row>
+    <row r="27" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="29"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="66"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="72"/>
-      <c r="M27" s="72"/>
-      <c r="N27" s="72"/>
-      <c r="O27" s="72"/>
-      <c r="P27" s="73"/>
-      <c r="Q27" s="74"/>
-      <c r="R27" s="75"/>
-      <c r="S27" s="75"/>
-      <c r="T27" s="75"/>
-      <c r="U27" s="75"/>
-      <c r="V27" s="75"/>
-      <c r="W27" s="75"/>
-      <c r="X27" s="75"/>
-      <c r="Y27" s="75"/>
-      <c r="Z27" s="75"/>
-      <c r="AA27" s="75"/>
-      <c r="AB27" s="75"/>
-      <c r="AC27" s="75"/>
-      <c r="AD27" s="75"/>
-      <c r="AE27" s="76"/>
-      <c r="AF27" s="71"/>
-      <c r="AG27" s="72"/>
-      <c r="AH27" s="72"/>
-      <c r="AI27" s="73"/>
-    </row>
-    <row r="28" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="101"/>
+      <c r="C27" s="102"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="101"/>
+      <c r="H27" s="106"/>
+      <c r="I27" s="102"/>
+      <c r="J27" s="107"/>
+      <c r="K27" s="108"/>
+      <c r="L27" s="108"/>
+      <c r="M27" s="108"/>
+      <c r="N27" s="108"/>
+      <c r="O27" s="108"/>
+      <c r="P27" s="109"/>
+      <c r="Q27" s="110"/>
+      <c r="R27" s="111"/>
+      <c r="S27" s="111"/>
+      <c r="T27" s="111"/>
+      <c r="U27" s="111"/>
+      <c r="V27" s="111"/>
+      <c r="W27" s="111"/>
+      <c r="X27" s="111"/>
+      <c r="Y27" s="111"/>
+      <c r="Z27" s="111"/>
+      <c r="AA27" s="111"/>
+      <c r="AB27" s="111"/>
+      <c r="AC27" s="111"/>
+      <c r="AD27" s="111"/>
+      <c r="AE27" s="112"/>
+      <c r="AF27" s="107"/>
+      <c r="AG27" s="108"/>
+      <c r="AH27" s="108"/>
+      <c r="AI27" s="109"/>
+    </row>
+    <row r="28" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="29"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="66"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="71"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="72"/>
-      <c r="M28" s="72"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="72"/>
-      <c r="P28" s="73"/>
-      <c r="Q28" s="74"/>
-      <c r="R28" s="75"/>
-      <c r="S28" s="75"/>
-      <c r="T28" s="75"/>
-      <c r="U28" s="75"/>
-      <c r="V28" s="75"/>
-      <c r="W28" s="75"/>
-      <c r="X28" s="75"/>
-      <c r="Y28" s="75"/>
-      <c r="Z28" s="75"/>
-      <c r="AA28" s="75"/>
-      <c r="AB28" s="75"/>
-      <c r="AC28" s="75"/>
-      <c r="AD28" s="75"/>
-      <c r="AE28" s="76"/>
-      <c r="AF28" s="71"/>
-      <c r="AG28" s="72"/>
-      <c r="AH28" s="72"/>
-      <c r="AI28" s="73"/>
-    </row>
-    <row r="29" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="101"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="103"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="101"/>
+      <c r="H28" s="106"/>
+      <c r="I28" s="102"/>
+      <c r="J28" s="107"/>
+      <c r="K28" s="108"/>
+      <c r="L28" s="108"/>
+      <c r="M28" s="108"/>
+      <c r="N28" s="108"/>
+      <c r="O28" s="108"/>
+      <c r="P28" s="109"/>
+      <c r="Q28" s="110"/>
+      <c r="R28" s="111"/>
+      <c r="S28" s="111"/>
+      <c r="T28" s="111"/>
+      <c r="U28" s="111"/>
+      <c r="V28" s="111"/>
+      <c r="W28" s="111"/>
+      <c r="X28" s="111"/>
+      <c r="Y28" s="111"/>
+      <c r="Z28" s="111"/>
+      <c r="AA28" s="111"/>
+      <c r="AB28" s="111"/>
+      <c r="AC28" s="111"/>
+      <c r="AD28" s="111"/>
+      <c r="AE28" s="112"/>
+      <c r="AF28" s="107"/>
+      <c r="AG28" s="108"/>
+      <c r="AH28" s="108"/>
+      <c r="AI28" s="109"/>
+    </row>
+    <row r="29" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="29"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="66"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="71"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="72"/>
-      <c r="M29" s="72"/>
-      <c r="N29" s="72"/>
-      <c r="O29" s="72"/>
-      <c r="P29" s="73"/>
-      <c r="Q29" s="74"/>
-      <c r="R29" s="75"/>
-      <c r="S29" s="75"/>
-      <c r="T29" s="75"/>
-      <c r="U29" s="75"/>
-      <c r="V29" s="75"/>
-      <c r="W29" s="75"/>
-      <c r="X29" s="75"/>
-      <c r="Y29" s="75"/>
-      <c r="Z29" s="75"/>
-      <c r="AA29" s="75"/>
-      <c r="AB29" s="75"/>
-      <c r="AC29" s="75"/>
-      <c r="AD29" s="75"/>
-      <c r="AE29" s="76"/>
-      <c r="AF29" s="71"/>
-      <c r="AG29" s="72"/>
-      <c r="AH29" s="72"/>
-      <c r="AI29" s="73"/>
-    </row>
-    <row r="30" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="101"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="103"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="101"/>
+      <c r="H29" s="106"/>
+      <c r="I29" s="102"/>
+      <c r="J29" s="107"/>
+      <c r="K29" s="108"/>
+      <c r="L29" s="108"/>
+      <c r="M29" s="108"/>
+      <c r="N29" s="108"/>
+      <c r="O29" s="108"/>
+      <c r="P29" s="109"/>
+      <c r="Q29" s="110"/>
+      <c r="R29" s="111"/>
+      <c r="S29" s="111"/>
+      <c r="T29" s="111"/>
+      <c r="U29" s="111"/>
+      <c r="V29" s="111"/>
+      <c r="W29" s="111"/>
+      <c r="X29" s="111"/>
+      <c r="Y29" s="111"/>
+      <c r="Z29" s="111"/>
+      <c r="AA29" s="111"/>
+      <c r="AB29" s="111"/>
+      <c r="AC29" s="111"/>
+      <c r="AD29" s="111"/>
+      <c r="AE29" s="112"/>
+      <c r="AF29" s="107"/>
+      <c r="AG29" s="108"/>
+      <c r="AH29" s="108"/>
+      <c r="AI29" s="109"/>
+    </row>
+    <row r="30" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="29"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="66"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="71"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="72"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="72"/>
-      <c r="O30" s="72"/>
-      <c r="P30" s="73"/>
-      <c r="Q30" s="74"/>
-      <c r="R30" s="75"/>
-      <c r="S30" s="75"/>
-      <c r="T30" s="75"/>
-      <c r="U30" s="75"/>
-      <c r="V30" s="75"/>
-      <c r="W30" s="75"/>
-      <c r="X30" s="75"/>
-      <c r="Y30" s="75"/>
-      <c r="Z30" s="75"/>
-      <c r="AA30" s="75"/>
-      <c r="AB30" s="75"/>
-      <c r="AC30" s="75"/>
-      <c r="AD30" s="75"/>
-      <c r="AE30" s="76"/>
-      <c r="AF30" s="71"/>
-      <c r="AG30" s="72"/>
-      <c r="AH30" s="72"/>
-      <c r="AI30" s="73"/>
-    </row>
-    <row r="31" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="101"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="105"/>
+      <c r="G30" s="101"/>
+      <c r="H30" s="106"/>
+      <c r="I30" s="102"/>
+      <c r="J30" s="107"/>
+      <c r="K30" s="108"/>
+      <c r="L30" s="108"/>
+      <c r="M30" s="108"/>
+      <c r="N30" s="108"/>
+      <c r="O30" s="108"/>
+      <c r="P30" s="109"/>
+      <c r="Q30" s="110"/>
+      <c r="R30" s="111"/>
+      <c r="S30" s="111"/>
+      <c r="T30" s="111"/>
+      <c r="U30" s="111"/>
+      <c r="V30" s="111"/>
+      <c r="W30" s="111"/>
+      <c r="X30" s="111"/>
+      <c r="Y30" s="111"/>
+      <c r="Z30" s="111"/>
+      <c r="AA30" s="111"/>
+      <c r="AB30" s="111"/>
+      <c r="AC30" s="111"/>
+      <c r="AD30" s="111"/>
+      <c r="AE30" s="112"/>
+      <c r="AF30" s="107"/>
+      <c r="AG30" s="108"/>
+      <c r="AH30" s="108"/>
+      <c r="AI30" s="109"/>
+    </row>
+    <row r="31" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="29"/>
-      <c r="B31" s="65"/>
-      <c r="C31" s="66"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="66"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="72"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="72"/>
-      <c r="O31" s="72"/>
-      <c r="P31" s="73"/>
-      <c r="Q31" s="74"/>
-      <c r="R31" s="75"/>
-      <c r="S31" s="75"/>
-      <c r="T31" s="75"/>
-      <c r="U31" s="75"/>
-      <c r="V31" s="75"/>
-      <c r="W31" s="75"/>
-      <c r="X31" s="75"/>
-      <c r="Y31" s="75"/>
-      <c r="Z31" s="75"/>
-      <c r="AA31" s="75"/>
-      <c r="AB31" s="75"/>
-      <c r="AC31" s="75"/>
-      <c r="AD31" s="75"/>
-      <c r="AE31" s="76"/>
-      <c r="AF31" s="71"/>
-      <c r="AG31" s="72"/>
-      <c r="AH31" s="72"/>
-      <c r="AI31" s="73"/>
-    </row>
-    <row r="32" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="101"/>
+      <c r="C31" s="102"/>
+      <c r="D31" s="103"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="105"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="106"/>
+      <c r="I31" s="102"/>
+      <c r="J31" s="107"/>
+      <c r="K31" s="108"/>
+      <c r="L31" s="108"/>
+      <c r="M31" s="108"/>
+      <c r="N31" s="108"/>
+      <c r="O31" s="108"/>
+      <c r="P31" s="109"/>
+      <c r="Q31" s="110"/>
+      <c r="R31" s="111"/>
+      <c r="S31" s="111"/>
+      <c r="T31" s="111"/>
+      <c r="U31" s="111"/>
+      <c r="V31" s="111"/>
+      <c r="W31" s="111"/>
+      <c r="X31" s="111"/>
+      <c r="Y31" s="111"/>
+      <c r="Z31" s="111"/>
+      <c r="AA31" s="111"/>
+      <c r="AB31" s="111"/>
+      <c r="AC31" s="111"/>
+      <c r="AD31" s="111"/>
+      <c r="AE31" s="112"/>
+      <c r="AF31" s="107"/>
+      <c r="AG31" s="108"/>
+      <c r="AH31" s="108"/>
+      <c r="AI31" s="109"/>
+    </row>
+    <row r="32" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29"/>
-      <c r="B32" s="65"/>
-      <c r="C32" s="66"/>
-      <c r="D32" s="67"/>
-      <c r="E32" s="68"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="70"/>
-      <c r="I32" s="66"/>
-      <c r="J32" s="71"/>
-      <c r="K32" s="77"/>
-      <c r="L32" s="72"/>
-      <c r="M32" s="72"/>
-      <c r="N32" s="72"/>
-      <c r="O32" s="72"/>
-      <c r="P32" s="73"/>
-      <c r="Q32" s="74"/>
-      <c r="R32" s="75"/>
-      <c r="S32" s="75"/>
-      <c r="T32" s="75"/>
-      <c r="U32" s="75"/>
-      <c r="V32" s="75"/>
-      <c r="W32" s="75"/>
-      <c r="X32" s="75"/>
-      <c r="Y32" s="75"/>
-      <c r="Z32" s="75"/>
-      <c r="AA32" s="75"/>
-      <c r="AB32" s="75"/>
-      <c r="AC32" s="75"/>
-      <c r="AD32" s="75"/>
-      <c r="AE32" s="76"/>
-      <c r="AF32" s="71"/>
-      <c r="AG32" s="72"/>
-      <c r="AH32" s="72"/>
-      <c r="AI32" s="73"/>
-    </row>
-    <row r="33" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="101"/>
+      <c r="C32" s="102"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="101"/>
+      <c r="H32" s="106"/>
+      <c r="I32" s="102"/>
+      <c r="J32" s="107"/>
+      <c r="K32" s="127"/>
+      <c r="L32" s="108"/>
+      <c r="M32" s="108"/>
+      <c r="N32" s="108"/>
+      <c r="O32" s="108"/>
+      <c r="P32" s="109"/>
+      <c r="Q32" s="110"/>
+      <c r="R32" s="111"/>
+      <c r="S32" s="111"/>
+      <c r="T32" s="111"/>
+      <c r="U32" s="111"/>
+      <c r="V32" s="111"/>
+      <c r="W32" s="111"/>
+      <c r="X32" s="111"/>
+      <c r="Y32" s="111"/>
+      <c r="Z32" s="111"/>
+      <c r="AA32" s="111"/>
+      <c r="AB32" s="111"/>
+      <c r="AC32" s="111"/>
+      <c r="AD32" s="111"/>
+      <c r="AE32" s="112"/>
+      <c r="AF32" s="107"/>
+      <c r="AG32" s="108"/>
+      <c r="AH32" s="108"/>
+      <c r="AI32" s="109"/>
+    </row>
+    <row r="33" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="29"/>
-      <c r="B33" s="65"/>
-      <c r="C33" s="66"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="65"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="66"/>
-      <c r="J33" s="71"/>
-      <c r="K33" s="72"/>
-      <c r="L33" s="72"/>
-      <c r="M33" s="72"/>
-      <c r="N33" s="72"/>
-      <c r="O33" s="72"/>
-      <c r="P33" s="73"/>
-      <c r="Q33" s="74"/>
-      <c r="R33" s="75"/>
-      <c r="S33" s="75"/>
-      <c r="T33" s="75"/>
-      <c r="U33" s="75"/>
-      <c r="V33" s="75"/>
-      <c r="W33" s="75"/>
-      <c r="X33" s="75"/>
-      <c r="Y33" s="75"/>
-      <c r="Z33" s="75"/>
-      <c r="AA33" s="75"/>
-      <c r="AB33" s="75"/>
-      <c r="AC33" s="75"/>
-      <c r="AD33" s="75"/>
-      <c r="AE33" s="76"/>
-      <c r="AF33" s="71"/>
-      <c r="AG33" s="72"/>
-      <c r="AH33" s="72"/>
-      <c r="AI33" s="73"/>
-    </row>
-    <row r="34" spans="1:35" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="B33" s="101"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="101"/>
+      <c r="H33" s="106"/>
+      <c r="I33" s="102"/>
+      <c r="J33" s="107"/>
+      <c r="K33" s="108"/>
+      <c r="L33" s="108"/>
+      <c r="M33" s="108"/>
+      <c r="N33" s="108"/>
+      <c r="O33" s="108"/>
+      <c r="P33" s="109"/>
+      <c r="Q33" s="110"/>
+      <c r="R33" s="111"/>
+      <c r="S33" s="111"/>
+      <c r="T33" s="111"/>
+      <c r="U33" s="111"/>
+      <c r="V33" s="111"/>
+      <c r="W33" s="111"/>
+      <c r="X33" s="111"/>
+      <c r="Y33" s="111"/>
+      <c r="Z33" s="111"/>
+      <c r="AA33" s="111"/>
+      <c r="AB33" s="111"/>
+      <c r="AC33" s="111"/>
+      <c r="AD33" s="111"/>
+      <c r="AE33" s="112"/>
+      <c r="AF33" s="107"/>
+      <c r="AG33" s="108"/>
+      <c r="AH33" s="108"/>
+      <c r="AI33" s="109"/>
+    </row>
+    <row r="34" spans="1:35" ht="14" x14ac:dyDescent="0.2">
       <c r="K34" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="179">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -8690,162 +9125,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1"/>
@@ -8860,305 +9139,305 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AL49"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:AL50"/>
+  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16" width="3.625" style="37" customWidth="1"/>
-    <col min="17" max="17" width="3.625" style="48" customWidth="1"/>
-    <col min="18" max="33" width="3.625" style="37" customWidth="1"/>
-    <col min="34" max="34" width="3.625" style="48" customWidth="1"/>
-    <col min="35" max="256" width="3.625" style="37"/>
-    <col min="257" max="290" width="3.625" style="37" customWidth="1"/>
-    <col min="291" max="512" width="3.625" style="37"/>
-    <col min="513" max="546" width="3.625" style="37" customWidth="1"/>
-    <col min="547" max="768" width="3.625" style="37"/>
-    <col min="769" max="802" width="3.625" style="37" customWidth="1"/>
-    <col min="803" max="1024" width="3.625" style="37"/>
-    <col min="1025" max="1058" width="3.625" style="37" customWidth="1"/>
-    <col min="1059" max="1280" width="3.625" style="37"/>
-    <col min="1281" max="1314" width="3.625" style="37" customWidth="1"/>
-    <col min="1315" max="1536" width="3.625" style="37"/>
-    <col min="1537" max="1570" width="3.625" style="37" customWidth="1"/>
-    <col min="1571" max="1792" width="3.625" style="37"/>
-    <col min="1793" max="1826" width="3.625" style="37" customWidth="1"/>
-    <col min="1827" max="2048" width="3.625" style="37"/>
-    <col min="2049" max="2082" width="3.625" style="37" customWidth="1"/>
-    <col min="2083" max="2304" width="3.625" style="37"/>
-    <col min="2305" max="2338" width="3.625" style="37" customWidth="1"/>
-    <col min="2339" max="2560" width="3.625" style="37"/>
-    <col min="2561" max="2594" width="3.625" style="37" customWidth="1"/>
-    <col min="2595" max="2816" width="3.625" style="37"/>
-    <col min="2817" max="2850" width="3.625" style="37" customWidth="1"/>
-    <col min="2851" max="3072" width="3.625" style="37"/>
-    <col min="3073" max="3106" width="3.625" style="37" customWidth="1"/>
-    <col min="3107" max="3328" width="3.625" style="37"/>
-    <col min="3329" max="3362" width="3.625" style="37" customWidth="1"/>
-    <col min="3363" max="3584" width="3.625" style="37"/>
-    <col min="3585" max="3618" width="3.625" style="37" customWidth="1"/>
-    <col min="3619" max="3840" width="3.625" style="37"/>
-    <col min="3841" max="3874" width="3.625" style="37" customWidth="1"/>
-    <col min="3875" max="4096" width="3.625" style="37"/>
-    <col min="4097" max="4130" width="3.625" style="37" customWidth="1"/>
-    <col min="4131" max="4352" width="3.625" style="37"/>
-    <col min="4353" max="4386" width="3.625" style="37" customWidth="1"/>
-    <col min="4387" max="4608" width="3.625" style="37"/>
-    <col min="4609" max="4642" width="3.625" style="37" customWidth="1"/>
-    <col min="4643" max="4864" width="3.625" style="37"/>
-    <col min="4865" max="4898" width="3.625" style="37" customWidth="1"/>
-    <col min="4899" max="5120" width="3.625" style="37"/>
-    <col min="5121" max="5154" width="3.625" style="37" customWidth="1"/>
-    <col min="5155" max="5376" width="3.625" style="37"/>
-    <col min="5377" max="5410" width="3.625" style="37" customWidth="1"/>
-    <col min="5411" max="5632" width="3.625" style="37"/>
-    <col min="5633" max="5666" width="3.625" style="37" customWidth="1"/>
-    <col min="5667" max="5888" width="3.625" style="37"/>
-    <col min="5889" max="5922" width="3.625" style="37" customWidth="1"/>
-    <col min="5923" max="6144" width="3.625" style="37"/>
-    <col min="6145" max="6178" width="3.625" style="37" customWidth="1"/>
-    <col min="6179" max="6400" width="3.625" style="37"/>
-    <col min="6401" max="6434" width="3.625" style="37" customWidth="1"/>
-    <col min="6435" max="6656" width="3.625" style="37"/>
-    <col min="6657" max="6690" width="3.625" style="37" customWidth="1"/>
-    <col min="6691" max="6912" width="3.625" style="37"/>
-    <col min="6913" max="6946" width="3.625" style="37" customWidth="1"/>
-    <col min="6947" max="7168" width="3.625" style="37"/>
-    <col min="7169" max="7202" width="3.625" style="37" customWidth="1"/>
-    <col min="7203" max="7424" width="3.625" style="37"/>
-    <col min="7425" max="7458" width="3.625" style="37" customWidth="1"/>
-    <col min="7459" max="7680" width="3.625" style="37"/>
-    <col min="7681" max="7714" width="3.625" style="37" customWidth="1"/>
-    <col min="7715" max="7936" width="3.625" style="37"/>
-    <col min="7937" max="7970" width="3.625" style="37" customWidth="1"/>
-    <col min="7971" max="8192" width="3.625" style="37"/>
-    <col min="8193" max="8226" width="3.625" style="37" customWidth="1"/>
-    <col min="8227" max="8448" width="3.625" style="37"/>
-    <col min="8449" max="8482" width="3.625" style="37" customWidth="1"/>
-    <col min="8483" max="8704" width="3.625" style="37"/>
-    <col min="8705" max="8738" width="3.625" style="37" customWidth="1"/>
-    <col min="8739" max="8960" width="3.625" style="37"/>
-    <col min="8961" max="8994" width="3.625" style="37" customWidth="1"/>
-    <col min="8995" max="9216" width="3.625" style="37"/>
-    <col min="9217" max="9250" width="3.625" style="37" customWidth="1"/>
-    <col min="9251" max="9472" width="3.625" style="37"/>
-    <col min="9473" max="9506" width="3.625" style="37" customWidth="1"/>
-    <col min="9507" max="9728" width="3.625" style="37"/>
-    <col min="9729" max="9762" width="3.625" style="37" customWidth="1"/>
-    <col min="9763" max="9984" width="3.625" style="37"/>
-    <col min="9985" max="10018" width="3.625" style="37" customWidth="1"/>
-    <col min="10019" max="10240" width="3.625" style="37"/>
-    <col min="10241" max="10274" width="3.625" style="37" customWidth="1"/>
-    <col min="10275" max="10496" width="3.625" style="37"/>
-    <col min="10497" max="10530" width="3.625" style="37" customWidth="1"/>
-    <col min="10531" max="10752" width="3.625" style="37"/>
-    <col min="10753" max="10786" width="3.625" style="37" customWidth="1"/>
-    <col min="10787" max="11008" width="3.625" style="37"/>
-    <col min="11009" max="11042" width="3.625" style="37" customWidth="1"/>
-    <col min="11043" max="11264" width="3.625" style="37"/>
-    <col min="11265" max="11298" width="3.625" style="37" customWidth="1"/>
-    <col min="11299" max="11520" width="3.625" style="37"/>
-    <col min="11521" max="11554" width="3.625" style="37" customWidth="1"/>
-    <col min="11555" max="11776" width="3.625" style="37"/>
-    <col min="11777" max="11810" width="3.625" style="37" customWidth="1"/>
-    <col min="11811" max="12032" width="3.625" style="37"/>
-    <col min="12033" max="12066" width="3.625" style="37" customWidth="1"/>
-    <col min="12067" max="12288" width="3.625" style="37"/>
-    <col min="12289" max="12322" width="3.625" style="37" customWidth="1"/>
-    <col min="12323" max="12544" width="3.625" style="37"/>
-    <col min="12545" max="12578" width="3.625" style="37" customWidth="1"/>
-    <col min="12579" max="12800" width="3.625" style="37"/>
-    <col min="12801" max="12834" width="3.625" style="37" customWidth="1"/>
-    <col min="12835" max="13056" width="3.625" style="37"/>
-    <col min="13057" max="13090" width="3.625" style="37" customWidth="1"/>
-    <col min="13091" max="13312" width="3.625" style="37"/>
-    <col min="13313" max="13346" width="3.625" style="37" customWidth="1"/>
-    <col min="13347" max="13568" width="3.625" style="37"/>
-    <col min="13569" max="13602" width="3.625" style="37" customWidth="1"/>
-    <col min="13603" max="13824" width="3.625" style="37"/>
-    <col min="13825" max="13858" width="3.625" style="37" customWidth="1"/>
-    <col min="13859" max="14080" width="3.625" style="37"/>
-    <col min="14081" max="14114" width="3.625" style="37" customWidth="1"/>
-    <col min="14115" max="14336" width="3.625" style="37"/>
-    <col min="14337" max="14370" width="3.625" style="37" customWidth="1"/>
-    <col min="14371" max="14592" width="3.625" style="37"/>
-    <col min="14593" max="14626" width="3.625" style="37" customWidth="1"/>
-    <col min="14627" max="14848" width="3.625" style="37"/>
-    <col min="14849" max="14882" width="3.625" style="37" customWidth="1"/>
-    <col min="14883" max="15104" width="3.625" style="37"/>
-    <col min="15105" max="15138" width="3.625" style="37" customWidth="1"/>
-    <col min="15139" max="15360" width="3.625" style="37"/>
-    <col min="15361" max="15394" width="3.625" style="37" customWidth="1"/>
-    <col min="15395" max="15616" width="3.625" style="37"/>
-    <col min="15617" max="15650" width="3.625" style="37" customWidth="1"/>
-    <col min="15651" max="15872" width="3.625" style="37"/>
-    <col min="15873" max="15906" width="3.625" style="37" customWidth="1"/>
-    <col min="15907" max="16128" width="3.625" style="37"/>
-    <col min="16129" max="16162" width="3.625" style="37" customWidth="1"/>
-    <col min="16163" max="16384" width="3.625" style="37"/>
+    <col min="1" max="16" width="3.6328125" style="37" customWidth="1"/>
+    <col min="17" max="17" width="3.6328125" style="48" customWidth="1"/>
+    <col min="18" max="33" width="3.6328125" style="37" customWidth="1"/>
+    <col min="34" max="34" width="3.6328125" style="48" customWidth="1"/>
+    <col min="35" max="256" width="3.6328125" style="37"/>
+    <col min="257" max="290" width="3.6328125" style="37" customWidth="1"/>
+    <col min="291" max="512" width="3.6328125" style="37"/>
+    <col min="513" max="546" width="3.6328125" style="37" customWidth="1"/>
+    <col min="547" max="768" width="3.6328125" style="37"/>
+    <col min="769" max="802" width="3.6328125" style="37" customWidth="1"/>
+    <col min="803" max="1024" width="3.6328125" style="37"/>
+    <col min="1025" max="1058" width="3.6328125" style="37" customWidth="1"/>
+    <col min="1059" max="1280" width="3.6328125" style="37"/>
+    <col min="1281" max="1314" width="3.6328125" style="37" customWidth="1"/>
+    <col min="1315" max="1536" width="3.6328125" style="37"/>
+    <col min="1537" max="1570" width="3.6328125" style="37" customWidth="1"/>
+    <col min="1571" max="1792" width="3.6328125" style="37"/>
+    <col min="1793" max="1826" width="3.6328125" style="37" customWidth="1"/>
+    <col min="1827" max="2048" width="3.6328125" style="37"/>
+    <col min="2049" max="2082" width="3.6328125" style="37" customWidth="1"/>
+    <col min="2083" max="2304" width="3.6328125" style="37"/>
+    <col min="2305" max="2338" width="3.6328125" style="37" customWidth="1"/>
+    <col min="2339" max="2560" width="3.6328125" style="37"/>
+    <col min="2561" max="2594" width="3.6328125" style="37" customWidth="1"/>
+    <col min="2595" max="2816" width="3.6328125" style="37"/>
+    <col min="2817" max="2850" width="3.6328125" style="37" customWidth="1"/>
+    <col min="2851" max="3072" width="3.6328125" style="37"/>
+    <col min="3073" max="3106" width="3.6328125" style="37" customWidth="1"/>
+    <col min="3107" max="3328" width="3.6328125" style="37"/>
+    <col min="3329" max="3362" width="3.6328125" style="37" customWidth="1"/>
+    <col min="3363" max="3584" width="3.6328125" style="37"/>
+    <col min="3585" max="3618" width="3.6328125" style="37" customWidth="1"/>
+    <col min="3619" max="3840" width="3.6328125" style="37"/>
+    <col min="3841" max="3874" width="3.6328125" style="37" customWidth="1"/>
+    <col min="3875" max="4096" width="3.6328125" style="37"/>
+    <col min="4097" max="4130" width="3.6328125" style="37" customWidth="1"/>
+    <col min="4131" max="4352" width="3.6328125" style="37"/>
+    <col min="4353" max="4386" width="3.6328125" style="37" customWidth="1"/>
+    <col min="4387" max="4608" width="3.6328125" style="37"/>
+    <col min="4609" max="4642" width="3.6328125" style="37" customWidth="1"/>
+    <col min="4643" max="4864" width="3.6328125" style="37"/>
+    <col min="4865" max="4898" width="3.6328125" style="37" customWidth="1"/>
+    <col min="4899" max="5120" width="3.6328125" style="37"/>
+    <col min="5121" max="5154" width="3.6328125" style="37" customWidth="1"/>
+    <col min="5155" max="5376" width="3.6328125" style="37"/>
+    <col min="5377" max="5410" width="3.6328125" style="37" customWidth="1"/>
+    <col min="5411" max="5632" width="3.6328125" style="37"/>
+    <col min="5633" max="5666" width="3.6328125" style="37" customWidth="1"/>
+    <col min="5667" max="5888" width="3.6328125" style="37"/>
+    <col min="5889" max="5922" width="3.6328125" style="37" customWidth="1"/>
+    <col min="5923" max="6144" width="3.6328125" style="37"/>
+    <col min="6145" max="6178" width="3.6328125" style="37" customWidth="1"/>
+    <col min="6179" max="6400" width="3.6328125" style="37"/>
+    <col min="6401" max="6434" width="3.6328125" style="37" customWidth="1"/>
+    <col min="6435" max="6656" width="3.6328125" style="37"/>
+    <col min="6657" max="6690" width="3.6328125" style="37" customWidth="1"/>
+    <col min="6691" max="6912" width="3.6328125" style="37"/>
+    <col min="6913" max="6946" width="3.6328125" style="37" customWidth="1"/>
+    <col min="6947" max="7168" width="3.6328125" style="37"/>
+    <col min="7169" max="7202" width="3.6328125" style="37" customWidth="1"/>
+    <col min="7203" max="7424" width="3.6328125" style="37"/>
+    <col min="7425" max="7458" width="3.6328125" style="37" customWidth="1"/>
+    <col min="7459" max="7680" width="3.6328125" style="37"/>
+    <col min="7681" max="7714" width="3.6328125" style="37" customWidth="1"/>
+    <col min="7715" max="7936" width="3.6328125" style="37"/>
+    <col min="7937" max="7970" width="3.6328125" style="37" customWidth="1"/>
+    <col min="7971" max="8192" width="3.6328125" style="37"/>
+    <col min="8193" max="8226" width="3.6328125" style="37" customWidth="1"/>
+    <col min="8227" max="8448" width="3.6328125" style="37"/>
+    <col min="8449" max="8482" width="3.6328125" style="37" customWidth="1"/>
+    <col min="8483" max="8704" width="3.6328125" style="37"/>
+    <col min="8705" max="8738" width="3.6328125" style="37" customWidth="1"/>
+    <col min="8739" max="8960" width="3.6328125" style="37"/>
+    <col min="8961" max="8994" width="3.6328125" style="37" customWidth="1"/>
+    <col min="8995" max="9216" width="3.6328125" style="37"/>
+    <col min="9217" max="9250" width="3.6328125" style="37" customWidth="1"/>
+    <col min="9251" max="9472" width="3.6328125" style="37"/>
+    <col min="9473" max="9506" width="3.6328125" style="37" customWidth="1"/>
+    <col min="9507" max="9728" width="3.6328125" style="37"/>
+    <col min="9729" max="9762" width="3.6328125" style="37" customWidth="1"/>
+    <col min="9763" max="9984" width="3.6328125" style="37"/>
+    <col min="9985" max="10018" width="3.6328125" style="37" customWidth="1"/>
+    <col min="10019" max="10240" width="3.6328125" style="37"/>
+    <col min="10241" max="10274" width="3.6328125" style="37" customWidth="1"/>
+    <col min="10275" max="10496" width="3.6328125" style="37"/>
+    <col min="10497" max="10530" width="3.6328125" style="37" customWidth="1"/>
+    <col min="10531" max="10752" width="3.6328125" style="37"/>
+    <col min="10753" max="10786" width="3.6328125" style="37" customWidth="1"/>
+    <col min="10787" max="11008" width="3.6328125" style="37"/>
+    <col min="11009" max="11042" width="3.6328125" style="37" customWidth="1"/>
+    <col min="11043" max="11264" width="3.6328125" style="37"/>
+    <col min="11265" max="11298" width="3.6328125" style="37" customWidth="1"/>
+    <col min="11299" max="11520" width="3.6328125" style="37"/>
+    <col min="11521" max="11554" width="3.6328125" style="37" customWidth="1"/>
+    <col min="11555" max="11776" width="3.6328125" style="37"/>
+    <col min="11777" max="11810" width="3.6328125" style="37" customWidth="1"/>
+    <col min="11811" max="12032" width="3.6328125" style="37"/>
+    <col min="12033" max="12066" width="3.6328125" style="37" customWidth="1"/>
+    <col min="12067" max="12288" width="3.6328125" style="37"/>
+    <col min="12289" max="12322" width="3.6328125" style="37" customWidth="1"/>
+    <col min="12323" max="12544" width="3.6328125" style="37"/>
+    <col min="12545" max="12578" width="3.6328125" style="37" customWidth="1"/>
+    <col min="12579" max="12800" width="3.6328125" style="37"/>
+    <col min="12801" max="12834" width="3.6328125" style="37" customWidth="1"/>
+    <col min="12835" max="13056" width="3.6328125" style="37"/>
+    <col min="13057" max="13090" width="3.6328125" style="37" customWidth="1"/>
+    <col min="13091" max="13312" width="3.6328125" style="37"/>
+    <col min="13313" max="13346" width="3.6328125" style="37" customWidth="1"/>
+    <col min="13347" max="13568" width="3.6328125" style="37"/>
+    <col min="13569" max="13602" width="3.6328125" style="37" customWidth="1"/>
+    <col min="13603" max="13824" width="3.6328125" style="37"/>
+    <col min="13825" max="13858" width="3.6328125" style="37" customWidth="1"/>
+    <col min="13859" max="14080" width="3.6328125" style="37"/>
+    <col min="14081" max="14114" width="3.6328125" style="37" customWidth="1"/>
+    <col min="14115" max="14336" width="3.6328125" style="37"/>
+    <col min="14337" max="14370" width="3.6328125" style="37" customWidth="1"/>
+    <col min="14371" max="14592" width="3.6328125" style="37"/>
+    <col min="14593" max="14626" width="3.6328125" style="37" customWidth="1"/>
+    <col min="14627" max="14848" width="3.6328125" style="37"/>
+    <col min="14849" max="14882" width="3.6328125" style="37" customWidth="1"/>
+    <col min="14883" max="15104" width="3.6328125" style="37"/>
+    <col min="15105" max="15138" width="3.6328125" style="37" customWidth="1"/>
+    <col min="15139" max="15360" width="3.6328125" style="37"/>
+    <col min="15361" max="15394" width="3.6328125" style="37" customWidth="1"/>
+    <col min="15395" max="15616" width="3.6328125" style="37"/>
+    <col min="15617" max="15650" width="3.6328125" style="37" customWidth="1"/>
+    <col min="15651" max="15872" width="3.6328125" style="37"/>
+    <col min="15873" max="15906" width="3.6328125" style="37" customWidth="1"/>
+    <col min="15907" max="16128" width="3.6328125" style="37"/>
+    <col min="16129" max="16162" width="3.6328125" style="37" customWidth="1"/>
+    <col min="16163" max="16384" width="3.6328125" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="98" t="s">
-        <v>294</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="101" t="str">
+    <row r="1" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="71" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="74" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="107" t="s">
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="80" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="116" t="str">
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="89" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarchを使用したシステム開発における標準WBS</v>
       </c>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="118"/>
-      <c r="AA1" s="128" t="s">
-        <v>282</v>
-      </c>
-      <c r="AB1" s="129"/>
-      <c r="AC1" s="125" t="str">
+      <c r="T1" s="90"/>
+      <c r="U1" s="90"/>
+      <c r="V1" s="90"/>
+      <c r="W1" s="90"/>
+      <c r="X1" s="90"/>
+      <c r="Y1" s="90"/>
+      <c r="Z1" s="91"/>
+      <c r="AA1" s="131" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB1" s="132"/>
+      <c r="AC1" s="98" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="126"/>
-      <c r="AE1" s="126"/>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="130">
+      <c r="AD1" s="99"/>
+      <c r="AE1" s="99"/>
+      <c r="AF1" s="100"/>
+      <c r="AG1" s="128">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="131"/>
-      <c r="AI1" s="132"/>
+      <c r="AH1" s="129"/>
+      <c r="AI1" s="130"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3"/>
     </row>
-    <row r="2" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="98" t="s">
-        <v>283</v>
-      </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="101" t="str">
+    <row r="2" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="74" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="110"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="120"/>
-      <c r="Y2" s="120"/>
-      <c r="Z2" s="121"/>
-      <c r="AA2" s="128" t="s">
-        <v>284</v>
-      </c>
-      <c r="AB2" s="129"/>
-      <c r="AC2" s="125" t="str">
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="85"/>
+      <c r="S2" s="92"/>
+      <c r="T2" s="93"/>
+      <c r="U2" s="93"/>
+      <c r="V2" s="93"/>
+      <c r="W2" s="93"/>
+      <c r="X2" s="93"/>
+      <c r="Y2" s="93"/>
+      <c r="Z2" s="94"/>
+      <c r="AA2" s="131" t="s">
+        <v>282</v>
+      </c>
+      <c r="AB2" s="132"/>
+      <c r="AC2" s="98" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="126"/>
-      <c r="AE2" s="126"/>
-      <c r="AF2" s="127"/>
-      <c r="AG2" s="130">
+      <c r="AD2" s="99"/>
+      <c r="AE2" s="99"/>
+      <c r="AF2" s="100"/>
+      <c r="AG2" s="128">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v>44455</v>
       </c>
-      <c r="AH2" s="131"/>
-      <c r="AI2" s="132"/>
+      <c r="AH2" s="129"/>
+      <c r="AI2" s="130"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
     </row>
-    <row r="3" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="98" t="s">
-        <v>285</v>
-      </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="101" t="str">
+    <row r="3" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="71" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="74" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="113"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
-      <c r="R3" s="115"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="123"/>
-      <c r="U3" s="123"/>
-      <c r="V3" s="123"/>
-      <c r="W3" s="123"/>
-      <c r="X3" s="123"/>
-      <c r="Y3" s="123"/>
-      <c r="Z3" s="124"/>
-      <c r="AA3" s="128"/>
-      <c r="AB3" s="129"/>
-      <c r="AC3" s="125" t="str">
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="75"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="87"/>
+      <c r="Q3" s="87"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="95"/>
+      <c r="T3" s="96"/>
+      <c r="U3" s="96"/>
+      <c r="V3" s="96"/>
+      <c r="W3" s="96"/>
+      <c r="X3" s="96"/>
+      <c r="Y3" s="96"/>
+      <c r="Z3" s="97"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="132"/>
+      <c r="AC3" s="98" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="126"/>
-      <c r="AE3" s="126"/>
-      <c r="AF3" s="127"/>
-      <c r="AG3" s="130" t="str">
+      <c r="AD3" s="99"/>
+      <c r="AE3" s="99"/>
+      <c r="AF3" s="100"/>
+      <c r="AG3" s="128" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="131"/>
-      <c r="AI3" s="132"/>
+      <c r="AH3" s="129"/>
+      <c r="AI3" s="130"/>
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
     </row>
-    <row r="4" spans="1:38" s="33" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:38" s="33" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="30"/>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -9195,7 +9474,7 @@
       <c r="AH4" s="30"/>
       <c r="AI4" s="30"/>
     </row>
-    <row r="5" spans="1:38" s="33" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" s="33" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="30"/>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
@@ -9213,7 +9492,7 @@
       <c r="O5" s="30"/>
       <c r="P5" s="30"/>
       <c r="Q5" s="16" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="R5" s="30"/>
       <c r="S5" s="30"/>
@@ -9234,7 +9513,7 @@
       <c r="AH5" s="30"/>
       <c r="AI5" s="30"/>
     </row>
-    <row r="6" spans="1:38" s="33" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" s="33" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="30"/>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -9271,10 +9550,10 @@
       <c r="AH6" s="30"/>
       <c r="AI6" s="30"/>
     </row>
-    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="30"/>
       <c r="B7" s="30" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C7" s="30"/>
       <c r="D7" s="30"/>
@@ -9310,11 +9589,11 @@
       <c r="AH7" s="36"/>
       <c r="AI7" s="30"/>
     </row>
-    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="30"/>
       <c r="B8" s="30"/>
       <c r="C8" s="34" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D8" s="30"/>
       <c r="E8" s="30"/>
@@ -9349,11 +9628,11 @@
       <c r="AH8" s="36"/>
       <c r="AI8" s="30"/>
     </row>
-    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="30"/>
       <c r="B9" s="30"/>
       <c r="C9" s="34" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
@@ -9387,11 +9666,11 @@
       <c r="AH9" s="36"/>
       <c r="AI9" s="30"/>
     </row>
-    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="30"/>
       <c r="B10" s="30"/>
       <c r="C10" s="34" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
@@ -9425,10 +9704,12 @@
       <c r="AH10" s="36"/>
       <c r="AI10" s="30"/>
     </row>
-    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="30"/>
       <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
+      <c r="C11" s="34" t="s">
+        <v>416</v>
+      </c>
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
       <c r="F11" s="30"/>
@@ -9461,11 +9742,9 @@
       <c r="AH11" s="36"/>
       <c r="AI11" s="30"/>
     </row>
-    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="30"/>
-      <c r="B12" s="30" t="s">
-        <v>305</v>
-      </c>
+      <c r="B12" s="30"/>
       <c r="C12" s="30"/>
       <c r="D12" s="30"/>
       <c r="E12" s="30"/>
@@ -9477,7 +9756,6 @@
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
       <c r="M12" s="30"/>
-      <c r="N12" s="35"/>
       <c r="O12" s="30"/>
       <c r="P12" s="32"/>
       <c r="Q12" s="30"/>
@@ -9500,9 +9778,11 @@
       <c r="AH12" s="36"/>
       <c r="AI12" s="30"/>
     </row>
-    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
+      <c r="B13" s="30" t="s">
+        <v>303</v>
+      </c>
       <c r="C13" s="30"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30"/>
@@ -9514,11 +9794,11 @@
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
+      <c r="N13" s="35"/>
       <c r="O13" s="30"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="30"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="32"/>
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
       <c r="U13" s="30"/>
@@ -9537,7 +9817,7 @@
       <c r="AH13" s="36"/>
       <c r="AI13" s="30"/>
     </row>
-    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="30"/>
       <c r="B14" s="30"/>
       <c r="C14" s="30"/>
@@ -9574,9 +9854,9 @@
       <c r="AH14" s="36"/>
       <c r="AI14" s="30"/>
     </row>
-    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="30"/>
-      <c r="B15" s="38"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="30"/>
       <c r="D15" s="30"/>
       <c r="E15" s="30"/>
@@ -9588,10 +9868,10 @@
       <c r="K15" s="30"/>
       <c r="L15" s="30"/>
       <c r="M15" s="30"/>
-      <c r="N15" s="35"/>
+      <c r="N15" s="30"/>
       <c r="O15" s="30"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="30"/>
+      <c r="P15" s="30"/>
+      <c r="Q15" s="38"/>
       <c r="R15" s="30"/>
       <c r="S15" s="30"/>
       <c r="T15" s="30"/>
@@ -9611,9 +9891,9 @@
       <c r="AH15" s="36"/>
       <c r="AI15" s="30"/>
     </row>
-    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
+      <c r="B16" s="38"/>
       <c r="C16" s="30"/>
       <c r="D16" s="30"/>
       <c r="E16" s="30"/>
@@ -9625,7 +9905,7 @@
       <c r="K16" s="30"/>
       <c r="L16" s="30"/>
       <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
+      <c r="N16" s="35"/>
       <c r="O16" s="30"/>
       <c r="P16" s="32"/>
       <c r="Q16" s="30"/>
@@ -9648,7 +9928,7 @@
       <c r="AH16" s="36"/>
       <c r="AI16" s="30"/>
     </row>
-    <row r="17" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="30"/>
       <c r="B17" s="30"/>
       <c r="C17" s="30"/>
@@ -9685,7 +9965,7 @@
       <c r="AH17" s="36"/>
       <c r="AI17" s="30"/>
     </row>
-    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="30"/>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
@@ -9722,7 +10002,7 @@
       <c r="AH18" s="36"/>
       <c r="AI18" s="30"/>
     </row>
-    <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="30"/>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
@@ -9759,7 +10039,7 @@
       <c r="AH19" s="36"/>
       <c r="AI19" s="30"/>
     </row>
-    <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="30"/>
       <c r="B20" s="30"/>
       <c r="C20" s="30"/>
@@ -9796,10 +10076,11 @@
       <c r="AH20" s="36"/>
       <c r="AI20" s="30"/>
     </row>
-    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="30"/>
       <c r="B21" s="30"/>
       <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
       <c r="E21" s="30"/>
       <c r="F21" s="30"/>
       <c r="G21" s="30"/>
@@ -9832,11 +10113,10 @@
       <c r="AH21" s="36"/>
       <c r="AI21" s="30"/>
     </row>
-    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="30"/>
       <c r="B22" s="30"/>
       <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
       <c r="E22" s="30"/>
       <c r="F22" s="30"/>
       <c r="G22" s="30"/>
@@ -9869,9 +10149,9 @@
       <c r="AH22" s="36"/>
       <c r="AI22" s="30"/>
     </row>
-    <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="30"/>
-      <c r="B23" s="38"/>
+      <c r="B23" s="30"/>
       <c r="C23" s="30"/>
       <c r="D23" s="30"/>
       <c r="E23" s="30"/>
@@ -9883,7 +10163,7 @@
       <c r="K23" s="30"/>
       <c r="L23" s="30"/>
       <c r="M23" s="30"/>
-      <c r="N23" s="35"/>
+      <c r="N23" s="30"/>
       <c r="O23" s="30"/>
       <c r="P23" s="32"/>
       <c r="Q23" s="30"/>
@@ -9906,9 +10186,9 @@
       <c r="AH23" s="36"/>
       <c r="AI23" s="30"/>
     </row>
-    <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
+      <c r="B24" s="38"/>
       <c r="C24" s="30"/>
       <c r="D24" s="30"/>
       <c r="E24" s="30"/>
@@ -9920,7 +10200,7 @@
       <c r="K24" s="30"/>
       <c r="L24" s="30"/>
       <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
+      <c r="N24" s="35"/>
       <c r="O24" s="30"/>
       <c r="P24" s="32"/>
       <c r="Q24" s="30"/>
@@ -9943,7 +10223,7 @@
       <c r="AH24" s="36"/>
       <c r="AI24" s="30"/>
     </row>
-    <row r="25" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="30"/>
       <c r="B25" s="30"/>
       <c r="C25" s="30"/>
@@ -9980,7 +10260,7 @@
       <c r="AH25" s="36"/>
       <c r="AI25" s="30"/>
     </row>
-    <row r="26" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="30"/>
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
@@ -10017,7 +10297,7 @@
       <c r="AH26" s="36"/>
       <c r="AI26" s="30"/>
     </row>
-    <row r="27" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="30"/>
       <c r="B27" s="30"/>
       <c r="C27" s="30"/>
@@ -10054,7 +10334,7 @@
       <c r="AH27" s="36"/>
       <c r="AI27" s="30"/>
     </row>
-    <row r="28" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="30"/>
       <c r="B28" s="30"/>
       <c r="C28" s="30"/>
@@ -10068,7 +10348,7 @@
       <c r="K28" s="30"/>
       <c r="L28" s="30"/>
       <c r="M28" s="30"/>
-      <c r="N28" s="35"/>
+      <c r="N28" s="30"/>
       <c r="O28" s="30"/>
       <c r="P28" s="32"/>
       <c r="Q28" s="30"/>
@@ -10091,7 +10371,7 @@
       <c r="AH28" s="36"/>
       <c r="AI28" s="30"/>
     </row>
-    <row r="29" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="30"/>
       <c r="B29" s="30"/>
       <c r="C29" s="30"/>
@@ -10105,7 +10385,7 @@
       <c r="K29" s="30"/>
       <c r="L29" s="30"/>
       <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
+      <c r="N29" s="35"/>
       <c r="O29" s="30"/>
       <c r="P29" s="32"/>
       <c r="Q29" s="30"/>
@@ -10128,8 +10408,8 @@
       <c r="AH29" s="36"/>
       <c r="AI29" s="30"/>
     </row>
-    <row r="30" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="39"/>
+    <row r="30" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="30"/>
       <c r="B30" s="30"/>
       <c r="C30" s="30"/>
       <c r="D30" s="30"/>
@@ -10149,26 +10429,26 @@
       <c r="R30" s="30"/>
       <c r="S30" s="30"/>
       <c r="T30" s="30"/>
-      <c r="U30" s="39"/>
-      <c r="V30" s="39"/>
-      <c r="W30" s="39"/>
-      <c r="X30" s="39"/>
-      <c r="Y30" s="39"/>
-      <c r="Z30" s="39"/>
-      <c r="AA30" s="39"/>
-      <c r="AB30" s="39"/>
-      <c r="AC30" s="39"/>
-      <c r="AD30" s="39"/>
-      <c r="AE30" s="39"/>
-      <c r="AF30" s="39"/>
-      <c r="AG30" s="40"/>
-      <c r="AH30" s="41"/>
-      <c r="AI30" s="39"/>
-    </row>
-    <row r="31" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U30" s="30"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="30"/>
+      <c r="X30" s="30"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="30"/>
+      <c r="AA30" s="30"/>
+      <c r="AB30" s="30"/>
+      <c r="AC30" s="30"/>
+      <c r="AD30" s="30"/>
+      <c r="AE30" s="30"/>
+      <c r="AF30" s="30"/>
+      <c r="AG30" s="32"/>
+      <c r="AH30" s="36"/>
+      <c r="AI30" s="30"/>
+    </row>
+    <row r="31" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="39"/>
       <c r="B31" s="30"/>
-      <c r="C31" s="32"/>
+      <c r="C31" s="30"/>
       <c r="D31" s="30"/>
       <c r="E31" s="30"/>
       <c r="F31" s="30"/>
@@ -10182,9 +10462,9 @@
       <c r="N31" s="30"/>
       <c r="O31" s="30"/>
       <c r="P31" s="32"/>
-      <c r="Q31" s="36"/>
+      <c r="Q31" s="30"/>
       <c r="R31" s="30"/>
-      <c r="S31" s="42"/>
+      <c r="S31" s="30"/>
       <c r="T31" s="30"/>
       <c r="U31" s="39"/>
       <c r="V31" s="39"/>
@@ -10202,27 +10482,27 @@
       <c r="AH31" s="41"/>
       <c r="AI31" s="39"/>
     </row>
-    <row r="32" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="39"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="39"/>
-      <c r="J32" s="39"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="39"/>
-      <c r="M32" s="39"/>
-      <c r="N32" s="39"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="44"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="32"/>
       <c r="Q32" s="36"/>
-      <c r="R32" s="39"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="39"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="42"/>
+      <c r="T32" s="30"/>
       <c r="U32" s="39"/>
       <c r="V32" s="39"/>
       <c r="W32" s="39"/>
@@ -10239,7 +10519,7 @@
       <c r="AH32" s="41"/>
       <c r="AI32" s="39"/>
     </row>
-    <row r="33" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="39"/>
       <c r="B33" s="39"/>
       <c r="C33" s="30"/>
@@ -10250,7 +10530,7 @@
       <c r="H33" s="39"/>
       <c r="I33" s="39"/>
       <c r="J33" s="39"/>
-      <c r="K33" s="39"/>
+      <c r="K33" s="43"/>
       <c r="L33" s="39"/>
       <c r="M33" s="39"/>
       <c r="N33" s="39"/>
@@ -10258,7 +10538,7 @@
       <c r="P33" s="44"/>
       <c r="Q33" s="36"/>
       <c r="R33" s="39"/>
-      <c r="S33" s="39"/>
+      <c r="S33" s="45"/>
       <c r="T33" s="39"/>
       <c r="U33" s="39"/>
       <c r="V33" s="39"/>
@@ -10276,7 +10556,7 @@
       <c r="AH33" s="41"/>
       <c r="AI33" s="39"/>
     </row>
-    <row r="34" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="39"/>
       <c r="B34" s="39"/>
       <c r="C34" s="30"/>
@@ -10287,7 +10567,7 @@
       <c r="H34" s="39"/>
       <c r="I34" s="39"/>
       <c r="J34" s="39"/>
-      <c r="K34" s="43"/>
+      <c r="K34" s="39"/>
       <c r="L34" s="39"/>
       <c r="M34" s="39"/>
       <c r="N34" s="39"/>
@@ -10295,7 +10575,7 @@
       <c r="P34" s="44"/>
       <c r="Q34" s="36"/>
       <c r="R34" s="39"/>
-      <c r="S34" s="45"/>
+      <c r="S34" s="39"/>
       <c r="T34" s="39"/>
       <c r="U34" s="39"/>
       <c r="V34" s="39"/>
@@ -10313,7 +10593,7 @@
       <c r="AH34" s="41"/>
       <c r="AI34" s="39"/>
     </row>
-    <row r="35" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="39"/>
       <c r="B35" s="39"/>
       <c r="C35" s="30"/>
@@ -10324,7 +10604,7 @@
       <c r="H35" s="39"/>
       <c r="I35" s="39"/>
       <c r="J35" s="39"/>
-      <c r="K35" s="39"/>
+      <c r="K35" s="43"/>
       <c r="L35" s="39"/>
       <c r="M35" s="39"/>
       <c r="N35" s="39"/>
@@ -10332,9 +10612,9 @@
       <c r="P35" s="44"/>
       <c r="Q35" s="36"/>
       <c r="R35" s="39"/>
-      <c r="S35" s="39"/>
+      <c r="S35" s="45"/>
       <c r="T35" s="39"/>
-      <c r="U35" s="46"/>
+      <c r="U35" s="39"/>
       <c r="V35" s="39"/>
       <c r="W35" s="39"/>
       <c r="X35" s="39"/>
@@ -10350,10 +10630,10 @@
       <c r="AH35" s="41"/>
       <c r="AI35" s="39"/>
     </row>
-    <row r="36" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="39"/>
       <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
+      <c r="C36" s="30"/>
       <c r="D36" s="39"/>
       <c r="E36" s="39"/>
       <c r="F36" s="39"/>
@@ -10367,11 +10647,11 @@
       <c r="N36" s="39"/>
       <c r="O36" s="39"/>
       <c r="P36" s="44"/>
-      <c r="Q36" s="41"/>
+      <c r="Q36" s="36"/>
       <c r="R36" s="39"/>
       <c r="S36" s="39"/>
       <c r="T36" s="39"/>
-      <c r="U36" s="39"/>
+      <c r="U36" s="46"/>
       <c r="V36" s="39"/>
       <c r="W36" s="39"/>
       <c r="X36" s="39"/>
@@ -10383,66 +10663,95 @@
       <c r="AD36" s="39"/>
       <c r="AE36" s="39"/>
       <c r="AF36" s="39"/>
-      <c r="AG36" s="39"/>
+      <c r="AG36" s="40"/>
       <c r="AH36" s="41"/>
       <c r="AI36" s="39"/>
     </row>
-    <row r="37" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="P37" s="47"/>
-      <c r="U37" s="49"/>
-      <c r="AG37" s="50"/>
-    </row>
-    <row r="38" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="39"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="39"/>
+      <c r="L37" s="39"/>
+      <c r="M37" s="39"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="44"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="39"/>
+      <c r="S37" s="39"/>
+      <c r="T37" s="39"/>
+      <c r="U37" s="39"/>
+      <c r="V37" s="39"/>
+      <c r="W37" s="39"/>
+      <c r="X37" s="39"/>
+      <c r="Y37" s="39"/>
+      <c r="Z37" s="39"/>
+      <c r="AA37" s="39"/>
+      <c r="AB37" s="39"/>
+      <c r="AC37" s="39"/>
+      <c r="AD37" s="39"/>
+      <c r="AE37" s="39"/>
+      <c r="AF37" s="39"/>
+      <c r="AG37" s="39"/>
+      <c r="AH37" s="41"/>
+      <c r="AI37" s="39"/>
+    </row>
+    <row r="38" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P38" s="47"/>
       <c r="U38" s="49"/>
-      <c r="AF38" s="50"/>
-      <c r="AG38" s="47"/>
-    </row>
-    <row r="39" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="T39" s="49"/>
+      <c r="AG38" s="50"/>
+    </row>
+    <row r="39" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U39" s="49"/>
       <c r="AF39" s="50"/>
-      <c r="AG39" s="50"/>
-    </row>
-    <row r="40" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AG40" s="47"/>
-    </row>
-    <row r="41" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AG39" s="47"/>
+    </row>
+    <row r="40" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="T40" s="49"/>
+      <c r="AF40" s="50"/>
+      <c r="AG40" s="50"/>
+    </row>
+    <row r="41" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AG41" s="47"/>
     </row>
-    <row r="42" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AF42" s="50"/>
+    <row r="42" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AG42" s="47"/>
     </row>
-    <row r="43" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AF43" s="50"/>
-      <c r="AG43" s="50"/>
-    </row>
-    <row r="44" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AG43" s="47"/>
+    </row>
+    <row r="44" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AF44" s="50"/>
       <c r="AG44" s="50"/>
     </row>
-    <row r="45" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AF45" s="50"/>
       <c r="AG45" s="50"/>
     </row>
-    <row r="46" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AF46" s="50"/>
+    <row r="46" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AG46" s="50"/>
     </row>
-    <row r="47" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AF47" s="50"/>
       <c r="AG47" s="50"/>
     </row>
-    <row r="49" spans="33:33" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AG49" s="50"/>
+    <row r="48" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AG48" s="50"/>
+    </row>
+    <row r="50" spans="33:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AG50" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -10452,6 +10761,14 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1"/>
@@ -10466,67 +10783,67 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AW69"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:AW110"/>
+  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="11" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="31" width="3.625" style="30" customWidth="1"/>
-    <col min="32" max="16384" width="3.625" style="30"/>
+    <col min="1" max="31" width="3.6328125" style="30" customWidth="1"/>
+    <col min="32" max="16384" width="3.6328125" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="98" t="s">
-        <v>294</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="101" t="str">
+    <row r="1" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="71" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="74" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="137" t="s">
-        <v>296</v>
-      </c>
-      <c r="P1" s="138"/>
-      <c r="Q1" s="138"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="116" t="str">
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="134" t="s">
+        <v>294</v>
+      </c>
+      <c r="P1" s="135"/>
+      <c r="Q1" s="135"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="89" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarchを使用したシステム開発における標準WBS</v>
       </c>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="118"/>
-      <c r="AA1" s="98" t="s">
+      <c r="T1" s="90"/>
+      <c r="U1" s="90"/>
+      <c r="V1" s="90"/>
+      <c r="W1" s="90"/>
+      <c r="X1" s="90"/>
+      <c r="Y1" s="90"/>
+      <c r="Z1" s="91"/>
+      <c r="AA1" s="71" t="s">
         <v>184</v>
       </c>
-      <c r="AB1" s="100"/>
-      <c r="AC1" s="125" t="str">
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="98" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="126"/>
-      <c r="AE1" s="126"/>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="130">
+      <c r="AD1" s="99"/>
+      <c r="AE1" s="99"/>
+      <c r="AF1" s="100"/>
+      <c r="AG1" s="128">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="131"/>
-      <c r="AI1" s="132"/>
+      <c r="AH1" s="129"/>
+      <c r="AI1" s="130"/>
       <c r="AJ1" s="30"/>
       <c r="AN1" s="51"/>
       <c r="AO1" s="30"/>
@@ -10539,55 +10856,55 @@
       <c r="AV1" s="30"/>
       <c r="AW1" s="30"/>
     </row>
-    <row r="2" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="98" t="s">
-        <v>283</v>
-      </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="101" t="str">
+    <row r="2" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="71" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="74" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="140"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="141"/>
-      <c r="R2" s="142"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="120"/>
-      <c r="Y2" s="120"/>
-      <c r="Z2" s="121"/>
-      <c r="AA2" s="98" t="s">
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="139"/>
+      <c r="S2" s="92"/>
+      <c r="T2" s="93"/>
+      <c r="U2" s="93"/>
+      <c r="V2" s="93"/>
+      <c r="W2" s="93"/>
+      <c r="X2" s="93"/>
+      <c r="Y2" s="93"/>
+      <c r="Z2" s="94"/>
+      <c r="AA2" s="71" t="s">
         <v>185</v>
       </c>
-      <c r="AB2" s="100"/>
-      <c r="AC2" s="125" t="str">
+      <c r="AB2" s="73"/>
+      <c r="AC2" s="98" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="126"/>
-      <c r="AE2" s="126"/>
-      <c r="AF2" s="127"/>
-      <c r="AG2" s="130">
+      <c r="AD2" s="99"/>
+      <c r="AE2" s="99"/>
+      <c r="AF2" s="100"/>
+      <c r="AG2" s="128">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v>44455</v>
       </c>
-      <c r="AH2" s="131"/>
-      <c r="AI2" s="132"/>
+      <c r="AH2" s="129"/>
+      <c r="AI2" s="130"/>
       <c r="AJ2" s="30"/>
       <c r="AN2" s="51"/>
       <c r="AO2" s="30"/>
@@ -10600,53 +10917,53 @@
       <c r="AV2" s="30"/>
       <c r="AW2" s="30"/>
     </row>
-    <row r="3" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="98" t="s">
-        <v>285</v>
-      </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="101" t="str">
+    <row r="3" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="71" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="74" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="143"/>
-      <c r="P3" s="144"/>
-      <c r="Q3" s="144"/>
-      <c r="R3" s="145"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="123"/>
-      <c r="U3" s="123"/>
-      <c r="V3" s="123"/>
-      <c r="W3" s="123"/>
-      <c r="X3" s="123"/>
-      <c r="Y3" s="123"/>
-      <c r="Z3" s="124"/>
-      <c r="AA3" s="98"/>
-      <c r="AB3" s="100"/>
-      <c r="AC3" s="125" t="str">
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="75"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="140"/>
+      <c r="P3" s="141"/>
+      <c r="Q3" s="141"/>
+      <c r="R3" s="142"/>
+      <c r="S3" s="95"/>
+      <c r="T3" s="96"/>
+      <c r="U3" s="96"/>
+      <c r="V3" s="96"/>
+      <c r="W3" s="96"/>
+      <c r="X3" s="96"/>
+      <c r="Y3" s="96"/>
+      <c r="Z3" s="97"/>
+      <c r="AA3" s="71"/>
+      <c r="AB3" s="73"/>
+      <c r="AC3" s="98" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="126"/>
-      <c r="AE3" s="126"/>
-      <c r="AF3" s="127"/>
-      <c r="AG3" s="130" t="str">
+      <c r="AD3" s="99"/>
+      <c r="AE3" s="99"/>
+      <c r="AF3" s="100"/>
+      <c r="AG3" s="128" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="131"/>
-      <c r="AI3" s="132"/>
+      <c r="AH3" s="129"/>
+      <c r="AI3" s="130"/>
       <c r="AJ3" s="53"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
@@ -10662,272 +10979,302 @@
       <c r="AV3" s="52"/>
       <c r="AW3" s="52"/>
     </row>
-    <row r="4" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="6" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="34" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="7" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="7" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="34"/>
     </row>
-    <row r="8" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="34"/>
       <c r="D8" s="54" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="9" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="9" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="34"/>
       <c r="D9" s="54" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="34"/>
       <c r="D10" s="54" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="11" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="34"/>
       <c r="D11" s="54" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="12" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="34"/>
       <c r="D12" s="54" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13" s="34"/>
       <c r="D13" s="54"/>
     </row>
-    <row r="14" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="34"/>
     </row>
-    <row r="15" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="34" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="16" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="34"/>
     </row>
-    <row r="17" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="34"/>
       <c r="D17" s="30" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="18" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="34"/>
     </row>
-    <row r="19" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C19" s="34"/>
     </row>
-    <row r="20" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="34"/>
     </row>
-    <row r="21" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="34"/>
     </row>
-    <row r="22" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C22" s="34"/>
     </row>
-    <row r="23" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="34"/>
     </row>
-    <row r="24" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="34"/>
     </row>
-    <row r="25" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="34"/>
     </row>
-    <row r="26" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C26" s="34"/>
     </row>
-    <row r="27" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C27" s="34"/>
     </row>
-    <row r="28" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C28" s="34"/>
     </row>
-    <row r="29" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C29" s="34"/>
     </row>
-    <row r="30" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C30" s="34"/>
     </row>
-    <row r="31" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C31" s="34"/>
     </row>
-    <row r="32" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C32" s="34"/>
     </row>
-    <row r="33" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C33" s="34"/>
     </row>
-    <row r="34" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C34" s="34"/>
     </row>
-    <row r="35" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C35" s="34"/>
     </row>
-    <row r="36" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C36" s="34"/>
     </row>
-    <row r="37" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C37" s="34"/>
     </row>
-    <row r="38" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C38" s="34"/>
     </row>
-    <row r="39" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C39" s="34"/>
     </row>
-    <row r="40" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C40" s="34"/>
       <c r="D40" s="54" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="41" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C41" s="34"/>
       <c r="D41" s="54" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="42" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C42" s="34"/>
       <c r="D42" s="54"/>
     </row>
-    <row r="43" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C43" s="34"/>
       <c r="D43" s="54" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="44" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C44" s="34"/>
       <c r="D44" s="54" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="45" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="45" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C45" s="34"/>
       <c r="D45" s="54"/>
     </row>
-    <row r="46" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C46" s="34"/>
       <c r="D46" s="54" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C47" s="34"/>
       <c r="D47" s="54" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C48" s="34"/>
       <c r="D48" s="54"/>
     </row>
-    <row r="49" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C49" s="34"/>
-      <c r="D49" s="54"/>
-    </row>
-    <row r="50" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C50" s="34" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="51" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C49" s="34" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C50" s="34"/>
+    </row>
+    <row r="51" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C51" s="34"/>
-    </row>
-    <row r="52" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D51" s="54" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C52" s="34"/>
       <c r="D52" s="54" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="53" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C53" s="34"/>
       <c r="D53" s="54" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="54" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C54" s="34"/>
       <c r="D54" s="54" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="55" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C55" s="34"/>
-      <c r="D55" s="54" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="56" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D55" s="54"/>
+    </row>
+    <row r="56" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C56" s="34"/>
-      <c r="D56" s="54"/>
-    </row>
-    <row r="57" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D56" s="54" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="34"/>
-      <c r="D57" s="54" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D57" s="55" t="s">
+        <v>305</v>
+      </c>
+      <c r="E57" s="143" t="s">
+        <v>107</v>
+      </c>
+      <c r="F57" s="144"/>
+      <c r="G57" s="144"/>
+      <c r="H57" s="144"/>
+      <c r="I57" s="144"/>
+      <c r="J57" s="145"/>
+      <c r="K57" s="143" t="s">
+        <v>178</v>
+      </c>
+      <c r="L57" s="144"/>
+      <c r="M57" s="144"/>
+      <c r="N57" s="144"/>
+      <c r="O57" s="144"/>
+      <c r="P57" s="144"/>
+      <c r="Q57" s="144"/>
+      <c r="R57" s="144"/>
+      <c r="S57" s="144"/>
+      <c r="T57" s="144"/>
+      <c r="U57" s="144"/>
+      <c r="V57" s="144"/>
+      <c r="W57" s="144"/>
+      <c r="X57" s="144"/>
+      <c r="Y57" s="144"/>
+      <c r="Z57" s="144"/>
+      <c r="AA57" s="144"/>
+      <c r="AB57" s="145"/>
+    </row>
+    <row r="58" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C58" s="34"/>
-      <c r="D58" s="55" t="s">
-        <v>307</v>
-      </c>
-      <c r="E58" s="134" t="s">
-        <v>107</v>
-      </c>
-      <c r="F58" s="135"/>
-      <c r="G58" s="135"/>
-      <c r="H58" s="135"/>
-      <c r="I58" s="135"/>
-      <c r="J58" s="136"/>
-      <c r="K58" s="134" t="s">
-        <v>178</v>
-      </c>
-      <c r="L58" s="135"/>
-      <c r="M58" s="135"/>
-      <c r="N58" s="135"/>
-      <c r="O58" s="135"/>
-      <c r="P58" s="135"/>
-      <c r="Q58" s="135"/>
-      <c r="R58" s="135"/>
-      <c r="S58" s="135"/>
-      <c r="T58" s="135"/>
-      <c r="U58" s="135"/>
-      <c r="V58" s="135"/>
-      <c r="W58" s="135"/>
-      <c r="X58" s="135"/>
-      <c r="Y58" s="135"/>
-      <c r="Z58" s="135"/>
-      <c r="AA58" s="135"/>
-      <c r="AB58" s="136"/>
-    </row>
-    <row r="59" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D58" s="56">
+        <v>1</v>
+      </c>
+      <c r="E58" s="133" t="s">
+        <v>34</v>
+      </c>
+      <c r="F58" s="133"/>
+      <c r="G58" s="133"/>
+      <c r="H58" s="133"/>
+      <c r="I58" s="133"/>
+      <c r="J58" s="133"/>
+      <c r="K58" s="133" t="s">
+        <v>18</v>
+      </c>
+      <c r="L58" s="133"/>
+      <c r="M58" s="133"/>
+      <c r="N58" s="133"/>
+      <c r="O58" s="133"/>
+      <c r="P58" s="133"/>
+      <c r="Q58" s="133"/>
+      <c r="R58" s="133"/>
+      <c r="S58" s="133"/>
+      <c r="T58" s="133"/>
+      <c r="U58" s="133"/>
+      <c r="V58" s="133"/>
+      <c r="W58" s="133"/>
+      <c r="X58" s="133"/>
+      <c r="Y58" s="133"/>
+      <c r="Z58" s="133"/>
+      <c r="AA58" s="133"/>
+      <c r="AB58" s="133"/>
+    </row>
+    <row r="59" spans="3:28" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C59" s="34"/>
       <c r="D59" s="56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="133" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F59" s="133"/>
       <c r="G59" s="133"/>
@@ -10935,7 +11282,7 @@
       <c r="I59" s="133"/>
       <c r="J59" s="133"/>
       <c r="K59" s="133" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L59" s="133"/>
       <c r="M59" s="133"/>
@@ -10955,13 +11302,13 @@
       <c r="AA59" s="133"/>
       <c r="AB59" s="133"/>
     </row>
-    <row r="60" spans="3:28" ht="48" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="3:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C60" s="34"/>
       <c r="D60" s="56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" s="133" t="s">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="F60" s="133"/>
       <c r="G60" s="133"/>
@@ -10969,7 +11316,7 @@
       <c r="I60" s="133"/>
       <c r="J60" s="133"/>
       <c r="K60" s="133" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="L60" s="133"/>
       <c r="M60" s="133"/>
@@ -10989,13 +11336,13 @@
       <c r="AA60" s="133"/>
       <c r="AB60" s="133"/>
     </row>
-    <row r="61" spans="3:28" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="3:28" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C61" s="34"/>
       <c r="D61" s="56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E61" s="133" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F61" s="133"/>
       <c r="G61" s="133"/>
@@ -11003,7 +11350,7 @@
       <c r="I61" s="133"/>
       <c r="J61" s="133"/>
       <c r="K61" s="133" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="L61" s="133"/>
       <c r="M61" s="133"/>
@@ -11023,13 +11370,13 @@
       <c r="AA61" s="133"/>
       <c r="AB61" s="133"/>
     </row>
-    <row r="62" spans="3:28" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="3:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C62" s="34"/>
       <c r="D62" s="56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E62" s="133" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F62" s="133"/>
       <c r="G62" s="133"/>
@@ -11037,7 +11384,7 @@
       <c r="I62" s="133"/>
       <c r="J62" s="133"/>
       <c r="K62" s="133" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L62" s="133"/>
       <c r="M62" s="133"/>
@@ -11057,13 +11404,13 @@
       <c r="AA62" s="133"/>
       <c r="AB62" s="133"/>
     </row>
-    <row r="63" spans="3:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="3:28" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C63" s="34"/>
       <c r="D63" s="56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E63" s="133" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="F63" s="133"/>
       <c r="G63" s="133"/>
@@ -11071,7 +11418,7 @@
       <c r="I63" s="133"/>
       <c r="J63" s="133"/>
       <c r="K63" s="133" t="s">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="L63" s="133"/>
       <c r="M63" s="133"/>
@@ -11091,13 +11438,13 @@
       <c r="AA63" s="133"/>
       <c r="AB63" s="133"/>
     </row>
-    <row r="64" spans="3:28" ht="72" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="3:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C64" s="34"/>
       <c r="D64" s="56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E64" s="133" t="s">
-        <v>225</v>
+        <v>155</v>
       </c>
       <c r="F64" s="133"/>
       <c r="G64" s="133"/>
@@ -11105,7 +11452,7 @@
       <c r="I64" s="133"/>
       <c r="J64" s="133"/>
       <c r="K64" s="133" t="s">
-        <v>308</v>
+        <v>221</v>
       </c>
       <c r="L64" s="133"/>
       <c r="M64" s="133"/>
@@ -11125,13 +11472,13 @@
       <c r="AA64" s="133"/>
       <c r="AB64" s="133"/>
     </row>
-    <row r="65" spans="3:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="3:28" ht="108" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C65" s="34"/>
       <c r="D65" s="56">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E65" s="133" t="s">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="F65" s="133"/>
       <c r="G65" s="133"/>
@@ -11139,7 +11486,7 @@
       <c r="I65" s="133"/>
       <c r="J65" s="133"/>
       <c r="K65" s="133" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="L65" s="133"/>
       <c r="M65" s="133"/>
@@ -11159,13 +11506,13 @@
       <c r="AA65" s="133"/>
       <c r="AB65" s="133"/>
     </row>
-    <row r="66" spans="3:28" ht="108" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="3:28" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C66" s="34"/>
       <c r="D66" s="56">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E66" s="133" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F66" s="133"/>
       <c r="G66" s="133"/>
@@ -11173,7 +11520,7 @@
       <c r="I66" s="133"/>
       <c r="J66" s="133"/>
       <c r="K66" s="133" t="s">
-        <v>217</v>
+        <v>22</v>
       </c>
       <c r="L66" s="133"/>
       <c r="M66" s="133"/>
@@ -11193,50 +11540,1056 @@
       <c r="AA66" s="133"/>
       <c r="AB66" s="133"/>
     </row>
-    <row r="67" spans="3:28" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C67" s="34"/>
-      <c r="D67" s="56">
+    </row>
+    <row r="68" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C68" s="34"/>
+    </row>
+    <row r="69" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="C69" s="30" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="71" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="D71" s="30" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="72" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="D72" s="30" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="74" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="D74" s="55" t="s">
+        <v>305</v>
+      </c>
+      <c r="E74" s="153" t="s">
+        <v>361</v>
+      </c>
+      <c r="F74" s="154"/>
+      <c r="G74" s="154"/>
+      <c r="H74" s="154"/>
+      <c r="I74" s="153" t="s">
+        <v>381</v>
+      </c>
+      <c r="J74" s="155"/>
+      <c r="K74" s="154"/>
+      <c r="L74" s="154"/>
+      <c r="M74" s="154"/>
+      <c r="N74" s="154"/>
+      <c r="O74" s="154"/>
+      <c r="P74" s="154"/>
+      <c r="Q74" s="154"/>
+      <c r="R74" s="154"/>
+      <c r="S74" s="154"/>
+      <c r="T74" s="155"/>
+      <c r="U74" s="160"/>
+      <c r="V74" s="161"/>
+      <c r="W74" s="161"/>
+      <c r="X74" s="161"/>
+      <c r="Y74" s="161"/>
+      <c r="Z74" s="161"/>
+      <c r="AA74" s="161"/>
+      <c r="AB74" s="161"/>
+    </row>
+    <row r="75" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="D75" s="150">
+        <v>1</v>
+      </c>
+      <c r="E75" s="150" t="s">
+        <v>362</v>
+      </c>
+      <c r="F75" s="151"/>
+      <c r="G75" s="151"/>
+      <c r="H75" s="151"/>
+      <c r="I75" s="157" t="s">
+        <v>397</v>
+      </c>
+      <c r="J75" s="152"/>
+      <c r="K75" s="151"/>
+      <c r="L75" s="151"/>
+      <c r="M75" s="151"/>
+      <c r="N75" s="151"/>
+      <c r="O75" s="151"/>
+      <c r="P75" s="151"/>
+      <c r="Q75" s="151"/>
+      <c r="R75" s="151"/>
+      <c r="S75" s="151"/>
+      <c r="T75" s="152"/>
+      <c r="U75" s="158"/>
+      <c r="V75" s="159"/>
+      <c r="W75" s="159"/>
+      <c r="X75" s="159"/>
+      <c r="Y75" s="159"/>
+      <c r="Z75" s="159"/>
+      <c r="AA75" s="159"/>
+      <c r="AB75" s="159"/>
+    </row>
+    <row r="76" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="D76" s="150">
+        <v>2</v>
+      </c>
+      <c r="E76" s="150" t="s">
+        <v>363</v>
+      </c>
+      <c r="F76" s="151"/>
+      <c r="G76" s="151"/>
+      <c r="H76" s="151"/>
+      <c r="I76" s="157" t="s">
+        <v>398</v>
+      </c>
+      <c r="J76" s="152"/>
+      <c r="K76" s="151"/>
+      <c r="L76" s="151"/>
+      <c r="M76" s="151"/>
+      <c r="N76" s="151"/>
+      <c r="O76" s="151"/>
+      <c r="P76" s="151"/>
+      <c r="Q76" s="151"/>
+      <c r="R76" s="151"/>
+      <c r="S76" s="151"/>
+      <c r="T76" s="152"/>
+      <c r="U76" s="158"/>
+      <c r="V76" s="159"/>
+      <c r="W76" s="159"/>
+      <c r="X76" s="159"/>
+      <c r="Y76" s="159"/>
+      <c r="Z76" s="159"/>
+      <c r="AA76" s="159"/>
+      <c r="AB76" s="159"/>
+    </row>
+    <row r="77" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="D77" s="150">
+        <v>3</v>
+      </c>
+      <c r="E77" s="150" t="s">
+        <v>364</v>
+      </c>
+      <c r="F77" s="151"/>
+      <c r="G77" s="151"/>
+      <c r="H77" s="151"/>
+      <c r="I77" s="157" t="s">
+        <v>399</v>
+      </c>
+      <c r="J77" s="152"/>
+      <c r="K77" s="151"/>
+      <c r="L77" s="151"/>
+      <c r="M77" s="151"/>
+      <c r="N77" s="151"/>
+      <c r="O77" s="151"/>
+      <c r="P77" s="151"/>
+      <c r="Q77" s="151"/>
+      <c r="R77" s="151"/>
+      <c r="S77" s="151"/>
+      <c r="T77" s="152"/>
+      <c r="U77" s="158"/>
+      <c r="V77" s="159"/>
+      <c r="W77" s="159"/>
+      <c r="X77" s="159"/>
+      <c r="Y77" s="159"/>
+      <c r="Z77" s="159"/>
+      <c r="AA77" s="159"/>
+      <c r="AB77" s="159"/>
+    </row>
+    <row r="78" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="D78" s="150">
+        <v>4</v>
+      </c>
+      <c r="E78" s="150" t="s">
+        <v>365</v>
+      </c>
+      <c r="F78" s="151"/>
+      <c r="G78" s="151"/>
+      <c r="H78" s="151"/>
+      <c r="I78" s="157" t="s">
+        <v>400</v>
+      </c>
+      <c r="J78" s="152"/>
+      <c r="K78" s="151"/>
+      <c r="L78" s="151"/>
+      <c r="M78" s="151"/>
+      <c r="N78" s="151"/>
+      <c r="O78" s="151"/>
+      <c r="P78" s="151"/>
+      <c r="Q78" s="151"/>
+      <c r="R78" s="151"/>
+      <c r="S78" s="151"/>
+      <c r="T78" s="152"/>
+      <c r="U78" s="158"/>
+      <c r="V78" s="159"/>
+      <c r="W78" s="159"/>
+      <c r="X78" s="159"/>
+      <c r="Y78" s="159"/>
+      <c r="Z78" s="159"/>
+      <c r="AA78" s="159"/>
+      <c r="AB78" s="159"/>
+    </row>
+    <row r="79" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="D79" s="150">
+        <v>5</v>
+      </c>
+      <c r="E79" s="150" t="s">
+        <v>366</v>
+      </c>
+      <c r="F79" s="151"/>
+      <c r="G79" s="151"/>
+      <c r="H79" s="151"/>
+      <c r="I79" s="157" t="s">
+        <v>401</v>
+      </c>
+      <c r="J79" s="152"/>
+      <c r="K79" s="151"/>
+      <c r="L79" s="151"/>
+      <c r="M79" s="151"/>
+      <c r="N79" s="151"/>
+      <c r="O79" s="151"/>
+      <c r="P79" s="151"/>
+      <c r="Q79" s="151"/>
+      <c r="R79" s="151"/>
+      <c r="S79" s="151"/>
+      <c r="T79" s="152"/>
+      <c r="U79" s="158"/>
+      <c r="V79" s="159"/>
+      <c r="W79" s="159"/>
+      <c r="X79" s="159"/>
+      <c r="Y79" s="159"/>
+      <c r="Z79" s="159"/>
+      <c r="AA79" s="159"/>
+      <c r="AB79" s="159"/>
+    </row>
+    <row r="80" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="D80" s="150">
+        <v>6</v>
+      </c>
+      <c r="E80" s="150" t="s">
+        <v>367</v>
+      </c>
+      <c r="F80" s="151"/>
+      <c r="G80" s="151"/>
+      <c r="H80" s="151"/>
+      <c r="I80" s="157" t="s">
+        <v>402</v>
+      </c>
+      <c r="J80" s="152"/>
+      <c r="K80" s="151"/>
+      <c r="L80" s="151"/>
+      <c r="M80" s="151"/>
+      <c r="N80" s="151"/>
+      <c r="O80" s="151"/>
+      <c r="P80" s="151"/>
+      <c r="Q80" s="151"/>
+      <c r="R80" s="151"/>
+      <c r="S80" s="151"/>
+      <c r="T80" s="152"/>
+      <c r="U80" s="158"/>
+      <c r="V80" s="159"/>
+      <c r="W80" s="159"/>
+      <c r="X80" s="159"/>
+      <c r="Y80" s="159"/>
+      <c r="Z80" s="159"/>
+      <c r="AA80" s="159"/>
+      <c r="AB80" s="159"/>
+    </row>
+    <row r="81" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D81" s="150">
+        <v>7</v>
+      </c>
+      <c r="E81" s="150" t="s">
+        <v>368</v>
+      </c>
+      <c r="F81" s="151"/>
+      <c r="G81" s="151"/>
+      <c r="H81" s="151"/>
+      <c r="I81" s="157" t="s">
+        <v>403</v>
+      </c>
+      <c r="J81" s="152"/>
+      <c r="K81" s="151"/>
+      <c r="L81" s="151"/>
+      <c r="M81" s="151"/>
+      <c r="N81" s="151"/>
+      <c r="O81" s="151"/>
+      <c r="P81" s="151"/>
+      <c r="Q81" s="151"/>
+      <c r="R81" s="151"/>
+      <c r="S81" s="151"/>
+      <c r="T81" s="152"/>
+      <c r="U81" s="158"/>
+      <c r="V81" s="159"/>
+      <c r="W81" s="159"/>
+      <c r="X81" s="159"/>
+      <c r="Y81" s="159"/>
+      <c r="Z81" s="159"/>
+      <c r="AA81" s="159"/>
+      <c r="AB81" s="159"/>
+    </row>
+    <row r="82" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D82" s="150">
+        <v>8</v>
+      </c>
+      <c r="E82" s="150" t="s">
+        <v>369</v>
+      </c>
+      <c r="F82" s="151"/>
+      <c r="G82" s="151"/>
+      <c r="H82" s="151"/>
+      <c r="I82" s="157" t="s">
+        <v>404</v>
+      </c>
+      <c r="J82" s="152"/>
+      <c r="K82" s="151"/>
+      <c r="L82" s="151"/>
+      <c r="M82" s="151"/>
+      <c r="N82" s="151"/>
+      <c r="O82" s="151"/>
+      <c r="P82" s="151"/>
+      <c r="Q82" s="151"/>
+      <c r="R82" s="151"/>
+      <c r="S82" s="151"/>
+      <c r="T82" s="152"/>
+      <c r="U82" s="158"/>
+      <c r="V82" s="159"/>
+      <c r="W82" s="159"/>
+      <c r="X82" s="159"/>
+      <c r="Y82" s="159"/>
+      <c r="Z82" s="159"/>
+      <c r="AA82" s="159"/>
+      <c r="AB82" s="159"/>
+    </row>
+    <row r="83" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D83" s="150">
         <v>9</v>
       </c>
-      <c r="E67" s="133" t="s">
-        <v>104</v>
-      </c>
-      <c r="F67" s="133"/>
-      <c r="G67" s="133"/>
-      <c r="H67" s="133"/>
-      <c r="I67" s="133"/>
-      <c r="J67" s="133"/>
-      <c r="K67" s="133" t="s">
-        <v>22</v>
-      </c>
-      <c r="L67" s="133"/>
-      <c r="M67" s="133"/>
-      <c r="N67" s="133"/>
-      <c r="O67" s="133"/>
-      <c r="P67" s="133"/>
-      <c r="Q67" s="133"/>
-      <c r="R67" s="133"/>
-      <c r="S67" s="133"/>
-      <c r="T67" s="133"/>
-      <c r="U67" s="133"/>
-      <c r="V67" s="133"/>
-      <c r="W67" s="133"/>
-      <c r="X67" s="133"/>
-      <c r="Y67" s="133"/>
-      <c r="Z67" s="133"/>
-      <c r="AA67" s="133"/>
-      <c r="AB67" s="133"/>
-    </row>
-    <row r="68" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C68" s="34"/>
-    </row>
-    <row r="69" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C69" s="34"/>
+      <c r="E83" s="150" t="s">
+        <v>370</v>
+      </c>
+      <c r="F83" s="151"/>
+      <c r="G83" s="151"/>
+      <c r="H83" s="151"/>
+      <c r="I83" s="157" t="s">
+        <v>405</v>
+      </c>
+      <c r="J83" s="152"/>
+      <c r="K83" s="151"/>
+      <c r="L83" s="151"/>
+      <c r="M83" s="151"/>
+      <c r="N83" s="151"/>
+      <c r="O83" s="151"/>
+      <c r="P83" s="151"/>
+      <c r="Q83" s="151"/>
+      <c r="R83" s="151"/>
+      <c r="S83" s="151"/>
+      <c r="T83" s="152"/>
+      <c r="U83" s="158"/>
+      <c r="V83" s="159"/>
+      <c r="W83" s="159"/>
+      <c r="X83" s="159"/>
+      <c r="Y83" s="159"/>
+      <c r="Z83" s="159"/>
+      <c r="AA83" s="159"/>
+      <c r="AB83" s="159"/>
+    </row>
+    <row r="84" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D84" s="150">
+        <v>10</v>
+      </c>
+      <c r="E84" s="150" t="s">
+        <v>371</v>
+      </c>
+      <c r="F84" s="151"/>
+      <c r="G84" s="151"/>
+      <c r="H84" s="151"/>
+      <c r="I84" s="157" t="s">
+        <v>406</v>
+      </c>
+      <c r="J84" s="152"/>
+      <c r="K84" s="151"/>
+      <c r="L84" s="151"/>
+      <c r="M84" s="151"/>
+      <c r="N84" s="151"/>
+      <c r="O84" s="151"/>
+      <c r="P84" s="151"/>
+      <c r="Q84" s="151"/>
+      <c r="R84" s="151"/>
+      <c r="S84" s="151"/>
+      <c r="T84" s="152"/>
+      <c r="U84" s="158"/>
+      <c r="V84" s="159"/>
+      <c r="W84" s="159"/>
+      <c r="X84" s="159"/>
+      <c r="Y84" s="159"/>
+      <c r="Z84" s="159"/>
+      <c r="AA84" s="159"/>
+      <c r="AB84" s="159"/>
+    </row>
+    <row r="85" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D85" s="150">
+        <v>11</v>
+      </c>
+      <c r="E85" s="150" t="s">
+        <v>372</v>
+      </c>
+      <c r="F85" s="151"/>
+      <c r="G85" s="151"/>
+      <c r="H85" s="151"/>
+      <c r="I85" s="157" t="s">
+        <v>407</v>
+      </c>
+      <c r="J85" s="152"/>
+      <c r="K85" s="151"/>
+      <c r="L85" s="151"/>
+      <c r="M85" s="151"/>
+      <c r="N85" s="151"/>
+      <c r="O85" s="151"/>
+      <c r="P85" s="151"/>
+      <c r="Q85" s="151"/>
+      <c r="R85" s="151"/>
+      <c r="S85" s="151"/>
+      <c r="T85" s="152"/>
+      <c r="U85" s="158"/>
+      <c r="V85" s="159"/>
+      <c r="W85" s="159"/>
+      <c r="X85" s="159"/>
+      <c r="Y85" s="159"/>
+      <c r="Z85" s="159"/>
+      <c r="AA85" s="159"/>
+      <c r="AB85" s="159"/>
+    </row>
+    <row r="86" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D86" s="150">
+        <v>12</v>
+      </c>
+      <c r="E86" s="150" t="s">
+        <v>373</v>
+      </c>
+      <c r="F86" s="151"/>
+      <c r="G86" s="151"/>
+      <c r="H86" s="151"/>
+      <c r="I86" s="157" t="s">
+        <v>408</v>
+      </c>
+      <c r="J86" s="152"/>
+      <c r="K86" s="151"/>
+      <c r="L86" s="151"/>
+      <c r="M86" s="151"/>
+      <c r="N86" s="151"/>
+      <c r="O86" s="151"/>
+      <c r="P86" s="151"/>
+      <c r="Q86" s="151"/>
+      <c r="R86" s="151"/>
+      <c r="S86" s="151"/>
+      <c r="T86" s="152"/>
+      <c r="U86" s="158"/>
+      <c r="V86" s="159"/>
+      <c r="W86" s="159"/>
+      <c r="X86" s="159"/>
+      <c r="Y86" s="159"/>
+      <c r="Z86" s="159"/>
+      <c r="AA86" s="159"/>
+      <c r="AB86" s="159"/>
+    </row>
+    <row r="87" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D87" s="150">
+        <v>13</v>
+      </c>
+      <c r="E87" s="150" t="s">
+        <v>374</v>
+      </c>
+      <c r="F87" s="151"/>
+      <c r="G87" s="151"/>
+      <c r="H87" s="151"/>
+      <c r="I87" s="157" t="s">
+        <v>409</v>
+      </c>
+      <c r="J87" s="152"/>
+      <c r="K87" s="151"/>
+      <c r="L87" s="151"/>
+      <c r="M87" s="151"/>
+      <c r="N87" s="151"/>
+      <c r="O87" s="151"/>
+      <c r="P87" s="151"/>
+      <c r="Q87" s="151"/>
+      <c r="R87" s="151"/>
+      <c r="S87" s="151"/>
+      <c r="T87" s="152"/>
+      <c r="U87" s="158"/>
+      <c r="V87" s="159"/>
+      <c r="W87" s="159"/>
+      <c r="X87" s="159"/>
+      <c r="Y87" s="159"/>
+      <c r="Z87" s="159"/>
+      <c r="AA87" s="159"/>
+      <c r="AB87" s="159"/>
+    </row>
+    <row r="88" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D88" s="150">
+        <v>14</v>
+      </c>
+      <c r="E88" s="150" t="s">
+        <v>375</v>
+      </c>
+      <c r="F88" s="151"/>
+      <c r="G88" s="151"/>
+      <c r="H88" s="151"/>
+      <c r="I88" s="157" t="s">
+        <v>410</v>
+      </c>
+      <c r="J88" s="152"/>
+      <c r="K88" s="151"/>
+      <c r="L88" s="151"/>
+      <c r="M88" s="151"/>
+      <c r="N88" s="151"/>
+      <c r="O88" s="151"/>
+      <c r="P88" s="151"/>
+      <c r="Q88" s="151"/>
+      <c r="R88" s="151"/>
+      <c r="S88" s="151"/>
+      <c r="T88" s="152"/>
+      <c r="U88" s="158"/>
+      <c r="V88" s="159"/>
+      <c r="W88" s="159"/>
+      <c r="X88" s="159"/>
+      <c r="Y88" s="159"/>
+      <c r="Z88" s="159"/>
+      <c r="AA88" s="159"/>
+      <c r="AB88" s="159"/>
+    </row>
+    <row r="89" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D89" s="150">
+        <v>15</v>
+      </c>
+      <c r="E89" s="150" t="s">
+        <v>376</v>
+      </c>
+      <c r="F89" s="151"/>
+      <c r="G89" s="151"/>
+      <c r="H89" s="151"/>
+      <c r="I89" s="157" t="s">
+        <v>411</v>
+      </c>
+      <c r="J89" s="152"/>
+      <c r="K89" s="151"/>
+      <c r="L89" s="151"/>
+      <c r="M89" s="151"/>
+      <c r="N89" s="151"/>
+      <c r="O89" s="151"/>
+      <c r="P89" s="151"/>
+      <c r="Q89" s="151"/>
+      <c r="R89" s="151"/>
+      <c r="S89" s="151"/>
+      <c r="T89" s="152"/>
+      <c r="U89" s="158"/>
+      <c r="V89" s="159"/>
+      <c r="W89" s="159"/>
+      <c r="X89" s="159"/>
+      <c r="Y89" s="159"/>
+      <c r="Z89" s="159"/>
+      <c r="AA89" s="159"/>
+      <c r="AB89" s="159"/>
+    </row>
+    <row r="90" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D90" s="150">
+        <v>16</v>
+      </c>
+      <c r="E90" s="150" t="s">
+        <v>377</v>
+      </c>
+      <c r="F90" s="151"/>
+      <c r="G90" s="151"/>
+      <c r="H90" s="151"/>
+      <c r="I90" s="157" t="s">
+        <v>412</v>
+      </c>
+      <c r="J90" s="152"/>
+      <c r="K90" s="151"/>
+      <c r="L90" s="151"/>
+      <c r="M90" s="151"/>
+      <c r="N90" s="151"/>
+      <c r="O90" s="151"/>
+      <c r="P90" s="151"/>
+      <c r="Q90" s="151"/>
+      <c r="R90" s="151"/>
+      <c r="S90" s="151"/>
+      <c r="T90" s="152"/>
+      <c r="U90" s="158"/>
+      <c r="V90" s="159"/>
+      <c r="W90" s="159"/>
+      <c r="X90" s="159"/>
+      <c r="Y90" s="159"/>
+      <c r="Z90" s="159"/>
+      <c r="AA90" s="159"/>
+      <c r="AB90" s="159"/>
+    </row>
+    <row r="91" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D91" s="150">
+        <v>17</v>
+      </c>
+      <c r="E91" s="150" t="s">
+        <v>378</v>
+      </c>
+      <c r="F91" s="151"/>
+      <c r="G91" s="151"/>
+      <c r="H91" s="151"/>
+      <c r="I91" s="157" t="s">
+        <v>413</v>
+      </c>
+      <c r="J91" s="152"/>
+      <c r="K91" s="151"/>
+      <c r="L91" s="151"/>
+      <c r="M91" s="151"/>
+      <c r="N91" s="151"/>
+      <c r="O91" s="151"/>
+      <c r="P91" s="151"/>
+      <c r="Q91" s="151"/>
+      <c r="R91" s="151"/>
+      <c r="S91" s="151"/>
+      <c r="T91" s="152"/>
+      <c r="U91" s="158"/>
+      <c r="V91" s="159"/>
+      <c r="W91" s="159"/>
+      <c r="X91" s="159"/>
+      <c r="Y91" s="159"/>
+      <c r="Z91" s="159"/>
+      <c r="AA91" s="159"/>
+      <c r="AB91" s="159"/>
+    </row>
+    <row r="92" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D92" s="150">
+        <v>18</v>
+      </c>
+      <c r="E92" s="150" t="s">
+        <v>379</v>
+      </c>
+      <c r="F92" s="151"/>
+      <c r="G92" s="151"/>
+      <c r="H92" s="151"/>
+      <c r="I92" s="157" t="s">
+        <v>414</v>
+      </c>
+      <c r="J92" s="152"/>
+      <c r="K92" s="151"/>
+      <c r="L92" s="151"/>
+      <c r="M92" s="151"/>
+      <c r="N92" s="151"/>
+      <c r="O92" s="151"/>
+      <c r="P92" s="151"/>
+      <c r="Q92" s="151"/>
+      <c r="R92" s="151"/>
+      <c r="S92" s="151"/>
+      <c r="T92" s="152"/>
+      <c r="U92" s="158"/>
+      <c r="V92" s="159"/>
+      <c r="W92" s="159"/>
+      <c r="X92" s="159"/>
+      <c r="Y92" s="159"/>
+      <c r="Z92" s="159"/>
+      <c r="AA92" s="159"/>
+      <c r="AB92" s="159"/>
+    </row>
+    <row r="93" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D93" s="150">
+        <v>19</v>
+      </c>
+      <c r="E93" s="150" t="s">
+        <v>380</v>
+      </c>
+      <c r="F93" s="151"/>
+      <c r="G93" s="151"/>
+      <c r="H93" s="151"/>
+      <c r="I93" s="157" t="s">
+        <v>415</v>
+      </c>
+      <c r="J93" s="152"/>
+      <c r="K93" s="151"/>
+      <c r="L93" s="151"/>
+      <c r="M93" s="151"/>
+      <c r="N93" s="151"/>
+      <c r="O93" s="151"/>
+      <c r="P93" s="151"/>
+      <c r="Q93" s="151"/>
+      <c r="R93" s="151"/>
+      <c r="S93" s="151"/>
+      <c r="T93" s="152"/>
+      <c r="U93" s="158"/>
+      <c r="V93" s="159"/>
+      <c r="W93" s="159"/>
+      <c r="X93" s="159"/>
+      <c r="Y93" s="159"/>
+      <c r="Z93" s="159"/>
+      <c r="AA93" s="159"/>
+      <c r="AB93" s="159"/>
+    </row>
+    <row r="96" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D96" s="30" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="97" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D97" s="30" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="98" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D98" s="30" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="99" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D99" s="30" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="101" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D101" s="55" t="s">
+        <v>305</v>
+      </c>
+      <c r="E101" s="153" t="s">
+        <v>419</v>
+      </c>
+      <c r="F101" s="154"/>
+      <c r="G101" s="154"/>
+      <c r="H101" s="154"/>
+      <c r="I101" s="154"/>
+      <c r="J101" s="154"/>
+      <c r="K101" s="154"/>
+      <c r="L101" s="154"/>
+      <c r="M101" s="154"/>
+      <c r="N101" s="155"/>
+      <c r="O101" s="153" t="s">
+        <v>420</v>
+      </c>
+      <c r="P101" s="154"/>
+      <c r="Q101" s="154"/>
+      <c r="R101" s="154"/>
+      <c r="S101" s="154"/>
+      <c r="T101" s="154"/>
+      <c r="U101" s="154"/>
+      <c r="V101" s="154"/>
+      <c r="W101" s="154"/>
+      <c r="X101" s="154"/>
+      <c r="Y101" s="154"/>
+      <c r="Z101" s="154"/>
+      <c r="AA101" s="154"/>
+      <c r="AB101" s="155"/>
+    </row>
+    <row r="102" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D102" s="150">
+        <v>1</v>
+      </c>
+      <c r="E102" s="150" t="s">
+        <v>383</v>
+      </c>
+      <c r="F102" s="151"/>
+      <c r="G102" s="151"/>
+      <c r="H102" s="151"/>
+      <c r="I102" s="151"/>
+      <c r="J102" s="151"/>
+      <c r="K102" s="151"/>
+      <c r="L102" s="151"/>
+      <c r="M102" s="151"/>
+      <c r="N102" s="152"/>
+      <c r="O102" s="156" t="s">
+        <v>396</v>
+      </c>
+      <c r="P102" s="151"/>
+      <c r="Q102" s="151"/>
+      <c r="R102" s="151"/>
+      <c r="S102" s="151"/>
+      <c r="T102" s="151"/>
+      <c r="U102" s="151"/>
+      <c r="V102" s="151"/>
+      <c r="W102" s="151"/>
+      <c r="X102" s="151"/>
+      <c r="Y102" s="151"/>
+      <c r="Z102" s="151"/>
+      <c r="AA102" s="151"/>
+      <c r="AB102" s="152"/>
+    </row>
+    <row r="103" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D103" s="150">
+        <v>2</v>
+      </c>
+      <c r="E103" s="150" t="s">
+        <v>384</v>
+      </c>
+      <c r="F103" s="151"/>
+      <c r="G103" s="151"/>
+      <c r="H103" s="151"/>
+      <c r="I103" s="151"/>
+      <c r="J103" s="151"/>
+      <c r="K103" s="151"/>
+      <c r="L103" s="151"/>
+      <c r="M103" s="151"/>
+      <c r="N103" s="152"/>
+      <c r="O103" s="156" t="s">
+        <v>385</v>
+      </c>
+      <c r="P103" s="151"/>
+      <c r="Q103" s="151"/>
+      <c r="R103" s="151"/>
+      <c r="S103" s="151"/>
+      <c r="T103" s="151"/>
+      <c r="U103" s="151"/>
+      <c r="V103" s="151"/>
+      <c r="W103" s="151"/>
+      <c r="X103" s="151"/>
+      <c r="Y103" s="151"/>
+      <c r="Z103" s="151"/>
+      <c r="AA103" s="151"/>
+      <c r="AB103" s="152"/>
+    </row>
+    <row r="104" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D104" s="150">
+        <v>3</v>
+      </c>
+      <c r="E104" s="150" t="s">
+        <v>386</v>
+      </c>
+      <c r="F104" s="151"/>
+      <c r="G104" s="151"/>
+      <c r="H104" s="151"/>
+      <c r="I104" s="151"/>
+      <c r="J104" s="151"/>
+      <c r="K104" s="151"/>
+      <c r="L104" s="151"/>
+      <c r="M104" s="151"/>
+      <c r="N104" s="152"/>
+      <c r="O104" s="156" t="s">
+        <v>387</v>
+      </c>
+      <c r="P104" s="151"/>
+      <c r="Q104" s="151"/>
+      <c r="R104" s="151"/>
+      <c r="S104" s="151"/>
+      <c r="T104" s="151"/>
+      <c r="U104" s="151"/>
+      <c r="V104" s="151"/>
+      <c r="W104" s="151"/>
+      <c r="X104" s="151"/>
+      <c r="Y104" s="151"/>
+      <c r="Z104" s="151"/>
+      <c r="AA104" s="151"/>
+      <c r="AB104" s="152"/>
+    </row>
+    <row r="105" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D105" s="150">
+        <v>4</v>
+      </c>
+      <c r="E105" s="150" t="s">
+        <v>388</v>
+      </c>
+      <c r="F105" s="151"/>
+      <c r="G105" s="151"/>
+      <c r="H105" s="151"/>
+      <c r="I105" s="151"/>
+      <c r="J105" s="151"/>
+      <c r="K105" s="151"/>
+      <c r="L105" s="151"/>
+      <c r="M105" s="151"/>
+      <c r="N105" s="152"/>
+      <c r="O105" s="156" t="s">
+        <v>389</v>
+      </c>
+      <c r="P105" s="151"/>
+      <c r="Q105" s="151"/>
+      <c r="R105" s="151"/>
+      <c r="S105" s="151"/>
+      <c r="T105" s="151"/>
+      <c r="U105" s="151"/>
+      <c r="V105" s="151"/>
+      <c r="W105" s="151"/>
+      <c r="X105" s="151"/>
+      <c r="Y105" s="151"/>
+      <c r="Z105" s="151"/>
+      <c r="AA105" s="151"/>
+      <c r="AB105" s="152"/>
+    </row>
+    <row r="106" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D106" s="150">
+        <v>5</v>
+      </c>
+      <c r="E106" s="150" t="s">
+        <v>390</v>
+      </c>
+      <c r="F106" s="151"/>
+      <c r="G106" s="151"/>
+      <c r="H106" s="151"/>
+      <c r="I106" s="151"/>
+      <c r="J106" s="151"/>
+      <c r="K106" s="151"/>
+      <c r="L106" s="151"/>
+      <c r="M106" s="151"/>
+      <c r="N106" s="152"/>
+      <c r="O106" s="156" t="s">
+        <v>391</v>
+      </c>
+      <c r="P106" s="151"/>
+      <c r="Q106" s="151"/>
+      <c r="R106" s="151"/>
+      <c r="S106" s="151"/>
+      <c r="T106" s="151"/>
+      <c r="U106" s="151"/>
+      <c r="V106" s="151"/>
+      <c r="W106" s="151"/>
+      <c r="X106" s="151"/>
+      <c r="Y106" s="151"/>
+      <c r="Z106" s="151"/>
+      <c r="AA106" s="151"/>
+      <c r="AB106" s="152"/>
+    </row>
+    <row r="107" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D107" s="150">
+        <v>6</v>
+      </c>
+      <c r="E107" s="150" t="s">
+        <v>392</v>
+      </c>
+      <c r="F107" s="151"/>
+      <c r="G107" s="151"/>
+      <c r="H107" s="151"/>
+      <c r="I107" s="151"/>
+      <c r="J107" s="151"/>
+      <c r="K107" s="151"/>
+      <c r="L107" s="151"/>
+      <c r="M107" s="151"/>
+      <c r="N107" s="152"/>
+      <c r="O107" s="156" t="s">
+        <v>393</v>
+      </c>
+      <c r="P107" s="151"/>
+      <c r="Q107" s="151"/>
+      <c r="R107" s="151"/>
+      <c r="S107" s="151"/>
+      <c r="T107" s="151"/>
+      <c r="U107" s="151"/>
+      <c r="V107" s="151"/>
+      <c r="W107" s="151"/>
+      <c r="X107" s="151"/>
+      <c r="Y107" s="151"/>
+      <c r="Z107" s="151"/>
+      <c r="AA107" s="151"/>
+      <c r="AB107" s="152"/>
+    </row>
+    <row r="108" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D108" s="150">
+        <v>7</v>
+      </c>
+      <c r="E108" s="150" t="s">
+        <v>394</v>
+      </c>
+      <c r="F108" s="151"/>
+      <c r="G108" s="151"/>
+      <c r="H108" s="151"/>
+      <c r="I108" s="151"/>
+      <c r="J108" s="151"/>
+      <c r="K108" s="151"/>
+      <c r="L108" s="151"/>
+      <c r="M108" s="151"/>
+      <c r="N108" s="152"/>
+      <c r="O108" s="156" t="s">
+        <v>395</v>
+      </c>
+      <c r="P108" s="151"/>
+      <c r="Q108" s="151"/>
+      <c r="R108" s="151"/>
+      <c r="S108" s="151"/>
+      <c r="T108" s="151"/>
+      <c r="U108" s="151"/>
+      <c r="V108" s="151"/>
+      <c r="W108" s="151"/>
+      <c r="X108" s="151"/>
+      <c r="Y108" s="151"/>
+      <c r="Z108" s="151"/>
+      <c r="AA108" s="151"/>
+      <c r="AB108" s="152"/>
+    </row>
+    <row r="109" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D109" s="149">
+        <v>8</v>
+      </c>
+      <c r="E109" s="150" t="s">
+        <v>421</v>
+      </c>
+      <c r="F109" s="151"/>
+      <c r="G109" s="151"/>
+      <c r="H109" s="151"/>
+      <c r="I109" s="151"/>
+      <c r="J109" s="151"/>
+      <c r="K109" s="151"/>
+      <c r="L109" s="151"/>
+      <c r="M109" s="151"/>
+      <c r="N109" s="152"/>
+      <c r="O109" s="157" t="s">
+        <v>422</v>
+      </c>
+      <c r="P109" s="151"/>
+      <c r="Q109" s="151"/>
+      <c r="R109" s="151"/>
+      <c r="S109" s="151"/>
+      <c r="T109" s="151"/>
+      <c r="U109" s="151"/>
+      <c r="V109" s="151"/>
+      <c r="W109" s="151"/>
+      <c r="X109" s="151"/>
+      <c r="Y109" s="151"/>
+      <c r="Z109" s="151"/>
+      <c r="AA109" s="151"/>
+      <c r="AB109" s="152"/>
+    </row>
+    <row r="110" spans="4:28" x14ac:dyDescent="0.2">
+      <c r="D110" s="159"/>
+      <c r="E110" s="159"/>
+      <c r="F110" s="159"/>
+      <c r="G110" s="159"/>
+      <c r="H110" s="159"/>
+      <c r="I110" s="159"/>
+      <c r="J110" s="159"/>
+      <c r="K110" s="159"/>
+      <c r="L110" s="159"/>
+      <c r="M110" s="159"/>
+      <c r="N110" s="159"/>
+      <c r="O110" s="162"/>
+      <c r="P110" s="159"/>
+      <c r="Q110" s="159"/>
+      <c r="R110" s="159"/>
+      <c r="S110" s="159"/>
+      <c r="T110" s="159"/>
+      <c r="U110" s="159"/>
+      <c r="V110" s="159"/>
+      <c r="W110" s="159"/>
+      <c r="X110" s="159"/>
+      <c r="Y110" s="159"/>
+      <c r="Z110" s="159"/>
+      <c r="AA110" s="159"/>
+      <c r="AB110" s="159"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="E66:J66"/>
+    <mergeCell ref="K66:AB66"/>
+    <mergeCell ref="E63:J63"/>
+    <mergeCell ref="K63:AB63"/>
+    <mergeCell ref="E64:J64"/>
+    <mergeCell ref="K64:AB64"/>
+    <mergeCell ref="E65:J65"/>
+    <mergeCell ref="K65:AB65"/>
     <mergeCell ref="E60:J60"/>
     <mergeCell ref="K60:AB60"/>
+    <mergeCell ref="E61:J61"/>
+    <mergeCell ref="K61:AB61"/>
+    <mergeCell ref="E62:J62"/>
+    <mergeCell ref="K62:AB62"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="E57:J57"/>
+    <mergeCell ref="K57:AB57"/>
+    <mergeCell ref="E58:J58"/>
+    <mergeCell ref="K58:AB58"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="E59:J59"/>
+    <mergeCell ref="K59:AB59"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
@@ -11251,39 +12604,47 @@
     <mergeCell ref="AC1:AF1"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="E58:J58"/>
-    <mergeCell ref="K58:AB58"/>
-    <mergeCell ref="E59:J59"/>
-    <mergeCell ref="K59:AB59"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="E61:J61"/>
-    <mergeCell ref="K61:AB61"/>
-    <mergeCell ref="E62:J62"/>
-    <mergeCell ref="K62:AB62"/>
-    <mergeCell ref="E63:J63"/>
-    <mergeCell ref="K63:AB63"/>
-    <mergeCell ref="E67:J67"/>
-    <mergeCell ref="K67:AB67"/>
-    <mergeCell ref="E64:J64"/>
-    <mergeCell ref="K64:AB64"/>
-    <mergeCell ref="E65:J65"/>
-    <mergeCell ref="K65:AB65"/>
-    <mergeCell ref="E66:J66"/>
-    <mergeCell ref="K66:AB66"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
+  <hyperlinks>
+    <hyperlink ref="AB75" r:id="rId1" display="https://jakarta.ee/specifications/faces/" xr:uid="{072C18AF-609F-4653-9808-3595E12CDA8B}"/>
+    <hyperlink ref="AB76" r:id="rId2" display="https://jakarta.ee/specifications/authentication/" xr:uid="{0A797D20-605F-46BB-ADCC-B14FE0BAE9E6}"/>
+    <hyperlink ref="AB77" r:id="rId3" display="https://jakarta.ee/specifications/authorization/" xr:uid="{DEEA3D02-1151-4A12-AE68-04AD5A22943B}"/>
+    <hyperlink ref="AB78" r:id="rId4" display="https://jakarta.ee/specifications/messaging/" xr:uid="{D8FBB6FF-C55B-4709-82BA-8B942F0EE8F3}"/>
+    <hyperlink ref="AB79" r:id="rId5" display="https://jakarta.ee/specifications/persistence/" xr:uid="{2B13828B-C59E-461B-BDE8-DF64D4AA2EBD}"/>
+    <hyperlink ref="AB80" r:id="rId6" display="https://jakarta.ee/specifications/transactions/" xr:uid="{4B4DFC95-691A-43EF-9BA6-3F253F48DED8}"/>
+    <hyperlink ref="AB81" r:id="rId7" display="https://jakarta.ee/specifications/batch/" xr:uid="{BDBD61B2-5A98-4723-9582-4D624CD9BC90}"/>
+    <hyperlink ref="AB82" r:id="rId8" display="https://jakarta.ee/specifications/connectors/" xr:uid="{63C049C0-B50F-4413-8D9E-D92B11C0DCB8}"/>
+    <hyperlink ref="AB83" r:id="rId9" display="https://jakarta.ee/specifications/activation/" xr:uid="{AB9F409E-AB6B-4558-A403-A228A8ABDA31}"/>
+    <hyperlink ref="AB84" r:id="rId10" display="https://jakarta.ee/specifications/expression-language/" xr:uid="{F62A3EF1-C282-4BCC-98A5-A6CA71C650B4}"/>
+    <hyperlink ref="AB85" r:id="rId11" display="https://jakarta.ee/specifications/enterprise-beans/" xr:uid="{704C23F0-9669-4135-B37D-FF9FAF28013A}"/>
+    <hyperlink ref="AB86" r:id="rId12" display="https://jakarta.ee/specifications/xml-binding/" xr:uid="{72A38165-5E11-4AE4-A696-C0EDB438F3FC}"/>
+    <hyperlink ref="AB87" r:id="rId13" display="https://jakarta.ee/specifications/jsonb/" xr:uid="{0C3AD5D6-3AFC-4F21-8554-C2193029568C}"/>
+    <hyperlink ref="AB88" r:id="rId14" display="https://jakarta.ee/specifications/jsonp/" xr:uid="{C91A89E6-4BB2-4045-AAFF-4A88EACA4FE5}"/>
+    <hyperlink ref="AB89" r:id="rId15" display="https://jakarta.ee/specifications/pages/" xr:uid="{E897019C-0949-48DE-8AA1-C7CAA399C7DE}"/>
+    <hyperlink ref="AB90" r:id="rId16" display="https://jakarta.ee/specifications/xml-web-services/" xr:uid="{BEBFEE85-BD91-44D7-BB2A-683DD7731328}"/>
+    <hyperlink ref="AB91" r:id="rId17" display="https://jakarta.ee/specifications/restful-ws/" xr:uid="{02390528-EB8B-4E6A-B1E9-9B563A6E8657}"/>
+    <hyperlink ref="AB92" r:id="rId18" display="https://jakarta.ee/specifications/tags/" xr:uid="{429F9649-389A-4EB4-A123-299AE69673C7}"/>
+    <hyperlink ref="AB93" r:id="rId19" display="https://jakarta.ee/specifications/cdi/" xr:uid="{0CBA927F-33E0-472C-B599-04E03CFEE5F6}"/>
+    <hyperlink ref="AB102" r:id="rId20" display="https://jakarta.ee/specifications/faces/" xr:uid="{3E8E8F6C-8C72-40CF-90F3-35DE205672A0}"/>
+    <hyperlink ref="AB103" r:id="rId21" display="https://jakarta.ee/specifications/authentication/" xr:uid="{EB5AB972-B2E5-4B5F-9185-8F2CDFCAEB9B}"/>
+    <hyperlink ref="AB104" r:id="rId22" display="https://jakarta.ee/specifications/authorization/" xr:uid="{07E3270E-64D8-4A50-A6C6-BEEEE196DEB6}"/>
+    <hyperlink ref="AB105" r:id="rId23" display="https://jakarta.ee/specifications/messaging/" xr:uid="{AF693CDB-C111-4E42-8805-6684D9EF64E5}"/>
+    <hyperlink ref="AB106" r:id="rId24" display="https://jakarta.ee/specifications/persistence/" xr:uid="{5C4CCC92-67D4-4D1D-B038-94E70D323BE5}"/>
+    <hyperlink ref="AB107" r:id="rId25" display="https://jakarta.ee/specifications/transactions/" xr:uid="{ECB6D077-F239-426A-B765-A5E1E83B5C4A}"/>
+    <hyperlink ref="AB108" r:id="rId26" display="https://jakarta.ee/specifications/batch/" xr:uid="{4E6AFAFA-315B-4DD7-A090-F4A2D1103E20}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId27"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;C- &amp;P -</oddFooter>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="48" max="34" man="1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="47" max="34" man="1"/>
+    <brk id="67" max="34" man="1"/>
   </rowBreaks>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId28"/>
 </worksheet>
 </file>
 
@@ -11293,22 +12654,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K49"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.375" style="10" customWidth="1"/>
-    <col min="2" max="2" width="21.75" style="10" customWidth="1"/>
-    <col min="3" max="3" width="25.625" style="11" customWidth="1"/>
-    <col min="4" max="4" width="35.625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="41.875" style="10" customWidth="1"/>
+    <col min="1" max="1" width="4.36328125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="21.7265625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="25.6328125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="35.6328125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="41.90625" style="10" customWidth="1"/>
     <col min="6" max="6" width="3" style="12" customWidth="1"/>
-    <col min="7" max="7" width="25.625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="25.6328125" style="10" customWidth="1"/>
     <col min="8" max="10" width="3" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="32.5" style="10" customWidth="1"/>
-    <col min="12" max="12" width="1.625" style="10" customWidth="1"/>
+    <col min="11" max="11" width="32.453125" style="10" customWidth="1"/>
+    <col min="12" max="12" width="1.6328125" style="10" customWidth="1"/>
     <col min="13" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="146" t="s">
         <v>34</v>
       </c>
@@ -11339,7 +12700,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="146"/>
       <c r="B2" s="146"/>
       <c r="C2" s="147"/>
@@ -11358,7 +12719,7 @@
       </c>
       <c r="K2" s="146"/>
     </row>
-    <row r="3" spans="1:11" ht="101.25" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" ht="99" x14ac:dyDescent="0.2">
       <c r="A3" s="57" t="s">
         <v>31</v>
       </c>
@@ -11372,26 +12733,26 @@
         <v>210</v>
       </c>
       <c r="E3" s="57" t="s">
+        <v>247</v>
+      </c>
+      <c r="F3" s="58" t="s">
         <v>248</v>
-      </c>
-      <c r="F3" s="58" t="s">
-        <v>249</v>
       </c>
       <c r="G3" s="57"/>
       <c r="H3" s="59" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I3" s="59" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J3" s="59" t="s">
         <v>115</v>
       </c>
       <c r="K3" s="57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="191.25" x14ac:dyDescent="0.15">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="187" x14ac:dyDescent="0.2">
       <c r="A4" s="57" t="s">
         <v>31</v>
       </c>
@@ -11421,10 +12782,10 @@
         <v>114</v>
       </c>
       <c r="K4" s="57" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.15">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="44" x14ac:dyDescent="0.2">
       <c r="A5" s="57" t="s">
         <v>31</v>
       </c>
@@ -11438,17 +12799,17 @@
         <v>129</v>
       </c>
       <c r="E5" s="57" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I5" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J5" s="59" t="s">
         <v>115</v>
@@ -11457,7 +12818,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="33.75" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" ht="33" x14ac:dyDescent="0.2">
       <c r="A6" s="57" t="s">
         <v>31</v>
       </c>
@@ -11471,35 +12832,35 @@
         <v>158</v>
       </c>
       <c r="E6" s="57" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F6" s="58" t="s">
         <v>53</v>
       </c>
       <c r="G6" s="57"/>
       <c r="H6" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J6" s="59" t="s">
         <v>126</v>
       </c>
       <c r="K6" s="57"/>
     </row>
-    <row r="7" spans="1:11" ht="157.5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" ht="165" x14ac:dyDescent="0.2">
       <c r="A7" s="57" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C7" s="61" t="s">
         <v>100</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E7" s="57" t="s">
         <v>82</v>
@@ -11508,7 +12869,7 @@
         <v>47</v>
       </c>
       <c r="G7" s="57" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H7" s="59" t="s">
         <v>123</v>
@@ -11520,10 +12881,10 @@
         <v>123</v>
       </c>
       <c r="K7" s="57" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="56.25" x14ac:dyDescent="0.15">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="55" x14ac:dyDescent="0.2">
       <c r="A8" s="57" t="s">
         <v>31</v>
       </c>
@@ -11549,27 +12910,27 @@
         <v>113</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J8" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K8" s="57" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="372.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" ht="372.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="57" t="s">
         <v>31</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C9" s="61" t="s">
         <v>36</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E9" s="57" t="s">
         <v>73</v>
@@ -11584,16 +12945,16 @@
         <v>113</v>
       </c>
       <c r="I9" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J9" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K9" s="57" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.15">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="44" x14ac:dyDescent="0.2">
       <c r="A10" s="57" t="s">
         <v>31</v>
       </c>
@@ -11607,10 +12968,10 @@
         <v>161</v>
       </c>
       <c r="E10" s="57" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G10" s="57" t="s">
         <v>51</v>
@@ -11619,16 +12980,16 @@
         <v>114</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J10" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K10" s="57" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="337.5" x14ac:dyDescent="0.15">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="330" x14ac:dyDescent="0.2">
       <c r="A11" s="57" t="s">
         <v>31</v>
       </c>
@@ -11642,26 +13003,26 @@
         <v>165</v>
       </c>
       <c r="E11" s="57" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G11" s="57"/>
       <c r="H11" s="59" t="s">
         <v>112</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J11" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K11" s="57" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="57" t="s">
         <v>31</v>
       </c>
@@ -11675,26 +13036,26 @@
         <v>165</v>
       </c>
       <c r="E12" s="57" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G12" s="57"/>
       <c r="H12" s="59" t="s">
         <v>112</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J12" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K12" s="57" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.15">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="44" x14ac:dyDescent="0.2">
       <c r="A13" s="57" t="s">
         <v>32</v>
       </c>
@@ -11702,30 +13063,30 @@
         <v>128</v>
       </c>
       <c r="C13" s="61" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D13" s="57" t="s">
         <v>5</v>
       </c>
       <c r="E13" s="57" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F13" s="58" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G13" s="57"/>
       <c r="H13" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I13" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J13" s="59" t="s">
         <v>116</v>
       </c>
       <c r="K13" s="57"/>
     </row>
-    <row r="14" spans="1:11" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11" ht="66" x14ac:dyDescent="0.2">
       <c r="A14" s="57" t="s">
         <v>32</v>
       </c>
@@ -11736,7 +13097,7 @@
         <v>40</v>
       </c>
       <c r="D14" s="57" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E14" s="57" t="s">
         <v>74</v>
@@ -11746,17 +13107,17 @@
       </c>
       <c r="G14" s="57"/>
       <c r="H14" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J14" s="59" t="s">
         <v>118</v>
       </c>
       <c r="K14" s="57"/>
     </row>
-    <row r="15" spans="1:11" ht="101.25" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11" ht="110" x14ac:dyDescent="0.2">
       <c r="A15" s="57" t="s">
         <v>32</v>
       </c>
@@ -11773,23 +13134,23 @@
         <v>7</v>
       </c>
       <c r="F15" s="58" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G15" s="57"/>
       <c r="H15" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I15" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J15" s="59" t="s">
         <v>115</v>
       </c>
       <c r="K15" s="57" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="78.75" x14ac:dyDescent="0.15">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="77" x14ac:dyDescent="0.2">
       <c r="A16" s="57" t="s">
         <v>32</v>
       </c>
@@ -11797,30 +13158,30 @@
         <v>150</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D16" s="57" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E16" s="57" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G16" s="57"/>
       <c r="H16" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I16" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J16" s="59" t="s">
         <v>126</v>
       </c>
       <c r="K16" s="57"/>
     </row>
-    <row r="17" spans="1:11" ht="146.25" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:11" ht="143" x14ac:dyDescent="0.2">
       <c r="A17" s="57" t="s">
         <v>32</v>
       </c>
@@ -11831,53 +13192,53 @@
         <v>78</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E17" s="57" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G17" s="57"/>
       <c r="H17" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I17" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J17" s="59" t="s">
         <v>116</v>
       </c>
       <c r="K17" s="57" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="157.5" x14ac:dyDescent="0.15">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="154" x14ac:dyDescent="0.2">
       <c r="A18" s="57" t="s">
         <v>32</v>
       </c>
       <c r="B18" s="57" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C18" s="61" t="s">
         <v>79</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E18" s="57" t="s">
         <v>8</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G18" s="57"/>
       <c r="H18" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I18" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J18" s="59" t="s">
         <v>119</v>
@@ -11886,31 +13247,31 @@
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="157.5" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:11" ht="154" x14ac:dyDescent="0.2">
       <c r="A19" s="57" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="57" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C19" s="61" t="s">
         <v>77</v>
       </c>
       <c r="D19" s="57" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E19" s="57" t="s">
         <v>9</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G19" s="57"/>
       <c r="H19" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I19" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J19" s="59" t="s">
         <v>119</v>
@@ -11919,7 +13280,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="90" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:11" ht="88" x14ac:dyDescent="0.2">
       <c r="A20" s="57" t="s">
         <v>32</v>
       </c>
@@ -11930,27 +13291,27 @@
         <v>1</v>
       </c>
       <c r="D20" s="57" t="s">
+        <v>250</v>
+      </c>
+      <c r="E20" s="57" t="s">
         <v>251</v>
       </c>
-      <c r="E20" s="57" t="s">
-        <v>252</v>
-      </c>
       <c r="F20" s="58" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G20" s="57"/>
       <c r="H20" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I20" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J20" s="59" t="s">
         <v>116</v>
       </c>
       <c r="K20" s="57"/>
     </row>
-    <row r="21" spans="1:11" ht="123.75" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:11" ht="121" x14ac:dyDescent="0.2">
       <c r="A21" s="57" t="s">
         <v>32</v>
       </c>
@@ -11973,17 +13334,17 @@
         <v>141</v>
       </c>
       <c r="H21" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I21" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J21" s="59" t="s">
         <v>115</v>
       </c>
       <c r="K21" s="57"/>
     </row>
-    <row r="22" spans="1:11" ht="270.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:11" ht="270.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="57" t="s">
         <v>32</v>
       </c>
@@ -11994,7 +13355,7 @@
         <v>176</v>
       </c>
       <c r="D22" s="57" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E22" s="57" t="s">
         <v>191</v>
@@ -12009,16 +13370,16 @@
         <v>113</v>
       </c>
       <c r="I22" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J22" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K22" s="57" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="123.75" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:11" ht="121" x14ac:dyDescent="0.2">
       <c r="A23" s="57" t="s">
         <v>32</v>
       </c>
@@ -12041,19 +13402,19 @@
         <v>55</v>
       </c>
       <c r="H23" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I23" s="59" t="s">
         <v>56</v>
       </c>
       <c r="J23" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K23" s="57" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="78.75" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:11" ht="77" x14ac:dyDescent="0.2">
       <c r="A24" s="57" t="s">
         <v>32</v>
       </c>
@@ -12076,10 +13437,10 @@
         <v>59</v>
       </c>
       <c r="H24" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I24" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J24" s="59" t="s">
         <v>117</v>
@@ -12088,7 +13449,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="56.25" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:11" ht="55" x14ac:dyDescent="0.2">
       <c r="A25" s="57" t="s">
         <v>32</v>
       </c>
@@ -12111,10 +13472,10 @@
         <v>62</v>
       </c>
       <c r="H25" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I25" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J25" s="59" t="s">
         <v>130</v>
@@ -12123,7 +13484,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:11" ht="44" x14ac:dyDescent="0.2">
       <c r="A26" s="57" t="s">
         <v>32</v>
       </c>
@@ -12134,7 +13495,7 @@
         <v>28</v>
       </c>
       <c r="D26" s="57" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E26" s="57" t="s">
         <v>29</v>
@@ -12146,10 +13507,10 @@
         <v>122</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I26" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J26" s="59" t="s">
         <v>121</v>
@@ -12158,7 +13519,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="90" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:11" ht="88" x14ac:dyDescent="0.2">
       <c r="A27" s="57" t="s">
         <v>193</v>
       </c>
@@ -12172,26 +13533,26 @@
         <v>168</v>
       </c>
       <c r="E27" s="57" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F27" s="60" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G27" s="57" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H27" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I27" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J27" s="59" t="s">
         <v>123</v>
       </c>
       <c r="K27" s="57"/>
     </row>
-    <row r="28" spans="1:11" ht="281.25" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:11" ht="275" x14ac:dyDescent="0.2">
       <c r="A28" s="57" t="s">
         <v>63</v>
       </c>
@@ -12202,31 +13563,31 @@
         <v>83</v>
       </c>
       <c r="D28" s="57" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E28" s="57" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F28" s="60" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G28" s="57" t="s">
-        <v>277</v>
+        <v>424</v>
       </c>
       <c r="H28" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I28" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J28" s="59" t="s">
         <v>113</v>
       </c>
       <c r="K28" s="57" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="281.25" x14ac:dyDescent="0.15">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="275" x14ac:dyDescent="0.2">
       <c r="A29" s="57" t="s">
         <v>192</v>
       </c>
@@ -12237,29 +13598,29 @@
         <v>85</v>
       </c>
       <c r="D29" s="57" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E29" s="57" t="s">
+        <v>274</v>
+      </c>
+      <c r="F29" s="60" t="s">
+        <v>334</v>
+      </c>
+      <c r="G29" s="57" t="s">
         <v>275</v>
       </c>
-      <c r="F29" s="60" t="s">
-        <v>336</v>
-      </c>
-      <c r="G29" s="57" t="s">
-        <v>276</v>
-      </c>
       <c r="H29" s="59" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I29" s="59" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J29" s="59" t="s">
         <v>123</v>
       </c>
       <c r="K29" s="57"/>
     </row>
-    <row r="30" spans="1:11" ht="270" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:11" ht="264" x14ac:dyDescent="0.2">
       <c r="A30" s="57" t="s">
         <v>193</v>
       </c>
@@ -12270,29 +13631,29 @@
         <v>84</v>
       </c>
       <c r="D30" s="57" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E30" s="57" t="s">
         <v>227</v>
       </c>
       <c r="F30" s="60" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G30" s="57" t="s">
         <v>229</v>
       </c>
       <c r="H30" s="59" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I30" s="59" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J30" s="59" t="s">
         <v>123</v>
       </c>
       <c r="K30" s="57"/>
     </row>
-    <row r="31" spans="1:11" ht="78.75" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:11" ht="77" x14ac:dyDescent="0.2">
       <c r="A31" s="57" t="s">
         <v>193</v>
       </c>
@@ -12300,30 +13661,30 @@
         <v>135</v>
       </c>
       <c r="C31" s="61" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D31" s="57" t="s">
         <v>154</v>
       </c>
       <c r="E31" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F31" s="58" t="s">
         <v>64</v>
       </c>
       <c r="G31" s="57"/>
       <c r="H31" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I31" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J31" s="59" t="s">
         <v>115</v>
       </c>
       <c r="K31" s="57"/>
     </row>
-    <row r="32" spans="1:11" ht="56.25" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:11" ht="55" x14ac:dyDescent="0.2">
       <c r="A32" s="57" t="s">
         <v>194</v>
       </c>
@@ -12334,7 +13695,7 @@
         <v>91</v>
       </c>
       <c r="D32" s="57" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E32" s="57" t="s">
         <v>136</v>
@@ -12344,17 +13705,17 @@
       </c>
       <c r="G32" s="57"/>
       <c r="H32" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I32" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J32" s="59" t="s">
         <v>116</v>
       </c>
       <c r="K32" s="57"/>
     </row>
-    <row r="33" spans="1:11" ht="33.75" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:11" ht="33" x14ac:dyDescent="0.2">
       <c r="A33" s="57" t="s">
         <v>194</v>
       </c>
@@ -12371,7 +13732,7 @@
         <v>12</v>
       </c>
       <c r="F33" s="60" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G33" s="57" t="s">
         <v>138</v>
@@ -12380,27 +13741,27 @@
         <v>113</v>
       </c>
       <c r="I33" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J33" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K33" s="57" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="135" x14ac:dyDescent="0.15">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="143" x14ac:dyDescent="0.2">
       <c r="A34" s="57" t="s">
         <v>194</v>
       </c>
       <c r="B34" s="57" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C34" s="61" t="s">
         <v>124</v>
       </c>
       <c r="D34" s="57" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E34" s="57" t="s">
         <v>89</v>
@@ -12413,27 +13774,27 @@
         <v>113</v>
       </c>
       <c r="I34" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J34" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K34" s="57" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="112.5" x14ac:dyDescent="0.15">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="121" x14ac:dyDescent="0.2">
       <c r="A35" s="57" t="s">
         <v>111</v>
       </c>
       <c r="B35" s="57" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C35" s="61" t="s">
         <v>226</v>
       </c>
       <c r="D35" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E35" s="57" t="s">
         <v>228</v>
@@ -12443,22 +13804,22 @@
       </c>
       <c r="G35" s="57"/>
       <c r="H35" s="62" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I35" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J35" s="59" t="s">
         <v>127</v>
       </c>
       <c r="K35" s="57"/>
     </row>
-    <row r="36" spans="1:11" ht="112.5" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:11" ht="121" x14ac:dyDescent="0.2">
       <c r="A36" s="57" t="s">
         <v>195</v>
       </c>
       <c r="B36" s="57" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C36" s="61" t="s">
         <v>35</v>
@@ -12474,48 +13835,48 @@
       </c>
       <c r="G36" s="57"/>
       <c r="H36" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I36" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J36" s="59" t="s">
         <v>116</v>
       </c>
       <c r="K36" s="57"/>
     </row>
-    <row r="37" spans="1:11" ht="123.75" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:11" ht="121" x14ac:dyDescent="0.2">
       <c r="A37" s="57" t="s">
         <v>111</v>
       </c>
       <c r="B37" s="57" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C37" s="61" t="s">
         <v>90</v>
       </c>
       <c r="D37" s="57" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E37" s="57" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F37" s="58" t="s">
         <v>64</v>
       </c>
       <c r="G37" s="57"/>
       <c r="H37" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I37" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J37" s="59" t="s">
         <v>112</v>
       </c>
       <c r="K37" s="57"/>
     </row>
-    <row r="38" spans="1:11" ht="33.75" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:11" ht="33" x14ac:dyDescent="0.2">
       <c r="A38" s="57" t="s">
         <v>68</v>
       </c>
@@ -12532,7 +13893,7 @@
         <v>12</v>
       </c>
       <c r="F38" s="60" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G38" s="57" t="s">
         <v>138</v>
@@ -12541,16 +13902,16 @@
         <v>113</v>
       </c>
       <c r="I38" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J38" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K38" s="57" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="135" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:11" ht="143" x14ac:dyDescent="0.2">
       <c r="A39" s="57" t="s">
         <v>196</v>
       </c>
@@ -12561,7 +13922,7 @@
         <v>124</v>
       </c>
       <c r="D39" s="57" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E39" s="57" t="s">
         <v>89</v>
@@ -12574,16 +13935,16 @@
         <v>113</v>
       </c>
       <c r="I39" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J39" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K39" s="57" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="45" x14ac:dyDescent="0.15">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="44" x14ac:dyDescent="0.2">
       <c r="A40" s="57" t="s">
         <v>197</v>
       </c>
@@ -12604,17 +13965,17 @@
       </c>
       <c r="G40" s="57"/>
       <c r="H40" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I40" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J40" s="59" t="s">
         <v>115</v>
       </c>
       <c r="K40" s="57"/>
     </row>
-    <row r="41" spans="1:11" ht="33.75" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:11" ht="33" x14ac:dyDescent="0.2">
       <c r="A41" s="57" t="s">
         <v>33</v>
       </c>
@@ -12631,7 +13992,7 @@
         <v>13</v>
       </c>
       <c r="F41" s="60" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G41" s="57" t="s">
         <v>138</v>
@@ -12640,27 +14001,27 @@
         <v>130</v>
       </c>
       <c r="I41" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J41" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K41" s="57" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="146.25" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:11" ht="143" x14ac:dyDescent="0.2">
       <c r="A42" s="57" t="s">
         <v>33</v>
       </c>
       <c r="B42" s="57" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C42" s="61" t="s">
         <v>198</v>
       </c>
       <c r="D42" s="57" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E42" s="57" t="s">
         <v>89</v>
@@ -12673,16 +14034,16 @@
         <v>126</v>
       </c>
       <c r="I42" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J42" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K42" s="57" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="56.25" x14ac:dyDescent="0.15">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="55" x14ac:dyDescent="0.2">
       <c r="A43" s="57" t="s">
         <v>99</v>
       </c>
@@ -12703,19 +14064,19 @@
       </c>
       <c r="G43" s="57"/>
       <c r="H43" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I43" s="59" t="s">
         <v>120</v>
       </c>
       <c r="J43" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K43" s="57" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="90" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:11" ht="88" x14ac:dyDescent="0.2">
       <c r="A44" s="57" t="s">
         <v>99</v>
       </c>
@@ -12736,36 +14097,36 @@
       </c>
       <c r="G44" s="57"/>
       <c r="H44" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I44" s="59" t="s">
         <v>119</v>
       </c>
       <c r="J44" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K44" s="57" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="135" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:11" ht="143" x14ac:dyDescent="0.2">
       <c r="A45" s="57" t="s">
         <v>99</v>
       </c>
       <c r="B45" s="57" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C45" s="61" t="s">
         <v>88</v>
       </c>
       <c r="D45" s="57" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E45" s="57" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F45" s="58" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G45" s="57"/>
       <c r="H45" s="59" t="s">
@@ -12775,13 +14136,13 @@
         <v>53</v>
       </c>
       <c r="J45" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K45" s="57" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="135" x14ac:dyDescent="0.15">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="143" x14ac:dyDescent="0.2">
       <c r="A46" s="57" t="s">
         <v>99</v>
       </c>
@@ -12810,30 +14171,30 @@
         <v>113</v>
       </c>
       <c r="J46" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K46" s="57" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="168.75" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:11" ht="165" x14ac:dyDescent="0.2">
       <c r="A47" s="57" t="s">
         <v>99</v>
       </c>
       <c r="B47" s="57" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C47" s="61" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D47" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="E47" s="57" t="s">
         <v>264</v>
       </c>
-      <c r="E47" s="57" t="s">
-        <v>265</v>
-      </c>
       <c r="F47" s="60" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G47" s="57"/>
       <c r="H47" s="59" t="s">
@@ -12843,13 +14204,13 @@
         <v>119</v>
       </c>
       <c r="J47" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K47" s="57" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="90" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:11" ht="88" x14ac:dyDescent="0.2">
       <c r="A48" s="57" t="s">
         <v>99</v>
       </c>
@@ -12860,10 +14221,10 @@
         <v>148</v>
       </c>
       <c r="D48" s="57" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E48" s="57" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F48" s="60" t="s">
         <v>71</v>
@@ -12876,13 +14237,13 @@
         <v>113</v>
       </c>
       <c r="J48" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K48" s="57" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="78.75" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:11" ht="77" x14ac:dyDescent="0.2">
       <c r="A49" s="57" t="s">
         <v>99</v>
       </c>
@@ -12893,13 +14254,13 @@
         <v>137</v>
       </c>
       <c r="D49" s="57" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E49" s="57" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F49" s="60" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G49" s="57"/>
       <c r="H49" s="59" t="s">
@@ -12909,7 +14270,7 @@
         <v>119</v>
       </c>
       <c r="J49" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K49" s="57" t="s">
         <v>179</v>
@@ -12930,7 +14291,7 @@
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="8" scale="68" fitToHeight="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="71" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;C- &amp;P -</oddFooter>
   </headerFooter>

--- a/010_開発プロセス標準/Nablarchを使用したシステム開発における標準WBS.xlsx
+++ b/010_開発プロセス標準/Nablarchを使用したシステム開発における標準WBS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B476C759-000E-42D5-975E-D55A089344D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA2247B-15D3-43F4-A9BA-875D23CA9FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="14" r:id="rId1"/>
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2. WBS'!$A$2:$E$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'1. 概要'!$A$1:$AI$110</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'1. 概要'!$A$1:$AI$94</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'2. WBS'!$A$1:$K$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$39</definedName>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="410">
   <si>
     <t xml:space="preserve">データベース論理設計
 </t>
@@ -4625,45 +4625,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>第１．２版</t>
-    <rPh sb="0" eb="1">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ハン</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>1.4. Nablarch6を使用する場合の記載の読み替えについて</t>
-    <rPh sb="15" eb="17">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>キサイ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Nablarch6はJakarta EE 10前提のフレームワークである。</t>
-    <rPh sb="23" eb="25">
-      <t>ゼンテイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>省略名</t>
-  </si>
-  <si>
     <t>JSF</t>
   </si>
   <si>
@@ -4680,9 +4641,6 @@
   </si>
   <si>
     <t>JTA</t>
-  </si>
-  <si>
-    <t>JBatch</t>
   </si>
   <si>
     <t>JCA</t>
@@ -4728,59 +4686,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>特に断りがない限り、本書に登場する省略名は、以下のようにJakarta EEの仕様を指すものとする。</t>
-    <rPh sb="39" eb="41">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>サ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>JAX-RS BeanValidationハンドラ</t>
-  </si>
-  <si>
-    <t>JAX-RSアダプタ</t>
-  </si>
-  <si>
-    <t>Jakarta RESTful Web Servicesアダプタ</t>
-  </si>
-  <si>
-    <t>JAX-RSサポート</t>
-  </si>
-  <si>
-    <t>Jakarta RESTful Web Servicesサポート</t>
-  </si>
-  <si>
-    <t>JAX-RSレスポンスハンドラ</t>
-  </si>
-  <si>
-    <t>Jakarta RESTful Web Servicesレスポンスハンドラ</t>
-  </si>
-  <si>
-    <t>JSPカスタムタグ</t>
-  </si>
-  <si>
-    <t>Jakarta Server Pagesカスタムタグ</t>
-  </si>
-  <si>
-    <t>JSP静的解析ツール</t>
-  </si>
-  <si>
-    <t>Jakarta Server Pages静的解析ツール</t>
-  </si>
-  <si>
-    <t>JSR352に準拠したバッチアプリケーション</t>
-  </si>
-  <si>
-    <t>Jakarta Batchに準拠したバッチアプリケーション</t>
-  </si>
-  <si>
-    <t>Jakarta RESTful Web Servcies Bean Validationハンドラ</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>Jakarta Faces</t>
   </si>
   <si>
@@ -4836,73 +4741,6 @@
   </si>
   <si>
     <t>Jakarta Contexts and Dependency Injection</t>
-  </si>
-  <si>
-    <t>1.4. Nablarch6を使用する場合の記載の読み替えについて</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>特に断りがない限り、本書に登場するNablarch5までの機能名・Fintanコンテンツ名は、</t>
-    <rPh sb="0" eb="1">
-      <t>トク</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>コトワ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>カギ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ホンショ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>トウジョウ</t>
-    </rPh>
-    <rPh sb="29" eb="32">
-      <t>キノウメイ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>以下のようにNablarch6からの機能名・Fintanコンテンツ名を指すものとする。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Nablarch5までの機能名・Fintanコンテンツ名</t>
-    <rPh sb="12" eb="15">
-      <t>キノウメイ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Nablarch6からの機能名・Fintanコンテンツ名</t>
-    <rPh sb="12" eb="15">
-      <t>キノウメイ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>JSPコーディング規約</t>
-    <rPh sb="9" eb="11">
-      <t>キヤク</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Jakarta Server Pagesコーディング規約</t>
-    <rPh sb="26" eb="28">
-      <t>キヤク</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>画面イメージはHTMLで作成すること。</t>
@@ -4934,28 +4772,109 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>Nablarch6がJakarta EE 10前提となることに伴い、いくつかの機能名が変更された。</t>
-    <rPh sb="23" eb="25">
-      <t>ゼンテイ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>トモナ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ヘンコウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>またFintanで提供されるコンテンツもNablarch6前提となることで、コンテンツ名が一部変更された。</t>
-    <rPh sb="29" eb="31">
-      <t>ゼンテイ</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>メイ</t>
+    <t>JBatch / JSR352</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>表記</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>1.4. 本書におけるJakartaEE仕様への読み替えについて</t>
+    <rPh sb="5" eb="7">
+      <t>ホンショ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>特に断りがない限り、以下の表記はJakarta EEの仕様を指すものとする。</t>
+    <rPh sb="10" eb="12">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>1.4. 本書におけるJakartaEE仕様への読み替えについて</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>第１．３版</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ハン</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>1.3版</t>
+    <rPh sb="3" eb="4">
+      <t>ハン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「1. 概要」シート</t>
+    <rPh sb="4" eb="6">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「1.4. 本書におけるJakartaEE仕様への読み替えについて」を追加。</t>
+    <rPh sb="35" eb="37">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>追加</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「2. WBS」シート
+　・K17
+　・G28</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「JSP自動生成ツール」が提供されなくなったため、記載を削除。</t>
+    <rPh sb="4" eb="8">
+      <t>ジドウセイセイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -5165,7 +5084,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -5370,6 +5289,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -5393,7 +5325,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5556,271 +5488,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="31" fontId="9" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="3" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="3" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -5830,6 +5503,294 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="9" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -5888,8 +5849,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7334250" y="285750"/>
-          <a:ext cx="1276350" cy="590550"/>
+          <a:off x="7953375" y="285750"/>
+          <a:ext cx="1400175" cy="590550"/>
           <a:chOff x="591" y="61"/>
           <a:chExt cx="147" cy="62"/>
         </a:xfrm>
@@ -6206,8 +6167,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="969065" y="2776331"/>
-          <a:ext cx="5994124" cy="2745684"/>
+          <a:off x="1034755" y="2752683"/>
+          <a:ext cx="6519641" cy="2722035"/>
           <a:chOff x="121" y="113"/>
           <a:chExt cx="729" cy="300"/>
         </a:xfrm>
@@ -7058,101 +7019,101 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S513"/>
-  <sheetFormatPr defaultColWidth="6.6328125" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="6.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="6.6328125" style="13"/>
+    <col min="1" max="16384" width="6.625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="14"/>
       <c r="C1" s="15"/>
     </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16"/>
     </row>
-    <row r="3" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="4" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="5" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="6" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="7" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="8" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="9" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="10" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="11" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="12" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="13" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="15" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="16" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="17" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="18" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="19" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="20" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="21" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="22" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F22" s="17"/>
       <c r="H22" s="17"/>
     </row>
-    <row r="23" spans="6:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="6:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
       <c r="J23" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="24" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="24" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F24" s="17"/>
       <c r="G24" s="17"/>
       <c r="H24" s="17"/>
     </row>
-    <row r="25" spans="6:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="6:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F25" s="17"/>
       <c r="G25" s="17"/>
       <c r="H25" s="17"/>
-      <c r="I25" s="64">
+      <c r="I25" s="76">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
-        <v>44455</v>
-      </c>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
-    </row>
-    <row r="26" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>45461</v>
+      </c>
+      <c r="J25" s="76"/>
+      <c r="K25" s="76"/>
+    </row>
+    <row r="26" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
       <c r="H26" s="17"/>
     </row>
-    <row r="27" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
     </row>
-    <row r="28" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F28" s="18"/>
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
     </row>
-    <row r="29" spans="6:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="6:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F29" s="17"/>
       <c r="H29" s="17"/>
     </row>
-    <row r="30" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F30" s="17"/>
       <c r="G30" s="19"/>
       <c r="H30" s="17"/>
     </row>
-    <row r="31" spans="6:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="6:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F31" s="17"/>
       <c r="G31" s="19"/>
       <c r="H31" s="17"/>
     </row>
-    <row r="32" spans="6:11" ht="19" x14ac:dyDescent="0.3">
+    <row r="32" spans="6:11" ht="18.75" x14ac:dyDescent="0.2">
       <c r="F32" s="17"/>
       <c r="G32" s="19"/>
       <c r="H32" s="17"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="6:19" ht="19" x14ac:dyDescent="0.3">
+    <row r="33" spans="6:19" ht="18.75" x14ac:dyDescent="0.2">
       <c r="F33" s="17"/>
       <c r="H33" s="17"/>
       <c r="J33" s="21"/>
@@ -7162,7 +7123,7 @@
       <c r="O33" s="21"/>
       <c r="P33" s="21"/>
     </row>
-    <row r="34" spans="6:19" ht="19" x14ac:dyDescent="0.3">
+    <row r="34" spans="6:19" ht="18.75" x14ac:dyDescent="0.2">
       <c r="F34" s="17"/>
       <c r="H34" s="17"/>
       <c r="J34" s="20"/>
@@ -7175,515 +7136,515 @@
       <c r="R34" s="23"/>
       <c r="S34" s="23"/>
     </row>
-    <row r="35" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="O35" s="21"/>
       <c r="P35" s="21"/>
       <c r="Q35" s="23"/>
       <c r="R35" s="23"/>
       <c r="S35" s="23"/>
     </row>
-    <row r="36" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="O36" s="24"/>
       <c r="P36" s="23"/>
       <c r="Q36" s="24"/>
       <c r="R36" s="23"/>
       <c r="S36" s="24"/>
     </row>
-    <row r="37" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="O37" s="25"/>
       <c r="P37" s="25"/>
       <c r="Q37" s="25"/>
       <c r="R37" s="26"/>
       <c r="S37" s="25"/>
     </row>
-    <row r="38" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="O38" s="25"/>
       <c r="P38" s="25"/>
       <c r="Q38" s="26"/>
       <c r="R38" s="26"/>
       <c r="S38" s="26"/>
     </row>
-    <row r="39" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="O39" s="25"/>
       <c r="P39" s="25"/>
       <c r="Q39" s="26"/>
       <c r="R39" s="26"/>
       <c r="S39" s="26"/>
     </row>
-    <row r="40" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="43" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="45" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="46" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="47" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="48" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="49" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="62" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="63" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="64" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="66" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="67" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="69" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="72" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="76" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="83" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="84" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="85" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="86" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="87" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="88" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="89" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="91" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="92" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="95" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="96" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="97" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="98" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="99" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="100" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="101" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="102" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="103" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="104" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="105" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="106" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="107" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="108" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="109" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="110" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="111" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="113" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="114" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="115" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="116" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="117" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="118" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="119" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="121" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="122" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="123" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="124" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="125" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I25:K25"/>
@@ -7703,164 +7664,164 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN34"/>
-  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="11" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="3.6328125" style="30"/>
+    <col min="1" max="16384" width="3.625" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="71" t="s">
+    <row r="1" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="110" t="s">
         <v>279</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="80" t="s">
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="119" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="89" t="s">
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="128" t="s">
         <v>291</v>
       </c>
-      <c r="T1" s="90"/>
-      <c r="U1" s="90"/>
-      <c r="V1" s="90"/>
-      <c r="W1" s="90"/>
-      <c r="X1" s="90"/>
-      <c r="Y1" s="90"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="71" t="s">
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
+      <c r="W1" s="129"/>
+      <c r="X1" s="129"/>
+      <c r="Y1" s="129"/>
+      <c r="Z1" s="130"/>
+      <c r="AA1" s="110" t="s">
         <v>280</v>
       </c>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="98" t="str">
+      <c r="AB1" s="112"/>
+      <c r="AC1" s="137" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="99"/>
-      <c r="AE1" s="99"/>
-      <c r="AF1" s="100"/>
-      <c r="AG1" s="65">
+      <c r="AD1" s="138"/>
+      <c r="AE1" s="138"/>
+      <c r="AF1" s="139"/>
+      <c r="AG1" s="104">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="66"/>
-      <c r="AI1" s="67"/>
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="106"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
       <c r="AN1" s="3"/>
     </row>
-    <row r="2" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="71" t="s">
+    <row r="2" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="110" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="75"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="84"/>
-      <c r="R2" s="85"/>
-      <c r="S2" s="92"/>
-      <c r="T2" s="93"/>
-      <c r="U2" s="93"/>
-      <c r="V2" s="93"/>
-      <c r="W2" s="93"/>
-      <c r="X2" s="93"/>
-      <c r="Y2" s="93"/>
-      <c r="Z2" s="94"/>
-      <c r="AA2" s="71" t="s">
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="115"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="123"/>
+      <c r="Q2" s="123"/>
+      <c r="R2" s="124"/>
+      <c r="S2" s="131"/>
+      <c r="T2" s="132"/>
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="132"/>
+      <c r="X2" s="132"/>
+      <c r="Y2" s="132"/>
+      <c r="Z2" s="133"/>
+      <c r="AA2" s="110" t="s">
         <v>282</v>
       </c>
-      <c r="AB2" s="73"/>
-      <c r="AC2" s="77" t="str">
+      <c r="AB2" s="112"/>
+      <c r="AC2" s="116" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="78"/>
-      <c r="AE2" s="78"/>
-      <c r="AF2" s="79"/>
-      <c r="AG2" s="65">
+      <c r="AD2" s="117"/>
+      <c r="AE2" s="117"/>
+      <c r="AF2" s="118"/>
+      <c r="AG2" s="104">
         <f>IF(D9="","",MAX(D9:F33))</f>
-        <v>44455</v>
-      </c>
-      <c r="AH2" s="66"/>
-      <c r="AI2" s="67"/>
+        <v>45461</v>
+      </c>
+      <c r="AH2" s="105"/>
+      <c r="AI2" s="106"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
     </row>
-    <row r="3" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="71" t="s">
+    <row r="3" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="110" t="s">
         <v>283</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="75"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="87"/>
-      <c r="Q3" s="87"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="95"/>
-      <c r="T3" s="96"/>
-      <c r="U3" s="96"/>
-      <c r="V3" s="96"/>
-      <c r="W3" s="96"/>
-      <c r="X3" s="96"/>
-      <c r="Y3" s="96"/>
-      <c r="Z3" s="97"/>
-      <c r="AA3" s="71"/>
-      <c r="AB3" s="73"/>
-      <c r="AC3" s="98"/>
-      <c r="AD3" s="99"/>
-      <c r="AE3" s="99"/>
-      <c r="AF3" s="100"/>
-      <c r="AG3" s="65"/>
-      <c r="AH3" s="66"/>
-      <c r="AI3" s="67"/>
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="114"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="126"/>
+      <c r="Q3" s="126"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="134"/>
+      <c r="T3" s="135"/>
+      <c r="U3" s="135"/>
+      <c r="V3" s="135"/>
+      <c r="W3" s="135"/>
+      <c r="X3" s="135"/>
+      <c r="Y3" s="135"/>
+      <c r="Z3" s="136"/>
+      <c r="AA3" s="110"/>
+      <c r="AB3" s="112"/>
+      <c r="AC3" s="137"/>
+      <c r="AD3" s="138"/>
+      <c r="AE3" s="138"/>
+      <c r="AF3" s="139"/>
+      <c r="AG3" s="104"/>
+      <c r="AH3" s="105"/>
+      <c r="AI3" s="106"/>
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
       <c r="AM3" s="2"/>
       <c r="AN3" s="2"/>
     </row>
-    <row r="5" spans="1:40" s="4" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" s="4" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N5" s="5" t="s">
         <v>183</v>
       </c>
@@ -7874,7 +7835,7 @@
       <c r="AH5" s="6"/>
       <c r="AI5" s="6"/>
     </row>
-    <row r="6" spans="1:40" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N6" s="5"/>
       <c r="AA6" s="6"/>
       <c r="AB6" s="6"/>
@@ -7886,1222 +7847,1088 @@
       <c r="AH6" s="6"/>
       <c r="AI6" s="6"/>
     </row>
-    <row r="7" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="107" t="s">
         <v>186</v>
       </c>
-      <c r="C7" s="69"/>
-      <c r="D7" s="68" t="s">
+      <c r="C7" s="108"/>
+      <c r="D7" s="107" t="s">
         <v>187</v>
       </c>
-      <c r="E7" s="70"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="68" t="s">
+      <c r="E7" s="109"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="107" t="s">
         <v>188</v>
       </c>
-      <c r="H7" s="70"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="68" t="s">
+      <c r="H7" s="109"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="107" t="s">
         <v>285</v>
       </c>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="69"/>
-      <c r="Q7" s="68" t="s">
+      <c r="K7" s="109"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="108"/>
+      <c r="Q7" s="107" t="s">
         <v>189</v>
       </c>
-      <c r="R7" s="70"/>
-      <c r="S7" s="70"/>
-      <c r="T7" s="70"/>
-      <c r="U7" s="70"/>
-      <c r="V7" s="70"/>
-      <c r="W7" s="70"/>
-      <c r="X7" s="70"/>
-      <c r="Y7" s="70"/>
-      <c r="Z7" s="70"/>
-      <c r="AA7" s="70"/>
-      <c r="AB7" s="70"/>
-      <c r="AC7" s="70"/>
-      <c r="AD7" s="70"/>
-      <c r="AE7" s="69"/>
-      <c r="AF7" s="68" t="s">
+      <c r="R7" s="109"/>
+      <c r="S7" s="109"/>
+      <c r="T7" s="109"/>
+      <c r="U7" s="109"/>
+      <c r="V7" s="109"/>
+      <c r="W7" s="109"/>
+      <c r="X7" s="109"/>
+      <c r="Y7" s="109"/>
+      <c r="Z7" s="109"/>
+      <c r="AA7" s="109"/>
+      <c r="AB7" s="109"/>
+      <c r="AC7" s="109"/>
+      <c r="AD7" s="109"/>
+      <c r="AE7" s="108"/>
+      <c r="AF7" s="107" t="s">
         <v>190</v>
       </c>
-      <c r="AG7" s="70"/>
-      <c r="AH7" s="70"/>
-      <c r="AI7" s="69"/>
-    </row>
-    <row r="8" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="AG7" s="109"/>
+      <c r="AH7" s="109"/>
+      <c r="AI7" s="108"/>
+    </row>
+    <row r="8" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="113" t="s">
+      <c r="B8" s="90" t="s">
         <v>286</v>
       </c>
-      <c r="C8" s="114"/>
-      <c r="D8" s="115">
+      <c r="C8" s="91"/>
+      <c r="D8" s="92">
         <v>43336</v>
       </c>
-      <c r="E8" s="116"/>
-      <c r="F8" s="117"/>
-      <c r="G8" s="118" t="s">
+      <c r="E8" s="93"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="95" t="s">
         <v>287</v>
       </c>
-      <c r="H8" s="119"/>
-      <c r="I8" s="120"/>
-      <c r="J8" s="121" t="s">
+      <c r="H8" s="96"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="98" t="s">
         <v>288</v>
       </c>
-      <c r="K8" s="122"/>
-      <c r="L8" s="122"/>
-      <c r="M8" s="122"/>
-      <c r="N8" s="122"/>
-      <c r="O8" s="122"/>
-      <c r="P8" s="123"/>
-      <c r="Q8" s="124" t="s">
+      <c r="K8" s="99"/>
+      <c r="L8" s="99"/>
+      <c r="M8" s="99"/>
+      <c r="N8" s="99"/>
+      <c r="O8" s="99"/>
+      <c r="P8" s="100"/>
+      <c r="Q8" s="101" t="s">
         <v>289</v>
       </c>
-      <c r="R8" s="125"/>
-      <c r="S8" s="125"/>
-      <c r="T8" s="125"/>
-      <c r="U8" s="125"/>
-      <c r="V8" s="125"/>
-      <c r="W8" s="125"/>
-      <c r="X8" s="125"/>
-      <c r="Y8" s="125"/>
-      <c r="Z8" s="125"/>
-      <c r="AA8" s="125"/>
-      <c r="AB8" s="125"/>
-      <c r="AC8" s="125"/>
-      <c r="AD8" s="125"/>
-      <c r="AE8" s="126"/>
-      <c r="AF8" s="121" t="s">
+      <c r="R8" s="102"/>
+      <c r="S8" s="102"/>
+      <c r="T8" s="102"/>
+      <c r="U8" s="102"/>
+      <c r="V8" s="102"/>
+      <c r="W8" s="102"/>
+      <c r="X8" s="102"/>
+      <c r="Y8" s="102"/>
+      <c r="Z8" s="102"/>
+      <c r="AA8" s="102"/>
+      <c r="AB8" s="102"/>
+      <c r="AC8" s="102"/>
+      <c r="AD8" s="102"/>
+      <c r="AE8" s="103"/>
+      <c r="AF8" s="98" t="s">
         <v>290</v>
       </c>
-      <c r="AG8" s="122"/>
-      <c r="AH8" s="122"/>
-      <c r="AI8" s="123"/>
-    </row>
-    <row r="9" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AG8" s="99"/>
+      <c r="AH8" s="99"/>
+      <c r="AI8" s="100"/>
+    </row>
+    <row r="9" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="29">
         <v>2</v>
       </c>
-      <c r="B9" s="101" t="s">
+      <c r="B9" s="77" t="s">
         <v>355</v>
       </c>
-      <c r="C9" s="102"/>
-      <c r="D9" s="103">
+      <c r="C9" s="78"/>
+      <c r="D9" s="79">
         <v>43896</v>
       </c>
-      <c r="E9" s="104"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="103" t="s">
+      <c r="E9" s="80"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="79" t="s">
         <v>337</v>
       </c>
-      <c r="H9" s="106"/>
-      <c r="I9" s="102"/>
-      <c r="J9" s="107" t="s">
+      <c r="H9" s="82"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="83" t="s">
         <v>338</v>
       </c>
-      <c r="K9" s="108"/>
-      <c r="L9" s="108"/>
-      <c r="M9" s="108"/>
-      <c r="N9" s="108"/>
-      <c r="O9" s="108"/>
-      <c r="P9" s="109"/>
-      <c r="Q9" s="110" t="s">
+      <c r="K9" s="84"/>
+      <c r="L9" s="84"/>
+      <c r="M9" s="84"/>
+      <c r="N9" s="84"/>
+      <c r="O9" s="84"/>
+      <c r="P9" s="85"/>
+      <c r="Q9" s="86" t="s">
         <v>353</v>
       </c>
-      <c r="R9" s="111"/>
-      <c r="S9" s="111"/>
-      <c r="T9" s="111"/>
-      <c r="U9" s="111"/>
-      <c r="V9" s="111"/>
-      <c r="W9" s="111"/>
-      <c r="X9" s="111"/>
-      <c r="Y9" s="111"/>
-      <c r="Z9" s="111"/>
-      <c r="AA9" s="111"/>
-      <c r="AB9" s="111"/>
-      <c r="AC9" s="111"/>
-      <c r="AD9" s="111"/>
-      <c r="AE9" s="112"/>
-      <c r="AF9" s="107" t="s">
+      <c r="R9" s="87"/>
+      <c r="S9" s="87"/>
+      <c r="T9" s="87"/>
+      <c r="U9" s="87"/>
+      <c r="V9" s="87"/>
+      <c r="W9" s="87"/>
+      <c r="X9" s="87"/>
+      <c r="Y9" s="87"/>
+      <c r="Z9" s="87"/>
+      <c r="AA9" s="87"/>
+      <c r="AB9" s="87"/>
+      <c r="AC9" s="87"/>
+      <c r="AD9" s="87"/>
+      <c r="AE9" s="88"/>
+      <c r="AF9" s="83" t="s">
         <v>290</v>
       </c>
-      <c r="AG9" s="108"/>
-      <c r="AH9" s="108"/>
-      <c r="AI9" s="109"/>
-    </row>
-    <row r="10" spans="1:40" s="9" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AG9" s="84"/>
+      <c r="AH9" s="84"/>
+      <c r="AI9" s="85"/>
+    </row>
+    <row r="10" spans="1:40" s="9" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="29">
         <v>3</v>
       </c>
-      <c r="B10" s="101" t="s">
+      <c r="B10" s="77" t="s">
         <v>356</v>
       </c>
-      <c r="C10" s="102"/>
-      <c r="D10" s="103">
+      <c r="C10" s="78"/>
+      <c r="D10" s="79">
         <v>44455</v>
       </c>
-      <c r="E10" s="104"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="103" t="s">
+      <c r="E10" s="80"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="79" t="s">
         <v>337</v>
       </c>
-      <c r="H10" s="106"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="107" t="s">
+      <c r="H10" s="82"/>
+      <c r="I10" s="78"/>
+      <c r="J10" s="83" t="s">
         <v>338</v>
       </c>
-      <c r="K10" s="108"/>
-      <c r="L10" s="108"/>
-      <c r="M10" s="108"/>
-      <c r="N10" s="108"/>
-      <c r="O10" s="108"/>
-      <c r="P10" s="109"/>
-      <c r="Q10" s="110" t="s">
+      <c r="K10" s="84"/>
+      <c r="L10" s="84"/>
+      <c r="M10" s="84"/>
+      <c r="N10" s="84"/>
+      <c r="O10" s="84"/>
+      <c r="P10" s="85"/>
+      <c r="Q10" s="86" t="s">
         <v>357</v>
       </c>
-      <c r="R10" s="111"/>
-      <c r="S10" s="111"/>
-      <c r="T10" s="111"/>
-      <c r="U10" s="111"/>
-      <c r="V10" s="111"/>
-      <c r="W10" s="111"/>
-      <c r="X10" s="111"/>
-      <c r="Y10" s="111"/>
-      <c r="Z10" s="111"/>
-      <c r="AA10" s="111"/>
-      <c r="AB10" s="111"/>
-      <c r="AC10" s="111"/>
-      <c r="AD10" s="111"/>
-      <c r="AE10" s="112"/>
-      <c r="AF10" s="107" t="s">
+      <c r="R10" s="87"/>
+      <c r="S10" s="87"/>
+      <c r="T10" s="87"/>
+      <c r="U10" s="87"/>
+      <c r="V10" s="87"/>
+      <c r="W10" s="87"/>
+      <c r="X10" s="87"/>
+      <c r="Y10" s="87"/>
+      <c r="Z10" s="87"/>
+      <c r="AA10" s="87"/>
+      <c r="AB10" s="87"/>
+      <c r="AC10" s="87"/>
+      <c r="AD10" s="87"/>
+      <c r="AE10" s="88"/>
+      <c r="AF10" s="83" t="s">
         <v>290</v>
       </c>
-      <c r="AG10" s="108"/>
-      <c r="AH10" s="108"/>
-      <c r="AI10" s="109"/>
-    </row>
-    <row r="11" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="29"/>
-      <c r="B11" s="101"/>
-      <c r="C11" s="102"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="101"/>
-      <c r="H11" s="106"/>
-      <c r="I11" s="102"/>
-      <c r="J11" s="107"/>
-      <c r="K11" s="108"/>
-      <c r="L11" s="108"/>
-      <c r="M11" s="108"/>
-      <c r="N11" s="108"/>
-      <c r="O11" s="108"/>
-      <c r="P11" s="109"/>
-      <c r="Q11" s="110"/>
-      <c r="R11" s="111"/>
-      <c r="S11" s="111"/>
-      <c r="T11" s="111"/>
-      <c r="U11" s="111"/>
-      <c r="V11" s="111"/>
-      <c r="W11" s="111"/>
-      <c r="X11" s="111"/>
-      <c r="Y11" s="111"/>
-      <c r="Z11" s="111"/>
-      <c r="AA11" s="111"/>
-      <c r="AB11" s="111"/>
-      <c r="AC11" s="111"/>
-      <c r="AD11" s="111"/>
-      <c r="AE11" s="112"/>
-      <c r="AF11" s="107"/>
-      <c r="AG11" s="108"/>
-      <c r="AH11" s="108"/>
-      <c r="AI11" s="109"/>
-    </row>
-    <row r="12" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="29"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="102"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="106"/>
-      <c r="I12" s="102"/>
-      <c r="J12" s="107"/>
-      <c r="K12" s="108"/>
-      <c r="L12" s="108"/>
-      <c r="M12" s="108"/>
-      <c r="N12" s="108"/>
-      <c r="O12" s="108"/>
-      <c r="P12" s="109"/>
-      <c r="Q12" s="110"/>
-      <c r="R12" s="111"/>
-      <c r="S12" s="111"/>
-      <c r="T12" s="111"/>
-      <c r="U12" s="111"/>
-      <c r="V12" s="111"/>
-      <c r="W12" s="111"/>
-      <c r="X12" s="111"/>
-      <c r="Y12" s="111"/>
-      <c r="Z12" s="111"/>
-      <c r="AA12" s="111"/>
-      <c r="AB12" s="111"/>
-      <c r="AC12" s="111"/>
-      <c r="AD12" s="111"/>
-      <c r="AE12" s="112"/>
-      <c r="AF12" s="107"/>
-      <c r="AG12" s="108"/>
-      <c r="AH12" s="108"/>
-      <c r="AI12" s="109"/>
-    </row>
-    <row r="13" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AG10" s="84"/>
+      <c r="AH10" s="84"/>
+      <c r="AI10" s="85"/>
+    </row>
+    <row r="11" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="161">
+        <v>4</v>
+      </c>
+      <c r="B11" s="162" t="s">
+        <v>404</v>
+      </c>
+      <c r="C11" s="163"/>
+      <c r="D11" s="164">
+        <v>45461</v>
+      </c>
+      <c r="E11" s="165"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="77" t="s">
+        <v>407</v>
+      </c>
+      <c r="H11" s="82"/>
+      <c r="I11" s="78"/>
+      <c r="J11" s="83" t="s">
+        <v>405</v>
+      </c>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84"/>
+      <c r="M11" s="84"/>
+      <c r="N11" s="84"/>
+      <c r="O11" s="84"/>
+      <c r="P11" s="85"/>
+      <c r="Q11" s="86" t="s">
+        <v>406</v>
+      </c>
+      <c r="R11" s="87"/>
+      <c r="S11" s="87"/>
+      <c r="T11" s="87"/>
+      <c r="U11" s="87"/>
+      <c r="V11" s="87"/>
+      <c r="W11" s="87"/>
+      <c r="X11" s="87"/>
+      <c r="Y11" s="87"/>
+      <c r="Z11" s="87"/>
+      <c r="AA11" s="87"/>
+      <c r="AB11" s="87"/>
+      <c r="AC11" s="87"/>
+      <c r="AD11" s="87"/>
+      <c r="AE11" s="88"/>
+      <c r="AF11" s="83" t="s">
+        <v>290</v>
+      </c>
+      <c r="AG11" s="84"/>
+      <c r="AH11" s="84"/>
+      <c r="AI11" s="85"/>
+    </row>
+    <row r="12" spans="1:40" s="9" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="28"/>
+      <c r="B12" s="167"/>
+      <c r="C12" s="168"/>
+      <c r="D12" s="169"/>
+      <c r="E12" s="170"/>
+      <c r="F12" s="171"/>
+      <c r="G12" s="77" t="s">
+        <v>337</v>
+      </c>
+      <c r="H12" s="82"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="86" t="s">
+        <v>408</v>
+      </c>
+      <c r="K12" s="84"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="84"/>
+      <c r="O12" s="84"/>
+      <c r="P12" s="85"/>
+      <c r="Q12" s="86" t="s">
+        <v>409</v>
+      </c>
+      <c r="R12" s="87"/>
+      <c r="S12" s="87"/>
+      <c r="T12" s="87"/>
+      <c r="U12" s="87"/>
+      <c r="V12" s="87"/>
+      <c r="W12" s="87"/>
+      <c r="X12" s="87"/>
+      <c r="Y12" s="87"/>
+      <c r="Z12" s="87"/>
+      <c r="AA12" s="87"/>
+      <c r="AB12" s="87"/>
+      <c r="AC12" s="87"/>
+      <c r="AD12" s="87"/>
+      <c r="AE12" s="88"/>
+      <c r="AF12" s="83" t="s">
+        <v>290</v>
+      </c>
+      <c r="AG12" s="84"/>
+      <c r="AH12" s="84"/>
+      <c r="AI12" s="85"/>
+    </row>
+    <row r="13" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="29"/>
-      <c r="B13" s="101"/>
-      <c r="C13" s="102"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="101"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="102"/>
-      <c r="J13" s="107"/>
-      <c r="K13" s="108"/>
-      <c r="L13" s="108"/>
-      <c r="M13" s="108"/>
-      <c r="N13" s="108"/>
-      <c r="O13" s="108"/>
-      <c r="P13" s="109"/>
-      <c r="Q13" s="110"/>
-      <c r="R13" s="111"/>
-      <c r="S13" s="111"/>
-      <c r="T13" s="111"/>
-      <c r="U13" s="111"/>
-      <c r="V13" s="111"/>
-      <c r="W13" s="111"/>
-      <c r="X13" s="111"/>
-      <c r="Y13" s="111"/>
-      <c r="Z13" s="111"/>
-      <c r="AA13" s="111"/>
-      <c r="AB13" s="111"/>
-      <c r="AC13" s="111"/>
-      <c r="AD13" s="111"/>
-      <c r="AE13" s="112"/>
-      <c r="AF13" s="107"/>
-      <c r="AG13" s="108"/>
-      <c r="AH13" s="108"/>
-      <c r="AI13" s="109"/>
-    </row>
-    <row r="14" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="77"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="78"/>
+      <c r="J13" s="83"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="84"/>
+      <c r="M13" s="84"/>
+      <c r="N13" s="84"/>
+      <c r="O13" s="84"/>
+      <c r="P13" s="85"/>
+      <c r="Q13" s="86"/>
+      <c r="R13" s="87"/>
+      <c r="S13" s="87"/>
+      <c r="T13" s="87"/>
+      <c r="U13" s="87"/>
+      <c r="V13" s="87"/>
+      <c r="W13" s="87"/>
+      <c r="X13" s="87"/>
+      <c r="Y13" s="87"/>
+      <c r="Z13" s="87"/>
+      <c r="AA13" s="87"/>
+      <c r="AB13" s="87"/>
+      <c r="AC13" s="87"/>
+      <c r="AD13" s="87"/>
+      <c r="AE13" s="88"/>
+      <c r="AF13" s="83"/>
+      <c r="AG13" s="84"/>
+      <c r="AH13" s="84"/>
+      <c r="AI13" s="85"/>
+    </row>
+    <row r="14" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="29"/>
-      <c r="B14" s="101"/>
-      <c r="C14" s="102"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="101"/>
-      <c r="H14" s="106"/>
-      <c r="I14" s="102"/>
-      <c r="J14" s="107"/>
-      <c r="K14" s="108"/>
-      <c r="L14" s="108"/>
-      <c r="M14" s="108"/>
-      <c r="N14" s="108"/>
-      <c r="O14" s="108"/>
-      <c r="P14" s="109"/>
-      <c r="Q14" s="110"/>
-      <c r="R14" s="111"/>
-      <c r="S14" s="111"/>
-      <c r="T14" s="111"/>
-      <c r="U14" s="111"/>
-      <c r="V14" s="111"/>
-      <c r="W14" s="111"/>
-      <c r="X14" s="111"/>
-      <c r="Y14" s="111"/>
-      <c r="Z14" s="111"/>
-      <c r="AA14" s="111"/>
-      <c r="AB14" s="111"/>
-      <c r="AC14" s="111"/>
-      <c r="AD14" s="111"/>
-      <c r="AE14" s="112"/>
-      <c r="AF14" s="107"/>
-      <c r="AG14" s="108"/>
-      <c r="AH14" s="108"/>
-      <c r="AI14" s="109"/>
-    </row>
-    <row r="15" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="77"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="84"/>
+      <c r="N14" s="84"/>
+      <c r="O14" s="84"/>
+      <c r="P14" s="85"/>
+      <c r="Q14" s="86"/>
+      <c r="R14" s="87"/>
+      <c r="S14" s="87"/>
+      <c r="T14" s="87"/>
+      <c r="U14" s="87"/>
+      <c r="V14" s="87"/>
+      <c r="W14" s="87"/>
+      <c r="X14" s="87"/>
+      <c r="Y14" s="87"/>
+      <c r="Z14" s="87"/>
+      <c r="AA14" s="87"/>
+      <c r="AB14" s="87"/>
+      <c r="AC14" s="87"/>
+      <c r="AD14" s="87"/>
+      <c r="AE14" s="88"/>
+      <c r="AF14" s="83"/>
+      <c r="AG14" s="84"/>
+      <c r="AH14" s="84"/>
+      <c r="AI14" s="85"/>
+    </row>
+    <row r="15" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="29"/>
-      <c r="B15" s="101"/>
-      <c r="C15" s="102"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="102"/>
-      <c r="J15" s="107"/>
-      <c r="K15" s="108"/>
-      <c r="L15" s="108"/>
-      <c r="M15" s="108"/>
-      <c r="N15" s="108"/>
-      <c r="O15" s="108"/>
-      <c r="P15" s="109"/>
-      <c r="Q15" s="110"/>
-      <c r="R15" s="111"/>
-      <c r="S15" s="111"/>
-      <c r="T15" s="111"/>
-      <c r="U15" s="111"/>
-      <c r="V15" s="111"/>
-      <c r="W15" s="111"/>
-      <c r="X15" s="111"/>
-      <c r="Y15" s="111"/>
-      <c r="Z15" s="111"/>
-      <c r="AA15" s="111"/>
-      <c r="AB15" s="111"/>
-      <c r="AC15" s="111"/>
-      <c r="AD15" s="111"/>
-      <c r="AE15" s="112"/>
-      <c r="AF15" s="107"/>
-      <c r="AG15" s="108"/>
-      <c r="AH15" s="108"/>
-      <c r="AI15" s="109"/>
-    </row>
-    <row r="16" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="77"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="78"/>
+      <c r="J15" s="83"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="84"/>
+      <c r="P15" s="85"/>
+      <c r="Q15" s="86"/>
+      <c r="R15" s="87"/>
+      <c r="S15" s="87"/>
+      <c r="T15" s="87"/>
+      <c r="U15" s="87"/>
+      <c r="V15" s="87"/>
+      <c r="W15" s="87"/>
+      <c r="X15" s="87"/>
+      <c r="Y15" s="87"/>
+      <c r="Z15" s="87"/>
+      <c r="AA15" s="87"/>
+      <c r="AB15" s="87"/>
+      <c r="AC15" s="87"/>
+      <c r="AD15" s="87"/>
+      <c r="AE15" s="88"/>
+      <c r="AF15" s="83"/>
+      <c r="AG15" s="84"/>
+      <c r="AH15" s="84"/>
+      <c r="AI15" s="85"/>
+    </row>
+    <row r="16" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="29"/>
-      <c r="B16" s="101"/>
-      <c r="C16" s="102"/>
-      <c r="D16" s="103"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="105"/>
-      <c r="G16" s="101"/>
-      <c r="H16" s="106"/>
-      <c r="I16" s="102"/>
-      <c r="J16" s="107"/>
-      <c r="K16" s="108"/>
-      <c r="L16" s="108"/>
-      <c r="M16" s="108"/>
-      <c r="N16" s="108"/>
-      <c r="O16" s="108"/>
-      <c r="P16" s="109"/>
-      <c r="Q16" s="110"/>
-      <c r="R16" s="111"/>
-      <c r="S16" s="111"/>
-      <c r="T16" s="111"/>
-      <c r="U16" s="111"/>
-      <c r="V16" s="111"/>
-      <c r="W16" s="111"/>
-      <c r="X16" s="111"/>
-      <c r="Y16" s="111"/>
-      <c r="Z16" s="111"/>
-      <c r="AA16" s="111"/>
-      <c r="AB16" s="111"/>
-      <c r="AC16" s="111"/>
-      <c r="AD16" s="111"/>
-      <c r="AE16" s="112"/>
-      <c r="AF16" s="107"/>
-      <c r="AG16" s="108"/>
-      <c r="AH16" s="108"/>
-      <c r="AI16" s="109"/>
-    </row>
-    <row r="17" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="77"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="78"/>
+      <c r="J16" s="83"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="84"/>
+      <c r="M16" s="84"/>
+      <c r="N16" s="84"/>
+      <c r="O16" s="84"/>
+      <c r="P16" s="85"/>
+      <c r="Q16" s="86"/>
+      <c r="R16" s="87"/>
+      <c r="S16" s="87"/>
+      <c r="T16" s="87"/>
+      <c r="U16" s="87"/>
+      <c r="V16" s="87"/>
+      <c r="W16" s="87"/>
+      <c r="X16" s="87"/>
+      <c r="Y16" s="87"/>
+      <c r="Z16" s="87"/>
+      <c r="AA16" s="87"/>
+      <c r="AB16" s="87"/>
+      <c r="AC16" s="87"/>
+      <c r="AD16" s="87"/>
+      <c r="AE16" s="88"/>
+      <c r="AF16" s="83"/>
+      <c r="AG16" s="84"/>
+      <c r="AH16" s="84"/>
+      <c r="AI16" s="85"/>
+    </row>
+    <row r="17" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="29"/>
-      <c r="B17" s="101"/>
-      <c r="C17" s="102"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="101"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="102"/>
-      <c r="J17" s="107"/>
-      <c r="K17" s="108"/>
-      <c r="L17" s="108"/>
-      <c r="M17" s="108"/>
-      <c r="N17" s="108"/>
-      <c r="O17" s="108"/>
-      <c r="P17" s="109"/>
-      <c r="Q17" s="110"/>
-      <c r="R17" s="111"/>
-      <c r="S17" s="111"/>
-      <c r="T17" s="111"/>
-      <c r="U17" s="111"/>
-      <c r="V17" s="111"/>
-      <c r="W17" s="111"/>
-      <c r="X17" s="111"/>
-      <c r="Y17" s="111"/>
-      <c r="Z17" s="111"/>
-      <c r="AA17" s="111"/>
-      <c r="AB17" s="111"/>
-      <c r="AC17" s="111"/>
-      <c r="AD17" s="111"/>
-      <c r="AE17" s="112"/>
-      <c r="AF17" s="107"/>
-      <c r="AG17" s="108"/>
-      <c r="AH17" s="108"/>
-      <c r="AI17" s="109"/>
-    </row>
-    <row r="18" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="77"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="82"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="83"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84"/>
+      <c r="M17" s="84"/>
+      <c r="N17" s="84"/>
+      <c r="O17" s="84"/>
+      <c r="P17" s="85"/>
+      <c r="Q17" s="86"/>
+      <c r="R17" s="87"/>
+      <c r="S17" s="87"/>
+      <c r="T17" s="87"/>
+      <c r="U17" s="87"/>
+      <c r="V17" s="87"/>
+      <c r="W17" s="87"/>
+      <c r="X17" s="87"/>
+      <c r="Y17" s="87"/>
+      <c r="Z17" s="87"/>
+      <c r="AA17" s="87"/>
+      <c r="AB17" s="87"/>
+      <c r="AC17" s="87"/>
+      <c r="AD17" s="87"/>
+      <c r="AE17" s="88"/>
+      <c r="AF17" s="83"/>
+      <c r="AG17" s="84"/>
+      <c r="AH17" s="84"/>
+      <c r="AI17" s="85"/>
+    </row>
+    <row r="18" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="29"/>
-      <c r="B18" s="101"/>
-      <c r="C18" s="102"/>
-      <c r="D18" s="103"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="105"/>
-      <c r="G18" s="101"/>
-      <c r="H18" s="106"/>
-      <c r="I18" s="102"/>
-      <c r="J18" s="107"/>
-      <c r="K18" s="108"/>
-      <c r="L18" s="108"/>
-      <c r="M18" s="108"/>
-      <c r="N18" s="108"/>
-      <c r="O18" s="108"/>
-      <c r="P18" s="109"/>
-      <c r="Q18" s="110"/>
-      <c r="R18" s="111"/>
-      <c r="S18" s="111"/>
-      <c r="T18" s="111"/>
-      <c r="U18" s="111"/>
-      <c r="V18" s="111"/>
-      <c r="W18" s="111"/>
-      <c r="X18" s="111"/>
-      <c r="Y18" s="111"/>
-      <c r="Z18" s="111"/>
-      <c r="AA18" s="111"/>
-      <c r="AB18" s="111"/>
-      <c r="AC18" s="111"/>
-      <c r="AD18" s="111"/>
-      <c r="AE18" s="112"/>
-      <c r="AF18" s="107"/>
-      <c r="AG18" s="108"/>
-      <c r="AH18" s="108"/>
-      <c r="AI18" s="109"/>
-    </row>
-    <row r="19" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="77"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="78"/>
+      <c r="J18" s="83"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="84"/>
+      <c r="P18" s="85"/>
+      <c r="Q18" s="86"/>
+      <c r="R18" s="87"/>
+      <c r="S18" s="87"/>
+      <c r="T18" s="87"/>
+      <c r="U18" s="87"/>
+      <c r="V18" s="87"/>
+      <c r="W18" s="87"/>
+      <c r="X18" s="87"/>
+      <c r="Y18" s="87"/>
+      <c r="Z18" s="87"/>
+      <c r="AA18" s="87"/>
+      <c r="AB18" s="87"/>
+      <c r="AC18" s="87"/>
+      <c r="AD18" s="87"/>
+      <c r="AE18" s="88"/>
+      <c r="AF18" s="83"/>
+      <c r="AG18" s="84"/>
+      <c r="AH18" s="84"/>
+      <c r="AI18" s="85"/>
+    </row>
+    <row r="19" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="29"/>
-      <c r="B19" s="101"/>
-      <c r="C19" s="102"/>
-      <c r="D19" s="103"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="105"/>
-      <c r="G19" s="101"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="107"/>
-      <c r="K19" s="108"/>
-      <c r="L19" s="108"/>
-      <c r="M19" s="108"/>
-      <c r="N19" s="108"/>
-      <c r="O19" s="108"/>
-      <c r="P19" s="109"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="111"/>
-      <c r="S19" s="111"/>
-      <c r="T19" s="111"/>
-      <c r="U19" s="111"/>
-      <c r="V19" s="111"/>
-      <c r="W19" s="111"/>
-      <c r="X19" s="111"/>
-      <c r="Y19" s="111"/>
-      <c r="Z19" s="111"/>
-      <c r="AA19" s="111"/>
-      <c r="AB19" s="111"/>
-      <c r="AC19" s="111"/>
-      <c r="AD19" s="111"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="107"/>
-      <c r="AG19" s="108"/>
-      <c r="AH19" s="108"/>
-      <c r="AI19" s="109"/>
-    </row>
-    <row r="20" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="77"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="82"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="83"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="85"/>
+      <c r="Q19" s="86"/>
+      <c r="R19" s="87"/>
+      <c r="S19" s="87"/>
+      <c r="T19" s="87"/>
+      <c r="U19" s="87"/>
+      <c r="V19" s="87"/>
+      <c r="W19" s="87"/>
+      <c r="X19" s="87"/>
+      <c r="Y19" s="87"/>
+      <c r="Z19" s="87"/>
+      <c r="AA19" s="87"/>
+      <c r="AB19" s="87"/>
+      <c r="AC19" s="87"/>
+      <c r="AD19" s="87"/>
+      <c r="AE19" s="88"/>
+      <c r="AF19" s="83"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="85"/>
+    </row>
+    <row r="20" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="29"/>
-      <c r="B20" s="101"/>
-      <c r="C20" s="102"/>
-      <c r="D20" s="103"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="101"/>
-      <c r="H20" s="106"/>
-      <c r="I20" s="102"/>
-      <c r="J20" s="107"/>
-      <c r="K20" s="108"/>
-      <c r="L20" s="108"/>
-      <c r="M20" s="108"/>
-      <c r="N20" s="108"/>
-      <c r="O20" s="108"/>
-      <c r="P20" s="109"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="111"/>
-      <c r="S20" s="111"/>
-      <c r="T20" s="111"/>
-      <c r="U20" s="111"/>
-      <c r="V20" s="111"/>
-      <c r="W20" s="111"/>
-      <c r="X20" s="111"/>
-      <c r="Y20" s="111"/>
-      <c r="Z20" s="111"/>
-      <c r="AA20" s="111"/>
-      <c r="AB20" s="111"/>
-      <c r="AC20" s="111"/>
-      <c r="AD20" s="111"/>
-      <c r="AE20" s="112"/>
-      <c r="AF20" s="107"/>
-      <c r="AG20" s="108"/>
-      <c r="AH20" s="108"/>
-      <c r="AI20" s="109"/>
-    </row>
-    <row r="21" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="77"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="82"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="83"/>
+      <c r="K20" s="84"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="84"/>
+      <c r="N20" s="84"/>
+      <c r="O20" s="84"/>
+      <c r="P20" s="85"/>
+      <c r="Q20" s="86"/>
+      <c r="R20" s="87"/>
+      <c r="S20" s="87"/>
+      <c r="T20" s="87"/>
+      <c r="U20" s="87"/>
+      <c r="V20" s="87"/>
+      <c r="W20" s="87"/>
+      <c r="X20" s="87"/>
+      <c r="Y20" s="87"/>
+      <c r="Z20" s="87"/>
+      <c r="AA20" s="87"/>
+      <c r="AB20" s="87"/>
+      <c r="AC20" s="87"/>
+      <c r="AD20" s="87"/>
+      <c r="AE20" s="88"/>
+      <c r="AF20" s="83"/>
+      <c r="AG20" s="84"/>
+      <c r="AH20" s="84"/>
+      <c r="AI20" s="85"/>
+    </row>
+    <row r="21" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="29"/>
-      <c r="B21" s="101"/>
-      <c r="C21" s="102"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="101"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="107"/>
-      <c r="K21" s="108"/>
-      <c r="L21" s="108"/>
-      <c r="M21" s="108"/>
-      <c r="N21" s="108"/>
-      <c r="O21" s="108"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="110"/>
-      <c r="R21" s="111"/>
-      <c r="S21" s="111"/>
-      <c r="T21" s="111"/>
-      <c r="U21" s="111"/>
-      <c r="V21" s="111"/>
-      <c r="W21" s="111"/>
-      <c r="X21" s="111"/>
-      <c r="Y21" s="111"/>
-      <c r="Z21" s="111"/>
-      <c r="AA21" s="111"/>
-      <c r="AB21" s="111"/>
-      <c r="AC21" s="111"/>
-      <c r="AD21" s="111"/>
-      <c r="AE21" s="112"/>
-      <c r="AF21" s="107"/>
-      <c r="AG21" s="108"/>
-      <c r="AH21" s="108"/>
-      <c r="AI21" s="109"/>
-    </row>
-    <row r="22" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="77"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="82"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="83"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="84"/>
+      <c r="O21" s="84"/>
+      <c r="P21" s="85"/>
+      <c r="Q21" s="86"/>
+      <c r="R21" s="87"/>
+      <c r="S21" s="87"/>
+      <c r="T21" s="87"/>
+      <c r="U21" s="87"/>
+      <c r="V21" s="87"/>
+      <c r="W21" s="87"/>
+      <c r="X21" s="87"/>
+      <c r="Y21" s="87"/>
+      <c r="Z21" s="87"/>
+      <c r="AA21" s="87"/>
+      <c r="AB21" s="87"/>
+      <c r="AC21" s="87"/>
+      <c r="AD21" s="87"/>
+      <c r="AE21" s="88"/>
+      <c r="AF21" s="83"/>
+      <c r="AG21" s="84"/>
+      <c r="AH21" s="84"/>
+      <c r="AI21" s="85"/>
+    </row>
+    <row r="22" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="29"/>
-      <c r="B22" s="101"/>
-      <c r="C22" s="102"/>
-      <c r="D22" s="103"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="105"/>
-      <c r="G22" s="101"/>
-      <c r="H22" s="106"/>
-      <c r="I22" s="102"/>
-      <c r="J22" s="107"/>
-      <c r="K22" s="108"/>
-      <c r="L22" s="108"/>
-      <c r="M22" s="108"/>
-      <c r="N22" s="108"/>
-      <c r="O22" s="108"/>
-      <c r="P22" s="109"/>
-      <c r="Q22" s="110"/>
-      <c r="R22" s="111"/>
-      <c r="S22" s="111"/>
-      <c r="T22" s="111"/>
-      <c r="U22" s="111"/>
-      <c r="V22" s="111"/>
-      <c r="W22" s="111"/>
-      <c r="X22" s="111"/>
-      <c r="Y22" s="111"/>
-      <c r="Z22" s="111"/>
-      <c r="AA22" s="111"/>
-      <c r="AB22" s="111"/>
-      <c r="AC22" s="111"/>
-      <c r="AD22" s="111"/>
-      <c r="AE22" s="112"/>
-      <c r="AF22" s="107"/>
-      <c r="AG22" s="108"/>
-      <c r="AH22" s="108"/>
-      <c r="AI22" s="109"/>
-    </row>
-    <row r="23" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="77"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="79"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="82"/>
+      <c r="I22" s="78"/>
+      <c r="J22" s="83"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="84"/>
+      <c r="P22" s="85"/>
+      <c r="Q22" s="86"/>
+      <c r="R22" s="87"/>
+      <c r="S22" s="87"/>
+      <c r="T22" s="87"/>
+      <c r="U22" s="87"/>
+      <c r="V22" s="87"/>
+      <c r="W22" s="87"/>
+      <c r="X22" s="87"/>
+      <c r="Y22" s="87"/>
+      <c r="Z22" s="87"/>
+      <c r="AA22" s="87"/>
+      <c r="AB22" s="87"/>
+      <c r="AC22" s="87"/>
+      <c r="AD22" s="87"/>
+      <c r="AE22" s="88"/>
+      <c r="AF22" s="83"/>
+      <c r="AG22" s="84"/>
+      <c r="AH22" s="84"/>
+      <c r="AI22" s="85"/>
+    </row>
+    <row r="23" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="29"/>
-      <c r="B23" s="101"/>
-      <c r="C23" s="102"/>
-      <c r="D23" s="103"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="105"/>
-      <c r="G23" s="101"/>
-      <c r="H23" s="106"/>
-      <c r="I23" s="102"/>
-      <c r="J23" s="107"/>
-      <c r="K23" s="108"/>
-      <c r="L23" s="108"/>
-      <c r="M23" s="108"/>
-      <c r="N23" s="108"/>
-      <c r="O23" s="108"/>
-      <c r="P23" s="109"/>
-      <c r="Q23" s="110"/>
-      <c r="R23" s="111"/>
-      <c r="S23" s="111"/>
-      <c r="T23" s="111"/>
-      <c r="U23" s="111"/>
-      <c r="V23" s="111"/>
-      <c r="W23" s="111"/>
-      <c r="X23" s="111"/>
-      <c r="Y23" s="111"/>
-      <c r="Z23" s="111"/>
-      <c r="AA23" s="111"/>
-      <c r="AB23" s="111"/>
-      <c r="AC23" s="111"/>
-      <c r="AD23" s="111"/>
-      <c r="AE23" s="112"/>
-      <c r="AF23" s="107"/>
-      <c r="AG23" s="108"/>
-      <c r="AH23" s="108"/>
-      <c r="AI23" s="109"/>
-    </row>
-    <row r="24" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="77"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="82"/>
+      <c r="I23" s="78"/>
+      <c r="J23" s="83"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="84"/>
+      <c r="O23" s="84"/>
+      <c r="P23" s="85"/>
+      <c r="Q23" s="86"/>
+      <c r="R23" s="87"/>
+      <c r="S23" s="87"/>
+      <c r="T23" s="87"/>
+      <c r="U23" s="87"/>
+      <c r="V23" s="87"/>
+      <c r="W23" s="87"/>
+      <c r="X23" s="87"/>
+      <c r="Y23" s="87"/>
+      <c r="Z23" s="87"/>
+      <c r="AA23" s="87"/>
+      <c r="AB23" s="87"/>
+      <c r="AC23" s="87"/>
+      <c r="AD23" s="87"/>
+      <c r="AE23" s="88"/>
+      <c r="AF23" s="83"/>
+      <c r="AG23" s="84"/>
+      <c r="AH23" s="84"/>
+      <c r="AI23" s="85"/>
+    </row>
+    <row r="24" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="29"/>
-      <c r="B24" s="101"/>
-      <c r="C24" s="102"/>
-      <c r="D24" s="103"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="105"/>
-      <c r="G24" s="101"/>
-      <c r="H24" s="106"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="107"/>
-      <c r="K24" s="108"/>
-      <c r="L24" s="108"/>
-      <c r="M24" s="108"/>
-      <c r="N24" s="108"/>
-      <c r="O24" s="108"/>
-      <c r="P24" s="109"/>
-      <c r="Q24" s="110"/>
-      <c r="R24" s="111"/>
-      <c r="S24" s="111"/>
-      <c r="T24" s="111"/>
-      <c r="U24" s="111"/>
-      <c r="V24" s="111"/>
-      <c r="W24" s="111"/>
-      <c r="X24" s="111"/>
-      <c r="Y24" s="111"/>
-      <c r="Z24" s="111"/>
-      <c r="AA24" s="111"/>
-      <c r="AB24" s="111"/>
-      <c r="AC24" s="111"/>
-      <c r="AD24" s="111"/>
-      <c r="AE24" s="112"/>
-      <c r="AF24" s="107"/>
-      <c r="AG24" s="108"/>
-      <c r="AH24" s="108"/>
-      <c r="AI24" s="109"/>
-    </row>
-    <row r="25" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="77"/>
+      <c r="C24" s="78"/>
+      <c r="D24" s="79"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="78"/>
+      <c r="J24" s="83"/>
+      <c r="K24" s="84"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="84"/>
+      <c r="N24" s="84"/>
+      <c r="O24" s="84"/>
+      <c r="P24" s="85"/>
+      <c r="Q24" s="86"/>
+      <c r="R24" s="87"/>
+      <c r="S24" s="87"/>
+      <c r="T24" s="87"/>
+      <c r="U24" s="87"/>
+      <c r="V24" s="87"/>
+      <c r="W24" s="87"/>
+      <c r="X24" s="87"/>
+      <c r="Y24" s="87"/>
+      <c r="Z24" s="87"/>
+      <c r="AA24" s="87"/>
+      <c r="AB24" s="87"/>
+      <c r="AC24" s="87"/>
+      <c r="AD24" s="87"/>
+      <c r="AE24" s="88"/>
+      <c r="AF24" s="83"/>
+      <c r="AG24" s="84"/>
+      <c r="AH24" s="84"/>
+      <c r="AI24" s="85"/>
+    </row>
+    <row r="25" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="29"/>
-      <c r="B25" s="101"/>
-      <c r="C25" s="102"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="105"/>
-      <c r="G25" s="101"/>
-      <c r="H25" s="106"/>
-      <c r="I25" s="102"/>
-      <c r="J25" s="107"/>
-      <c r="K25" s="108"/>
-      <c r="L25" s="108"/>
-      <c r="M25" s="108"/>
-      <c r="N25" s="108"/>
-      <c r="O25" s="108"/>
-      <c r="P25" s="109"/>
-      <c r="Q25" s="110"/>
-      <c r="R25" s="111"/>
-      <c r="S25" s="111"/>
-      <c r="T25" s="111"/>
-      <c r="U25" s="111"/>
-      <c r="V25" s="111"/>
-      <c r="W25" s="111"/>
-      <c r="X25" s="111"/>
-      <c r="Y25" s="111"/>
-      <c r="Z25" s="111"/>
-      <c r="AA25" s="111"/>
-      <c r="AB25" s="111"/>
-      <c r="AC25" s="111"/>
-      <c r="AD25" s="111"/>
-      <c r="AE25" s="112"/>
-      <c r="AF25" s="107"/>
-      <c r="AG25" s="108"/>
-      <c r="AH25" s="108"/>
-      <c r="AI25" s="109"/>
-    </row>
-    <row r="26" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="77"/>
+      <c r="C25" s="78"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="82"/>
+      <c r="I25" s="78"/>
+      <c r="J25" s="83"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="84"/>
+      <c r="O25" s="84"/>
+      <c r="P25" s="85"/>
+      <c r="Q25" s="86"/>
+      <c r="R25" s="87"/>
+      <c r="S25" s="87"/>
+      <c r="T25" s="87"/>
+      <c r="U25" s="87"/>
+      <c r="V25" s="87"/>
+      <c r="W25" s="87"/>
+      <c r="X25" s="87"/>
+      <c r="Y25" s="87"/>
+      <c r="Z25" s="87"/>
+      <c r="AA25" s="87"/>
+      <c r="AB25" s="87"/>
+      <c r="AC25" s="87"/>
+      <c r="AD25" s="87"/>
+      <c r="AE25" s="88"/>
+      <c r="AF25" s="83"/>
+      <c r="AG25" s="84"/>
+      <c r="AH25" s="84"/>
+      <c r="AI25" s="85"/>
+    </row>
+    <row r="26" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="29"/>
-      <c r="B26" s="101"/>
-      <c r="C26" s="102"/>
-      <c r="D26" s="103"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="105"/>
-      <c r="G26" s="101"/>
-      <c r="H26" s="106"/>
-      <c r="I26" s="102"/>
-      <c r="J26" s="107"/>
-      <c r="K26" s="108"/>
-      <c r="L26" s="108"/>
-      <c r="M26" s="108"/>
-      <c r="N26" s="108"/>
-      <c r="O26" s="108"/>
-      <c r="P26" s="109"/>
-      <c r="Q26" s="110"/>
-      <c r="R26" s="111"/>
-      <c r="S26" s="111"/>
-      <c r="T26" s="111"/>
-      <c r="U26" s="111"/>
-      <c r="V26" s="111"/>
-      <c r="W26" s="111"/>
-      <c r="X26" s="111"/>
-      <c r="Y26" s="111"/>
-      <c r="Z26" s="111"/>
-      <c r="AA26" s="111"/>
-      <c r="AB26" s="111"/>
-      <c r="AC26" s="111"/>
-      <c r="AD26" s="111"/>
-      <c r="AE26" s="112"/>
-      <c r="AF26" s="107"/>
-      <c r="AG26" s="108"/>
-      <c r="AH26" s="108"/>
-      <c r="AI26" s="109"/>
-    </row>
-    <row r="27" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="77"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="82"/>
+      <c r="I26" s="78"/>
+      <c r="J26" s="83"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="84"/>
+      <c r="O26" s="84"/>
+      <c r="P26" s="85"/>
+      <c r="Q26" s="86"/>
+      <c r="R26" s="87"/>
+      <c r="S26" s="87"/>
+      <c r="T26" s="87"/>
+      <c r="U26" s="87"/>
+      <c r="V26" s="87"/>
+      <c r="W26" s="87"/>
+      <c r="X26" s="87"/>
+      <c r="Y26" s="87"/>
+      <c r="Z26" s="87"/>
+      <c r="AA26" s="87"/>
+      <c r="AB26" s="87"/>
+      <c r="AC26" s="87"/>
+      <c r="AD26" s="87"/>
+      <c r="AE26" s="88"/>
+      <c r="AF26" s="83"/>
+      <c r="AG26" s="84"/>
+      <c r="AH26" s="84"/>
+      <c r="AI26" s="85"/>
+    </row>
+    <row r="27" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="29"/>
-      <c r="B27" s="101"/>
-      <c r="C27" s="102"/>
-      <c r="D27" s="103"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="105"/>
-      <c r="G27" s="101"/>
-      <c r="H27" s="106"/>
-      <c r="I27" s="102"/>
-      <c r="J27" s="107"/>
-      <c r="K27" s="108"/>
-      <c r="L27" s="108"/>
-      <c r="M27" s="108"/>
-      <c r="N27" s="108"/>
-      <c r="O27" s="108"/>
-      <c r="P27" s="109"/>
-      <c r="Q27" s="110"/>
-      <c r="R27" s="111"/>
-      <c r="S27" s="111"/>
-      <c r="T27" s="111"/>
-      <c r="U27" s="111"/>
-      <c r="V27" s="111"/>
-      <c r="W27" s="111"/>
-      <c r="X27" s="111"/>
-      <c r="Y27" s="111"/>
-      <c r="Z27" s="111"/>
-      <c r="AA27" s="111"/>
-      <c r="AB27" s="111"/>
-      <c r="AC27" s="111"/>
-      <c r="AD27" s="111"/>
-      <c r="AE27" s="112"/>
-      <c r="AF27" s="107"/>
-      <c r="AG27" s="108"/>
-      <c r="AH27" s="108"/>
-      <c r="AI27" s="109"/>
-    </row>
-    <row r="28" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="77"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="82"/>
+      <c r="I27" s="78"/>
+      <c r="J27" s="83"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="84"/>
+      <c r="O27" s="84"/>
+      <c r="P27" s="85"/>
+      <c r="Q27" s="86"/>
+      <c r="R27" s="87"/>
+      <c r="S27" s="87"/>
+      <c r="T27" s="87"/>
+      <c r="U27" s="87"/>
+      <c r="V27" s="87"/>
+      <c r="W27" s="87"/>
+      <c r="X27" s="87"/>
+      <c r="Y27" s="87"/>
+      <c r="Z27" s="87"/>
+      <c r="AA27" s="87"/>
+      <c r="AB27" s="87"/>
+      <c r="AC27" s="87"/>
+      <c r="AD27" s="87"/>
+      <c r="AE27" s="88"/>
+      <c r="AF27" s="83"/>
+      <c r="AG27" s="84"/>
+      <c r="AH27" s="84"/>
+      <c r="AI27" s="85"/>
+    </row>
+    <row r="28" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="29"/>
-      <c r="B28" s="101"/>
-      <c r="C28" s="102"/>
-      <c r="D28" s="103"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="105"/>
-      <c r="G28" s="101"/>
-      <c r="H28" s="106"/>
-      <c r="I28" s="102"/>
-      <c r="J28" s="107"/>
-      <c r="K28" s="108"/>
-      <c r="L28" s="108"/>
-      <c r="M28" s="108"/>
-      <c r="N28" s="108"/>
-      <c r="O28" s="108"/>
-      <c r="P28" s="109"/>
-      <c r="Q28" s="110"/>
-      <c r="R28" s="111"/>
-      <c r="S28" s="111"/>
-      <c r="T28" s="111"/>
-      <c r="U28" s="111"/>
-      <c r="V28" s="111"/>
-      <c r="W28" s="111"/>
-      <c r="X28" s="111"/>
-      <c r="Y28" s="111"/>
-      <c r="Z28" s="111"/>
-      <c r="AA28" s="111"/>
-      <c r="AB28" s="111"/>
-      <c r="AC28" s="111"/>
-      <c r="AD28" s="111"/>
-      <c r="AE28" s="112"/>
-      <c r="AF28" s="107"/>
-      <c r="AG28" s="108"/>
-      <c r="AH28" s="108"/>
-      <c r="AI28" s="109"/>
-    </row>
-    <row r="29" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="77"/>
+      <c r="C28" s="78"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="82"/>
+      <c r="I28" s="78"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="84"/>
+      <c r="O28" s="84"/>
+      <c r="P28" s="85"/>
+      <c r="Q28" s="86"/>
+      <c r="R28" s="87"/>
+      <c r="S28" s="87"/>
+      <c r="T28" s="87"/>
+      <c r="U28" s="87"/>
+      <c r="V28" s="87"/>
+      <c r="W28" s="87"/>
+      <c r="X28" s="87"/>
+      <c r="Y28" s="87"/>
+      <c r="Z28" s="87"/>
+      <c r="AA28" s="87"/>
+      <c r="AB28" s="87"/>
+      <c r="AC28" s="87"/>
+      <c r="AD28" s="87"/>
+      <c r="AE28" s="88"/>
+      <c r="AF28" s="83"/>
+      <c r="AG28" s="84"/>
+      <c r="AH28" s="84"/>
+      <c r="AI28" s="85"/>
+    </row>
+    <row r="29" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="29"/>
-      <c r="B29" s="101"/>
-      <c r="C29" s="102"/>
-      <c r="D29" s="103"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="105"/>
-      <c r="G29" s="101"/>
-      <c r="H29" s="106"/>
-      <c r="I29" s="102"/>
-      <c r="J29" s="107"/>
-      <c r="K29" s="108"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="108"/>
-      <c r="N29" s="108"/>
-      <c r="O29" s="108"/>
-      <c r="P29" s="109"/>
-      <c r="Q29" s="110"/>
-      <c r="R29" s="111"/>
-      <c r="S29" s="111"/>
-      <c r="T29" s="111"/>
-      <c r="U29" s="111"/>
-      <c r="V29" s="111"/>
-      <c r="W29" s="111"/>
-      <c r="X29" s="111"/>
-      <c r="Y29" s="111"/>
-      <c r="Z29" s="111"/>
-      <c r="AA29" s="111"/>
-      <c r="AB29" s="111"/>
-      <c r="AC29" s="111"/>
-      <c r="AD29" s="111"/>
-      <c r="AE29" s="112"/>
-      <c r="AF29" s="107"/>
-      <c r="AG29" s="108"/>
-      <c r="AH29" s="108"/>
-      <c r="AI29" s="109"/>
-    </row>
-    <row r="30" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="77"/>
+      <c r="C29" s="78"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="82"/>
+      <c r="I29" s="78"/>
+      <c r="J29" s="83"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="84"/>
+      <c r="P29" s="85"/>
+      <c r="Q29" s="86"/>
+      <c r="R29" s="87"/>
+      <c r="S29" s="87"/>
+      <c r="T29" s="87"/>
+      <c r="U29" s="87"/>
+      <c r="V29" s="87"/>
+      <c r="W29" s="87"/>
+      <c r="X29" s="87"/>
+      <c r="Y29" s="87"/>
+      <c r="Z29" s="87"/>
+      <c r="AA29" s="87"/>
+      <c r="AB29" s="87"/>
+      <c r="AC29" s="87"/>
+      <c r="AD29" s="87"/>
+      <c r="AE29" s="88"/>
+      <c r="AF29" s="83"/>
+      <c r="AG29" s="84"/>
+      <c r="AH29" s="84"/>
+      <c r="AI29" s="85"/>
+    </row>
+    <row r="30" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="29"/>
-      <c r="B30" s="101"/>
-      <c r="C30" s="102"/>
-      <c r="D30" s="103"/>
-      <c r="E30" s="104"/>
-      <c r="F30" s="105"/>
-      <c r="G30" s="101"/>
-      <c r="H30" s="106"/>
-      <c r="I30" s="102"/>
-      <c r="J30" s="107"/>
-      <c r="K30" s="108"/>
-      <c r="L30" s="108"/>
-      <c r="M30" s="108"/>
-      <c r="N30" s="108"/>
-      <c r="O30" s="108"/>
-      <c r="P30" s="109"/>
-      <c r="Q30" s="110"/>
-      <c r="R30" s="111"/>
-      <c r="S30" s="111"/>
-      <c r="T30" s="111"/>
-      <c r="U30" s="111"/>
-      <c r="V30" s="111"/>
-      <c r="W30" s="111"/>
-      <c r="X30" s="111"/>
-      <c r="Y30" s="111"/>
-      <c r="Z30" s="111"/>
-      <c r="AA30" s="111"/>
-      <c r="AB30" s="111"/>
-      <c r="AC30" s="111"/>
-      <c r="AD30" s="111"/>
-      <c r="AE30" s="112"/>
-      <c r="AF30" s="107"/>
-      <c r="AG30" s="108"/>
-      <c r="AH30" s="108"/>
-      <c r="AI30" s="109"/>
-    </row>
-    <row r="31" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="77"/>
+      <c r="C30" s="78"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="82"/>
+      <c r="I30" s="78"/>
+      <c r="J30" s="83"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="84"/>
+      <c r="O30" s="84"/>
+      <c r="P30" s="85"/>
+      <c r="Q30" s="86"/>
+      <c r="R30" s="87"/>
+      <c r="S30" s="87"/>
+      <c r="T30" s="87"/>
+      <c r="U30" s="87"/>
+      <c r="V30" s="87"/>
+      <c r="W30" s="87"/>
+      <c r="X30" s="87"/>
+      <c r="Y30" s="87"/>
+      <c r="Z30" s="87"/>
+      <c r="AA30" s="87"/>
+      <c r="AB30" s="87"/>
+      <c r="AC30" s="87"/>
+      <c r="AD30" s="87"/>
+      <c r="AE30" s="88"/>
+      <c r="AF30" s="83"/>
+      <c r="AG30" s="84"/>
+      <c r="AH30" s="84"/>
+      <c r="AI30" s="85"/>
+    </row>
+    <row r="31" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="29"/>
-      <c r="B31" s="101"/>
-      <c r="C31" s="102"/>
-      <c r="D31" s="103"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="105"/>
-      <c r="G31" s="101"/>
-      <c r="H31" s="106"/>
-      <c r="I31" s="102"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="108"/>
-      <c r="L31" s="108"/>
-      <c r="M31" s="108"/>
-      <c r="N31" s="108"/>
-      <c r="O31" s="108"/>
-      <c r="P31" s="109"/>
-      <c r="Q31" s="110"/>
-      <c r="R31" s="111"/>
-      <c r="S31" s="111"/>
-      <c r="T31" s="111"/>
-      <c r="U31" s="111"/>
-      <c r="V31" s="111"/>
-      <c r="W31" s="111"/>
-      <c r="X31" s="111"/>
-      <c r="Y31" s="111"/>
-      <c r="Z31" s="111"/>
-      <c r="AA31" s="111"/>
-      <c r="AB31" s="111"/>
-      <c r="AC31" s="111"/>
-      <c r="AD31" s="111"/>
-      <c r="AE31" s="112"/>
-      <c r="AF31" s="107"/>
-      <c r="AG31" s="108"/>
-      <c r="AH31" s="108"/>
-      <c r="AI31" s="109"/>
-    </row>
-    <row r="32" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="77"/>
+      <c r="C31" s="78"/>
+      <c r="D31" s="79"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="82"/>
+      <c r="I31" s="78"/>
+      <c r="J31" s="83"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="84"/>
+      <c r="O31" s="84"/>
+      <c r="P31" s="85"/>
+      <c r="Q31" s="86"/>
+      <c r="R31" s="87"/>
+      <c r="S31" s="87"/>
+      <c r="T31" s="87"/>
+      <c r="U31" s="87"/>
+      <c r="V31" s="87"/>
+      <c r="W31" s="87"/>
+      <c r="X31" s="87"/>
+      <c r="Y31" s="87"/>
+      <c r="Z31" s="87"/>
+      <c r="AA31" s="87"/>
+      <c r="AB31" s="87"/>
+      <c r="AC31" s="87"/>
+      <c r="AD31" s="87"/>
+      <c r="AE31" s="88"/>
+      <c r="AF31" s="83"/>
+      <c r="AG31" s="84"/>
+      <c r="AH31" s="84"/>
+      <c r="AI31" s="85"/>
+    </row>
+    <row r="32" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="29"/>
-      <c r="B32" s="101"/>
-      <c r="C32" s="102"/>
-      <c r="D32" s="103"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="105"/>
-      <c r="G32" s="101"/>
-      <c r="H32" s="106"/>
-      <c r="I32" s="102"/>
-      <c r="J32" s="107"/>
-      <c r="K32" s="127"/>
-      <c r="L32" s="108"/>
-      <c r="M32" s="108"/>
-      <c r="N32" s="108"/>
-      <c r="O32" s="108"/>
-      <c r="P32" s="109"/>
-      <c r="Q32" s="110"/>
-      <c r="R32" s="111"/>
-      <c r="S32" s="111"/>
-      <c r="T32" s="111"/>
-      <c r="U32" s="111"/>
-      <c r="V32" s="111"/>
-      <c r="W32" s="111"/>
-      <c r="X32" s="111"/>
-      <c r="Y32" s="111"/>
-      <c r="Z32" s="111"/>
-      <c r="AA32" s="111"/>
-      <c r="AB32" s="111"/>
-      <c r="AC32" s="111"/>
-      <c r="AD32" s="111"/>
-      <c r="AE32" s="112"/>
-      <c r="AF32" s="107"/>
-      <c r="AG32" s="108"/>
-      <c r="AH32" s="108"/>
-      <c r="AI32" s="109"/>
-    </row>
-    <row r="33" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="77"/>
+      <c r="C32" s="78"/>
+      <c r="D32" s="79"/>
+      <c r="E32" s="80"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="82"/>
+      <c r="I32" s="78"/>
+      <c r="J32" s="83"/>
+      <c r="K32" s="89"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="84"/>
+      <c r="N32" s="84"/>
+      <c r="O32" s="84"/>
+      <c r="P32" s="85"/>
+      <c r="Q32" s="86"/>
+      <c r="R32" s="87"/>
+      <c r="S32" s="87"/>
+      <c r="T32" s="87"/>
+      <c r="U32" s="87"/>
+      <c r="V32" s="87"/>
+      <c r="W32" s="87"/>
+      <c r="X32" s="87"/>
+      <c r="Y32" s="87"/>
+      <c r="Z32" s="87"/>
+      <c r="AA32" s="87"/>
+      <c r="AB32" s="87"/>
+      <c r="AC32" s="87"/>
+      <c r="AD32" s="87"/>
+      <c r="AE32" s="88"/>
+      <c r="AF32" s="83"/>
+      <c r="AG32" s="84"/>
+      <c r="AH32" s="84"/>
+      <c r="AI32" s="85"/>
+    </row>
+    <row r="33" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="29"/>
-      <c r="B33" s="101"/>
-      <c r="C33" s="102"/>
-      <c r="D33" s="103"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="105"/>
-      <c r="G33" s="101"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="102"/>
-      <c r="J33" s="107"/>
-      <c r="K33" s="108"/>
-      <c r="L33" s="108"/>
-      <c r="M33" s="108"/>
-      <c r="N33" s="108"/>
-      <c r="O33" s="108"/>
-      <c r="P33" s="109"/>
-      <c r="Q33" s="110"/>
-      <c r="R33" s="111"/>
-      <c r="S33" s="111"/>
-      <c r="T33" s="111"/>
-      <c r="U33" s="111"/>
-      <c r="V33" s="111"/>
-      <c r="W33" s="111"/>
-      <c r="X33" s="111"/>
-      <c r="Y33" s="111"/>
-      <c r="Z33" s="111"/>
-      <c r="AA33" s="111"/>
-      <c r="AB33" s="111"/>
-      <c r="AC33" s="111"/>
-      <c r="AD33" s="111"/>
-      <c r="AE33" s="112"/>
-      <c r="AF33" s="107"/>
-      <c r="AG33" s="108"/>
-      <c r="AH33" s="108"/>
-      <c r="AI33" s="109"/>
-    </row>
-    <row r="34" spans="1:35" ht="14" x14ac:dyDescent="0.2">
+      <c r="B33" s="77"/>
+      <c r="C33" s="78"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="82"/>
+      <c r="I33" s="78"/>
+      <c r="J33" s="83"/>
+      <c r="K33" s="84"/>
+      <c r="L33" s="84"/>
+      <c r="M33" s="84"/>
+      <c r="N33" s="84"/>
+      <c r="O33" s="84"/>
+      <c r="P33" s="85"/>
+      <c r="Q33" s="86"/>
+      <c r="R33" s="87"/>
+      <c r="S33" s="87"/>
+      <c r="T33" s="87"/>
+      <c r="U33" s="87"/>
+      <c r="V33" s="87"/>
+      <c r="W33" s="87"/>
+      <c r="X33" s="87"/>
+      <c r="Y33" s="87"/>
+      <c r="Z33" s="87"/>
+      <c r="AA33" s="87"/>
+      <c r="AB33" s="87"/>
+      <c r="AC33" s="87"/>
+      <c r="AD33" s="87"/>
+      <c r="AE33" s="88"/>
+      <c r="AF33" s="83"/>
+      <c r="AG33" s="84"/>
+      <c r="AH33" s="84"/>
+      <c r="AI33" s="85"/>
+    </row>
+    <row r="34" spans="1:35" ht="14.25" x14ac:dyDescent="0.15">
       <c r="K34" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="179">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -9125,6 +8952,162 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1"/>
@@ -9140,304 +9123,304 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AL50"/>
-  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16" width="3.6328125" style="37" customWidth="1"/>
-    <col min="17" max="17" width="3.6328125" style="48" customWidth="1"/>
-    <col min="18" max="33" width="3.6328125" style="37" customWidth="1"/>
-    <col min="34" max="34" width="3.6328125" style="48" customWidth="1"/>
-    <col min="35" max="256" width="3.6328125" style="37"/>
-    <col min="257" max="290" width="3.6328125" style="37" customWidth="1"/>
-    <col min="291" max="512" width="3.6328125" style="37"/>
-    <col min="513" max="546" width="3.6328125" style="37" customWidth="1"/>
-    <col min="547" max="768" width="3.6328125" style="37"/>
-    <col min="769" max="802" width="3.6328125" style="37" customWidth="1"/>
-    <col min="803" max="1024" width="3.6328125" style="37"/>
-    <col min="1025" max="1058" width="3.6328125" style="37" customWidth="1"/>
-    <col min="1059" max="1280" width="3.6328125" style="37"/>
-    <col min="1281" max="1314" width="3.6328125" style="37" customWidth="1"/>
-    <col min="1315" max="1536" width="3.6328125" style="37"/>
-    <col min="1537" max="1570" width="3.6328125" style="37" customWidth="1"/>
-    <col min="1571" max="1792" width="3.6328125" style="37"/>
-    <col min="1793" max="1826" width="3.6328125" style="37" customWidth="1"/>
-    <col min="1827" max="2048" width="3.6328125" style="37"/>
-    <col min="2049" max="2082" width="3.6328125" style="37" customWidth="1"/>
-    <col min="2083" max="2304" width="3.6328125" style="37"/>
-    <col min="2305" max="2338" width="3.6328125" style="37" customWidth="1"/>
-    <col min="2339" max="2560" width="3.6328125" style="37"/>
-    <col min="2561" max="2594" width="3.6328125" style="37" customWidth="1"/>
-    <col min="2595" max="2816" width="3.6328125" style="37"/>
-    <col min="2817" max="2850" width="3.6328125" style="37" customWidth="1"/>
-    <col min="2851" max="3072" width="3.6328125" style="37"/>
-    <col min="3073" max="3106" width="3.6328125" style="37" customWidth="1"/>
-    <col min="3107" max="3328" width="3.6328125" style="37"/>
-    <col min="3329" max="3362" width="3.6328125" style="37" customWidth="1"/>
-    <col min="3363" max="3584" width="3.6328125" style="37"/>
-    <col min="3585" max="3618" width="3.6328125" style="37" customWidth="1"/>
-    <col min="3619" max="3840" width="3.6328125" style="37"/>
-    <col min="3841" max="3874" width="3.6328125" style="37" customWidth="1"/>
-    <col min="3875" max="4096" width="3.6328125" style="37"/>
-    <col min="4097" max="4130" width="3.6328125" style="37" customWidth="1"/>
-    <col min="4131" max="4352" width="3.6328125" style="37"/>
-    <col min="4353" max="4386" width="3.6328125" style="37" customWidth="1"/>
-    <col min="4387" max="4608" width="3.6328125" style="37"/>
-    <col min="4609" max="4642" width="3.6328125" style="37" customWidth="1"/>
-    <col min="4643" max="4864" width="3.6328125" style="37"/>
-    <col min="4865" max="4898" width="3.6328125" style="37" customWidth="1"/>
-    <col min="4899" max="5120" width="3.6328125" style="37"/>
-    <col min="5121" max="5154" width="3.6328125" style="37" customWidth="1"/>
-    <col min="5155" max="5376" width="3.6328125" style="37"/>
-    <col min="5377" max="5410" width="3.6328125" style="37" customWidth="1"/>
-    <col min="5411" max="5632" width="3.6328125" style="37"/>
-    <col min="5633" max="5666" width="3.6328125" style="37" customWidth="1"/>
-    <col min="5667" max="5888" width="3.6328125" style="37"/>
-    <col min="5889" max="5922" width="3.6328125" style="37" customWidth="1"/>
-    <col min="5923" max="6144" width="3.6328125" style="37"/>
-    <col min="6145" max="6178" width="3.6328125" style="37" customWidth="1"/>
-    <col min="6179" max="6400" width="3.6328125" style="37"/>
-    <col min="6401" max="6434" width="3.6328125" style="37" customWidth="1"/>
-    <col min="6435" max="6656" width="3.6328125" style="37"/>
-    <col min="6657" max="6690" width="3.6328125" style="37" customWidth="1"/>
-    <col min="6691" max="6912" width="3.6328125" style="37"/>
-    <col min="6913" max="6946" width="3.6328125" style="37" customWidth="1"/>
-    <col min="6947" max="7168" width="3.6328125" style="37"/>
-    <col min="7169" max="7202" width="3.6328125" style="37" customWidth="1"/>
-    <col min="7203" max="7424" width="3.6328125" style="37"/>
-    <col min="7425" max="7458" width="3.6328125" style="37" customWidth="1"/>
-    <col min="7459" max="7680" width="3.6328125" style="37"/>
-    <col min="7681" max="7714" width="3.6328125" style="37" customWidth="1"/>
-    <col min="7715" max="7936" width="3.6328125" style="37"/>
-    <col min="7937" max="7970" width="3.6328125" style="37" customWidth="1"/>
-    <col min="7971" max="8192" width="3.6328125" style="37"/>
-    <col min="8193" max="8226" width="3.6328125" style="37" customWidth="1"/>
-    <col min="8227" max="8448" width="3.6328125" style="37"/>
-    <col min="8449" max="8482" width="3.6328125" style="37" customWidth="1"/>
-    <col min="8483" max="8704" width="3.6328125" style="37"/>
-    <col min="8705" max="8738" width="3.6328125" style="37" customWidth="1"/>
-    <col min="8739" max="8960" width="3.6328125" style="37"/>
-    <col min="8961" max="8994" width="3.6328125" style="37" customWidth="1"/>
-    <col min="8995" max="9216" width="3.6328125" style="37"/>
-    <col min="9217" max="9250" width="3.6328125" style="37" customWidth="1"/>
-    <col min="9251" max="9472" width="3.6328125" style="37"/>
-    <col min="9473" max="9506" width="3.6328125" style="37" customWidth="1"/>
-    <col min="9507" max="9728" width="3.6328125" style="37"/>
-    <col min="9729" max="9762" width="3.6328125" style="37" customWidth="1"/>
-    <col min="9763" max="9984" width="3.6328125" style="37"/>
-    <col min="9985" max="10018" width="3.6328125" style="37" customWidth="1"/>
-    <col min="10019" max="10240" width="3.6328125" style="37"/>
-    <col min="10241" max="10274" width="3.6328125" style="37" customWidth="1"/>
-    <col min="10275" max="10496" width="3.6328125" style="37"/>
-    <col min="10497" max="10530" width="3.6328125" style="37" customWidth="1"/>
-    <col min="10531" max="10752" width="3.6328125" style="37"/>
-    <col min="10753" max="10786" width="3.6328125" style="37" customWidth="1"/>
-    <col min="10787" max="11008" width="3.6328125" style="37"/>
-    <col min="11009" max="11042" width="3.6328125" style="37" customWidth="1"/>
-    <col min="11043" max="11264" width="3.6328125" style="37"/>
-    <col min="11265" max="11298" width="3.6328125" style="37" customWidth="1"/>
-    <col min="11299" max="11520" width="3.6328125" style="37"/>
-    <col min="11521" max="11554" width="3.6328125" style="37" customWidth="1"/>
-    <col min="11555" max="11776" width="3.6328125" style="37"/>
-    <col min="11777" max="11810" width="3.6328125" style="37" customWidth="1"/>
-    <col min="11811" max="12032" width="3.6328125" style="37"/>
-    <col min="12033" max="12066" width="3.6328125" style="37" customWidth="1"/>
-    <col min="12067" max="12288" width="3.6328125" style="37"/>
-    <col min="12289" max="12322" width="3.6328125" style="37" customWidth="1"/>
-    <col min="12323" max="12544" width="3.6328125" style="37"/>
-    <col min="12545" max="12578" width="3.6328125" style="37" customWidth="1"/>
-    <col min="12579" max="12800" width="3.6328125" style="37"/>
-    <col min="12801" max="12834" width="3.6328125" style="37" customWidth="1"/>
-    <col min="12835" max="13056" width="3.6328125" style="37"/>
-    <col min="13057" max="13090" width="3.6328125" style="37" customWidth="1"/>
-    <col min="13091" max="13312" width="3.6328125" style="37"/>
-    <col min="13313" max="13346" width="3.6328125" style="37" customWidth="1"/>
-    <col min="13347" max="13568" width="3.6328125" style="37"/>
-    <col min="13569" max="13602" width="3.6328125" style="37" customWidth="1"/>
-    <col min="13603" max="13824" width="3.6328125" style="37"/>
-    <col min="13825" max="13858" width="3.6328125" style="37" customWidth="1"/>
-    <col min="13859" max="14080" width="3.6328125" style="37"/>
-    <col min="14081" max="14114" width="3.6328125" style="37" customWidth="1"/>
-    <col min="14115" max="14336" width="3.6328125" style="37"/>
-    <col min="14337" max="14370" width="3.6328125" style="37" customWidth="1"/>
-    <col min="14371" max="14592" width="3.6328125" style="37"/>
-    <col min="14593" max="14626" width="3.6328125" style="37" customWidth="1"/>
-    <col min="14627" max="14848" width="3.6328125" style="37"/>
-    <col min="14849" max="14882" width="3.6328125" style="37" customWidth="1"/>
-    <col min="14883" max="15104" width="3.6328125" style="37"/>
-    <col min="15105" max="15138" width="3.6328125" style="37" customWidth="1"/>
-    <col min="15139" max="15360" width="3.6328125" style="37"/>
-    <col min="15361" max="15394" width="3.6328125" style="37" customWidth="1"/>
-    <col min="15395" max="15616" width="3.6328125" style="37"/>
-    <col min="15617" max="15650" width="3.6328125" style="37" customWidth="1"/>
-    <col min="15651" max="15872" width="3.6328125" style="37"/>
-    <col min="15873" max="15906" width="3.6328125" style="37" customWidth="1"/>
-    <col min="15907" max="16128" width="3.6328125" style="37"/>
-    <col min="16129" max="16162" width="3.6328125" style="37" customWidth="1"/>
-    <col min="16163" max="16384" width="3.6328125" style="37"/>
+    <col min="1" max="16" width="3.625" style="37" customWidth="1"/>
+    <col min="17" max="17" width="3.625" style="48" customWidth="1"/>
+    <col min="18" max="33" width="3.625" style="37" customWidth="1"/>
+    <col min="34" max="34" width="3.625" style="48" customWidth="1"/>
+    <col min="35" max="256" width="3.625" style="37"/>
+    <col min="257" max="290" width="3.625" style="37" customWidth="1"/>
+    <col min="291" max="512" width="3.625" style="37"/>
+    <col min="513" max="546" width="3.625" style="37" customWidth="1"/>
+    <col min="547" max="768" width="3.625" style="37"/>
+    <col min="769" max="802" width="3.625" style="37" customWidth="1"/>
+    <col min="803" max="1024" width="3.625" style="37"/>
+    <col min="1025" max="1058" width="3.625" style="37" customWidth="1"/>
+    <col min="1059" max="1280" width="3.625" style="37"/>
+    <col min="1281" max="1314" width="3.625" style="37" customWidth="1"/>
+    <col min="1315" max="1536" width="3.625" style="37"/>
+    <col min="1537" max="1570" width="3.625" style="37" customWidth="1"/>
+    <col min="1571" max="1792" width="3.625" style="37"/>
+    <col min="1793" max="1826" width="3.625" style="37" customWidth="1"/>
+    <col min="1827" max="2048" width="3.625" style="37"/>
+    <col min="2049" max="2082" width="3.625" style="37" customWidth="1"/>
+    <col min="2083" max="2304" width="3.625" style="37"/>
+    <col min="2305" max="2338" width="3.625" style="37" customWidth="1"/>
+    <col min="2339" max="2560" width="3.625" style="37"/>
+    <col min="2561" max="2594" width="3.625" style="37" customWidth="1"/>
+    <col min="2595" max="2816" width="3.625" style="37"/>
+    <col min="2817" max="2850" width="3.625" style="37" customWidth="1"/>
+    <col min="2851" max="3072" width="3.625" style="37"/>
+    <col min="3073" max="3106" width="3.625" style="37" customWidth="1"/>
+    <col min="3107" max="3328" width="3.625" style="37"/>
+    <col min="3329" max="3362" width="3.625" style="37" customWidth="1"/>
+    <col min="3363" max="3584" width="3.625" style="37"/>
+    <col min="3585" max="3618" width="3.625" style="37" customWidth="1"/>
+    <col min="3619" max="3840" width="3.625" style="37"/>
+    <col min="3841" max="3874" width="3.625" style="37" customWidth="1"/>
+    <col min="3875" max="4096" width="3.625" style="37"/>
+    <col min="4097" max="4130" width="3.625" style="37" customWidth="1"/>
+    <col min="4131" max="4352" width="3.625" style="37"/>
+    <col min="4353" max="4386" width="3.625" style="37" customWidth="1"/>
+    <col min="4387" max="4608" width="3.625" style="37"/>
+    <col min="4609" max="4642" width="3.625" style="37" customWidth="1"/>
+    <col min="4643" max="4864" width="3.625" style="37"/>
+    <col min="4865" max="4898" width="3.625" style="37" customWidth="1"/>
+    <col min="4899" max="5120" width="3.625" style="37"/>
+    <col min="5121" max="5154" width="3.625" style="37" customWidth="1"/>
+    <col min="5155" max="5376" width="3.625" style="37"/>
+    <col min="5377" max="5410" width="3.625" style="37" customWidth="1"/>
+    <col min="5411" max="5632" width="3.625" style="37"/>
+    <col min="5633" max="5666" width="3.625" style="37" customWidth="1"/>
+    <col min="5667" max="5888" width="3.625" style="37"/>
+    <col min="5889" max="5922" width="3.625" style="37" customWidth="1"/>
+    <col min="5923" max="6144" width="3.625" style="37"/>
+    <col min="6145" max="6178" width="3.625" style="37" customWidth="1"/>
+    <col min="6179" max="6400" width="3.625" style="37"/>
+    <col min="6401" max="6434" width="3.625" style="37" customWidth="1"/>
+    <col min="6435" max="6656" width="3.625" style="37"/>
+    <col min="6657" max="6690" width="3.625" style="37" customWidth="1"/>
+    <col min="6691" max="6912" width="3.625" style="37"/>
+    <col min="6913" max="6946" width="3.625" style="37" customWidth="1"/>
+    <col min="6947" max="7168" width="3.625" style="37"/>
+    <col min="7169" max="7202" width="3.625" style="37" customWidth="1"/>
+    <col min="7203" max="7424" width="3.625" style="37"/>
+    <col min="7425" max="7458" width="3.625" style="37" customWidth="1"/>
+    <col min="7459" max="7680" width="3.625" style="37"/>
+    <col min="7681" max="7714" width="3.625" style="37" customWidth="1"/>
+    <col min="7715" max="7936" width="3.625" style="37"/>
+    <col min="7937" max="7970" width="3.625" style="37" customWidth="1"/>
+    <col min="7971" max="8192" width="3.625" style="37"/>
+    <col min="8193" max="8226" width="3.625" style="37" customWidth="1"/>
+    <col min="8227" max="8448" width="3.625" style="37"/>
+    <col min="8449" max="8482" width="3.625" style="37" customWidth="1"/>
+    <col min="8483" max="8704" width="3.625" style="37"/>
+    <col min="8705" max="8738" width="3.625" style="37" customWidth="1"/>
+    <col min="8739" max="8960" width="3.625" style="37"/>
+    <col min="8961" max="8994" width="3.625" style="37" customWidth="1"/>
+    <col min="8995" max="9216" width="3.625" style="37"/>
+    <col min="9217" max="9250" width="3.625" style="37" customWidth="1"/>
+    <col min="9251" max="9472" width="3.625" style="37"/>
+    <col min="9473" max="9506" width="3.625" style="37" customWidth="1"/>
+    <col min="9507" max="9728" width="3.625" style="37"/>
+    <col min="9729" max="9762" width="3.625" style="37" customWidth="1"/>
+    <col min="9763" max="9984" width="3.625" style="37"/>
+    <col min="9985" max="10018" width="3.625" style="37" customWidth="1"/>
+    <col min="10019" max="10240" width="3.625" style="37"/>
+    <col min="10241" max="10274" width="3.625" style="37" customWidth="1"/>
+    <col min="10275" max="10496" width="3.625" style="37"/>
+    <col min="10497" max="10530" width="3.625" style="37" customWidth="1"/>
+    <col min="10531" max="10752" width="3.625" style="37"/>
+    <col min="10753" max="10786" width="3.625" style="37" customWidth="1"/>
+    <col min="10787" max="11008" width="3.625" style="37"/>
+    <col min="11009" max="11042" width="3.625" style="37" customWidth="1"/>
+    <col min="11043" max="11264" width="3.625" style="37"/>
+    <col min="11265" max="11298" width="3.625" style="37" customWidth="1"/>
+    <col min="11299" max="11520" width="3.625" style="37"/>
+    <col min="11521" max="11554" width="3.625" style="37" customWidth="1"/>
+    <col min="11555" max="11776" width="3.625" style="37"/>
+    <col min="11777" max="11810" width="3.625" style="37" customWidth="1"/>
+    <col min="11811" max="12032" width="3.625" style="37"/>
+    <col min="12033" max="12066" width="3.625" style="37" customWidth="1"/>
+    <col min="12067" max="12288" width="3.625" style="37"/>
+    <col min="12289" max="12322" width="3.625" style="37" customWidth="1"/>
+    <col min="12323" max="12544" width="3.625" style="37"/>
+    <col min="12545" max="12578" width="3.625" style="37" customWidth="1"/>
+    <col min="12579" max="12800" width="3.625" style="37"/>
+    <col min="12801" max="12834" width="3.625" style="37" customWidth="1"/>
+    <col min="12835" max="13056" width="3.625" style="37"/>
+    <col min="13057" max="13090" width="3.625" style="37" customWidth="1"/>
+    <col min="13091" max="13312" width="3.625" style="37"/>
+    <col min="13313" max="13346" width="3.625" style="37" customWidth="1"/>
+    <col min="13347" max="13568" width="3.625" style="37"/>
+    <col min="13569" max="13602" width="3.625" style="37" customWidth="1"/>
+    <col min="13603" max="13824" width="3.625" style="37"/>
+    <col min="13825" max="13858" width="3.625" style="37" customWidth="1"/>
+    <col min="13859" max="14080" width="3.625" style="37"/>
+    <col min="14081" max="14114" width="3.625" style="37" customWidth="1"/>
+    <col min="14115" max="14336" width="3.625" style="37"/>
+    <col min="14337" max="14370" width="3.625" style="37" customWidth="1"/>
+    <col min="14371" max="14592" width="3.625" style="37"/>
+    <col min="14593" max="14626" width="3.625" style="37" customWidth="1"/>
+    <col min="14627" max="14848" width="3.625" style="37"/>
+    <col min="14849" max="14882" width="3.625" style="37" customWidth="1"/>
+    <col min="14883" max="15104" width="3.625" style="37"/>
+    <col min="15105" max="15138" width="3.625" style="37" customWidth="1"/>
+    <col min="15139" max="15360" width="3.625" style="37"/>
+    <col min="15361" max="15394" width="3.625" style="37" customWidth="1"/>
+    <col min="15395" max="15616" width="3.625" style="37"/>
+    <col min="15617" max="15650" width="3.625" style="37" customWidth="1"/>
+    <col min="15651" max="15872" width="3.625" style="37"/>
+    <col min="15873" max="15906" width="3.625" style="37" customWidth="1"/>
+    <col min="15907" max="16128" width="3.625" style="37"/>
+    <col min="16129" max="16162" width="3.625" style="37" customWidth="1"/>
+    <col min="16163" max="16384" width="3.625" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="71" t="s">
+    <row r="1" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="110" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="74" t="str">
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="113" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="80" t="s">
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="119" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="89" t="str">
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="128" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarchを使用したシステム開発における標準WBS</v>
       </c>
-      <c r="T1" s="90"/>
-      <c r="U1" s="90"/>
-      <c r="V1" s="90"/>
-      <c r="W1" s="90"/>
-      <c r="X1" s="90"/>
-      <c r="Y1" s="90"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="131" t="s">
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
+      <c r="W1" s="129"/>
+      <c r="X1" s="129"/>
+      <c r="Y1" s="129"/>
+      <c r="Z1" s="130"/>
+      <c r="AA1" s="140" t="s">
         <v>280</v>
       </c>
-      <c r="AB1" s="132"/>
-      <c r="AC1" s="98" t="str">
+      <c r="AB1" s="141"/>
+      <c r="AC1" s="137" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="99"/>
-      <c r="AE1" s="99"/>
-      <c r="AF1" s="100"/>
-      <c r="AG1" s="128">
+      <c r="AD1" s="138"/>
+      <c r="AE1" s="138"/>
+      <c r="AF1" s="139"/>
+      <c r="AG1" s="142">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="129"/>
-      <c r="AI1" s="130"/>
+      <c r="AH1" s="143"/>
+      <c r="AI1" s="144"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3"/>
     </row>
-    <row r="2" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="71" t="s">
+    <row r="2" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="110" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="74" t="str">
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="113" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="75"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="84"/>
-      <c r="R2" s="85"/>
-      <c r="S2" s="92"/>
-      <c r="T2" s="93"/>
-      <c r="U2" s="93"/>
-      <c r="V2" s="93"/>
-      <c r="W2" s="93"/>
-      <c r="X2" s="93"/>
-      <c r="Y2" s="93"/>
-      <c r="Z2" s="94"/>
-      <c r="AA2" s="131" t="s">
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="115"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="123"/>
+      <c r="Q2" s="123"/>
+      <c r="R2" s="124"/>
+      <c r="S2" s="131"/>
+      <c r="T2" s="132"/>
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="132"/>
+      <c r="X2" s="132"/>
+      <c r="Y2" s="132"/>
+      <c r="Z2" s="133"/>
+      <c r="AA2" s="140" t="s">
         <v>282</v>
       </c>
-      <c r="AB2" s="132"/>
-      <c r="AC2" s="98" t="str">
+      <c r="AB2" s="141"/>
+      <c r="AC2" s="137" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="99"/>
-      <c r="AE2" s="99"/>
-      <c r="AF2" s="100"/>
-      <c r="AG2" s="128">
+      <c r="AD2" s="138"/>
+      <c r="AE2" s="138"/>
+      <c r="AF2" s="139"/>
+      <c r="AG2" s="142">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>44455</v>
-      </c>
-      <c r="AH2" s="129"/>
-      <c r="AI2" s="130"/>
+        <v>45461</v>
+      </c>
+      <c r="AH2" s="143"/>
+      <c r="AI2" s="144"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
     </row>
-    <row r="3" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="71" t="s">
+    <row r="3" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="110" t="s">
         <v>283</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="74" t="str">
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="113" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="75"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="87"/>
-      <c r="Q3" s="87"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="95"/>
-      <c r="T3" s="96"/>
-      <c r="U3" s="96"/>
-      <c r="V3" s="96"/>
-      <c r="W3" s="96"/>
-      <c r="X3" s="96"/>
-      <c r="Y3" s="96"/>
-      <c r="Z3" s="97"/>
-      <c r="AA3" s="131"/>
-      <c r="AB3" s="132"/>
-      <c r="AC3" s="98" t="str">
+      <c r="F3" s="114"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="114"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="126"/>
+      <c r="Q3" s="126"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="134"/>
+      <c r="T3" s="135"/>
+      <c r="U3" s="135"/>
+      <c r="V3" s="135"/>
+      <c r="W3" s="135"/>
+      <c r="X3" s="135"/>
+      <c r="Y3" s="135"/>
+      <c r="Z3" s="136"/>
+      <c r="AA3" s="140"/>
+      <c r="AB3" s="141"/>
+      <c r="AC3" s="137" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="99"/>
-      <c r="AE3" s="99"/>
-      <c r="AF3" s="100"/>
-      <c r="AG3" s="128" t="str">
+      <c r="AD3" s="138"/>
+      <c r="AE3" s="138"/>
+      <c r="AF3" s="139"/>
+      <c r="AG3" s="142" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="129"/>
-      <c r="AI3" s="130"/>
+      <c r="AH3" s="143"/>
+      <c r="AI3" s="144"/>
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
     </row>
-    <row r="4" spans="1:38" s="33" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:38" s="33" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="30"/>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -9474,7 +9457,7 @@
       <c r="AH4" s="30"/>
       <c r="AI4" s="30"/>
     </row>
-    <row r="5" spans="1:38" s="33" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" s="33" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="30"/>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
@@ -9513,7 +9496,7 @@
       <c r="AH5" s="30"/>
       <c r="AI5" s="30"/>
     </row>
-    <row r="6" spans="1:38" s="33" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" s="33" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="30"/>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -9550,7 +9533,7 @@
       <c r="AH6" s="30"/>
       <c r="AI6" s="30"/>
     </row>
-    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="30"/>
       <c r="B7" s="30" t="s">
         <v>302</v>
@@ -9589,7 +9572,7 @@
       <c r="AH7" s="36"/>
       <c r="AI7" s="30"/>
     </row>
-    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="30"/>
       <c r="B8" s="30"/>
       <c r="C8" s="34" t="s">
@@ -9628,7 +9611,7 @@
       <c r="AH8" s="36"/>
       <c r="AI8" s="30"/>
     </row>
-    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="30"/>
       <c r="B9" s="30"/>
       <c r="C9" s="34" t="s">
@@ -9666,7 +9649,7 @@
       <c r="AH9" s="36"/>
       <c r="AI9" s="30"/>
     </row>
-    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="30"/>
       <c r="B10" s="30"/>
       <c r="C10" s="34" t="s">
@@ -9704,11 +9687,11 @@
       <c r="AH10" s="36"/>
       <c r="AI10" s="30"/>
     </row>
-    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="30"/>
       <c r="B11" s="30"/>
       <c r="C11" s="34" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
@@ -9742,7 +9725,7 @@
       <c r="AH11" s="36"/>
       <c r="AI11" s="30"/>
     </row>
-    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="30"/>
       <c r="B12" s="30"/>
       <c r="C12" s="30"/>
@@ -9778,7 +9761,7 @@
       <c r="AH12" s="36"/>
       <c r="AI12" s="30"/>
     </row>
-    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="30"/>
       <c r="B13" s="30" t="s">
         <v>303</v>
@@ -9817,7 +9800,7 @@
       <c r="AH13" s="36"/>
       <c r="AI13" s="30"/>
     </row>
-    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="30"/>
       <c r="B14" s="30"/>
       <c r="C14" s="30"/>
@@ -9854,7 +9837,7 @@
       <c r="AH14" s="36"/>
       <c r="AI14" s="30"/>
     </row>
-    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="30"/>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
@@ -9891,7 +9874,7 @@
       <c r="AH15" s="36"/>
       <c r="AI15" s="30"/>
     </row>
-    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="30"/>
       <c r="B16" s="38"/>
       <c r="C16" s="30"/>
@@ -9928,7 +9911,7 @@
       <c r="AH16" s="36"/>
       <c r="AI16" s="30"/>
     </row>
-    <row r="17" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="30"/>
       <c r="B17" s="30"/>
       <c r="C17" s="30"/>
@@ -9965,7 +9948,7 @@
       <c r="AH17" s="36"/>
       <c r="AI17" s="30"/>
     </row>
-    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="30"/>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
@@ -10002,7 +9985,7 @@
       <c r="AH18" s="36"/>
       <c r="AI18" s="30"/>
     </row>
-    <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="30"/>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
@@ -10039,7 +10022,7 @@
       <c r="AH19" s="36"/>
       <c r="AI19" s="30"/>
     </row>
-    <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="30"/>
       <c r="B20" s="30"/>
       <c r="C20" s="30"/>
@@ -10076,7 +10059,7 @@
       <c r="AH20" s="36"/>
       <c r="AI20" s="30"/>
     </row>
-    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="30"/>
       <c r="B21" s="30"/>
       <c r="C21" s="30"/>
@@ -10113,7 +10096,7 @@
       <c r="AH21" s="36"/>
       <c r="AI21" s="30"/>
     </row>
-    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="30"/>
       <c r="B22" s="30"/>
       <c r="C22" s="30"/>
@@ -10149,7 +10132,7 @@
       <c r="AH22" s="36"/>
       <c r="AI22" s="30"/>
     </row>
-    <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="30"/>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
@@ -10186,7 +10169,7 @@
       <c r="AH23" s="36"/>
       <c r="AI23" s="30"/>
     </row>
-    <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="30"/>
       <c r="B24" s="38"/>
       <c r="C24" s="30"/>
@@ -10223,7 +10206,7 @@
       <c r="AH24" s="36"/>
       <c r="AI24" s="30"/>
     </row>
-    <row r="25" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="30"/>
       <c r="B25" s="30"/>
       <c r="C25" s="30"/>
@@ -10260,7 +10243,7 @@
       <c r="AH25" s="36"/>
       <c r="AI25" s="30"/>
     </row>
-    <row r="26" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="30"/>
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
@@ -10297,7 +10280,7 @@
       <c r="AH26" s="36"/>
       <c r="AI26" s="30"/>
     </row>
-    <row r="27" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="30"/>
       <c r="B27" s="30"/>
       <c r="C27" s="30"/>
@@ -10334,7 +10317,7 @@
       <c r="AH27" s="36"/>
       <c r="AI27" s="30"/>
     </row>
-    <row r="28" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="30"/>
       <c r="B28" s="30"/>
       <c r="C28" s="30"/>
@@ -10371,7 +10354,7 @@
       <c r="AH28" s="36"/>
       <c r="AI28" s="30"/>
     </row>
-    <row r="29" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="30"/>
       <c r="B29" s="30"/>
       <c r="C29" s="30"/>
@@ -10408,7 +10391,7 @@
       <c r="AH29" s="36"/>
       <c r="AI29" s="30"/>
     </row>
-    <row r="30" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="30"/>
       <c r="B30" s="30"/>
       <c r="C30" s="30"/>
@@ -10445,7 +10428,7 @@
       <c r="AH30" s="36"/>
       <c r="AI30" s="30"/>
     </row>
-    <row r="31" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="39"/>
       <c r="B31" s="30"/>
       <c r="C31" s="30"/>
@@ -10482,7 +10465,7 @@
       <c r="AH31" s="41"/>
       <c r="AI31" s="39"/>
     </row>
-    <row r="32" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="39"/>
       <c r="B32" s="30"/>
       <c r="C32" s="32"/>
@@ -10519,7 +10502,7 @@
       <c r="AH32" s="41"/>
       <c r="AI32" s="39"/>
     </row>
-    <row r="33" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="39"/>
       <c r="B33" s="39"/>
       <c r="C33" s="30"/>
@@ -10556,7 +10539,7 @@
       <c r="AH33" s="41"/>
       <c r="AI33" s="39"/>
     </row>
-    <row r="34" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="39"/>
       <c r="B34" s="39"/>
       <c r="C34" s="30"/>
@@ -10593,7 +10576,7 @@
       <c r="AH34" s="41"/>
       <c r="AI34" s="39"/>
     </row>
-    <row r="35" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="39"/>
       <c r="B35" s="39"/>
       <c r="C35" s="30"/>
@@ -10630,7 +10613,7 @@
       <c r="AH35" s="41"/>
       <c r="AI35" s="39"/>
     </row>
-    <row r="36" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="39"/>
       <c r="B36" s="39"/>
       <c r="C36" s="30"/>
@@ -10667,7 +10650,7 @@
       <c r="AH36" s="41"/>
       <c r="AI36" s="39"/>
     </row>
-    <row r="37" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="39"/>
       <c r="B37" s="39"/>
       <c r="C37" s="39"/>
@@ -10704,54 +10687,62 @@
       <c r="AH37" s="41"/>
       <c r="AI37" s="39"/>
     </row>
-    <row r="38" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="P38" s="47"/>
       <c r="U38" s="49"/>
       <c r="AG38" s="50"/>
     </row>
-    <row r="39" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="U39" s="49"/>
       <c r="AF39" s="50"/>
       <c r="AG39" s="47"/>
     </row>
-    <row r="40" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="T40" s="49"/>
       <c r="AF40" s="50"/>
       <c r="AG40" s="50"/>
     </row>
-    <row r="41" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AG41" s="47"/>
     </row>
-    <row r="42" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AG42" s="47"/>
     </row>
-    <row r="43" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AF43" s="50"/>
       <c r="AG43" s="47"/>
     </row>
-    <row r="44" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AF44" s="50"/>
       <c r="AG44" s="50"/>
     </row>
-    <row r="45" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AF45" s="50"/>
       <c r="AG45" s="50"/>
     </row>
-    <row r="46" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AG46" s="50"/>
     </row>
-    <row r="47" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AF47" s="50"/>
       <c r="AG47" s="50"/>
     </row>
-    <row r="48" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AG48" s="50"/>
     </row>
-    <row r="50" spans="33:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="33:33" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AG50" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -10761,14 +10752,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1"/>
@@ -10783,67 +10766,67 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AW110"/>
-  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="11" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AW94"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="31" width="3.6328125" style="30" customWidth="1"/>
-    <col min="32" max="16384" width="3.6328125" style="30"/>
+    <col min="1" max="31" width="3.625" style="30" customWidth="1"/>
+    <col min="32" max="16384" width="3.625" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="71" t="s">
+    <row r="1" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="110" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="74" t="str">
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="113" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="134" t="s">
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="149" t="s">
         <v>294</v>
       </c>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="136"/>
-      <c r="S1" s="89" t="str">
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="128" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarchを使用したシステム開発における標準WBS</v>
       </c>
-      <c r="T1" s="90"/>
-      <c r="U1" s="90"/>
-      <c r="V1" s="90"/>
-      <c r="W1" s="90"/>
-      <c r="X1" s="90"/>
-      <c r="Y1" s="90"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="71" t="s">
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
+      <c r="W1" s="129"/>
+      <c r="X1" s="129"/>
+      <c r="Y1" s="129"/>
+      <c r="Z1" s="130"/>
+      <c r="AA1" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="98" t="str">
+      <c r="AB1" s="112"/>
+      <c r="AC1" s="137" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="99"/>
-      <c r="AE1" s="99"/>
-      <c r="AF1" s="100"/>
-      <c r="AG1" s="128">
+      <c r="AD1" s="138"/>
+      <c r="AE1" s="138"/>
+      <c r="AF1" s="139"/>
+      <c r="AG1" s="142">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="129"/>
-      <c r="AI1" s="130"/>
+      <c r="AH1" s="143"/>
+      <c r="AI1" s="144"/>
       <c r="AJ1" s="30"/>
       <c r="AN1" s="51"/>
       <c r="AO1" s="30"/>
@@ -10856,55 +10839,55 @@
       <c r="AV1" s="30"/>
       <c r="AW1" s="30"/>
     </row>
-    <row r="2" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="71" t="s">
+    <row r="2" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="110" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="74" t="str">
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="113" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="75"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="137"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="139"/>
-      <c r="S2" s="92"/>
-      <c r="T2" s="93"/>
-      <c r="U2" s="93"/>
-      <c r="V2" s="93"/>
-      <c r="W2" s="93"/>
-      <c r="X2" s="93"/>
-      <c r="Y2" s="93"/>
-      <c r="Z2" s="94"/>
-      <c r="AA2" s="71" t="s">
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="115"/>
+      <c r="O2" s="152"/>
+      <c r="P2" s="153"/>
+      <c r="Q2" s="153"/>
+      <c r="R2" s="154"/>
+      <c r="S2" s="131"/>
+      <c r="T2" s="132"/>
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="132"/>
+      <c r="X2" s="132"/>
+      <c r="Y2" s="132"/>
+      <c r="Z2" s="133"/>
+      <c r="AA2" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="AB2" s="73"/>
-      <c r="AC2" s="98" t="str">
+      <c r="AB2" s="112"/>
+      <c r="AC2" s="137" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="99"/>
-      <c r="AE2" s="99"/>
-      <c r="AF2" s="100"/>
-      <c r="AG2" s="128">
+      <c r="AD2" s="138"/>
+      <c r="AE2" s="138"/>
+      <c r="AF2" s="139"/>
+      <c r="AG2" s="142">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>44455</v>
-      </c>
-      <c r="AH2" s="129"/>
-      <c r="AI2" s="130"/>
+        <v>45461</v>
+      </c>
+      <c r="AH2" s="143"/>
+      <c r="AI2" s="144"/>
       <c r="AJ2" s="30"/>
       <c r="AN2" s="51"/>
       <c r="AO2" s="30"/>
@@ -10917,53 +10900,53 @@
       <c r="AV2" s="30"/>
       <c r="AW2" s="30"/>
     </row>
-    <row r="3" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="71" t="s">
+    <row r="3" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="110" t="s">
         <v>283</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="74" t="str">
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="113" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="75"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="140"/>
-      <c r="P3" s="141"/>
-      <c r="Q3" s="141"/>
-      <c r="R3" s="142"/>
-      <c r="S3" s="95"/>
-      <c r="T3" s="96"/>
-      <c r="U3" s="96"/>
-      <c r="V3" s="96"/>
-      <c r="W3" s="96"/>
-      <c r="X3" s="96"/>
-      <c r="Y3" s="96"/>
-      <c r="Z3" s="97"/>
-      <c r="AA3" s="71"/>
-      <c r="AB3" s="73"/>
-      <c r="AC3" s="98" t="str">
+      <c r="F3" s="114"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="114"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="155"/>
+      <c r="P3" s="156"/>
+      <c r="Q3" s="156"/>
+      <c r="R3" s="157"/>
+      <c r="S3" s="134"/>
+      <c r="T3" s="135"/>
+      <c r="U3" s="135"/>
+      <c r="V3" s="135"/>
+      <c r="W3" s="135"/>
+      <c r="X3" s="135"/>
+      <c r="Y3" s="135"/>
+      <c r="Z3" s="136"/>
+      <c r="AA3" s="110"/>
+      <c r="AB3" s="112"/>
+      <c r="AC3" s="137" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="99"/>
-      <c r="AE3" s="99"/>
-      <c r="AF3" s="100"/>
-      <c r="AG3" s="128" t="str">
+      <c r="AD3" s="138"/>
+      <c r="AE3" s="138"/>
+      <c r="AF3" s="139"/>
+      <c r="AG3" s="142" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="129"/>
-      <c r="AI3" s="130"/>
+      <c r="AH3" s="143"/>
+      <c r="AI3" s="144"/>
       <c r="AJ3" s="53"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
@@ -10979,1615 +10962,1272 @@
       <c r="AV3" s="52"/>
       <c r="AW3" s="52"/>
     </row>
-    <row r="4" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="5" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="34" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="6" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="34" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="7" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="34"/>
     </row>
-    <row r="8" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="34"/>
       <c r="D8" s="54" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="9" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C9" s="34"/>
       <c r="D9" s="54" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C10" s="34"/>
       <c r="D10" s="54" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="11" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C11" s="34"/>
       <c r="D11" s="54" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="12" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="34"/>
       <c r="D12" s="54" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="34"/>
       <c r="D13" s="54"/>
     </row>
-    <row r="14" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C14" s="34"/>
     </row>
-    <row r="15" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C15" s="34" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="16" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C16" s="34"/>
     </row>
-    <row r="17" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="34"/>
       <c r="D17" s="30" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="34"/>
     </row>
-    <row r="19" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="34"/>
     </row>
-    <row r="20" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C20" s="34"/>
     </row>
-    <row r="21" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="34"/>
     </row>
-    <row r="22" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C22" s="34"/>
     </row>
-    <row r="23" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C23" s="34"/>
     </row>
-    <row r="24" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="34"/>
     </row>
-    <row r="25" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="34"/>
     </row>
-    <row r="26" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C26" s="34"/>
     </row>
-    <row r="27" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C27" s="34"/>
     </row>
-    <row r="28" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C28" s="34"/>
     </row>
-    <row r="29" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C29" s="34"/>
     </row>
-    <row r="30" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C30" s="34"/>
     </row>
-    <row r="31" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C31" s="34"/>
     </row>
-    <row r="32" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C32" s="34"/>
     </row>
-    <row r="33" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C33" s="34"/>
     </row>
-    <row r="34" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C34" s="34"/>
     </row>
-    <row r="35" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C35" s="34"/>
     </row>
-    <row r="36" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C36" s="34"/>
     </row>
-    <row r="37" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C37" s="34"/>
     </row>
-    <row r="38" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C38" s="34"/>
     </row>
-    <row r="39" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C39" s="34"/>
     </row>
-    <row r="40" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C40" s="34"/>
       <c r="D40" s="54" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="41" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C41" s="34"/>
       <c r="D41" s="54" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="42" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C42" s="34"/>
       <c r="D42" s="54"/>
     </row>
-    <row r="43" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="34"/>
       <c r="D43" s="54" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="44" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="34"/>
       <c r="D44" s="54" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="45" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="34"/>
       <c r="D45" s="54"/>
     </row>
-    <row r="46" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="34"/>
       <c r="D46" s="54" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="34"/>
       <c r="D47" s="54" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C48" s="34"/>
       <c r="D48" s="54"/>
     </row>
-    <row r="49" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C49" s="34" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="50" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C50" s="34"/>
     </row>
-    <row r="51" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C51" s="34"/>
       <c r="D51" s="54" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="52" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C52" s="34"/>
       <c r="D52" s="54" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="53" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C53" s="34"/>
       <c r="D53" s="54" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="54" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C54" s="34"/>
       <c r="D54" s="54" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="55" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C55" s="34"/>
       <c r="D55" s="54"/>
     </row>
-    <row r="56" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C56" s="34"/>
       <c r="D56" s="54" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:28" x14ac:dyDescent="0.15">
       <c r="C57" s="34"/>
       <c r="D57" s="55" t="s">
         <v>305</v>
       </c>
-      <c r="E57" s="143" t="s">
+      <c r="E57" s="146" t="s">
         <v>107</v>
       </c>
-      <c r="F57" s="144"/>
-      <c r="G57" s="144"/>
-      <c r="H57" s="144"/>
-      <c r="I57" s="144"/>
-      <c r="J57" s="145"/>
-      <c r="K57" s="143" t="s">
+      <c r="F57" s="147"/>
+      <c r="G57" s="147"/>
+      <c r="H57" s="147"/>
+      <c r="I57" s="147"/>
+      <c r="J57" s="148"/>
+      <c r="K57" s="146" t="s">
         <v>178</v>
       </c>
-      <c r="L57" s="144"/>
-      <c r="M57" s="144"/>
-      <c r="N57" s="144"/>
-      <c r="O57" s="144"/>
-      <c r="P57" s="144"/>
-      <c r="Q57" s="144"/>
-      <c r="R57" s="144"/>
-      <c r="S57" s="144"/>
-      <c r="T57" s="144"/>
-      <c r="U57" s="144"/>
-      <c r="V57" s="144"/>
-      <c r="W57" s="144"/>
-      <c r="X57" s="144"/>
-      <c r="Y57" s="144"/>
-      <c r="Z57" s="144"/>
-      <c r="AA57" s="144"/>
-      <c r="AB57" s="145"/>
-    </row>
-    <row r="58" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L57" s="147"/>
+      <c r="M57" s="147"/>
+      <c r="N57" s="147"/>
+      <c r="O57" s="147"/>
+      <c r="P57" s="147"/>
+      <c r="Q57" s="147"/>
+      <c r="R57" s="147"/>
+      <c r="S57" s="147"/>
+      <c r="T57" s="147"/>
+      <c r="U57" s="147"/>
+      <c r="V57" s="147"/>
+      <c r="W57" s="147"/>
+      <c r="X57" s="147"/>
+      <c r="Y57" s="147"/>
+      <c r="Z57" s="147"/>
+      <c r="AA57" s="147"/>
+      <c r="AB57" s="148"/>
+    </row>
+    <row r="58" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="34"/>
       <c r="D58" s="56">
         <v>1</v>
       </c>
-      <c r="E58" s="133" t="s">
+      <c r="E58" s="145" t="s">
         <v>34</v>
       </c>
-      <c r="F58" s="133"/>
-      <c r="G58" s="133"/>
-      <c r="H58" s="133"/>
-      <c r="I58" s="133"/>
-      <c r="J58" s="133"/>
-      <c r="K58" s="133" t="s">
+      <c r="F58" s="145"/>
+      <c r="G58" s="145"/>
+      <c r="H58" s="145"/>
+      <c r="I58" s="145"/>
+      <c r="J58" s="145"/>
+      <c r="K58" s="145" t="s">
         <v>18</v>
       </c>
-      <c r="L58" s="133"/>
-      <c r="M58" s="133"/>
-      <c r="N58" s="133"/>
-      <c r="O58" s="133"/>
-      <c r="P58" s="133"/>
-      <c r="Q58" s="133"/>
-      <c r="R58" s="133"/>
-      <c r="S58" s="133"/>
-      <c r="T58" s="133"/>
-      <c r="U58" s="133"/>
-      <c r="V58" s="133"/>
-      <c r="W58" s="133"/>
-      <c r="X58" s="133"/>
-      <c r="Y58" s="133"/>
-      <c r="Z58" s="133"/>
-      <c r="AA58" s="133"/>
-      <c r="AB58" s="133"/>
-    </row>
-    <row r="59" spans="3:28" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L58" s="145"/>
+      <c r="M58" s="145"/>
+      <c r="N58" s="145"/>
+      <c r="O58" s="145"/>
+      <c r="P58" s="145"/>
+      <c r="Q58" s="145"/>
+      <c r="R58" s="145"/>
+      <c r="S58" s="145"/>
+      <c r="T58" s="145"/>
+      <c r="U58" s="145"/>
+      <c r="V58" s="145"/>
+      <c r="W58" s="145"/>
+      <c r="X58" s="145"/>
+      <c r="Y58" s="145"/>
+      <c r="Z58" s="145"/>
+      <c r="AA58" s="145"/>
+      <c r="AB58" s="145"/>
+    </row>
+    <row r="59" spans="3:28" ht="48" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C59" s="34"/>
       <c r="D59" s="56">
         <v>2</v>
       </c>
-      <c r="E59" s="133" t="s">
+      <c r="E59" s="145" t="s">
         <v>43</v>
       </c>
-      <c r="F59" s="133"/>
-      <c r="G59" s="133"/>
-      <c r="H59" s="133"/>
-      <c r="I59" s="133"/>
-      <c r="J59" s="133"/>
-      <c r="K59" s="133" t="s">
+      <c r="F59" s="145"/>
+      <c r="G59" s="145"/>
+      <c r="H59" s="145"/>
+      <c r="I59" s="145"/>
+      <c r="J59" s="145"/>
+      <c r="K59" s="145" t="s">
         <v>19</v>
       </c>
-      <c r="L59" s="133"/>
-      <c r="M59" s="133"/>
-      <c r="N59" s="133"/>
-      <c r="O59" s="133"/>
-      <c r="P59" s="133"/>
-      <c r="Q59" s="133"/>
-      <c r="R59" s="133"/>
-      <c r="S59" s="133"/>
-      <c r="T59" s="133"/>
-      <c r="U59" s="133"/>
-      <c r="V59" s="133"/>
-      <c r="W59" s="133"/>
-      <c r="X59" s="133"/>
-      <c r="Y59" s="133"/>
-      <c r="Z59" s="133"/>
-      <c r="AA59" s="133"/>
-      <c r="AB59" s="133"/>
-    </row>
-    <row r="60" spans="3:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L59" s="145"/>
+      <c r="M59" s="145"/>
+      <c r="N59" s="145"/>
+      <c r="O59" s="145"/>
+      <c r="P59" s="145"/>
+      <c r="Q59" s="145"/>
+      <c r="R59" s="145"/>
+      <c r="S59" s="145"/>
+      <c r="T59" s="145"/>
+      <c r="U59" s="145"/>
+      <c r="V59" s="145"/>
+      <c r="W59" s="145"/>
+      <c r="X59" s="145"/>
+      <c r="Y59" s="145"/>
+      <c r="Z59" s="145"/>
+      <c r="AA59" s="145"/>
+      <c r="AB59" s="145"/>
+    </row>
+    <row r="60" spans="3:28" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C60" s="34"/>
       <c r="D60" s="56">
         <v>3</v>
       </c>
-      <c r="E60" s="133" t="s">
+      <c r="E60" s="145" t="s">
         <v>200</v>
       </c>
-      <c r="F60" s="133"/>
-      <c r="G60" s="133"/>
-      <c r="H60" s="133"/>
-      <c r="I60" s="133"/>
-      <c r="J60" s="133"/>
-      <c r="K60" s="133" t="s">
+      <c r="F60" s="145"/>
+      <c r="G60" s="145"/>
+      <c r="H60" s="145"/>
+      <c r="I60" s="145"/>
+      <c r="J60" s="145"/>
+      <c r="K60" s="145" t="s">
         <v>106</v>
       </c>
-      <c r="L60" s="133"/>
-      <c r="M60" s="133"/>
-      <c r="N60" s="133"/>
-      <c r="O60" s="133"/>
-      <c r="P60" s="133"/>
-      <c r="Q60" s="133"/>
-      <c r="R60" s="133"/>
-      <c r="S60" s="133"/>
-      <c r="T60" s="133"/>
-      <c r="U60" s="133"/>
-      <c r="V60" s="133"/>
-      <c r="W60" s="133"/>
-      <c r="X60" s="133"/>
-      <c r="Y60" s="133"/>
-      <c r="Z60" s="133"/>
-      <c r="AA60" s="133"/>
-      <c r="AB60" s="133"/>
-    </row>
-    <row r="61" spans="3:28" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L60" s="145"/>
+      <c r="M60" s="145"/>
+      <c r="N60" s="145"/>
+      <c r="O60" s="145"/>
+      <c r="P60" s="145"/>
+      <c r="Q60" s="145"/>
+      <c r="R60" s="145"/>
+      <c r="S60" s="145"/>
+      <c r="T60" s="145"/>
+      <c r="U60" s="145"/>
+      <c r="V60" s="145"/>
+      <c r="W60" s="145"/>
+      <c r="X60" s="145"/>
+      <c r="Y60" s="145"/>
+      <c r="Z60" s="145"/>
+      <c r="AA60" s="145"/>
+      <c r="AB60" s="145"/>
+    </row>
+    <row r="61" spans="3:28" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C61" s="34"/>
       <c r="D61" s="56">
         <v>4</v>
       </c>
-      <c r="E61" s="133" t="s">
+      <c r="E61" s="145" t="s">
         <v>201</v>
       </c>
-      <c r="F61" s="133"/>
-      <c r="G61" s="133"/>
-      <c r="H61" s="133"/>
-      <c r="I61" s="133"/>
-      <c r="J61" s="133"/>
-      <c r="K61" s="133" t="s">
+      <c r="F61" s="145"/>
+      <c r="G61" s="145"/>
+      <c r="H61" s="145"/>
+      <c r="I61" s="145"/>
+      <c r="J61" s="145"/>
+      <c r="K61" s="145" t="s">
         <v>20</v>
       </c>
-      <c r="L61" s="133"/>
-      <c r="M61" s="133"/>
-      <c r="N61" s="133"/>
-      <c r="O61" s="133"/>
-      <c r="P61" s="133"/>
-      <c r="Q61" s="133"/>
-      <c r="R61" s="133"/>
-      <c r="S61" s="133"/>
-      <c r="T61" s="133"/>
-      <c r="U61" s="133"/>
-      <c r="V61" s="133"/>
-      <c r="W61" s="133"/>
-      <c r="X61" s="133"/>
-      <c r="Y61" s="133"/>
-      <c r="Z61" s="133"/>
-      <c r="AA61" s="133"/>
-      <c r="AB61" s="133"/>
-    </row>
-    <row r="62" spans="3:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L61" s="145"/>
+      <c r="M61" s="145"/>
+      <c r="N61" s="145"/>
+      <c r="O61" s="145"/>
+      <c r="P61" s="145"/>
+      <c r="Q61" s="145"/>
+      <c r="R61" s="145"/>
+      <c r="S61" s="145"/>
+      <c r="T61" s="145"/>
+      <c r="U61" s="145"/>
+      <c r="V61" s="145"/>
+      <c r="W61" s="145"/>
+      <c r="X61" s="145"/>
+      <c r="Y61" s="145"/>
+      <c r="Z61" s="145"/>
+      <c r="AA61" s="145"/>
+      <c r="AB61" s="145"/>
+    </row>
+    <row r="62" spans="3:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C62" s="34"/>
       <c r="D62" s="56">
         <v>5</v>
       </c>
-      <c r="E62" s="133" t="s">
+      <c r="E62" s="145" t="s">
         <v>202</v>
       </c>
-      <c r="F62" s="133"/>
-      <c r="G62" s="133"/>
-      <c r="H62" s="133"/>
-      <c r="I62" s="133"/>
-      <c r="J62" s="133"/>
-      <c r="K62" s="133" t="s">
+      <c r="F62" s="145"/>
+      <c r="G62" s="145"/>
+      <c r="H62" s="145"/>
+      <c r="I62" s="145"/>
+      <c r="J62" s="145"/>
+      <c r="K62" s="145" t="s">
         <v>21</v>
       </c>
-      <c r="L62" s="133"/>
-      <c r="M62" s="133"/>
-      <c r="N62" s="133"/>
-      <c r="O62" s="133"/>
-      <c r="P62" s="133"/>
-      <c r="Q62" s="133"/>
-      <c r="R62" s="133"/>
-      <c r="S62" s="133"/>
-      <c r="T62" s="133"/>
-      <c r="U62" s="133"/>
-      <c r="V62" s="133"/>
-      <c r="W62" s="133"/>
-      <c r="X62" s="133"/>
-      <c r="Y62" s="133"/>
-      <c r="Z62" s="133"/>
-      <c r="AA62" s="133"/>
-      <c r="AB62" s="133"/>
-    </row>
-    <row r="63" spans="3:28" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L62" s="145"/>
+      <c r="M62" s="145"/>
+      <c r="N62" s="145"/>
+      <c r="O62" s="145"/>
+      <c r="P62" s="145"/>
+      <c r="Q62" s="145"/>
+      <c r="R62" s="145"/>
+      <c r="S62" s="145"/>
+      <c r="T62" s="145"/>
+      <c r="U62" s="145"/>
+      <c r="V62" s="145"/>
+      <c r="W62" s="145"/>
+      <c r="X62" s="145"/>
+      <c r="Y62" s="145"/>
+      <c r="Z62" s="145"/>
+      <c r="AA62" s="145"/>
+      <c r="AB62" s="145"/>
+    </row>
+    <row r="63" spans="3:28" ht="72" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C63" s="34"/>
       <c r="D63" s="56">
         <v>6</v>
       </c>
-      <c r="E63" s="133" t="s">
+      <c r="E63" s="145" t="s">
         <v>225</v>
       </c>
-      <c r="F63" s="133"/>
-      <c r="G63" s="133"/>
-      <c r="H63" s="133"/>
-      <c r="I63" s="133"/>
-      <c r="J63" s="133"/>
-      <c r="K63" s="133" t="s">
+      <c r="F63" s="145"/>
+      <c r="G63" s="145"/>
+      <c r="H63" s="145"/>
+      <c r="I63" s="145"/>
+      <c r="J63" s="145"/>
+      <c r="K63" s="145" t="s">
         <v>306</v>
       </c>
-      <c r="L63" s="133"/>
-      <c r="M63" s="133"/>
-      <c r="N63" s="133"/>
-      <c r="O63" s="133"/>
-      <c r="P63" s="133"/>
-      <c r="Q63" s="133"/>
-      <c r="R63" s="133"/>
-      <c r="S63" s="133"/>
-      <c r="T63" s="133"/>
-      <c r="U63" s="133"/>
-      <c r="V63" s="133"/>
-      <c r="W63" s="133"/>
-      <c r="X63" s="133"/>
-      <c r="Y63" s="133"/>
-      <c r="Z63" s="133"/>
-      <c r="AA63" s="133"/>
-      <c r="AB63" s="133"/>
-    </row>
-    <row r="64" spans="3:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L63" s="145"/>
+      <c r="M63" s="145"/>
+      <c r="N63" s="145"/>
+      <c r="O63" s="145"/>
+      <c r="P63" s="145"/>
+      <c r="Q63" s="145"/>
+      <c r="R63" s="145"/>
+      <c r="S63" s="145"/>
+      <c r="T63" s="145"/>
+      <c r="U63" s="145"/>
+      <c r="V63" s="145"/>
+      <c r="W63" s="145"/>
+      <c r="X63" s="145"/>
+      <c r="Y63" s="145"/>
+      <c r="Z63" s="145"/>
+      <c r="AA63" s="145"/>
+      <c r="AB63" s="145"/>
+    </row>
+    <row r="64" spans="3:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C64" s="34"/>
       <c r="D64" s="56">
         <v>7</v>
       </c>
-      <c r="E64" s="133" t="s">
+      <c r="E64" s="145" t="s">
         <v>155</v>
       </c>
-      <c r="F64" s="133"/>
-      <c r="G64" s="133"/>
-      <c r="H64" s="133"/>
-      <c r="I64" s="133"/>
-      <c r="J64" s="133"/>
-      <c r="K64" s="133" t="s">
+      <c r="F64" s="145"/>
+      <c r="G64" s="145"/>
+      <c r="H64" s="145"/>
+      <c r="I64" s="145"/>
+      <c r="J64" s="145"/>
+      <c r="K64" s="145" t="s">
         <v>221</v>
       </c>
-      <c r="L64" s="133"/>
-      <c r="M64" s="133"/>
-      <c r="N64" s="133"/>
-      <c r="O64" s="133"/>
-      <c r="P64" s="133"/>
-      <c r="Q64" s="133"/>
-      <c r="R64" s="133"/>
-      <c r="S64" s="133"/>
-      <c r="T64" s="133"/>
-      <c r="U64" s="133"/>
-      <c r="V64" s="133"/>
-      <c r="W64" s="133"/>
-      <c r="X64" s="133"/>
-      <c r="Y64" s="133"/>
-      <c r="Z64" s="133"/>
-      <c r="AA64" s="133"/>
-      <c r="AB64" s="133"/>
-    </row>
-    <row r="65" spans="3:28" ht="108" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L64" s="145"/>
+      <c r="M64" s="145"/>
+      <c r="N64" s="145"/>
+      <c r="O64" s="145"/>
+      <c r="P64" s="145"/>
+      <c r="Q64" s="145"/>
+      <c r="R64" s="145"/>
+      <c r="S64" s="145"/>
+      <c r="T64" s="145"/>
+      <c r="U64" s="145"/>
+      <c r="V64" s="145"/>
+      <c r="W64" s="145"/>
+      <c r="X64" s="145"/>
+      <c r="Y64" s="145"/>
+      <c r="Z64" s="145"/>
+      <c r="AA64" s="145"/>
+      <c r="AB64" s="145"/>
+    </row>
+    <row r="65" spans="3:28" ht="108" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C65" s="34"/>
       <c r="D65" s="56">
         <v>8</v>
       </c>
-      <c r="E65" s="133" t="s">
+      <c r="E65" s="145" t="s">
         <v>102</v>
       </c>
-      <c r="F65" s="133"/>
-      <c r="G65" s="133"/>
-      <c r="H65" s="133"/>
-      <c r="I65" s="133"/>
-      <c r="J65" s="133"/>
-      <c r="K65" s="133" t="s">
+      <c r="F65" s="145"/>
+      <c r="G65" s="145"/>
+      <c r="H65" s="145"/>
+      <c r="I65" s="145"/>
+      <c r="J65" s="145"/>
+      <c r="K65" s="145" t="s">
         <v>217</v>
       </c>
-      <c r="L65" s="133"/>
-      <c r="M65" s="133"/>
-      <c r="N65" s="133"/>
-      <c r="O65" s="133"/>
-      <c r="P65" s="133"/>
-      <c r="Q65" s="133"/>
-      <c r="R65" s="133"/>
-      <c r="S65" s="133"/>
-      <c r="T65" s="133"/>
-      <c r="U65" s="133"/>
-      <c r="V65" s="133"/>
-      <c r="W65" s="133"/>
-      <c r="X65" s="133"/>
-      <c r="Y65" s="133"/>
-      <c r="Z65" s="133"/>
-      <c r="AA65" s="133"/>
-      <c r="AB65" s="133"/>
-    </row>
-    <row r="66" spans="3:28" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L65" s="145"/>
+      <c r="M65" s="145"/>
+      <c r="N65" s="145"/>
+      <c r="O65" s="145"/>
+      <c r="P65" s="145"/>
+      <c r="Q65" s="145"/>
+      <c r="R65" s="145"/>
+      <c r="S65" s="145"/>
+      <c r="T65" s="145"/>
+      <c r="U65" s="145"/>
+      <c r="V65" s="145"/>
+      <c r="W65" s="145"/>
+      <c r="X65" s="145"/>
+      <c r="Y65" s="145"/>
+      <c r="Z65" s="145"/>
+      <c r="AA65" s="145"/>
+      <c r="AB65" s="145"/>
+    </row>
+    <row r="66" spans="3:28" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C66" s="34"/>
       <c r="D66" s="56">
         <v>9</v>
       </c>
-      <c r="E66" s="133" t="s">
+      <c r="E66" s="145" t="s">
         <v>104</v>
       </c>
-      <c r="F66" s="133"/>
-      <c r="G66" s="133"/>
-      <c r="H66" s="133"/>
-      <c r="I66" s="133"/>
-      <c r="J66" s="133"/>
-      <c r="K66" s="133" t="s">
+      <c r="F66" s="145"/>
+      <c r="G66" s="145"/>
+      <c r="H66" s="145"/>
+      <c r="I66" s="145"/>
+      <c r="J66" s="145"/>
+      <c r="K66" s="145" t="s">
         <v>22</v>
       </c>
-      <c r="L66" s="133"/>
-      <c r="M66" s="133"/>
-      <c r="N66" s="133"/>
-      <c r="O66" s="133"/>
-      <c r="P66" s="133"/>
-      <c r="Q66" s="133"/>
-      <c r="R66" s="133"/>
-      <c r="S66" s="133"/>
-      <c r="T66" s="133"/>
-      <c r="U66" s="133"/>
-      <c r="V66" s="133"/>
-      <c r="W66" s="133"/>
-      <c r="X66" s="133"/>
-      <c r="Y66" s="133"/>
-      <c r="Z66" s="133"/>
-      <c r="AA66" s="133"/>
-      <c r="AB66" s="133"/>
-    </row>
-    <row r="67" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L66" s="145"/>
+      <c r="M66" s="145"/>
+      <c r="N66" s="145"/>
+      <c r="O66" s="145"/>
+      <c r="P66" s="145"/>
+      <c r="Q66" s="145"/>
+      <c r="R66" s="145"/>
+      <c r="S66" s="145"/>
+      <c r="T66" s="145"/>
+      <c r="U66" s="145"/>
+      <c r="V66" s="145"/>
+      <c r="W66" s="145"/>
+      <c r="X66" s="145"/>
+      <c r="Y66" s="145"/>
+      <c r="Z66" s="145"/>
+      <c r="AA66" s="145"/>
+      <c r="AB66" s="145"/>
+    </row>
+    <row r="67" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C67" s="34"/>
     </row>
-    <row r="68" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C68" s="34"/>
     </row>
-    <row r="69" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="69" spans="3:28" x14ac:dyDescent="0.15">
       <c r="C69" s="30" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D71" s="30" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="73" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D73" s="55" t="s">
+        <v>305</v>
+      </c>
+      <c r="E73" s="67" t="s">
+        <v>399</v>
+      </c>
+      <c r="F73" s="68"/>
+      <c r="G73" s="68"/>
+      <c r="H73" s="68"/>
+      <c r="I73" s="67" t="s">
+        <v>376</v>
+      </c>
+      <c r="J73" s="69"/>
+      <c r="K73" s="68"/>
+      <c r="L73" s="68"/>
+      <c r="M73" s="68"/>
+      <c r="N73" s="68"/>
+      <c r="O73" s="68"/>
+      <c r="P73" s="68"/>
+      <c r="Q73" s="68"/>
+      <c r="R73" s="68"/>
+      <c r="S73" s="68"/>
+      <c r="T73" s="69"/>
+      <c r="U73" s="73"/>
+      <c r="V73" s="74"/>
+      <c r="W73" s="74"/>
+      <c r="X73" s="74"/>
+      <c r="Y73" s="74"/>
+      <c r="Z73" s="74"/>
+      <c r="AA73" s="74"/>
+      <c r="AB73" s="74"/>
+    </row>
+    <row r="74" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D74" s="64">
+        <v>1</v>
+      </c>
+      <c r="E74" s="64" t="s">
+        <v>358</v>
+      </c>
+      <c r="F74" s="65"/>
+      <c r="G74" s="65"/>
+      <c r="H74" s="65"/>
+      <c r="I74" s="70" t="s">
+        <v>377</v>
+      </c>
+      <c r="J74" s="66"/>
+      <c r="K74" s="65"/>
+      <c r="L74" s="65"/>
+      <c r="M74" s="65"/>
+      <c r="N74" s="65"/>
+      <c r="O74" s="65"/>
+      <c r="P74" s="65"/>
+      <c r="Q74" s="65"/>
+      <c r="R74" s="65"/>
+      <c r="S74" s="65"/>
+      <c r="T74" s="66"/>
+      <c r="U74" s="71"/>
+      <c r="V74" s="72"/>
+      <c r="W74" s="72"/>
+      <c r="X74" s="72"/>
+      <c r="Y74" s="72"/>
+      <c r="Z74" s="72"/>
+      <c r="AA74" s="72"/>
+      <c r="AB74" s="72"/>
+    </row>
+    <row r="75" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D75" s="64">
+        <v>2</v>
+      </c>
+      <c r="E75" s="64" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="71" spans="3:28" x14ac:dyDescent="0.2">
-      <c r="D71" s="30" t="s">
+      <c r="F75" s="65"/>
+      <c r="G75" s="65"/>
+      <c r="H75" s="65"/>
+      <c r="I75" s="70" t="s">
+        <v>378</v>
+      </c>
+      <c r="J75" s="66"/>
+      <c r="K75" s="65"/>
+      <c r="L75" s="65"/>
+      <c r="M75" s="65"/>
+      <c r="N75" s="65"/>
+      <c r="O75" s="65"/>
+      <c r="P75" s="65"/>
+      <c r="Q75" s="65"/>
+      <c r="R75" s="65"/>
+      <c r="S75" s="65"/>
+      <c r="T75" s="66"/>
+      <c r="U75" s="71"/>
+      <c r="V75" s="72"/>
+      <c r="W75" s="72"/>
+      <c r="X75" s="72"/>
+      <c r="Y75" s="72"/>
+      <c r="Z75" s="72"/>
+      <c r="AA75" s="72"/>
+      <c r="AB75" s="72"/>
+    </row>
+    <row r="76" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D76" s="64">
+        <v>3</v>
+      </c>
+      <c r="E76" s="64" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="72" spans="3:28" x14ac:dyDescent="0.2">
-      <c r="D72" s="30" t="s">
+      <c r="F76" s="65"/>
+      <c r="G76" s="65"/>
+      <c r="H76" s="65"/>
+      <c r="I76" s="70" t="s">
+        <v>379</v>
+      </c>
+      <c r="J76" s="66"/>
+      <c r="K76" s="65"/>
+      <c r="L76" s="65"/>
+      <c r="M76" s="65"/>
+      <c r="N76" s="65"/>
+      <c r="O76" s="65"/>
+      <c r="P76" s="65"/>
+      <c r="Q76" s="65"/>
+      <c r="R76" s="65"/>
+      <c r="S76" s="65"/>
+      <c r="T76" s="66"/>
+      <c r="U76" s="71"/>
+      <c r="V76" s="72"/>
+      <c r="W76" s="72"/>
+      <c r="X76" s="72"/>
+      <c r="Y76" s="72"/>
+      <c r="Z76" s="72"/>
+      <c r="AA76" s="72"/>
+      <c r="AB76" s="72"/>
+    </row>
+    <row r="77" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D77" s="64">
+        <v>4</v>
+      </c>
+      <c r="E77" s="64" t="s">
+        <v>361</v>
+      </c>
+      <c r="F77" s="65"/>
+      <c r="G77" s="65"/>
+      <c r="H77" s="65"/>
+      <c r="I77" s="70" t="s">
+        <v>380</v>
+      </c>
+      <c r="J77" s="66"/>
+      <c r="K77" s="65"/>
+      <c r="L77" s="65"/>
+      <c r="M77" s="65"/>
+      <c r="N77" s="65"/>
+      <c r="O77" s="65"/>
+      <c r="P77" s="65"/>
+      <c r="Q77" s="65"/>
+      <c r="R77" s="65"/>
+      <c r="S77" s="65"/>
+      <c r="T77" s="66"/>
+      <c r="U77" s="71"/>
+      <c r="V77" s="72"/>
+      <c r="W77" s="72"/>
+      <c r="X77" s="72"/>
+      <c r="Y77" s="72"/>
+      <c r="Z77" s="72"/>
+      <c r="AA77" s="72"/>
+      <c r="AB77" s="72"/>
+    </row>
+    <row r="78" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D78" s="64">
+        <v>5</v>
+      </c>
+      <c r="E78" s="64" t="s">
+        <v>362</v>
+      </c>
+      <c r="F78" s="65"/>
+      <c r="G78" s="65"/>
+      <c r="H78" s="65"/>
+      <c r="I78" s="70" t="s">
+        <v>381</v>
+      </c>
+      <c r="J78" s="66"/>
+      <c r="K78" s="65"/>
+      <c r="L78" s="65"/>
+      <c r="M78" s="65"/>
+      <c r="N78" s="65"/>
+      <c r="O78" s="65"/>
+      <c r="P78" s="65"/>
+      <c r="Q78" s="65"/>
+      <c r="R78" s="65"/>
+      <c r="S78" s="65"/>
+      <c r="T78" s="66"/>
+      <c r="U78" s="71"/>
+      <c r="V78" s="72"/>
+      <c r="W78" s="72"/>
+      <c r="X78" s="72"/>
+      <c r="Y78" s="72"/>
+      <c r="Z78" s="72"/>
+      <c r="AA78" s="72"/>
+      <c r="AB78" s="72"/>
+    </row>
+    <row r="79" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D79" s="64">
+        <v>6</v>
+      </c>
+      <c r="E79" s="64" t="s">
+        <v>363</v>
+      </c>
+      <c r="F79" s="65"/>
+      <c r="G79" s="65"/>
+      <c r="H79" s="65"/>
+      <c r="I79" s="70" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="74" spans="3:28" x14ac:dyDescent="0.2">
-      <c r="D74" s="55" t="s">
-        <v>305</v>
-      </c>
-      <c r="E74" s="153" t="s">
-        <v>361</v>
-      </c>
-      <c r="F74" s="154"/>
-      <c r="G74" s="154"/>
-      <c r="H74" s="154"/>
-      <c r="I74" s="153" t="s">
-        <v>381</v>
-      </c>
-      <c r="J74" s="155"/>
-      <c r="K74" s="154"/>
-      <c r="L74" s="154"/>
-      <c r="M74" s="154"/>
-      <c r="N74" s="154"/>
-      <c r="O74" s="154"/>
-      <c r="P74" s="154"/>
-      <c r="Q74" s="154"/>
-      <c r="R74" s="154"/>
-      <c r="S74" s="154"/>
-      <c r="T74" s="155"/>
-      <c r="U74" s="160"/>
-      <c r="V74" s="161"/>
-      <c r="W74" s="161"/>
-      <c r="X74" s="161"/>
-      <c r="Y74" s="161"/>
-      <c r="Z74" s="161"/>
-      <c r="AA74" s="161"/>
-      <c r="AB74" s="161"/>
-    </row>
-    <row r="75" spans="3:28" x14ac:dyDescent="0.2">
-      <c r="D75" s="150">
-        <v>1</v>
-      </c>
-      <c r="E75" s="150" t="s">
-        <v>362</v>
-      </c>
-      <c r="F75" s="151"/>
-      <c r="G75" s="151"/>
-      <c r="H75" s="151"/>
-      <c r="I75" s="157" t="s">
-        <v>397</v>
-      </c>
-      <c r="J75" s="152"/>
-      <c r="K75" s="151"/>
-      <c r="L75" s="151"/>
-      <c r="M75" s="151"/>
-      <c r="N75" s="151"/>
-      <c r="O75" s="151"/>
-      <c r="P75" s="151"/>
-      <c r="Q75" s="151"/>
-      <c r="R75" s="151"/>
-      <c r="S75" s="151"/>
-      <c r="T75" s="152"/>
-      <c r="U75" s="158"/>
-      <c r="V75" s="159"/>
-      <c r="W75" s="159"/>
-      <c r="X75" s="159"/>
-      <c r="Y75" s="159"/>
-      <c r="Z75" s="159"/>
-      <c r="AA75" s="159"/>
-      <c r="AB75" s="159"/>
-    </row>
-    <row r="76" spans="3:28" x14ac:dyDescent="0.2">
-      <c r="D76" s="150">
-        <v>2</v>
-      </c>
-      <c r="E76" s="150" t="s">
-        <v>363</v>
-      </c>
-      <c r="F76" s="151"/>
-      <c r="G76" s="151"/>
-      <c r="H76" s="151"/>
-      <c r="I76" s="157" t="s">
+      <c r="J79" s="66"/>
+      <c r="K79" s="65"/>
+      <c r="L79" s="65"/>
+      <c r="M79" s="65"/>
+      <c r="N79" s="65"/>
+      <c r="O79" s="65"/>
+      <c r="P79" s="65"/>
+      <c r="Q79" s="65"/>
+      <c r="R79" s="65"/>
+      <c r="S79" s="65"/>
+      <c r="T79" s="66"/>
+      <c r="U79" s="71"/>
+      <c r="V79" s="72"/>
+      <c r="W79" s="72"/>
+      <c r="X79" s="72"/>
+      <c r="Y79" s="72"/>
+      <c r="Z79" s="72"/>
+      <c r="AA79" s="72"/>
+      <c r="AB79" s="72"/>
+    </row>
+    <row r="80" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D80" s="64">
+        <v>7</v>
+      </c>
+      <c r="E80" s="64" t="s">
         <v>398</v>
       </c>
-      <c r="J76" s="152"/>
-      <c r="K76" s="151"/>
-      <c r="L76" s="151"/>
-      <c r="M76" s="151"/>
-      <c r="N76" s="151"/>
-      <c r="O76" s="151"/>
-      <c r="P76" s="151"/>
-      <c r="Q76" s="151"/>
-      <c r="R76" s="151"/>
-      <c r="S76" s="151"/>
-      <c r="T76" s="152"/>
-      <c r="U76" s="158"/>
-      <c r="V76" s="159"/>
-      <c r="W76" s="159"/>
-      <c r="X76" s="159"/>
-      <c r="Y76" s="159"/>
-      <c r="Z76" s="159"/>
-      <c r="AA76" s="159"/>
-      <c r="AB76" s="159"/>
-    </row>
-    <row r="77" spans="3:28" x14ac:dyDescent="0.2">
-      <c r="D77" s="150">
-        <v>3</v>
-      </c>
-      <c r="E77" s="150" t="s">
+      <c r="F80" s="65"/>
+      <c r="G80" s="65"/>
+      <c r="H80" s="65"/>
+      <c r="I80" s="70" t="s">
+        <v>383</v>
+      </c>
+      <c r="J80" s="66"/>
+      <c r="K80" s="65"/>
+      <c r="L80" s="65"/>
+      <c r="M80" s="65"/>
+      <c r="N80" s="65"/>
+      <c r="O80" s="65"/>
+      <c r="P80" s="65"/>
+      <c r="Q80" s="65"/>
+      <c r="R80" s="65"/>
+      <c r="S80" s="65"/>
+      <c r="T80" s="66"/>
+      <c r="U80" s="71"/>
+      <c r="V80" s="72"/>
+      <c r="W80" s="72"/>
+      <c r="X80" s="72"/>
+      <c r="Y80" s="72"/>
+      <c r="Z80" s="72"/>
+      <c r="AA80" s="72"/>
+      <c r="AB80" s="72"/>
+    </row>
+    <row r="81" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D81" s="64">
+        <v>8</v>
+      </c>
+      <c r="E81" s="64" t="s">
         <v>364</v>
       </c>
-      <c r="F77" s="151"/>
-      <c r="G77" s="151"/>
-      <c r="H77" s="151"/>
-      <c r="I77" s="157" t="s">
-        <v>399</v>
-      </c>
-      <c r="J77" s="152"/>
-      <c r="K77" s="151"/>
-      <c r="L77" s="151"/>
-      <c r="M77" s="151"/>
-      <c r="N77" s="151"/>
-      <c r="O77" s="151"/>
-      <c r="P77" s="151"/>
-      <c r="Q77" s="151"/>
-      <c r="R77" s="151"/>
-      <c r="S77" s="151"/>
-      <c r="T77" s="152"/>
-      <c r="U77" s="158"/>
-      <c r="V77" s="159"/>
-      <c r="W77" s="159"/>
-      <c r="X77" s="159"/>
-      <c r="Y77" s="159"/>
-      <c r="Z77" s="159"/>
-      <c r="AA77" s="159"/>
-      <c r="AB77" s="159"/>
-    </row>
-    <row r="78" spans="3:28" x14ac:dyDescent="0.2">
-      <c r="D78" s="150">
-        <v>4</v>
-      </c>
-      <c r="E78" s="150" t="s">
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="70" t="s">
+        <v>384</v>
+      </c>
+      <c r="J81" s="66"/>
+      <c r="K81" s="65"/>
+      <c r="L81" s="65"/>
+      <c r="M81" s="65"/>
+      <c r="N81" s="65"/>
+      <c r="O81" s="65"/>
+      <c r="P81" s="65"/>
+      <c r="Q81" s="65"/>
+      <c r="R81" s="65"/>
+      <c r="S81" s="65"/>
+      <c r="T81" s="66"/>
+      <c r="U81" s="71"/>
+      <c r="V81" s="72"/>
+      <c r="W81" s="72"/>
+      <c r="X81" s="72"/>
+      <c r="Y81" s="72"/>
+      <c r="Z81" s="72"/>
+      <c r="AA81" s="72"/>
+      <c r="AB81" s="72"/>
+    </row>
+    <row r="82" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D82" s="64">
+        <v>9</v>
+      </c>
+      <c r="E82" s="64" t="s">
         <v>365</v>
       </c>
-      <c r="F78" s="151"/>
-      <c r="G78" s="151"/>
-      <c r="H78" s="151"/>
-      <c r="I78" s="157" t="s">
-        <v>400</v>
-      </c>
-      <c r="J78" s="152"/>
-      <c r="K78" s="151"/>
-      <c r="L78" s="151"/>
-      <c r="M78" s="151"/>
-      <c r="N78" s="151"/>
-      <c r="O78" s="151"/>
-      <c r="P78" s="151"/>
-      <c r="Q78" s="151"/>
-      <c r="R78" s="151"/>
-      <c r="S78" s="151"/>
-      <c r="T78" s="152"/>
-      <c r="U78" s="158"/>
-      <c r="V78" s="159"/>
-      <c r="W78" s="159"/>
-      <c r="X78" s="159"/>
-      <c r="Y78" s="159"/>
-      <c r="Z78" s="159"/>
-      <c r="AA78" s="159"/>
-      <c r="AB78" s="159"/>
-    </row>
-    <row r="79" spans="3:28" x14ac:dyDescent="0.2">
-      <c r="D79" s="150">
-        <v>5</v>
-      </c>
-      <c r="E79" s="150" t="s">
+      <c r="F82" s="65"/>
+      <c r="G82" s="65"/>
+      <c r="H82" s="65"/>
+      <c r="I82" s="70" t="s">
+        <v>385</v>
+      </c>
+      <c r="J82" s="66"/>
+      <c r="K82" s="65"/>
+      <c r="L82" s="65"/>
+      <c r="M82" s="65"/>
+      <c r="N82" s="65"/>
+      <c r="O82" s="65"/>
+      <c r="P82" s="65"/>
+      <c r="Q82" s="65"/>
+      <c r="R82" s="65"/>
+      <c r="S82" s="65"/>
+      <c r="T82" s="66"/>
+      <c r="U82" s="71"/>
+      <c r="V82" s="72"/>
+      <c r="W82" s="72"/>
+      <c r="X82" s="72"/>
+      <c r="Y82" s="72"/>
+      <c r="Z82" s="72"/>
+      <c r="AA82" s="72"/>
+      <c r="AB82" s="72"/>
+    </row>
+    <row r="83" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D83" s="64">
+        <v>10</v>
+      </c>
+      <c r="E83" s="64" t="s">
         <v>366</v>
       </c>
-      <c r="F79" s="151"/>
-      <c r="G79" s="151"/>
-      <c r="H79" s="151"/>
-      <c r="I79" s="157" t="s">
-        <v>401</v>
-      </c>
-      <c r="J79" s="152"/>
-      <c r="K79" s="151"/>
-      <c r="L79" s="151"/>
-      <c r="M79" s="151"/>
-      <c r="N79" s="151"/>
-      <c r="O79" s="151"/>
-      <c r="P79" s="151"/>
-      <c r="Q79" s="151"/>
-      <c r="R79" s="151"/>
-      <c r="S79" s="151"/>
-      <c r="T79" s="152"/>
-      <c r="U79" s="158"/>
-      <c r="V79" s="159"/>
-      <c r="W79" s="159"/>
-      <c r="X79" s="159"/>
-      <c r="Y79" s="159"/>
-      <c r="Z79" s="159"/>
-      <c r="AA79" s="159"/>
-      <c r="AB79" s="159"/>
-    </row>
-    <row r="80" spans="3:28" x14ac:dyDescent="0.2">
-      <c r="D80" s="150">
-        <v>6</v>
-      </c>
-      <c r="E80" s="150" t="s">
+      <c r="F83" s="65"/>
+      <c r="G83" s="65"/>
+      <c r="H83" s="65"/>
+      <c r="I83" s="70" t="s">
+        <v>386</v>
+      </c>
+      <c r="J83" s="66"/>
+      <c r="K83" s="65"/>
+      <c r="L83" s="65"/>
+      <c r="M83" s="65"/>
+      <c r="N83" s="65"/>
+      <c r="O83" s="65"/>
+      <c r="P83" s="65"/>
+      <c r="Q83" s="65"/>
+      <c r="R83" s="65"/>
+      <c r="S83" s="65"/>
+      <c r="T83" s="66"/>
+      <c r="U83" s="71"/>
+      <c r="V83" s="72"/>
+      <c r="W83" s="72"/>
+      <c r="X83" s="72"/>
+      <c r="Y83" s="72"/>
+      <c r="Z83" s="72"/>
+      <c r="AA83" s="72"/>
+      <c r="AB83" s="72"/>
+    </row>
+    <row r="84" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D84" s="64">
+        <v>11</v>
+      </c>
+      <c r="E84" s="64" t="s">
         <v>367</v>
       </c>
-      <c r="F80" s="151"/>
-      <c r="G80" s="151"/>
-      <c r="H80" s="151"/>
-      <c r="I80" s="157" t="s">
-        <v>402</v>
-      </c>
-      <c r="J80" s="152"/>
-      <c r="K80" s="151"/>
-      <c r="L80" s="151"/>
-      <c r="M80" s="151"/>
-      <c r="N80" s="151"/>
-      <c r="O80" s="151"/>
-      <c r="P80" s="151"/>
-      <c r="Q80" s="151"/>
-      <c r="R80" s="151"/>
-      <c r="S80" s="151"/>
-      <c r="T80" s="152"/>
-      <c r="U80" s="158"/>
-      <c r="V80" s="159"/>
-      <c r="W80" s="159"/>
-      <c r="X80" s="159"/>
-      <c r="Y80" s="159"/>
-      <c r="Z80" s="159"/>
-      <c r="AA80" s="159"/>
-      <c r="AB80" s="159"/>
-    </row>
-    <row r="81" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D81" s="150">
-        <v>7</v>
-      </c>
-      <c r="E81" s="150" t="s">
+      <c r="F84" s="65"/>
+      <c r="G84" s="65"/>
+      <c r="H84" s="65"/>
+      <c r="I84" s="70" t="s">
+        <v>387</v>
+      </c>
+      <c r="J84" s="66"/>
+      <c r="K84" s="65"/>
+      <c r="L84" s="65"/>
+      <c r="M84" s="65"/>
+      <c r="N84" s="65"/>
+      <c r="O84" s="65"/>
+      <c r="P84" s="65"/>
+      <c r="Q84" s="65"/>
+      <c r="R84" s="65"/>
+      <c r="S84" s="65"/>
+      <c r="T84" s="66"/>
+      <c r="U84" s="71"/>
+      <c r="V84" s="72"/>
+      <c r="W84" s="72"/>
+      <c r="X84" s="72"/>
+      <c r="Y84" s="72"/>
+      <c r="Z84" s="72"/>
+      <c r="AA84" s="72"/>
+      <c r="AB84" s="72"/>
+    </row>
+    <row r="85" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D85" s="64">
+        <v>12</v>
+      </c>
+      <c r="E85" s="64" t="s">
         <v>368</v>
       </c>
-      <c r="F81" s="151"/>
-      <c r="G81" s="151"/>
-      <c r="H81" s="151"/>
-      <c r="I81" s="157" t="s">
-        <v>403</v>
-      </c>
-      <c r="J81" s="152"/>
-      <c r="K81" s="151"/>
-      <c r="L81" s="151"/>
-      <c r="M81" s="151"/>
-      <c r="N81" s="151"/>
-      <c r="O81" s="151"/>
-      <c r="P81" s="151"/>
-      <c r="Q81" s="151"/>
-      <c r="R81" s="151"/>
-      <c r="S81" s="151"/>
-      <c r="T81" s="152"/>
-      <c r="U81" s="158"/>
-      <c r="V81" s="159"/>
-      <c r="W81" s="159"/>
-      <c r="X81" s="159"/>
-      <c r="Y81" s="159"/>
-      <c r="Z81" s="159"/>
-      <c r="AA81" s="159"/>
-      <c r="AB81" s="159"/>
-    </row>
-    <row r="82" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D82" s="150">
-        <v>8</v>
-      </c>
-      <c r="E82" s="150" t="s">
+      <c r="F85" s="65"/>
+      <c r="G85" s="65"/>
+      <c r="H85" s="65"/>
+      <c r="I85" s="70" t="s">
+        <v>388</v>
+      </c>
+      <c r="J85" s="66"/>
+      <c r="K85" s="65"/>
+      <c r="L85" s="65"/>
+      <c r="M85" s="65"/>
+      <c r="N85" s="65"/>
+      <c r="O85" s="65"/>
+      <c r="P85" s="65"/>
+      <c r="Q85" s="65"/>
+      <c r="R85" s="65"/>
+      <c r="S85" s="65"/>
+      <c r="T85" s="66"/>
+      <c r="U85" s="71"/>
+      <c r="V85" s="72"/>
+      <c r="W85" s="72"/>
+      <c r="X85" s="72"/>
+      <c r="Y85" s="72"/>
+      <c r="Z85" s="72"/>
+      <c r="AA85" s="72"/>
+      <c r="AB85" s="72"/>
+    </row>
+    <row r="86" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D86" s="64">
+        <v>13</v>
+      </c>
+      <c r="E86" s="64" t="s">
         <v>369</v>
       </c>
-      <c r="F82" s="151"/>
-      <c r="G82" s="151"/>
-      <c r="H82" s="151"/>
-      <c r="I82" s="157" t="s">
-        <v>404</v>
-      </c>
-      <c r="J82" s="152"/>
-      <c r="K82" s="151"/>
-      <c r="L82" s="151"/>
-      <c r="M82" s="151"/>
-      <c r="N82" s="151"/>
-      <c r="O82" s="151"/>
-      <c r="P82" s="151"/>
-      <c r="Q82" s="151"/>
-      <c r="R82" s="151"/>
-      <c r="S82" s="151"/>
-      <c r="T82" s="152"/>
-      <c r="U82" s="158"/>
-      <c r="V82" s="159"/>
-      <c r="W82" s="159"/>
-      <c r="X82" s="159"/>
-      <c r="Y82" s="159"/>
-      <c r="Z82" s="159"/>
-      <c r="AA82" s="159"/>
-      <c r="AB82" s="159"/>
-    </row>
-    <row r="83" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D83" s="150">
-        <v>9</v>
-      </c>
-      <c r="E83" s="150" t="s">
+      <c r="F86" s="65"/>
+      <c r="G86" s="65"/>
+      <c r="H86" s="65"/>
+      <c r="I86" s="70" t="s">
+        <v>389</v>
+      </c>
+      <c r="J86" s="66"/>
+      <c r="K86" s="65"/>
+      <c r="L86" s="65"/>
+      <c r="M86" s="65"/>
+      <c r="N86" s="65"/>
+      <c r="O86" s="65"/>
+      <c r="P86" s="65"/>
+      <c r="Q86" s="65"/>
+      <c r="R86" s="65"/>
+      <c r="S86" s="65"/>
+      <c r="T86" s="66"/>
+      <c r="U86" s="71"/>
+      <c r="V86" s="72"/>
+      <c r="W86" s="72"/>
+      <c r="X86" s="72"/>
+      <c r="Y86" s="72"/>
+      <c r="Z86" s="72"/>
+      <c r="AA86" s="72"/>
+      <c r="AB86" s="72"/>
+    </row>
+    <row r="87" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D87" s="64">
+        <v>14</v>
+      </c>
+      <c r="E87" s="64" t="s">
         <v>370</v>
       </c>
-      <c r="F83" s="151"/>
-      <c r="G83" s="151"/>
-      <c r="H83" s="151"/>
-      <c r="I83" s="157" t="s">
-        <v>405</v>
-      </c>
-      <c r="J83" s="152"/>
-      <c r="K83" s="151"/>
-      <c r="L83" s="151"/>
-      <c r="M83" s="151"/>
-      <c r="N83" s="151"/>
-      <c r="O83" s="151"/>
-      <c r="P83" s="151"/>
-      <c r="Q83" s="151"/>
-      <c r="R83" s="151"/>
-      <c r="S83" s="151"/>
-      <c r="T83" s="152"/>
-      <c r="U83" s="158"/>
-      <c r="V83" s="159"/>
-      <c r="W83" s="159"/>
-      <c r="X83" s="159"/>
-      <c r="Y83" s="159"/>
-      <c r="Z83" s="159"/>
-      <c r="AA83" s="159"/>
-      <c r="AB83" s="159"/>
-    </row>
-    <row r="84" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D84" s="150">
-        <v>10</v>
-      </c>
-      <c r="E84" s="150" t="s">
+      <c r="F87" s="65"/>
+      <c r="G87" s="65"/>
+      <c r="H87" s="65"/>
+      <c r="I87" s="70" t="s">
+        <v>390</v>
+      </c>
+      <c r="J87" s="66"/>
+      <c r="K87" s="65"/>
+      <c r="L87" s="65"/>
+      <c r="M87" s="65"/>
+      <c r="N87" s="65"/>
+      <c r="O87" s="65"/>
+      <c r="P87" s="65"/>
+      <c r="Q87" s="65"/>
+      <c r="R87" s="65"/>
+      <c r="S87" s="65"/>
+      <c r="T87" s="66"/>
+      <c r="U87" s="71"/>
+      <c r="V87" s="72"/>
+      <c r="W87" s="72"/>
+      <c r="X87" s="72"/>
+      <c r="Y87" s="72"/>
+      <c r="Z87" s="72"/>
+      <c r="AA87" s="72"/>
+      <c r="AB87" s="72"/>
+    </row>
+    <row r="88" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D88" s="64">
+        <v>15</v>
+      </c>
+      <c r="E88" s="64" t="s">
         <v>371</v>
       </c>
-      <c r="F84" s="151"/>
-      <c r="G84" s="151"/>
-      <c r="H84" s="151"/>
-      <c r="I84" s="157" t="s">
-        <v>406</v>
-      </c>
-      <c r="J84" s="152"/>
-      <c r="K84" s="151"/>
-      <c r="L84" s="151"/>
-      <c r="M84" s="151"/>
-      <c r="N84" s="151"/>
-      <c r="O84" s="151"/>
-      <c r="P84" s="151"/>
-      <c r="Q84" s="151"/>
-      <c r="R84" s="151"/>
-      <c r="S84" s="151"/>
-      <c r="T84" s="152"/>
-      <c r="U84" s="158"/>
-      <c r="V84" s="159"/>
-      <c r="W84" s="159"/>
-      <c r="X84" s="159"/>
-      <c r="Y84" s="159"/>
-      <c r="Z84" s="159"/>
-      <c r="AA84" s="159"/>
-      <c r="AB84" s="159"/>
-    </row>
-    <row r="85" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D85" s="150">
-        <v>11</v>
-      </c>
-      <c r="E85" s="150" t="s">
+      <c r="F88" s="65"/>
+      <c r="G88" s="65"/>
+      <c r="H88" s="65"/>
+      <c r="I88" s="70" t="s">
+        <v>391</v>
+      </c>
+      <c r="J88" s="66"/>
+      <c r="K88" s="65"/>
+      <c r="L88" s="65"/>
+      <c r="M88" s="65"/>
+      <c r="N88" s="65"/>
+      <c r="O88" s="65"/>
+      <c r="P88" s="65"/>
+      <c r="Q88" s="65"/>
+      <c r="R88" s="65"/>
+      <c r="S88" s="65"/>
+      <c r="T88" s="66"/>
+      <c r="U88" s="71"/>
+      <c r="V88" s="72"/>
+      <c r="W88" s="72"/>
+      <c r="X88" s="72"/>
+      <c r="Y88" s="72"/>
+      <c r="Z88" s="72"/>
+      <c r="AA88" s="72"/>
+      <c r="AB88" s="72"/>
+    </row>
+    <row r="89" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D89" s="64">
+        <v>16</v>
+      </c>
+      <c r="E89" s="64" t="s">
         <v>372</v>
       </c>
-      <c r="F85" s="151"/>
-      <c r="G85" s="151"/>
-      <c r="H85" s="151"/>
-      <c r="I85" s="157" t="s">
-        <v>407</v>
-      </c>
-      <c r="J85" s="152"/>
-      <c r="K85" s="151"/>
-      <c r="L85" s="151"/>
-      <c r="M85" s="151"/>
-      <c r="N85" s="151"/>
-      <c r="O85" s="151"/>
-      <c r="P85" s="151"/>
-      <c r="Q85" s="151"/>
-      <c r="R85" s="151"/>
-      <c r="S85" s="151"/>
-      <c r="T85" s="152"/>
-      <c r="U85" s="158"/>
-      <c r="V85" s="159"/>
-      <c r="W85" s="159"/>
-      <c r="X85" s="159"/>
-      <c r="Y85" s="159"/>
-      <c r="Z85" s="159"/>
-      <c r="AA85" s="159"/>
-      <c r="AB85" s="159"/>
-    </row>
-    <row r="86" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D86" s="150">
-        <v>12</v>
-      </c>
-      <c r="E86" s="150" t="s">
+      <c r="F89" s="65"/>
+      <c r="G89" s="65"/>
+      <c r="H89" s="65"/>
+      <c r="I89" s="70" t="s">
+        <v>392</v>
+      </c>
+      <c r="J89" s="66"/>
+      <c r="K89" s="65"/>
+      <c r="L89" s="65"/>
+      <c r="M89" s="65"/>
+      <c r="N89" s="65"/>
+      <c r="O89" s="65"/>
+      <c r="P89" s="65"/>
+      <c r="Q89" s="65"/>
+      <c r="R89" s="65"/>
+      <c r="S89" s="65"/>
+      <c r="T89" s="66"/>
+      <c r="U89" s="71"/>
+      <c r="V89" s="72"/>
+      <c r="W89" s="72"/>
+      <c r="X89" s="72"/>
+      <c r="Y89" s="72"/>
+      <c r="Z89" s="72"/>
+      <c r="AA89" s="72"/>
+      <c r="AB89" s="72"/>
+    </row>
+    <row r="90" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D90" s="64">
+        <v>17</v>
+      </c>
+      <c r="E90" s="64" t="s">
         <v>373</v>
       </c>
-      <c r="F86" s="151"/>
-      <c r="G86" s="151"/>
-      <c r="H86" s="151"/>
-      <c r="I86" s="157" t="s">
-        <v>408</v>
-      </c>
-      <c r="J86" s="152"/>
-      <c r="K86" s="151"/>
-      <c r="L86" s="151"/>
-      <c r="M86" s="151"/>
-      <c r="N86" s="151"/>
-      <c r="O86" s="151"/>
-      <c r="P86" s="151"/>
-      <c r="Q86" s="151"/>
-      <c r="R86" s="151"/>
-      <c r="S86" s="151"/>
-      <c r="T86" s="152"/>
-      <c r="U86" s="158"/>
-      <c r="V86" s="159"/>
-      <c r="W86" s="159"/>
-      <c r="X86" s="159"/>
-      <c r="Y86" s="159"/>
-      <c r="Z86" s="159"/>
-      <c r="AA86" s="159"/>
-      <c r="AB86" s="159"/>
-    </row>
-    <row r="87" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D87" s="150">
-        <v>13</v>
-      </c>
-      <c r="E87" s="150" t="s">
+      <c r="F90" s="65"/>
+      <c r="G90" s="65"/>
+      <c r="H90" s="65"/>
+      <c r="I90" s="70" t="s">
+        <v>393</v>
+      </c>
+      <c r="J90" s="66"/>
+      <c r="K90" s="65"/>
+      <c r="L90" s="65"/>
+      <c r="M90" s="65"/>
+      <c r="N90" s="65"/>
+      <c r="O90" s="65"/>
+      <c r="P90" s="65"/>
+      <c r="Q90" s="65"/>
+      <c r="R90" s="65"/>
+      <c r="S90" s="65"/>
+      <c r="T90" s="66"/>
+      <c r="U90" s="71"/>
+      <c r="V90" s="72"/>
+      <c r="W90" s="72"/>
+      <c r="X90" s="72"/>
+      <c r="Y90" s="72"/>
+      <c r="Z90" s="72"/>
+      <c r="AA90" s="72"/>
+      <c r="AB90" s="72"/>
+    </row>
+    <row r="91" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D91" s="64">
+        <v>18</v>
+      </c>
+      <c r="E91" s="64" t="s">
         <v>374</v>
       </c>
-      <c r="F87" s="151"/>
-      <c r="G87" s="151"/>
-      <c r="H87" s="151"/>
-      <c r="I87" s="157" t="s">
-        <v>409</v>
-      </c>
-      <c r="J87" s="152"/>
-      <c r="K87" s="151"/>
-      <c r="L87" s="151"/>
-      <c r="M87" s="151"/>
-      <c r="N87" s="151"/>
-      <c r="O87" s="151"/>
-      <c r="P87" s="151"/>
-      <c r="Q87" s="151"/>
-      <c r="R87" s="151"/>
-      <c r="S87" s="151"/>
-      <c r="T87" s="152"/>
-      <c r="U87" s="158"/>
-      <c r="V87" s="159"/>
-      <c r="W87" s="159"/>
-      <c r="X87" s="159"/>
-      <c r="Y87" s="159"/>
-      <c r="Z87" s="159"/>
-      <c r="AA87" s="159"/>
-      <c r="AB87" s="159"/>
-    </row>
-    <row r="88" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D88" s="150">
-        <v>14</v>
-      </c>
-      <c r="E88" s="150" t="s">
+      <c r="F91" s="65"/>
+      <c r="G91" s="65"/>
+      <c r="H91" s="65"/>
+      <c r="I91" s="70" t="s">
+        <v>394</v>
+      </c>
+      <c r="J91" s="66"/>
+      <c r="K91" s="65"/>
+      <c r="L91" s="65"/>
+      <c r="M91" s="65"/>
+      <c r="N91" s="65"/>
+      <c r="O91" s="65"/>
+      <c r="P91" s="65"/>
+      <c r="Q91" s="65"/>
+      <c r="R91" s="65"/>
+      <c r="S91" s="65"/>
+      <c r="T91" s="66"/>
+      <c r="U91" s="71"/>
+      <c r="V91" s="72"/>
+      <c r="W91" s="72"/>
+      <c r="X91" s="72"/>
+      <c r="Y91" s="72"/>
+      <c r="Z91" s="72"/>
+      <c r="AA91" s="72"/>
+      <c r="AB91" s="72"/>
+    </row>
+    <row r="92" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D92" s="64">
+        <v>19</v>
+      </c>
+      <c r="E92" s="64" t="s">
         <v>375</v>
       </c>
-      <c r="F88" s="151"/>
-      <c r="G88" s="151"/>
-      <c r="H88" s="151"/>
-      <c r="I88" s="157" t="s">
-        <v>410</v>
-      </c>
-      <c r="J88" s="152"/>
-      <c r="K88" s="151"/>
-      <c r="L88" s="151"/>
-      <c r="M88" s="151"/>
-      <c r="N88" s="151"/>
-      <c r="O88" s="151"/>
-      <c r="P88" s="151"/>
-      <c r="Q88" s="151"/>
-      <c r="R88" s="151"/>
-      <c r="S88" s="151"/>
-      <c r="T88" s="152"/>
-      <c r="U88" s="158"/>
-      <c r="V88" s="159"/>
-      <c r="W88" s="159"/>
-      <c r="X88" s="159"/>
-      <c r="Y88" s="159"/>
-      <c r="Z88" s="159"/>
-      <c r="AA88" s="159"/>
-      <c r="AB88" s="159"/>
-    </row>
-    <row r="89" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D89" s="150">
-        <v>15</v>
-      </c>
-      <c r="E89" s="150" t="s">
-        <v>376</v>
-      </c>
-      <c r="F89" s="151"/>
-      <c r="G89" s="151"/>
-      <c r="H89" s="151"/>
-      <c r="I89" s="157" t="s">
-        <v>411</v>
-      </c>
-      <c r="J89" s="152"/>
-      <c r="K89" s="151"/>
-      <c r="L89" s="151"/>
-      <c r="M89" s="151"/>
-      <c r="N89" s="151"/>
-      <c r="O89" s="151"/>
-      <c r="P89" s="151"/>
-      <c r="Q89" s="151"/>
-      <c r="R89" s="151"/>
-      <c r="S89" s="151"/>
-      <c r="T89" s="152"/>
-      <c r="U89" s="158"/>
-      <c r="V89" s="159"/>
-      <c r="W89" s="159"/>
-      <c r="X89" s="159"/>
-      <c r="Y89" s="159"/>
-      <c r="Z89" s="159"/>
-      <c r="AA89" s="159"/>
-      <c r="AB89" s="159"/>
-    </row>
-    <row r="90" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D90" s="150">
-        <v>16</v>
-      </c>
-      <c r="E90" s="150" t="s">
-        <v>377</v>
-      </c>
-      <c r="F90" s="151"/>
-      <c r="G90" s="151"/>
-      <c r="H90" s="151"/>
-      <c r="I90" s="157" t="s">
-        <v>412</v>
-      </c>
-      <c r="J90" s="152"/>
-      <c r="K90" s="151"/>
-      <c r="L90" s="151"/>
-      <c r="M90" s="151"/>
-      <c r="N90" s="151"/>
-      <c r="O90" s="151"/>
-      <c r="P90" s="151"/>
-      <c r="Q90" s="151"/>
-      <c r="R90" s="151"/>
-      <c r="S90" s="151"/>
-      <c r="T90" s="152"/>
-      <c r="U90" s="158"/>
-      <c r="V90" s="159"/>
-      <c r="W90" s="159"/>
-      <c r="X90" s="159"/>
-      <c r="Y90" s="159"/>
-      <c r="Z90" s="159"/>
-      <c r="AA90" s="159"/>
-      <c r="AB90" s="159"/>
-    </row>
-    <row r="91" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D91" s="150">
-        <v>17</v>
-      </c>
-      <c r="E91" s="150" t="s">
-        <v>378</v>
-      </c>
-      <c r="F91" s="151"/>
-      <c r="G91" s="151"/>
-      <c r="H91" s="151"/>
-      <c r="I91" s="157" t="s">
-        <v>413</v>
-      </c>
-      <c r="J91" s="152"/>
-      <c r="K91" s="151"/>
-      <c r="L91" s="151"/>
-      <c r="M91" s="151"/>
-      <c r="N91" s="151"/>
-      <c r="O91" s="151"/>
-      <c r="P91" s="151"/>
-      <c r="Q91" s="151"/>
-      <c r="R91" s="151"/>
-      <c r="S91" s="151"/>
-      <c r="T91" s="152"/>
-      <c r="U91" s="158"/>
-      <c r="V91" s="159"/>
-      <c r="W91" s="159"/>
-      <c r="X91" s="159"/>
-      <c r="Y91" s="159"/>
-      <c r="Z91" s="159"/>
-      <c r="AA91" s="159"/>
-      <c r="AB91" s="159"/>
-    </row>
-    <row r="92" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D92" s="150">
-        <v>18</v>
-      </c>
-      <c r="E92" s="150" t="s">
-        <v>379</v>
-      </c>
-      <c r="F92" s="151"/>
-      <c r="G92" s="151"/>
-      <c r="H92" s="151"/>
-      <c r="I92" s="157" t="s">
-        <v>414</v>
-      </c>
-      <c r="J92" s="152"/>
-      <c r="K92" s="151"/>
-      <c r="L92" s="151"/>
-      <c r="M92" s="151"/>
-      <c r="N92" s="151"/>
-      <c r="O92" s="151"/>
-      <c r="P92" s="151"/>
-      <c r="Q92" s="151"/>
-      <c r="R92" s="151"/>
-      <c r="S92" s="151"/>
-      <c r="T92" s="152"/>
-      <c r="U92" s="158"/>
-      <c r="V92" s="159"/>
-      <c r="W92" s="159"/>
-      <c r="X92" s="159"/>
-      <c r="Y92" s="159"/>
-      <c r="Z92" s="159"/>
-      <c r="AA92" s="159"/>
-      <c r="AB92" s="159"/>
-    </row>
-    <row r="93" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D93" s="150">
-        <v>19</v>
-      </c>
-      <c r="E93" s="150" t="s">
-        <v>380</v>
-      </c>
-      <c r="F93" s="151"/>
-      <c r="G93" s="151"/>
-      <c r="H93" s="151"/>
-      <c r="I93" s="157" t="s">
-        <v>415</v>
-      </c>
-      <c r="J93" s="152"/>
-      <c r="K93" s="151"/>
-      <c r="L93" s="151"/>
-      <c r="M93" s="151"/>
-      <c r="N93" s="151"/>
-      <c r="O93" s="151"/>
-      <c r="P93" s="151"/>
-      <c r="Q93" s="151"/>
-      <c r="R93" s="151"/>
-      <c r="S93" s="151"/>
-      <c r="T93" s="152"/>
-      <c r="U93" s="158"/>
-      <c r="V93" s="159"/>
-      <c r="W93" s="159"/>
-      <c r="X93" s="159"/>
-      <c r="Y93" s="159"/>
-      <c r="Z93" s="159"/>
-      <c r="AA93" s="159"/>
-      <c r="AB93" s="159"/>
-    </row>
-    <row r="96" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D96" s="30" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="97" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D97" s="30" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="98" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D98" s="30" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="99" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D99" s="30" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="101" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D101" s="55" t="s">
-        <v>305</v>
-      </c>
-      <c r="E101" s="153" t="s">
-        <v>419</v>
-      </c>
-      <c r="F101" s="154"/>
-      <c r="G101" s="154"/>
-      <c r="H101" s="154"/>
-      <c r="I101" s="154"/>
-      <c r="J101" s="154"/>
-      <c r="K101" s="154"/>
-      <c r="L101" s="154"/>
-      <c r="M101" s="154"/>
-      <c r="N101" s="155"/>
-      <c r="O101" s="153" t="s">
-        <v>420</v>
-      </c>
-      <c r="P101" s="154"/>
-      <c r="Q101" s="154"/>
-      <c r="R101" s="154"/>
-      <c r="S101" s="154"/>
-      <c r="T101" s="154"/>
-      <c r="U101" s="154"/>
-      <c r="V101" s="154"/>
-      <c r="W101" s="154"/>
-      <c r="X101" s="154"/>
-      <c r="Y101" s="154"/>
-      <c r="Z101" s="154"/>
-      <c r="AA101" s="154"/>
-      <c r="AB101" s="155"/>
-    </row>
-    <row r="102" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D102" s="150">
-        <v>1</v>
-      </c>
-      <c r="E102" s="150" t="s">
-        <v>383</v>
-      </c>
-      <c r="F102" s="151"/>
-      <c r="G102" s="151"/>
-      <c r="H102" s="151"/>
-      <c r="I102" s="151"/>
-      <c r="J102" s="151"/>
-      <c r="K102" s="151"/>
-      <c r="L102" s="151"/>
-      <c r="M102" s="151"/>
-      <c r="N102" s="152"/>
-      <c r="O102" s="156" t="s">
-        <v>396</v>
-      </c>
-      <c r="P102" s="151"/>
-      <c r="Q102" s="151"/>
-      <c r="R102" s="151"/>
-      <c r="S102" s="151"/>
-      <c r="T102" s="151"/>
-      <c r="U102" s="151"/>
-      <c r="V102" s="151"/>
-      <c r="W102" s="151"/>
-      <c r="X102" s="151"/>
-      <c r="Y102" s="151"/>
-      <c r="Z102" s="151"/>
-      <c r="AA102" s="151"/>
-      <c r="AB102" s="152"/>
-    </row>
-    <row r="103" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D103" s="150">
-        <v>2</v>
-      </c>
-      <c r="E103" s="150" t="s">
-        <v>384</v>
-      </c>
-      <c r="F103" s="151"/>
-      <c r="G103" s="151"/>
-      <c r="H103" s="151"/>
-      <c r="I103" s="151"/>
-      <c r="J103" s="151"/>
-      <c r="K103" s="151"/>
-      <c r="L103" s="151"/>
-      <c r="M103" s="151"/>
-      <c r="N103" s="152"/>
-      <c r="O103" s="156" t="s">
-        <v>385</v>
-      </c>
-      <c r="P103" s="151"/>
-      <c r="Q103" s="151"/>
-      <c r="R103" s="151"/>
-      <c r="S103" s="151"/>
-      <c r="T103" s="151"/>
-      <c r="U103" s="151"/>
-      <c r="V103" s="151"/>
-      <c r="W103" s="151"/>
-      <c r="X103" s="151"/>
-      <c r="Y103" s="151"/>
-      <c r="Z103" s="151"/>
-      <c r="AA103" s="151"/>
-      <c r="AB103" s="152"/>
-    </row>
-    <row r="104" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D104" s="150">
-        <v>3</v>
-      </c>
-      <c r="E104" s="150" t="s">
-        <v>386</v>
-      </c>
-      <c r="F104" s="151"/>
-      <c r="G104" s="151"/>
-      <c r="H104" s="151"/>
-      <c r="I104" s="151"/>
-      <c r="J104" s="151"/>
-      <c r="K104" s="151"/>
-      <c r="L104" s="151"/>
-      <c r="M104" s="151"/>
-      <c r="N104" s="152"/>
-      <c r="O104" s="156" t="s">
-        <v>387</v>
-      </c>
-      <c r="P104" s="151"/>
-      <c r="Q104" s="151"/>
-      <c r="R104" s="151"/>
-      <c r="S104" s="151"/>
-      <c r="T104" s="151"/>
-      <c r="U104" s="151"/>
-      <c r="V104" s="151"/>
-      <c r="W104" s="151"/>
-      <c r="X104" s="151"/>
-      <c r="Y104" s="151"/>
-      <c r="Z104" s="151"/>
-      <c r="AA104" s="151"/>
-      <c r="AB104" s="152"/>
-    </row>
-    <row r="105" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D105" s="150">
-        <v>4</v>
-      </c>
-      <c r="E105" s="150" t="s">
-        <v>388</v>
-      </c>
-      <c r="F105" s="151"/>
-      <c r="G105" s="151"/>
-      <c r="H105" s="151"/>
-      <c r="I105" s="151"/>
-      <c r="J105" s="151"/>
-      <c r="K105" s="151"/>
-      <c r="L105" s="151"/>
-      <c r="M105" s="151"/>
-      <c r="N105" s="152"/>
-      <c r="O105" s="156" t="s">
-        <v>389</v>
-      </c>
-      <c r="P105" s="151"/>
-      <c r="Q105" s="151"/>
-      <c r="R105" s="151"/>
-      <c r="S105" s="151"/>
-      <c r="T105" s="151"/>
-      <c r="U105" s="151"/>
-      <c r="V105" s="151"/>
-      <c r="W105" s="151"/>
-      <c r="X105" s="151"/>
-      <c r="Y105" s="151"/>
-      <c r="Z105" s="151"/>
-      <c r="AA105" s="151"/>
-      <c r="AB105" s="152"/>
-    </row>
-    <row r="106" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D106" s="150">
-        <v>5</v>
-      </c>
-      <c r="E106" s="150" t="s">
-        <v>390</v>
-      </c>
-      <c r="F106" s="151"/>
-      <c r="G106" s="151"/>
-      <c r="H106" s="151"/>
-      <c r="I106" s="151"/>
-      <c r="J106" s="151"/>
-      <c r="K106" s="151"/>
-      <c r="L106" s="151"/>
-      <c r="M106" s="151"/>
-      <c r="N106" s="152"/>
-      <c r="O106" s="156" t="s">
-        <v>391</v>
-      </c>
-      <c r="P106" s="151"/>
-      <c r="Q106" s="151"/>
-      <c r="R106" s="151"/>
-      <c r="S106" s="151"/>
-      <c r="T106" s="151"/>
-      <c r="U106" s="151"/>
-      <c r="V106" s="151"/>
-      <c r="W106" s="151"/>
-      <c r="X106" s="151"/>
-      <c r="Y106" s="151"/>
-      <c r="Z106" s="151"/>
-      <c r="AA106" s="151"/>
-      <c r="AB106" s="152"/>
-    </row>
-    <row r="107" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D107" s="150">
-        <v>6</v>
-      </c>
-      <c r="E107" s="150" t="s">
-        <v>392</v>
-      </c>
-      <c r="F107" s="151"/>
-      <c r="G107" s="151"/>
-      <c r="H107" s="151"/>
-      <c r="I107" s="151"/>
-      <c r="J107" s="151"/>
-      <c r="K107" s="151"/>
-      <c r="L107" s="151"/>
-      <c r="M107" s="151"/>
-      <c r="N107" s="152"/>
-      <c r="O107" s="156" t="s">
-        <v>393</v>
-      </c>
-      <c r="P107" s="151"/>
-      <c r="Q107" s="151"/>
-      <c r="R107" s="151"/>
-      <c r="S107" s="151"/>
-      <c r="T107" s="151"/>
-      <c r="U107" s="151"/>
-      <c r="V107" s="151"/>
-      <c r="W107" s="151"/>
-      <c r="X107" s="151"/>
-      <c r="Y107" s="151"/>
-      <c r="Z107" s="151"/>
-      <c r="AA107" s="151"/>
-      <c r="AB107" s="152"/>
-    </row>
-    <row r="108" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D108" s="150">
-        <v>7</v>
-      </c>
-      <c r="E108" s="150" t="s">
-        <v>394</v>
-      </c>
-      <c r="F108" s="151"/>
-      <c r="G108" s="151"/>
-      <c r="H108" s="151"/>
-      <c r="I108" s="151"/>
-      <c r="J108" s="151"/>
-      <c r="K108" s="151"/>
-      <c r="L108" s="151"/>
-      <c r="M108" s="151"/>
-      <c r="N108" s="152"/>
-      <c r="O108" s="156" t="s">
+      <c r="F92" s="65"/>
+      <c r="G92" s="65"/>
+      <c r="H92" s="65"/>
+      <c r="I92" s="70" t="s">
         <v>395</v>
       </c>
-      <c r="P108" s="151"/>
-      <c r="Q108" s="151"/>
-      <c r="R108" s="151"/>
-      <c r="S108" s="151"/>
-      <c r="T108" s="151"/>
-      <c r="U108" s="151"/>
-      <c r="V108" s="151"/>
-      <c r="W108" s="151"/>
-      <c r="X108" s="151"/>
-      <c r="Y108" s="151"/>
-      <c r="Z108" s="151"/>
-      <c r="AA108" s="151"/>
-      <c r="AB108" s="152"/>
-    </row>
-    <row r="109" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D109" s="149">
-        <v>8</v>
-      </c>
-      <c r="E109" s="150" t="s">
-        <v>421</v>
-      </c>
-      <c r="F109" s="151"/>
-      <c r="G109" s="151"/>
-      <c r="H109" s="151"/>
-      <c r="I109" s="151"/>
-      <c r="J109" s="151"/>
-      <c r="K109" s="151"/>
-      <c r="L109" s="151"/>
-      <c r="M109" s="151"/>
-      <c r="N109" s="152"/>
-      <c r="O109" s="157" t="s">
-        <v>422</v>
-      </c>
-      <c r="P109" s="151"/>
-      <c r="Q109" s="151"/>
-      <c r="R109" s="151"/>
-      <c r="S109" s="151"/>
-      <c r="T109" s="151"/>
-      <c r="U109" s="151"/>
-      <c r="V109" s="151"/>
-      <c r="W109" s="151"/>
-      <c r="X109" s="151"/>
-      <c r="Y109" s="151"/>
-      <c r="Z109" s="151"/>
-      <c r="AA109" s="151"/>
-      <c r="AB109" s="152"/>
-    </row>
-    <row r="110" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="D110" s="159"/>
-      <c r="E110" s="159"/>
-      <c r="F110" s="159"/>
-      <c r="G110" s="159"/>
-      <c r="H110" s="159"/>
-      <c r="I110" s="159"/>
-      <c r="J110" s="159"/>
-      <c r="K110" s="159"/>
-      <c r="L110" s="159"/>
-      <c r="M110" s="159"/>
-      <c r="N110" s="159"/>
-      <c r="O110" s="162"/>
-      <c r="P110" s="159"/>
-      <c r="Q110" s="159"/>
-      <c r="R110" s="159"/>
-      <c r="S110" s="159"/>
-      <c r="T110" s="159"/>
-      <c r="U110" s="159"/>
-      <c r="V110" s="159"/>
-      <c r="W110" s="159"/>
-      <c r="X110" s="159"/>
-      <c r="Y110" s="159"/>
-      <c r="Z110" s="159"/>
-      <c r="AA110" s="159"/>
-      <c r="AB110" s="159"/>
+      <c r="J92" s="66"/>
+      <c r="K92" s="65"/>
+      <c r="L92" s="65"/>
+      <c r="M92" s="65"/>
+      <c r="N92" s="65"/>
+      <c r="O92" s="65"/>
+      <c r="P92" s="65"/>
+      <c r="Q92" s="65"/>
+      <c r="R92" s="65"/>
+      <c r="S92" s="65"/>
+      <c r="T92" s="66"/>
+      <c r="U92" s="71"/>
+      <c r="V92" s="72"/>
+      <c r="W92" s="72"/>
+      <c r="X92" s="72"/>
+      <c r="Y92" s="72"/>
+      <c r="Z92" s="72"/>
+      <c r="AA92" s="72"/>
+      <c r="AB92" s="72"/>
+    </row>
+    <row r="94" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D94" s="72"/>
+      <c r="E94" s="72"/>
+      <c r="F94" s="72"/>
+      <c r="G94" s="72"/>
+      <c r="H94" s="72"/>
+      <c r="I94" s="72"/>
+      <c r="J94" s="72"/>
+      <c r="K94" s="72"/>
+      <c r="L94" s="72"/>
+      <c r="M94" s="72"/>
+      <c r="N94" s="72"/>
+      <c r="O94" s="75"/>
+      <c r="P94" s="72"/>
+      <c r="Q94" s="72"/>
+      <c r="R94" s="72"/>
+      <c r="S94" s="72"/>
+      <c r="T94" s="72"/>
+      <c r="U94" s="72"/>
+      <c r="V94" s="72"/>
+      <c r="W94" s="72"/>
+      <c r="X94" s="72"/>
+      <c r="Y94" s="72"/>
+      <c r="Z94" s="72"/>
+      <c r="AA94" s="72"/>
+      <c r="AB94" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="E66:J66"/>
-    <mergeCell ref="K66:AB66"/>
-    <mergeCell ref="E63:J63"/>
-    <mergeCell ref="K63:AB63"/>
-    <mergeCell ref="E64:J64"/>
-    <mergeCell ref="K64:AB64"/>
-    <mergeCell ref="E65:J65"/>
-    <mergeCell ref="K65:AB65"/>
-    <mergeCell ref="E60:J60"/>
-    <mergeCell ref="K60:AB60"/>
-    <mergeCell ref="E61:J61"/>
-    <mergeCell ref="K61:AB61"/>
-    <mergeCell ref="E62:J62"/>
-    <mergeCell ref="K62:AB62"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="E57:J57"/>
-    <mergeCell ref="K57:AB57"/>
-    <mergeCell ref="E58:J58"/>
-    <mergeCell ref="K58:AB58"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
     <mergeCell ref="E59:J59"/>
     <mergeCell ref="K59:AB59"/>
     <mergeCell ref="AG1:AI1"/>
@@ -12604,39 +12244,53 @@
     <mergeCell ref="AC1:AF1"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="E57:J57"/>
+    <mergeCell ref="K57:AB57"/>
+    <mergeCell ref="E58:J58"/>
+    <mergeCell ref="K58:AB58"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="E60:J60"/>
+    <mergeCell ref="K60:AB60"/>
+    <mergeCell ref="E61:J61"/>
+    <mergeCell ref="K61:AB61"/>
+    <mergeCell ref="E62:J62"/>
+    <mergeCell ref="K62:AB62"/>
+    <mergeCell ref="E66:J66"/>
+    <mergeCell ref="K66:AB66"/>
+    <mergeCell ref="E63:J63"/>
+    <mergeCell ref="K63:AB63"/>
+    <mergeCell ref="E64:J64"/>
+    <mergeCell ref="K64:AB64"/>
+    <mergeCell ref="E65:J65"/>
+    <mergeCell ref="K65:AB65"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="AB75" r:id="rId1" display="https://jakarta.ee/specifications/faces/" xr:uid="{072C18AF-609F-4653-9808-3595E12CDA8B}"/>
-    <hyperlink ref="AB76" r:id="rId2" display="https://jakarta.ee/specifications/authentication/" xr:uid="{0A797D20-605F-46BB-ADCC-B14FE0BAE9E6}"/>
-    <hyperlink ref="AB77" r:id="rId3" display="https://jakarta.ee/specifications/authorization/" xr:uid="{DEEA3D02-1151-4A12-AE68-04AD5A22943B}"/>
-    <hyperlink ref="AB78" r:id="rId4" display="https://jakarta.ee/specifications/messaging/" xr:uid="{D8FBB6FF-C55B-4709-82BA-8B942F0EE8F3}"/>
-    <hyperlink ref="AB79" r:id="rId5" display="https://jakarta.ee/specifications/persistence/" xr:uid="{2B13828B-C59E-461B-BDE8-DF64D4AA2EBD}"/>
-    <hyperlink ref="AB80" r:id="rId6" display="https://jakarta.ee/specifications/transactions/" xr:uid="{4B4DFC95-691A-43EF-9BA6-3F253F48DED8}"/>
-    <hyperlink ref="AB81" r:id="rId7" display="https://jakarta.ee/specifications/batch/" xr:uid="{BDBD61B2-5A98-4723-9582-4D624CD9BC90}"/>
-    <hyperlink ref="AB82" r:id="rId8" display="https://jakarta.ee/specifications/connectors/" xr:uid="{63C049C0-B50F-4413-8D9E-D92B11C0DCB8}"/>
-    <hyperlink ref="AB83" r:id="rId9" display="https://jakarta.ee/specifications/activation/" xr:uid="{AB9F409E-AB6B-4558-A403-A228A8ABDA31}"/>
-    <hyperlink ref="AB84" r:id="rId10" display="https://jakarta.ee/specifications/expression-language/" xr:uid="{F62A3EF1-C282-4BCC-98A5-A6CA71C650B4}"/>
-    <hyperlink ref="AB85" r:id="rId11" display="https://jakarta.ee/specifications/enterprise-beans/" xr:uid="{704C23F0-9669-4135-B37D-FF9FAF28013A}"/>
-    <hyperlink ref="AB86" r:id="rId12" display="https://jakarta.ee/specifications/xml-binding/" xr:uid="{72A38165-5E11-4AE4-A696-C0EDB438F3FC}"/>
-    <hyperlink ref="AB87" r:id="rId13" display="https://jakarta.ee/specifications/jsonb/" xr:uid="{0C3AD5D6-3AFC-4F21-8554-C2193029568C}"/>
-    <hyperlink ref="AB88" r:id="rId14" display="https://jakarta.ee/specifications/jsonp/" xr:uid="{C91A89E6-4BB2-4045-AAFF-4A88EACA4FE5}"/>
-    <hyperlink ref="AB89" r:id="rId15" display="https://jakarta.ee/specifications/pages/" xr:uid="{E897019C-0949-48DE-8AA1-C7CAA399C7DE}"/>
-    <hyperlink ref="AB90" r:id="rId16" display="https://jakarta.ee/specifications/xml-web-services/" xr:uid="{BEBFEE85-BD91-44D7-BB2A-683DD7731328}"/>
-    <hyperlink ref="AB91" r:id="rId17" display="https://jakarta.ee/specifications/restful-ws/" xr:uid="{02390528-EB8B-4E6A-B1E9-9B563A6E8657}"/>
-    <hyperlink ref="AB92" r:id="rId18" display="https://jakarta.ee/specifications/tags/" xr:uid="{429F9649-389A-4EB4-A123-299AE69673C7}"/>
-    <hyperlink ref="AB93" r:id="rId19" display="https://jakarta.ee/specifications/cdi/" xr:uid="{0CBA927F-33E0-472C-B599-04E03CFEE5F6}"/>
-    <hyperlink ref="AB102" r:id="rId20" display="https://jakarta.ee/specifications/faces/" xr:uid="{3E8E8F6C-8C72-40CF-90F3-35DE205672A0}"/>
-    <hyperlink ref="AB103" r:id="rId21" display="https://jakarta.ee/specifications/authentication/" xr:uid="{EB5AB972-B2E5-4B5F-9185-8F2CDFCAEB9B}"/>
-    <hyperlink ref="AB104" r:id="rId22" display="https://jakarta.ee/specifications/authorization/" xr:uid="{07E3270E-64D8-4A50-A6C6-BEEEE196DEB6}"/>
-    <hyperlink ref="AB105" r:id="rId23" display="https://jakarta.ee/specifications/messaging/" xr:uid="{AF693CDB-C111-4E42-8805-6684D9EF64E5}"/>
-    <hyperlink ref="AB106" r:id="rId24" display="https://jakarta.ee/specifications/persistence/" xr:uid="{5C4CCC92-67D4-4D1D-B038-94E70D323BE5}"/>
-    <hyperlink ref="AB107" r:id="rId25" display="https://jakarta.ee/specifications/transactions/" xr:uid="{ECB6D077-F239-426A-B765-A5E1E83B5C4A}"/>
-    <hyperlink ref="AB108" r:id="rId26" display="https://jakarta.ee/specifications/batch/" xr:uid="{4E6AFAFA-315B-4DD7-A090-F4A2D1103E20}"/>
+    <hyperlink ref="AB74" r:id="rId1" display="https://jakarta.ee/specifications/faces/" xr:uid="{072C18AF-609F-4653-9808-3595E12CDA8B}"/>
+    <hyperlink ref="AB75" r:id="rId2" display="https://jakarta.ee/specifications/authentication/" xr:uid="{0A797D20-605F-46BB-ADCC-B14FE0BAE9E6}"/>
+    <hyperlink ref="AB76" r:id="rId3" display="https://jakarta.ee/specifications/authorization/" xr:uid="{DEEA3D02-1151-4A12-AE68-04AD5A22943B}"/>
+    <hyperlink ref="AB77" r:id="rId4" display="https://jakarta.ee/specifications/messaging/" xr:uid="{D8FBB6FF-C55B-4709-82BA-8B942F0EE8F3}"/>
+    <hyperlink ref="AB78" r:id="rId5" display="https://jakarta.ee/specifications/persistence/" xr:uid="{2B13828B-C59E-461B-BDE8-DF64D4AA2EBD}"/>
+    <hyperlink ref="AB79" r:id="rId6" display="https://jakarta.ee/specifications/transactions/" xr:uid="{4B4DFC95-691A-43EF-9BA6-3F253F48DED8}"/>
+    <hyperlink ref="AB80" r:id="rId7" display="https://jakarta.ee/specifications/batch/" xr:uid="{BDBD61B2-5A98-4723-9582-4D624CD9BC90}"/>
+    <hyperlink ref="AB81" r:id="rId8" display="https://jakarta.ee/specifications/connectors/" xr:uid="{63C049C0-B50F-4413-8D9E-D92B11C0DCB8}"/>
+    <hyperlink ref="AB82" r:id="rId9" display="https://jakarta.ee/specifications/activation/" xr:uid="{AB9F409E-AB6B-4558-A403-A228A8ABDA31}"/>
+    <hyperlink ref="AB83" r:id="rId10" display="https://jakarta.ee/specifications/expression-language/" xr:uid="{F62A3EF1-C282-4BCC-98A5-A6CA71C650B4}"/>
+    <hyperlink ref="AB84" r:id="rId11" display="https://jakarta.ee/specifications/enterprise-beans/" xr:uid="{704C23F0-9669-4135-B37D-FF9FAF28013A}"/>
+    <hyperlink ref="AB85" r:id="rId12" display="https://jakarta.ee/specifications/xml-binding/" xr:uid="{72A38165-5E11-4AE4-A696-C0EDB438F3FC}"/>
+    <hyperlink ref="AB86" r:id="rId13" display="https://jakarta.ee/specifications/jsonb/" xr:uid="{0C3AD5D6-3AFC-4F21-8554-C2193029568C}"/>
+    <hyperlink ref="AB87" r:id="rId14" display="https://jakarta.ee/specifications/jsonp/" xr:uid="{C91A89E6-4BB2-4045-AAFF-4A88EACA4FE5}"/>
+    <hyperlink ref="AB88" r:id="rId15" display="https://jakarta.ee/specifications/pages/" xr:uid="{E897019C-0949-48DE-8AA1-C7CAA399C7DE}"/>
+    <hyperlink ref="AB89" r:id="rId16" display="https://jakarta.ee/specifications/xml-web-services/" xr:uid="{BEBFEE85-BD91-44D7-BB2A-683DD7731328}"/>
+    <hyperlink ref="AB90" r:id="rId17" display="https://jakarta.ee/specifications/restful-ws/" xr:uid="{02390528-EB8B-4E6A-B1E9-9B563A6E8657}"/>
+    <hyperlink ref="AB91" r:id="rId18" display="https://jakarta.ee/specifications/tags/" xr:uid="{429F9649-389A-4EB4-A123-299AE69673C7}"/>
+    <hyperlink ref="AB92" r:id="rId19" display="https://jakarta.ee/specifications/cdi/" xr:uid="{0CBA927F-33E0-472C-B599-04E03CFEE5F6}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId27"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId20"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;C- &amp;P -</oddFooter>
   </headerFooter>
@@ -12644,7 +12298,7 @@
     <brk id="47" max="34" man="1"/>
     <brk id="67" max="34" man="1"/>
   </rowBreaks>
-  <drawing r:id="rId28"/>
+  <drawing r:id="rId21"/>
 </worksheet>
 </file>
 
@@ -12654,60 +12308,60 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.36328125" style="10" customWidth="1"/>
-    <col min="2" max="2" width="21.7265625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="25.6328125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="35.6328125" style="10" customWidth="1"/>
-    <col min="5" max="5" width="41.90625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="4.375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="21.75" style="10" customWidth="1"/>
+    <col min="3" max="3" width="25.625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="35.625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="41.875" style="10" customWidth="1"/>
     <col min="6" max="6" width="3" style="12" customWidth="1"/>
-    <col min="7" max="7" width="25.6328125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="25.625" style="10" customWidth="1"/>
     <col min="8" max="10" width="3" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="32.453125" style="10" customWidth="1"/>
-    <col min="12" max="12" width="1.6328125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="32.5" style="10" customWidth="1"/>
+    <col min="12" max="12" width="1.625" style="10" customWidth="1"/>
     <col min="13" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="146" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A1" s="158" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="158" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="159" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="146" t="s">
+      <c r="D1" s="158" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="146" t="s">
+      <c r="E1" s="158" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="146" t="s">
+      <c r="F1" s="158" t="s">
         <v>231</v>
       </c>
-      <c r="G1" s="146" t="s">
+      <c r="G1" s="158" t="s">
         <v>224</v>
       </c>
-      <c r="H1" s="146" t="s">
+      <c r="H1" s="158" t="s">
         <v>102</v>
       </c>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146" t="s">
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="146"/>
-      <c r="B2" s="146"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="148"/>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2" s="158"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="160"/>
       <c r="H2" s="63" t="s">
         <v>218</v>
       </c>
@@ -12717,9 +12371,9 @@
       <c r="J2" s="63" t="s">
         <v>220</v>
       </c>
-      <c r="K2" s="146"/>
-    </row>
-    <row r="3" spans="1:11" ht="99" x14ac:dyDescent="0.2">
+      <c r="K2" s="158"/>
+    </row>
+    <row r="3" spans="1:11" ht="101.25" x14ac:dyDescent="0.15">
       <c r="A3" s="57" t="s">
         <v>31</v>
       </c>
@@ -12752,7 +12406,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="191.25" x14ac:dyDescent="0.15">
       <c r="A4" s="57" t="s">
         <v>31</v>
       </c>
@@ -12785,7 +12439,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="44" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.15">
       <c r="A5" s="57" t="s">
         <v>31</v>
       </c>
@@ -12818,7 +12472,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="33.75" x14ac:dyDescent="0.15">
       <c r="A6" s="57" t="s">
         <v>31</v>
       </c>
@@ -12849,7 +12503,7 @@
       </c>
       <c r="K6" s="57"/>
     </row>
-    <row r="7" spans="1:11" ht="165" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="157.5" x14ac:dyDescent="0.15">
       <c r="A7" s="57" t="s">
         <v>31</v>
       </c>
@@ -12884,7 +12538,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="55" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="56.25" x14ac:dyDescent="0.15">
       <c r="A8" s="57" t="s">
         <v>31</v>
       </c>
@@ -12919,7 +12573,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="372.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="372.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="57" t="s">
         <v>31</v>
       </c>
@@ -12954,7 +12608,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="44" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.15">
       <c r="A10" s="57" t="s">
         <v>31</v>
       </c>
@@ -12989,7 +12643,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="330" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="337.5" x14ac:dyDescent="0.15">
       <c r="A11" s="57" t="s">
         <v>31</v>
       </c>
@@ -13022,7 +12676,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="57" t="s">
         <v>31</v>
       </c>
@@ -13055,7 +12709,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="44" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.15">
       <c r="A13" s="57" t="s">
         <v>32</v>
       </c>
@@ -13086,7 +12740,7 @@
       </c>
       <c r="K13" s="57"/>
     </row>
-    <row r="14" spans="1:11" ht="66" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A14" s="57" t="s">
         <v>32</v>
       </c>
@@ -13117,7 +12771,7 @@
       </c>
       <c r="K14" s="57"/>
     </row>
-    <row r="15" spans="1:11" ht="110" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="101.25" x14ac:dyDescent="0.15">
       <c r="A15" s="57" t="s">
         <v>32</v>
       </c>
@@ -13150,7 +12804,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="77" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="78.75" x14ac:dyDescent="0.15">
       <c r="A16" s="57" t="s">
         <v>32</v>
       </c>
@@ -13181,7 +12835,7 @@
       </c>
       <c r="K16" s="57"/>
     </row>
-    <row r="17" spans="1:11" ht="143" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="146.25" x14ac:dyDescent="0.15">
       <c r="A17" s="57" t="s">
         <v>32</v>
       </c>
@@ -13211,10 +12865,10 @@
         <v>116</v>
       </c>
       <c r="K17" s="57" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="154" x14ac:dyDescent="0.2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="157.5" x14ac:dyDescent="0.15">
       <c r="A18" s="57" t="s">
         <v>32</v>
       </c>
@@ -13247,7 +12901,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="154" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="157.5" x14ac:dyDescent="0.15">
       <c r="A19" s="57" t="s">
         <v>32</v>
       </c>
@@ -13280,7 +12934,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="88" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="90" x14ac:dyDescent="0.15">
       <c r="A20" s="57" t="s">
         <v>32</v>
       </c>
@@ -13311,7 +12965,7 @@
       </c>
       <c r="K20" s="57"/>
     </row>
-    <row r="21" spans="1:11" ht="121" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="123.75" x14ac:dyDescent="0.15">
       <c r="A21" s="57" t="s">
         <v>32</v>
       </c>
@@ -13344,7 +12998,7 @@
       </c>
       <c r="K21" s="57"/>
     </row>
-    <row r="22" spans="1:11" ht="270.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="270.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="57" t="s">
         <v>32</v>
       </c>
@@ -13379,7 +13033,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="121" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="123.75" x14ac:dyDescent="0.15">
       <c r="A23" s="57" t="s">
         <v>32</v>
       </c>
@@ -13414,7 +13068,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="77" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="78.75" x14ac:dyDescent="0.15">
       <c r="A24" s="57" t="s">
         <v>32</v>
       </c>
@@ -13449,7 +13103,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="55" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="56.25" x14ac:dyDescent="0.15">
       <c r="A25" s="57" t="s">
         <v>32</v>
       </c>
@@ -13484,7 +13138,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="44" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.15">
       <c r="A26" s="57" t="s">
         <v>32</v>
       </c>
@@ -13519,7 +13173,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="88" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="90" x14ac:dyDescent="0.15">
       <c r="A27" s="57" t="s">
         <v>193</v>
       </c>
@@ -13552,7 +13206,7 @@
       </c>
       <c r="K27" s="57"/>
     </row>
-    <row r="28" spans="1:11" ht="275" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="281.25" x14ac:dyDescent="0.15">
       <c r="A28" s="57" t="s">
         <v>63</v>
       </c>
@@ -13572,7 +13226,7 @@
         <v>335</v>
       </c>
       <c r="G28" s="57" t="s">
-        <v>424</v>
+        <v>397</v>
       </c>
       <c r="H28" s="59" t="s">
         <v>308</v>
@@ -13587,7 +13241,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="275" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="281.25" x14ac:dyDescent="0.15">
       <c r="A29" s="57" t="s">
         <v>192</v>
       </c>
@@ -13620,7 +13274,7 @@
       </c>
       <c r="K29" s="57"/>
     </row>
-    <row r="30" spans="1:11" ht="264" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="270" x14ac:dyDescent="0.15">
       <c r="A30" s="57" t="s">
         <v>193</v>
       </c>
@@ -13653,7 +13307,7 @@
       </c>
       <c r="K30" s="57"/>
     </row>
-    <row r="31" spans="1:11" ht="77" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="78.75" x14ac:dyDescent="0.15">
       <c r="A31" s="57" t="s">
         <v>193</v>
       </c>
@@ -13684,7 +13338,7 @@
       </c>
       <c r="K31" s="57"/>
     </row>
-    <row r="32" spans="1:11" ht="55" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="56.25" x14ac:dyDescent="0.15">
       <c r="A32" s="57" t="s">
         <v>194</v>
       </c>
@@ -13715,7 +13369,7 @@
       </c>
       <c r="K32" s="57"/>
     </row>
-    <row r="33" spans="1:11" ht="33" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="33.75" x14ac:dyDescent="0.15">
       <c r="A33" s="57" t="s">
         <v>194</v>
       </c>
@@ -13750,7 +13404,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="143" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="135" x14ac:dyDescent="0.15">
       <c r="A34" s="57" t="s">
         <v>194</v>
       </c>
@@ -13783,7 +13437,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="121" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="112.5" x14ac:dyDescent="0.15">
       <c r="A35" s="57" t="s">
         <v>111</v>
       </c>
@@ -13814,7 +13468,7 @@
       </c>
       <c r="K35" s="57"/>
     </row>
-    <row r="36" spans="1:11" ht="121" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="112.5" x14ac:dyDescent="0.15">
       <c r="A36" s="57" t="s">
         <v>195</v>
       </c>
@@ -13845,7 +13499,7 @@
       </c>
       <c r="K36" s="57"/>
     </row>
-    <row r="37" spans="1:11" ht="121" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="123.75" x14ac:dyDescent="0.15">
       <c r="A37" s="57" t="s">
         <v>111</v>
       </c>
@@ -13876,7 +13530,7 @@
       </c>
       <c r="K37" s="57"/>
     </row>
-    <row r="38" spans="1:11" ht="33" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="33.75" x14ac:dyDescent="0.15">
       <c r="A38" s="57" t="s">
         <v>68</v>
       </c>
@@ -13911,7 +13565,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="143" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" ht="135" x14ac:dyDescent="0.15">
       <c r="A39" s="57" t="s">
         <v>196</v>
       </c>
@@ -13944,7 +13598,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="44" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="45" x14ac:dyDescent="0.15">
       <c r="A40" s="57" t="s">
         <v>197</v>
       </c>
@@ -13975,7 +13629,7 @@
       </c>
       <c r="K40" s="57"/>
     </row>
-    <row r="41" spans="1:11" ht="33" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="33.75" x14ac:dyDescent="0.15">
       <c r="A41" s="57" t="s">
         <v>33</v>
       </c>
@@ -14010,7 +13664,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="143" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="146.25" x14ac:dyDescent="0.15">
       <c r="A42" s="57" t="s">
         <v>33</v>
       </c>
@@ -14043,7 +13697,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="55" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" ht="56.25" x14ac:dyDescent="0.15">
       <c r="A43" s="57" t="s">
         <v>99</v>
       </c>
@@ -14076,7 +13730,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="88" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" ht="90" x14ac:dyDescent="0.15">
       <c r="A44" s="57" t="s">
         <v>99</v>
       </c>
@@ -14109,7 +13763,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="143" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" ht="135" x14ac:dyDescent="0.15">
       <c r="A45" s="57" t="s">
         <v>99</v>
       </c>
@@ -14142,7 +13796,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="143" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" ht="135" x14ac:dyDescent="0.15">
       <c r="A46" s="57" t="s">
         <v>99</v>
       </c>
@@ -14177,7 +13831,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="165" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" ht="168.75" x14ac:dyDescent="0.15">
       <c r="A47" s="57" t="s">
         <v>99</v>
       </c>
@@ -14210,7 +13864,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="88" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="90" x14ac:dyDescent="0.15">
       <c r="A48" s="57" t="s">
         <v>99</v>
       </c>
@@ -14243,7 +13897,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="77" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="78.75" x14ac:dyDescent="0.15">
       <c r="A49" s="57" t="s">
         <v>99</v>
       </c>

--- a/010_開発プロセス標準/Nablarchを使用したシステム開発における標準WBS.xlsx
+++ b/010_開発プロセス標準/Nablarchを使用したシステム開発における標準WBS.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA2247B-15D3-43F4-A9BA-875D23CA9FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8801ECF9-3A4F-4F32-9F67-E8C2A424BD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3240" yWindow="2445" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="14" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="409">
   <si>
     <t xml:space="preserve">データベース論理設計
 </t>
@@ -4741,16 +4741,6 @@
   </si>
   <si>
     <t>Jakarta Contexts and Dependency Injection</t>
-  </si>
-  <si>
-    <t>画面イメージはHTMLで作成すること。</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve">プログラミング・単体テストガイド
@@ -5504,6 +5494,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="31" fontId="9" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5546,6 +5539,36 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -5758,39 +5781,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -6695,9 +6685,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6735,9 +6725,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6770,26 +6760,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6822,26 +6795,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7059,7 +7015,7 @@
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
       <c r="J23" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7071,12 +7027,12 @@
       <c r="F25" s="17"/>
       <c r="G25" s="17"/>
       <c r="H25" s="17"/>
-      <c r="I25" s="76">
+      <c r="I25" s="77">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
         <v>45461</v>
       </c>
-      <c r="J25" s="76"/>
-      <c r="K25" s="76"/>
+      <c r="J25" s="77"/>
+      <c r="K25" s="77"/>
     </row>
     <row r="26" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F26" s="17"/>
@@ -7670,55 +7626,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="121" t="s">
         <v>279</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="119" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="130" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="128" t="s">
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="139" t="s">
         <v>291</v>
       </c>
-      <c r="T1" s="129"/>
-      <c r="U1" s="129"/>
-      <c r="V1" s="129"/>
-      <c r="W1" s="129"/>
-      <c r="X1" s="129"/>
-      <c r="Y1" s="129"/>
-      <c r="Z1" s="130"/>
-      <c r="AA1" s="110" t="s">
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
+      <c r="Y1" s="140"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="121" t="s">
         <v>280</v>
       </c>
-      <c r="AB1" s="112"/>
-      <c r="AC1" s="137" t="str">
+      <c r="AB1" s="123"/>
+      <c r="AC1" s="148" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="138"/>
-      <c r="AE1" s="138"/>
-      <c r="AF1" s="139"/>
-      <c r="AG1" s="104">
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="150"/>
+      <c r="AG1" s="115">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="106"/>
+      <c r="AH1" s="116"/>
+      <c r="AI1" s="117"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="2"/>
@@ -7726,51 +7682,51 @@
       <c r="AN1" s="3"/>
     </row>
     <row r="2" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="121" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="115"/>
-      <c r="O2" s="122"/>
-      <c r="P2" s="123"/>
-      <c r="Q2" s="123"/>
-      <c r="R2" s="124"/>
-      <c r="S2" s="131"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="132"/>
-      <c r="W2" s="132"/>
-      <c r="X2" s="132"/>
-      <c r="Y2" s="132"/>
-      <c r="Z2" s="133"/>
-      <c r="AA2" s="110" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="133"/>
+      <c r="P2" s="134"/>
+      <c r="Q2" s="134"/>
+      <c r="R2" s="135"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="143"/>
+      <c r="U2" s="143"/>
+      <c r="V2" s="143"/>
+      <c r="W2" s="143"/>
+      <c r="X2" s="143"/>
+      <c r="Y2" s="143"/>
+      <c r="Z2" s="144"/>
+      <c r="AA2" s="121" t="s">
         <v>282</v>
       </c>
-      <c r="AB2" s="112"/>
-      <c r="AC2" s="116" t="str">
+      <c r="AB2" s="123"/>
+      <c r="AC2" s="127" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="117"/>
-      <c r="AE2" s="117"/>
-      <c r="AF2" s="118"/>
-      <c r="AG2" s="104">
+      <c r="AD2" s="128"/>
+      <c r="AE2" s="128"/>
+      <c r="AF2" s="129"/>
+      <c r="AG2" s="115">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>45461</v>
       </c>
-      <c r="AH2" s="105"/>
-      <c r="AI2" s="106"/>
+      <c r="AH2" s="116"/>
+      <c r="AI2" s="117"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
@@ -7778,43 +7734,43 @@
       <c r="AN2" s="2"/>
     </row>
     <row r="3" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="110" t="s">
+      <c r="A3" s="121" t="s">
         <v>283</v>
       </c>
-      <c r="B3" s="111"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="125"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="127"/>
-      <c r="S3" s="134"/>
-      <c r="T3" s="135"/>
-      <c r="U3" s="135"/>
-      <c r="V3" s="135"/>
-      <c r="W3" s="135"/>
-      <c r="X3" s="135"/>
-      <c r="Y3" s="135"/>
-      <c r="Z3" s="136"/>
-      <c r="AA3" s="110"/>
-      <c r="AB3" s="112"/>
-      <c r="AC3" s="137"/>
-      <c r="AD3" s="138"/>
-      <c r="AE3" s="138"/>
-      <c r="AF3" s="139"/>
-      <c r="AG3" s="104"/>
-      <c r="AH3" s="105"/>
-      <c r="AI3" s="106"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="137"/>
+      <c r="Q3" s="137"/>
+      <c r="R3" s="138"/>
+      <c r="S3" s="145"/>
+      <c r="T3" s="146"/>
+      <c r="U3" s="146"/>
+      <c r="V3" s="146"/>
+      <c r="W3" s="146"/>
+      <c r="X3" s="146"/>
+      <c r="Y3" s="146"/>
+      <c r="Z3" s="147"/>
+      <c r="AA3" s="121"/>
+      <c r="AB3" s="123"/>
+      <c r="AC3" s="148"/>
+      <c r="AD3" s="149"/>
+      <c r="AE3" s="149"/>
+      <c r="AF3" s="150"/>
+      <c r="AG3" s="115"/>
+      <c r="AH3" s="116"/>
+      <c r="AI3" s="117"/>
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
@@ -7851,1078 +7807,1078 @@
       <c r="A7" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="B7" s="107" t="s">
+      <c r="B7" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="C7" s="108"/>
-      <c r="D7" s="107" t="s">
+      <c r="C7" s="119"/>
+      <c r="D7" s="118" t="s">
         <v>187</v>
       </c>
-      <c r="E7" s="109"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="107" t="s">
+      <c r="E7" s="120"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="H7" s="109"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="107" t="s">
+      <c r="H7" s="120"/>
+      <c r="I7" s="119"/>
+      <c r="J7" s="118" t="s">
         <v>285</v>
       </c>
-      <c r="K7" s="109"/>
-      <c r="L7" s="109"/>
-      <c r="M7" s="109"/>
-      <c r="N7" s="109"/>
-      <c r="O7" s="109"/>
-      <c r="P7" s="108"/>
-      <c r="Q7" s="107" t="s">
+      <c r="K7" s="120"/>
+      <c r="L7" s="120"/>
+      <c r="M7" s="120"/>
+      <c r="N7" s="120"/>
+      <c r="O7" s="120"/>
+      <c r="P7" s="119"/>
+      <c r="Q7" s="118" t="s">
         <v>189</v>
       </c>
-      <c r="R7" s="109"/>
-      <c r="S7" s="109"/>
-      <c r="T7" s="109"/>
-      <c r="U7" s="109"/>
-      <c r="V7" s="109"/>
-      <c r="W7" s="109"/>
-      <c r="X7" s="109"/>
-      <c r="Y7" s="109"/>
-      <c r="Z7" s="109"/>
-      <c r="AA7" s="109"/>
-      <c r="AB7" s="109"/>
-      <c r="AC7" s="109"/>
-      <c r="AD7" s="109"/>
-      <c r="AE7" s="108"/>
-      <c r="AF7" s="107" t="s">
+      <c r="R7" s="120"/>
+      <c r="S7" s="120"/>
+      <c r="T7" s="120"/>
+      <c r="U7" s="120"/>
+      <c r="V7" s="120"/>
+      <c r="W7" s="120"/>
+      <c r="X7" s="120"/>
+      <c r="Y7" s="120"/>
+      <c r="Z7" s="120"/>
+      <c r="AA7" s="120"/>
+      <c r="AB7" s="120"/>
+      <c r="AC7" s="120"/>
+      <c r="AD7" s="120"/>
+      <c r="AE7" s="119"/>
+      <c r="AF7" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AG7" s="109"/>
-      <c r="AH7" s="109"/>
-      <c r="AI7" s="108"/>
+      <c r="AG7" s="120"/>
+      <c r="AH7" s="120"/>
+      <c r="AI7" s="119"/>
     </row>
     <row r="8" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="90" t="s">
+      <c r="B8" s="101" t="s">
         <v>286</v>
       </c>
-      <c r="C8" s="91"/>
-      <c r="D8" s="92">
+      <c r="C8" s="102"/>
+      <c r="D8" s="103">
         <v>43336</v>
       </c>
-      <c r="E8" s="93"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="95" t="s">
+      <c r="E8" s="104"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="106" t="s">
         <v>287</v>
       </c>
-      <c r="H8" s="96"/>
-      <c r="I8" s="97"/>
-      <c r="J8" s="98" t="s">
+      <c r="H8" s="107"/>
+      <c r="I8" s="108"/>
+      <c r="J8" s="109" t="s">
         <v>288</v>
       </c>
-      <c r="K8" s="99"/>
-      <c r="L8" s="99"/>
-      <c r="M8" s="99"/>
-      <c r="N8" s="99"/>
-      <c r="O8" s="99"/>
-      <c r="P8" s="100"/>
-      <c r="Q8" s="101" t="s">
+      <c r="K8" s="110"/>
+      <c r="L8" s="110"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="110"/>
+      <c r="O8" s="110"/>
+      <c r="P8" s="111"/>
+      <c r="Q8" s="112" t="s">
         <v>289</v>
       </c>
-      <c r="R8" s="102"/>
-      <c r="S8" s="102"/>
-      <c r="T8" s="102"/>
-      <c r="U8" s="102"/>
-      <c r="V8" s="102"/>
-      <c r="W8" s="102"/>
-      <c r="X8" s="102"/>
-      <c r="Y8" s="102"/>
-      <c r="Z8" s="102"/>
-      <c r="AA8" s="102"/>
-      <c r="AB8" s="102"/>
-      <c r="AC8" s="102"/>
-      <c r="AD8" s="102"/>
-      <c r="AE8" s="103"/>
-      <c r="AF8" s="98" t="s">
+      <c r="R8" s="113"/>
+      <c r="S8" s="113"/>
+      <c r="T8" s="113"/>
+      <c r="U8" s="113"/>
+      <c r="V8" s="113"/>
+      <c r="W8" s="113"/>
+      <c r="X8" s="113"/>
+      <c r="Y8" s="113"/>
+      <c r="Z8" s="113"/>
+      <c r="AA8" s="113"/>
+      <c r="AB8" s="113"/>
+      <c r="AC8" s="113"/>
+      <c r="AD8" s="113"/>
+      <c r="AE8" s="114"/>
+      <c r="AF8" s="109" t="s">
         <v>290</v>
       </c>
-      <c r="AG8" s="99"/>
-      <c r="AH8" s="99"/>
-      <c r="AI8" s="100"/>
+      <c r="AG8" s="110"/>
+      <c r="AH8" s="110"/>
+      <c r="AI8" s="111"/>
     </row>
     <row r="9" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="29">
         <v>2</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="78" t="s">
         <v>355</v>
       </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="79">
+      <c r="C9" s="79"/>
+      <c r="D9" s="80">
         <v>43896</v>
       </c>
-      <c r="E9" s="80"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="79" t="s">
+      <c r="E9" s="81"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="80" t="s">
         <v>337</v>
       </c>
-      <c r="H9" s="82"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="83" t="s">
+      <c r="H9" s="83"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="84" t="s">
         <v>338</v>
       </c>
-      <c r="K9" s="84"/>
-      <c r="L9" s="84"/>
-      <c r="M9" s="84"/>
-      <c r="N9" s="84"/>
-      <c r="O9" s="84"/>
-      <c r="P9" s="85"/>
-      <c r="Q9" s="86" t="s">
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="85"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="85"/>
+      <c r="P9" s="86"/>
+      <c r="Q9" s="87" t="s">
         <v>353</v>
       </c>
-      <c r="R9" s="87"/>
-      <c r="S9" s="87"/>
-      <c r="T9" s="87"/>
-      <c r="U9" s="87"/>
-      <c r="V9" s="87"/>
-      <c r="W9" s="87"/>
-      <c r="X9" s="87"/>
-      <c r="Y9" s="87"/>
-      <c r="Z9" s="87"/>
-      <c r="AA9" s="87"/>
-      <c r="AB9" s="87"/>
-      <c r="AC9" s="87"/>
-      <c r="AD9" s="87"/>
-      <c r="AE9" s="88"/>
-      <c r="AF9" s="83" t="s">
+      <c r="R9" s="88"/>
+      <c r="S9" s="88"/>
+      <c r="T9" s="88"/>
+      <c r="U9" s="88"/>
+      <c r="V9" s="88"/>
+      <c r="W9" s="88"/>
+      <c r="X9" s="88"/>
+      <c r="Y9" s="88"/>
+      <c r="Z9" s="88"/>
+      <c r="AA9" s="88"/>
+      <c r="AB9" s="88"/>
+      <c r="AC9" s="88"/>
+      <c r="AD9" s="88"/>
+      <c r="AE9" s="89"/>
+      <c r="AF9" s="84" t="s">
         <v>290</v>
       </c>
-      <c r="AG9" s="84"/>
-      <c r="AH9" s="84"/>
-      <c r="AI9" s="85"/>
+      <c r="AG9" s="85"/>
+      <c r="AH9" s="85"/>
+      <c r="AI9" s="86"/>
     </row>
     <row r="10" spans="1:40" s="9" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="29">
         <v>3</v>
       </c>
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="78" t="s">
         <v>356</v>
       </c>
-      <c r="C10" s="78"/>
-      <c r="D10" s="79">
+      <c r="C10" s="79"/>
+      <c r="D10" s="80">
         <v>44455</v>
       </c>
-      <c r="E10" s="80"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="79" t="s">
+      <c r="E10" s="81"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="80" t="s">
         <v>337</v>
       </c>
-      <c r="H10" s="82"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="83" t="s">
+      <c r="H10" s="83"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="84" t="s">
         <v>338</v>
       </c>
-      <c r="K10" s="84"/>
-      <c r="L10" s="84"/>
-      <c r="M10" s="84"/>
-      <c r="N10" s="84"/>
-      <c r="O10" s="84"/>
-      <c r="P10" s="85"/>
-      <c r="Q10" s="86" t="s">
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="86"/>
+      <c r="Q10" s="87" t="s">
         <v>357</v>
       </c>
-      <c r="R10" s="87"/>
-      <c r="S10" s="87"/>
-      <c r="T10" s="87"/>
-      <c r="U10" s="87"/>
-      <c r="V10" s="87"/>
-      <c r="W10" s="87"/>
-      <c r="X10" s="87"/>
-      <c r="Y10" s="87"/>
-      <c r="Z10" s="87"/>
-      <c r="AA10" s="87"/>
-      <c r="AB10" s="87"/>
-      <c r="AC10" s="87"/>
-      <c r="AD10" s="87"/>
-      <c r="AE10" s="88"/>
-      <c r="AF10" s="83" t="s">
+      <c r="R10" s="88"/>
+      <c r="S10" s="88"/>
+      <c r="T10" s="88"/>
+      <c r="U10" s="88"/>
+      <c r="V10" s="88"/>
+      <c r="W10" s="88"/>
+      <c r="X10" s="88"/>
+      <c r="Y10" s="88"/>
+      <c r="Z10" s="88"/>
+      <c r="AA10" s="88"/>
+      <c r="AB10" s="88"/>
+      <c r="AC10" s="88"/>
+      <c r="AD10" s="88"/>
+      <c r="AE10" s="89"/>
+      <c r="AF10" s="84" t="s">
         <v>290</v>
       </c>
-      <c r="AG10" s="84"/>
-      <c r="AH10" s="84"/>
-      <c r="AI10" s="85"/>
+      <c r="AG10" s="85"/>
+      <c r="AH10" s="85"/>
+      <c r="AI10" s="86"/>
     </row>
     <row r="11" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="161">
+      <c r="A11" s="76">
         <v>4</v>
       </c>
-      <c r="B11" s="162" t="s">
+      <c r="B11" s="96" t="s">
+        <v>403</v>
+      </c>
+      <c r="C11" s="97"/>
+      <c r="D11" s="98">
+        <v>45461</v>
+      </c>
+      <c r="E11" s="99"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="78" t="s">
+        <v>406</v>
+      </c>
+      <c r="H11" s="83"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="84" t="s">
         <v>404</v>
       </c>
-      <c r="C11" s="163"/>
-      <c r="D11" s="164">
-        <v>45461</v>
-      </c>
-      <c r="E11" s="165"/>
-      <c r="F11" s="166"/>
-      <c r="G11" s="77" t="s">
-        <v>407</v>
-      </c>
-      <c r="H11" s="82"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="83" t="s">
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="85"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="85"/>
+      <c r="P11" s="86"/>
+      <c r="Q11" s="87" t="s">
         <v>405</v>
       </c>
-      <c r="K11" s="84"/>
-      <c r="L11" s="84"/>
-      <c r="M11" s="84"/>
-      <c r="N11" s="84"/>
-      <c r="O11" s="84"/>
-      <c r="P11" s="85"/>
-      <c r="Q11" s="86" t="s">
-        <v>406</v>
-      </c>
-      <c r="R11" s="87"/>
-      <c r="S11" s="87"/>
-      <c r="T11" s="87"/>
-      <c r="U11" s="87"/>
-      <c r="V11" s="87"/>
-      <c r="W11" s="87"/>
-      <c r="X11" s="87"/>
-      <c r="Y11" s="87"/>
-      <c r="Z11" s="87"/>
-      <c r="AA11" s="87"/>
-      <c r="AB11" s="87"/>
-      <c r="AC11" s="87"/>
-      <c r="AD11" s="87"/>
-      <c r="AE11" s="88"/>
-      <c r="AF11" s="83" t="s">
+      <c r="R11" s="88"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="88"/>
+      <c r="U11" s="88"/>
+      <c r="V11" s="88"/>
+      <c r="W11" s="88"/>
+      <c r="X11" s="88"/>
+      <c r="Y11" s="88"/>
+      <c r="Z11" s="88"/>
+      <c r="AA11" s="88"/>
+      <c r="AB11" s="88"/>
+      <c r="AC11" s="88"/>
+      <c r="AD11" s="88"/>
+      <c r="AE11" s="89"/>
+      <c r="AF11" s="84" t="s">
         <v>290</v>
       </c>
-      <c r="AG11" s="84"/>
-      <c r="AH11" s="84"/>
-      <c r="AI11" s="85"/>
+      <c r="AG11" s="85"/>
+      <c r="AH11" s="85"/>
+      <c r="AI11" s="86"/>
     </row>
     <row r="12" spans="1:40" s="9" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="28"/>
-      <c r="B12" s="167"/>
-      <c r="C12" s="168"/>
-      <c r="D12" s="169"/>
-      <c r="E12" s="170"/>
-      <c r="F12" s="171"/>
-      <c r="G12" s="77" t="s">
+      <c r="B12" s="91"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="78" t="s">
         <v>337</v>
       </c>
-      <c r="H12" s="82"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="86" t="s">
+      <c r="H12" s="83"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="87" t="s">
+        <v>407</v>
+      </c>
+      <c r="K12" s="85"/>
+      <c r="L12" s="85"/>
+      <c r="M12" s="85"/>
+      <c r="N12" s="85"/>
+      <c r="O12" s="85"/>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="87" t="s">
         <v>408</v>
       </c>
-      <c r="K12" s="84"/>
-      <c r="L12" s="84"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="84"/>
-      <c r="O12" s="84"/>
-      <c r="P12" s="85"/>
-      <c r="Q12" s="86" t="s">
-        <v>409</v>
-      </c>
-      <c r="R12" s="87"/>
-      <c r="S12" s="87"/>
-      <c r="T12" s="87"/>
-      <c r="U12" s="87"/>
-      <c r="V12" s="87"/>
-      <c r="W12" s="87"/>
-      <c r="X12" s="87"/>
-      <c r="Y12" s="87"/>
-      <c r="Z12" s="87"/>
-      <c r="AA12" s="87"/>
-      <c r="AB12" s="87"/>
-      <c r="AC12" s="87"/>
-      <c r="AD12" s="87"/>
-      <c r="AE12" s="88"/>
-      <c r="AF12" s="83" t="s">
+      <c r="R12" s="88"/>
+      <c r="S12" s="88"/>
+      <c r="T12" s="88"/>
+      <c r="U12" s="88"/>
+      <c r="V12" s="88"/>
+      <c r="W12" s="88"/>
+      <c r="X12" s="88"/>
+      <c r="Y12" s="88"/>
+      <c r="Z12" s="88"/>
+      <c r="AA12" s="88"/>
+      <c r="AB12" s="88"/>
+      <c r="AC12" s="88"/>
+      <c r="AD12" s="88"/>
+      <c r="AE12" s="89"/>
+      <c r="AF12" s="84" t="s">
         <v>290</v>
       </c>
-      <c r="AG12" s="84"/>
-      <c r="AH12" s="84"/>
-      <c r="AI12" s="85"/>
+      <c r="AG12" s="85"/>
+      <c r="AH12" s="85"/>
+      <c r="AI12" s="86"/>
     </row>
     <row r="13" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="29"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="84"/>
-      <c r="L13" s="84"/>
-      <c r="M13" s="84"/>
-      <c r="N13" s="84"/>
-      <c r="O13" s="84"/>
-      <c r="P13" s="85"/>
-      <c r="Q13" s="86"/>
-      <c r="R13" s="87"/>
-      <c r="S13" s="87"/>
-      <c r="T13" s="87"/>
-      <c r="U13" s="87"/>
-      <c r="V13" s="87"/>
-      <c r="W13" s="87"/>
-      <c r="X13" s="87"/>
-      <c r="Y13" s="87"/>
-      <c r="Z13" s="87"/>
-      <c r="AA13" s="87"/>
-      <c r="AB13" s="87"/>
-      <c r="AC13" s="87"/>
-      <c r="AD13" s="87"/>
-      <c r="AE13" s="88"/>
-      <c r="AF13" s="83"/>
-      <c r="AG13" s="84"/>
-      <c r="AH13" s="84"/>
-      <c r="AI13" s="85"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
+      <c r="M13" s="85"/>
+      <c r="N13" s="85"/>
+      <c r="O13" s="85"/>
+      <c r="P13" s="86"/>
+      <c r="Q13" s="87"/>
+      <c r="R13" s="88"/>
+      <c r="S13" s="88"/>
+      <c r="T13" s="88"/>
+      <c r="U13" s="88"/>
+      <c r="V13" s="88"/>
+      <c r="W13" s="88"/>
+      <c r="X13" s="88"/>
+      <c r="Y13" s="88"/>
+      <c r="Z13" s="88"/>
+      <c r="AA13" s="88"/>
+      <c r="AB13" s="88"/>
+      <c r="AC13" s="88"/>
+      <c r="AD13" s="88"/>
+      <c r="AE13" s="89"/>
+      <c r="AF13" s="84"/>
+      <c r="AG13" s="85"/>
+      <c r="AH13" s="85"/>
+      <c r="AI13" s="86"/>
     </row>
     <row r="14" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="29"/>
-      <c r="B14" s="77"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="82"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="84"/>
-      <c r="L14" s="84"/>
-      <c r="M14" s="84"/>
-      <c r="N14" s="84"/>
-      <c r="O14" s="84"/>
-      <c r="P14" s="85"/>
-      <c r="Q14" s="86"/>
-      <c r="R14" s="87"/>
-      <c r="S14" s="87"/>
-      <c r="T14" s="87"/>
-      <c r="U14" s="87"/>
-      <c r="V14" s="87"/>
-      <c r="W14" s="87"/>
-      <c r="X14" s="87"/>
-      <c r="Y14" s="87"/>
-      <c r="Z14" s="87"/>
-      <c r="AA14" s="87"/>
-      <c r="AB14" s="87"/>
-      <c r="AC14" s="87"/>
-      <c r="AD14" s="87"/>
-      <c r="AE14" s="88"/>
-      <c r="AF14" s="83"/>
-      <c r="AG14" s="84"/>
-      <c r="AH14" s="84"/>
-      <c r="AI14" s="85"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="85"/>
+      <c r="L14" s="85"/>
+      <c r="M14" s="85"/>
+      <c r="N14" s="85"/>
+      <c r="O14" s="85"/>
+      <c r="P14" s="86"/>
+      <c r="Q14" s="87"/>
+      <c r="R14" s="88"/>
+      <c r="S14" s="88"/>
+      <c r="T14" s="88"/>
+      <c r="U14" s="88"/>
+      <c r="V14" s="88"/>
+      <c r="W14" s="88"/>
+      <c r="X14" s="88"/>
+      <c r="Y14" s="88"/>
+      <c r="Z14" s="88"/>
+      <c r="AA14" s="88"/>
+      <c r="AB14" s="88"/>
+      <c r="AC14" s="88"/>
+      <c r="AD14" s="88"/>
+      <c r="AE14" s="89"/>
+      <c r="AF14" s="84"/>
+      <c r="AG14" s="85"/>
+      <c r="AH14" s="85"/>
+      <c r="AI14" s="86"/>
     </row>
     <row r="15" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="29"/>
-      <c r="B15" s="77"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="81"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="82"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="84"/>
-      <c r="M15" s="84"/>
-      <c r="N15" s="84"/>
-      <c r="O15" s="84"/>
-      <c r="P15" s="85"/>
-      <c r="Q15" s="86"/>
-      <c r="R15" s="87"/>
-      <c r="S15" s="87"/>
-      <c r="T15" s="87"/>
-      <c r="U15" s="87"/>
-      <c r="V15" s="87"/>
-      <c r="W15" s="87"/>
-      <c r="X15" s="87"/>
-      <c r="Y15" s="87"/>
-      <c r="Z15" s="87"/>
-      <c r="AA15" s="87"/>
-      <c r="AB15" s="87"/>
-      <c r="AC15" s="87"/>
-      <c r="AD15" s="87"/>
-      <c r="AE15" s="88"/>
-      <c r="AF15" s="83"/>
-      <c r="AG15" s="84"/>
-      <c r="AH15" s="84"/>
-      <c r="AI15" s="85"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="85"/>
+      <c r="M15" s="85"/>
+      <c r="N15" s="85"/>
+      <c r="O15" s="85"/>
+      <c r="P15" s="86"/>
+      <c r="Q15" s="87"/>
+      <c r="R15" s="88"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="88"/>
+      <c r="U15" s="88"/>
+      <c r="V15" s="88"/>
+      <c r="W15" s="88"/>
+      <c r="X15" s="88"/>
+      <c r="Y15" s="88"/>
+      <c r="Z15" s="88"/>
+      <c r="AA15" s="88"/>
+      <c r="AB15" s="88"/>
+      <c r="AC15" s="88"/>
+      <c r="AD15" s="88"/>
+      <c r="AE15" s="89"/>
+      <c r="AF15" s="84"/>
+      <c r="AG15" s="85"/>
+      <c r="AH15" s="85"/>
+      <c r="AI15" s="86"/>
     </row>
     <row r="16" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="29"/>
-      <c r="B16" s="77"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="82"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="83"/>
-      <c r="K16" s="84"/>
-      <c r="L16" s="84"/>
-      <c r="M16" s="84"/>
-      <c r="N16" s="84"/>
-      <c r="O16" s="84"/>
-      <c r="P16" s="85"/>
-      <c r="Q16" s="86"/>
-      <c r="R16" s="87"/>
-      <c r="S16" s="87"/>
-      <c r="T16" s="87"/>
-      <c r="U16" s="87"/>
-      <c r="V16" s="87"/>
-      <c r="W16" s="87"/>
-      <c r="X16" s="87"/>
-      <c r="Y16" s="87"/>
-      <c r="Z16" s="87"/>
-      <c r="AA16" s="87"/>
-      <c r="AB16" s="87"/>
-      <c r="AC16" s="87"/>
-      <c r="AD16" s="87"/>
-      <c r="AE16" s="88"/>
-      <c r="AF16" s="83"/>
-      <c r="AG16" s="84"/>
-      <c r="AH16" s="84"/>
-      <c r="AI16" s="85"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="85"/>
+      <c r="L16" s="85"/>
+      <c r="M16" s="85"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="85"/>
+      <c r="P16" s="86"/>
+      <c r="Q16" s="87"/>
+      <c r="R16" s="88"/>
+      <c r="S16" s="88"/>
+      <c r="T16" s="88"/>
+      <c r="U16" s="88"/>
+      <c r="V16" s="88"/>
+      <c r="W16" s="88"/>
+      <c r="X16" s="88"/>
+      <c r="Y16" s="88"/>
+      <c r="Z16" s="88"/>
+      <c r="AA16" s="88"/>
+      <c r="AB16" s="88"/>
+      <c r="AC16" s="88"/>
+      <c r="AD16" s="88"/>
+      <c r="AE16" s="89"/>
+      <c r="AF16" s="84"/>
+      <c r="AG16" s="85"/>
+      <c r="AH16" s="85"/>
+      <c r="AI16" s="86"/>
     </row>
     <row r="17" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="29"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="82"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="83"/>
-      <c r="K17" s="84"/>
-      <c r="L17" s="84"/>
-      <c r="M17" s="84"/>
-      <c r="N17" s="84"/>
-      <c r="O17" s="84"/>
-      <c r="P17" s="85"/>
-      <c r="Q17" s="86"/>
-      <c r="R17" s="87"/>
-      <c r="S17" s="87"/>
-      <c r="T17" s="87"/>
-      <c r="U17" s="87"/>
-      <c r="V17" s="87"/>
-      <c r="W17" s="87"/>
-      <c r="X17" s="87"/>
-      <c r="Y17" s="87"/>
-      <c r="Z17" s="87"/>
-      <c r="AA17" s="87"/>
-      <c r="AB17" s="87"/>
-      <c r="AC17" s="87"/>
-      <c r="AD17" s="87"/>
-      <c r="AE17" s="88"/>
-      <c r="AF17" s="83"/>
-      <c r="AG17" s="84"/>
-      <c r="AH17" s="84"/>
-      <c r="AI17" s="85"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="85"/>
+      <c r="L17" s="85"/>
+      <c r="M17" s="85"/>
+      <c r="N17" s="85"/>
+      <c r="O17" s="85"/>
+      <c r="P17" s="86"/>
+      <c r="Q17" s="87"/>
+      <c r="R17" s="88"/>
+      <c r="S17" s="88"/>
+      <c r="T17" s="88"/>
+      <c r="U17" s="88"/>
+      <c r="V17" s="88"/>
+      <c r="W17" s="88"/>
+      <c r="X17" s="88"/>
+      <c r="Y17" s="88"/>
+      <c r="Z17" s="88"/>
+      <c r="AA17" s="88"/>
+      <c r="AB17" s="88"/>
+      <c r="AC17" s="88"/>
+      <c r="AD17" s="88"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="84"/>
+      <c r="AG17" s="85"/>
+      <c r="AH17" s="85"/>
+      <c r="AI17" s="86"/>
     </row>
     <row r="18" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="29"/>
-      <c r="B18" s="77"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="81"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="82"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="83"/>
-      <c r="K18" s="84"/>
-      <c r="L18" s="84"/>
-      <c r="M18" s="84"/>
-      <c r="N18" s="84"/>
-      <c r="O18" s="84"/>
-      <c r="P18" s="85"/>
-      <c r="Q18" s="86"/>
-      <c r="R18" s="87"/>
-      <c r="S18" s="87"/>
-      <c r="T18" s="87"/>
-      <c r="U18" s="87"/>
-      <c r="V18" s="87"/>
-      <c r="W18" s="87"/>
-      <c r="X18" s="87"/>
-      <c r="Y18" s="87"/>
-      <c r="Z18" s="87"/>
-      <c r="AA18" s="87"/>
-      <c r="AB18" s="87"/>
-      <c r="AC18" s="87"/>
-      <c r="AD18" s="87"/>
-      <c r="AE18" s="88"/>
-      <c r="AF18" s="83"/>
-      <c r="AG18" s="84"/>
-      <c r="AH18" s="84"/>
-      <c r="AI18" s="85"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="85"/>
+      <c r="M18" s="85"/>
+      <c r="N18" s="85"/>
+      <c r="O18" s="85"/>
+      <c r="P18" s="86"/>
+      <c r="Q18" s="87"/>
+      <c r="R18" s="88"/>
+      <c r="S18" s="88"/>
+      <c r="T18" s="88"/>
+      <c r="U18" s="88"/>
+      <c r="V18" s="88"/>
+      <c r="W18" s="88"/>
+      <c r="X18" s="88"/>
+      <c r="Y18" s="88"/>
+      <c r="Z18" s="88"/>
+      <c r="AA18" s="88"/>
+      <c r="AB18" s="88"/>
+      <c r="AC18" s="88"/>
+      <c r="AD18" s="88"/>
+      <c r="AE18" s="89"/>
+      <c r="AF18" s="84"/>
+      <c r="AG18" s="85"/>
+      <c r="AH18" s="85"/>
+      <c r="AI18" s="86"/>
     </row>
     <row r="19" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="29"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="81"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="82"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="83"/>
-      <c r="K19" s="84"/>
-      <c r="L19" s="84"/>
-      <c r="M19" s="84"/>
-      <c r="N19" s="84"/>
-      <c r="O19" s="84"/>
-      <c r="P19" s="85"/>
-      <c r="Q19" s="86"/>
-      <c r="R19" s="87"/>
-      <c r="S19" s="87"/>
-      <c r="T19" s="87"/>
-      <c r="U19" s="87"/>
-      <c r="V19" s="87"/>
-      <c r="W19" s="87"/>
-      <c r="X19" s="87"/>
-      <c r="Y19" s="87"/>
-      <c r="Z19" s="87"/>
-      <c r="AA19" s="87"/>
-      <c r="AB19" s="87"/>
-      <c r="AC19" s="87"/>
-      <c r="AD19" s="87"/>
-      <c r="AE19" s="88"/>
-      <c r="AF19" s="83"/>
-      <c r="AG19" s="84"/>
-      <c r="AH19" s="84"/>
-      <c r="AI19" s="85"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="85"/>
+      <c r="L19" s="85"/>
+      <c r="M19" s="85"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="85"/>
+      <c r="P19" s="86"/>
+      <c r="Q19" s="87"/>
+      <c r="R19" s="88"/>
+      <c r="S19" s="88"/>
+      <c r="T19" s="88"/>
+      <c r="U19" s="88"/>
+      <c r="V19" s="88"/>
+      <c r="W19" s="88"/>
+      <c r="X19" s="88"/>
+      <c r="Y19" s="88"/>
+      <c r="Z19" s="88"/>
+      <c r="AA19" s="88"/>
+      <c r="AB19" s="88"/>
+      <c r="AC19" s="88"/>
+      <c r="AD19" s="88"/>
+      <c r="AE19" s="89"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="85"/>
+      <c r="AH19" s="85"/>
+      <c r="AI19" s="86"/>
     </row>
     <row r="20" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="29"/>
-      <c r="B20" s="77"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="82"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="84"/>
-      <c r="L20" s="84"/>
-      <c r="M20" s="84"/>
-      <c r="N20" s="84"/>
-      <c r="O20" s="84"/>
-      <c r="P20" s="85"/>
-      <c r="Q20" s="86"/>
-      <c r="R20" s="87"/>
-      <c r="S20" s="87"/>
-      <c r="T20" s="87"/>
-      <c r="U20" s="87"/>
-      <c r="V20" s="87"/>
-      <c r="W20" s="87"/>
-      <c r="X20" s="87"/>
-      <c r="Y20" s="87"/>
-      <c r="Z20" s="87"/>
-      <c r="AA20" s="87"/>
-      <c r="AB20" s="87"/>
-      <c r="AC20" s="87"/>
-      <c r="AD20" s="87"/>
-      <c r="AE20" s="88"/>
-      <c r="AF20" s="83"/>
-      <c r="AG20" s="84"/>
-      <c r="AH20" s="84"/>
-      <c r="AI20" s="85"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="84"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="85"/>
+      <c r="M20" s="85"/>
+      <c r="N20" s="85"/>
+      <c r="O20" s="85"/>
+      <c r="P20" s="86"/>
+      <c r="Q20" s="87"/>
+      <c r="R20" s="88"/>
+      <c r="S20" s="88"/>
+      <c r="T20" s="88"/>
+      <c r="U20" s="88"/>
+      <c r="V20" s="88"/>
+      <c r="W20" s="88"/>
+      <c r="X20" s="88"/>
+      <c r="Y20" s="88"/>
+      <c r="Z20" s="88"/>
+      <c r="AA20" s="88"/>
+      <c r="AB20" s="88"/>
+      <c r="AC20" s="88"/>
+      <c r="AD20" s="88"/>
+      <c r="AE20" s="89"/>
+      <c r="AF20" s="84"/>
+      <c r="AG20" s="85"/>
+      <c r="AH20" s="85"/>
+      <c r="AI20" s="86"/>
     </row>
     <row r="21" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="29"/>
-      <c r="B21" s="77"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="82"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="83"/>
-      <c r="K21" s="84"/>
-      <c r="L21" s="84"/>
-      <c r="M21" s="84"/>
-      <c r="N21" s="84"/>
-      <c r="O21" s="84"/>
-      <c r="P21" s="85"/>
-      <c r="Q21" s="86"/>
-      <c r="R21" s="87"/>
-      <c r="S21" s="87"/>
-      <c r="T21" s="87"/>
-      <c r="U21" s="87"/>
-      <c r="V21" s="87"/>
-      <c r="W21" s="87"/>
-      <c r="X21" s="87"/>
-      <c r="Y21" s="87"/>
-      <c r="Z21" s="87"/>
-      <c r="AA21" s="87"/>
-      <c r="AB21" s="87"/>
-      <c r="AC21" s="87"/>
-      <c r="AD21" s="87"/>
-      <c r="AE21" s="88"/>
-      <c r="AF21" s="83"/>
-      <c r="AG21" s="84"/>
-      <c r="AH21" s="84"/>
-      <c r="AI21" s="85"/>
+      <c r="B21" s="78"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="85"/>
+      <c r="L21" s="85"/>
+      <c r="M21" s="85"/>
+      <c r="N21" s="85"/>
+      <c r="O21" s="85"/>
+      <c r="P21" s="86"/>
+      <c r="Q21" s="87"/>
+      <c r="R21" s="88"/>
+      <c r="S21" s="88"/>
+      <c r="T21" s="88"/>
+      <c r="U21" s="88"/>
+      <c r="V21" s="88"/>
+      <c r="W21" s="88"/>
+      <c r="X21" s="88"/>
+      <c r="Y21" s="88"/>
+      <c r="Z21" s="88"/>
+      <c r="AA21" s="88"/>
+      <c r="AB21" s="88"/>
+      <c r="AC21" s="88"/>
+      <c r="AD21" s="88"/>
+      <c r="AE21" s="89"/>
+      <c r="AF21" s="84"/>
+      <c r="AG21" s="85"/>
+      <c r="AH21" s="85"/>
+      <c r="AI21" s="86"/>
     </row>
     <row r="22" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="29"/>
-      <c r="B22" s="77"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="82"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="83"/>
-      <c r="K22" s="84"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="84"/>
-      <c r="N22" s="84"/>
-      <c r="O22" s="84"/>
-      <c r="P22" s="85"/>
-      <c r="Q22" s="86"/>
-      <c r="R22" s="87"/>
-      <c r="S22" s="87"/>
-      <c r="T22" s="87"/>
-      <c r="U22" s="87"/>
-      <c r="V22" s="87"/>
-      <c r="W22" s="87"/>
-      <c r="X22" s="87"/>
-      <c r="Y22" s="87"/>
-      <c r="Z22" s="87"/>
-      <c r="AA22" s="87"/>
-      <c r="AB22" s="87"/>
-      <c r="AC22" s="87"/>
-      <c r="AD22" s="87"/>
-      <c r="AE22" s="88"/>
-      <c r="AF22" s="83"/>
-      <c r="AG22" s="84"/>
-      <c r="AH22" s="84"/>
-      <c r="AI22" s="85"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="85"/>
+      <c r="L22" s="85"/>
+      <c r="M22" s="85"/>
+      <c r="N22" s="85"/>
+      <c r="O22" s="85"/>
+      <c r="P22" s="86"/>
+      <c r="Q22" s="87"/>
+      <c r="R22" s="88"/>
+      <c r="S22" s="88"/>
+      <c r="T22" s="88"/>
+      <c r="U22" s="88"/>
+      <c r="V22" s="88"/>
+      <c r="W22" s="88"/>
+      <c r="X22" s="88"/>
+      <c r="Y22" s="88"/>
+      <c r="Z22" s="88"/>
+      <c r="AA22" s="88"/>
+      <c r="AB22" s="88"/>
+      <c r="AC22" s="88"/>
+      <c r="AD22" s="88"/>
+      <c r="AE22" s="89"/>
+      <c r="AF22" s="84"/>
+      <c r="AG22" s="85"/>
+      <c r="AH22" s="85"/>
+      <c r="AI22" s="86"/>
     </row>
     <row r="23" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="29"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="82"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="84"/>
-      <c r="L23" s="84"/>
-      <c r="M23" s="84"/>
-      <c r="N23" s="84"/>
-      <c r="O23" s="84"/>
-      <c r="P23" s="85"/>
-      <c r="Q23" s="86"/>
-      <c r="R23" s="87"/>
-      <c r="S23" s="87"/>
-      <c r="T23" s="87"/>
-      <c r="U23" s="87"/>
-      <c r="V23" s="87"/>
-      <c r="W23" s="87"/>
-      <c r="X23" s="87"/>
-      <c r="Y23" s="87"/>
-      <c r="Z23" s="87"/>
-      <c r="AA23" s="87"/>
-      <c r="AB23" s="87"/>
-      <c r="AC23" s="87"/>
-      <c r="AD23" s="87"/>
-      <c r="AE23" s="88"/>
-      <c r="AF23" s="83"/>
-      <c r="AG23" s="84"/>
-      <c r="AH23" s="84"/>
-      <c r="AI23" s="85"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="85"/>
+      <c r="M23" s="85"/>
+      <c r="N23" s="85"/>
+      <c r="O23" s="85"/>
+      <c r="P23" s="86"/>
+      <c r="Q23" s="87"/>
+      <c r="R23" s="88"/>
+      <c r="S23" s="88"/>
+      <c r="T23" s="88"/>
+      <c r="U23" s="88"/>
+      <c r="V23" s="88"/>
+      <c r="W23" s="88"/>
+      <c r="X23" s="88"/>
+      <c r="Y23" s="88"/>
+      <c r="Z23" s="88"/>
+      <c r="AA23" s="88"/>
+      <c r="AB23" s="88"/>
+      <c r="AC23" s="88"/>
+      <c r="AD23" s="88"/>
+      <c r="AE23" s="89"/>
+      <c r="AF23" s="84"/>
+      <c r="AG23" s="85"/>
+      <c r="AH23" s="85"/>
+      <c r="AI23" s="86"/>
     </row>
     <row r="24" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="29"/>
-      <c r="B24" s="77"/>
-      <c r="C24" s="78"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="81"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="82"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="84"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="84"/>
-      <c r="N24" s="84"/>
-      <c r="O24" s="84"/>
-      <c r="P24" s="85"/>
-      <c r="Q24" s="86"/>
-      <c r="R24" s="87"/>
-      <c r="S24" s="87"/>
-      <c r="T24" s="87"/>
-      <c r="U24" s="87"/>
-      <c r="V24" s="87"/>
-      <c r="W24" s="87"/>
-      <c r="X24" s="87"/>
-      <c r="Y24" s="87"/>
-      <c r="Z24" s="87"/>
-      <c r="AA24" s="87"/>
-      <c r="AB24" s="87"/>
-      <c r="AC24" s="87"/>
-      <c r="AD24" s="87"/>
-      <c r="AE24" s="88"/>
-      <c r="AF24" s="83"/>
-      <c r="AG24" s="84"/>
-      <c r="AH24" s="84"/>
-      <c r="AI24" s="85"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="79"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="85"/>
+      <c r="L24" s="85"/>
+      <c r="M24" s="85"/>
+      <c r="N24" s="85"/>
+      <c r="O24" s="85"/>
+      <c r="P24" s="86"/>
+      <c r="Q24" s="87"/>
+      <c r="R24" s="88"/>
+      <c r="S24" s="88"/>
+      <c r="T24" s="88"/>
+      <c r="U24" s="88"/>
+      <c r="V24" s="88"/>
+      <c r="W24" s="88"/>
+      <c r="X24" s="88"/>
+      <c r="Y24" s="88"/>
+      <c r="Z24" s="88"/>
+      <c r="AA24" s="88"/>
+      <c r="AB24" s="88"/>
+      <c r="AC24" s="88"/>
+      <c r="AD24" s="88"/>
+      <c r="AE24" s="89"/>
+      <c r="AF24" s="84"/>
+      <c r="AG24" s="85"/>
+      <c r="AH24" s="85"/>
+      <c r="AI24" s="86"/>
     </row>
     <row r="25" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="29"/>
-      <c r="B25" s="77"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="81"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="82"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="83"/>
-      <c r="K25" s="84"/>
-      <c r="L25" s="84"/>
-      <c r="M25" s="84"/>
-      <c r="N25" s="84"/>
-      <c r="O25" s="84"/>
-      <c r="P25" s="85"/>
-      <c r="Q25" s="86"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="87"/>
-      <c r="V25" s="87"/>
-      <c r="W25" s="87"/>
-      <c r="X25" s="87"/>
-      <c r="Y25" s="87"/>
-      <c r="Z25" s="87"/>
-      <c r="AA25" s="87"/>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="87"/>
-      <c r="AD25" s="87"/>
-      <c r="AE25" s="88"/>
-      <c r="AF25" s="83"/>
-      <c r="AG25" s="84"/>
-      <c r="AH25" s="84"/>
-      <c r="AI25" s="85"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="78"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="85"/>
+      <c r="L25" s="85"/>
+      <c r="M25" s="85"/>
+      <c r="N25" s="85"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="88"/>
+      <c r="S25" s="88"/>
+      <c r="T25" s="88"/>
+      <c r="U25" s="88"/>
+      <c r="V25" s="88"/>
+      <c r="W25" s="88"/>
+      <c r="X25" s="88"/>
+      <c r="Y25" s="88"/>
+      <c r="Z25" s="88"/>
+      <c r="AA25" s="88"/>
+      <c r="AB25" s="88"/>
+      <c r="AC25" s="88"/>
+      <c r="AD25" s="88"/>
+      <c r="AE25" s="89"/>
+      <c r="AF25" s="84"/>
+      <c r="AG25" s="85"/>
+      <c r="AH25" s="85"/>
+      <c r="AI25" s="86"/>
     </row>
     <row r="26" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="29"/>
-      <c r="B26" s="77"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="77"/>
-      <c r="H26" s="82"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="83"/>
-      <c r="K26" s="84"/>
-      <c r="L26" s="84"/>
-      <c r="M26" s="84"/>
-      <c r="N26" s="84"/>
-      <c r="O26" s="84"/>
-      <c r="P26" s="85"/>
-      <c r="Q26" s="86"/>
-      <c r="R26" s="87"/>
-      <c r="S26" s="87"/>
-      <c r="T26" s="87"/>
-      <c r="U26" s="87"/>
-      <c r="V26" s="87"/>
-      <c r="W26" s="87"/>
-      <c r="X26" s="87"/>
-      <c r="Y26" s="87"/>
-      <c r="Z26" s="87"/>
-      <c r="AA26" s="87"/>
-      <c r="AB26" s="87"/>
-      <c r="AC26" s="87"/>
-      <c r="AD26" s="87"/>
-      <c r="AE26" s="88"/>
-      <c r="AF26" s="83"/>
-      <c r="AG26" s="84"/>
-      <c r="AH26" s="84"/>
-      <c r="AI26" s="85"/>
+      <c r="B26" s="78"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="79"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="85"/>
+      <c r="L26" s="85"/>
+      <c r="M26" s="85"/>
+      <c r="N26" s="85"/>
+      <c r="O26" s="85"/>
+      <c r="P26" s="86"/>
+      <c r="Q26" s="87"/>
+      <c r="R26" s="88"/>
+      <c r="S26" s="88"/>
+      <c r="T26" s="88"/>
+      <c r="U26" s="88"/>
+      <c r="V26" s="88"/>
+      <c r="W26" s="88"/>
+      <c r="X26" s="88"/>
+      <c r="Y26" s="88"/>
+      <c r="Z26" s="88"/>
+      <c r="AA26" s="88"/>
+      <c r="AB26" s="88"/>
+      <c r="AC26" s="88"/>
+      <c r="AD26" s="88"/>
+      <c r="AE26" s="89"/>
+      <c r="AF26" s="84"/>
+      <c r="AG26" s="85"/>
+      <c r="AH26" s="85"/>
+      <c r="AI26" s="86"/>
     </row>
     <row r="27" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="29"/>
-      <c r="B27" s="77"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="81"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="82"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="83"/>
-      <c r="K27" s="84"/>
-      <c r="L27" s="84"/>
-      <c r="M27" s="84"/>
-      <c r="N27" s="84"/>
-      <c r="O27" s="84"/>
-      <c r="P27" s="85"/>
-      <c r="Q27" s="86"/>
-      <c r="R27" s="87"/>
-      <c r="S27" s="87"/>
-      <c r="T27" s="87"/>
-      <c r="U27" s="87"/>
-      <c r="V27" s="87"/>
-      <c r="W27" s="87"/>
-      <c r="X27" s="87"/>
-      <c r="Y27" s="87"/>
-      <c r="Z27" s="87"/>
-      <c r="AA27" s="87"/>
-      <c r="AB27" s="87"/>
-      <c r="AC27" s="87"/>
-      <c r="AD27" s="87"/>
-      <c r="AE27" s="88"/>
-      <c r="AF27" s="83"/>
-      <c r="AG27" s="84"/>
-      <c r="AH27" s="84"/>
-      <c r="AI27" s="85"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="79"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="83"/>
+      <c r="I27" s="79"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="85"/>
+      <c r="M27" s="85"/>
+      <c r="N27" s="85"/>
+      <c r="O27" s="85"/>
+      <c r="P27" s="86"/>
+      <c r="Q27" s="87"/>
+      <c r="R27" s="88"/>
+      <c r="S27" s="88"/>
+      <c r="T27" s="88"/>
+      <c r="U27" s="88"/>
+      <c r="V27" s="88"/>
+      <c r="W27" s="88"/>
+      <c r="X27" s="88"/>
+      <c r="Y27" s="88"/>
+      <c r="Z27" s="88"/>
+      <c r="AA27" s="88"/>
+      <c r="AB27" s="88"/>
+      <c r="AC27" s="88"/>
+      <c r="AD27" s="88"/>
+      <c r="AE27" s="89"/>
+      <c r="AF27" s="84"/>
+      <c r="AG27" s="85"/>
+      <c r="AH27" s="85"/>
+      <c r="AI27" s="86"/>
     </row>
     <row r="28" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="29"/>
-      <c r="B28" s="77"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="81"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="82"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="84"/>
-      <c r="L28" s="84"/>
-      <c r="M28" s="84"/>
-      <c r="N28" s="84"/>
-      <c r="O28" s="84"/>
-      <c r="P28" s="85"/>
-      <c r="Q28" s="86"/>
-      <c r="R28" s="87"/>
-      <c r="S28" s="87"/>
-      <c r="T28" s="87"/>
-      <c r="U28" s="87"/>
-      <c r="V28" s="87"/>
-      <c r="W28" s="87"/>
-      <c r="X28" s="87"/>
-      <c r="Y28" s="87"/>
-      <c r="Z28" s="87"/>
-      <c r="AA28" s="87"/>
-      <c r="AB28" s="87"/>
-      <c r="AC28" s="87"/>
-      <c r="AD28" s="87"/>
-      <c r="AE28" s="88"/>
-      <c r="AF28" s="83"/>
-      <c r="AG28" s="84"/>
-      <c r="AH28" s="84"/>
-      <c r="AI28" s="85"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="79"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="78"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="85"/>
+      <c r="L28" s="85"/>
+      <c r="M28" s="85"/>
+      <c r="N28" s="85"/>
+      <c r="O28" s="85"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="87"/>
+      <c r="R28" s="88"/>
+      <c r="S28" s="88"/>
+      <c r="T28" s="88"/>
+      <c r="U28" s="88"/>
+      <c r="V28" s="88"/>
+      <c r="W28" s="88"/>
+      <c r="X28" s="88"/>
+      <c r="Y28" s="88"/>
+      <c r="Z28" s="88"/>
+      <c r="AA28" s="88"/>
+      <c r="AB28" s="88"/>
+      <c r="AC28" s="88"/>
+      <c r="AD28" s="88"/>
+      <c r="AE28" s="89"/>
+      <c r="AF28" s="84"/>
+      <c r="AG28" s="85"/>
+      <c r="AH28" s="85"/>
+      <c r="AI28" s="86"/>
     </row>
     <row r="29" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="29"/>
-      <c r="B29" s="77"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="82"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="83"/>
-      <c r="K29" s="84"/>
-      <c r="L29" s="84"/>
-      <c r="M29" s="84"/>
-      <c r="N29" s="84"/>
-      <c r="O29" s="84"/>
-      <c r="P29" s="85"/>
-      <c r="Q29" s="86"/>
-      <c r="R29" s="87"/>
-      <c r="S29" s="87"/>
-      <c r="T29" s="87"/>
-      <c r="U29" s="87"/>
-      <c r="V29" s="87"/>
-      <c r="W29" s="87"/>
-      <c r="X29" s="87"/>
-      <c r="Y29" s="87"/>
-      <c r="Z29" s="87"/>
-      <c r="AA29" s="87"/>
-      <c r="AB29" s="87"/>
-      <c r="AC29" s="87"/>
-      <c r="AD29" s="87"/>
-      <c r="AE29" s="88"/>
-      <c r="AF29" s="83"/>
-      <c r="AG29" s="84"/>
-      <c r="AH29" s="84"/>
-      <c r="AI29" s="85"/>
+      <c r="B29" s="78"/>
+      <c r="C29" s="79"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="78"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="85"/>
+      <c r="M29" s="85"/>
+      <c r="N29" s="85"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="86"/>
+      <c r="Q29" s="87"/>
+      <c r="R29" s="88"/>
+      <c r="S29" s="88"/>
+      <c r="T29" s="88"/>
+      <c r="U29" s="88"/>
+      <c r="V29" s="88"/>
+      <c r="W29" s="88"/>
+      <c r="X29" s="88"/>
+      <c r="Y29" s="88"/>
+      <c r="Z29" s="88"/>
+      <c r="AA29" s="88"/>
+      <c r="AB29" s="88"/>
+      <c r="AC29" s="88"/>
+      <c r="AD29" s="88"/>
+      <c r="AE29" s="89"/>
+      <c r="AF29" s="84"/>
+      <c r="AG29" s="85"/>
+      <c r="AH29" s="85"/>
+      <c r="AI29" s="86"/>
     </row>
     <row r="30" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="29"/>
-      <c r="B30" s="77"/>
-      <c r="C30" s="78"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="81"/>
-      <c r="G30" s="77"/>
-      <c r="H30" s="82"/>
-      <c r="I30" s="78"/>
-      <c r="J30" s="83"/>
-      <c r="K30" s="84"/>
-      <c r="L30" s="84"/>
-      <c r="M30" s="84"/>
-      <c r="N30" s="84"/>
-      <c r="O30" s="84"/>
-      <c r="P30" s="85"/>
-      <c r="Q30" s="86"/>
-      <c r="R30" s="87"/>
-      <c r="S30" s="87"/>
-      <c r="T30" s="87"/>
-      <c r="U30" s="87"/>
-      <c r="V30" s="87"/>
-      <c r="W30" s="87"/>
-      <c r="X30" s="87"/>
-      <c r="Y30" s="87"/>
-      <c r="Z30" s="87"/>
-      <c r="AA30" s="87"/>
-      <c r="AB30" s="87"/>
-      <c r="AC30" s="87"/>
-      <c r="AD30" s="87"/>
-      <c r="AE30" s="88"/>
-      <c r="AF30" s="83"/>
-      <c r="AG30" s="84"/>
-      <c r="AH30" s="84"/>
-      <c r="AI30" s="85"/>
+      <c r="B30" s="78"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="85"/>
+      <c r="L30" s="85"/>
+      <c r="M30" s="85"/>
+      <c r="N30" s="85"/>
+      <c r="O30" s="85"/>
+      <c r="P30" s="86"/>
+      <c r="Q30" s="87"/>
+      <c r="R30" s="88"/>
+      <c r="S30" s="88"/>
+      <c r="T30" s="88"/>
+      <c r="U30" s="88"/>
+      <c r="V30" s="88"/>
+      <c r="W30" s="88"/>
+      <c r="X30" s="88"/>
+      <c r="Y30" s="88"/>
+      <c r="Z30" s="88"/>
+      <c r="AA30" s="88"/>
+      <c r="AB30" s="88"/>
+      <c r="AC30" s="88"/>
+      <c r="AD30" s="88"/>
+      <c r="AE30" s="89"/>
+      <c r="AF30" s="84"/>
+      <c r="AG30" s="85"/>
+      <c r="AH30" s="85"/>
+      <c r="AI30" s="86"/>
     </row>
     <row r="31" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="29"/>
-      <c r="B31" s="77"/>
-      <c r="C31" s="78"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="82"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="83"/>
-      <c r="K31" s="84"/>
-      <c r="L31" s="84"/>
-      <c r="M31" s="84"/>
-      <c r="N31" s="84"/>
-      <c r="O31" s="84"/>
-      <c r="P31" s="85"/>
-      <c r="Q31" s="86"/>
-      <c r="R31" s="87"/>
-      <c r="S31" s="87"/>
-      <c r="T31" s="87"/>
-      <c r="U31" s="87"/>
-      <c r="V31" s="87"/>
-      <c r="W31" s="87"/>
-      <c r="X31" s="87"/>
-      <c r="Y31" s="87"/>
-      <c r="Z31" s="87"/>
-      <c r="AA31" s="87"/>
-      <c r="AB31" s="87"/>
-      <c r="AC31" s="87"/>
-      <c r="AD31" s="87"/>
-      <c r="AE31" s="88"/>
-      <c r="AF31" s="83"/>
-      <c r="AG31" s="84"/>
-      <c r="AH31" s="84"/>
-      <c r="AI31" s="85"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="79"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="79"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="85"/>
+      <c r="P31" s="86"/>
+      <c r="Q31" s="87"/>
+      <c r="R31" s="88"/>
+      <c r="S31" s="88"/>
+      <c r="T31" s="88"/>
+      <c r="U31" s="88"/>
+      <c r="V31" s="88"/>
+      <c r="W31" s="88"/>
+      <c r="X31" s="88"/>
+      <c r="Y31" s="88"/>
+      <c r="Z31" s="88"/>
+      <c r="AA31" s="88"/>
+      <c r="AB31" s="88"/>
+      <c r="AC31" s="88"/>
+      <c r="AD31" s="88"/>
+      <c r="AE31" s="89"/>
+      <c r="AF31" s="84"/>
+      <c r="AG31" s="85"/>
+      <c r="AH31" s="85"/>
+      <c r="AI31" s="86"/>
     </row>
     <row r="32" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="29"/>
-      <c r="B32" s="77"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="82"/>
-      <c r="I32" s="78"/>
-      <c r="J32" s="83"/>
-      <c r="K32" s="89"/>
-      <c r="L32" s="84"/>
-      <c r="M32" s="84"/>
-      <c r="N32" s="84"/>
-      <c r="O32" s="84"/>
-      <c r="P32" s="85"/>
-      <c r="Q32" s="86"/>
-      <c r="R32" s="87"/>
-      <c r="S32" s="87"/>
-      <c r="T32" s="87"/>
-      <c r="U32" s="87"/>
-      <c r="V32" s="87"/>
-      <c r="W32" s="87"/>
-      <c r="X32" s="87"/>
-      <c r="Y32" s="87"/>
-      <c r="Z32" s="87"/>
-      <c r="AA32" s="87"/>
-      <c r="AB32" s="87"/>
-      <c r="AC32" s="87"/>
-      <c r="AD32" s="87"/>
-      <c r="AE32" s="88"/>
-      <c r="AF32" s="83"/>
-      <c r="AG32" s="84"/>
-      <c r="AH32" s="84"/>
-      <c r="AI32" s="85"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="79"/>
+      <c r="D32" s="80"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="85"/>
+      <c r="M32" s="85"/>
+      <c r="N32" s="85"/>
+      <c r="O32" s="85"/>
+      <c r="P32" s="86"/>
+      <c r="Q32" s="87"/>
+      <c r="R32" s="88"/>
+      <c r="S32" s="88"/>
+      <c r="T32" s="88"/>
+      <c r="U32" s="88"/>
+      <c r="V32" s="88"/>
+      <c r="W32" s="88"/>
+      <c r="X32" s="88"/>
+      <c r="Y32" s="88"/>
+      <c r="Z32" s="88"/>
+      <c r="AA32" s="88"/>
+      <c r="AB32" s="88"/>
+      <c r="AC32" s="88"/>
+      <c r="AD32" s="88"/>
+      <c r="AE32" s="89"/>
+      <c r="AF32" s="84"/>
+      <c r="AG32" s="85"/>
+      <c r="AH32" s="85"/>
+      <c r="AI32" s="86"/>
     </row>
     <row r="33" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="29"/>
-      <c r="B33" s="77"/>
-      <c r="C33" s="78"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="82"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="83"/>
-      <c r="K33" s="84"/>
-      <c r="L33" s="84"/>
-      <c r="M33" s="84"/>
-      <c r="N33" s="84"/>
-      <c r="O33" s="84"/>
-      <c r="P33" s="85"/>
-      <c r="Q33" s="86"/>
-      <c r="R33" s="87"/>
-      <c r="S33" s="87"/>
-      <c r="T33" s="87"/>
-      <c r="U33" s="87"/>
-      <c r="V33" s="87"/>
-      <c r="W33" s="87"/>
-      <c r="X33" s="87"/>
-      <c r="Y33" s="87"/>
-      <c r="Z33" s="87"/>
-      <c r="AA33" s="87"/>
-      <c r="AB33" s="87"/>
-      <c r="AC33" s="87"/>
-      <c r="AD33" s="87"/>
-      <c r="AE33" s="88"/>
-      <c r="AF33" s="83"/>
-      <c r="AG33" s="84"/>
-      <c r="AH33" s="84"/>
-      <c r="AI33" s="85"/>
+      <c r="B33" s="78"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="78"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="84"/>
+      <c r="K33" s="85"/>
+      <c r="L33" s="85"/>
+      <c r="M33" s="85"/>
+      <c r="N33" s="85"/>
+      <c r="O33" s="85"/>
+      <c r="P33" s="86"/>
+      <c r="Q33" s="87"/>
+      <c r="R33" s="88"/>
+      <c r="S33" s="88"/>
+      <c r="T33" s="88"/>
+      <c r="U33" s="88"/>
+      <c r="V33" s="88"/>
+      <c r="W33" s="88"/>
+      <c r="X33" s="88"/>
+      <c r="Y33" s="88"/>
+      <c r="Z33" s="88"/>
+      <c r="AA33" s="88"/>
+      <c r="AB33" s="88"/>
+      <c r="AC33" s="88"/>
+      <c r="AD33" s="88"/>
+      <c r="AE33" s="89"/>
+      <c r="AF33" s="84"/>
+      <c r="AG33" s="85"/>
+      <c r="AH33" s="85"/>
+      <c r="AI33" s="86"/>
     </row>
     <row r="34" spans="1:35" ht="14.25" x14ac:dyDescent="0.15">
       <c r="K34" s="31"/>
@@ -9259,163 +9215,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="121" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="113" t="str">
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="119" t="s">
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="130" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="128" t="str">
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="139" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarchを使用したシステム開発における標準WBS</v>
       </c>
-      <c r="T1" s="129"/>
-      <c r="U1" s="129"/>
-      <c r="V1" s="129"/>
-      <c r="W1" s="129"/>
-      <c r="X1" s="129"/>
-      <c r="Y1" s="129"/>
-      <c r="Z1" s="130"/>
-      <c r="AA1" s="140" t="s">
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
+      <c r="Y1" s="140"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="151" t="s">
         <v>280</v>
       </c>
-      <c r="AB1" s="141"/>
-      <c r="AC1" s="137" t="str">
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="138"/>
-      <c r="AE1" s="138"/>
-      <c r="AF1" s="139"/>
-      <c r="AG1" s="142">
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="150"/>
+      <c r="AG1" s="153">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="143"/>
-      <c r="AI1" s="144"/>
+      <c r="AH1" s="154"/>
+      <c r="AI1" s="155"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3"/>
     </row>
     <row r="2" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="121" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="113" t="str">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="115"/>
-      <c r="O2" s="122"/>
-      <c r="P2" s="123"/>
-      <c r="Q2" s="123"/>
-      <c r="R2" s="124"/>
-      <c r="S2" s="131"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="132"/>
-      <c r="W2" s="132"/>
-      <c r="X2" s="132"/>
-      <c r="Y2" s="132"/>
-      <c r="Z2" s="133"/>
-      <c r="AA2" s="140" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="133"/>
+      <c r="P2" s="134"/>
+      <c r="Q2" s="134"/>
+      <c r="R2" s="135"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="143"/>
+      <c r="U2" s="143"/>
+      <c r="V2" s="143"/>
+      <c r="W2" s="143"/>
+      <c r="X2" s="143"/>
+      <c r="Y2" s="143"/>
+      <c r="Z2" s="144"/>
+      <c r="AA2" s="151" t="s">
         <v>282</v>
       </c>
-      <c r="AB2" s="141"/>
-      <c r="AC2" s="137" t="str">
+      <c r="AB2" s="152"/>
+      <c r="AC2" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="138"/>
-      <c r="AE2" s="138"/>
-      <c r="AF2" s="139"/>
-      <c r="AG2" s="142">
+      <c r="AD2" s="149"/>
+      <c r="AE2" s="149"/>
+      <c r="AF2" s="150"/>
+      <c r="AG2" s="153">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v>45461</v>
       </c>
-      <c r="AH2" s="143"/>
-      <c r="AI2" s="144"/>
+      <c r="AH2" s="154"/>
+      <c r="AI2" s="155"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="110" t="s">
+      <c r="A3" s="121" t="s">
         <v>283</v>
       </c>
-      <c r="B3" s="111"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="113" t="str">
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="125"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="127"/>
-      <c r="S3" s="134"/>
-      <c r="T3" s="135"/>
-      <c r="U3" s="135"/>
-      <c r="V3" s="135"/>
-      <c r="W3" s="135"/>
-      <c r="X3" s="135"/>
-      <c r="Y3" s="135"/>
-      <c r="Z3" s="136"/>
-      <c r="AA3" s="140"/>
-      <c r="AB3" s="141"/>
-      <c r="AC3" s="137" t="str">
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="137"/>
+      <c r="Q3" s="137"/>
+      <c r="R3" s="138"/>
+      <c r="S3" s="145"/>
+      <c r="T3" s="146"/>
+      <c r="U3" s="146"/>
+      <c r="V3" s="146"/>
+      <c r="W3" s="146"/>
+      <c r="X3" s="146"/>
+      <c r="Y3" s="146"/>
+      <c r="Z3" s="147"/>
+      <c r="AA3" s="151"/>
+      <c r="AB3" s="152"/>
+      <c r="AC3" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="138"/>
-      <c r="AE3" s="138"/>
-      <c r="AF3" s="139"/>
-      <c r="AG3" s="142" t="str">
+      <c r="AD3" s="149"/>
+      <c r="AE3" s="149"/>
+      <c r="AF3" s="150"/>
+      <c r="AG3" s="153" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="143"/>
-      <c r="AI3" s="144"/>
+      <c r="AH3" s="154"/>
+      <c r="AI3" s="155"/>
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
@@ -9691,7 +9647,7 @@
       <c r="A11" s="30"/>
       <c r="B11" s="30"/>
       <c r="C11" s="34" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
@@ -10774,59 +10730,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="121" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="113" t="str">
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="149" t="s">
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="160" t="s">
         <v>294</v>
       </c>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="128" t="str">
+      <c r="P1" s="161"/>
+      <c r="Q1" s="161"/>
+      <c r="R1" s="162"/>
+      <c r="S1" s="139" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarchを使用したシステム開発における標準WBS</v>
       </c>
-      <c r="T1" s="129"/>
-      <c r="U1" s="129"/>
-      <c r="V1" s="129"/>
-      <c r="W1" s="129"/>
-      <c r="X1" s="129"/>
-      <c r="Y1" s="129"/>
-      <c r="Z1" s="130"/>
-      <c r="AA1" s="110" t="s">
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
+      <c r="Y1" s="140"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="AB1" s="112"/>
-      <c r="AC1" s="137" t="str">
+      <c r="AB1" s="123"/>
+      <c r="AC1" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="138"/>
-      <c r="AE1" s="138"/>
-      <c r="AF1" s="139"/>
-      <c r="AG1" s="142">
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="150"/>
+      <c r="AG1" s="153">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="143"/>
-      <c r="AI1" s="144"/>
+      <c r="AH1" s="154"/>
+      <c r="AI1" s="155"/>
       <c r="AJ1" s="30"/>
       <c r="AN1" s="51"/>
       <c r="AO1" s="30"/>
@@ -10840,54 +10796,54 @@
       <c r="AW1" s="30"/>
     </row>
     <row r="2" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="121" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="113" t="str">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="115"/>
-      <c r="O2" s="152"/>
-      <c r="P2" s="153"/>
-      <c r="Q2" s="153"/>
-      <c r="R2" s="154"/>
-      <c r="S2" s="131"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="132"/>
-      <c r="W2" s="132"/>
-      <c r="X2" s="132"/>
-      <c r="Y2" s="132"/>
-      <c r="Z2" s="133"/>
-      <c r="AA2" s="110" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="164"/>
+      <c r="Q2" s="164"/>
+      <c r="R2" s="165"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="143"/>
+      <c r="U2" s="143"/>
+      <c r="V2" s="143"/>
+      <c r="W2" s="143"/>
+      <c r="X2" s="143"/>
+      <c r="Y2" s="143"/>
+      <c r="Z2" s="144"/>
+      <c r="AA2" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="AB2" s="112"/>
-      <c r="AC2" s="137" t="str">
+      <c r="AB2" s="123"/>
+      <c r="AC2" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="138"/>
-      <c r="AE2" s="138"/>
-      <c r="AF2" s="139"/>
-      <c r="AG2" s="142">
+      <c r="AD2" s="149"/>
+      <c r="AE2" s="149"/>
+      <c r="AF2" s="150"/>
+      <c r="AG2" s="153">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v>45461</v>
       </c>
-      <c r="AH2" s="143"/>
-      <c r="AI2" s="144"/>
+      <c r="AH2" s="154"/>
+      <c r="AI2" s="155"/>
       <c r="AJ2" s="30"/>
       <c r="AN2" s="51"/>
       <c r="AO2" s="30"/>
@@ -10901,52 +10857,52 @@
       <c r="AW2" s="30"/>
     </row>
     <row r="3" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="110" t="s">
+      <c r="A3" s="121" t="s">
         <v>283</v>
       </c>
-      <c r="B3" s="111"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="113" t="str">
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="155"/>
-      <c r="P3" s="156"/>
-      <c r="Q3" s="156"/>
-      <c r="R3" s="157"/>
-      <c r="S3" s="134"/>
-      <c r="T3" s="135"/>
-      <c r="U3" s="135"/>
-      <c r="V3" s="135"/>
-      <c r="W3" s="135"/>
-      <c r="X3" s="135"/>
-      <c r="Y3" s="135"/>
-      <c r="Z3" s="136"/>
-      <c r="AA3" s="110"/>
-      <c r="AB3" s="112"/>
-      <c r="AC3" s="137" t="str">
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="166"/>
+      <c r="P3" s="167"/>
+      <c r="Q3" s="167"/>
+      <c r="R3" s="168"/>
+      <c r="S3" s="145"/>
+      <c r="T3" s="146"/>
+      <c r="U3" s="146"/>
+      <c r="V3" s="146"/>
+      <c r="W3" s="146"/>
+      <c r="X3" s="146"/>
+      <c r="Y3" s="146"/>
+      <c r="Z3" s="147"/>
+      <c r="AA3" s="121"/>
+      <c r="AB3" s="123"/>
+      <c r="AC3" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="138"/>
-      <c r="AE3" s="138"/>
-      <c r="AF3" s="139"/>
-      <c r="AG3" s="142" t="str">
+      <c r="AD3" s="149"/>
+      <c r="AE3" s="149"/>
+      <c r="AF3" s="150"/>
+      <c r="AG3" s="153" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="143"/>
-      <c r="AI3" s="144"/>
+      <c r="AH3" s="154"/>
+      <c r="AI3" s="155"/>
       <c r="AJ3" s="53"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
@@ -11188,340 +11144,340 @@
       <c r="D57" s="55" t="s">
         <v>305</v>
       </c>
-      <c r="E57" s="146" t="s">
+      <c r="E57" s="157" t="s">
         <v>107</v>
       </c>
-      <c r="F57" s="147"/>
-      <c r="G57" s="147"/>
-      <c r="H57" s="147"/>
-      <c r="I57" s="147"/>
-      <c r="J57" s="148"/>
-      <c r="K57" s="146" t="s">
+      <c r="F57" s="158"/>
+      <c r="G57" s="158"/>
+      <c r="H57" s="158"/>
+      <c r="I57" s="158"/>
+      <c r="J57" s="159"/>
+      <c r="K57" s="157" t="s">
         <v>178</v>
       </c>
-      <c r="L57" s="147"/>
-      <c r="M57" s="147"/>
-      <c r="N57" s="147"/>
-      <c r="O57" s="147"/>
-      <c r="P57" s="147"/>
-      <c r="Q57" s="147"/>
-      <c r="R57" s="147"/>
-      <c r="S57" s="147"/>
-      <c r="T57" s="147"/>
-      <c r="U57" s="147"/>
-      <c r="V57" s="147"/>
-      <c r="W57" s="147"/>
-      <c r="X57" s="147"/>
-      <c r="Y57" s="147"/>
-      <c r="Z57" s="147"/>
-      <c r="AA57" s="147"/>
-      <c r="AB57" s="148"/>
+      <c r="L57" s="158"/>
+      <c r="M57" s="158"/>
+      <c r="N57" s="158"/>
+      <c r="O57" s="158"/>
+      <c r="P57" s="158"/>
+      <c r="Q57" s="158"/>
+      <c r="R57" s="158"/>
+      <c r="S57" s="158"/>
+      <c r="T57" s="158"/>
+      <c r="U57" s="158"/>
+      <c r="V57" s="158"/>
+      <c r="W57" s="158"/>
+      <c r="X57" s="158"/>
+      <c r="Y57" s="158"/>
+      <c r="Z57" s="158"/>
+      <c r="AA57" s="158"/>
+      <c r="AB57" s="159"/>
     </row>
     <row r="58" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="34"/>
       <c r="D58" s="56">
         <v>1</v>
       </c>
-      <c r="E58" s="145" t="s">
+      <c r="E58" s="156" t="s">
         <v>34</v>
       </c>
-      <c r="F58" s="145"/>
-      <c r="G58" s="145"/>
-      <c r="H58" s="145"/>
-      <c r="I58" s="145"/>
-      <c r="J58" s="145"/>
-      <c r="K58" s="145" t="s">
+      <c r="F58" s="156"/>
+      <c r="G58" s="156"/>
+      <c r="H58" s="156"/>
+      <c r="I58" s="156"/>
+      <c r="J58" s="156"/>
+      <c r="K58" s="156" t="s">
         <v>18</v>
       </c>
-      <c r="L58" s="145"/>
-      <c r="M58" s="145"/>
-      <c r="N58" s="145"/>
-      <c r="O58" s="145"/>
-      <c r="P58" s="145"/>
-      <c r="Q58" s="145"/>
-      <c r="R58" s="145"/>
-      <c r="S58" s="145"/>
-      <c r="T58" s="145"/>
-      <c r="U58" s="145"/>
-      <c r="V58" s="145"/>
-      <c r="W58" s="145"/>
-      <c r="X58" s="145"/>
-      <c r="Y58" s="145"/>
-      <c r="Z58" s="145"/>
-      <c r="AA58" s="145"/>
-      <c r="AB58" s="145"/>
+      <c r="L58" s="156"/>
+      <c r="M58" s="156"/>
+      <c r="N58" s="156"/>
+      <c r="O58" s="156"/>
+      <c r="P58" s="156"/>
+      <c r="Q58" s="156"/>
+      <c r="R58" s="156"/>
+      <c r="S58" s="156"/>
+      <c r="T58" s="156"/>
+      <c r="U58" s="156"/>
+      <c r="V58" s="156"/>
+      <c r="W58" s="156"/>
+      <c r="X58" s="156"/>
+      <c r="Y58" s="156"/>
+      <c r="Z58" s="156"/>
+      <c r="AA58" s="156"/>
+      <c r="AB58" s="156"/>
     </row>
     <row r="59" spans="3:28" ht="48" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C59" s="34"/>
       <c r="D59" s="56">
         <v>2</v>
       </c>
-      <c r="E59" s="145" t="s">
+      <c r="E59" s="156" t="s">
         <v>43</v>
       </c>
-      <c r="F59" s="145"/>
-      <c r="G59" s="145"/>
-      <c r="H59" s="145"/>
-      <c r="I59" s="145"/>
-      <c r="J59" s="145"/>
-      <c r="K59" s="145" t="s">
+      <c r="F59" s="156"/>
+      <c r="G59" s="156"/>
+      <c r="H59" s="156"/>
+      <c r="I59" s="156"/>
+      <c r="J59" s="156"/>
+      <c r="K59" s="156" t="s">
         <v>19</v>
       </c>
-      <c r="L59" s="145"/>
-      <c r="M59" s="145"/>
-      <c r="N59" s="145"/>
-      <c r="O59" s="145"/>
-      <c r="P59" s="145"/>
-      <c r="Q59" s="145"/>
-      <c r="R59" s="145"/>
-      <c r="S59" s="145"/>
-      <c r="T59" s="145"/>
-      <c r="U59" s="145"/>
-      <c r="V59" s="145"/>
-      <c r="W59" s="145"/>
-      <c r="X59" s="145"/>
-      <c r="Y59" s="145"/>
-      <c r="Z59" s="145"/>
-      <c r="AA59" s="145"/>
-      <c r="AB59" s="145"/>
+      <c r="L59" s="156"/>
+      <c r="M59" s="156"/>
+      <c r="N59" s="156"/>
+      <c r="O59" s="156"/>
+      <c r="P59" s="156"/>
+      <c r="Q59" s="156"/>
+      <c r="R59" s="156"/>
+      <c r="S59" s="156"/>
+      <c r="T59" s="156"/>
+      <c r="U59" s="156"/>
+      <c r="V59" s="156"/>
+      <c r="W59" s="156"/>
+      <c r="X59" s="156"/>
+      <c r="Y59" s="156"/>
+      <c r="Z59" s="156"/>
+      <c r="AA59" s="156"/>
+      <c r="AB59" s="156"/>
     </row>
     <row r="60" spans="3:28" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C60" s="34"/>
       <c r="D60" s="56">
         <v>3</v>
       </c>
-      <c r="E60" s="145" t="s">
+      <c r="E60" s="156" t="s">
         <v>200</v>
       </c>
-      <c r="F60" s="145"/>
-      <c r="G60" s="145"/>
-      <c r="H60" s="145"/>
-      <c r="I60" s="145"/>
-      <c r="J60" s="145"/>
-      <c r="K60" s="145" t="s">
+      <c r="F60" s="156"/>
+      <c r="G60" s="156"/>
+      <c r="H60" s="156"/>
+      <c r="I60" s="156"/>
+      <c r="J60" s="156"/>
+      <c r="K60" s="156" t="s">
         <v>106</v>
       </c>
-      <c r="L60" s="145"/>
-      <c r="M60" s="145"/>
-      <c r="N60" s="145"/>
-      <c r="O60" s="145"/>
-      <c r="P60" s="145"/>
-      <c r="Q60" s="145"/>
-      <c r="R60" s="145"/>
-      <c r="S60" s="145"/>
-      <c r="T60" s="145"/>
-      <c r="U60" s="145"/>
-      <c r="V60" s="145"/>
-      <c r="W60" s="145"/>
-      <c r="X60" s="145"/>
-      <c r="Y60" s="145"/>
-      <c r="Z60" s="145"/>
-      <c r="AA60" s="145"/>
-      <c r="AB60" s="145"/>
+      <c r="L60" s="156"/>
+      <c r="M60" s="156"/>
+      <c r="N60" s="156"/>
+      <c r="O60" s="156"/>
+      <c r="P60" s="156"/>
+      <c r="Q60" s="156"/>
+      <c r="R60" s="156"/>
+      <c r="S60" s="156"/>
+      <c r="T60" s="156"/>
+      <c r="U60" s="156"/>
+      <c r="V60" s="156"/>
+      <c r="W60" s="156"/>
+      <c r="X60" s="156"/>
+      <c r="Y60" s="156"/>
+      <c r="Z60" s="156"/>
+      <c r="AA60" s="156"/>
+      <c r="AB60" s="156"/>
     </row>
     <row r="61" spans="3:28" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C61" s="34"/>
       <c r="D61" s="56">
         <v>4</v>
       </c>
-      <c r="E61" s="145" t="s">
+      <c r="E61" s="156" t="s">
         <v>201</v>
       </c>
-      <c r="F61" s="145"/>
-      <c r="G61" s="145"/>
-      <c r="H61" s="145"/>
-      <c r="I61" s="145"/>
-      <c r="J61" s="145"/>
-      <c r="K61" s="145" t="s">
+      <c r="F61" s="156"/>
+      <c r="G61" s="156"/>
+      <c r="H61" s="156"/>
+      <c r="I61" s="156"/>
+      <c r="J61" s="156"/>
+      <c r="K61" s="156" t="s">
         <v>20</v>
       </c>
-      <c r="L61" s="145"/>
-      <c r="M61" s="145"/>
-      <c r="N61" s="145"/>
-      <c r="O61" s="145"/>
-      <c r="P61" s="145"/>
-      <c r="Q61" s="145"/>
-      <c r="R61" s="145"/>
-      <c r="S61" s="145"/>
-      <c r="T61" s="145"/>
-      <c r="U61" s="145"/>
-      <c r="V61" s="145"/>
-      <c r="W61" s="145"/>
-      <c r="X61" s="145"/>
-      <c r="Y61" s="145"/>
-      <c r="Z61" s="145"/>
-      <c r="AA61" s="145"/>
-      <c r="AB61" s="145"/>
+      <c r="L61" s="156"/>
+      <c r="M61" s="156"/>
+      <c r="N61" s="156"/>
+      <c r="O61" s="156"/>
+      <c r="P61" s="156"/>
+      <c r="Q61" s="156"/>
+      <c r="R61" s="156"/>
+      <c r="S61" s="156"/>
+      <c r="T61" s="156"/>
+      <c r="U61" s="156"/>
+      <c r="V61" s="156"/>
+      <c r="W61" s="156"/>
+      <c r="X61" s="156"/>
+      <c r="Y61" s="156"/>
+      <c r="Z61" s="156"/>
+      <c r="AA61" s="156"/>
+      <c r="AB61" s="156"/>
     </row>
     <row r="62" spans="3:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C62" s="34"/>
       <c r="D62" s="56">
         <v>5</v>
       </c>
-      <c r="E62" s="145" t="s">
+      <c r="E62" s="156" t="s">
         <v>202</v>
       </c>
-      <c r="F62" s="145"/>
-      <c r="G62" s="145"/>
-      <c r="H62" s="145"/>
-      <c r="I62" s="145"/>
-      <c r="J62" s="145"/>
-      <c r="K62" s="145" t="s">
+      <c r="F62" s="156"/>
+      <c r="G62" s="156"/>
+      <c r="H62" s="156"/>
+      <c r="I62" s="156"/>
+      <c r="J62" s="156"/>
+      <c r="K62" s="156" t="s">
         <v>21</v>
       </c>
-      <c r="L62" s="145"/>
-      <c r="M62" s="145"/>
-      <c r="N62" s="145"/>
-      <c r="O62" s="145"/>
-      <c r="P62" s="145"/>
-      <c r="Q62" s="145"/>
-      <c r="R62" s="145"/>
-      <c r="S62" s="145"/>
-      <c r="T62" s="145"/>
-      <c r="U62" s="145"/>
-      <c r="V62" s="145"/>
-      <c r="W62" s="145"/>
-      <c r="X62" s="145"/>
-      <c r="Y62" s="145"/>
-      <c r="Z62" s="145"/>
-      <c r="AA62" s="145"/>
-      <c r="AB62" s="145"/>
+      <c r="L62" s="156"/>
+      <c r="M62" s="156"/>
+      <c r="N62" s="156"/>
+      <c r="O62" s="156"/>
+      <c r="P62" s="156"/>
+      <c r="Q62" s="156"/>
+      <c r="R62" s="156"/>
+      <c r="S62" s="156"/>
+      <c r="T62" s="156"/>
+      <c r="U62" s="156"/>
+      <c r="V62" s="156"/>
+      <c r="W62" s="156"/>
+      <c r="X62" s="156"/>
+      <c r="Y62" s="156"/>
+      <c r="Z62" s="156"/>
+      <c r="AA62" s="156"/>
+      <c r="AB62" s="156"/>
     </row>
     <row r="63" spans="3:28" ht="72" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C63" s="34"/>
       <c r="D63" s="56">
         <v>6</v>
       </c>
-      <c r="E63" s="145" t="s">
+      <c r="E63" s="156" t="s">
         <v>225</v>
       </c>
-      <c r="F63" s="145"/>
-      <c r="G63" s="145"/>
-      <c r="H63" s="145"/>
-      <c r="I63" s="145"/>
-      <c r="J63" s="145"/>
-      <c r="K63" s="145" t="s">
+      <c r="F63" s="156"/>
+      <c r="G63" s="156"/>
+      <c r="H63" s="156"/>
+      <c r="I63" s="156"/>
+      <c r="J63" s="156"/>
+      <c r="K63" s="156" t="s">
         <v>306</v>
       </c>
-      <c r="L63" s="145"/>
-      <c r="M63" s="145"/>
-      <c r="N63" s="145"/>
-      <c r="O63" s="145"/>
-      <c r="P63" s="145"/>
-      <c r="Q63" s="145"/>
-      <c r="R63" s="145"/>
-      <c r="S63" s="145"/>
-      <c r="T63" s="145"/>
-      <c r="U63" s="145"/>
-      <c r="V63" s="145"/>
-      <c r="W63" s="145"/>
-      <c r="X63" s="145"/>
-      <c r="Y63" s="145"/>
-      <c r="Z63" s="145"/>
-      <c r="AA63" s="145"/>
-      <c r="AB63" s="145"/>
+      <c r="L63" s="156"/>
+      <c r="M63" s="156"/>
+      <c r="N63" s="156"/>
+      <c r="O63" s="156"/>
+      <c r="P63" s="156"/>
+      <c r="Q63" s="156"/>
+      <c r="R63" s="156"/>
+      <c r="S63" s="156"/>
+      <c r="T63" s="156"/>
+      <c r="U63" s="156"/>
+      <c r="V63" s="156"/>
+      <c r="W63" s="156"/>
+      <c r="X63" s="156"/>
+      <c r="Y63" s="156"/>
+      <c r="Z63" s="156"/>
+      <c r="AA63" s="156"/>
+      <c r="AB63" s="156"/>
     </row>
     <row r="64" spans="3:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C64" s="34"/>
       <c r="D64" s="56">
         <v>7</v>
       </c>
-      <c r="E64" s="145" t="s">
+      <c r="E64" s="156" t="s">
         <v>155</v>
       </c>
-      <c r="F64" s="145"/>
-      <c r="G64" s="145"/>
-      <c r="H64" s="145"/>
-      <c r="I64" s="145"/>
-      <c r="J64" s="145"/>
-      <c r="K64" s="145" t="s">
+      <c r="F64" s="156"/>
+      <c r="G64" s="156"/>
+      <c r="H64" s="156"/>
+      <c r="I64" s="156"/>
+      <c r="J64" s="156"/>
+      <c r="K64" s="156" t="s">
         <v>221</v>
       </c>
-      <c r="L64" s="145"/>
-      <c r="M64" s="145"/>
-      <c r="N64" s="145"/>
-      <c r="O64" s="145"/>
-      <c r="P64" s="145"/>
-      <c r="Q64" s="145"/>
-      <c r="R64" s="145"/>
-      <c r="S64" s="145"/>
-      <c r="T64" s="145"/>
-      <c r="U64" s="145"/>
-      <c r="V64" s="145"/>
-      <c r="W64" s="145"/>
-      <c r="X64" s="145"/>
-      <c r="Y64" s="145"/>
-      <c r="Z64" s="145"/>
-      <c r="AA64" s="145"/>
-      <c r="AB64" s="145"/>
+      <c r="L64" s="156"/>
+      <c r="M64" s="156"/>
+      <c r="N64" s="156"/>
+      <c r="O64" s="156"/>
+      <c r="P64" s="156"/>
+      <c r="Q64" s="156"/>
+      <c r="R64" s="156"/>
+      <c r="S64" s="156"/>
+      <c r="T64" s="156"/>
+      <c r="U64" s="156"/>
+      <c r="V64" s="156"/>
+      <c r="W64" s="156"/>
+      <c r="X64" s="156"/>
+      <c r="Y64" s="156"/>
+      <c r="Z64" s="156"/>
+      <c r="AA64" s="156"/>
+      <c r="AB64" s="156"/>
     </row>
     <row r="65" spans="3:28" ht="108" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C65" s="34"/>
       <c r="D65" s="56">
         <v>8</v>
       </c>
-      <c r="E65" s="145" t="s">
+      <c r="E65" s="156" t="s">
         <v>102</v>
       </c>
-      <c r="F65" s="145"/>
-      <c r="G65" s="145"/>
-      <c r="H65" s="145"/>
-      <c r="I65" s="145"/>
-      <c r="J65" s="145"/>
-      <c r="K65" s="145" t="s">
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="156" t="s">
         <v>217</v>
       </c>
-      <c r="L65" s="145"/>
-      <c r="M65" s="145"/>
-      <c r="N65" s="145"/>
-      <c r="O65" s="145"/>
-      <c r="P65" s="145"/>
-      <c r="Q65" s="145"/>
-      <c r="R65" s="145"/>
-      <c r="S65" s="145"/>
-      <c r="T65" s="145"/>
-      <c r="U65" s="145"/>
-      <c r="V65" s="145"/>
-      <c r="W65" s="145"/>
-      <c r="X65" s="145"/>
-      <c r="Y65" s="145"/>
-      <c r="Z65" s="145"/>
-      <c r="AA65" s="145"/>
-      <c r="AB65" s="145"/>
+      <c r="L65" s="156"/>
+      <c r="M65" s="156"/>
+      <c r="N65" s="156"/>
+      <c r="O65" s="156"/>
+      <c r="P65" s="156"/>
+      <c r="Q65" s="156"/>
+      <c r="R65" s="156"/>
+      <c r="S65" s="156"/>
+      <c r="T65" s="156"/>
+      <c r="U65" s="156"/>
+      <c r="V65" s="156"/>
+      <c r="W65" s="156"/>
+      <c r="X65" s="156"/>
+      <c r="Y65" s="156"/>
+      <c r="Z65" s="156"/>
+      <c r="AA65" s="156"/>
+      <c r="AB65" s="156"/>
     </row>
     <row r="66" spans="3:28" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C66" s="34"/>
       <c r="D66" s="56">
         <v>9</v>
       </c>
-      <c r="E66" s="145" t="s">
+      <c r="E66" s="156" t="s">
         <v>104</v>
       </c>
-      <c r="F66" s="145"/>
-      <c r="G66" s="145"/>
-      <c r="H66" s="145"/>
-      <c r="I66" s="145"/>
-      <c r="J66" s="145"/>
-      <c r="K66" s="145" t="s">
+      <c r="F66" s="156"/>
+      <c r="G66" s="156"/>
+      <c r="H66" s="156"/>
+      <c r="I66" s="156"/>
+      <c r="J66" s="156"/>
+      <c r="K66" s="156" t="s">
         <v>22</v>
       </c>
-      <c r="L66" s="145"/>
-      <c r="M66" s="145"/>
-      <c r="N66" s="145"/>
-      <c r="O66" s="145"/>
-      <c r="P66" s="145"/>
-      <c r="Q66" s="145"/>
-      <c r="R66" s="145"/>
-      <c r="S66" s="145"/>
-      <c r="T66" s="145"/>
-      <c r="U66" s="145"/>
-      <c r="V66" s="145"/>
-      <c r="W66" s="145"/>
-      <c r="X66" s="145"/>
-      <c r="Y66" s="145"/>
-      <c r="Z66" s="145"/>
-      <c r="AA66" s="145"/>
-      <c r="AB66" s="145"/>
+      <c r="L66" s="156"/>
+      <c r="M66" s="156"/>
+      <c r="N66" s="156"/>
+      <c r="O66" s="156"/>
+      <c r="P66" s="156"/>
+      <c r="Q66" s="156"/>
+      <c r="R66" s="156"/>
+      <c r="S66" s="156"/>
+      <c r="T66" s="156"/>
+      <c r="U66" s="156"/>
+      <c r="V66" s="156"/>
+      <c r="W66" s="156"/>
+      <c r="X66" s="156"/>
+      <c r="Y66" s="156"/>
+      <c r="Z66" s="156"/>
+      <c r="AA66" s="156"/>
+      <c r="AB66" s="156"/>
     </row>
     <row r="67" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C67" s="34"/>
@@ -11531,12 +11487,12 @@
     </row>
     <row r="69" spans="3:28" x14ac:dyDescent="0.15">
       <c r="C69" s="30" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="71" spans="3:28" x14ac:dyDescent="0.15">
       <c r="D71" s="30" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="73" spans="3:28" x14ac:dyDescent="0.15">
@@ -11544,7 +11500,7 @@
         <v>305</v>
       </c>
       <c r="E73" s="67" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F73" s="68"/>
       <c r="G73" s="68"/>
@@ -11775,7 +11731,7 @@
         <v>7</v>
       </c>
       <c r="E80" s="64" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F80" s="65"/>
       <c r="G80" s="65"/>
@@ -12324,44 +12280,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="169" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="158" t="s">
+      <c r="B1" s="169" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="159" t="s">
+      <c r="C1" s="170" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="158" t="s">
+      <c r="D1" s="169" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="158" t="s">
+      <c r="E1" s="169" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="158" t="s">
+      <c r="F1" s="169" t="s">
         <v>231</v>
       </c>
-      <c r="G1" s="158" t="s">
+      <c r="G1" s="169" t="s">
         <v>224</v>
       </c>
-      <c r="H1" s="158" t="s">
+      <c r="H1" s="169" t="s">
         <v>102</v>
       </c>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158" t="s">
+      <c r="I1" s="169"/>
+      <c r="J1" s="169"/>
+      <c r="K1" s="169" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A2" s="158"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="160"/>
+      <c r="A2" s="169"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="171"/>
       <c r="H2" s="63" t="s">
         <v>218</v>
       </c>
@@ -12371,7 +12327,7 @@
       <c r="J2" s="63" t="s">
         <v>220</v>
       </c>
-      <c r="K2" s="158"/>
+      <c r="K2" s="169"/>
     </row>
     <row r="3" spans="1:11" ht="101.25" x14ac:dyDescent="0.15">
       <c r="A3" s="57" t="s">
@@ -12864,9 +12820,7 @@
       <c r="J17" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="K17" s="57" t="s">
-        <v>396</v>
-      </c>
+      <c r="K17" s="57"/>
     </row>
     <row r="18" spans="1:11" ht="157.5" x14ac:dyDescent="0.15">
       <c r="A18" s="57" t="s">
@@ -13226,7 +13180,7 @@
         <v>335</v>
       </c>
       <c r="G28" s="57" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H28" s="59" t="s">
         <v>308</v>

--- a/010_開発プロセス標準/Nablarchを使用したシステム開発における標準WBS.xlsx
+++ b/010_開発プロセス標準/Nablarchを使用したシステム開発における標準WBS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8801ECF9-3A4F-4F32-9F67-E8C2A424BD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17502AE4-333B-428D-93C9-74B47E449D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="2445" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1035" yWindow="3390" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="14" r:id="rId1"/>
@@ -4762,10 +4762,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>JBatch / JSR352</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>表記</t>
     <rPh sb="0" eb="2">
       <t>ヒョウキ</t>
@@ -4866,6 +4862,10 @@
     <rPh sb="28" eb="30">
       <t>サクジョ</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>jBatch / JSR352</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -5500,6 +5500,114 @@
     <xf numFmtId="31" fontId="9" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -5536,188 +5644,89 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -5725,18 +5734,36 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5745,33 +5772,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6157,8 +6157,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1034755" y="2752683"/>
-          <a:ext cx="6519641" cy="2722035"/>
+          <a:off x="1035740" y="2776331"/>
+          <a:ext cx="6527524" cy="2745684"/>
           <a:chOff x="121" y="113"/>
           <a:chExt cx="729" cy="300"/>
         </a:xfrm>
@@ -7015,7 +7015,7 @@
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
       <c r="J23" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="24" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7626,55 +7626,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="84" t="s">
         <v>279</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
-      <c r="L1" s="125"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="130" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="93" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="132"/>
-      <c r="S1" s="139" t="s">
+      <c r="P1" s="94"/>
+      <c r="Q1" s="94"/>
+      <c r="R1" s="95"/>
+      <c r="S1" s="102" t="s">
         <v>291</v>
       </c>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-      <c r="X1" s="140"/>
-      <c r="Y1" s="140"/>
-      <c r="Z1" s="141"/>
-      <c r="AA1" s="121" t="s">
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
+      <c r="V1" s="103"/>
+      <c r="W1" s="103"/>
+      <c r="X1" s="103"/>
+      <c r="Y1" s="103"/>
+      <c r="Z1" s="104"/>
+      <c r="AA1" s="84" t="s">
         <v>280</v>
       </c>
-      <c r="AB1" s="123"/>
-      <c r="AC1" s="148" t="str">
+      <c r="AB1" s="86"/>
+      <c r="AC1" s="111" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="149"/>
-      <c r="AE1" s="149"/>
-      <c r="AF1" s="150"/>
-      <c r="AG1" s="115">
+      <c r="AD1" s="112"/>
+      <c r="AE1" s="112"/>
+      <c r="AF1" s="113"/>
+      <c r="AG1" s="78">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="116"/>
-      <c r="AI1" s="117"/>
+      <c r="AH1" s="79"/>
+      <c r="AI1" s="80"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="2"/>
@@ -7682,51 +7682,51 @@
       <c r="AN1" s="3"/>
     </row>
     <row r="2" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="84" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="122"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="125"/>
-      <c r="M2" s="125"/>
-      <c r="N2" s="126"/>
-      <c r="O2" s="133"/>
-      <c r="P2" s="134"/>
-      <c r="Q2" s="134"/>
-      <c r="R2" s="135"/>
-      <c r="S2" s="142"/>
-      <c r="T2" s="143"/>
-      <c r="U2" s="143"/>
-      <c r="V2" s="143"/>
-      <c r="W2" s="143"/>
-      <c r="X2" s="143"/>
-      <c r="Y2" s="143"/>
-      <c r="Z2" s="144"/>
-      <c r="AA2" s="121" t="s">
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97"/>
+      <c r="R2" s="98"/>
+      <c r="S2" s="105"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="106"/>
+      <c r="W2" s="106"/>
+      <c r="X2" s="106"/>
+      <c r="Y2" s="106"/>
+      <c r="Z2" s="107"/>
+      <c r="AA2" s="84" t="s">
         <v>282</v>
       </c>
-      <c r="AB2" s="123"/>
-      <c r="AC2" s="127" t="str">
+      <c r="AB2" s="86"/>
+      <c r="AC2" s="90" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="128"/>
-      <c r="AE2" s="128"/>
-      <c r="AF2" s="129"/>
-      <c r="AG2" s="115">
+      <c r="AD2" s="91"/>
+      <c r="AE2" s="91"/>
+      <c r="AF2" s="92"/>
+      <c r="AG2" s="78">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>45461</v>
       </c>
-      <c r="AH2" s="116"/>
-      <c r="AI2" s="117"/>
+      <c r="AH2" s="79"/>
+      <c r="AI2" s="80"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
@@ -7734,43 +7734,43 @@
       <c r="AN2" s="2"/>
     </row>
     <row r="3" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="121" t="s">
+      <c r="A3" s="84" t="s">
         <v>283</v>
       </c>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="125"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="125"/>
-      <c r="K3" s="125"/>
-      <c r="L3" s="125"/>
-      <c r="M3" s="125"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="137"/>
-      <c r="Q3" s="137"/>
-      <c r="R3" s="138"/>
-      <c r="S3" s="145"/>
-      <c r="T3" s="146"/>
-      <c r="U3" s="146"/>
-      <c r="V3" s="146"/>
-      <c r="W3" s="146"/>
-      <c r="X3" s="146"/>
-      <c r="Y3" s="146"/>
-      <c r="Z3" s="147"/>
-      <c r="AA3" s="121"/>
-      <c r="AB3" s="123"/>
-      <c r="AC3" s="148"/>
-      <c r="AD3" s="149"/>
-      <c r="AE3" s="149"/>
-      <c r="AF3" s="150"/>
-      <c r="AG3" s="115"/>
-      <c r="AH3" s="116"/>
-      <c r="AI3" s="117"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="99"/>
+      <c r="P3" s="100"/>
+      <c r="Q3" s="100"/>
+      <c r="R3" s="101"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="109"/>
+      <c r="U3" s="109"/>
+      <c r="V3" s="109"/>
+      <c r="W3" s="109"/>
+      <c r="X3" s="109"/>
+      <c r="Y3" s="109"/>
+      <c r="Z3" s="110"/>
+      <c r="AA3" s="84"/>
+      <c r="AB3" s="86"/>
+      <c r="AC3" s="111"/>
+      <c r="AD3" s="112"/>
+      <c r="AE3" s="112"/>
+      <c r="AF3" s="113"/>
+      <c r="AG3" s="78"/>
+      <c r="AH3" s="79"/>
+      <c r="AI3" s="80"/>
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
@@ -7807,1084 +7807,1240 @@
       <c r="A7" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="B7" s="118" t="s">
+      <c r="B7" s="81" t="s">
         <v>186</v>
       </c>
-      <c r="C7" s="119"/>
-      <c r="D7" s="118" t="s">
+      <c r="C7" s="82"/>
+      <c r="D7" s="81" t="s">
         <v>187</v>
       </c>
-      <c r="E7" s="120"/>
-      <c r="F7" s="119"/>
-      <c r="G7" s="118" t="s">
+      <c r="E7" s="83"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="81" t="s">
         <v>188</v>
       </c>
-      <c r="H7" s="120"/>
-      <c r="I7" s="119"/>
-      <c r="J7" s="118" t="s">
+      <c r="H7" s="83"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="81" t="s">
         <v>285</v>
       </c>
-      <c r="K7" s="120"/>
-      <c r="L7" s="120"/>
-      <c r="M7" s="120"/>
-      <c r="N7" s="120"/>
-      <c r="O7" s="120"/>
-      <c r="P7" s="119"/>
-      <c r="Q7" s="118" t="s">
+      <c r="K7" s="83"/>
+      <c r="L7" s="83"/>
+      <c r="M7" s="83"/>
+      <c r="N7" s="83"/>
+      <c r="O7" s="83"/>
+      <c r="P7" s="82"/>
+      <c r="Q7" s="81" t="s">
         <v>189</v>
       </c>
-      <c r="R7" s="120"/>
-      <c r="S7" s="120"/>
-      <c r="T7" s="120"/>
-      <c r="U7" s="120"/>
-      <c r="V7" s="120"/>
-      <c r="W7" s="120"/>
-      <c r="X7" s="120"/>
-      <c r="Y7" s="120"/>
-      <c r="Z7" s="120"/>
-      <c r="AA7" s="120"/>
-      <c r="AB7" s="120"/>
-      <c r="AC7" s="120"/>
-      <c r="AD7" s="120"/>
-      <c r="AE7" s="119"/>
-      <c r="AF7" s="118" t="s">
+      <c r="R7" s="83"/>
+      <c r="S7" s="83"/>
+      <c r="T7" s="83"/>
+      <c r="U7" s="83"/>
+      <c r="V7" s="83"/>
+      <c r="W7" s="83"/>
+      <c r="X7" s="83"/>
+      <c r="Y7" s="83"/>
+      <c r="Z7" s="83"/>
+      <c r="AA7" s="83"/>
+      <c r="AB7" s="83"/>
+      <c r="AC7" s="83"/>
+      <c r="AD7" s="83"/>
+      <c r="AE7" s="82"/>
+      <c r="AF7" s="81" t="s">
         <v>190</v>
       </c>
-      <c r="AG7" s="120"/>
-      <c r="AH7" s="120"/>
-      <c r="AI7" s="119"/>
+      <c r="AG7" s="83"/>
+      <c r="AH7" s="83"/>
+      <c r="AI7" s="82"/>
     </row>
     <row r="8" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="101" t="s">
+      <c r="B8" s="126" t="s">
         <v>286</v>
       </c>
-      <c r="C8" s="102"/>
-      <c r="D8" s="103">
+      <c r="C8" s="127"/>
+      <c r="D8" s="128">
         <v>43336</v>
       </c>
-      <c r="E8" s="104"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="106" t="s">
+      <c r="E8" s="129"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="131" t="s">
         <v>287</v>
       </c>
-      <c r="H8" s="107"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="109" t="s">
+      <c r="H8" s="132"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="134" t="s">
         <v>288</v>
       </c>
-      <c r="K8" s="110"/>
-      <c r="L8" s="110"/>
-      <c r="M8" s="110"/>
-      <c r="N8" s="110"/>
-      <c r="O8" s="110"/>
-      <c r="P8" s="111"/>
-      <c r="Q8" s="112" t="s">
+      <c r="K8" s="135"/>
+      <c r="L8" s="135"/>
+      <c r="M8" s="135"/>
+      <c r="N8" s="135"/>
+      <c r="O8" s="135"/>
+      <c r="P8" s="136"/>
+      <c r="Q8" s="137" t="s">
         <v>289</v>
       </c>
-      <c r="R8" s="113"/>
-      <c r="S8" s="113"/>
-      <c r="T8" s="113"/>
-      <c r="U8" s="113"/>
-      <c r="V8" s="113"/>
-      <c r="W8" s="113"/>
-      <c r="X8" s="113"/>
-      <c r="Y8" s="113"/>
-      <c r="Z8" s="113"/>
-      <c r="AA8" s="113"/>
-      <c r="AB8" s="113"/>
-      <c r="AC8" s="113"/>
-      <c r="AD8" s="113"/>
-      <c r="AE8" s="114"/>
-      <c r="AF8" s="109" t="s">
+      <c r="R8" s="138"/>
+      <c r="S8" s="138"/>
+      <c r="T8" s="138"/>
+      <c r="U8" s="138"/>
+      <c r="V8" s="138"/>
+      <c r="W8" s="138"/>
+      <c r="X8" s="138"/>
+      <c r="Y8" s="138"/>
+      <c r="Z8" s="138"/>
+      <c r="AA8" s="138"/>
+      <c r="AB8" s="138"/>
+      <c r="AC8" s="138"/>
+      <c r="AD8" s="138"/>
+      <c r="AE8" s="139"/>
+      <c r="AF8" s="134" t="s">
         <v>290</v>
       </c>
-      <c r="AG8" s="110"/>
-      <c r="AH8" s="110"/>
-      <c r="AI8" s="111"/>
+      <c r="AG8" s="135"/>
+      <c r="AH8" s="135"/>
+      <c r="AI8" s="136"/>
     </row>
     <row r="9" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="29">
         <v>2</v>
       </c>
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="114" t="s">
         <v>355</v>
       </c>
-      <c r="C9" s="79"/>
-      <c r="D9" s="80">
+      <c r="C9" s="115"/>
+      <c r="D9" s="116">
         <v>43896</v>
       </c>
-      <c r="E9" s="81"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="80" t="s">
+      <c r="E9" s="117"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="116" t="s">
         <v>337</v>
       </c>
-      <c r="H9" s="83"/>
-      <c r="I9" s="79"/>
-      <c r="J9" s="84" t="s">
+      <c r="H9" s="119"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="120" t="s">
         <v>338</v>
       </c>
-      <c r="K9" s="85"/>
-      <c r="L9" s="85"/>
-      <c r="M9" s="85"/>
-      <c r="N9" s="85"/>
-      <c r="O9" s="85"/>
-      <c r="P9" s="86"/>
-      <c r="Q9" s="87" t="s">
+      <c r="K9" s="121"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="122"/>
+      <c r="Q9" s="123" t="s">
         <v>353</v>
       </c>
-      <c r="R9" s="88"/>
-      <c r="S9" s="88"/>
-      <c r="T9" s="88"/>
-      <c r="U9" s="88"/>
-      <c r="V9" s="88"/>
-      <c r="W9" s="88"/>
-      <c r="X9" s="88"/>
-      <c r="Y9" s="88"/>
-      <c r="Z9" s="88"/>
-      <c r="AA9" s="88"/>
-      <c r="AB9" s="88"/>
-      <c r="AC9" s="88"/>
-      <c r="AD9" s="88"/>
-      <c r="AE9" s="89"/>
-      <c r="AF9" s="84" t="s">
+      <c r="R9" s="124"/>
+      <c r="S9" s="124"/>
+      <c r="T9" s="124"/>
+      <c r="U9" s="124"/>
+      <c r="V9" s="124"/>
+      <c r="W9" s="124"/>
+      <c r="X9" s="124"/>
+      <c r="Y9" s="124"/>
+      <c r="Z9" s="124"/>
+      <c r="AA9" s="124"/>
+      <c r="AB9" s="124"/>
+      <c r="AC9" s="124"/>
+      <c r="AD9" s="124"/>
+      <c r="AE9" s="125"/>
+      <c r="AF9" s="120" t="s">
         <v>290</v>
       </c>
-      <c r="AG9" s="85"/>
-      <c r="AH9" s="85"/>
-      <c r="AI9" s="86"/>
+      <c r="AG9" s="121"/>
+      <c r="AH9" s="121"/>
+      <c r="AI9" s="122"/>
     </row>
     <row r="10" spans="1:40" s="9" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="29">
         <v>3</v>
       </c>
-      <c r="B10" s="78" t="s">
+      <c r="B10" s="114" t="s">
         <v>356</v>
       </c>
-      <c r="C10" s="79"/>
-      <c r="D10" s="80">
+      <c r="C10" s="115"/>
+      <c r="D10" s="116">
         <v>44455</v>
       </c>
-      <c r="E10" s="81"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="80" t="s">
+      <c r="E10" s="117"/>
+      <c r="F10" s="118"/>
+      <c r="G10" s="116" t="s">
         <v>337</v>
       </c>
-      <c r="H10" s="83"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="84" t="s">
+      <c r="H10" s="119"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="120" t="s">
         <v>338</v>
       </c>
-      <c r="K10" s="85"/>
-      <c r="L10" s="85"/>
-      <c r="M10" s="85"/>
-      <c r="N10" s="85"/>
-      <c r="O10" s="85"/>
-      <c r="P10" s="86"/>
-      <c r="Q10" s="87" t="s">
+      <c r="K10" s="121"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="121"/>
+      <c r="P10" s="122"/>
+      <c r="Q10" s="123" t="s">
         <v>357</v>
       </c>
-      <c r="R10" s="88"/>
-      <c r="S10" s="88"/>
-      <c r="T10" s="88"/>
-      <c r="U10" s="88"/>
-      <c r="V10" s="88"/>
-      <c r="W10" s="88"/>
-      <c r="X10" s="88"/>
-      <c r="Y10" s="88"/>
-      <c r="Z10" s="88"/>
-      <c r="AA10" s="88"/>
-      <c r="AB10" s="88"/>
-      <c r="AC10" s="88"/>
-      <c r="AD10" s="88"/>
-      <c r="AE10" s="89"/>
-      <c r="AF10" s="84" t="s">
+      <c r="R10" s="124"/>
+      <c r="S10" s="124"/>
+      <c r="T10" s="124"/>
+      <c r="U10" s="124"/>
+      <c r="V10" s="124"/>
+      <c r="W10" s="124"/>
+      <c r="X10" s="124"/>
+      <c r="Y10" s="124"/>
+      <c r="Z10" s="124"/>
+      <c r="AA10" s="124"/>
+      <c r="AB10" s="124"/>
+      <c r="AC10" s="124"/>
+      <c r="AD10" s="124"/>
+      <c r="AE10" s="125"/>
+      <c r="AF10" s="120" t="s">
         <v>290</v>
       </c>
-      <c r="AG10" s="85"/>
-      <c r="AH10" s="85"/>
-      <c r="AI10" s="86"/>
+      <c r="AG10" s="121"/>
+      <c r="AH10" s="121"/>
+      <c r="AI10" s="122"/>
     </row>
     <row r="11" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="76">
         <v>4</v>
       </c>
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="140" t="s">
+        <v>402</v>
+      </c>
+      <c r="C11" s="141"/>
+      <c r="D11" s="142">
+        <v>45461</v>
+      </c>
+      <c r="E11" s="143"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="114" t="s">
+        <v>405</v>
+      </c>
+      <c r="H11" s="119"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="120" t="s">
         <v>403</v>
       </c>
-      <c r="C11" s="97"/>
-      <c r="D11" s="98">
-        <v>45461</v>
-      </c>
-      <c r="E11" s="99"/>
-      <c r="F11" s="100"/>
-      <c r="G11" s="78" t="s">
-        <v>406</v>
-      </c>
-      <c r="H11" s="83"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="84" t="s">
+      <c r="K11" s="121"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="121"/>
+      <c r="P11" s="122"/>
+      <c r="Q11" s="123" t="s">
         <v>404</v>
       </c>
-      <c r="K11" s="85"/>
-      <c r="L11" s="85"/>
-      <c r="M11" s="85"/>
-      <c r="N11" s="85"/>
-      <c r="O11" s="85"/>
-      <c r="P11" s="86"/>
-      <c r="Q11" s="87" t="s">
-        <v>405</v>
-      </c>
-      <c r="R11" s="88"/>
-      <c r="S11" s="88"/>
-      <c r="T11" s="88"/>
-      <c r="U11" s="88"/>
-      <c r="V11" s="88"/>
-      <c r="W11" s="88"/>
-      <c r="X11" s="88"/>
-      <c r="Y11" s="88"/>
-      <c r="Z11" s="88"/>
-      <c r="AA11" s="88"/>
-      <c r="AB11" s="88"/>
-      <c r="AC11" s="88"/>
-      <c r="AD11" s="88"/>
-      <c r="AE11" s="89"/>
-      <c r="AF11" s="84" t="s">
+      <c r="R11" s="124"/>
+      <c r="S11" s="124"/>
+      <c r="T11" s="124"/>
+      <c r="U11" s="124"/>
+      <c r="V11" s="124"/>
+      <c r="W11" s="124"/>
+      <c r="X11" s="124"/>
+      <c r="Y11" s="124"/>
+      <c r="Z11" s="124"/>
+      <c r="AA11" s="124"/>
+      <c r="AB11" s="124"/>
+      <c r="AC11" s="124"/>
+      <c r="AD11" s="124"/>
+      <c r="AE11" s="125"/>
+      <c r="AF11" s="120" t="s">
         <v>290</v>
       </c>
-      <c r="AG11" s="85"/>
-      <c r="AH11" s="85"/>
-      <c r="AI11" s="86"/>
+      <c r="AG11" s="121"/>
+      <c r="AH11" s="121"/>
+      <c r="AI11" s="122"/>
     </row>
     <row r="12" spans="1:40" s="9" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="28"/>
-      <c r="B12" s="91"/>
-      <c r="C12" s="92"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="78" t="s">
+      <c r="B12" s="145"/>
+      <c r="C12" s="146"/>
+      <c r="D12" s="147"/>
+      <c r="E12" s="148"/>
+      <c r="F12" s="149"/>
+      <c r="G12" s="114" t="s">
         <v>337</v>
       </c>
-      <c r="H12" s="83"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="87" t="s">
+      <c r="H12" s="119"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="123" t="s">
+        <v>406</v>
+      </c>
+      <c r="K12" s="121"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="121"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="122"/>
+      <c r="Q12" s="123" t="s">
         <v>407</v>
       </c>
-      <c r="K12" s="85"/>
-      <c r="L12" s="85"/>
-      <c r="M12" s="85"/>
-      <c r="N12" s="85"/>
-      <c r="O12" s="85"/>
-      <c r="P12" s="86"/>
-      <c r="Q12" s="87" t="s">
-        <v>408</v>
-      </c>
-      <c r="R12" s="88"/>
-      <c r="S12" s="88"/>
-      <c r="T12" s="88"/>
-      <c r="U12" s="88"/>
-      <c r="V12" s="88"/>
-      <c r="W12" s="88"/>
-      <c r="X12" s="88"/>
-      <c r="Y12" s="88"/>
-      <c r="Z12" s="88"/>
-      <c r="AA12" s="88"/>
-      <c r="AB12" s="88"/>
-      <c r="AC12" s="88"/>
-      <c r="AD12" s="88"/>
-      <c r="AE12" s="89"/>
-      <c r="AF12" s="84" t="s">
+      <c r="R12" s="124"/>
+      <c r="S12" s="124"/>
+      <c r="T12" s="124"/>
+      <c r="U12" s="124"/>
+      <c r="V12" s="124"/>
+      <c r="W12" s="124"/>
+      <c r="X12" s="124"/>
+      <c r="Y12" s="124"/>
+      <c r="Z12" s="124"/>
+      <c r="AA12" s="124"/>
+      <c r="AB12" s="124"/>
+      <c r="AC12" s="124"/>
+      <c r="AD12" s="124"/>
+      <c r="AE12" s="125"/>
+      <c r="AF12" s="120" t="s">
         <v>290</v>
       </c>
-      <c r="AG12" s="85"/>
-      <c r="AH12" s="85"/>
-      <c r="AI12" s="86"/>
+      <c r="AG12" s="121"/>
+      <c r="AH12" s="121"/>
+      <c r="AI12" s="122"/>
     </row>
     <row r="13" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="29"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="80"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="84"/>
-      <c r="K13" s="85"/>
-      <c r="L13" s="85"/>
-      <c r="M13" s="85"/>
-      <c r="N13" s="85"/>
-      <c r="O13" s="85"/>
-      <c r="P13" s="86"/>
-      <c r="Q13" s="87"/>
-      <c r="R13" s="88"/>
-      <c r="S13" s="88"/>
-      <c r="T13" s="88"/>
-      <c r="U13" s="88"/>
-      <c r="V13" s="88"/>
-      <c r="W13" s="88"/>
-      <c r="X13" s="88"/>
-      <c r="Y13" s="88"/>
-      <c r="Z13" s="88"/>
-      <c r="AA13" s="88"/>
-      <c r="AB13" s="88"/>
-      <c r="AC13" s="88"/>
-      <c r="AD13" s="88"/>
-      <c r="AE13" s="89"/>
-      <c r="AF13" s="84"/>
-      <c r="AG13" s="85"/>
-      <c r="AH13" s="85"/>
-      <c r="AI13" s="86"/>
+      <c r="B13" s="114"/>
+      <c r="C13" s="115"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="114"/>
+      <c r="H13" s="119"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="120"/>
+      <c r="K13" s="121"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="121"/>
+      <c r="P13" s="122"/>
+      <c r="Q13" s="123"/>
+      <c r="R13" s="124"/>
+      <c r="S13" s="124"/>
+      <c r="T13" s="124"/>
+      <c r="U13" s="124"/>
+      <c r="V13" s="124"/>
+      <c r="W13" s="124"/>
+      <c r="X13" s="124"/>
+      <c r="Y13" s="124"/>
+      <c r="Z13" s="124"/>
+      <c r="AA13" s="124"/>
+      <c r="AB13" s="124"/>
+      <c r="AC13" s="124"/>
+      <c r="AD13" s="124"/>
+      <c r="AE13" s="125"/>
+      <c r="AF13" s="120"/>
+      <c r="AG13" s="121"/>
+      <c r="AH13" s="121"/>
+      <c r="AI13" s="122"/>
     </row>
     <row r="14" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="29"/>
-      <c r="B14" s="78"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="82"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="84"/>
-      <c r="K14" s="85"/>
-      <c r="L14" s="85"/>
-      <c r="M14" s="85"/>
-      <c r="N14" s="85"/>
-      <c r="O14" s="85"/>
-      <c r="P14" s="86"/>
-      <c r="Q14" s="87"/>
-      <c r="R14" s="88"/>
-      <c r="S14" s="88"/>
-      <c r="T14" s="88"/>
-      <c r="U14" s="88"/>
-      <c r="V14" s="88"/>
-      <c r="W14" s="88"/>
-      <c r="X14" s="88"/>
-      <c r="Y14" s="88"/>
-      <c r="Z14" s="88"/>
-      <c r="AA14" s="88"/>
-      <c r="AB14" s="88"/>
-      <c r="AC14" s="88"/>
-      <c r="AD14" s="88"/>
-      <c r="AE14" s="89"/>
-      <c r="AF14" s="84"/>
-      <c r="AG14" s="85"/>
-      <c r="AH14" s="85"/>
-      <c r="AI14" s="86"/>
+      <c r="B14" s="114"/>
+      <c r="C14" s="115"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="117"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="120"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="122"/>
+      <c r="Q14" s="123"/>
+      <c r="R14" s="124"/>
+      <c r="S14" s="124"/>
+      <c r="T14" s="124"/>
+      <c r="U14" s="124"/>
+      <c r="V14" s="124"/>
+      <c r="W14" s="124"/>
+      <c r="X14" s="124"/>
+      <c r="Y14" s="124"/>
+      <c r="Z14" s="124"/>
+      <c r="AA14" s="124"/>
+      <c r="AB14" s="124"/>
+      <c r="AC14" s="124"/>
+      <c r="AD14" s="124"/>
+      <c r="AE14" s="125"/>
+      <c r="AF14" s="120"/>
+      <c r="AG14" s="121"/>
+      <c r="AH14" s="121"/>
+      <c r="AI14" s="122"/>
     </row>
     <row r="15" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="29"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="85"/>
-      <c r="L15" s="85"/>
-      <c r="M15" s="85"/>
-      <c r="N15" s="85"/>
-      <c r="O15" s="85"/>
-      <c r="P15" s="86"/>
-      <c r="Q15" s="87"/>
-      <c r="R15" s="88"/>
-      <c r="S15" s="88"/>
-      <c r="T15" s="88"/>
-      <c r="U15" s="88"/>
-      <c r="V15" s="88"/>
-      <c r="W15" s="88"/>
-      <c r="X15" s="88"/>
-      <c r="Y15" s="88"/>
-      <c r="Z15" s="88"/>
-      <c r="AA15" s="88"/>
-      <c r="AB15" s="88"/>
-      <c r="AC15" s="88"/>
-      <c r="AD15" s="88"/>
-      <c r="AE15" s="89"/>
-      <c r="AF15" s="84"/>
-      <c r="AG15" s="85"/>
-      <c r="AH15" s="85"/>
-      <c r="AI15" s="86"/>
+      <c r="B15" s="114"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="120"/>
+      <c r="K15" s="121"/>
+      <c r="L15" s="121"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="121"/>
+      <c r="P15" s="122"/>
+      <c r="Q15" s="123"/>
+      <c r="R15" s="124"/>
+      <c r="S15" s="124"/>
+      <c r="T15" s="124"/>
+      <c r="U15" s="124"/>
+      <c r="V15" s="124"/>
+      <c r="W15" s="124"/>
+      <c r="X15" s="124"/>
+      <c r="Y15" s="124"/>
+      <c r="Z15" s="124"/>
+      <c r="AA15" s="124"/>
+      <c r="AB15" s="124"/>
+      <c r="AC15" s="124"/>
+      <c r="AD15" s="124"/>
+      <c r="AE15" s="125"/>
+      <c r="AF15" s="120"/>
+      <c r="AG15" s="121"/>
+      <c r="AH15" s="121"/>
+      <c r="AI15" s="122"/>
     </row>
     <row r="16" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="29"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="84"/>
-      <c r="K16" s="85"/>
-      <c r="L16" s="85"/>
-      <c r="M16" s="85"/>
-      <c r="N16" s="85"/>
-      <c r="O16" s="85"/>
-      <c r="P16" s="86"/>
-      <c r="Q16" s="87"/>
-      <c r="R16" s="88"/>
-      <c r="S16" s="88"/>
-      <c r="T16" s="88"/>
-      <c r="U16" s="88"/>
-      <c r="V16" s="88"/>
-      <c r="W16" s="88"/>
-      <c r="X16" s="88"/>
-      <c r="Y16" s="88"/>
-      <c r="Z16" s="88"/>
-      <c r="AA16" s="88"/>
-      <c r="AB16" s="88"/>
-      <c r="AC16" s="88"/>
-      <c r="AD16" s="88"/>
-      <c r="AE16" s="89"/>
-      <c r="AF16" s="84"/>
-      <c r="AG16" s="85"/>
-      <c r="AH16" s="85"/>
-      <c r="AI16" s="86"/>
+      <c r="B16" s="114"/>
+      <c r="C16" s="115"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="118"/>
+      <c r="G16" s="114"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="115"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="121"/>
+      <c r="L16" s="121"/>
+      <c r="M16" s="121"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="121"/>
+      <c r="P16" s="122"/>
+      <c r="Q16" s="123"/>
+      <c r="R16" s="124"/>
+      <c r="S16" s="124"/>
+      <c r="T16" s="124"/>
+      <c r="U16" s="124"/>
+      <c r="V16" s="124"/>
+      <c r="W16" s="124"/>
+      <c r="X16" s="124"/>
+      <c r="Y16" s="124"/>
+      <c r="Z16" s="124"/>
+      <c r="AA16" s="124"/>
+      <c r="AB16" s="124"/>
+      <c r="AC16" s="124"/>
+      <c r="AD16" s="124"/>
+      <c r="AE16" s="125"/>
+      <c r="AF16" s="120"/>
+      <c r="AG16" s="121"/>
+      <c r="AH16" s="121"/>
+      <c r="AI16" s="122"/>
     </row>
     <row r="17" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="29"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="82"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="84"/>
-      <c r="K17" s="85"/>
-      <c r="L17" s="85"/>
-      <c r="M17" s="85"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="85"/>
-      <c r="P17" s="86"/>
-      <c r="Q17" s="87"/>
-      <c r="R17" s="88"/>
-      <c r="S17" s="88"/>
-      <c r="T17" s="88"/>
-      <c r="U17" s="88"/>
-      <c r="V17" s="88"/>
-      <c r="W17" s="88"/>
-      <c r="X17" s="88"/>
-      <c r="Y17" s="88"/>
-      <c r="Z17" s="88"/>
-      <c r="AA17" s="88"/>
-      <c r="AB17" s="88"/>
-      <c r="AC17" s="88"/>
-      <c r="AD17" s="88"/>
-      <c r="AE17" s="89"/>
-      <c r="AF17" s="84"/>
-      <c r="AG17" s="85"/>
-      <c r="AH17" s="85"/>
-      <c r="AI17" s="86"/>
+      <c r="B17" s="114"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="120"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="121"/>
+      <c r="P17" s="122"/>
+      <c r="Q17" s="123"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="124"/>
+      <c r="T17" s="124"/>
+      <c r="U17" s="124"/>
+      <c r="V17" s="124"/>
+      <c r="W17" s="124"/>
+      <c r="X17" s="124"/>
+      <c r="Y17" s="124"/>
+      <c r="Z17" s="124"/>
+      <c r="AA17" s="124"/>
+      <c r="AB17" s="124"/>
+      <c r="AC17" s="124"/>
+      <c r="AD17" s="124"/>
+      <c r="AE17" s="125"/>
+      <c r="AF17" s="120"/>
+      <c r="AG17" s="121"/>
+      <c r="AH17" s="121"/>
+      <c r="AI17" s="122"/>
     </row>
     <row r="18" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="29"/>
-      <c r="B18" s="78"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="82"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="84"/>
-      <c r="K18" s="85"/>
-      <c r="L18" s="85"/>
-      <c r="M18" s="85"/>
-      <c r="N18" s="85"/>
-      <c r="O18" s="85"/>
-      <c r="P18" s="86"/>
-      <c r="Q18" s="87"/>
-      <c r="R18" s="88"/>
-      <c r="S18" s="88"/>
-      <c r="T18" s="88"/>
-      <c r="U18" s="88"/>
-      <c r="V18" s="88"/>
-      <c r="W18" s="88"/>
-      <c r="X18" s="88"/>
-      <c r="Y18" s="88"/>
-      <c r="Z18" s="88"/>
-      <c r="AA18" s="88"/>
-      <c r="AB18" s="88"/>
-      <c r="AC18" s="88"/>
-      <c r="AD18" s="88"/>
-      <c r="AE18" s="89"/>
-      <c r="AF18" s="84"/>
-      <c r="AG18" s="85"/>
-      <c r="AH18" s="85"/>
-      <c r="AI18" s="86"/>
+      <c r="B18" s="114"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="114"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="121"/>
+      <c r="L18" s="121"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="121"/>
+      <c r="P18" s="122"/>
+      <c r="Q18" s="123"/>
+      <c r="R18" s="124"/>
+      <c r="S18" s="124"/>
+      <c r="T18" s="124"/>
+      <c r="U18" s="124"/>
+      <c r="V18" s="124"/>
+      <c r="W18" s="124"/>
+      <c r="X18" s="124"/>
+      <c r="Y18" s="124"/>
+      <c r="Z18" s="124"/>
+      <c r="AA18" s="124"/>
+      <c r="AB18" s="124"/>
+      <c r="AC18" s="124"/>
+      <c r="AD18" s="124"/>
+      <c r="AE18" s="125"/>
+      <c r="AF18" s="120"/>
+      <c r="AG18" s="121"/>
+      <c r="AH18" s="121"/>
+      <c r="AI18" s="122"/>
     </row>
     <row r="19" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="29"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="82"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="84"/>
-      <c r="K19" s="85"/>
-      <c r="L19" s="85"/>
-      <c r="M19" s="85"/>
-      <c r="N19" s="85"/>
-      <c r="O19" s="85"/>
-      <c r="P19" s="86"/>
-      <c r="Q19" s="87"/>
-      <c r="R19" s="88"/>
-      <c r="S19" s="88"/>
-      <c r="T19" s="88"/>
-      <c r="U19" s="88"/>
-      <c r="V19" s="88"/>
-      <c r="W19" s="88"/>
-      <c r="X19" s="88"/>
-      <c r="Y19" s="88"/>
-      <c r="Z19" s="88"/>
-      <c r="AA19" s="88"/>
-      <c r="AB19" s="88"/>
-      <c r="AC19" s="88"/>
-      <c r="AD19" s="88"/>
-      <c r="AE19" s="89"/>
-      <c r="AF19" s="84"/>
-      <c r="AG19" s="85"/>
-      <c r="AH19" s="85"/>
-      <c r="AI19" s="86"/>
+      <c r="B19" s="114"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="114"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="115"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="121"/>
+      <c r="L19" s="121"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="121"/>
+      <c r="P19" s="122"/>
+      <c r="Q19" s="123"/>
+      <c r="R19" s="124"/>
+      <c r="S19" s="124"/>
+      <c r="T19" s="124"/>
+      <c r="U19" s="124"/>
+      <c r="V19" s="124"/>
+      <c r="W19" s="124"/>
+      <c r="X19" s="124"/>
+      <c r="Y19" s="124"/>
+      <c r="Z19" s="124"/>
+      <c r="AA19" s="124"/>
+      <c r="AB19" s="124"/>
+      <c r="AC19" s="124"/>
+      <c r="AD19" s="124"/>
+      <c r="AE19" s="125"/>
+      <c r="AF19" s="120"/>
+      <c r="AG19" s="121"/>
+      <c r="AH19" s="121"/>
+      <c r="AI19" s="122"/>
     </row>
     <row r="20" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="29"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="84"/>
-      <c r="K20" s="85"/>
-      <c r="L20" s="85"/>
-      <c r="M20" s="85"/>
-      <c r="N20" s="85"/>
-      <c r="O20" s="85"/>
-      <c r="P20" s="86"/>
-      <c r="Q20" s="87"/>
-      <c r="R20" s="88"/>
-      <c r="S20" s="88"/>
-      <c r="T20" s="88"/>
-      <c r="U20" s="88"/>
-      <c r="V20" s="88"/>
-      <c r="W20" s="88"/>
-      <c r="X20" s="88"/>
-      <c r="Y20" s="88"/>
-      <c r="Z20" s="88"/>
-      <c r="AA20" s="88"/>
-      <c r="AB20" s="88"/>
-      <c r="AC20" s="88"/>
-      <c r="AD20" s="88"/>
-      <c r="AE20" s="89"/>
-      <c r="AF20" s="84"/>
-      <c r="AG20" s="85"/>
-      <c r="AH20" s="85"/>
-      <c r="AI20" s="86"/>
+      <c r="B20" s="114"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="114"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="115"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="121"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="121"/>
+      <c r="P20" s="122"/>
+      <c r="Q20" s="123"/>
+      <c r="R20" s="124"/>
+      <c r="S20" s="124"/>
+      <c r="T20" s="124"/>
+      <c r="U20" s="124"/>
+      <c r="V20" s="124"/>
+      <c r="W20" s="124"/>
+      <c r="X20" s="124"/>
+      <c r="Y20" s="124"/>
+      <c r="Z20" s="124"/>
+      <c r="AA20" s="124"/>
+      <c r="AB20" s="124"/>
+      <c r="AC20" s="124"/>
+      <c r="AD20" s="124"/>
+      <c r="AE20" s="125"/>
+      <c r="AF20" s="120"/>
+      <c r="AG20" s="121"/>
+      <c r="AH20" s="121"/>
+      <c r="AI20" s="122"/>
     </row>
     <row r="21" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="29"/>
-      <c r="B21" s="78"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="78"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="84"/>
-      <c r="K21" s="85"/>
-      <c r="L21" s="85"/>
-      <c r="M21" s="85"/>
-      <c r="N21" s="85"/>
-      <c r="O21" s="85"/>
-      <c r="P21" s="86"/>
-      <c r="Q21" s="87"/>
-      <c r="R21" s="88"/>
-      <c r="S21" s="88"/>
-      <c r="T21" s="88"/>
-      <c r="U21" s="88"/>
-      <c r="V21" s="88"/>
-      <c r="W21" s="88"/>
-      <c r="X21" s="88"/>
-      <c r="Y21" s="88"/>
-      <c r="Z21" s="88"/>
-      <c r="AA21" s="88"/>
-      <c r="AB21" s="88"/>
-      <c r="AC21" s="88"/>
-      <c r="AD21" s="88"/>
-      <c r="AE21" s="89"/>
-      <c r="AF21" s="84"/>
-      <c r="AG21" s="85"/>
-      <c r="AH21" s="85"/>
-      <c r="AI21" s="86"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="115"/>
+      <c r="D21" s="116"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="114"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="115"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="121"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="121"/>
+      <c r="P21" s="122"/>
+      <c r="Q21" s="123"/>
+      <c r="R21" s="124"/>
+      <c r="S21" s="124"/>
+      <c r="T21" s="124"/>
+      <c r="U21" s="124"/>
+      <c r="V21" s="124"/>
+      <c r="W21" s="124"/>
+      <c r="X21" s="124"/>
+      <c r="Y21" s="124"/>
+      <c r="Z21" s="124"/>
+      <c r="AA21" s="124"/>
+      <c r="AB21" s="124"/>
+      <c r="AC21" s="124"/>
+      <c r="AD21" s="124"/>
+      <c r="AE21" s="125"/>
+      <c r="AF21" s="120"/>
+      <c r="AG21" s="121"/>
+      <c r="AH21" s="121"/>
+      <c r="AI21" s="122"/>
     </row>
     <row r="22" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="29"/>
-      <c r="B22" s="78"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="78"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="79"/>
-      <c r="J22" s="84"/>
-      <c r="K22" s="85"/>
-      <c r="L22" s="85"/>
-      <c r="M22" s="85"/>
-      <c r="N22" s="85"/>
-      <c r="O22" s="85"/>
-      <c r="P22" s="86"/>
-      <c r="Q22" s="87"/>
-      <c r="R22" s="88"/>
-      <c r="S22" s="88"/>
-      <c r="T22" s="88"/>
-      <c r="U22" s="88"/>
-      <c r="V22" s="88"/>
-      <c r="W22" s="88"/>
-      <c r="X22" s="88"/>
-      <c r="Y22" s="88"/>
-      <c r="Z22" s="88"/>
-      <c r="AA22" s="88"/>
-      <c r="AB22" s="88"/>
-      <c r="AC22" s="88"/>
-      <c r="AD22" s="88"/>
-      <c r="AE22" s="89"/>
-      <c r="AF22" s="84"/>
-      <c r="AG22" s="85"/>
-      <c r="AH22" s="85"/>
-      <c r="AI22" s="86"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="115"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="121"/>
+      <c r="L22" s="121"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="121"/>
+      <c r="P22" s="122"/>
+      <c r="Q22" s="123"/>
+      <c r="R22" s="124"/>
+      <c r="S22" s="124"/>
+      <c r="T22" s="124"/>
+      <c r="U22" s="124"/>
+      <c r="V22" s="124"/>
+      <c r="W22" s="124"/>
+      <c r="X22" s="124"/>
+      <c r="Y22" s="124"/>
+      <c r="Z22" s="124"/>
+      <c r="AA22" s="124"/>
+      <c r="AB22" s="124"/>
+      <c r="AC22" s="124"/>
+      <c r="AD22" s="124"/>
+      <c r="AE22" s="125"/>
+      <c r="AF22" s="120"/>
+      <c r="AG22" s="121"/>
+      <c r="AH22" s="121"/>
+      <c r="AI22" s="122"/>
     </row>
     <row r="23" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="29"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="82"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="84"/>
-      <c r="K23" s="85"/>
-      <c r="L23" s="85"/>
-      <c r="M23" s="85"/>
-      <c r="N23" s="85"/>
-      <c r="O23" s="85"/>
-      <c r="P23" s="86"/>
-      <c r="Q23" s="87"/>
-      <c r="R23" s="88"/>
-      <c r="S23" s="88"/>
-      <c r="T23" s="88"/>
-      <c r="U23" s="88"/>
-      <c r="V23" s="88"/>
-      <c r="W23" s="88"/>
-      <c r="X23" s="88"/>
-      <c r="Y23" s="88"/>
-      <c r="Z23" s="88"/>
-      <c r="AA23" s="88"/>
-      <c r="AB23" s="88"/>
-      <c r="AC23" s="88"/>
-      <c r="AD23" s="88"/>
-      <c r="AE23" s="89"/>
-      <c r="AF23" s="84"/>
-      <c r="AG23" s="85"/>
-      <c r="AH23" s="85"/>
-      <c r="AI23" s="86"/>
+      <c r="B23" s="114"/>
+      <c r="C23" s="115"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="114"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="115"/>
+      <c r="J23" s="120"/>
+      <c r="K23" s="121"/>
+      <c r="L23" s="121"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="121"/>
+      <c r="P23" s="122"/>
+      <c r="Q23" s="123"/>
+      <c r="R23" s="124"/>
+      <c r="S23" s="124"/>
+      <c r="T23" s="124"/>
+      <c r="U23" s="124"/>
+      <c r="V23" s="124"/>
+      <c r="W23" s="124"/>
+      <c r="X23" s="124"/>
+      <c r="Y23" s="124"/>
+      <c r="Z23" s="124"/>
+      <c r="AA23" s="124"/>
+      <c r="AB23" s="124"/>
+      <c r="AC23" s="124"/>
+      <c r="AD23" s="124"/>
+      <c r="AE23" s="125"/>
+      <c r="AF23" s="120"/>
+      <c r="AG23" s="121"/>
+      <c r="AH23" s="121"/>
+      <c r="AI23" s="122"/>
     </row>
     <row r="24" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="29"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="79"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="81"/>
-      <c r="F24" s="82"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="79"/>
-      <c r="J24" s="84"/>
-      <c r="K24" s="85"/>
-      <c r="L24" s="85"/>
-      <c r="M24" s="85"/>
-      <c r="N24" s="85"/>
-      <c r="O24" s="85"/>
-      <c r="P24" s="86"/>
-      <c r="Q24" s="87"/>
-      <c r="R24" s="88"/>
-      <c r="S24" s="88"/>
-      <c r="T24" s="88"/>
-      <c r="U24" s="88"/>
-      <c r="V24" s="88"/>
-      <c r="W24" s="88"/>
-      <c r="X24" s="88"/>
-      <c r="Y24" s="88"/>
-      <c r="Z24" s="88"/>
-      <c r="AA24" s="88"/>
-      <c r="AB24" s="88"/>
-      <c r="AC24" s="88"/>
-      <c r="AD24" s="88"/>
-      <c r="AE24" s="89"/>
-      <c r="AF24" s="84"/>
-      <c r="AG24" s="85"/>
-      <c r="AH24" s="85"/>
-      <c r="AI24" s="86"/>
+      <c r="B24" s="114"/>
+      <c r="C24" s="115"/>
+      <c r="D24" s="116"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="114"/>
+      <c r="H24" s="119"/>
+      <c r="I24" s="115"/>
+      <c r="J24" s="120"/>
+      <c r="K24" s="121"/>
+      <c r="L24" s="121"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="121"/>
+      <c r="P24" s="122"/>
+      <c r="Q24" s="123"/>
+      <c r="R24" s="124"/>
+      <c r="S24" s="124"/>
+      <c r="T24" s="124"/>
+      <c r="U24" s="124"/>
+      <c r="V24" s="124"/>
+      <c r="W24" s="124"/>
+      <c r="X24" s="124"/>
+      <c r="Y24" s="124"/>
+      <c r="Z24" s="124"/>
+      <c r="AA24" s="124"/>
+      <c r="AB24" s="124"/>
+      <c r="AC24" s="124"/>
+      <c r="AD24" s="124"/>
+      <c r="AE24" s="125"/>
+      <c r="AF24" s="120"/>
+      <c r="AG24" s="121"/>
+      <c r="AH24" s="121"/>
+      <c r="AI24" s="122"/>
     </row>
     <row r="25" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="29"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="81"/>
-      <c r="F25" s="82"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="84"/>
-      <c r="K25" s="85"/>
-      <c r="L25" s="85"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="85"/>
-      <c r="O25" s="85"/>
-      <c r="P25" s="86"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="88"/>
-      <c r="S25" s="88"/>
-      <c r="T25" s="88"/>
-      <c r="U25" s="88"/>
-      <c r="V25" s="88"/>
-      <c r="W25" s="88"/>
-      <c r="X25" s="88"/>
-      <c r="Y25" s="88"/>
-      <c r="Z25" s="88"/>
-      <c r="AA25" s="88"/>
-      <c r="AB25" s="88"/>
-      <c r="AC25" s="88"/>
-      <c r="AD25" s="88"/>
-      <c r="AE25" s="89"/>
-      <c r="AF25" s="84"/>
-      <c r="AG25" s="85"/>
-      <c r="AH25" s="85"/>
-      <c r="AI25" s="86"/>
+      <c r="B25" s="114"/>
+      <c r="C25" s="115"/>
+      <c r="D25" s="116"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="118"/>
+      <c r="G25" s="114"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="115"/>
+      <c r="J25" s="120"/>
+      <c r="K25" s="121"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="121"/>
+      <c r="P25" s="122"/>
+      <c r="Q25" s="123"/>
+      <c r="R25" s="124"/>
+      <c r="S25" s="124"/>
+      <c r="T25" s="124"/>
+      <c r="U25" s="124"/>
+      <c r="V25" s="124"/>
+      <c r="W25" s="124"/>
+      <c r="X25" s="124"/>
+      <c r="Y25" s="124"/>
+      <c r="Z25" s="124"/>
+      <c r="AA25" s="124"/>
+      <c r="AB25" s="124"/>
+      <c r="AC25" s="124"/>
+      <c r="AD25" s="124"/>
+      <c r="AE25" s="125"/>
+      <c r="AF25" s="120"/>
+      <c r="AG25" s="121"/>
+      <c r="AH25" s="121"/>
+      <c r="AI25" s="122"/>
     </row>
     <row r="26" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="29"/>
-      <c r="B26" s="78"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="81"/>
-      <c r="F26" s="82"/>
-      <c r="G26" s="78"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="79"/>
-      <c r="J26" s="84"/>
-      <c r="K26" s="85"/>
-      <c r="L26" s="85"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="85"/>
-      <c r="O26" s="85"/>
-      <c r="P26" s="86"/>
-      <c r="Q26" s="87"/>
-      <c r="R26" s="88"/>
-      <c r="S26" s="88"/>
-      <c r="T26" s="88"/>
-      <c r="U26" s="88"/>
-      <c r="V26" s="88"/>
-      <c r="W26" s="88"/>
-      <c r="X26" s="88"/>
-      <c r="Y26" s="88"/>
-      <c r="Z26" s="88"/>
-      <c r="AA26" s="88"/>
-      <c r="AB26" s="88"/>
-      <c r="AC26" s="88"/>
-      <c r="AD26" s="88"/>
-      <c r="AE26" s="89"/>
-      <c r="AF26" s="84"/>
-      <c r="AG26" s="85"/>
-      <c r="AH26" s="85"/>
-      <c r="AI26" s="86"/>
+      <c r="B26" s="114"/>
+      <c r="C26" s="115"/>
+      <c r="D26" s="116"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="114"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="115"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="121"/>
+      <c r="L26" s="121"/>
+      <c r="M26" s="121"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="121"/>
+      <c r="P26" s="122"/>
+      <c r="Q26" s="123"/>
+      <c r="R26" s="124"/>
+      <c r="S26" s="124"/>
+      <c r="T26" s="124"/>
+      <c r="U26" s="124"/>
+      <c r="V26" s="124"/>
+      <c r="W26" s="124"/>
+      <c r="X26" s="124"/>
+      <c r="Y26" s="124"/>
+      <c r="Z26" s="124"/>
+      <c r="AA26" s="124"/>
+      <c r="AB26" s="124"/>
+      <c r="AC26" s="124"/>
+      <c r="AD26" s="124"/>
+      <c r="AE26" s="125"/>
+      <c r="AF26" s="120"/>
+      <c r="AG26" s="121"/>
+      <c r="AH26" s="121"/>
+      <c r="AI26" s="122"/>
     </row>
     <row r="27" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="29"/>
-      <c r="B27" s="78"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="81"/>
-      <c r="F27" s="82"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="79"/>
-      <c r="J27" s="84"/>
-      <c r="K27" s="85"/>
-      <c r="L27" s="85"/>
-      <c r="M27" s="85"/>
-      <c r="N27" s="85"/>
-      <c r="O27" s="85"/>
-      <c r="P27" s="86"/>
-      <c r="Q27" s="87"/>
-      <c r="R27" s="88"/>
-      <c r="S27" s="88"/>
-      <c r="T27" s="88"/>
-      <c r="U27" s="88"/>
-      <c r="V27" s="88"/>
-      <c r="W27" s="88"/>
-      <c r="X27" s="88"/>
-      <c r="Y27" s="88"/>
-      <c r="Z27" s="88"/>
-      <c r="AA27" s="88"/>
-      <c r="AB27" s="88"/>
-      <c r="AC27" s="88"/>
-      <c r="AD27" s="88"/>
-      <c r="AE27" s="89"/>
-      <c r="AF27" s="84"/>
-      <c r="AG27" s="85"/>
-      <c r="AH27" s="85"/>
-      <c r="AI27" s="86"/>
+      <c r="B27" s="114"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="118"/>
+      <c r="G27" s="114"/>
+      <c r="H27" s="119"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="121"/>
+      <c r="L27" s="121"/>
+      <c r="M27" s="121"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="121"/>
+      <c r="P27" s="122"/>
+      <c r="Q27" s="123"/>
+      <c r="R27" s="124"/>
+      <c r="S27" s="124"/>
+      <c r="T27" s="124"/>
+      <c r="U27" s="124"/>
+      <c r="V27" s="124"/>
+      <c r="W27" s="124"/>
+      <c r="X27" s="124"/>
+      <c r="Y27" s="124"/>
+      <c r="Z27" s="124"/>
+      <c r="AA27" s="124"/>
+      <c r="AB27" s="124"/>
+      <c r="AC27" s="124"/>
+      <c r="AD27" s="124"/>
+      <c r="AE27" s="125"/>
+      <c r="AF27" s="120"/>
+      <c r="AG27" s="121"/>
+      <c r="AH27" s="121"/>
+      <c r="AI27" s="122"/>
     </row>
     <row r="28" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="29"/>
-      <c r="B28" s="78"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="81"/>
-      <c r="F28" s="82"/>
-      <c r="G28" s="78"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="84"/>
-      <c r="K28" s="85"/>
-      <c r="L28" s="85"/>
-      <c r="M28" s="85"/>
-      <c r="N28" s="85"/>
-      <c r="O28" s="85"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="87"/>
-      <c r="R28" s="88"/>
-      <c r="S28" s="88"/>
-      <c r="T28" s="88"/>
-      <c r="U28" s="88"/>
-      <c r="V28" s="88"/>
-      <c r="W28" s="88"/>
-      <c r="X28" s="88"/>
-      <c r="Y28" s="88"/>
-      <c r="Z28" s="88"/>
-      <c r="AA28" s="88"/>
-      <c r="AB28" s="88"/>
-      <c r="AC28" s="88"/>
-      <c r="AD28" s="88"/>
-      <c r="AE28" s="89"/>
-      <c r="AF28" s="84"/>
-      <c r="AG28" s="85"/>
-      <c r="AH28" s="85"/>
-      <c r="AI28" s="86"/>
+      <c r="B28" s="114"/>
+      <c r="C28" s="115"/>
+      <c r="D28" s="116"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="118"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="115"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="121"/>
+      <c r="L28" s="121"/>
+      <c r="M28" s="121"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="121"/>
+      <c r="P28" s="122"/>
+      <c r="Q28" s="123"/>
+      <c r="R28" s="124"/>
+      <c r="S28" s="124"/>
+      <c r="T28" s="124"/>
+      <c r="U28" s="124"/>
+      <c r="V28" s="124"/>
+      <c r="W28" s="124"/>
+      <c r="X28" s="124"/>
+      <c r="Y28" s="124"/>
+      <c r="Z28" s="124"/>
+      <c r="AA28" s="124"/>
+      <c r="AB28" s="124"/>
+      <c r="AC28" s="124"/>
+      <c r="AD28" s="124"/>
+      <c r="AE28" s="125"/>
+      <c r="AF28" s="120"/>
+      <c r="AG28" s="121"/>
+      <c r="AH28" s="121"/>
+      <c r="AI28" s="122"/>
     </row>
     <row r="29" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="29"/>
-      <c r="B29" s="78"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="82"/>
-      <c r="G29" s="78"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="79"/>
-      <c r="J29" s="84"/>
-      <c r="K29" s="85"/>
-      <c r="L29" s="85"/>
-      <c r="M29" s="85"/>
-      <c r="N29" s="85"/>
-      <c r="O29" s="85"/>
-      <c r="P29" s="86"/>
-      <c r="Q29" s="87"/>
-      <c r="R29" s="88"/>
-      <c r="S29" s="88"/>
-      <c r="T29" s="88"/>
-      <c r="U29" s="88"/>
-      <c r="V29" s="88"/>
-      <c r="W29" s="88"/>
-      <c r="X29" s="88"/>
-      <c r="Y29" s="88"/>
-      <c r="Z29" s="88"/>
-      <c r="AA29" s="88"/>
-      <c r="AB29" s="88"/>
-      <c r="AC29" s="88"/>
-      <c r="AD29" s="88"/>
-      <c r="AE29" s="89"/>
-      <c r="AF29" s="84"/>
-      <c r="AG29" s="85"/>
-      <c r="AH29" s="85"/>
-      <c r="AI29" s="86"/>
+      <c r="B29" s="114"/>
+      <c r="C29" s="115"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="118"/>
+      <c r="G29" s="114"/>
+      <c r="H29" s="119"/>
+      <c r="I29" s="115"/>
+      <c r="J29" s="120"/>
+      <c r="K29" s="121"/>
+      <c r="L29" s="121"/>
+      <c r="M29" s="121"/>
+      <c r="N29" s="121"/>
+      <c r="O29" s="121"/>
+      <c r="P29" s="122"/>
+      <c r="Q29" s="123"/>
+      <c r="R29" s="124"/>
+      <c r="S29" s="124"/>
+      <c r="T29" s="124"/>
+      <c r="U29" s="124"/>
+      <c r="V29" s="124"/>
+      <c r="W29" s="124"/>
+      <c r="X29" s="124"/>
+      <c r="Y29" s="124"/>
+      <c r="Z29" s="124"/>
+      <c r="AA29" s="124"/>
+      <c r="AB29" s="124"/>
+      <c r="AC29" s="124"/>
+      <c r="AD29" s="124"/>
+      <c r="AE29" s="125"/>
+      <c r="AF29" s="120"/>
+      <c r="AG29" s="121"/>
+      <c r="AH29" s="121"/>
+      <c r="AI29" s="122"/>
     </row>
     <row r="30" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="29"/>
-      <c r="B30" s="78"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="82"/>
-      <c r="G30" s="78"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="79"/>
-      <c r="J30" s="84"/>
-      <c r="K30" s="85"/>
-      <c r="L30" s="85"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="85"/>
-      <c r="O30" s="85"/>
-      <c r="P30" s="86"/>
-      <c r="Q30" s="87"/>
-      <c r="R30" s="88"/>
-      <c r="S30" s="88"/>
-      <c r="T30" s="88"/>
-      <c r="U30" s="88"/>
-      <c r="V30" s="88"/>
-      <c r="W30" s="88"/>
-      <c r="X30" s="88"/>
-      <c r="Y30" s="88"/>
-      <c r="Z30" s="88"/>
-      <c r="AA30" s="88"/>
-      <c r="AB30" s="88"/>
-      <c r="AC30" s="88"/>
-      <c r="AD30" s="88"/>
-      <c r="AE30" s="89"/>
-      <c r="AF30" s="84"/>
-      <c r="AG30" s="85"/>
-      <c r="AH30" s="85"/>
-      <c r="AI30" s="86"/>
+      <c r="B30" s="114"/>
+      <c r="C30" s="115"/>
+      <c r="D30" s="116"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="118"/>
+      <c r="G30" s="114"/>
+      <c r="H30" s="119"/>
+      <c r="I30" s="115"/>
+      <c r="J30" s="120"/>
+      <c r="K30" s="121"/>
+      <c r="L30" s="121"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="121"/>
+      <c r="P30" s="122"/>
+      <c r="Q30" s="123"/>
+      <c r="R30" s="124"/>
+      <c r="S30" s="124"/>
+      <c r="T30" s="124"/>
+      <c r="U30" s="124"/>
+      <c r="V30" s="124"/>
+      <c r="W30" s="124"/>
+      <c r="X30" s="124"/>
+      <c r="Y30" s="124"/>
+      <c r="Z30" s="124"/>
+      <c r="AA30" s="124"/>
+      <c r="AB30" s="124"/>
+      <c r="AC30" s="124"/>
+      <c r="AD30" s="124"/>
+      <c r="AE30" s="125"/>
+      <c r="AF30" s="120"/>
+      <c r="AG30" s="121"/>
+      <c r="AH30" s="121"/>
+      <c r="AI30" s="122"/>
     </row>
     <row r="31" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="29"/>
-      <c r="B31" s="78"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="82"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="79"/>
-      <c r="J31" s="84"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="85"/>
-      <c r="M31" s="85"/>
-      <c r="N31" s="85"/>
-      <c r="O31" s="85"/>
-      <c r="P31" s="86"/>
-      <c r="Q31" s="87"/>
-      <c r="R31" s="88"/>
-      <c r="S31" s="88"/>
-      <c r="T31" s="88"/>
-      <c r="U31" s="88"/>
-      <c r="V31" s="88"/>
-      <c r="W31" s="88"/>
-      <c r="X31" s="88"/>
-      <c r="Y31" s="88"/>
-      <c r="Z31" s="88"/>
-      <c r="AA31" s="88"/>
-      <c r="AB31" s="88"/>
-      <c r="AC31" s="88"/>
-      <c r="AD31" s="88"/>
-      <c r="AE31" s="89"/>
-      <c r="AF31" s="84"/>
-      <c r="AG31" s="85"/>
-      <c r="AH31" s="85"/>
-      <c r="AI31" s="86"/>
+      <c r="B31" s="114"/>
+      <c r="C31" s="115"/>
+      <c r="D31" s="116"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="118"/>
+      <c r="G31" s="114"/>
+      <c r="H31" s="119"/>
+      <c r="I31" s="115"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="121"/>
+      <c r="L31" s="121"/>
+      <c r="M31" s="121"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="121"/>
+      <c r="P31" s="122"/>
+      <c r="Q31" s="123"/>
+      <c r="R31" s="124"/>
+      <c r="S31" s="124"/>
+      <c r="T31" s="124"/>
+      <c r="U31" s="124"/>
+      <c r="V31" s="124"/>
+      <c r="W31" s="124"/>
+      <c r="X31" s="124"/>
+      <c r="Y31" s="124"/>
+      <c r="Z31" s="124"/>
+      <c r="AA31" s="124"/>
+      <c r="AB31" s="124"/>
+      <c r="AC31" s="124"/>
+      <c r="AD31" s="124"/>
+      <c r="AE31" s="125"/>
+      <c r="AF31" s="120"/>
+      <c r="AG31" s="121"/>
+      <c r="AH31" s="121"/>
+      <c r="AI31" s="122"/>
     </row>
     <row r="32" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="29"/>
-      <c r="B32" s="78"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="79"/>
-      <c r="J32" s="84"/>
-      <c r="K32" s="90"/>
-      <c r="L32" s="85"/>
-      <c r="M32" s="85"/>
-      <c r="N32" s="85"/>
-      <c r="O32" s="85"/>
-      <c r="P32" s="86"/>
-      <c r="Q32" s="87"/>
-      <c r="R32" s="88"/>
-      <c r="S32" s="88"/>
-      <c r="T32" s="88"/>
-      <c r="U32" s="88"/>
-      <c r="V32" s="88"/>
-      <c r="W32" s="88"/>
-      <c r="X32" s="88"/>
-      <c r="Y32" s="88"/>
-      <c r="Z32" s="88"/>
-      <c r="AA32" s="88"/>
-      <c r="AB32" s="88"/>
-      <c r="AC32" s="88"/>
-      <c r="AD32" s="88"/>
-      <c r="AE32" s="89"/>
-      <c r="AF32" s="84"/>
-      <c r="AG32" s="85"/>
-      <c r="AH32" s="85"/>
-      <c r="AI32" s="86"/>
+      <c r="B32" s="114"/>
+      <c r="C32" s="115"/>
+      <c r="D32" s="116"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="118"/>
+      <c r="G32" s="114"/>
+      <c r="H32" s="119"/>
+      <c r="I32" s="115"/>
+      <c r="J32" s="120"/>
+      <c r="K32" s="150"/>
+      <c r="L32" s="121"/>
+      <c r="M32" s="121"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="121"/>
+      <c r="P32" s="122"/>
+      <c r="Q32" s="123"/>
+      <c r="R32" s="124"/>
+      <c r="S32" s="124"/>
+      <c r="T32" s="124"/>
+      <c r="U32" s="124"/>
+      <c r="V32" s="124"/>
+      <c r="W32" s="124"/>
+      <c r="X32" s="124"/>
+      <c r="Y32" s="124"/>
+      <c r="Z32" s="124"/>
+      <c r="AA32" s="124"/>
+      <c r="AB32" s="124"/>
+      <c r="AC32" s="124"/>
+      <c r="AD32" s="124"/>
+      <c r="AE32" s="125"/>
+      <c r="AF32" s="120"/>
+      <c r="AG32" s="121"/>
+      <c r="AH32" s="121"/>
+      <c r="AI32" s="122"/>
     </row>
     <row r="33" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="29"/>
-      <c r="B33" s="78"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="84"/>
-      <c r="K33" s="85"/>
-      <c r="L33" s="85"/>
-      <c r="M33" s="85"/>
-      <c r="N33" s="85"/>
-      <c r="O33" s="85"/>
-      <c r="P33" s="86"/>
-      <c r="Q33" s="87"/>
-      <c r="R33" s="88"/>
-      <c r="S33" s="88"/>
-      <c r="T33" s="88"/>
-      <c r="U33" s="88"/>
-      <c r="V33" s="88"/>
-      <c r="W33" s="88"/>
-      <c r="X33" s="88"/>
-      <c r="Y33" s="88"/>
-      <c r="Z33" s="88"/>
-      <c r="AA33" s="88"/>
-      <c r="AB33" s="88"/>
-      <c r="AC33" s="88"/>
-      <c r="AD33" s="88"/>
-      <c r="AE33" s="89"/>
-      <c r="AF33" s="84"/>
-      <c r="AG33" s="85"/>
-      <c r="AH33" s="85"/>
-      <c r="AI33" s="86"/>
+      <c r="B33" s="114"/>
+      <c r="C33" s="115"/>
+      <c r="D33" s="116"/>
+      <c r="E33" s="117"/>
+      <c r="F33" s="118"/>
+      <c r="G33" s="114"/>
+      <c r="H33" s="119"/>
+      <c r="I33" s="115"/>
+      <c r="J33" s="120"/>
+      <c r="K33" s="121"/>
+      <c r="L33" s="121"/>
+      <c r="M33" s="121"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="121"/>
+      <c r="P33" s="122"/>
+      <c r="Q33" s="123"/>
+      <c r="R33" s="124"/>
+      <c r="S33" s="124"/>
+      <c r="T33" s="124"/>
+      <c r="U33" s="124"/>
+      <c r="V33" s="124"/>
+      <c r="W33" s="124"/>
+      <c r="X33" s="124"/>
+      <c r="Y33" s="124"/>
+      <c r="Z33" s="124"/>
+      <c r="AA33" s="124"/>
+      <c r="AB33" s="124"/>
+      <c r="AC33" s="124"/>
+      <c r="AD33" s="124"/>
+      <c r="AE33" s="125"/>
+      <c r="AF33" s="120"/>
+      <c r="AG33" s="121"/>
+      <c r="AH33" s="121"/>
+      <c r="AI33" s="122"/>
     </row>
     <row r="34" spans="1:35" ht="14.25" x14ac:dyDescent="0.15">
       <c r="K34" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="179">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -8908,162 +9064,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1"/>
@@ -9215,163 +9215,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="84" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="124" t="str">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="87" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
-      <c r="L1" s="125"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="130" t="s">
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="93" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="132"/>
-      <c r="S1" s="139" t="str">
+      <c r="P1" s="94"/>
+      <c r="Q1" s="94"/>
+      <c r="R1" s="95"/>
+      <c r="S1" s="102" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarchを使用したシステム開発における標準WBS</v>
       </c>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-      <c r="X1" s="140"/>
-      <c r="Y1" s="140"/>
-      <c r="Z1" s="141"/>
-      <c r="AA1" s="151" t="s">
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
+      <c r="V1" s="103"/>
+      <c r="W1" s="103"/>
+      <c r="X1" s="103"/>
+      <c r="Y1" s="103"/>
+      <c r="Z1" s="104"/>
+      <c r="AA1" s="154" t="s">
         <v>280</v>
       </c>
-      <c r="AB1" s="152"/>
-      <c r="AC1" s="148" t="str">
+      <c r="AB1" s="155"/>
+      <c r="AC1" s="111" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="149"/>
-      <c r="AE1" s="149"/>
-      <c r="AF1" s="150"/>
-      <c r="AG1" s="153">
+      <c r="AD1" s="112"/>
+      <c r="AE1" s="112"/>
+      <c r="AF1" s="113"/>
+      <c r="AG1" s="151">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="154"/>
-      <c r="AI1" s="155"/>
+      <c r="AH1" s="152"/>
+      <c r="AI1" s="153"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3"/>
     </row>
     <row r="2" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="84" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="122"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="124" t="str">
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="87" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="125"/>
-      <c r="M2" s="125"/>
-      <c r="N2" s="126"/>
-      <c r="O2" s="133"/>
-      <c r="P2" s="134"/>
-      <c r="Q2" s="134"/>
-      <c r="R2" s="135"/>
-      <c r="S2" s="142"/>
-      <c r="T2" s="143"/>
-      <c r="U2" s="143"/>
-      <c r="V2" s="143"/>
-      <c r="W2" s="143"/>
-      <c r="X2" s="143"/>
-      <c r="Y2" s="143"/>
-      <c r="Z2" s="144"/>
-      <c r="AA2" s="151" t="s">
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97"/>
+      <c r="R2" s="98"/>
+      <c r="S2" s="105"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="106"/>
+      <c r="W2" s="106"/>
+      <c r="X2" s="106"/>
+      <c r="Y2" s="106"/>
+      <c r="Z2" s="107"/>
+      <c r="AA2" s="154" t="s">
         <v>282</v>
       </c>
-      <c r="AB2" s="152"/>
-      <c r="AC2" s="148" t="str">
+      <c r="AB2" s="155"/>
+      <c r="AC2" s="111" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="149"/>
-      <c r="AE2" s="149"/>
-      <c r="AF2" s="150"/>
-      <c r="AG2" s="153">
+      <c r="AD2" s="112"/>
+      <c r="AE2" s="112"/>
+      <c r="AF2" s="113"/>
+      <c r="AG2" s="151">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v>45461</v>
       </c>
-      <c r="AH2" s="154"/>
-      <c r="AI2" s="155"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="121" t="s">
+      <c r="A3" s="84" t="s">
         <v>283</v>
       </c>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="124" t="str">
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="87" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="125"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="125"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="125"/>
-      <c r="K3" s="125"/>
-      <c r="L3" s="125"/>
-      <c r="M3" s="125"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="137"/>
-      <c r="Q3" s="137"/>
-      <c r="R3" s="138"/>
-      <c r="S3" s="145"/>
-      <c r="T3" s="146"/>
-      <c r="U3" s="146"/>
-      <c r="V3" s="146"/>
-      <c r="W3" s="146"/>
-      <c r="X3" s="146"/>
-      <c r="Y3" s="146"/>
-      <c r="Z3" s="147"/>
-      <c r="AA3" s="151"/>
-      <c r="AB3" s="152"/>
-      <c r="AC3" s="148" t="str">
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="99"/>
+      <c r="P3" s="100"/>
+      <c r="Q3" s="100"/>
+      <c r="R3" s="101"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="109"/>
+      <c r="U3" s="109"/>
+      <c r="V3" s="109"/>
+      <c r="W3" s="109"/>
+      <c r="X3" s="109"/>
+      <c r="Y3" s="109"/>
+      <c r="Z3" s="110"/>
+      <c r="AA3" s="154"/>
+      <c r="AB3" s="155"/>
+      <c r="AC3" s="111" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="149"/>
-      <c r="AE3" s="149"/>
-      <c r="AF3" s="150"/>
-      <c r="AG3" s="153" t="str">
+      <c r="AD3" s="112"/>
+      <c r="AE3" s="112"/>
+      <c r="AF3" s="113"/>
+      <c r="AG3" s="151" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="154"/>
-      <c r="AI3" s="155"/>
+      <c r="AH3" s="152"/>
+      <c r="AI3" s="153"/>
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
@@ -9647,7 +9647,7 @@
       <c r="A11" s="30"/>
       <c r="B11" s="30"/>
       <c r="C11" s="34" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
@@ -10691,14 +10691,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -10708,6 +10700,14 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1"/>
@@ -10730,59 +10730,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="84" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="124" t="str">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="87" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
-      <c r="L1" s="125"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="160" t="s">
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="157" t="s">
         <v>294</v>
       </c>
-      <c r="P1" s="161"/>
-      <c r="Q1" s="161"/>
-      <c r="R1" s="162"/>
-      <c r="S1" s="139" t="str">
+      <c r="P1" s="158"/>
+      <c r="Q1" s="158"/>
+      <c r="R1" s="159"/>
+      <c r="S1" s="102" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarchを使用したシステム開発における標準WBS</v>
       </c>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-      <c r="X1" s="140"/>
-      <c r="Y1" s="140"/>
-      <c r="Z1" s="141"/>
-      <c r="AA1" s="121" t="s">
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
+      <c r="V1" s="103"/>
+      <c r="W1" s="103"/>
+      <c r="X1" s="103"/>
+      <c r="Y1" s="103"/>
+      <c r="Z1" s="104"/>
+      <c r="AA1" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="AB1" s="123"/>
-      <c r="AC1" s="148" t="str">
+      <c r="AB1" s="86"/>
+      <c r="AC1" s="111" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="149"/>
-      <c r="AE1" s="149"/>
-      <c r="AF1" s="150"/>
-      <c r="AG1" s="153">
+      <c r="AD1" s="112"/>
+      <c r="AE1" s="112"/>
+      <c r="AF1" s="113"/>
+      <c r="AG1" s="151">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="154"/>
-      <c r="AI1" s="155"/>
+      <c r="AH1" s="152"/>
+      <c r="AI1" s="153"/>
       <c r="AJ1" s="30"/>
       <c r="AN1" s="51"/>
       <c r="AO1" s="30"/>
@@ -10796,54 +10796,54 @@
       <c r="AW1" s="30"/>
     </row>
     <row r="2" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="84" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="122"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="124" t="str">
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="87" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="125"/>
-      <c r="M2" s="125"/>
-      <c r="N2" s="126"/>
-      <c r="O2" s="163"/>
-      <c r="P2" s="164"/>
-      <c r="Q2" s="164"/>
-      <c r="R2" s="165"/>
-      <c r="S2" s="142"/>
-      <c r="T2" s="143"/>
-      <c r="U2" s="143"/>
-      <c r="V2" s="143"/>
-      <c r="W2" s="143"/>
-      <c r="X2" s="143"/>
-      <c r="Y2" s="143"/>
-      <c r="Z2" s="144"/>
-      <c r="AA2" s="121" t="s">
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="160"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="161"/>
+      <c r="R2" s="162"/>
+      <c r="S2" s="105"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="106"/>
+      <c r="W2" s="106"/>
+      <c r="X2" s="106"/>
+      <c r="Y2" s="106"/>
+      <c r="Z2" s="107"/>
+      <c r="AA2" s="84" t="s">
         <v>185</v>
       </c>
-      <c r="AB2" s="123"/>
-      <c r="AC2" s="148" t="str">
+      <c r="AB2" s="86"/>
+      <c r="AC2" s="111" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="149"/>
-      <c r="AE2" s="149"/>
-      <c r="AF2" s="150"/>
-      <c r="AG2" s="153">
+      <c r="AD2" s="112"/>
+      <c r="AE2" s="112"/>
+      <c r="AF2" s="113"/>
+      <c r="AG2" s="151">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v>45461</v>
       </c>
-      <c r="AH2" s="154"/>
-      <c r="AI2" s="155"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
       <c r="AJ2" s="30"/>
       <c r="AN2" s="51"/>
       <c r="AO2" s="30"/>
@@ -10857,52 +10857,52 @@
       <c r="AW2" s="30"/>
     </row>
     <row r="3" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="121" t="s">
+      <c r="A3" s="84" t="s">
         <v>283</v>
       </c>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="124" t="str">
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="87" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="125"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="125"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="125"/>
-      <c r="K3" s="125"/>
-      <c r="L3" s="125"/>
-      <c r="M3" s="125"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="166"/>
-      <c r="P3" s="167"/>
-      <c r="Q3" s="167"/>
-      <c r="R3" s="168"/>
-      <c r="S3" s="145"/>
-      <c r="T3" s="146"/>
-      <c r="U3" s="146"/>
-      <c r="V3" s="146"/>
-      <c r="W3" s="146"/>
-      <c r="X3" s="146"/>
-      <c r="Y3" s="146"/>
-      <c r="Z3" s="147"/>
-      <c r="AA3" s="121"/>
-      <c r="AB3" s="123"/>
-      <c r="AC3" s="148" t="str">
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="163"/>
+      <c r="P3" s="164"/>
+      <c r="Q3" s="164"/>
+      <c r="R3" s="165"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="109"/>
+      <c r="U3" s="109"/>
+      <c r="V3" s="109"/>
+      <c r="W3" s="109"/>
+      <c r="X3" s="109"/>
+      <c r="Y3" s="109"/>
+      <c r="Z3" s="110"/>
+      <c r="AA3" s="84"/>
+      <c r="AB3" s="86"/>
+      <c r="AC3" s="111" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="149"/>
-      <c r="AE3" s="149"/>
-      <c r="AF3" s="150"/>
-      <c r="AG3" s="153" t="str">
+      <c r="AD3" s="112"/>
+      <c r="AE3" s="112"/>
+      <c r="AF3" s="113"/>
+      <c r="AG3" s="151" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="154"/>
-      <c r="AI3" s="155"/>
+      <c r="AH3" s="152"/>
+      <c r="AI3" s="153"/>
       <c r="AJ3" s="53"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
@@ -11144,34 +11144,34 @@
       <c r="D57" s="55" t="s">
         <v>305</v>
       </c>
-      <c r="E57" s="157" t="s">
+      <c r="E57" s="166" t="s">
         <v>107</v>
       </c>
-      <c r="F57" s="158"/>
-      <c r="G57" s="158"/>
-      <c r="H57" s="158"/>
-      <c r="I57" s="158"/>
-      <c r="J57" s="159"/>
-      <c r="K57" s="157" t="s">
+      <c r="F57" s="167"/>
+      <c r="G57" s="167"/>
+      <c r="H57" s="167"/>
+      <c r="I57" s="167"/>
+      <c r="J57" s="168"/>
+      <c r="K57" s="166" t="s">
         <v>178</v>
       </c>
-      <c r="L57" s="158"/>
-      <c r="M57" s="158"/>
-      <c r="N57" s="158"/>
-      <c r="O57" s="158"/>
-      <c r="P57" s="158"/>
-      <c r="Q57" s="158"/>
-      <c r="R57" s="158"/>
-      <c r="S57" s="158"/>
-      <c r="T57" s="158"/>
-      <c r="U57" s="158"/>
-      <c r="V57" s="158"/>
-      <c r="W57" s="158"/>
-      <c r="X57" s="158"/>
-      <c r="Y57" s="158"/>
-      <c r="Z57" s="158"/>
-      <c r="AA57" s="158"/>
-      <c r="AB57" s="159"/>
+      <c r="L57" s="167"/>
+      <c r="M57" s="167"/>
+      <c r="N57" s="167"/>
+      <c r="O57" s="167"/>
+      <c r="P57" s="167"/>
+      <c r="Q57" s="167"/>
+      <c r="R57" s="167"/>
+      <c r="S57" s="167"/>
+      <c r="T57" s="167"/>
+      <c r="U57" s="167"/>
+      <c r="V57" s="167"/>
+      <c r="W57" s="167"/>
+      <c r="X57" s="167"/>
+      <c r="Y57" s="167"/>
+      <c r="Z57" s="167"/>
+      <c r="AA57" s="167"/>
+      <c r="AB57" s="168"/>
     </row>
     <row r="58" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="34"/>
@@ -11487,12 +11487,12 @@
     </row>
     <row r="69" spans="3:28" x14ac:dyDescent="0.15">
       <c r="C69" s="30" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="71" spans="3:28" x14ac:dyDescent="0.15">
       <c r="D71" s="30" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="73" spans="3:28" x14ac:dyDescent="0.15">
@@ -11500,7 +11500,7 @@
         <v>305</v>
       </c>
       <c r="E73" s="67" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F73" s="68"/>
       <c r="G73" s="68"/>
@@ -11731,7 +11731,7 @@
         <v>7</v>
       </c>
       <c r="E80" s="64" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F80" s="65"/>
       <c r="G80" s="65"/>
@@ -12184,6 +12184,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="E66:J66"/>
+    <mergeCell ref="K66:AB66"/>
+    <mergeCell ref="E63:J63"/>
+    <mergeCell ref="K63:AB63"/>
+    <mergeCell ref="E64:J64"/>
+    <mergeCell ref="K64:AB64"/>
+    <mergeCell ref="E65:J65"/>
+    <mergeCell ref="K65:AB65"/>
+    <mergeCell ref="E60:J60"/>
+    <mergeCell ref="K60:AB60"/>
+    <mergeCell ref="E61:J61"/>
+    <mergeCell ref="K61:AB61"/>
+    <mergeCell ref="E62:J62"/>
+    <mergeCell ref="K62:AB62"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="E57:J57"/>
+    <mergeCell ref="K57:AB57"/>
+    <mergeCell ref="E58:J58"/>
+    <mergeCell ref="K58:AB58"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
     <mergeCell ref="E59:J59"/>
     <mergeCell ref="K59:AB59"/>
     <mergeCell ref="AG1:AI1"/>
@@ -12200,27 +12221,6 @@
     <mergeCell ref="AC1:AF1"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="E57:J57"/>
-    <mergeCell ref="K57:AB57"/>
-    <mergeCell ref="E58:J58"/>
-    <mergeCell ref="K58:AB58"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="E60:J60"/>
-    <mergeCell ref="K60:AB60"/>
-    <mergeCell ref="E61:J61"/>
-    <mergeCell ref="K61:AB61"/>
-    <mergeCell ref="E62:J62"/>
-    <mergeCell ref="K62:AB62"/>
-    <mergeCell ref="E66:J66"/>
-    <mergeCell ref="K66:AB66"/>
-    <mergeCell ref="E63:J63"/>
-    <mergeCell ref="K63:AB63"/>
-    <mergeCell ref="E64:J64"/>
-    <mergeCell ref="K64:AB64"/>
-    <mergeCell ref="E65:J65"/>
-    <mergeCell ref="K65:AB65"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>

--- a/010_開発プロセス標準/Nablarchを使用したシステム開発における標準WBS.xlsx
+++ b/010_開発プロセス標準/Nablarchを使用したシステム開発における標準WBS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17502AE4-333B-428D-93C9-74B47E449D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF795742-DDE3-4A13-B9E7-631570388A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1035" yWindow="3390" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="1530" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="14" r:id="rId1"/>
@@ -5500,6 +5500,117 @@
     <xf numFmtId="31" fontId="9" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -5608,116 +5719,11 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -5728,15 +5734,18 @@
     <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -5763,15 +5772,6 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7029,7 +7029,7 @@
       <c r="H25" s="17"/>
       <c r="I25" s="77">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
-        <v>45461</v>
+        <v>45565</v>
       </c>
       <c r="J25" s="77"/>
       <c r="K25" s="77"/>
@@ -7626,55 +7626,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="121" t="s">
         <v>279</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="93" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="130" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="95"/>
-      <c r="S1" s="102" t="s">
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="139" t="s">
         <v>291</v>
       </c>
-      <c r="T1" s="103"/>
-      <c r="U1" s="103"/>
-      <c r="V1" s="103"/>
-      <c r="W1" s="103"/>
-      <c r="X1" s="103"/>
-      <c r="Y1" s="103"/>
-      <c r="Z1" s="104"/>
-      <c r="AA1" s="84" t="s">
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
+      <c r="Y1" s="140"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="121" t="s">
         <v>280</v>
       </c>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="111" t="str">
+      <c r="AB1" s="123"/>
+      <c r="AC1" s="148" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="112"/>
-      <c r="AE1" s="112"/>
-      <c r="AF1" s="113"/>
-      <c r="AG1" s="78">
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="150"/>
+      <c r="AG1" s="115">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="79"/>
-      <c r="AI1" s="80"/>
+      <c r="AH1" s="116"/>
+      <c r="AI1" s="117"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="2"/>
@@ -7682,51 +7682,51 @@
       <c r="AN1" s="3"/>
     </row>
     <row r="2" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="121" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="97"/>
-      <c r="Q2" s="97"/>
-      <c r="R2" s="98"/>
-      <c r="S2" s="105"/>
-      <c r="T2" s="106"/>
-      <c r="U2" s="106"/>
-      <c r="V2" s="106"/>
-      <c r="W2" s="106"/>
-      <c r="X2" s="106"/>
-      <c r="Y2" s="106"/>
-      <c r="Z2" s="107"/>
-      <c r="AA2" s="84" t="s">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="133"/>
+      <c r="P2" s="134"/>
+      <c r="Q2" s="134"/>
+      <c r="R2" s="135"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="143"/>
+      <c r="U2" s="143"/>
+      <c r="V2" s="143"/>
+      <c r="W2" s="143"/>
+      <c r="X2" s="143"/>
+      <c r="Y2" s="143"/>
+      <c r="Z2" s="144"/>
+      <c r="AA2" s="121" t="s">
         <v>282</v>
       </c>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="90" t="str">
+      <c r="AB2" s="123"/>
+      <c r="AC2" s="127" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="91"/>
-      <c r="AE2" s="91"/>
-      <c r="AF2" s="92"/>
-      <c r="AG2" s="78">
+      <c r="AD2" s="128"/>
+      <c r="AE2" s="128"/>
+      <c r="AF2" s="129"/>
+      <c r="AG2" s="115">
         <f>IF(D9="","",MAX(D9:F33))</f>
-        <v>45461</v>
-      </c>
-      <c r="AH2" s="79"/>
-      <c r="AI2" s="80"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="116"/>
+      <c r="AI2" s="117"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
@@ -7734,43 +7734,43 @@
       <c r="AN2" s="2"/>
     </row>
     <row r="3" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="121" t="s">
         <v>283</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="99"/>
-      <c r="P3" s="100"/>
-      <c r="Q3" s="100"/>
-      <c r="R3" s="101"/>
-      <c r="S3" s="108"/>
-      <c r="T3" s="109"/>
-      <c r="U3" s="109"/>
-      <c r="V3" s="109"/>
-      <c r="W3" s="109"/>
-      <c r="X3" s="109"/>
-      <c r="Y3" s="109"/>
-      <c r="Z3" s="110"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="111"/>
-      <c r="AD3" s="112"/>
-      <c r="AE3" s="112"/>
-      <c r="AF3" s="113"/>
-      <c r="AG3" s="78"/>
-      <c r="AH3" s="79"/>
-      <c r="AI3" s="80"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="137"/>
+      <c r="Q3" s="137"/>
+      <c r="R3" s="138"/>
+      <c r="S3" s="145"/>
+      <c r="T3" s="146"/>
+      <c r="U3" s="146"/>
+      <c r="V3" s="146"/>
+      <c r="W3" s="146"/>
+      <c r="X3" s="146"/>
+      <c r="Y3" s="146"/>
+      <c r="Z3" s="147"/>
+      <c r="AA3" s="121"/>
+      <c r="AB3" s="123"/>
+      <c r="AC3" s="148"/>
+      <c r="AD3" s="149"/>
+      <c r="AE3" s="149"/>
+      <c r="AF3" s="150"/>
+      <c r="AG3" s="115"/>
+      <c r="AH3" s="116"/>
+      <c r="AI3" s="117"/>
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
@@ -7807,1240 +7807,1084 @@
       <c r="A7" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="B7" s="81" t="s">
+      <c r="B7" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="C7" s="82"/>
-      <c r="D7" s="81" t="s">
+      <c r="C7" s="119"/>
+      <c r="D7" s="118" t="s">
         <v>187</v>
       </c>
-      <c r="E7" s="83"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="81" t="s">
+      <c r="E7" s="120"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="H7" s="83"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="81" t="s">
+      <c r="H7" s="120"/>
+      <c r="I7" s="119"/>
+      <c r="J7" s="118" t="s">
         <v>285</v>
       </c>
-      <c r="K7" s="83"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="83"/>
-      <c r="N7" s="83"/>
-      <c r="O7" s="83"/>
-      <c r="P7" s="82"/>
-      <c r="Q7" s="81" t="s">
+      <c r="K7" s="120"/>
+      <c r="L7" s="120"/>
+      <c r="M7" s="120"/>
+      <c r="N7" s="120"/>
+      <c r="O7" s="120"/>
+      <c r="P7" s="119"/>
+      <c r="Q7" s="118" t="s">
         <v>189</v>
       </c>
-      <c r="R7" s="83"/>
-      <c r="S7" s="83"/>
-      <c r="T7" s="83"/>
-      <c r="U7" s="83"/>
-      <c r="V7" s="83"/>
-      <c r="W7" s="83"/>
-      <c r="X7" s="83"/>
-      <c r="Y7" s="83"/>
-      <c r="Z7" s="83"/>
-      <c r="AA7" s="83"/>
-      <c r="AB7" s="83"/>
-      <c r="AC7" s="83"/>
-      <c r="AD7" s="83"/>
-      <c r="AE7" s="82"/>
-      <c r="AF7" s="81" t="s">
+      <c r="R7" s="120"/>
+      <c r="S7" s="120"/>
+      <c r="T7" s="120"/>
+      <c r="U7" s="120"/>
+      <c r="V7" s="120"/>
+      <c r="W7" s="120"/>
+      <c r="X7" s="120"/>
+      <c r="Y7" s="120"/>
+      <c r="Z7" s="120"/>
+      <c r="AA7" s="120"/>
+      <c r="AB7" s="120"/>
+      <c r="AC7" s="120"/>
+      <c r="AD7" s="120"/>
+      <c r="AE7" s="119"/>
+      <c r="AF7" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AG7" s="83"/>
-      <c r="AH7" s="83"/>
-      <c r="AI7" s="82"/>
+      <c r="AG7" s="120"/>
+      <c r="AH7" s="120"/>
+      <c r="AI7" s="119"/>
     </row>
     <row r="8" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="126" t="s">
+      <c r="B8" s="101" t="s">
         <v>286</v>
       </c>
-      <c r="C8" s="127"/>
-      <c r="D8" s="128">
+      <c r="C8" s="102"/>
+      <c r="D8" s="103">
         <v>43336</v>
       </c>
-      <c r="E8" s="129"/>
-      <c r="F8" s="130"/>
-      <c r="G8" s="131" t="s">
+      <c r="E8" s="104"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="106" t="s">
         <v>287</v>
       </c>
-      <c r="H8" s="132"/>
-      <c r="I8" s="133"/>
-      <c r="J8" s="134" t="s">
+      <c r="H8" s="107"/>
+      <c r="I8" s="108"/>
+      <c r="J8" s="109" t="s">
         <v>288</v>
       </c>
-      <c r="K8" s="135"/>
-      <c r="L8" s="135"/>
-      <c r="M8" s="135"/>
-      <c r="N8" s="135"/>
-      <c r="O8" s="135"/>
-      <c r="P8" s="136"/>
-      <c r="Q8" s="137" t="s">
+      <c r="K8" s="110"/>
+      <c r="L8" s="110"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="110"/>
+      <c r="O8" s="110"/>
+      <c r="P8" s="111"/>
+      <c r="Q8" s="112" t="s">
         <v>289</v>
       </c>
-      <c r="R8" s="138"/>
-      <c r="S8" s="138"/>
-      <c r="T8" s="138"/>
-      <c r="U8" s="138"/>
-      <c r="V8" s="138"/>
-      <c r="W8" s="138"/>
-      <c r="X8" s="138"/>
-      <c r="Y8" s="138"/>
-      <c r="Z8" s="138"/>
-      <c r="AA8" s="138"/>
-      <c r="AB8" s="138"/>
-      <c r="AC8" s="138"/>
-      <c r="AD8" s="138"/>
-      <c r="AE8" s="139"/>
-      <c r="AF8" s="134" t="s">
+      <c r="R8" s="113"/>
+      <c r="S8" s="113"/>
+      <c r="T8" s="113"/>
+      <c r="U8" s="113"/>
+      <c r="V8" s="113"/>
+      <c r="W8" s="113"/>
+      <c r="X8" s="113"/>
+      <c r="Y8" s="113"/>
+      <c r="Z8" s="113"/>
+      <c r="AA8" s="113"/>
+      <c r="AB8" s="113"/>
+      <c r="AC8" s="113"/>
+      <c r="AD8" s="113"/>
+      <c r="AE8" s="114"/>
+      <c r="AF8" s="109" t="s">
         <v>290</v>
       </c>
-      <c r="AG8" s="135"/>
-      <c r="AH8" s="135"/>
-      <c r="AI8" s="136"/>
+      <c r="AG8" s="110"/>
+      <c r="AH8" s="110"/>
+      <c r="AI8" s="111"/>
     </row>
     <row r="9" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="29">
         <v>2</v>
       </c>
-      <c r="B9" s="114" t="s">
+      <c r="B9" s="78" t="s">
         <v>355</v>
       </c>
-      <c r="C9" s="115"/>
-      <c r="D9" s="116">
+      <c r="C9" s="79"/>
+      <c r="D9" s="80">
         <v>43896</v>
       </c>
-      <c r="E9" s="117"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="116" t="s">
+      <c r="E9" s="81"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="80" t="s">
         <v>337</v>
       </c>
-      <c r="H9" s="119"/>
-      <c r="I9" s="115"/>
-      <c r="J9" s="120" t="s">
+      <c r="H9" s="83"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="84" t="s">
         <v>338</v>
       </c>
-      <c r="K9" s="121"/>
-      <c r="L9" s="121"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="121"/>
-      <c r="O9" s="121"/>
-      <c r="P9" s="122"/>
-      <c r="Q9" s="123" t="s">
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="85"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="85"/>
+      <c r="P9" s="86"/>
+      <c r="Q9" s="87" t="s">
         <v>353</v>
       </c>
-      <c r="R9" s="124"/>
-      <c r="S9" s="124"/>
-      <c r="T9" s="124"/>
-      <c r="U9" s="124"/>
-      <c r="V9" s="124"/>
-      <c r="W9" s="124"/>
-      <c r="X9" s="124"/>
-      <c r="Y9" s="124"/>
-      <c r="Z9" s="124"/>
-      <c r="AA9" s="124"/>
-      <c r="AB9" s="124"/>
-      <c r="AC9" s="124"/>
-      <c r="AD9" s="124"/>
-      <c r="AE9" s="125"/>
-      <c r="AF9" s="120" t="s">
+      <c r="R9" s="88"/>
+      <c r="S9" s="88"/>
+      <c r="T9" s="88"/>
+      <c r="U9" s="88"/>
+      <c r="V9" s="88"/>
+      <c r="W9" s="88"/>
+      <c r="X9" s="88"/>
+      <c r="Y9" s="88"/>
+      <c r="Z9" s="88"/>
+      <c r="AA9" s="88"/>
+      <c r="AB9" s="88"/>
+      <c r="AC9" s="88"/>
+      <c r="AD9" s="88"/>
+      <c r="AE9" s="89"/>
+      <c r="AF9" s="84" t="s">
         <v>290</v>
       </c>
-      <c r="AG9" s="121"/>
-      <c r="AH9" s="121"/>
-      <c r="AI9" s="122"/>
+      <c r="AG9" s="85"/>
+      <c r="AH9" s="85"/>
+      <c r="AI9" s="86"/>
     </row>
     <row r="10" spans="1:40" s="9" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="29">
         <v>3</v>
       </c>
-      <c r="B10" s="114" t="s">
+      <c r="B10" s="78" t="s">
         <v>356</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="116">
+      <c r="C10" s="79"/>
+      <c r="D10" s="80">
         <v>44455</v>
       </c>
-      <c r="E10" s="117"/>
-      <c r="F10" s="118"/>
-      <c r="G10" s="116" t="s">
+      <c r="E10" s="81"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="80" t="s">
         <v>337</v>
       </c>
-      <c r="H10" s="119"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="120" t="s">
+      <c r="H10" s="83"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="84" t="s">
         <v>338</v>
       </c>
-      <c r="K10" s="121"/>
-      <c r="L10" s="121"/>
-      <c r="M10" s="121"/>
-      <c r="N10" s="121"/>
-      <c r="O10" s="121"/>
-      <c r="P10" s="122"/>
-      <c r="Q10" s="123" t="s">
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="86"/>
+      <c r="Q10" s="87" t="s">
         <v>357</v>
       </c>
-      <c r="R10" s="124"/>
-      <c r="S10" s="124"/>
-      <c r="T10" s="124"/>
-      <c r="U10" s="124"/>
-      <c r="V10" s="124"/>
-      <c r="W10" s="124"/>
-      <c r="X10" s="124"/>
-      <c r="Y10" s="124"/>
-      <c r="Z10" s="124"/>
-      <c r="AA10" s="124"/>
-      <c r="AB10" s="124"/>
-      <c r="AC10" s="124"/>
-      <c r="AD10" s="124"/>
-      <c r="AE10" s="125"/>
-      <c r="AF10" s="120" t="s">
+      <c r="R10" s="88"/>
+      <c r="S10" s="88"/>
+      <c r="T10" s="88"/>
+      <c r="U10" s="88"/>
+      <c r="V10" s="88"/>
+      <c r="W10" s="88"/>
+      <c r="X10" s="88"/>
+      <c r="Y10" s="88"/>
+      <c r="Z10" s="88"/>
+      <c r="AA10" s="88"/>
+      <c r="AB10" s="88"/>
+      <c r="AC10" s="88"/>
+      <c r="AD10" s="88"/>
+      <c r="AE10" s="89"/>
+      <c r="AF10" s="84" t="s">
         <v>290</v>
       </c>
-      <c r="AG10" s="121"/>
-      <c r="AH10" s="121"/>
-      <c r="AI10" s="122"/>
+      <c r="AG10" s="85"/>
+      <c r="AH10" s="85"/>
+      <c r="AI10" s="86"/>
     </row>
     <row r="11" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="76">
         <v>4</v>
       </c>
-      <c r="B11" s="140" t="s">
+      <c r="B11" s="96" t="s">
         <v>402</v>
       </c>
-      <c r="C11" s="141"/>
-      <c r="D11" s="142">
-        <v>45461</v>
-      </c>
-      <c r="E11" s="143"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="114" t="s">
+      <c r="C11" s="97"/>
+      <c r="D11" s="98">
+        <v>45565</v>
+      </c>
+      <c r="E11" s="99"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="78" t="s">
         <v>405</v>
       </c>
-      <c r="H11" s="119"/>
-      <c r="I11" s="115"/>
-      <c r="J11" s="120" t="s">
+      <c r="H11" s="83"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="84" t="s">
         <v>403</v>
       </c>
-      <c r="K11" s="121"/>
-      <c r="L11" s="121"/>
-      <c r="M11" s="121"/>
-      <c r="N11" s="121"/>
-      <c r="O11" s="121"/>
-      <c r="P11" s="122"/>
-      <c r="Q11" s="123" t="s">
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="85"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="85"/>
+      <c r="P11" s="86"/>
+      <c r="Q11" s="87" t="s">
         <v>404</v>
       </c>
-      <c r="R11" s="124"/>
-      <c r="S11" s="124"/>
-      <c r="T11" s="124"/>
-      <c r="U11" s="124"/>
-      <c r="V11" s="124"/>
-      <c r="W11" s="124"/>
-      <c r="X11" s="124"/>
-      <c r="Y11" s="124"/>
-      <c r="Z11" s="124"/>
-      <c r="AA11" s="124"/>
-      <c r="AB11" s="124"/>
-      <c r="AC11" s="124"/>
-      <c r="AD11" s="124"/>
-      <c r="AE11" s="125"/>
-      <c r="AF11" s="120" t="s">
+      <c r="R11" s="88"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="88"/>
+      <c r="U11" s="88"/>
+      <c r="V11" s="88"/>
+      <c r="W11" s="88"/>
+      <c r="X11" s="88"/>
+      <c r="Y11" s="88"/>
+      <c r="Z11" s="88"/>
+      <c r="AA11" s="88"/>
+      <c r="AB11" s="88"/>
+      <c r="AC11" s="88"/>
+      <c r="AD11" s="88"/>
+      <c r="AE11" s="89"/>
+      <c r="AF11" s="84" t="s">
         <v>290</v>
       </c>
-      <c r="AG11" s="121"/>
-      <c r="AH11" s="121"/>
-      <c r="AI11" s="122"/>
+      <c r="AG11" s="85"/>
+      <c r="AH11" s="85"/>
+      <c r="AI11" s="86"/>
     </row>
     <row r="12" spans="1:40" s="9" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="28"/>
-      <c r="B12" s="145"/>
-      <c r="C12" s="146"/>
-      <c r="D12" s="147"/>
-      <c r="E12" s="148"/>
-      <c r="F12" s="149"/>
-      <c r="G12" s="114" t="s">
+      <c r="B12" s="91"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="78" t="s">
         <v>337</v>
       </c>
-      <c r="H12" s="119"/>
-      <c r="I12" s="115"/>
-      <c r="J12" s="123" t="s">
+      <c r="H12" s="83"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="87" t="s">
         <v>406</v>
       </c>
-      <c r="K12" s="121"/>
-      <c r="L12" s="121"/>
-      <c r="M12" s="121"/>
-      <c r="N12" s="121"/>
-      <c r="O12" s="121"/>
-      <c r="P12" s="122"/>
-      <c r="Q12" s="123" t="s">
+      <c r="K12" s="85"/>
+      <c r="L12" s="85"/>
+      <c r="M12" s="85"/>
+      <c r="N12" s="85"/>
+      <c r="O12" s="85"/>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="87" t="s">
         <v>407</v>
       </c>
-      <c r="R12" s="124"/>
-      <c r="S12" s="124"/>
-      <c r="T12" s="124"/>
-      <c r="U12" s="124"/>
-      <c r="V12" s="124"/>
-      <c r="W12" s="124"/>
-      <c r="X12" s="124"/>
-      <c r="Y12" s="124"/>
-      <c r="Z12" s="124"/>
-      <c r="AA12" s="124"/>
-      <c r="AB12" s="124"/>
-      <c r="AC12" s="124"/>
-      <c r="AD12" s="124"/>
-      <c r="AE12" s="125"/>
-      <c r="AF12" s="120" t="s">
+      <c r="R12" s="88"/>
+      <c r="S12" s="88"/>
+      <c r="T12" s="88"/>
+      <c r="U12" s="88"/>
+      <c r="V12" s="88"/>
+      <c r="W12" s="88"/>
+      <c r="X12" s="88"/>
+      <c r="Y12" s="88"/>
+      <c r="Z12" s="88"/>
+      <c r="AA12" s="88"/>
+      <c r="AB12" s="88"/>
+      <c r="AC12" s="88"/>
+      <c r="AD12" s="88"/>
+      <c r="AE12" s="89"/>
+      <c r="AF12" s="84" t="s">
         <v>290</v>
       </c>
-      <c r="AG12" s="121"/>
-      <c r="AH12" s="121"/>
-      <c r="AI12" s="122"/>
+      <c r="AG12" s="85"/>
+      <c r="AH12" s="85"/>
+      <c r="AI12" s="86"/>
     </row>
     <row r="13" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="29"/>
-      <c r="B13" s="114"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="116"/>
-      <c r="E13" s="117"/>
-      <c r="F13" s="118"/>
-      <c r="G13" s="114"/>
-      <c r="H13" s="119"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="120"/>
-      <c r="K13" s="121"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="122"/>
-      <c r="Q13" s="123"/>
-      <c r="R13" s="124"/>
-      <c r="S13" s="124"/>
-      <c r="T13" s="124"/>
-      <c r="U13" s="124"/>
-      <c r="V13" s="124"/>
-      <c r="W13" s="124"/>
-      <c r="X13" s="124"/>
-      <c r="Y13" s="124"/>
-      <c r="Z13" s="124"/>
-      <c r="AA13" s="124"/>
-      <c r="AB13" s="124"/>
-      <c r="AC13" s="124"/>
-      <c r="AD13" s="124"/>
-      <c r="AE13" s="125"/>
-      <c r="AF13" s="120"/>
-      <c r="AG13" s="121"/>
-      <c r="AH13" s="121"/>
-      <c r="AI13" s="122"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
+      <c r="M13" s="85"/>
+      <c r="N13" s="85"/>
+      <c r="O13" s="85"/>
+      <c r="P13" s="86"/>
+      <c r="Q13" s="87"/>
+      <c r="R13" s="88"/>
+      <c r="S13" s="88"/>
+      <c r="T13" s="88"/>
+      <c r="U13" s="88"/>
+      <c r="V13" s="88"/>
+      <c r="W13" s="88"/>
+      <c r="X13" s="88"/>
+      <c r="Y13" s="88"/>
+      <c r="Z13" s="88"/>
+      <c r="AA13" s="88"/>
+      <c r="AB13" s="88"/>
+      <c r="AC13" s="88"/>
+      <c r="AD13" s="88"/>
+      <c r="AE13" s="89"/>
+      <c r="AF13" s="84"/>
+      <c r="AG13" s="85"/>
+      <c r="AH13" s="85"/>
+      <c r="AI13" s="86"/>
     </row>
     <row r="14" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="29"/>
-      <c r="B14" s="114"/>
-      <c r="C14" s="115"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="117"/>
-      <c r="F14" s="118"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="120"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="122"/>
-      <c r="Q14" s="123"/>
-      <c r="R14" s="124"/>
-      <c r="S14" s="124"/>
-      <c r="T14" s="124"/>
-      <c r="U14" s="124"/>
-      <c r="V14" s="124"/>
-      <c r="W14" s="124"/>
-      <c r="X14" s="124"/>
-      <c r="Y14" s="124"/>
-      <c r="Z14" s="124"/>
-      <c r="AA14" s="124"/>
-      <c r="AB14" s="124"/>
-      <c r="AC14" s="124"/>
-      <c r="AD14" s="124"/>
-      <c r="AE14" s="125"/>
-      <c r="AF14" s="120"/>
-      <c r="AG14" s="121"/>
-      <c r="AH14" s="121"/>
-      <c r="AI14" s="122"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="85"/>
+      <c r="L14" s="85"/>
+      <c r="M14" s="85"/>
+      <c r="N14" s="85"/>
+      <c r="O14" s="85"/>
+      <c r="P14" s="86"/>
+      <c r="Q14" s="87"/>
+      <c r="R14" s="88"/>
+      <c r="S14" s="88"/>
+      <c r="T14" s="88"/>
+      <c r="U14" s="88"/>
+      <c r="V14" s="88"/>
+      <c r="W14" s="88"/>
+      <c r="X14" s="88"/>
+      <c r="Y14" s="88"/>
+      <c r="Z14" s="88"/>
+      <c r="AA14" s="88"/>
+      <c r="AB14" s="88"/>
+      <c r="AC14" s="88"/>
+      <c r="AD14" s="88"/>
+      <c r="AE14" s="89"/>
+      <c r="AF14" s="84"/>
+      <c r="AG14" s="85"/>
+      <c r="AH14" s="85"/>
+      <c r="AI14" s="86"/>
     </row>
     <row r="15" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="29"/>
-      <c r="B15" s="114"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="119"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="120"/>
-      <c r="K15" s="121"/>
-      <c r="L15" s="121"/>
-      <c r="M15" s="121"/>
-      <c r="N15" s="121"/>
-      <c r="O15" s="121"/>
-      <c r="P15" s="122"/>
-      <c r="Q15" s="123"/>
-      <c r="R15" s="124"/>
-      <c r="S15" s="124"/>
-      <c r="T15" s="124"/>
-      <c r="U15" s="124"/>
-      <c r="V15" s="124"/>
-      <c r="W15" s="124"/>
-      <c r="X15" s="124"/>
-      <c r="Y15" s="124"/>
-      <c r="Z15" s="124"/>
-      <c r="AA15" s="124"/>
-      <c r="AB15" s="124"/>
-      <c r="AC15" s="124"/>
-      <c r="AD15" s="124"/>
-      <c r="AE15" s="125"/>
-      <c r="AF15" s="120"/>
-      <c r="AG15" s="121"/>
-      <c r="AH15" s="121"/>
-      <c r="AI15" s="122"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="85"/>
+      <c r="M15" s="85"/>
+      <c r="N15" s="85"/>
+      <c r="O15" s="85"/>
+      <c r="P15" s="86"/>
+      <c r="Q15" s="87"/>
+      <c r="R15" s="88"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="88"/>
+      <c r="U15" s="88"/>
+      <c r="V15" s="88"/>
+      <c r="W15" s="88"/>
+      <c r="X15" s="88"/>
+      <c r="Y15" s="88"/>
+      <c r="Z15" s="88"/>
+      <c r="AA15" s="88"/>
+      <c r="AB15" s="88"/>
+      <c r="AC15" s="88"/>
+      <c r="AD15" s="88"/>
+      <c r="AE15" s="89"/>
+      <c r="AF15" s="84"/>
+      <c r="AG15" s="85"/>
+      <c r="AH15" s="85"/>
+      <c r="AI15" s="86"/>
     </row>
     <row r="16" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="29"/>
-      <c r="B16" s="114"/>
-      <c r="C16" s="115"/>
-      <c r="D16" s="116"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="114"/>
-      <c r="H16" s="119"/>
-      <c r="I16" s="115"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="121"/>
-      <c r="L16" s="121"/>
-      <c r="M16" s="121"/>
-      <c r="N16" s="121"/>
-      <c r="O16" s="121"/>
-      <c r="P16" s="122"/>
-      <c r="Q16" s="123"/>
-      <c r="R16" s="124"/>
-      <c r="S16" s="124"/>
-      <c r="T16" s="124"/>
-      <c r="U16" s="124"/>
-      <c r="V16" s="124"/>
-      <c r="W16" s="124"/>
-      <c r="X16" s="124"/>
-      <c r="Y16" s="124"/>
-      <c r="Z16" s="124"/>
-      <c r="AA16" s="124"/>
-      <c r="AB16" s="124"/>
-      <c r="AC16" s="124"/>
-      <c r="AD16" s="124"/>
-      <c r="AE16" s="125"/>
-      <c r="AF16" s="120"/>
-      <c r="AG16" s="121"/>
-      <c r="AH16" s="121"/>
-      <c r="AI16" s="122"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="85"/>
+      <c r="L16" s="85"/>
+      <c r="M16" s="85"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="85"/>
+      <c r="P16" s="86"/>
+      <c r="Q16" s="87"/>
+      <c r="R16" s="88"/>
+      <c r="S16" s="88"/>
+      <c r="T16" s="88"/>
+      <c r="U16" s="88"/>
+      <c r="V16" s="88"/>
+      <c r="W16" s="88"/>
+      <c r="X16" s="88"/>
+      <c r="Y16" s="88"/>
+      <c r="Z16" s="88"/>
+      <c r="AA16" s="88"/>
+      <c r="AB16" s="88"/>
+      <c r="AC16" s="88"/>
+      <c r="AD16" s="88"/>
+      <c r="AE16" s="89"/>
+      <c r="AF16" s="84"/>
+      <c r="AG16" s="85"/>
+      <c r="AH16" s="85"/>
+      <c r="AI16" s="86"/>
     </row>
     <row r="17" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="29"/>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116"/>
-      <c r="E17" s="117"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="119"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="120"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="121"/>
-      <c r="P17" s="122"/>
-      <c r="Q17" s="123"/>
-      <c r="R17" s="124"/>
-      <c r="S17" s="124"/>
-      <c r="T17" s="124"/>
-      <c r="U17" s="124"/>
-      <c r="V17" s="124"/>
-      <c r="W17" s="124"/>
-      <c r="X17" s="124"/>
-      <c r="Y17" s="124"/>
-      <c r="Z17" s="124"/>
-      <c r="AA17" s="124"/>
-      <c r="AB17" s="124"/>
-      <c r="AC17" s="124"/>
-      <c r="AD17" s="124"/>
-      <c r="AE17" s="125"/>
-      <c r="AF17" s="120"/>
-      <c r="AG17" s="121"/>
-      <c r="AH17" s="121"/>
-      <c r="AI17" s="122"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="85"/>
+      <c r="L17" s="85"/>
+      <c r="M17" s="85"/>
+      <c r="N17" s="85"/>
+      <c r="O17" s="85"/>
+      <c r="P17" s="86"/>
+      <c r="Q17" s="87"/>
+      <c r="R17" s="88"/>
+      <c r="S17" s="88"/>
+      <c r="T17" s="88"/>
+      <c r="U17" s="88"/>
+      <c r="V17" s="88"/>
+      <c r="W17" s="88"/>
+      <c r="X17" s="88"/>
+      <c r="Y17" s="88"/>
+      <c r="Z17" s="88"/>
+      <c r="AA17" s="88"/>
+      <c r="AB17" s="88"/>
+      <c r="AC17" s="88"/>
+      <c r="AD17" s="88"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="84"/>
+      <c r="AG17" s="85"/>
+      <c r="AH17" s="85"/>
+      <c r="AI17" s="86"/>
     </row>
     <row r="18" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="29"/>
-      <c r="B18" s="114"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="119"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="120"/>
-      <c r="K18" s="121"/>
-      <c r="L18" s="121"/>
-      <c r="M18" s="121"/>
-      <c r="N18" s="121"/>
-      <c r="O18" s="121"/>
-      <c r="P18" s="122"/>
-      <c r="Q18" s="123"/>
-      <c r="R18" s="124"/>
-      <c r="S18" s="124"/>
-      <c r="T18" s="124"/>
-      <c r="U18" s="124"/>
-      <c r="V18" s="124"/>
-      <c r="W18" s="124"/>
-      <c r="X18" s="124"/>
-      <c r="Y18" s="124"/>
-      <c r="Z18" s="124"/>
-      <c r="AA18" s="124"/>
-      <c r="AB18" s="124"/>
-      <c r="AC18" s="124"/>
-      <c r="AD18" s="124"/>
-      <c r="AE18" s="125"/>
-      <c r="AF18" s="120"/>
-      <c r="AG18" s="121"/>
-      <c r="AH18" s="121"/>
-      <c r="AI18" s="122"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="85"/>
+      <c r="M18" s="85"/>
+      <c r="N18" s="85"/>
+      <c r="O18" s="85"/>
+      <c r="P18" s="86"/>
+      <c r="Q18" s="87"/>
+      <c r="R18" s="88"/>
+      <c r="S18" s="88"/>
+      <c r="T18" s="88"/>
+      <c r="U18" s="88"/>
+      <c r="V18" s="88"/>
+      <c r="W18" s="88"/>
+      <c r="X18" s="88"/>
+      <c r="Y18" s="88"/>
+      <c r="Z18" s="88"/>
+      <c r="AA18" s="88"/>
+      <c r="AB18" s="88"/>
+      <c r="AC18" s="88"/>
+      <c r="AD18" s="88"/>
+      <c r="AE18" s="89"/>
+      <c r="AF18" s="84"/>
+      <c r="AG18" s="85"/>
+      <c r="AH18" s="85"/>
+      <c r="AI18" s="86"/>
     </row>
     <row r="19" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="29"/>
-      <c r="B19" s="114"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="114"/>
-      <c r="H19" s="119"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="120"/>
-      <c r="K19" s="121"/>
-      <c r="L19" s="121"/>
-      <c r="M19" s="121"/>
-      <c r="N19" s="121"/>
-      <c r="O19" s="121"/>
-      <c r="P19" s="122"/>
-      <c r="Q19" s="123"/>
-      <c r="R19" s="124"/>
-      <c r="S19" s="124"/>
-      <c r="T19" s="124"/>
-      <c r="U19" s="124"/>
-      <c r="V19" s="124"/>
-      <c r="W19" s="124"/>
-      <c r="X19" s="124"/>
-      <c r="Y19" s="124"/>
-      <c r="Z19" s="124"/>
-      <c r="AA19" s="124"/>
-      <c r="AB19" s="124"/>
-      <c r="AC19" s="124"/>
-      <c r="AD19" s="124"/>
-      <c r="AE19" s="125"/>
-      <c r="AF19" s="120"/>
-      <c r="AG19" s="121"/>
-      <c r="AH19" s="121"/>
-      <c r="AI19" s="122"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="85"/>
+      <c r="L19" s="85"/>
+      <c r="M19" s="85"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="85"/>
+      <c r="P19" s="86"/>
+      <c r="Q19" s="87"/>
+      <c r="R19" s="88"/>
+      <c r="S19" s="88"/>
+      <c r="T19" s="88"/>
+      <c r="U19" s="88"/>
+      <c r="V19" s="88"/>
+      <c r="W19" s="88"/>
+      <c r="X19" s="88"/>
+      <c r="Y19" s="88"/>
+      <c r="Z19" s="88"/>
+      <c r="AA19" s="88"/>
+      <c r="AB19" s="88"/>
+      <c r="AC19" s="88"/>
+      <c r="AD19" s="88"/>
+      <c r="AE19" s="89"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="85"/>
+      <c r="AH19" s="85"/>
+      <c r="AI19" s="86"/>
     </row>
     <row r="20" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="29"/>
-      <c r="B20" s="114"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="116"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="114"/>
-      <c r="H20" s="119"/>
-      <c r="I20" s="115"/>
-      <c r="J20" s="120"/>
-      <c r="K20" s="121"/>
-      <c r="L20" s="121"/>
-      <c r="M20" s="121"/>
-      <c r="N20" s="121"/>
-      <c r="O20" s="121"/>
-      <c r="P20" s="122"/>
-      <c r="Q20" s="123"/>
-      <c r="R20" s="124"/>
-      <c r="S20" s="124"/>
-      <c r="T20" s="124"/>
-      <c r="U20" s="124"/>
-      <c r="V20" s="124"/>
-      <c r="W20" s="124"/>
-      <c r="X20" s="124"/>
-      <c r="Y20" s="124"/>
-      <c r="Z20" s="124"/>
-      <c r="AA20" s="124"/>
-      <c r="AB20" s="124"/>
-      <c r="AC20" s="124"/>
-      <c r="AD20" s="124"/>
-      <c r="AE20" s="125"/>
-      <c r="AF20" s="120"/>
-      <c r="AG20" s="121"/>
-      <c r="AH20" s="121"/>
-      <c r="AI20" s="122"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="84"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="85"/>
+      <c r="M20" s="85"/>
+      <c r="N20" s="85"/>
+      <c r="O20" s="85"/>
+      <c r="P20" s="86"/>
+      <c r="Q20" s="87"/>
+      <c r="R20" s="88"/>
+      <c r="S20" s="88"/>
+      <c r="T20" s="88"/>
+      <c r="U20" s="88"/>
+      <c r="V20" s="88"/>
+      <c r="W20" s="88"/>
+      <c r="X20" s="88"/>
+      <c r="Y20" s="88"/>
+      <c r="Z20" s="88"/>
+      <c r="AA20" s="88"/>
+      <c r="AB20" s="88"/>
+      <c r="AC20" s="88"/>
+      <c r="AD20" s="88"/>
+      <c r="AE20" s="89"/>
+      <c r="AF20" s="84"/>
+      <c r="AG20" s="85"/>
+      <c r="AH20" s="85"/>
+      <c r="AI20" s="86"/>
     </row>
     <row r="21" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="29"/>
-      <c r="B21" s="114"/>
-      <c r="C21" s="115"/>
-      <c r="D21" s="116"/>
-      <c r="E21" s="117"/>
-      <c r="F21" s="118"/>
-      <c r="G21" s="114"/>
-      <c r="H21" s="119"/>
-      <c r="I21" s="115"/>
-      <c r="J21" s="120"/>
-      <c r="K21" s="121"/>
-      <c r="L21" s="121"/>
-      <c r="M21" s="121"/>
-      <c r="N21" s="121"/>
-      <c r="O21" s="121"/>
-      <c r="P21" s="122"/>
-      <c r="Q21" s="123"/>
-      <c r="R21" s="124"/>
-      <c r="S21" s="124"/>
-      <c r="T21" s="124"/>
-      <c r="U21" s="124"/>
-      <c r="V21" s="124"/>
-      <c r="W21" s="124"/>
-      <c r="X21" s="124"/>
-      <c r="Y21" s="124"/>
-      <c r="Z21" s="124"/>
-      <c r="AA21" s="124"/>
-      <c r="AB21" s="124"/>
-      <c r="AC21" s="124"/>
-      <c r="AD21" s="124"/>
-      <c r="AE21" s="125"/>
-      <c r="AF21" s="120"/>
-      <c r="AG21" s="121"/>
-      <c r="AH21" s="121"/>
-      <c r="AI21" s="122"/>
+      <c r="B21" s="78"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="85"/>
+      <c r="L21" s="85"/>
+      <c r="M21" s="85"/>
+      <c r="N21" s="85"/>
+      <c r="O21" s="85"/>
+      <c r="P21" s="86"/>
+      <c r="Q21" s="87"/>
+      <c r="R21" s="88"/>
+      <c r="S21" s="88"/>
+      <c r="T21" s="88"/>
+      <c r="U21" s="88"/>
+      <c r="V21" s="88"/>
+      <c r="W21" s="88"/>
+      <c r="X21" s="88"/>
+      <c r="Y21" s="88"/>
+      <c r="Z21" s="88"/>
+      <c r="AA21" s="88"/>
+      <c r="AB21" s="88"/>
+      <c r="AC21" s="88"/>
+      <c r="AD21" s="88"/>
+      <c r="AE21" s="89"/>
+      <c r="AF21" s="84"/>
+      <c r="AG21" s="85"/>
+      <c r="AH21" s="85"/>
+      <c r="AI21" s="86"/>
     </row>
     <row r="22" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="29"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="116"/>
-      <c r="E22" s="117"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="114"/>
-      <c r="H22" s="119"/>
-      <c r="I22" s="115"/>
-      <c r="J22" s="120"/>
-      <c r="K22" s="121"/>
-      <c r="L22" s="121"/>
-      <c r="M22" s="121"/>
-      <c r="N22" s="121"/>
-      <c r="O22" s="121"/>
-      <c r="P22" s="122"/>
-      <c r="Q22" s="123"/>
-      <c r="R22" s="124"/>
-      <c r="S22" s="124"/>
-      <c r="T22" s="124"/>
-      <c r="U22" s="124"/>
-      <c r="V22" s="124"/>
-      <c r="W22" s="124"/>
-      <c r="X22" s="124"/>
-      <c r="Y22" s="124"/>
-      <c r="Z22" s="124"/>
-      <c r="AA22" s="124"/>
-      <c r="AB22" s="124"/>
-      <c r="AC22" s="124"/>
-      <c r="AD22" s="124"/>
-      <c r="AE22" s="125"/>
-      <c r="AF22" s="120"/>
-      <c r="AG22" s="121"/>
-      <c r="AH22" s="121"/>
-      <c r="AI22" s="122"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="85"/>
+      <c r="L22" s="85"/>
+      <c r="M22" s="85"/>
+      <c r="N22" s="85"/>
+      <c r="O22" s="85"/>
+      <c r="P22" s="86"/>
+      <c r="Q22" s="87"/>
+      <c r="R22" s="88"/>
+      <c r="S22" s="88"/>
+      <c r="T22" s="88"/>
+      <c r="U22" s="88"/>
+      <c r="V22" s="88"/>
+      <c r="W22" s="88"/>
+      <c r="X22" s="88"/>
+      <c r="Y22" s="88"/>
+      <c r="Z22" s="88"/>
+      <c r="AA22" s="88"/>
+      <c r="AB22" s="88"/>
+      <c r="AC22" s="88"/>
+      <c r="AD22" s="88"/>
+      <c r="AE22" s="89"/>
+      <c r="AF22" s="84"/>
+      <c r="AG22" s="85"/>
+      <c r="AH22" s="85"/>
+      <c r="AI22" s="86"/>
     </row>
     <row r="23" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="29"/>
-      <c r="B23" s="114"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="116"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="114"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="115"/>
-      <c r="J23" s="120"/>
-      <c r="K23" s="121"/>
-      <c r="L23" s="121"/>
-      <c r="M23" s="121"/>
-      <c r="N23" s="121"/>
-      <c r="O23" s="121"/>
-      <c r="P23" s="122"/>
-      <c r="Q23" s="123"/>
-      <c r="R23" s="124"/>
-      <c r="S23" s="124"/>
-      <c r="T23" s="124"/>
-      <c r="U23" s="124"/>
-      <c r="V23" s="124"/>
-      <c r="W23" s="124"/>
-      <c r="X23" s="124"/>
-      <c r="Y23" s="124"/>
-      <c r="Z23" s="124"/>
-      <c r="AA23" s="124"/>
-      <c r="AB23" s="124"/>
-      <c r="AC23" s="124"/>
-      <c r="AD23" s="124"/>
-      <c r="AE23" s="125"/>
-      <c r="AF23" s="120"/>
-      <c r="AG23" s="121"/>
-      <c r="AH23" s="121"/>
-      <c r="AI23" s="122"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="85"/>
+      <c r="M23" s="85"/>
+      <c r="N23" s="85"/>
+      <c r="O23" s="85"/>
+      <c r="P23" s="86"/>
+      <c r="Q23" s="87"/>
+      <c r="R23" s="88"/>
+      <c r="S23" s="88"/>
+      <c r="T23" s="88"/>
+      <c r="U23" s="88"/>
+      <c r="V23" s="88"/>
+      <c r="W23" s="88"/>
+      <c r="X23" s="88"/>
+      <c r="Y23" s="88"/>
+      <c r="Z23" s="88"/>
+      <c r="AA23" s="88"/>
+      <c r="AB23" s="88"/>
+      <c r="AC23" s="88"/>
+      <c r="AD23" s="88"/>
+      <c r="AE23" s="89"/>
+      <c r="AF23" s="84"/>
+      <c r="AG23" s="85"/>
+      <c r="AH23" s="85"/>
+      <c r="AI23" s="86"/>
     </row>
     <row r="24" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="29"/>
-      <c r="B24" s="114"/>
-      <c r="C24" s="115"/>
-      <c r="D24" s="116"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="118"/>
-      <c r="G24" s="114"/>
-      <c r="H24" s="119"/>
-      <c r="I24" s="115"/>
-      <c r="J24" s="120"/>
-      <c r="K24" s="121"/>
-      <c r="L24" s="121"/>
-      <c r="M24" s="121"/>
-      <c r="N24" s="121"/>
-      <c r="O24" s="121"/>
-      <c r="P24" s="122"/>
-      <c r="Q24" s="123"/>
-      <c r="R24" s="124"/>
-      <c r="S24" s="124"/>
-      <c r="T24" s="124"/>
-      <c r="U24" s="124"/>
-      <c r="V24" s="124"/>
-      <c r="W24" s="124"/>
-      <c r="X24" s="124"/>
-      <c r="Y24" s="124"/>
-      <c r="Z24" s="124"/>
-      <c r="AA24" s="124"/>
-      <c r="AB24" s="124"/>
-      <c r="AC24" s="124"/>
-      <c r="AD24" s="124"/>
-      <c r="AE24" s="125"/>
-      <c r="AF24" s="120"/>
-      <c r="AG24" s="121"/>
-      <c r="AH24" s="121"/>
-      <c r="AI24" s="122"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="79"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="85"/>
+      <c r="L24" s="85"/>
+      <c r="M24" s="85"/>
+      <c r="N24" s="85"/>
+      <c r="O24" s="85"/>
+      <c r="P24" s="86"/>
+      <c r="Q24" s="87"/>
+      <c r="R24" s="88"/>
+      <c r="S24" s="88"/>
+      <c r="T24" s="88"/>
+      <c r="U24" s="88"/>
+      <c r="V24" s="88"/>
+      <c r="W24" s="88"/>
+      <c r="X24" s="88"/>
+      <c r="Y24" s="88"/>
+      <c r="Z24" s="88"/>
+      <c r="AA24" s="88"/>
+      <c r="AB24" s="88"/>
+      <c r="AC24" s="88"/>
+      <c r="AD24" s="88"/>
+      <c r="AE24" s="89"/>
+      <c r="AF24" s="84"/>
+      <c r="AG24" s="85"/>
+      <c r="AH24" s="85"/>
+      <c r="AI24" s="86"/>
     </row>
     <row r="25" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="29"/>
-      <c r="B25" s="114"/>
-      <c r="C25" s="115"/>
-      <c r="D25" s="116"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="118"/>
-      <c r="G25" s="114"/>
-      <c r="H25" s="119"/>
-      <c r="I25" s="115"/>
-      <c r="J25" s="120"/>
-      <c r="K25" s="121"/>
-      <c r="L25" s="121"/>
-      <c r="M25" s="121"/>
-      <c r="N25" s="121"/>
-      <c r="O25" s="121"/>
-      <c r="P25" s="122"/>
-      <c r="Q25" s="123"/>
-      <c r="R25" s="124"/>
-      <c r="S25" s="124"/>
-      <c r="T25" s="124"/>
-      <c r="U25" s="124"/>
-      <c r="V25" s="124"/>
-      <c r="W25" s="124"/>
-      <c r="X25" s="124"/>
-      <c r="Y25" s="124"/>
-      <c r="Z25" s="124"/>
-      <c r="AA25" s="124"/>
-      <c r="AB25" s="124"/>
-      <c r="AC25" s="124"/>
-      <c r="AD25" s="124"/>
-      <c r="AE25" s="125"/>
-      <c r="AF25" s="120"/>
-      <c r="AG25" s="121"/>
-      <c r="AH25" s="121"/>
-      <c r="AI25" s="122"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="78"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="85"/>
+      <c r="L25" s="85"/>
+      <c r="M25" s="85"/>
+      <c r="N25" s="85"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="88"/>
+      <c r="S25" s="88"/>
+      <c r="T25" s="88"/>
+      <c r="U25" s="88"/>
+      <c r="V25" s="88"/>
+      <c r="W25" s="88"/>
+      <c r="X25" s="88"/>
+      <c r="Y25" s="88"/>
+      <c r="Z25" s="88"/>
+      <c r="AA25" s="88"/>
+      <c r="AB25" s="88"/>
+      <c r="AC25" s="88"/>
+      <c r="AD25" s="88"/>
+      <c r="AE25" s="89"/>
+      <c r="AF25" s="84"/>
+      <c r="AG25" s="85"/>
+      <c r="AH25" s="85"/>
+      <c r="AI25" s="86"/>
     </row>
     <row r="26" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="29"/>
-      <c r="B26" s="114"/>
-      <c r="C26" s="115"/>
-      <c r="D26" s="116"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="118"/>
-      <c r="G26" s="114"/>
-      <c r="H26" s="119"/>
-      <c r="I26" s="115"/>
-      <c r="J26" s="120"/>
-      <c r="K26" s="121"/>
-      <c r="L26" s="121"/>
-      <c r="M26" s="121"/>
-      <c r="N26" s="121"/>
-      <c r="O26" s="121"/>
-      <c r="P26" s="122"/>
-      <c r="Q26" s="123"/>
-      <c r="R26" s="124"/>
-      <c r="S26" s="124"/>
-      <c r="T26" s="124"/>
-      <c r="U26" s="124"/>
-      <c r="V26" s="124"/>
-      <c r="W26" s="124"/>
-      <c r="X26" s="124"/>
-      <c r="Y26" s="124"/>
-      <c r="Z26" s="124"/>
-      <c r="AA26" s="124"/>
-      <c r="AB26" s="124"/>
-      <c r="AC26" s="124"/>
-      <c r="AD26" s="124"/>
-      <c r="AE26" s="125"/>
-      <c r="AF26" s="120"/>
-      <c r="AG26" s="121"/>
-      <c r="AH26" s="121"/>
-      <c r="AI26" s="122"/>
+      <c r="B26" s="78"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="79"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="85"/>
+      <c r="L26" s="85"/>
+      <c r="M26" s="85"/>
+      <c r="N26" s="85"/>
+      <c r="O26" s="85"/>
+      <c r="P26" s="86"/>
+      <c r="Q26" s="87"/>
+      <c r="R26" s="88"/>
+      <c r="S26" s="88"/>
+      <c r="T26" s="88"/>
+      <c r="U26" s="88"/>
+      <c r="V26" s="88"/>
+      <c r="W26" s="88"/>
+      <c r="X26" s="88"/>
+      <c r="Y26" s="88"/>
+      <c r="Z26" s="88"/>
+      <c r="AA26" s="88"/>
+      <c r="AB26" s="88"/>
+      <c r="AC26" s="88"/>
+      <c r="AD26" s="88"/>
+      <c r="AE26" s="89"/>
+      <c r="AF26" s="84"/>
+      <c r="AG26" s="85"/>
+      <c r="AH26" s="85"/>
+      <c r="AI26" s="86"/>
     </row>
     <row r="27" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="29"/>
-      <c r="B27" s="114"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="116"/>
-      <c r="E27" s="117"/>
-      <c r="F27" s="118"/>
-      <c r="G27" s="114"/>
-      <c r="H27" s="119"/>
-      <c r="I27" s="115"/>
-      <c r="J27" s="120"/>
-      <c r="K27" s="121"/>
-      <c r="L27" s="121"/>
-      <c r="M27" s="121"/>
-      <c r="N27" s="121"/>
-      <c r="O27" s="121"/>
-      <c r="P27" s="122"/>
-      <c r="Q27" s="123"/>
-      <c r="R27" s="124"/>
-      <c r="S27" s="124"/>
-      <c r="T27" s="124"/>
-      <c r="U27" s="124"/>
-      <c r="V27" s="124"/>
-      <c r="W27" s="124"/>
-      <c r="X27" s="124"/>
-      <c r="Y27" s="124"/>
-      <c r="Z27" s="124"/>
-      <c r="AA27" s="124"/>
-      <c r="AB27" s="124"/>
-      <c r="AC27" s="124"/>
-      <c r="AD27" s="124"/>
-      <c r="AE27" s="125"/>
-      <c r="AF27" s="120"/>
-      <c r="AG27" s="121"/>
-      <c r="AH27" s="121"/>
-      <c r="AI27" s="122"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="79"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="83"/>
+      <c r="I27" s="79"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="85"/>
+      <c r="M27" s="85"/>
+      <c r="N27" s="85"/>
+      <c r="O27" s="85"/>
+      <c r="P27" s="86"/>
+      <c r="Q27" s="87"/>
+      <c r="R27" s="88"/>
+      <c r="S27" s="88"/>
+      <c r="T27" s="88"/>
+      <c r="U27" s="88"/>
+      <c r="V27" s="88"/>
+      <c r="W27" s="88"/>
+      <c r="X27" s="88"/>
+      <c r="Y27" s="88"/>
+      <c r="Z27" s="88"/>
+      <c r="AA27" s="88"/>
+      <c r="AB27" s="88"/>
+      <c r="AC27" s="88"/>
+      <c r="AD27" s="88"/>
+      <c r="AE27" s="89"/>
+      <c r="AF27" s="84"/>
+      <c r="AG27" s="85"/>
+      <c r="AH27" s="85"/>
+      <c r="AI27" s="86"/>
     </row>
     <row r="28" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="29"/>
-      <c r="B28" s="114"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="116"/>
-      <c r="E28" s="117"/>
-      <c r="F28" s="118"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="115"/>
-      <c r="J28" s="120"/>
-      <c r="K28" s="121"/>
-      <c r="L28" s="121"/>
-      <c r="M28" s="121"/>
-      <c r="N28" s="121"/>
-      <c r="O28" s="121"/>
-      <c r="P28" s="122"/>
-      <c r="Q28" s="123"/>
-      <c r="R28" s="124"/>
-      <c r="S28" s="124"/>
-      <c r="T28" s="124"/>
-      <c r="U28" s="124"/>
-      <c r="V28" s="124"/>
-      <c r="W28" s="124"/>
-      <c r="X28" s="124"/>
-      <c r="Y28" s="124"/>
-      <c r="Z28" s="124"/>
-      <c r="AA28" s="124"/>
-      <c r="AB28" s="124"/>
-      <c r="AC28" s="124"/>
-      <c r="AD28" s="124"/>
-      <c r="AE28" s="125"/>
-      <c r="AF28" s="120"/>
-      <c r="AG28" s="121"/>
-      <c r="AH28" s="121"/>
-      <c r="AI28" s="122"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="79"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="78"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="85"/>
+      <c r="L28" s="85"/>
+      <c r="M28" s="85"/>
+      <c r="N28" s="85"/>
+      <c r="O28" s="85"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="87"/>
+      <c r="R28" s="88"/>
+      <c r="S28" s="88"/>
+      <c r="T28" s="88"/>
+      <c r="U28" s="88"/>
+      <c r="V28" s="88"/>
+      <c r="W28" s="88"/>
+      <c r="X28" s="88"/>
+      <c r="Y28" s="88"/>
+      <c r="Z28" s="88"/>
+      <c r="AA28" s="88"/>
+      <c r="AB28" s="88"/>
+      <c r="AC28" s="88"/>
+      <c r="AD28" s="88"/>
+      <c r="AE28" s="89"/>
+      <c r="AF28" s="84"/>
+      <c r="AG28" s="85"/>
+      <c r="AH28" s="85"/>
+      <c r="AI28" s="86"/>
     </row>
     <row r="29" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="29"/>
-      <c r="B29" s="114"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="116"/>
-      <c r="E29" s="117"/>
-      <c r="F29" s="118"/>
-      <c r="G29" s="114"/>
-      <c r="H29" s="119"/>
-      <c r="I29" s="115"/>
-      <c r="J29" s="120"/>
-      <c r="K29" s="121"/>
-      <c r="L29" s="121"/>
-      <c r="M29" s="121"/>
-      <c r="N29" s="121"/>
-      <c r="O29" s="121"/>
-      <c r="P29" s="122"/>
-      <c r="Q29" s="123"/>
-      <c r="R29" s="124"/>
-      <c r="S29" s="124"/>
-      <c r="T29" s="124"/>
-      <c r="U29" s="124"/>
-      <c r="V29" s="124"/>
-      <c r="W29" s="124"/>
-      <c r="X29" s="124"/>
-      <c r="Y29" s="124"/>
-      <c r="Z29" s="124"/>
-      <c r="AA29" s="124"/>
-      <c r="AB29" s="124"/>
-      <c r="AC29" s="124"/>
-      <c r="AD29" s="124"/>
-      <c r="AE29" s="125"/>
-      <c r="AF29" s="120"/>
-      <c r="AG29" s="121"/>
-      <c r="AH29" s="121"/>
-      <c r="AI29" s="122"/>
+      <c r="B29" s="78"/>
+      <c r="C29" s="79"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="78"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="85"/>
+      <c r="M29" s="85"/>
+      <c r="N29" s="85"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="86"/>
+      <c r="Q29" s="87"/>
+      <c r="R29" s="88"/>
+      <c r="S29" s="88"/>
+      <c r="T29" s="88"/>
+      <c r="U29" s="88"/>
+      <c r="V29" s="88"/>
+      <c r="W29" s="88"/>
+      <c r="X29" s="88"/>
+      <c r="Y29" s="88"/>
+      <c r="Z29" s="88"/>
+      <c r="AA29" s="88"/>
+      <c r="AB29" s="88"/>
+      <c r="AC29" s="88"/>
+      <c r="AD29" s="88"/>
+      <c r="AE29" s="89"/>
+      <c r="AF29" s="84"/>
+      <c r="AG29" s="85"/>
+      <c r="AH29" s="85"/>
+      <c r="AI29" s="86"/>
     </row>
     <row r="30" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="29"/>
-      <c r="B30" s="114"/>
-      <c r="C30" s="115"/>
-      <c r="D30" s="116"/>
-      <c r="E30" s="117"/>
-      <c r="F30" s="118"/>
-      <c r="G30" s="114"/>
-      <c r="H30" s="119"/>
-      <c r="I30" s="115"/>
-      <c r="J30" s="120"/>
-      <c r="K30" s="121"/>
-      <c r="L30" s="121"/>
-      <c r="M30" s="121"/>
-      <c r="N30" s="121"/>
-      <c r="O30" s="121"/>
-      <c r="P30" s="122"/>
-      <c r="Q30" s="123"/>
-      <c r="R30" s="124"/>
-      <c r="S30" s="124"/>
-      <c r="T30" s="124"/>
-      <c r="U30" s="124"/>
-      <c r="V30" s="124"/>
-      <c r="W30" s="124"/>
-      <c r="X30" s="124"/>
-      <c r="Y30" s="124"/>
-      <c r="Z30" s="124"/>
-      <c r="AA30" s="124"/>
-      <c r="AB30" s="124"/>
-      <c r="AC30" s="124"/>
-      <c r="AD30" s="124"/>
-      <c r="AE30" s="125"/>
-      <c r="AF30" s="120"/>
-      <c r="AG30" s="121"/>
-      <c r="AH30" s="121"/>
-      <c r="AI30" s="122"/>
+      <c r="B30" s="78"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="85"/>
+      <c r="L30" s="85"/>
+      <c r="M30" s="85"/>
+      <c r="N30" s="85"/>
+      <c r="O30" s="85"/>
+      <c r="P30" s="86"/>
+      <c r="Q30" s="87"/>
+      <c r="R30" s="88"/>
+      <c r="S30" s="88"/>
+      <c r="T30" s="88"/>
+      <c r="U30" s="88"/>
+      <c r="V30" s="88"/>
+      <c r="W30" s="88"/>
+      <c r="X30" s="88"/>
+      <c r="Y30" s="88"/>
+      <c r="Z30" s="88"/>
+      <c r="AA30" s="88"/>
+      <c r="AB30" s="88"/>
+      <c r="AC30" s="88"/>
+      <c r="AD30" s="88"/>
+      <c r="AE30" s="89"/>
+      <c r="AF30" s="84"/>
+      <c r="AG30" s="85"/>
+      <c r="AH30" s="85"/>
+      <c r="AI30" s="86"/>
     </row>
     <row r="31" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="29"/>
-      <c r="B31" s="114"/>
-      <c r="C31" s="115"/>
-      <c r="D31" s="116"/>
-      <c r="E31" s="117"/>
-      <c r="F31" s="118"/>
-      <c r="G31" s="114"/>
-      <c r="H31" s="119"/>
-      <c r="I31" s="115"/>
-      <c r="J31" s="120"/>
-      <c r="K31" s="121"/>
-      <c r="L31" s="121"/>
-      <c r="M31" s="121"/>
-      <c r="N31" s="121"/>
-      <c r="O31" s="121"/>
-      <c r="P31" s="122"/>
-      <c r="Q31" s="123"/>
-      <c r="R31" s="124"/>
-      <c r="S31" s="124"/>
-      <c r="T31" s="124"/>
-      <c r="U31" s="124"/>
-      <c r="V31" s="124"/>
-      <c r="W31" s="124"/>
-      <c r="X31" s="124"/>
-      <c r="Y31" s="124"/>
-      <c r="Z31" s="124"/>
-      <c r="AA31" s="124"/>
-      <c r="AB31" s="124"/>
-      <c r="AC31" s="124"/>
-      <c r="AD31" s="124"/>
-      <c r="AE31" s="125"/>
-      <c r="AF31" s="120"/>
-      <c r="AG31" s="121"/>
-      <c r="AH31" s="121"/>
-      <c r="AI31" s="122"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="79"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="79"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="85"/>
+      <c r="P31" s="86"/>
+      <c r="Q31" s="87"/>
+      <c r="R31" s="88"/>
+      <c r="S31" s="88"/>
+      <c r="T31" s="88"/>
+      <c r="U31" s="88"/>
+      <c r="V31" s="88"/>
+      <c r="W31" s="88"/>
+      <c r="X31" s="88"/>
+      <c r="Y31" s="88"/>
+      <c r="Z31" s="88"/>
+      <c r="AA31" s="88"/>
+      <c r="AB31" s="88"/>
+      <c r="AC31" s="88"/>
+      <c r="AD31" s="88"/>
+      <c r="AE31" s="89"/>
+      <c r="AF31" s="84"/>
+      <c r="AG31" s="85"/>
+      <c r="AH31" s="85"/>
+      <c r="AI31" s="86"/>
     </row>
     <row r="32" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="29"/>
-      <c r="B32" s="114"/>
-      <c r="C32" s="115"/>
-      <c r="D32" s="116"/>
-      <c r="E32" s="117"/>
-      <c r="F32" s="118"/>
-      <c r="G32" s="114"/>
-      <c r="H32" s="119"/>
-      <c r="I32" s="115"/>
-      <c r="J32" s="120"/>
-      <c r="K32" s="150"/>
-      <c r="L32" s="121"/>
-      <c r="M32" s="121"/>
-      <c r="N32" s="121"/>
-      <c r="O32" s="121"/>
-      <c r="P32" s="122"/>
-      <c r="Q32" s="123"/>
-      <c r="R32" s="124"/>
-      <c r="S32" s="124"/>
-      <c r="T32" s="124"/>
-      <c r="U32" s="124"/>
-      <c r="V32" s="124"/>
-      <c r="W32" s="124"/>
-      <c r="X32" s="124"/>
-      <c r="Y32" s="124"/>
-      <c r="Z32" s="124"/>
-      <c r="AA32" s="124"/>
-      <c r="AB32" s="124"/>
-      <c r="AC32" s="124"/>
-      <c r="AD32" s="124"/>
-      <c r="AE32" s="125"/>
-      <c r="AF32" s="120"/>
-      <c r="AG32" s="121"/>
-      <c r="AH32" s="121"/>
-      <c r="AI32" s="122"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="79"/>
+      <c r="D32" s="80"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="85"/>
+      <c r="M32" s="85"/>
+      <c r="N32" s="85"/>
+      <c r="O32" s="85"/>
+      <c r="P32" s="86"/>
+      <c r="Q32" s="87"/>
+      <c r="R32" s="88"/>
+      <c r="S32" s="88"/>
+      <c r="T32" s="88"/>
+      <c r="U32" s="88"/>
+      <c r="V32" s="88"/>
+      <c r="W32" s="88"/>
+      <c r="X32" s="88"/>
+      <c r="Y32" s="88"/>
+      <c r="Z32" s="88"/>
+      <c r="AA32" s="88"/>
+      <c r="AB32" s="88"/>
+      <c r="AC32" s="88"/>
+      <c r="AD32" s="88"/>
+      <c r="AE32" s="89"/>
+      <c r="AF32" s="84"/>
+      <c r="AG32" s="85"/>
+      <c r="AH32" s="85"/>
+      <c r="AI32" s="86"/>
     </row>
     <row r="33" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="29"/>
-      <c r="B33" s="114"/>
-      <c r="C33" s="115"/>
-      <c r="D33" s="116"/>
-      <c r="E33" s="117"/>
-      <c r="F33" s="118"/>
-      <c r="G33" s="114"/>
-      <c r="H33" s="119"/>
-      <c r="I33" s="115"/>
-      <c r="J33" s="120"/>
-      <c r="K33" s="121"/>
-      <c r="L33" s="121"/>
-      <c r="M33" s="121"/>
-      <c r="N33" s="121"/>
-      <c r="O33" s="121"/>
-      <c r="P33" s="122"/>
-      <c r="Q33" s="123"/>
-      <c r="R33" s="124"/>
-      <c r="S33" s="124"/>
-      <c r="T33" s="124"/>
-      <c r="U33" s="124"/>
-      <c r="V33" s="124"/>
-      <c r="W33" s="124"/>
-      <c r="X33" s="124"/>
-      <c r="Y33" s="124"/>
-      <c r="Z33" s="124"/>
-      <c r="AA33" s="124"/>
-      <c r="AB33" s="124"/>
-      <c r="AC33" s="124"/>
-      <c r="AD33" s="124"/>
-      <c r="AE33" s="125"/>
-      <c r="AF33" s="120"/>
-      <c r="AG33" s="121"/>
-      <c r="AH33" s="121"/>
-      <c r="AI33" s="122"/>
+      <c r="B33" s="78"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="78"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="84"/>
+      <c r="K33" s="85"/>
+      <c r="L33" s="85"/>
+      <c r="M33" s="85"/>
+      <c r="N33" s="85"/>
+      <c r="O33" s="85"/>
+      <c r="P33" s="86"/>
+      <c r="Q33" s="87"/>
+      <c r="R33" s="88"/>
+      <c r="S33" s="88"/>
+      <c r="T33" s="88"/>
+      <c r="U33" s="88"/>
+      <c r="V33" s="88"/>
+      <c r="W33" s="88"/>
+      <c r="X33" s="88"/>
+      <c r="Y33" s="88"/>
+      <c r="Z33" s="88"/>
+      <c r="AA33" s="88"/>
+      <c r="AB33" s="88"/>
+      <c r="AC33" s="88"/>
+      <c r="AD33" s="88"/>
+      <c r="AE33" s="89"/>
+      <c r="AF33" s="84"/>
+      <c r="AG33" s="85"/>
+      <c r="AH33" s="85"/>
+      <c r="AI33" s="86"/>
     </row>
     <row r="34" spans="1:35" ht="14.25" x14ac:dyDescent="0.15">
       <c r="K34" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="179">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -9064,6 +8908,162 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1"/>
@@ -9215,163 +9215,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="121" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87" t="str">
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="93" t="s">
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="130" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="95"/>
-      <c r="S1" s="102" t="str">
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="139" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarchを使用したシステム開発における標準WBS</v>
       </c>
-      <c r="T1" s="103"/>
-      <c r="U1" s="103"/>
-      <c r="V1" s="103"/>
-      <c r="W1" s="103"/>
-      <c r="X1" s="103"/>
-      <c r="Y1" s="103"/>
-      <c r="Z1" s="104"/>
-      <c r="AA1" s="154" t="s">
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
+      <c r="Y1" s="140"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="151" t="s">
         <v>280</v>
       </c>
-      <c r="AB1" s="155"/>
-      <c r="AC1" s="111" t="str">
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="112"/>
-      <c r="AE1" s="112"/>
-      <c r="AF1" s="113"/>
-      <c r="AG1" s="151">
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="150"/>
+      <c r="AG1" s="153">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="152"/>
-      <c r="AI1" s="153"/>
+      <c r="AH1" s="154"/>
+      <c r="AI1" s="155"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3"/>
     </row>
     <row r="2" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="121" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87" t="str">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="97"/>
-      <c r="Q2" s="97"/>
-      <c r="R2" s="98"/>
-      <c r="S2" s="105"/>
-      <c r="T2" s="106"/>
-      <c r="U2" s="106"/>
-      <c r="V2" s="106"/>
-      <c r="W2" s="106"/>
-      <c r="X2" s="106"/>
-      <c r="Y2" s="106"/>
-      <c r="Z2" s="107"/>
-      <c r="AA2" s="154" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="133"/>
+      <c r="P2" s="134"/>
+      <c r="Q2" s="134"/>
+      <c r="R2" s="135"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="143"/>
+      <c r="U2" s="143"/>
+      <c r="V2" s="143"/>
+      <c r="W2" s="143"/>
+      <c r="X2" s="143"/>
+      <c r="Y2" s="143"/>
+      <c r="Z2" s="144"/>
+      <c r="AA2" s="151" t="s">
         <v>282</v>
       </c>
-      <c r="AB2" s="155"/>
-      <c r="AC2" s="111" t="str">
+      <c r="AB2" s="152"/>
+      <c r="AC2" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="112"/>
-      <c r="AE2" s="112"/>
-      <c r="AF2" s="113"/>
-      <c r="AG2" s="151">
+      <c r="AD2" s="149"/>
+      <c r="AE2" s="149"/>
+      <c r="AF2" s="150"/>
+      <c r="AG2" s="153">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>45461</v>
-      </c>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="153"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="154"/>
+      <c r="AI2" s="155"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="121" t="s">
         <v>283</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87" t="str">
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="99"/>
-      <c r="P3" s="100"/>
-      <c r="Q3" s="100"/>
-      <c r="R3" s="101"/>
-      <c r="S3" s="108"/>
-      <c r="T3" s="109"/>
-      <c r="U3" s="109"/>
-      <c r="V3" s="109"/>
-      <c r="W3" s="109"/>
-      <c r="X3" s="109"/>
-      <c r="Y3" s="109"/>
-      <c r="Z3" s="110"/>
-      <c r="AA3" s="154"/>
-      <c r="AB3" s="155"/>
-      <c r="AC3" s="111" t="str">
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="137"/>
+      <c r="Q3" s="137"/>
+      <c r="R3" s="138"/>
+      <c r="S3" s="145"/>
+      <c r="T3" s="146"/>
+      <c r="U3" s="146"/>
+      <c r="V3" s="146"/>
+      <c r="W3" s="146"/>
+      <c r="X3" s="146"/>
+      <c r="Y3" s="146"/>
+      <c r="Z3" s="147"/>
+      <c r="AA3" s="151"/>
+      <c r="AB3" s="152"/>
+      <c r="AC3" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="112"/>
-      <c r="AE3" s="112"/>
-      <c r="AF3" s="113"/>
-      <c r="AG3" s="151" t="str">
+      <c r="AD3" s="149"/>
+      <c r="AE3" s="149"/>
+      <c r="AF3" s="150"/>
+      <c r="AG3" s="153" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="152"/>
-      <c r="AI3" s="153"/>
+      <c r="AH3" s="154"/>
+      <c r="AI3" s="155"/>
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
@@ -10691,6 +10691,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -10700,14 +10708,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1"/>
@@ -10730,59 +10730,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="121" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87" t="str">
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="157" t="s">
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="160" t="s">
         <v>294</v>
       </c>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
-      <c r="R1" s="159"/>
-      <c r="S1" s="102" t="str">
+      <c r="P1" s="161"/>
+      <c r="Q1" s="161"/>
+      <c r="R1" s="162"/>
+      <c r="S1" s="139" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarchを使用したシステム開発における標準WBS</v>
       </c>
-      <c r="T1" s="103"/>
-      <c r="U1" s="103"/>
-      <c r="V1" s="103"/>
-      <c r="W1" s="103"/>
-      <c r="X1" s="103"/>
-      <c r="Y1" s="103"/>
-      <c r="Z1" s="104"/>
-      <c r="AA1" s="84" t="s">
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
+      <c r="Y1" s="140"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="111" t="str">
+      <c r="AB1" s="123"/>
+      <c r="AC1" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="112"/>
-      <c r="AE1" s="112"/>
-      <c r="AF1" s="113"/>
-      <c r="AG1" s="151">
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="150"/>
+      <c r="AG1" s="153">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="152"/>
-      <c r="AI1" s="153"/>
+      <c r="AH1" s="154"/>
+      <c r="AI1" s="155"/>
       <c r="AJ1" s="30"/>
       <c r="AN1" s="51"/>
       <c r="AO1" s="30"/>
@@ -10796,54 +10796,54 @@
       <c r="AW1" s="30"/>
     </row>
     <row r="2" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="121" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87" t="str">
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="160"/>
-      <c r="P2" s="161"/>
-      <c r="Q2" s="161"/>
-      <c r="R2" s="162"/>
-      <c r="S2" s="105"/>
-      <c r="T2" s="106"/>
-      <c r="U2" s="106"/>
-      <c r="V2" s="106"/>
-      <c r="W2" s="106"/>
-      <c r="X2" s="106"/>
-      <c r="Y2" s="106"/>
-      <c r="Z2" s="107"/>
-      <c r="AA2" s="84" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="164"/>
+      <c r="Q2" s="164"/>
+      <c r="R2" s="165"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="143"/>
+      <c r="U2" s="143"/>
+      <c r="V2" s="143"/>
+      <c r="W2" s="143"/>
+      <c r="X2" s="143"/>
+      <c r="Y2" s="143"/>
+      <c r="Z2" s="144"/>
+      <c r="AA2" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="111" t="str">
+      <c r="AB2" s="123"/>
+      <c r="AC2" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="112"/>
-      <c r="AE2" s="112"/>
-      <c r="AF2" s="113"/>
-      <c r="AG2" s="151">
+      <c r="AD2" s="149"/>
+      <c r="AE2" s="149"/>
+      <c r="AF2" s="150"/>
+      <c r="AG2" s="153">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>45461</v>
-      </c>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="153"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="154"/>
+      <c r="AI2" s="155"/>
       <c r="AJ2" s="30"/>
       <c r="AN2" s="51"/>
       <c r="AO2" s="30"/>
@@ -10857,52 +10857,52 @@
       <c r="AW2" s="30"/>
     </row>
     <row r="3" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="121" t="s">
         <v>283</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87" t="str">
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="163"/>
-      <c r="P3" s="164"/>
-      <c r="Q3" s="164"/>
-      <c r="R3" s="165"/>
-      <c r="S3" s="108"/>
-      <c r="T3" s="109"/>
-      <c r="U3" s="109"/>
-      <c r="V3" s="109"/>
-      <c r="W3" s="109"/>
-      <c r="X3" s="109"/>
-      <c r="Y3" s="109"/>
-      <c r="Z3" s="110"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="111" t="str">
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="166"/>
+      <c r="P3" s="167"/>
+      <c r="Q3" s="167"/>
+      <c r="R3" s="168"/>
+      <c r="S3" s="145"/>
+      <c r="T3" s="146"/>
+      <c r="U3" s="146"/>
+      <c r="V3" s="146"/>
+      <c r="W3" s="146"/>
+      <c r="X3" s="146"/>
+      <c r="Y3" s="146"/>
+      <c r="Z3" s="147"/>
+      <c r="AA3" s="121"/>
+      <c r="AB3" s="123"/>
+      <c r="AC3" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="112"/>
-      <c r="AE3" s="112"/>
-      <c r="AF3" s="113"/>
-      <c r="AG3" s="151" t="str">
+      <c r="AD3" s="149"/>
+      <c r="AE3" s="149"/>
+      <c r="AF3" s="150"/>
+      <c r="AG3" s="153" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="152"/>
-      <c r="AI3" s="153"/>
+      <c r="AH3" s="154"/>
+      <c r="AI3" s="155"/>
       <c r="AJ3" s="53"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
@@ -11144,34 +11144,34 @@
       <c r="D57" s="55" t="s">
         <v>305</v>
       </c>
-      <c r="E57" s="166" t="s">
+      <c r="E57" s="157" t="s">
         <v>107</v>
       </c>
-      <c r="F57" s="167"/>
-      <c r="G57" s="167"/>
-      <c r="H57" s="167"/>
-      <c r="I57" s="167"/>
-      <c r="J57" s="168"/>
-      <c r="K57" s="166" t="s">
+      <c r="F57" s="158"/>
+      <c r="G57" s="158"/>
+      <c r="H57" s="158"/>
+      <c r="I57" s="158"/>
+      <c r="J57" s="159"/>
+      <c r="K57" s="157" t="s">
         <v>178</v>
       </c>
-      <c r="L57" s="167"/>
-      <c r="M57" s="167"/>
-      <c r="N57" s="167"/>
-      <c r="O57" s="167"/>
-      <c r="P57" s="167"/>
-      <c r="Q57" s="167"/>
-      <c r="R57" s="167"/>
-      <c r="S57" s="167"/>
-      <c r="T57" s="167"/>
-      <c r="U57" s="167"/>
-      <c r="V57" s="167"/>
-      <c r="W57" s="167"/>
-      <c r="X57" s="167"/>
-      <c r="Y57" s="167"/>
-      <c r="Z57" s="167"/>
-      <c r="AA57" s="167"/>
-      <c r="AB57" s="168"/>
+      <c r="L57" s="158"/>
+      <c r="M57" s="158"/>
+      <c r="N57" s="158"/>
+      <c r="O57" s="158"/>
+      <c r="P57" s="158"/>
+      <c r="Q57" s="158"/>
+      <c r="R57" s="158"/>
+      <c r="S57" s="158"/>
+      <c r="T57" s="158"/>
+      <c r="U57" s="158"/>
+      <c r="V57" s="158"/>
+      <c r="W57" s="158"/>
+      <c r="X57" s="158"/>
+      <c r="Y57" s="158"/>
+      <c r="Z57" s="158"/>
+      <c r="AA57" s="158"/>
+      <c r="AB57" s="159"/>
     </row>
     <row r="58" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="34"/>
@@ -12184,27 +12184,6 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="E66:J66"/>
-    <mergeCell ref="K66:AB66"/>
-    <mergeCell ref="E63:J63"/>
-    <mergeCell ref="K63:AB63"/>
-    <mergeCell ref="E64:J64"/>
-    <mergeCell ref="K64:AB64"/>
-    <mergeCell ref="E65:J65"/>
-    <mergeCell ref="K65:AB65"/>
-    <mergeCell ref="E60:J60"/>
-    <mergeCell ref="K60:AB60"/>
-    <mergeCell ref="E61:J61"/>
-    <mergeCell ref="K61:AB61"/>
-    <mergeCell ref="E62:J62"/>
-    <mergeCell ref="K62:AB62"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="E57:J57"/>
-    <mergeCell ref="K57:AB57"/>
-    <mergeCell ref="E58:J58"/>
-    <mergeCell ref="K58:AB58"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
     <mergeCell ref="E59:J59"/>
     <mergeCell ref="K59:AB59"/>
     <mergeCell ref="AG1:AI1"/>
@@ -12221,6 +12200,27 @@
     <mergeCell ref="AC1:AF1"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="E57:J57"/>
+    <mergeCell ref="K57:AB57"/>
+    <mergeCell ref="E58:J58"/>
+    <mergeCell ref="K58:AB58"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="E60:J60"/>
+    <mergeCell ref="K60:AB60"/>
+    <mergeCell ref="E61:J61"/>
+    <mergeCell ref="K61:AB61"/>
+    <mergeCell ref="E62:J62"/>
+    <mergeCell ref="K62:AB62"/>
+    <mergeCell ref="E66:J66"/>
+    <mergeCell ref="K66:AB66"/>
+    <mergeCell ref="E63:J63"/>
+    <mergeCell ref="K63:AB63"/>
+    <mergeCell ref="E64:J64"/>
+    <mergeCell ref="K64:AB64"/>
+    <mergeCell ref="E65:J65"/>
+    <mergeCell ref="K65:AB65"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>

--- a/010_開発プロセス標準/Nablarchを使用したシステム開発における標準WBS.xlsx
+++ b/010_開発プロセス標準/Nablarchを使用したシステム開発における標準WBS.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650A631E-9E7D-4FB2-97FF-4C102CFCFAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF795742-DDE3-4A13-B9E7-631570388A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="1530" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="14" r:id="rId1"/>
@@ -16,11 +16,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2. WBS'!$A$2:$E$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'1. 概要'!$A$1:$AI$70</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'1. 概要'!$A$1:$AI$94</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'2. WBS'!$A$1:$K$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">目次!$A$1:$AI$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">目次!$A$1:$AI$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'1. 概要'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'2. WBS'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="409">
   <si>
     <t xml:space="preserve">データベース論理設計
 </t>
@@ -2971,52 +2971,6 @@
 標</t>
     <rPh sb="2" eb="3">
       <t>シルベ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">画面イメージはHTMLで作成すること。PG・UTI工程において、JSP自動生成ツールを使用することで、HTML→JSP変換の作業負荷を軽減できる。
-JSP自動生成ツールの詳細は、Nablarch Toolboxの下記ドキュメントを参照。
-・JSP自動生成ツール
-</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>コウテイ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ヘンカン</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>サギョウ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>フカ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>ケイゲン</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="106" eb="108">
-      <t>カキ</t>
-    </rPh>
-    <rPh sb="115" eb="117">
-      <t>サンショウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -3623,26 +3577,6 @@
       <t>タンタイ</t>
     </rPh>
     <rPh sb="93" eb="95">
-      <t>ヒョウジュン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">プログラミング・単体テストガイド
-マスタデータ投入ツール
-JSP自動生成ツール
-SQL自動生成ツール
-HTMLチェックツール
-JSP静的解析ツール
-Java静的解析ツール
-使用不許可APIチェックツール
-リクエスト単体データ作成ツール
-単体テスト標準
-</t>
-    <rPh sb="118" eb="120">
-      <t>タンタイ</t>
-    </rPh>
-    <rPh sb="123" eb="125">
       <t>ヒョウジュン</t>
     </rPh>
     <phoneticPr fontId="3"/>
@@ -4691,7 +4625,187 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>第１．２版</t>
+    <t>JSF</t>
+  </si>
+  <si>
+    <t>JASPIC</t>
+  </si>
+  <si>
+    <t>JACC</t>
+  </si>
+  <si>
+    <t>JMS</t>
+  </si>
+  <si>
+    <t>JPA</t>
+  </si>
+  <si>
+    <t>JTA</t>
+  </si>
+  <si>
+    <t>JCA</t>
+  </si>
+  <si>
+    <t>JAF</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t>EJB</t>
+  </si>
+  <si>
+    <t>JAXB</t>
+  </si>
+  <si>
+    <t>JSON-B</t>
+  </si>
+  <si>
+    <t>JSON-P</t>
+  </si>
+  <si>
+    <t>JSP</t>
+  </si>
+  <si>
+    <t>JAX-WS</t>
+  </si>
+  <si>
+    <t>JAX-RS</t>
+  </si>
+  <si>
+    <t>JSTL</t>
+  </si>
+  <si>
+    <t>CDI</t>
+  </si>
+  <si>
+    <t>Jakarta EE仕様</t>
+    <rPh sb="10" eb="12">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Jakarta Faces</t>
+  </si>
+  <si>
+    <t>Jakarta Authentication</t>
+  </si>
+  <si>
+    <t>Jakarta Authorization</t>
+  </si>
+  <si>
+    <t>Jakarta Messaging</t>
+  </si>
+  <si>
+    <t>Jakarta Persistence</t>
+  </si>
+  <si>
+    <t>Jakarta Transactions</t>
+  </si>
+  <si>
+    <t>Jakarta Batch</t>
+  </si>
+  <si>
+    <t>Jakarta Connectors</t>
+  </si>
+  <si>
+    <t>Jakarta Activation</t>
+  </si>
+  <si>
+    <t>Jakarta Expression Language</t>
+  </si>
+  <si>
+    <t>Jakarta Enterprise Beans</t>
+  </si>
+  <si>
+    <t>Jakarta XML Binding</t>
+  </si>
+  <si>
+    <t>Jakarta JSON Binding</t>
+  </si>
+  <si>
+    <t>Jakarta JSON Processing</t>
+  </si>
+  <si>
+    <t>Jakarta Server Pages</t>
+  </si>
+  <si>
+    <t>Jakarta XML Web Services</t>
+  </si>
+  <si>
+    <t>Jakarta RESTful Web Services</t>
+  </si>
+  <si>
+    <t>Jakarta Standard Tag Library</t>
+  </si>
+  <si>
+    <t>Jakarta Contexts and Dependency Injection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プログラミング・単体テストガイド
+マスタデータ投入ツール
+SQL自動生成ツール
+HTMLチェックツール
+JSP静的解析ツール
+Java静的解析ツール
+使用不許可APIチェックツール
+リクエスト単体データ作成ツール
+単体テスト標準
+</t>
+    <rPh sb="107" eb="109">
+      <t>タンタイ</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>ヒョウジュン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>表記</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>1.4. 本書におけるJakartaEE仕様への読み替えについて</t>
+    <rPh sb="5" eb="7">
+      <t>ホンショ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>特に断りがない限り、以下の表記はJakarta EEの仕様を指すものとする。</t>
+    <rPh sb="10" eb="12">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>1.4. 本書におけるJakartaEE仕様への読み替えについて</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>第１．３版</t>
     <rPh sb="0" eb="1">
       <t>ダイ</t>
     </rPh>
@@ -4699,6 +4813,60 @@
       <t>ハン</t>
     </rPh>
     <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>1.3版</t>
+    <rPh sb="3" eb="4">
+      <t>ハン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「1. 概要」シート</t>
+    <rPh sb="4" eb="6">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「1.4. 本書におけるJakartaEE仕様への読み替えについて」を追加。</t>
+    <rPh sb="35" eb="37">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>追加</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「2. WBS」シート
+　・K17
+　・G28</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「JSP自動生成ツール」が提供されなくなったため、記載を削除。</t>
+    <rPh sb="4" eb="8">
+      <t>ジドウセイセイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>jBatch / JSR352</t>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -4906,7 +5074,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -5111,6 +5279,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -5134,7 +5315,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5297,6 +5478,25 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="31" fontId="9" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5338,6 +5538,36 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -6455,9 +6685,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6495,9 +6725,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6530,26 +6760,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6582,26 +6795,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6819,7 +7015,7 @@
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
       <c r="J23" s="1" t="s">
-        <v>360</v>
+        <v>401</v>
       </c>
     </row>
     <row r="24" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6831,12 +7027,12 @@
       <c r="F25" s="17"/>
       <c r="G25" s="17"/>
       <c r="H25" s="17"/>
-      <c r="I25" s="64">
+      <c r="I25" s="77">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
-        <v>44455</v>
-      </c>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
+        <v>45565</v>
+      </c>
+      <c r="J25" s="77"/>
+      <c r="K25" s="77"/>
     </row>
     <row r="26" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F26" s="17"/>
@@ -7430,55 +7626,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="98" t="s">
-        <v>281</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="107" t="s">
+      <c r="A1" s="121" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="130" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="116" t="s">
-        <v>293</v>
-      </c>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="118"/>
-      <c r="AA1" s="98" t="s">
-        <v>282</v>
-      </c>
-      <c r="AB1" s="100"/>
-      <c r="AC1" s="125" t="str">
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="139" t="s">
+        <v>291</v>
+      </c>
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
+      <c r="Y1" s="140"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="121" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB1" s="123"/>
+      <c r="AC1" s="148" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="126"/>
-      <c r="AE1" s="126"/>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="92">
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="150"/>
+      <c r="AG1" s="115">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="93"/>
-      <c r="AI1" s="94"/>
+      <c r="AH1" s="116"/>
+      <c r="AI1" s="117"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="2"/>
@@ -7486,51 +7682,51 @@
       <c r="AN1" s="3"/>
     </row>
     <row r="2" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="98" t="s">
-        <v>283</v>
-      </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="110"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="120"/>
-      <c r="Y2" s="120"/>
-      <c r="Z2" s="121"/>
-      <c r="AA2" s="98" t="s">
-        <v>284</v>
-      </c>
-      <c r="AB2" s="100"/>
-      <c r="AC2" s="104" t="str">
+      <c r="A2" s="121" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="133"/>
+      <c r="P2" s="134"/>
+      <c r="Q2" s="134"/>
+      <c r="R2" s="135"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="143"/>
+      <c r="U2" s="143"/>
+      <c r="V2" s="143"/>
+      <c r="W2" s="143"/>
+      <c r="X2" s="143"/>
+      <c r="Y2" s="143"/>
+      <c r="Z2" s="144"/>
+      <c r="AA2" s="121" t="s">
+        <v>282</v>
+      </c>
+      <c r="AB2" s="123"/>
+      <c r="AC2" s="127" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="105"/>
-      <c r="AE2" s="105"/>
-      <c r="AF2" s="106"/>
-      <c r="AG2" s="92">
+      <c r="AD2" s="128"/>
+      <c r="AE2" s="128"/>
+      <c r="AF2" s="129"/>
+      <c r="AG2" s="115">
         <f>IF(D9="","",MAX(D9:F33))</f>
-        <v>44455</v>
-      </c>
-      <c r="AH2" s="93"/>
-      <c r="AI2" s="94"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="116"/>
+      <c r="AI2" s="117"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
@@ -7538,43 +7734,43 @@
       <c r="AN2" s="2"/>
     </row>
     <row r="3" spans="1:40" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="98" t="s">
-        <v>285</v>
-      </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="113"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
-      <c r="R3" s="115"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="123"/>
-      <c r="U3" s="123"/>
-      <c r="V3" s="123"/>
-      <c r="W3" s="123"/>
-      <c r="X3" s="123"/>
-      <c r="Y3" s="123"/>
-      <c r="Z3" s="124"/>
-      <c r="AA3" s="98"/>
-      <c r="AB3" s="100"/>
-      <c r="AC3" s="125"/>
-      <c r="AD3" s="126"/>
-      <c r="AE3" s="126"/>
-      <c r="AF3" s="127"/>
-      <c r="AG3" s="92"/>
-      <c r="AH3" s="93"/>
-      <c r="AI3" s="94"/>
+      <c r="A3" s="121" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="137"/>
+      <c r="Q3" s="137"/>
+      <c r="R3" s="138"/>
+      <c r="S3" s="145"/>
+      <c r="T3" s="146"/>
+      <c r="U3" s="146"/>
+      <c r="V3" s="146"/>
+      <c r="W3" s="146"/>
+      <c r="X3" s="146"/>
+      <c r="Y3" s="146"/>
+      <c r="Z3" s="147"/>
+      <c r="AA3" s="121"/>
+      <c r="AB3" s="123"/>
+      <c r="AC3" s="148"/>
+      <c r="AD3" s="149"/>
+      <c r="AE3" s="149"/>
+      <c r="AF3" s="150"/>
+      <c r="AG3" s="115"/>
+      <c r="AH3" s="116"/>
+      <c r="AI3" s="117"/>
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
@@ -7609,1058 +7805,1080 @@
     </row>
     <row r="7" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="27" t="s">
-        <v>286</v>
-      </c>
-      <c r="B7" s="95" t="s">
+        <v>284</v>
+      </c>
+      <c r="B7" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="C7" s="96"/>
-      <c r="D7" s="95" t="s">
+      <c r="C7" s="119"/>
+      <c r="D7" s="118" t="s">
         <v>187</v>
       </c>
-      <c r="E7" s="97"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="95" t="s">
+      <c r="E7" s="120"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="H7" s="97"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="95" t="s">
-        <v>287</v>
-      </c>
-      <c r="K7" s="97"/>
-      <c r="L7" s="97"/>
-      <c r="M7" s="97"/>
-      <c r="N7" s="97"/>
-      <c r="O7" s="97"/>
-      <c r="P7" s="96"/>
-      <c r="Q7" s="95" t="s">
+      <c r="H7" s="120"/>
+      <c r="I7" s="119"/>
+      <c r="J7" s="118" t="s">
+        <v>285</v>
+      </c>
+      <c r="K7" s="120"/>
+      <c r="L7" s="120"/>
+      <c r="M7" s="120"/>
+      <c r="N7" s="120"/>
+      <c r="O7" s="120"/>
+      <c r="P7" s="119"/>
+      <c r="Q7" s="118" t="s">
         <v>189</v>
       </c>
-      <c r="R7" s="97"/>
-      <c r="S7" s="97"/>
-      <c r="T7" s="97"/>
-      <c r="U7" s="97"/>
-      <c r="V7" s="97"/>
-      <c r="W7" s="97"/>
-      <c r="X7" s="97"/>
-      <c r="Y7" s="97"/>
-      <c r="Z7" s="97"/>
-      <c r="AA7" s="97"/>
-      <c r="AB7" s="97"/>
-      <c r="AC7" s="97"/>
-      <c r="AD7" s="97"/>
-      <c r="AE7" s="96"/>
-      <c r="AF7" s="95" t="s">
+      <c r="R7" s="120"/>
+      <c r="S7" s="120"/>
+      <c r="T7" s="120"/>
+      <c r="U7" s="120"/>
+      <c r="V7" s="120"/>
+      <c r="W7" s="120"/>
+      <c r="X7" s="120"/>
+      <c r="Y7" s="120"/>
+      <c r="Z7" s="120"/>
+      <c r="AA7" s="120"/>
+      <c r="AB7" s="120"/>
+      <c r="AC7" s="120"/>
+      <c r="AD7" s="120"/>
+      <c r="AE7" s="119"/>
+      <c r="AF7" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AG7" s="97"/>
-      <c r="AH7" s="97"/>
-      <c r="AI7" s="96"/>
+      <c r="AG7" s="120"/>
+      <c r="AH7" s="120"/>
+      <c r="AI7" s="119"/>
     </row>
     <row r="8" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="101" t="s">
+        <v>286</v>
+      </c>
+      <c r="C8" s="102"/>
+      <c r="D8" s="103">
+        <v>43336</v>
+      </c>
+      <c r="E8" s="104"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="106" t="s">
+        <v>287</v>
+      </c>
+      <c r="H8" s="107"/>
+      <c r="I8" s="108"/>
+      <c r="J8" s="109" t="s">
         <v>288</v>
       </c>
-      <c r="C8" s="79"/>
-      <c r="D8" s="80">
-        <v>43336</v>
-      </c>
-      <c r="E8" s="81"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="83" t="s">
+      <c r="K8" s="110"/>
+      <c r="L8" s="110"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="110"/>
+      <c r="O8" s="110"/>
+      <c r="P8" s="111"/>
+      <c r="Q8" s="112" t="s">
         <v>289</v>
       </c>
-      <c r="H8" s="84"/>
-      <c r="I8" s="85"/>
-      <c r="J8" s="86" t="s">
+      <c r="R8" s="113"/>
+      <c r="S8" s="113"/>
+      <c r="T8" s="113"/>
+      <c r="U8" s="113"/>
+      <c r="V8" s="113"/>
+      <c r="W8" s="113"/>
+      <c r="X8" s="113"/>
+      <c r="Y8" s="113"/>
+      <c r="Z8" s="113"/>
+      <c r="AA8" s="113"/>
+      <c r="AB8" s="113"/>
+      <c r="AC8" s="113"/>
+      <c r="AD8" s="113"/>
+      <c r="AE8" s="114"/>
+      <c r="AF8" s="109" t="s">
         <v>290</v>
       </c>
-      <c r="K8" s="87"/>
-      <c r="L8" s="87"/>
-      <c r="M8" s="87"/>
-      <c r="N8" s="87"/>
-      <c r="O8" s="87"/>
-      <c r="P8" s="88"/>
-      <c r="Q8" s="89" t="s">
-        <v>291</v>
-      </c>
-      <c r="R8" s="90"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="90"/>
-      <c r="U8" s="90"/>
-      <c r="V8" s="90"/>
-      <c r="W8" s="90"/>
-      <c r="X8" s="90"/>
-      <c r="Y8" s="90"/>
-      <c r="Z8" s="90"/>
-      <c r="AA8" s="90"/>
-      <c r="AB8" s="90"/>
-      <c r="AC8" s="90"/>
-      <c r="AD8" s="90"/>
-      <c r="AE8" s="91"/>
-      <c r="AF8" s="86" t="s">
-        <v>292</v>
-      </c>
-      <c r="AG8" s="87"/>
-      <c r="AH8" s="87"/>
-      <c r="AI8" s="88"/>
+      <c r="AG8" s="110"/>
+      <c r="AH8" s="110"/>
+      <c r="AI8" s="111"/>
     </row>
     <row r="9" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="29">
         <v>2</v>
       </c>
-      <c r="B9" s="65" t="s">
-        <v>357</v>
-      </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="67">
+      <c r="B9" s="78" t="s">
+        <v>355</v>
+      </c>
+      <c r="C9" s="79"/>
+      <c r="D9" s="80">
         <v>43896</v>
       </c>
-      <c r="E9" s="68"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="67" t="s">
-        <v>339</v>
-      </c>
-      <c r="H9" s="70"/>
-      <c r="I9" s="66"/>
-      <c r="J9" s="71" t="s">
-        <v>340</v>
-      </c>
-      <c r="K9" s="72"/>
-      <c r="L9" s="72"/>
-      <c r="M9" s="72"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="72"/>
-      <c r="P9" s="73"/>
-      <c r="Q9" s="74" t="s">
-        <v>355</v>
-      </c>
-      <c r="R9" s="75"/>
-      <c r="S9" s="75"/>
-      <c r="T9" s="75"/>
-      <c r="U9" s="75"/>
-      <c r="V9" s="75"/>
-      <c r="W9" s="75"/>
-      <c r="X9" s="75"/>
-      <c r="Y9" s="75"/>
-      <c r="Z9" s="75"/>
-      <c r="AA9" s="75"/>
-      <c r="AB9" s="75"/>
-      <c r="AC9" s="75"/>
-      <c r="AD9" s="75"/>
-      <c r="AE9" s="76"/>
-      <c r="AF9" s="71" t="s">
-        <v>292</v>
-      </c>
-      <c r="AG9" s="72"/>
-      <c r="AH9" s="72"/>
-      <c r="AI9" s="73"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="80" t="s">
+        <v>337</v>
+      </c>
+      <c r="H9" s="83"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="84" t="s">
+        <v>338</v>
+      </c>
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="85"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="85"/>
+      <c r="P9" s="86"/>
+      <c r="Q9" s="87" t="s">
+        <v>353</v>
+      </c>
+      <c r="R9" s="88"/>
+      <c r="S9" s="88"/>
+      <c r="T9" s="88"/>
+      <c r="U9" s="88"/>
+      <c r="V9" s="88"/>
+      <c r="W9" s="88"/>
+      <c r="X9" s="88"/>
+      <c r="Y9" s="88"/>
+      <c r="Z9" s="88"/>
+      <c r="AA9" s="88"/>
+      <c r="AB9" s="88"/>
+      <c r="AC9" s="88"/>
+      <c r="AD9" s="88"/>
+      <c r="AE9" s="89"/>
+      <c r="AF9" s="84" t="s">
+        <v>290</v>
+      </c>
+      <c r="AG9" s="85"/>
+      <c r="AH9" s="85"/>
+      <c r="AI9" s="86"/>
     </row>
     <row r="10" spans="1:40" s="9" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="29">
         <v>3</v>
       </c>
-      <c r="B10" s="65" t="s">
-        <v>358</v>
-      </c>
-      <c r="C10" s="66"/>
-      <c r="D10" s="67">
+      <c r="B10" s="78" t="s">
+        <v>356</v>
+      </c>
+      <c r="C10" s="79"/>
+      <c r="D10" s="80">
         <v>44455</v>
       </c>
-      <c r="E10" s="68"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="67" t="s">
-        <v>339</v>
-      </c>
-      <c r="H10" s="70"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="71" t="s">
-        <v>340</v>
-      </c>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="73"/>
-      <c r="Q10" s="74" t="s">
-        <v>359</v>
-      </c>
-      <c r="R10" s="75"/>
-      <c r="S10" s="75"/>
-      <c r="T10" s="75"/>
-      <c r="U10" s="75"/>
-      <c r="V10" s="75"/>
-      <c r="W10" s="75"/>
-      <c r="X10" s="75"/>
-      <c r="Y10" s="75"/>
-      <c r="Z10" s="75"/>
-      <c r="AA10" s="75"/>
-      <c r="AB10" s="75"/>
-      <c r="AC10" s="75"/>
-      <c r="AD10" s="75"/>
-      <c r="AE10" s="76"/>
-      <c r="AF10" s="71" t="s">
-        <v>292</v>
-      </c>
-      <c r="AG10" s="72"/>
-      <c r="AH10" s="72"/>
-      <c r="AI10" s="73"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="80" t="s">
+        <v>337</v>
+      </c>
+      <c r="H10" s="83"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="84" t="s">
+        <v>338</v>
+      </c>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="86"/>
+      <c r="Q10" s="87" t="s">
+        <v>357</v>
+      </c>
+      <c r="R10" s="88"/>
+      <c r="S10" s="88"/>
+      <c r="T10" s="88"/>
+      <c r="U10" s="88"/>
+      <c r="V10" s="88"/>
+      <c r="W10" s="88"/>
+      <c r="X10" s="88"/>
+      <c r="Y10" s="88"/>
+      <c r="Z10" s="88"/>
+      <c r="AA10" s="88"/>
+      <c r="AB10" s="88"/>
+      <c r="AC10" s="88"/>
+      <c r="AD10" s="88"/>
+      <c r="AE10" s="89"/>
+      <c r="AF10" s="84" t="s">
+        <v>290</v>
+      </c>
+      <c r="AG10" s="85"/>
+      <c r="AH10" s="85"/>
+      <c r="AI10" s="86"/>
     </row>
     <row r="11" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="29"/>
-      <c r="B11" s="65"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="73"/>
-      <c r="Q11" s="74"/>
-      <c r="R11" s="75"/>
-      <c r="S11" s="75"/>
-      <c r="T11" s="75"/>
-      <c r="U11" s="75"/>
-      <c r="V11" s="75"/>
-      <c r="W11" s="75"/>
-      <c r="X11" s="75"/>
-      <c r="Y11" s="75"/>
-      <c r="Z11" s="75"/>
-      <c r="AA11" s="75"/>
-      <c r="AB11" s="75"/>
-      <c r="AC11" s="75"/>
-      <c r="AD11" s="75"/>
-      <c r="AE11" s="76"/>
-      <c r="AF11" s="71"/>
-      <c r="AG11" s="72"/>
-      <c r="AH11" s="72"/>
-      <c r="AI11" s="73"/>
-    </row>
-    <row r="12" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="29"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="66"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="P12" s="73"/>
-      <c r="Q12" s="74"/>
-      <c r="R12" s="75"/>
-      <c r="S12" s="75"/>
-      <c r="T12" s="75"/>
-      <c r="U12" s="75"/>
-      <c r="V12" s="75"/>
-      <c r="W12" s="75"/>
-      <c r="X12" s="75"/>
-      <c r="Y12" s="75"/>
-      <c r="Z12" s="75"/>
-      <c r="AA12" s="75"/>
-      <c r="AB12" s="75"/>
-      <c r="AC12" s="75"/>
-      <c r="AD12" s="75"/>
-      <c r="AE12" s="76"/>
-      <c r="AF12" s="71"/>
-      <c r="AG12" s="72"/>
-      <c r="AH12" s="72"/>
-      <c r="AI12" s="73"/>
+      <c r="A11" s="76">
+        <v>4</v>
+      </c>
+      <c r="B11" s="96" t="s">
+        <v>402</v>
+      </c>
+      <c r="C11" s="97"/>
+      <c r="D11" s="98">
+        <v>45565</v>
+      </c>
+      <c r="E11" s="99"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="78" t="s">
+        <v>405</v>
+      </c>
+      <c r="H11" s="83"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="84" t="s">
+        <v>403</v>
+      </c>
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="85"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="85"/>
+      <c r="P11" s="86"/>
+      <c r="Q11" s="87" t="s">
+        <v>404</v>
+      </c>
+      <c r="R11" s="88"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="88"/>
+      <c r="U11" s="88"/>
+      <c r="V11" s="88"/>
+      <c r="W11" s="88"/>
+      <c r="X11" s="88"/>
+      <c r="Y11" s="88"/>
+      <c r="Z11" s="88"/>
+      <c r="AA11" s="88"/>
+      <c r="AB11" s="88"/>
+      <c r="AC11" s="88"/>
+      <c r="AD11" s="88"/>
+      <c r="AE11" s="89"/>
+      <c r="AF11" s="84" t="s">
+        <v>290</v>
+      </c>
+      <c r="AG11" s="85"/>
+      <c r="AH11" s="85"/>
+      <c r="AI11" s="86"/>
+    </row>
+    <row r="12" spans="1:40" s="9" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="28"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="78" t="s">
+        <v>337</v>
+      </c>
+      <c r="H12" s="83"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="87" t="s">
+        <v>406</v>
+      </c>
+      <c r="K12" s="85"/>
+      <c r="L12" s="85"/>
+      <c r="M12" s="85"/>
+      <c r="N12" s="85"/>
+      <c r="O12" s="85"/>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="87" t="s">
+        <v>407</v>
+      </c>
+      <c r="R12" s="88"/>
+      <c r="S12" s="88"/>
+      <c r="T12" s="88"/>
+      <c r="U12" s="88"/>
+      <c r="V12" s="88"/>
+      <c r="W12" s="88"/>
+      <c r="X12" s="88"/>
+      <c r="Y12" s="88"/>
+      <c r="Z12" s="88"/>
+      <c r="AA12" s="88"/>
+      <c r="AB12" s="88"/>
+      <c r="AC12" s="88"/>
+      <c r="AD12" s="88"/>
+      <c r="AE12" s="89"/>
+      <c r="AF12" s="84" t="s">
+        <v>290</v>
+      </c>
+      <c r="AG12" s="85"/>
+      <c r="AH12" s="85"/>
+      <c r="AI12" s="86"/>
     </row>
     <row r="13" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="29"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="72"/>
-      <c r="M13" s="72"/>
-      <c r="N13" s="72"/>
-      <c r="O13" s="72"/>
-      <c r="P13" s="73"/>
-      <c r="Q13" s="74"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="75"/>
-      <c r="U13" s="75"/>
-      <c r="V13" s="75"/>
-      <c r="W13" s="75"/>
-      <c r="X13" s="75"/>
-      <c r="Y13" s="75"/>
-      <c r="Z13" s="75"/>
-      <c r="AA13" s="75"/>
-      <c r="AB13" s="75"/>
-      <c r="AC13" s="75"/>
-      <c r="AD13" s="75"/>
-      <c r="AE13" s="76"/>
-      <c r="AF13" s="71"/>
-      <c r="AG13" s="72"/>
-      <c r="AH13" s="72"/>
-      <c r="AI13" s="73"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
+      <c r="M13" s="85"/>
+      <c r="N13" s="85"/>
+      <c r="O13" s="85"/>
+      <c r="P13" s="86"/>
+      <c r="Q13" s="87"/>
+      <c r="R13" s="88"/>
+      <c r="S13" s="88"/>
+      <c r="T13" s="88"/>
+      <c r="U13" s="88"/>
+      <c r="V13" s="88"/>
+      <c r="W13" s="88"/>
+      <c r="X13" s="88"/>
+      <c r="Y13" s="88"/>
+      <c r="Z13" s="88"/>
+      <c r="AA13" s="88"/>
+      <c r="AB13" s="88"/>
+      <c r="AC13" s="88"/>
+      <c r="AD13" s="88"/>
+      <c r="AE13" s="89"/>
+      <c r="AF13" s="84"/>
+      <c r="AG13" s="85"/>
+      <c r="AH13" s="85"/>
+      <c r="AI13" s="86"/>
     </row>
     <row r="14" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="29"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="72"/>
-      <c r="M14" s="72"/>
-      <c r="N14" s="72"/>
-      <c r="O14" s="72"/>
-      <c r="P14" s="73"/>
-      <c r="Q14" s="74"/>
-      <c r="R14" s="75"/>
-      <c r="S14" s="75"/>
-      <c r="T14" s="75"/>
-      <c r="U14" s="75"/>
-      <c r="V14" s="75"/>
-      <c r="W14" s="75"/>
-      <c r="X14" s="75"/>
-      <c r="Y14" s="75"/>
-      <c r="Z14" s="75"/>
-      <c r="AA14" s="75"/>
-      <c r="AB14" s="75"/>
-      <c r="AC14" s="75"/>
-      <c r="AD14" s="75"/>
-      <c r="AE14" s="76"/>
-      <c r="AF14" s="71"/>
-      <c r="AG14" s="72"/>
-      <c r="AH14" s="72"/>
-      <c r="AI14" s="73"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="85"/>
+      <c r="L14" s="85"/>
+      <c r="M14" s="85"/>
+      <c r="N14" s="85"/>
+      <c r="O14" s="85"/>
+      <c r="P14" s="86"/>
+      <c r="Q14" s="87"/>
+      <c r="R14" s="88"/>
+      <c r="S14" s="88"/>
+      <c r="T14" s="88"/>
+      <c r="U14" s="88"/>
+      <c r="V14" s="88"/>
+      <c r="W14" s="88"/>
+      <c r="X14" s="88"/>
+      <c r="Y14" s="88"/>
+      <c r="Z14" s="88"/>
+      <c r="AA14" s="88"/>
+      <c r="AB14" s="88"/>
+      <c r="AC14" s="88"/>
+      <c r="AD14" s="88"/>
+      <c r="AE14" s="89"/>
+      <c r="AF14" s="84"/>
+      <c r="AG14" s="85"/>
+      <c r="AH14" s="85"/>
+      <c r="AI14" s="86"/>
     </row>
     <row r="15" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="29"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="72"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="72"/>
-      <c r="P15" s="73"/>
-      <c r="Q15" s="74"/>
-      <c r="R15" s="75"/>
-      <c r="S15" s="75"/>
-      <c r="T15" s="75"/>
-      <c r="U15" s="75"/>
-      <c r="V15" s="75"/>
-      <c r="W15" s="75"/>
-      <c r="X15" s="75"/>
-      <c r="Y15" s="75"/>
-      <c r="Z15" s="75"/>
-      <c r="AA15" s="75"/>
-      <c r="AB15" s="75"/>
-      <c r="AC15" s="75"/>
-      <c r="AD15" s="75"/>
-      <c r="AE15" s="76"/>
-      <c r="AF15" s="71"/>
-      <c r="AG15" s="72"/>
-      <c r="AH15" s="72"/>
-      <c r="AI15" s="73"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="85"/>
+      <c r="M15" s="85"/>
+      <c r="N15" s="85"/>
+      <c r="O15" s="85"/>
+      <c r="P15" s="86"/>
+      <c r="Q15" s="87"/>
+      <c r="R15" s="88"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="88"/>
+      <c r="U15" s="88"/>
+      <c r="V15" s="88"/>
+      <c r="W15" s="88"/>
+      <c r="X15" s="88"/>
+      <c r="Y15" s="88"/>
+      <c r="Z15" s="88"/>
+      <c r="AA15" s="88"/>
+      <c r="AB15" s="88"/>
+      <c r="AC15" s="88"/>
+      <c r="AD15" s="88"/>
+      <c r="AE15" s="89"/>
+      <c r="AF15" s="84"/>
+      <c r="AG15" s="85"/>
+      <c r="AH15" s="85"/>
+      <c r="AI15" s="86"/>
     </row>
     <row r="16" spans="1:40" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="29"/>
-      <c r="B16" s="65"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="72"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="72"/>
-      <c r="N16" s="72"/>
-      <c r="O16" s="72"/>
-      <c r="P16" s="73"/>
-      <c r="Q16" s="74"/>
-      <c r="R16" s="75"/>
-      <c r="S16" s="75"/>
-      <c r="T16" s="75"/>
-      <c r="U16" s="75"/>
-      <c r="V16" s="75"/>
-      <c r="W16" s="75"/>
-      <c r="X16" s="75"/>
-      <c r="Y16" s="75"/>
-      <c r="Z16" s="75"/>
-      <c r="AA16" s="75"/>
-      <c r="AB16" s="75"/>
-      <c r="AC16" s="75"/>
-      <c r="AD16" s="75"/>
-      <c r="AE16" s="76"/>
-      <c r="AF16" s="71"/>
-      <c r="AG16" s="72"/>
-      <c r="AH16" s="72"/>
-      <c r="AI16" s="73"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="85"/>
+      <c r="L16" s="85"/>
+      <c r="M16" s="85"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="85"/>
+      <c r="P16" s="86"/>
+      <c r="Q16" s="87"/>
+      <c r="R16" s="88"/>
+      <c r="S16" s="88"/>
+      <c r="T16" s="88"/>
+      <c r="U16" s="88"/>
+      <c r="V16" s="88"/>
+      <c r="W16" s="88"/>
+      <c r="X16" s="88"/>
+      <c r="Y16" s="88"/>
+      <c r="Z16" s="88"/>
+      <c r="AA16" s="88"/>
+      <c r="AB16" s="88"/>
+      <c r="AC16" s="88"/>
+      <c r="AD16" s="88"/>
+      <c r="AE16" s="89"/>
+      <c r="AF16" s="84"/>
+      <c r="AG16" s="85"/>
+      <c r="AH16" s="85"/>
+      <c r="AI16" s="86"/>
     </row>
     <row r="17" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="29"/>
-      <c r="B17" s="65"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="72"/>
-      <c r="L17" s="72"/>
-      <c r="M17" s="72"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="72"/>
-      <c r="P17" s="73"/>
-      <c r="Q17" s="74"/>
-      <c r="R17" s="75"/>
-      <c r="S17" s="75"/>
-      <c r="T17" s="75"/>
-      <c r="U17" s="75"/>
-      <c r="V17" s="75"/>
-      <c r="W17" s="75"/>
-      <c r="X17" s="75"/>
-      <c r="Y17" s="75"/>
-      <c r="Z17" s="75"/>
-      <c r="AA17" s="75"/>
-      <c r="AB17" s="75"/>
-      <c r="AC17" s="75"/>
-      <c r="AD17" s="75"/>
-      <c r="AE17" s="76"/>
-      <c r="AF17" s="71"/>
-      <c r="AG17" s="72"/>
-      <c r="AH17" s="72"/>
-      <c r="AI17" s="73"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="85"/>
+      <c r="L17" s="85"/>
+      <c r="M17" s="85"/>
+      <c r="N17" s="85"/>
+      <c r="O17" s="85"/>
+      <c r="P17" s="86"/>
+      <c r="Q17" s="87"/>
+      <c r="R17" s="88"/>
+      <c r="S17" s="88"/>
+      <c r="T17" s="88"/>
+      <c r="U17" s="88"/>
+      <c r="V17" s="88"/>
+      <c r="W17" s="88"/>
+      <c r="X17" s="88"/>
+      <c r="Y17" s="88"/>
+      <c r="Z17" s="88"/>
+      <c r="AA17" s="88"/>
+      <c r="AB17" s="88"/>
+      <c r="AC17" s="88"/>
+      <c r="AD17" s="88"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="84"/>
+      <c r="AG17" s="85"/>
+      <c r="AH17" s="85"/>
+      <c r="AI17" s="86"/>
     </row>
     <row r="18" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="29"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="72"/>
-      <c r="L18" s="72"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="72"/>
-      <c r="O18" s="72"/>
-      <c r="P18" s="73"/>
-      <c r="Q18" s="74"/>
-      <c r="R18" s="75"/>
-      <c r="S18" s="75"/>
-      <c r="T18" s="75"/>
-      <c r="U18" s="75"/>
-      <c r="V18" s="75"/>
-      <c r="W18" s="75"/>
-      <c r="X18" s="75"/>
-      <c r="Y18" s="75"/>
-      <c r="Z18" s="75"/>
-      <c r="AA18" s="75"/>
-      <c r="AB18" s="75"/>
-      <c r="AC18" s="75"/>
-      <c r="AD18" s="75"/>
-      <c r="AE18" s="76"/>
-      <c r="AF18" s="71"/>
-      <c r="AG18" s="72"/>
-      <c r="AH18" s="72"/>
-      <c r="AI18" s="73"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="85"/>
+      <c r="M18" s="85"/>
+      <c r="N18" s="85"/>
+      <c r="O18" s="85"/>
+      <c r="P18" s="86"/>
+      <c r="Q18" s="87"/>
+      <c r="R18" s="88"/>
+      <c r="S18" s="88"/>
+      <c r="T18" s="88"/>
+      <c r="U18" s="88"/>
+      <c r="V18" s="88"/>
+      <c r="W18" s="88"/>
+      <c r="X18" s="88"/>
+      <c r="Y18" s="88"/>
+      <c r="Z18" s="88"/>
+      <c r="AA18" s="88"/>
+      <c r="AB18" s="88"/>
+      <c r="AC18" s="88"/>
+      <c r="AD18" s="88"/>
+      <c r="AE18" s="89"/>
+      <c r="AF18" s="84"/>
+      <c r="AG18" s="85"/>
+      <c r="AH18" s="85"/>
+      <c r="AI18" s="86"/>
     </row>
     <row r="19" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="29"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="72"/>
-      <c r="L19" s="72"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="72"/>
-      <c r="O19" s="72"/>
-      <c r="P19" s="73"/>
-      <c r="Q19" s="74"/>
-      <c r="R19" s="75"/>
-      <c r="S19" s="75"/>
-      <c r="T19" s="75"/>
-      <c r="U19" s="75"/>
-      <c r="V19" s="75"/>
-      <c r="W19" s="75"/>
-      <c r="X19" s="75"/>
-      <c r="Y19" s="75"/>
-      <c r="Z19" s="75"/>
-      <c r="AA19" s="75"/>
-      <c r="AB19" s="75"/>
-      <c r="AC19" s="75"/>
-      <c r="AD19" s="75"/>
-      <c r="AE19" s="76"/>
-      <c r="AF19" s="71"/>
-      <c r="AG19" s="72"/>
-      <c r="AH19" s="72"/>
-      <c r="AI19" s="73"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="85"/>
+      <c r="L19" s="85"/>
+      <c r="M19" s="85"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="85"/>
+      <c r="P19" s="86"/>
+      <c r="Q19" s="87"/>
+      <c r="R19" s="88"/>
+      <c r="S19" s="88"/>
+      <c r="T19" s="88"/>
+      <c r="U19" s="88"/>
+      <c r="V19" s="88"/>
+      <c r="W19" s="88"/>
+      <c r="X19" s="88"/>
+      <c r="Y19" s="88"/>
+      <c r="Z19" s="88"/>
+      <c r="AA19" s="88"/>
+      <c r="AB19" s="88"/>
+      <c r="AC19" s="88"/>
+      <c r="AD19" s="88"/>
+      <c r="AE19" s="89"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="85"/>
+      <c r="AH19" s="85"/>
+      <c r="AI19" s="86"/>
     </row>
     <row r="20" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="29"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="66"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="72"/>
-      <c r="L20" s="72"/>
-      <c r="M20" s="72"/>
-      <c r="N20" s="72"/>
-      <c r="O20" s="72"/>
-      <c r="P20" s="73"/>
-      <c r="Q20" s="74"/>
-      <c r="R20" s="75"/>
-      <c r="S20" s="75"/>
-      <c r="T20" s="75"/>
-      <c r="U20" s="75"/>
-      <c r="V20" s="75"/>
-      <c r="W20" s="75"/>
-      <c r="X20" s="75"/>
-      <c r="Y20" s="75"/>
-      <c r="Z20" s="75"/>
-      <c r="AA20" s="75"/>
-      <c r="AB20" s="75"/>
-      <c r="AC20" s="75"/>
-      <c r="AD20" s="75"/>
-      <c r="AE20" s="76"/>
-      <c r="AF20" s="71"/>
-      <c r="AG20" s="72"/>
-      <c r="AH20" s="72"/>
-      <c r="AI20" s="73"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="84"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="85"/>
+      <c r="M20" s="85"/>
+      <c r="N20" s="85"/>
+      <c r="O20" s="85"/>
+      <c r="P20" s="86"/>
+      <c r="Q20" s="87"/>
+      <c r="R20" s="88"/>
+      <c r="S20" s="88"/>
+      <c r="T20" s="88"/>
+      <c r="U20" s="88"/>
+      <c r="V20" s="88"/>
+      <c r="W20" s="88"/>
+      <c r="X20" s="88"/>
+      <c r="Y20" s="88"/>
+      <c r="Z20" s="88"/>
+      <c r="AA20" s="88"/>
+      <c r="AB20" s="88"/>
+      <c r="AC20" s="88"/>
+      <c r="AD20" s="88"/>
+      <c r="AE20" s="89"/>
+      <c r="AF20" s="84"/>
+      <c r="AG20" s="85"/>
+      <c r="AH20" s="85"/>
+      <c r="AI20" s="86"/>
     </row>
     <row r="21" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="29"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="72"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="72"/>
-      <c r="P21" s="73"/>
-      <c r="Q21" s="74"/>
-      <c r="R21" s="75"/>
-      <c r="S21" s="75"/>
-      <c r="T21" s="75"/>
-      <c r="U21" s="75"/>
-      <c r="V21" s="75"/>
-      <c r="W21" s="75"/>
-      <c r="X21" s="75"/>
-      <c r="Y21" s="75"/>
-      <c r="Z21" s="75"/>
-      <c r="AA21" s="75"/>
-      <c r="AB21" s="75"/>
-      <c r="AC21" s="75"/>
-      <c r="AD21" s="75"/>
-      <c r="AE21" s="76"/>
-      <c r="AF21" s="71"/>
-      <c r="AG21" s="72"/>
-      <c r="AH21" s="72"/>
-      <c r="AI21" s="73"/>
+      <c r="B21" s="78"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="85"/>
+      <c r="L21" s="85"/>
+      <c r="M21" s="85"/>
+      <c r="N21" s="85"/>
+      <c r="O21" s="85"/>
+      <c r="P21" s="86"/>
+      <c r="Q21" s="87"/>
+      <c r="R21" s="88"/>
+      <c r="S21" s="88"/>
+      <c r="T21" s="88"/>
+      <c r="U21" s="88"/>
+      <c r="V21" s="88"/>
+      <c r="W21" s="88"/>
+      <c r="X21" s="88"/>
+      <c r="Y21" s="88"/>
+      <c r="Z21" s="88"/>
+      <c r="AA21" s="88"/>
+      <c r="AB21" s="88"/>
+      <c r="AC21" s="88"/>
+      <c r="AD21" s="88"/>
+      <c r="AE21" s="89"/>
+      <c r="AF21" s="84"/>
+      <c r="AG21" s="85"/>
+      <c r="AH21" s="85"/>
+      <c r="AI21" s="86"/>
     </row>
     <row r="22" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="29"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="72"/>
-      <c r="P22" s="73"/>
-      <c r="Q22" s="74"/>
-      <c r="R22" s="75"/>
-      <c r="S22" s="75"/>
-      <c r="T22" s="75"/>
-      <c r="U22" s="75"/>
-      <c r="V22" s="75"/>
-      <c r="W22" s="75"/>
-      <c r="X22" s="75"/>
-      <c r="Y22" s="75"/>
-      <c r="Z22" s="75"/>
-      <c r="AA22" s="75"/>
-      <c r="AB22" s="75"/>
-      <c r="AC22" s="75"/>
-      <c r="AD22" s="75"/>
-      <c r="AE22" s="76"/>
-      <c r="AF22" s="71"/>
-      <c r="AG22" s="72"/>
-      <c r="AH22" s="72"/>
-      <c r="AI22" s="73"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="85"/>
+      <c r="L22" s="85"/>
+      <c r="M22" s="85"/>
+      <c r="N22" s="85"/>
+      <c r="O22" s="85"/>
+      <c r="P22" s="86"/>
+      <c r="Q22" s="87"/>
+      <c r="R22" s="88"/>
+      <c r="S22" s="88"/>
+      <c r="T22" s="88"/>
+      <c r="U22" s="88"/>
+      <c r="V22" s="88"/>
+      <c r="W22" s="88"/>
+      <c r="X22" s="88"/>
+      <c r="Y22" s="88"/>
+      <c r="Z22" s="88"/>
+      <c r="AA22" s="88"/>
+      <c r="AB22" s="88"/>
+      <c r="AC22" s="88"/>
+      <c r="AD22" s="88"/>
+      <c r="AE22" s="89"/>
+      <c r="AF22" s="84"/>
+      <c r="AG22" s="85"/>
+      <c r="AH22" s="85"/>
+      <c r="AI22" s="86"/>
     </row>
     <row r="23" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="29"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="71"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="72"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="72"/>
-      <c r="P23" s="73"/>
-      <c r="Q23" s="74"/>
-      <c r="R23" s="75"/>
-      <c r="S23" s="75"/>
-      <c r="T23" s="75"/>
-      <c r="U23" s="75"/>
-      <c r="V23" s="75"/>
-      <c r="W23" s="75"/>
-      <c r="X23" s="75"/>
-      <c r="Y23" s="75"/>
-      <c r="Z23" s="75"/>
-      <c r="AA23" s="75"/>
-      <c r="AB23" s="75"/>
-      <c r="AC23" s="75"/>
-      <c r="AD23" s="75"/>
-      <c r="AE23" s="76"/>
-      <c r="AF23" s="71"/>
-      <c r="AG23" s="72"/>
-      <c r="AH23" s="72"/>
-      <c r="AI23" s="73"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="85"/>
+      <c r="M23" s="85"/>
+      <c r="N23" s="85"/>
+      <c r="O23" s="85"/>
+      <c r="P23" s="86"/>
+      <c r="Q23" s="87"/>
+      <c r="R23" s="88"/>
+      <c r="S23" s="88"/>
+      <c r="T23" s="88"/>
+      <c r="U23" s="88"/>
+      <c r="V23" s="88"/>
+      <c r="W23" s="88"/>
+      <c r="X23" s="88"/>
+      <c r="Y23" s="88"/>
+      <c r="Z23" s="88"/>
+      <c r="AA23" s="88"/>
+      <c r="AB23" s="88"/>
+      <c r="AC23" s="88"/>
+      <c r="AD23" s="88"/>
+      <c r="AE23" s="89"/>
+      <c r="AF23" s="84"/>
+      <c r="AG23" s="85"/>
+      <c r="AH23" s="85"/>
+      <c r="AI23" s="86"/>
     </row>
     <row r="24" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="29"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="66"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="66"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="72"/>
-      <c r="N24" s="72"/>
-      <c r="O24" s="72"/>
-      <c r="P24" s="73"/>
-      <c r="Q24" s="74"/>
-      <c r="R24" s="75"/>
-      <c r="S24" s="75"/>
-      <c r="T24" s="75"/>
-      <c r="U24" s="75"/>
-      <c r="V24" s="75"/>
-      <c r="W24" s="75"/>
-      <c r="X24" s="75"/>
-      <c r="Y24" s="75"/>
-      <c r="Z24" s="75"/>
-      <c r="AA24" s="75"/>
-      <c r="AB24" s="75"/>
-      <c r="AC24" s="75"/>
-      <c r="AD24" s="75"/>
-      <c r="AE24" s="76"/>
-      <c r="AF24" s="71"/>
-      <c r="AG24" s="72"/>
-      <c r="AH24" s="72"/>
-      <c r="AI24" s="73"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="79"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="85"/>
+      <c r="L24" s="85"/>
+      <c r="M24" s="85"/>
+      <c r="N24" s="85"/>
+      <c r="O24" s="85"/>
+      <c r="P24" s="86"/>
+      <c r="Q24" s="87"/>
+      <c r="R24" s="88"/>
+      <c r="S24" s="88"/>
+      <c r="T24" s="88"/>
+      <c r="U24" s="88"/>
+      <c r="V24" s="88"/>
+      <c r="W24" s="88"/>
+      <c r="X24" s="88"/>
+      <c r="Y24" s="88"/>
+      <c r="Z24" s="88"/>
+      <c r="AA24" s="88"/>
+      <c r="AB24" s="88"/>
+      <c r="AC24" s="88"/>
+      <c r="AD24" s="88"/>
+      <c r="AE24" s="89"/>
+      <c r="AF24" s="84"/>
+      <c r="AG24" s="85"/>
+      <c r="AH24" s="85"/>
+      <c r="AI24" s="86"/>
     </row>
     <row r="25" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="29"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="66"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="72"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="72"/>
-      <c r="P25" s="73"/>
-      <c r="Q25" s="74"/>
-      <c r="R25" s="75"/>
-      <c r="S25" s="75"/>
-      <c r="T25" s="75"/>
-      <c r="U25" s="75"/>
-      <c r="V25" s="75"/>
-      <c r="W25" s="75"/>
-      <c r="X25" s="75"/>
-      <c r="Y25" s="75"/>
-      <c r="Z25" s="75"/>
-      <c r="AA25" s="75"/>
-      <c r="AB25" s="75"/>
-      <c r="AC25" s="75"/>
-      <c r="AD25" s="75"/>
-      <c r="AE25" s="76"/>
-      <c r="AF25" s="71"/>
-      <c r="AG25" s="72"/>
-      <c r="AH25" s="72"/>
-      <c r="AI25" s="73"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="78"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="85"/>
+      <c r="L25" s="85"/>
+      <c r="M25" s="85"/>
+      <c r="N25" s="85"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="88"/>
+      <c r="S25" s="88"/>
+      <c r="T25" s="88"/>
+      <c r="U25" s="88"/>
+      <c r="V25" s="88"/>
+      <c r="W25" s="88"/>
+      <c r="X25" s="88"/>
+      <c r="Y25" s="88"/>
+      <c r="Z25" s="88"/>
+      <c r="AA25" s="88"/>
+      <c r="AB25" s="88"/>
+      <c r="AC25" s="88"/>
+      <c r="AD25" s="88"/>
+      <c r="AE25" s="89"/>
+      <c r="AF25" s="84"/>
+      <c r="AG25" s="85"/>
+      <c r="AH25" s="85"/>
+      <c r="AI25" s="86"/>
     </row>
     <row r="26" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="29"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="72"/>
-      <c r="M26" s="72"/>
-      <c r="N26" s="72"/>
-      <c r="O26" s="72"/>
-      <c r="P26" s="73"/>
-      <c r="Q26" s="74"/>
-      <c r="R26" s="75"/>
-      <c r="S26" s="75"/>
-      <c r="T26" s="75"/>
-      <c r="U26" s="75"/>
-      <c r="V26" s="75"/>
-      <c r="W26" s="75"/>
-      <c r="X26" s="75"/>
-      <c r="Y26" s="75"/>
-      <c r="Z26" s="75"/>
-      <c r="AA26" s="75"/>
-      <c r="AB26" s="75"/>
-      <c r="AC26" s="75"/>
-      <c r="AD26" s="75"/>
-      <c r="AE26" s="76"/>
-      <c r="AF26" s="71"/>
-      <c r="AG26" s="72"/>
-      <c r="AH26" s="72"/>
-      <c r="AI26" s="73"/>
+      <c r="B26" s="78"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="79"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="85"/>
+      <c r="L26" s="85"/>
+      <c r="M26" s="85"/>
+      <c r="N26" s="85"/>
+      <c r="O26" s="85"/>
+      <c r="P26" s="86"/>
+      <c r="Q26" s="87"/>
+      <c r="R26" s="88"/>
+      <c r="S26" s="88"/>
+      <c r="T26" s="88"/>
+      <c r="U26" s="88"/>
+      <c r="V26" s="88"/>
+      <c r="W26" s="88"/>
+      <c r="X26" s="88"/>
+      <c r="Y26" s="88"/>
+      <c r="Z26" s="88"/>
+      <c r="AA26" s="88"/>
+      <c r="AB26" s="88"/>
+      <c r="AC26" s="88"/>
+      <c r="AD26" s="88"/>
+      <c r="AE26" s="89"/>
+      <c r="AF26" s="84"/>
+      <c r="AG26" s="85"/>
+      <c r="AH26" s="85"/>
+      <c r="AI26" s="86"/>
     </row>
     <row r="27" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="29"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="66"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="72"/>
-      <c r="M27" s="72"/>
-      <c r="N27" s="72"/>
-      <c r="O27" s="72"/>
-      <c r="P27" s="73"/>
-      <c r="Q27" s="74"/>
-      <c r="R27" s="75"/>
-      <c r="S27" s="75"/>
-      <c r="T27" s="75"/>
-      <c r="U27" s="75"/>
-      <c r="V27" s="75"/>
-      <c r="W27" s="75"/>
-      <c r="X27" s="75"/>
-      <c r="Y27" s="75"/>
-      <c r="Z27" s="75"/>
-      <c r="AA27" s="75"/>
-      <c r="AB27" s="75"/>
-      <c r="AC27" s="75"/>
-      <c r="AD27" s="75"/>
-      <c r="AE27" s="76"/>
-      <c r="AF27" s="71"/>
-      <c r="AG27" s="72"/>
-      <c r="AH27" s="72"/>
-      <c r="AI27" s="73"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="79"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="83"/>
+      <c r="I27" s="79"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="85"/>
+      <c r="M27" s="85"/>
+      <c r="N27" s="85"/>
+      <c r="O27" s="85"/>
+      <c r="P27" s="86"/>
+      <c r="Q27" s="87"/>
+      <c r="R27" s="88"/>
+      <c r="S27" s="88"/>
+      <c r="T27" s="88"/>
+      <c r="U27" s="88"/>
+      <c r="V27" s="88"/>
+      <c r="W27" s="88"/>
+      <c r="X27" s="88"/>
+      <c r="Y27" s="88"/>
+      <c r="Z27" s="88"/>
+      <c r="AA27" s="88"/>
+      <c r="AB27" s="88"/>
+      <c r="AC27" s="88"/>
+      <c r="AD27" s="88"/>
+      <c r="AE27" s="89"/>
+      <c r="AF27" s="84"/>
+      <c r="AG27" s="85"/>
+      <c r="AH27" s="85"/>
+      <c r="AI27" s="86"/>
     </row>
     <row r="28" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="29"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="66"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="71"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="72"/>
-      <c r="M28" s="72"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="72"/>
-      <c r="P28" s="73"/>
-      <c r="Q28" s="74"/>
-      <c r="R28" s="75"/>
-      <c r="S28" s="75"/>
-      <c r="T28" s="75"/>
-      <c r="U28" s="75"/>
-      <c r="V28" s="75"/>
-      <c r="W28" s="75"/>
-      <c r="X28" s="75"/>
-      <c r="Y28" s="75"/>
-      <c r="Z28" s="75"/>
-      <c r="AA28" s="75"/>
-      <c r="AB28" s="75"/>
-      <c r="AC28" s="75"/>
-      <c r="AD28" s="75"/>
-      <c r="AE28" s="76"/>
-      <c r="AF28" s="71"/>
-      <c r="AG28" s="72"/>
-      <c r="AH28" s="72"/>
-      <c r="AI28" s="73"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="79"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="78"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="85"/>
+      <c r="L28" s="85"/>
+      <c r="M28" s="85"/>
+      <c r="N28" s="85"/>
+      <c r="O28" s="85"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="87"/>
+      <c r="R28" s="88"/>
+      <c r="S28" s="88"/>
+      <c r="T28" s="88"/>
+      <c r="U28" s="88"/>
+      <c r="V28" s="88"/>
+      <c r="W28" s="88"/>
+      <c r="X28" s="88"/>
+      <c r="Y28" s="88"/>
+      <c r="Z28" s="88"/>
+      <c r="AA28" s="88"/>
+      <c r="AB28" s="88"/>
+      <c r="AC28" s="88"/>
+      <c r="AD28" s="88"/>
+      <c r="AE28" s="89"/>
+      <c r="AF28" s="84"/>
+      <c r="AG28" s="85"/>
+      <c r="AH28" s="85"/>
+      <c r="AI28" s="86"/>
     </row>
     <row r="29" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="29"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="66"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="71"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="72"/>
-      <c r="M29" s="72"/>
-      <c r="N29" s="72"/>
-      <c r="O29" s="72"/>
-      <c r="P29" s="73"/>
-      <c r="Q29" s="74"/>
-      <c r="R29" s="75"/>
-      <c r="S29" s="75"/>
-      <c r="T29" s="75"/>
-      <c r="U29" s="75"/>
-      <c r="V29" s="75"/>
-      <c r="W29" s="75"/>
-      <c r="X29" s="75"/>
-      <c r="Y29" s="75"/>
-      <c r="Z29" s="75"/>
-      <c r="AA29" s="75"/>
-      <c r="AB29" s="75"/>
-      <c r="AC29" s="75"/>
-      <c r="AD29" s="75"/>
-      <c r="AE29" s="76"/>
-      <c r="AF29" s="71"/>
-      <c r="AG29" s="72"/>
-      <c r="AH29" s="72"/>
-      <c r="AI29" s="73"/>
+      <c r="B29" s="78"/>
+      <c r="C29" s="79"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="78"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="85"/>
+      <c r="M29" s="85"/>
+      <c r="N29" s="85"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="86"/>
+      <c r="Q29" s="87"/>
+      <c r="R29" s="88"/>
+      <c r="S29" s="88"/>
+      <c r="T29" s="88"/>
+      <c r="U29" s="88"/>
+      <c r="V29" s="88"/>
+      <c r="W29" s="88"/>
+      <c r="X29" s="88"/>
+      <c r="Y29" s="88"/>
+      <c r="Z29" s="88"/>
+      <c r="AA29" s="88"/>
+      <c r="AB29" s="88"/>
+      <c r="AC29" s="88"/>
+      <c r="AD29" s="88"/>
+      <c r="AE29" s="89"/>
+      <c r="AF29" s="84"/>
+      <c r="AG29" s="85"/>
+      <c r="AH29" s="85"/>
+      <c r="AI29" s="86"/>
     </row>
     <row r="30" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="29"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="66"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="71"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="72"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="72"/>
-      <c r="O30" s="72"/>
-      <c r="P30" s="73"/>
-      <c r="Q30" s="74"/>
-      <c r="R30" s="75"/>
-      <c r="S30" s="75"/>
-      <c r="T30" s="75"/>
-      <c r="U30" s="75"/>
-      <c r="V30" s="75"/>
-      <c r="W30" s="75"/>
-      <c r="X30" s="75"/>
-      <c r="Y30" s="75"/>
-      <c r="Z30" s="75"/>
-      <c r="AA30" s="75"/>
-      <c r="AB30" s="75"/>
-      <c r="AC30" s="75"/>
-      <c r="AD30" s="75"/>
-      <c r="AE30" s="76"/>
-      <c r="AF30" s="71"/>
-      <c r="AG30" s="72"/>
-      <c r="AH30" s="72"/>
-      <c r="AI30" s="73"/>
+      <c r="B30" s="78"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="85"/>
+      <c r="L30" s="85"/>
+      <c r="M30" s="85"/>
+      <c r="N30" s="85"/>
+      <c r="O30" s="85"/>
+      <c r="P30" s="86"/>
+      <c r="Q30" s="87"/>
+      <c r="R30" s="88"/>
+      <c r="S30" s="88"/>
+      <c r="T30" s="88"/>
+      <c r="U30" s="88"/>
+      <c r="V30" s="88"/>
+      <c r="W30" s="88"/>
+      <c r="X30" s="88"/>
+      <c r="Y30" s="88"/>
+      <c r="Z30" s="88"/>
+      <c r="AA30" s="88"/>
+      <c r="AB30" s="88"/>
+      <c r="AC30" s="88"/>
+      <c r="AD30" s="88"/>
+      <c r="AE30" s="89"/>
+      <c r="AF30" s="84"/>
+      <c r="AG30" s="85"/>
+      <c r="AH30" s="85"/>
+      <c r="AI30" s="86"/>
     </row>
     <row r="31" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="29"/>
-      <c r="B31" s="65"/>
-      <c r="C31" s="66"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="66"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="72"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="72"/>
-      <c r="O31" s="72"/>
-      <c r="P31" s="73"/>
-      <c r="Q31" s="74"/>
-      <c r="R31" s="75"/>
-      <c r="S31" s="75"/>
-      <c r="T31" s="75"/>
-      <c r="U31" s="75"/>
-      <c r="V31" s="75"/>
-      <c r="W31" s="75"/>
-      <c r="X31" s="75"/>
-      <c r="Y31" s="75"/>
-      <c r="Z31" s="75"/>
-      <c r="AA31" s="75"/>
-      <c r="AB31" s="75"/>
-      <c r="AC31" s="75"/>
-      <c r="AD31" s="75"/>
-      <c r="AE31" s="76"/>
-      <c r="AF31" s="71"/>
-      <c r="AG31" s="72"/>
-      <c r="AH31" s="72"/>
-      <c r="AI31" s="73"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="79"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="79"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="85"/>
+      <c r="P31" s="86"/>
+      <c r="Q31" s="87"/>
+      <c r="R31" s="88"/>
+      <c r="S31" s="88"/>
+      <c r="T31" s="88"/>
+      <c r="U31" s="88"/>
+      <c r="V31" s="88"/>
+      <c r="W31" s="88"/>
+      <c r="X31" s="88"/>
+      <c r="Y31" s="88"/>
+      <c r="Z31" s="88"/>
+      <c r="AA31" s="88"/>
+      <c r="AB31" s="88"/>
+      <c r="AC31" s="88"/>
+      <c r="AD31" s="88"/>
+      <c r="AE31" s="89"/>
+      <c r="AF31" s="84"/>
+      <c r="AG31" s="85"/>
+      <c r="AH31" s="85"/>
+      <c r="AI31" s="86"/>
     </row>
     <row r="32" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="29"/>
-      <c r="B32" s="65"/>
-      <c r="C32" s="66"/>
-      <c r="D32" s="67"/>
-      <c r="E32" s="68"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="70"/>
-      <c r="I32" s="66"/>
-      <c r="J32" s="71"/>
-      <c r="K32" s="77"/>
-      <c r="L32" s="72"/>
-      <c r="M32" s="72"/>
-      <c r="N32" s="72"/>
-      <c r="O32" s="72"/>
-      <c r="P32" s="73"/>
-      <c r="Q32" s="74"/>
-      <c r="R32" s="75"/>
-      <c r="S32" s="75"/>
-      <c r="T32" s="75"/>
-      <c r="U32" s="75"/>
-      <c r="V32" s="75"/>
-      <c r="W32" s="75"/>
-      <c r="X32" s="75"/>
-      <c r="Y32" s="75"/>
-      <c r="Z32" s="75"/>
-      <c r="AA32" s="75"/>
-      <c r="AB32" s="75"/>
-      <c r="AC32" s="75"/>
-      <c r="AD32" s="75"/>
-      <c r="AE32" s="76"/>
-      <c r="AF32" s="71"/>
-      <c r="AG32" s="72"/>
-      <c r="AH32" s="72"/>
-      <c r="AI32" s="73"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="79"/>
+      <c r="D32" s="80"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="85"/>
+      <c r="M32" s="85"/>
+      <c r="N32" s="85"/>
+      <c r="O32" s="85"/>
+      <c r="P32" s="86"/>
+      <c r="Q32" s="87"/>
+      <c r="R32" s="88"/>
+      <c r="S32" s="88"/>
+      <c r="T32" s="88"/>
+      <c r="U32" s="88"/>
+      <c r="V32" s="88"/>
+      <c r="W32" s="88"/>
+      <c r="X32" s="88"/>
+      <c r="Y32" s="88"/>
+      <c r="Z32" s="88"/>
+      <c r="AA32" s="88"/>
+      <c r="AB32" s="88"/>
+      <c r="AC32" s="88"/>
+      <c r="AD32" s="88"/>
+      <c r="AE32" s="89"/>
+      <c r="AF32" s="84"/>
+      <c r="AG32" s="85"/>
+      <c r="AH32" s="85"/>
+      <c r="AI32" s="86"/>
     </row>
     <row r="33" spans="1:35" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="29"/>
-      <c r="B33" s="65"/>
-      <c r="C33" s="66"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="65"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="66"/>
-      <c r="J33" s="71"/>
-      <c r="K33" s="72"/>
-      <c r="L33" s="72"/>
-      <c r="M33" s="72"/>
-      <c r="N33" s="72"/>
-      <c r="O33" s="72"/>
-      <c r="P33" s="73"/>
-      <c r="Q33" s="74"/>
-      <c r="R33" s="75"/>
-      <c r="S33" s="75"/>
-      <c r="T33" s="75"/>
-      <c r="U33" s="75"/>
-      <c r="V33" s="75"/>
-      <c r="W33" s="75"/>
-      <c r="X33" s="75"/>
-      <c r="Y33" s="75"/>
-      <c r="Z33" s="75"/>
-      <c r="AA33" s="75"/>
-      <c r="AB33" s="75"/>
-      <c r="AC33" s="75"/>
-      <c r="AD33" s="75"/>
-      <c r="AE33" s="76"/>
-      <c r="AF33" s="71"/>
-      <c r="AG33" s="72"/>
-      <c r="AH33" s="72"/>
-      <c r="AI33" s="73"/>
+      <c r="B33" s="78"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="78"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="84"/>
+      <c r="K33" s="85"/>
+      <c r="L33" s="85"/>
+      <c r="M33" s="85"/>
+      <c r="N33" s="85"/>
+      <c r="O33" s="85"/>
+      <c r="P33" s="86"/>
+      <c r="Q33" s="87"/>
+      <c r="R33" s="88"/>
+      <c r="S33" s="88"/>
+      <c r="T33" s="88"/>
+      <c r="U33" s="88"/>
+      <c r="V33" s="88"/>
+      <c r="W33" s="88"/>
+      <c r="X33" s="88"/>
+      <c r="Y33" s="88"/>
+      <c r="Z33" s="88"/>
+      <c r="AA33" s="88"/>
+      <c r="AB33" s="88"/>
+      <c r="AC33" s="88"/>
+      <c r="AD33" s="88"/>
+      <c r="AE33" s="89"/>
+      <c r="AF33" s="84"/>
+      <c r="AG33" s="85"/>
+      <c r="AH33" s="85"/>
+      <c r="AI33" s="86"/>
     </row>
     <row r="34" spans="1:35" ht="14.25" x14ac:dyDescent="0.15">
       <c r="K34" s="31"/>
@@ -8860,7 +9078,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AL49"/>
+  <dimension ref="A1:AL50"/>
   <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16" width="3.625" style="37" customWidth="1"/>
@@ -8997,163 +9215,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="98" t="s">
-        <v>294</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="101" t="str">
+      <c r="A1" s="121" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="107" t="s">
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="130" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="116" t="str">
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="139" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarchを使用したシステム開発における標準WBS</v>
       </c>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="118"/>
-      <c r="AA1" s="128" t="s">
-        <v>282</v>
-      </c>
-      <c r="AB1" s="129"/>
-      <c r="AC1" s="125" t="str">
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
+      <c r="Y1" s="140"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="151" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="126"/>
-      <c r="AE1" s="126"/>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="130">
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="150"/>
+      <c r="AG1" s="153">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="131"/>
-      <c r="AI1" s="132"/>
+      <c r="AH1" s="154"/>
+      <c r="AI1" s="155"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3"/>
     </row>
     <row r="2" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="98" t="s">
-        <v>283</v>
-      </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="101" t="str">
+      <c r="A2" s="121" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="110"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="120"/>
-      <c r="Y2" s="120"/>
-      <c r="Z2" s="121"/>
-      <c r="AA2" s="128" t="s">
-        <v>284</v>
-      </c>
-      <c r="AB2" s="129"/>
-      <c r="AC2" s="125" t="str">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="133"/>
+      <c r="P2" s="134"/>
+      <c r="Q2" s="134"/>
+      <c r="R2" s="135"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="143"/>
+      <c r="U2" s="143"/>
+      <c r="V2" s="143"/>
+      <c r="W2" s="143"/>
+      <c r="X2" s="143"/>
+      <c r="Y2" s="143"/>
+      <c r="Z2" s="144"/>
+      <c r="AA2" s="151" t="s">
+        <v>282</v>
+      </c>
+      <c r="AB2" s="152"/>
+      <c r="AC2" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="126"/>
-      <c r="AE2" s="126"/>
-      <c r="AF2" s="127"/>
-      <c r="AG2" s="130">
+      <c r="AD2" s="149"/>
+      <c r="AE2" s="149"/>
+      <c r="AF2" s="150"/>
+      <c r="AG2" s="153">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>44455</v>
-      </c>
-      <c r="AH2" s="131"/>
-      <c r="AI2" s="132"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="154"/>
+      <c r="AI2" s="155"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:38" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="98" t="s">
-        <v>285</v>
-      </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="101" t="str">
+      <c r="A3" s="121" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="113"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
-      <c r="R3" s="115"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="123"/>
-      <c r="U3" s="123"/>
-      <c r="V3" s="123"/>
-      <c r="W3" s="123"/>
-      <c r="X3" s="123"/>
-      <c r="Y3" s="123"/>
-      <c r="Z3" s="124"/>
-      <c r="AA3" s="128"/>
-      <c r="AB3" s="129"/>
-      <c r="AC3" s="125" t="str">
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="137"/>
+      <c r="Q3" s="137"/>
+      <c r="R3" s="138"/>
+      <c r="S3" s="145"/>
+      <c r="T3" s="146"/>
+      <c r="U3" s="146"/>
+      <c r="V3" s="146"/>
+      <c r="W3" s="146"/>
+      <c r="X3" s="146"/>
+      <c r="Y3" s="146"/>
+      <c r="Z3" s="147"/>
+      <c r="AA3" s="151"/>
+      <c r="AB3" s="152"/>
+      <c r="AC3" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="126"/>
-      <c r="AE3" s="126"/>
-      <c r="AF3" s="127"/>
-      <c r="AG3" s="130" t="str">
+      <c r="AD3" s="149"/>
+      <c r="AE3" s="149"/>
+      <c r="AF3" s="150"/>
+      <c r="AG3" s="153" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="131"/>
-      <c r="AI3" s="132"/>
+      <c r="AH3" s="154"/>
+      <c r="AI3" s="155"/>
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
@@ -9213,7 +9431,7 @@
       <c r="O5" s="30"/>
       <c r="P5" s="30"/>
       <c r="Q5" s="16" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="R5" s="30"/>
       <c r="S5" s="30"/>
@@ -9274,7 +9492,7 @@
     <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="30"/>
       <c r="B7" s="30" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C7" s="30"/>
       <c r="D7" s="30"/>
@@ -9314,7 +9532,7 @@
       <c r="A8" s="30"/>
       <c r="B8" s="30"/>
       <c r="C8" s="34" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D8" s="30"/>
       <c r="E8" s="30"/>
@@ -9353,7 +9571,7 @@
       <c r="A9" s="30"/>
       <c r="B9" s="30"/>
       <c r="C9" s="34" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
@@ -9391,7 +9609,7 @@
       <c r="A10" s="30"/>
       <c r="B10" s="30"/>
       <c r="C10" s="34" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
@@ -9428,7 +9646,9 @@
     <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="30"/>
       <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
+      <c r="C11" s="34" t="s">
+        <v>400</v>
+      </c>
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
       <c r="F11" s="30"/>
@@ -9463,9 +9683,7 @@
     </row>
     <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="30"/>
-      <c r="B12" s="30" t="s">
-        <v>305</v>
-      </c>
+      <c r="B12" s="30"/>
       <c r="C12" s="30"/>
       <c r="D12" s="30"/>
       <c r="E12" s="30"/>
@@ -9477,7 +9695,6 @@
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
       <c r="M12" s="30"/>
-      <c r="N12" s="35"/>
       <c r="O12" s="30"/>
       <c r="P12" s="32"/>
       <c r="Q12" s="30"/>
@@ -9502,7 +9719,9 @@
     </row>
     <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
+      <c r="B13" s="30" t="s">
+        <v>303</v>
+      </c>
       <c r="C13" s="30"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30"/>
@@ -9514,11 +9733,11 @@
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
+      <c r="N13" s="35"/>
       <c r="O13" s="30"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="30"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="32"/>
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
       <c r="U13" s="30"/>
@@ -9576,7 +9795,7 @@
     </row>
     <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="30"/>
-      <c r="B15" s="38"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="30"/>
       <c r="D15" s="30"/>
       <c r="E15" s="30"/>
@@ -9588,10 +9807,10 @@
       <c r="K15" s="30"/>
       <c r="L15" s="30"/>
       <c r="M15" s="30"/>
-      <c r="N15" s="35"/>
+      <c r="N15" s="30"/>
       <c r="O15" s="30"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="30"/>
+      <c r="P15" s="30"/>
+      <c r="Q15" s="38"/>
       <c r="R15" s="30"/>
       <c r="S15" s="30"/>
       <c r="T15" s="30"/>
@@ -9613,7 +9832,7 @@
     </row>
     <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
+      <c r="B16" s="38"/>
       <c r="C16" s="30"/>
       <c r="D16" s="30"/>
       <c r="E16" s="30"/>
@@ -9625,7 +9844,7 @@
       <c r="K16" s="30"/>
       <c r="L16" s="30"/>
       <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
+      <c r="N16" s="35"/>
       <c r="O16" s="30"/>
       <c r="P16" s="32"/>
       <c r="Q16" s="30"/>
@@ -9800,6 +10019,7 @@
       <c r="A21" s="30"/>
       <c r="B21" s="30"/>
       <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
       <c r="E21" s="30"/>
       <c r="F21" s="30"/>
       <c r="G21" s="30"/>
@@ -9836,7 +10056,6 @@
       <c r="A22" s="30"/>
       <c r="B22" s="30"/>
       <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
       <c r="E22" s="30"/>
       <c r="F22" s="30"/>
       <c r="G22" s="30"/>
@@ -9871,7 +10090,7 @@
     </row>
     <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="30"/>
-      <c r="B23" s="38"/>
+      <c r="B23" s="30"/>
       <c r="C23" s="30"/>
       <c r="D23" s="30"/>
       <c r="E23" s="30"/>
@@ -9883,7 +10102,7 @@
       <c r="K23" s="30"/>
       <c r="L23" s="30"/>
       <c r="M23" s="30"/>
-      <c r="N23" s="35"/>
+      <c r="N23" s="30"/>
       <c r="O23" s="30"/>
       <c r="P23" s="32"/>
       <c r="Q23" s="30"/>
@@ -9908,7 +10127,7 @@
     </row>
     <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
+      <c r="B24" s="38"/>
       <c r="C24" s="30"/>
       <c r="D24" s="30"/>
       <c r="E24" s="30"/>
@@ -9920,7 +10139,7 @@
       <c r="K24" s="30"/>
       <c r="L24" s="30"/>
       <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
+      <c r="N24" s="35"/>
       <c r="O24" s="30"/>
       <c r="P24" s="32"/>
       <c r="Q24" s="30"/>
@@ -10068,7 +10287,7 @@
       <c r="K28" s="30"/>
       <c r="L28" s="30"/>
       <c r="M28" s="30"/>
-      <c r="N28" s="35"/>
+      <c r="N28" s="30"/>
       <c r="O28" s="30"/>
       <c r="P28" s="32"/>
       <c r="Q28" s="30"/>
@@ -10105,7 +10324,7 @@
       <c r="K29" s="30"/>
       <c r="L29" s="30"/>
       <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
+      <c r="N29" s="35"/>
       <c r="O29" s="30"/>
       <c r="P29" s="32"/>
       <c r="Q29" s="30"/>
@@ -10129,7 +10348,7 @@
       <c r="AI29" s="30"/>
     </row>
     <row r="30" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="39"/>
+      <c r="A30" s="30"/>
       <c r="B30" s="30"/>
       <c r="C30" s="30"/>
       <c r="D30" s="30"/>
@@ -10149,26 +10368,26 @@
       <c r="R30" s="30"/>
       <c r="S30" s="30"/>
       <c r="T30" s="30"/>
-      <c r="U30" s="39"/>
-      <c r="V30" s="39"/>
-      <c r="W30" s="39"/>
-      <c r="X30" s="39"/>
-      <c r="Y30" s="39"/>
-      <c r="Z30" s="39"/>
-      <c r="AA30" s="39"/>
-      <c r="AB30" s="39"/>
-      <c r="AC30" s="39"/>
-      <c r="AD30" s="39"/>
-      <c r="AE30" s="39"/>
-      <c r="AF30" s="39"/>
-      <c r="AG30" s="40"/>
-      <c r="AH30" s="41"/>
-      <c r="AI30" s="39"/>
+      <c r="U30" s="30"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="30"/>
+      <c r="X30" s="30"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="30"/>
+      <c r="AA30" s="30"/>
+      <c r="AB30" s="30"/>
+      <c r="AC30" s="30"/>
+      <c r="AD30" s="30"/>
+      <c r="AE30" s="30"/>
+      <c r="AF30" s="30"/>
+      <c r="AG30" s="32"/>
+      <c r="AH30" s="36"/>
+      <c r="AI30" s="30"/>
     </row>
     <row r="31" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="39"/>
       <c r="B31" s="30"/>
-      <c r="C31" s="32"/>
+      <c r="C31" s="30"/>
       <c r="D31" s="30"/>
       <c r="E31" s="30"/>
       <c r="F31" s="30"/>
@@ -10182,9 +10401,9 @@
       <c r="N31" s="30"/>
       <c r="O31" s="30"/>
       <c r="P31" s="32"/>
-      <c r="Q31" s="36"/>
+      <c r="Q31" s="30"/>
       <c r="R31" s="30"/>
-      <c r="S31" s="42"/>
+      <c r="S31" s="30"/>
       <c r="T31" s="30"/>
       <c r="U31" s="39"/>
       <c r="V31" s="39"/>
@@ -10204,25 +10423,25 @@
     </row>
     <row r="32" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="39"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="39"/>
-      <c r="J32" s="39"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="39"/>
-      <c r="M32" s="39"/>
-      <c r="N32" s="39"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="44"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="32"/>
       <c r="Q32" s="36"/>
-      <c r="R32" s="39"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="39"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="42"/>
+      <c r="T32" s="30"/>
       <c r="U32" s="39"/>
       <c r="V32" s="39"/>
       <c r="W32" s="39"/>
@@ -10250,7 +10469,7 @@
       <c r="H33" s="39"/>
       <c r="I33" s="39"/>
       <c r="J33" s="39"/>
-      <c r="K33" s="39"/>
+      <c r="K33" s="43"/>
       <c r="L33" s="39"/>
       <c r="M33" s="39"/>
       <c r="N33" s="39"/>
@@ -10258,7 +10477,7 @@
       <c r="P33" s="44"/>
       <c r="Q33" s="36"/>
       <c r="R33" s="39"/>
-      <c r="S33" s="39"/>
+      <c r="S33" s="45"/>
       <c r="T33" s="39"/>
       <c r="U33" s="39"/>
       <c r="V33" s="39"/>
@@ -10287,7 +10506,7 @@
       <c r="H34" s="39"/>
       <c r="I34" s="39"/>
       <c r="J34" s="39"/>
-      <c r="K34" s="43"/>
+      <c r="K34" s="39"/>
       <c r="L34" s="39"/>
       <c r="M34" s="39"/>
       <c r="N34" s="39"/>
@@ -10295,7 +10514,7 @@
       <c r="P34" s="44"/>
       <c r="Q34" s="36"/>
       <c r="R34" s="39"/>
-      <c r="S34" s="45"/>
+      <c r="S34" s="39"/>
       <c r="T34" s="39"/>
       <c r="U34" s="39"/>
       <c r="V34" s="39"/>
@@ -10324,7 +10543,7 @@
       <c r="H35" s="39"/>
       <c r="I35" s="39"/>
       <c r="J35" s="39"/>
-      <c r="K35" s="39"/>
+      <c r="K35" s="43"/>
       <c r="L35" s="39"/>
       <c r="M35" s="39"/>
       <c r="N35" s="39"/>
@@ -10332,9 +10551,9 @@
       <c r="P35" s="44"/>
       <c r="Q35" s="36"/>
       <c r="R35" s="39"/>
-      <c r="S35" s="39"/>
+      <c r="S35" s="45"/>
       <c r="T35" s="39"/>
-      <c r="U35" s="46"/>
+      <c r="U35" s="39"/>
       <c r="V35" s="39"/>
       <c r="W35" s="39"/>
       <c r="X35" s="39"/>
@@ -10353,7 +10572,7 @@
     <row r="36" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="39"/>
       <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
+      <c r="C36" s="30"/>
       <c r="D36" s="39"/>
       <c r="E36" s="39"/>
       <c r="F36" s="39"/>
@@ -10367,11 +10586,11 @@
       <c r="N36" s="39"/>
       <c r="O36" s="39"/>
       <c r="P36" s="44"/>
-      <c r="Q36" s="41"/>
+      <c r="Q36" s="36"/>
       <c r="R36" s="39"/>
       <c r="S36" s="39"/>
       <c r="T36" s="39"/>
-      <c r="U36" s="39"/>
+      <c r="U36" s="46"/>
       <c r="V36" s="39"/>
       <c r="W36" s="39"/>
       <c r="X36" s="39"/>
@@ -10383,55 +10602,92 @@
       <c r="AD36" s="39"/>
       <c r="AE36" s="39"/>
       <c r="AF36" s="39"/>
-      <c r="AG36" s="39"/>
+      <c r="AG36" s="40"/>
       <c r="AH36" s="41"/>
       <c r="AI36" s="39"/>
     </row>
     <row r="37" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="P37" s="47"/>
-      <c r="U37" s="49"/>
-      <c r="AG37" s="50"/>
+      <c r="A37" s="39"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="39"/>
+      <c r="L37" s="39"/>
+      <c r="M37" s="39"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="44"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="39"/>
+      <c r="S37" s="39"/>
+      <c r="T37" s="39"/>
+      <c r="U37" s="39"/>
+      <c r="V37" s="39"/>
+      <c r="W37" s="39"/>
+      <c r="X37" s="39"/>
+      <c r="Y37" s="39"/>
+      <c r="Z37" s="39"/>
+      <c r="AA37" s="39"/>
+      <c r="AB37" s="39"/>
+      <c r="AC37" s="39"/>
+      <c r="AD37" s="39"/>
+      <c r="AE37" s="39"/>
+      <c r="AF37" s="39"/>
+      <c r="AG37" s="39"/>
+      <c r="AH37" s="41"/>
+      <c r="AI37" s="39"/>
     </row>
     <row r="38" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P38" s="47"/>
       <c r="U38" s="49"/>
-      <c r="AF38" s="50"/>
-      <c r="AG38" s="47"/>
+      <c r="AG38" s="50"/>
     </row>
     <row r="39" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="T39" s="49"/>
+      <c r="U39" s="49"/>
       <c r="AF39" s="50"/>
-      <c r="AG39" s="50"/>
+      <c r="AG39" s="47"/>
     </row>
     <row r="40" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AG40" s="47"/>
+      <c r="T40" s="49"/>
+      <c r="AF40" s="50"/>
+      <c r="AG40" s="50"/>
     </row>
     <row r="41" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AG41" s="47"/>
     </row>
     <row r="42" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AF42" s="50"/>
       <c r="AG42" s="47"/>
     </row>
     <row r="43" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AF43" s="50"/>
-      <c r="AG43" s="50"/>
+      <c r="AG43" s="47"/>
     </row>
     <row r="44" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AF44" s="50"/>
       <c r="AG44" s="50"/>
     </row>
     <row r="45" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AF45" s="50"/>
       <c r="AG45" s="50"/>
     </row>
     <row r="46" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AF46" s="50"/>
       <c r="AG46" s="50"/>
     </row>
     <row r="47" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AF47" s="50"/>
       <c r="AG47" s="50"/>
     </row>
-    <row r="49" spans="33:33" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AG49" s="50"/>
+    <row r="48" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AG48" s="50"/>
+    </row>
+    <row r="50" spans="33:33" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AG50" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -10466,7 +10722,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AW69"/>
+  <dimension ref="A1:AW94"/>
   <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="31" width="3.625" style="30" customWidth="1"/>
@@ -10474,59 +10730,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="98" t="s">
-        <v>294</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="101" t="str">
+      <c r="A1" s="121" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="137" t="s">
-        <v>296</v>
-      </c>
-      <c r="P1" s="138"/>
-      <c r="Q1" s="138"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="116" t="str">
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="160" t="s">
+        <v>294</v>
+      </c>
+      <c r="P1" s="161"/>
+      <c r="Q1" s="161"/>
+      <c r="R1" s="162"/>
+      <c r="S1" s="139" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarchを使用したシステム開発における標準WBS</v>
       </c>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="118"/>
-      <c r="AA1" s="98" t="s">
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
+      <c r="Y1" s="140"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="AB1" s="100"/>
-      <c r="AC1" s="125" t="str">
+      <c r="AB1" s="123"/>
+      <c r="AC1" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="126"/>
-      <c r="AE1" s="126"/>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="130">
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="150"/>
+      <c r="AG1" s="153">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="131"/>
-      <c r="AI1" s="132"/>
+      <c r="AH1" s="154"/>
+      <c r="AI1" s="155"/>
       <c r="AJ1" s="30"/>
       <c r="AN1" s="51"/>
       <c r="AO1" s="30"/>
@@ -10540,54 +10796,54 @@
       <c r="AW1" s="30"/>
     </row>
     <row r="2" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="98" t="s">
-        <v>283</v>
-      </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="101" t="str">
+      <c r="A2" s="121" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="140"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="141"/>
-      <c r="R2" s="142"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="120"/>
-      <c r="Y2" s="120"/>
-      <c r="Z2" s="121"/>
-      <c r="AA2" s="98" t="s">
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="164"/>
+      <c r="Q2" s="164"/>
+      <c r="R2" s="165"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="143"/>
+      <c r="U2" s="143"/>
+      <c r="V2" s="143"/>
+      <c r="W2" s="143"/>
+      <c r="X2" s="143"/>
+      <c r="Y2" s="143"/>
+      <c r="Z2" s="144"/>
+      <c r="AA2" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="AB2" s="100"/>
-      <c r="AC2" s="125" t="str">
+      <c r="AB2" s="123"/>
+      <c r="AC2" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="126"/>
-      <c r="AE2" s="126"/>
-      <c r="AF2" s="127"/>
-      <c r="AG2" s="130">
+      <c r="AD2" s="149"/>
+      <c r="AE2" s="149"/>
+      <c r="AF2" s="150"/>
+      <c r="AG2" s="153">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>44455</v>
-      </c>
-      <c r="AH2" s="131"/>
-      <c r="AI2" s="132"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="154"/>
+      <c r="AI2" s="155"/>
       <c r="AJ2" s="30"/>
       <c r="AN2" s="51"/>
       <c r="AO2" s="30"/>
@@ -10601,52 +10857,52 @@
       <c r="AW2" s="30"/>
     </row>
     <row r="3" spans="1:49" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="98" t="s">
-        <v>285</v>
-      </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="101" t="str">
+      <c r="A3" s="121" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="124" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="143"/>
-      <c r="P3" s="144"/>
-      <c r="Q3" s="144"/>
-      <c r="R3" s="145"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="123"/>
-      <c r="U3" s="123"/>
-      <c r="V3" s="123"/>
-      <c r="W3" s="123"/>
-      <c r="X3" s="123"/>
-      <c r="Y3" s="123"/>
-      <c r="Z3" s="124"/>
-      <c r="AA3" s="98"/>
-      <c r="AB3" s="100"/>
-      <c r="AC3" s="125" t="str">
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="166"/>
+      <c r="P3" s="167"/>
+      <c r="Q3" s="167"/>
+      <c r="R3" s="168"/>
+      <c r="S3" s="145"/>
+      <c r="T3" s="146"/>
+      <c r="U3" s="146"/>
+      <c r="V3" s="146"/>
+      <c r="W3" s="146"/>
+      <c r="X3" s="146"/>
+      <c r="Y3" s="146"/>
+      <c r="Z3" s="147"/>
+      <c r="AA3" s="121"/>
+      <c r="AB3" s="123"/>
+      <c r="AC3" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="126"/>
-      <c r="AE3" s="126"/>
-      <c r="AF3" s="127"/>
-      <c r="AG3" s="130" t="str">
+      <c r="AD3" s="149"/>
+      <c r="AE3" s="149"/>
+      <c r="AF3" s="150"/>
+      <c r="AG3" s="153" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="131"/>
-      <c r="AI3" s="132"/>
+      <c r="AH3" s="154"/>
+      <c r="AI3" s="155"/>
       <c r="AJ3" s="53"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
@@ -10665,12 +10921,12 @@
     <row r="4" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="5" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="34" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="34" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -10679,7 +10935,7 @@
     <row r="8" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="34"/>
       <c r="D8" s="54" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -10697,7 +10953,7 @@
     <row r="11" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C11" s="34"/>
       <c r="D11" s="54" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -10715,7 +10971,7 @@
     </row>
     <row r="15" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C15" s="34" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:49" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -10724,7 +10980,7 @@
     <row r="17" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="34"/>
       <c r="D17" s="30" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -10812,13 +11068,13 @@
     <row r="43" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="34"/>
       <c r="D43" s="54" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="44" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="34"/>
       <c r="D44" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="45" spans="3:4" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -10842,401 +11098,1094 @@
       <c r="D48" s="54"/>
     </row>
     <row r="49" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C49" s="34"/>
-      <c r="D49" s="54"/>
+      <c r="C49" s="34" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="50" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C50" s="34" t="s">
-        <v>303</v>
-      </c>
+      <c r="C50" s="34"/>
     </row>
     <row r="51" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C51" s="34"/>
+      <c r="D51" s="54" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="52" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C52" s="34"/>
       <c r="D52" s="54" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="53" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C53" s="34"/>
       <c r="D53" s="54" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="54" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C54" s="34"/>
       <c r="D54" s="54" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="55" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C55" s="34"/>
-      <c r="D55" s="54" t="s">
-        <v>213</v>
-      </c>
+      <c r="D55" s="54"/>
     </row>
     <row r="56" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C56" s="34"/>
-      <c r="D56" s="54"/>
-    </row>
-    <row r="57" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D56" s="54" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.15">
       <c r="C57" s="34"/>
-      <c r="D57" s="54" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D57" s="55" t="s">
+        <v>305</v>
+      </c>
+      <c r="E57" s="157" t="s">
+        <v>107</v>
+      </c>
+      <c r="F57" s="158"/>
+      <c r="G57" s="158"/>
+      <c r="H57" s="158"/>
+      <c r="I57" s="158"/>
+      <c r="J57" s="159"/>
+      <c r="K57" s="157" t="s">
+        <v>178</v>
+      </c>
+      <c r="L57" s="158"/>
+      <c r="M57" s="158"/>
+      <c r="N57" s="158"/>
+      <c r="O57" s="158"/>
+      <c r="P57" s="158"/>
+      <c r="Q57" s="158"/>
+      <c r="R57" s="158"/>
+      <c r="S57" s="158"/>
+      <c r="T57" s="158"/>
+      <c r="U57" s="158"/>
+      <c r="V57" s="158"/>
+      <c r="W57" s="158"/>
+      <c r="X57" s="158"/>
+      <c r="Y57" s="158"/>
+      <c r="Z57" s="158"/>
+      <c r="AA57" s="158"/>
+      <c r="AB57" s="159"/>
+    </row>
+    <row r="58" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="34"/>
-      <c r="D58" s="55" t="s">
-        <v>307</v>
-      </c>
-      <c r="E58" s="134" t="s">
-        <v>107</v>
-      </c>
-      <c r="F58" s="135"/>
-      <c r="G58" s="135"/>
-      <c r="H58" s="135"/>
-      <c r="I58" s="135"/>
-      <c r="J58" s="136"/>
-      <c r="K58" s="134" t="s">
-        <v>178</v>
-      </c>
-      <c r="L58" s="135"/>
-      <c r="M58" s="135"/>
-      <c r="N58" s="135"/>
-      <c r="O58" s="135"/>
-      <c r="P58" s="135"/>
-      <c r="Q58" s="135"/>
-      <c r="R58" s="135"/>
-      <c r="S58" s="135"/>
-      <c r="T58" s="135"/>
-      <c r="U58" s="135"/>
-      <c r="V58" s="135"/>
-      <c r="W58" s="135"/>
-      <c r="X58" s="135"/>
-      <c r="Y58" s="135"/>
-      <c r="Z58" s="135"/>
-      <c r="AA58" s="135"/>
-      <c r="AB58" s="136"/>
-    </row>
-    <row r="59" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D58" s="56">
+        <v>1</v>
+      </c>
+      <c r="E58" s="156" t="s">
+        <v>34</v>
+      </c>
+      <c r="F58" s="156"/>
+      <c r="G58" s="156"/>
+      <c r="H58" s="156"/>
+      <c r="I58" s="156"/>
+      <c r="J58" s="156"/>
+      <c r="K58" s="156" t="s">
+        <v>18</v>
+      </c>
+      <c r="L58" s="156"/>
+      <c r="M58" s="156"/>
+      <c r="N58" s="156"/>
+      <c r="O58" s="156"/>
+      <c r="P58" s="156"/>
+      <c r="Q58" s="156"/>
+      <c r="R58" s="156"/>
+      <c r="S58" s="156"/>
+      <c r="T58" s="156"/>
+      <c r="U58" s="156"/>
+      <c r="V58" s="156"/>
+      <c r="W58" s="156"/>
+      <c r="X58" s="156"/>
+      <c r="Y58" s="156"/>
+      <c r="Z58" s="156"/>
+      <c r="AA58" s="156"/>
+      <c r="AB58" s="156"/>
+    </row>
+    <row r="59" spans="3:28" ht="48" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C59" s="34"/>
       <c r="D59" s="56">
-        <v>1</v>
-      </c>
-      <c r="E59" s="133" t="s">
-        <v>34</v>
-      </c>
-      <c r="F59" s="133"/>
-      <c r="G59" s="133"/>
-      <c r="H59" s="133"/>
-      <c r="I59" s="133"/>
-      <c r="J59" s="133"/>
-      <c r="K59" s="133" t="s">
-        <v>18</v>
-      </c>
-      <c r="L59" s="133"/>
-      <c r="M59" s="133"/>
-      <c r="N59" s="133"/>
-      <c r="O59" s="133"/>
-      <c r="P59" s="133"/>
-      <c r="Q59" s="133"/>
-      <c r="R59" s="133"/>
-      <c r="S59" s="133"/>
-      <c r="T59" s="133"/>
-      <c r="U59" s="133"/>
-      <c r="V59" s="133"/>
-      <c r="W59" s="133"/>
-      <c r="X59" s="133"/>
-      <c r="Y59" s="133"/>
-      <c r="Z59" s="133"/>
-      <c r="AA59" s="133"/>
-      <c r="AB59" s="133"/>
-    </row>
-    <row r="60" spans="3:28" ht="48" customHeight="1" x14ac:dyDescent="0.15">
+        <v>2</v>
+      </c>
+      <c r="E59" s="156" t="s">
+        <v>43</v>
+      </c>
+      <c r="F59" s="156"/>
+      <c r="G59" s="156"/>
+      <c r="H59" s="156"/>
+      <c r="I59" s="156"/>
+      <c r="J59" s="156"/>
+      <c r="K59" s="156" t="s">
+        <v>19</v>
+      </c>
+      <c r="L59" s="156"/>
+      <c r="M59" s="156"/>
+      <c r="N59" s="156"/>
+      <c r="O59" s="156"/>
+      <c r="P59" s="156"/>
+      <c r="Q59" s="156"/>
+      <c r="R59" s="156"/>
+      <c r="S59" s="156"/>
+      <c r="T59" s="156"/>
+      <c r="U59" s="156"/>
+      <c r="V59" s="156"/>
+      <c r="W59" s="156"/>
+      <c r="X59" s="156"/>
+      <c r="Y59" s="156"/>
+      <c r="Z59" s="156"/>
+      <c r="AA59" s="156"/>
+      <c r="AB59" s="156"/>
+    </row>
+    <row r="60" spans="3:28" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C60" s="34"/>
       <c r="D60" s="56">
-        <v>2</v>
-      </c>
-      <c r="E60" s="133" t="s">
-        <v>43</v>
-      </c>
-      <c r="F60" s="133"/>
-      <c r="G60" s="133"/>
-      <c r="H60" s="133"/>
-      <c r="I60" s="133"/>
-      <c r="J60" s="133"/>
-      <c r="K60" s="133" t="s">
-        <v>19</v>
-      </c>
-      <c r="L60" s="133"/>
-      <c r="M60" s="133"/>
-      <c r="N60" s="133"/>
-      <c r="O60" s="133"/>
-      <c r="P60" s="133"/>
-      <c r="Q60" s="133"/>
-      <c r="R60" s="133"/>
-      <c r="S60" s="133"/>
-      <c r="T60" s="133"/>
-      <c r="U60" s="133"/>
-      <c r="V60" s="133"/>
-      <c r="W60" s="133"/>
-      <c r="X60" s="133"/>
-      <c r="Y60" s="133"/>
-      <c r="Z60" s="133"/>
-      <c r="AA60" s="133"/>
-      <c r="AB60" s="133"/>
-    </row>
-    <row r="61" spans="3:28" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>3</v>
+      </c>
+      <c r="E60" s="156" t="s">
+        <v>200</v>
+      </c>
+      <c r="F60" s="156"/>
+      <c r="G60" s="156"/>
+      <c r="H60" s="156"/>
+      <c r="I60" s="156"/>
+      <c r="J60" s="156"/>
+      <c r="K60" s="156" t="s">
+        <v>106</v>
+      </c>
+      <c r="L60" s="156"/>
+      <c r="M60" s="156"/>
+      <c r="N60" s="156"/>
+      <c r="O60" s="156"/>
+      <c r="P60" s="156"/>
+      <c r="Q60" s="156"/>
+      <c r="R60" s="156"/>
+      <c r="S60" s="156"/>
+      <c r="T60" s="156"/>
+      <c r="U60" s="156"/>
+      <c r="V60" s="156"/>
+      <c r="W60" s="156"/>
+      <c r="X60" s="156"/>
+      <c r="Y60" s="156"/>
+      <c r="Z60" s="156"/>
+      <c r="AA60" s="156"/>
+      <c r="AB60" s="156"/>
+    </row>
+    <row r="61" spans="3:28" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C61" s="34"/>
       <c r="D61" s="56">
-        <v>3</v>
-      </c>
-      <c r="E61" s="133" t="s">
-        <v>200</v>
-      </c>
-      <c r="F61" s="133"/>
-      <c r="G61" s="133"/>
-      <c r="H61" s="133"/>
-      <c r="I61" s="133"/>
-      <c r="J61" s="133"/>
-      <c r="K61" s="133" t="s">
-        <v>106</v>
-      </c>
-      <c r="L61" s="133"/>
-      <c r="M61" s="133"/>
-      <c r="N61" s="133"/>
-      <c r="O61" s="133"/>
-      <c r="P61" s="133"/>
-      <c r="Q61" s="133"/>
-      <c r="R61" s="133"/>
-      <c r="S61" s="133"/>
-      <c r="T61" s="133"/>
-      <c r="U61" s="133"/>
-      <c r="V61" s="133"/>
-      <c r="W61" s="133"/>
-      <c r="X61" s="133"/>
-      <c r="Y61" s="133"/>
-      <c r="Z61" s="133"/>
-      <c r="AA61" s="133"/>
-      <c r="AB61" s="133"/>
-    </row>
-    <row r="62" spans="3:28" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>4</v>
+      </c>
+      <c r="E61" s="156" t="s">
+        <v>201</v>
+      </c>
+      <c r="F61" s="156"/>
+      <c r="G61" s="156"/>
+      <c r="H61" s="156"/>
+      <c r="I61" s="156"/>
+      <c r="J61" s="156"/>
+      <c r="K61" s="156" t="s">
+        <v>20</v>
+      </c>
+      <c r="L61" s="156"/>
+      <c r="M61" s="156"/>
+      <c r="N61" s="156"/>
+      <c r="O61" s="156"/>
+      <c r="P61" s="156"/>
+      <c r="Q61" s="156"/>
+      <c r="R61" s="156"/>
+      <c r="S61" s="156"/>
+      <c r="T61" s="156"/>
+      <c r="U61" s="156"/>
+      <c r="V61" s="156"/>
+      <c r="W61" s="156"/>
+      <c r="X61" s="156"/>
+      <c r="Y61" s="156"/>
+      <c r="Z61" s="156"/>
+      <c r="AA61" s="156"/>
+      <c r="AB61" s="156"/>
+    </row>
+    <row r="62" spans="3:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C62" s="34"/>
       <c r="D62" s="56">
-        <v>4</v>
-      </c>
-      <c r="E62" s="133" t="s">
-        <v>201</v>
-      </c>
-      <c r="F62" s="133"/>
-      <c r="G62" s="133"/>
-      <c r="H62" s="133"/>
-      <c r="I62" s="133"/>
-      <c r="J62" s="133"/>
-      <c r="K62" s="133" t="s">
-        <v>20</v>
-      </c>
-      <c r="L62" s="133"/>
-      <c r="M62" s="133"/>
-      <c r="N62" s="133"/>
-      <c r="O62" s="133"/>
-      <c r="P62" s="133"/>
-      <c r="Q62" s="133"/>
-      <c r="R62" s="133"/>
-      <c r="S62" s="133"/>
-      <c r="T62" s="133"/>
-      <c r="U62" s="133"/>
-      <c r="V62" s="133"/>
-      <c r="W62" s="133"/>
-      <c r="X62" s="133"/>
-      <c r="Y62" s="133"/>
-      <c r="Z62" s="133"/>
-      <c r="AA62" s="133"/>
-      <c r="AB62" s="133"/>
-    </row>
-    <row r="63" spans="3:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+      <c r="E62" s="156" t="s">
+        <v>202</v>
+      </c>
+      <c r="F62" s="156"/>
+      <c r="G62" s="156"/>
+      <c r="H62" s="156"/>
+      <c r="I62" s="156"/>
+      <c r="J62" s="156"/>
+      <c r="K62" s="156" t="s">
+        <v>21</v>
+      </c>
+      <c r="L62" s="156"/>
+      <c r="M62" s="156"/>
+      <c r="N62" s="156"/>
+      <c r="O62" s="156"/>
+      <c r="P62" s="156"/>
+      <c r="Q62" s="156"/>
+      <c r="R62" s="156"/>
+      <c r="S62" s="156"/>
+      <c r="T62" s="156"/>
+      <c r="U62" s="156"/>
+      <c r="V62" s="156"/>
+      <c r="W62" s="156"/>
+      <c r="X62" s="156"/>
+      <c r="Y62" s="156"/>
+      <c r="Z62" s="156"/>
+      <c r="AA62" s="156"/>
+      <c r="AB62" s="156"/>
+    </row>
+    <row r="63" spans="3:28" ht="72" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C63" s="34"/>
       <c r="D63" s="56">
-        <v>5</v>
-      </c>
-      <c r="E63" s="133" t="s">
-        <v>202</v>
-      </c>
-      <c r="F63" s="133"/>
-      <c r="G63" s="133"/>
-      <c r="H63" s="133"/>
-      <c r="I63" s="133"/>
-      <c r="J63" s="133"/>
-      <c r="K63" s="133" t="s">
-        <v>21</v>
-      </c>
-      <c r="L63" s="133"/>
-      <c r="M63" s="133"/>
-      <c r="N63" s="133"/>
-      <c r="O63" s="133"/>
-      <c r="P63" s="133"/>
-      <c r="Q63" s="133"/>
-      <c r="R63" s="133"/>
-      <c r="S63" s="133"/>
-      <c r="T63" s="133"/>
-      <c r="U63" s="133"/>
-      <c r="V63" s="133"/>
-      <c r="W63" s="133"/>
-      <c r="X63" s="133"/>
-      <c r="Y63" s="133"/>
-      <c r="Z63" s="133"/>
-      <c r="AA63" s="133"/>
-      <c r="AB63" s="133"/>
-    </row>
-    <row r="64" spans="3:28" ht="72" customHeight="1" x14ac:dyDescent="0.15">
+        <v>6</v>
+      </c>
+      <c r="E63" s="156" t="s">
+        <v>225</v>
+      </c>
+      <c r="F63" s="156"/>
+      <c r="G63" s="156"/>
+      <c r="H63" s="156"/>
+      <c r="I63" s="156"/>
+      <c r="J63" s="156"/>
+      <c r="K63" s="156" t="s">
+        <v>306</v>
+      </c>
+      <c r="L63" s="156"/>
+      <c r="M63" s="156"/>
+      <c r="N63" s="156"/>
+      <c r="O63" s="156"/>
+      <c r="P63" s="156"/>
+      <c r="Q63" s="156"/>
+      <c r="R63" s="156"/>
+      <c r="S63" s="156"/>
+      <c r="T63" s="156"/>
+      <c r="U63" s="156"/>
+      <c r="V63" s="156"/>
+      <c r="W63" s="156"/>
+      <c r="X63" s="156"/>
+      <c r="Y63" s="156"/>
+      <c r="Z63" s="156"/>
+      <c r="AA63" s="156"/>
+      <c r="AB63" s="156"/>
+    </row>
+    <row r="64" spans="3:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C64" s="34"/>
       <c r="D64" s="56">
-        <v>6</v>
-      </c>
-      <c r="E64" s="133" t="s">
-        <v>225</v>
-      </c>
-      <c r="F64" s="133"/>
-      <c r="G64" s="133"/>
-      <c r="H64" s="133"/>
-      <c r="I64" s="133"/>
-      <c r="J64" s="133"/>
-      <c r="K64" s="133" t="s">
-        <v>308</v>
-      </c>
-      <c r="L64" s="133"/>
-      <c r="M64" s="133"/>
-      <c r="N64" s="133"/>
-      <c r="O64" s="133"/>
-      <c r="P64" s="133"/>
-      <c r="Q64" s="133"/>
-      <c r="R64" s="133"/>
-      <c r="S64" s="133"/>
-      <c r="T64" s="133"/>
-      <c r="U64" s="133"/>
-      <c r="V64" s="133"/>
-      <c r="W64" s="133"/>
-      <c r="X64" s="133"/>
-      <c r="Y64" s="133"/>
-      <c r="Z64" s="133"/>
-      <c r="AA64" s="133"/>
-      <c r="AB64" s="133"/>
-    </row>
-    <row r="65" spans="3:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+      <c r="E64" s="156" t="s">
+        <v>155</v>
+      </c>
+      <c r="F64" s="156"/>
+      <c r="G64" s="156"/>
+      <c r="H64" s="156"/>
+      <c r="I64" s="156"/>
+      <c r="J64" s="156"/>
+      <c r="K64" s="156" t="s">
+        <v>221</v>
+      </c>
+      <c r="L64" s="156"/>
+      <c r="M64" s="156"/>
+      <c r="N64" s="156"/>
+      <c r="O64" s="156"/>
+      <c r="P64" s="156"/>
+      <c r="Q64" s="156"/>
+      <c r="R64" s="156"/>
+      <c r="S64" s="156"/>
+      <c r="T64" s="156"/>
+      <c r="U64" s="156"/>
+      <c r="V64" s="156"/>
+      <c r="W64" s="156"/>
+      <c r="X64" s="156"/>
+      <c r="Y64" s="156"/>
+      <c r="Z64" s="156"/>
+      <c r="AA64" s="156"/>
+      <c r="AB64" s="156"/>
+    </row>
+    <row r="65" spans="3:28" ht="108" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C65" s="34"/>
       <c r="D65" s="56">
-        <v>7</v>
-      </c>
-      <c r="E65" s="133" t="s">
-        <v>155</v>
-      </c>
-      <c r="F65" s="133"/>
-      <c r="G65" s="133"/>
-      <c r="H65" s="133"/>
-      <c r="I65" s="133"/>
-      <c r="J65" s="133"/>
-      <c r="K65" s="133" t="s">
-        <v>221</v>
-      </c>
-      <c r="L65" s="133"/>
-      <c r="M65" s="133"/>
-      <c r="N65" s="133"/>
-      <c r="O65" s="133"/>
-      <c r="P65" s="133"/>
-      <c r="Q65" s="133"/>
-      <c r="R65" s="133"/>
-      <c r="S65" s="133"/>
-      <c r="T65" s="133"/>
-      <c r="U65" s="133"/>
-      <c r="V65" s="133"/>
-      <c r="W65" s="133"/>
-      <c r="X65" s="133"/>
-      <c r="Y65" s="133"/>
-      <c r="Z65" s="133"/>
-      <c r="AA65" s="133"/>
-      <c r="AB65" s="133"/>
-    </row>
-    <row r="66" spans="3:28" ht="108" customHeight="1" x14ac:dyDescent="0.15">
+        <v>8</v>
+      </c>
+      <c r="E65" s="156" t="s">
+        <v>102</v>
+      </c>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="156" t="s">
+        <v>217</v>
+      </c>
+      <c r="L65" s="156"/>
+      <c r="M65" s="156"/>
+      <c r="N65" s="156"/>
+      <c r="O65" s="156"/>
+      <c r="P65" s="156"/>
+      <c r="Q65" s="156"/>
+      <c r="R65" s="156"/>
+      <c r="S65" s="156"/>
+      <c r="T65" s="156"/>
+      <c r="U65" s="156"/>
+      <c r="V65" s="156"/>
+      <c r="W65" s="156"/>
+      <c r="X65" s="156"/>
+      <c r="Y65" s="156"/>
+      <c r="Z65" s="156"/>
+      <c r="AA65" s="156"/>
+      <c r="AB65" s="156"/>
+    </row>
+    <row r="66" spans="3:28" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C66" s="34"/>
       <c r="D66" s="56">
-        <v>8</v>
-      </c>
-      <c r="E66" s="133" t="s">
-        <v>102</v>
-      </c>
-      <c r="F66" s="133"/>
-      <c r="G66" s="133"/>
-      <c r="H66" s="133"/>
-      <c r="I66" s="133"/>
-      <c r="J66" s="133"/>
-      <c r="K66" s="133" t="s">
-        <v>217</v>
-      </c>
-      <c r="L66" s="133"/>
-      <c r="M66" s="133"/>
-      <c r="N66" s="133"/>
-      <c r="O66" s="133"/>
-      <c r="P66" s="133"/>
-      <c r="Q66" s="133"/>
-      <c r="R66" s="133"/>
-      <c r="S66" s="133"/>
-      <c r="T66" s="133"/>
-      <c r="U66" s="133"/>
-      <c r="V66" s="133"/>
-      <c r="W66" s="133"/>
-      <c r="X66" s="133"/>
-      <c r="Y66" s="133"/>
-      <c r="Z66" s="133"/>
-      <c r="AA66" s="133"/>
-      <c r="AB66" s="133"/>
-    </row>
-    <row r="67" spans="3:28" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>9</v>
+      </c>
+      <c r="E66" s="156" t="s">
+        <v>104</v>
+      </c>
+      <c r="F66" s="156"/>
+      <c r="G66" s="156"/>
+      <c r="H66" s="156"/>
+      <c r="I66" s="156"/>
+      <c r="J66" s="156"/>
+      <c r="K66" s="156" t="s">
+        <v>22</v>
+      </c>
+      <c r="L66" s="156"/>
+      <c r="M66" s="156"/>
+      <c r="N66" s="156"/>
+      <c r="O66" s="156"/>
+      <c r="P66" s="156"/>
+      <c r="Q66" s="156"/>
+      <c r="R66" s="156"/>
+      <c r="S66" s="156"/>
+      <c r="T66" s="156"/>
+      <c r="U66" s="156"/>
+      <c r="V66" s="156"/>
+      <c r="W66" s="156"/>
+      <c r="X66" s="156"/>
+      <c r="Y66" s="156"/>
+      <c r="Z66" s="156"/>
+      <c r="AA66" s="156"/>
+      <c r="AB66" s="156"/>
+    </row>
+    <row r="67" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C67" s="34"/>
-      <c r="D67" s="56">
-        <v>9</v>
-      </c>
-      <c r="E67" s="133" t="s">
-        <v>104</v>
-      </c>
-      <c r="F67" s="133"/>
-      <c r="G67" s="133"/>
-      <c r="H67" s="133"/>
-      <c r="I67" s="133"/>
-      <c r="J67" s="133"/>
-      <c r="K67" s="133" t="s">
-        <v>22</v>
-      </c>
-      <c r="L67" s="133"/>
-      <c r="M67" s="133"/>
-      <c r="N67" s="133"/>
-      <c r="O67" s="133"/>
-      <c r="P67" s="133"/>
-      <c r="Q67" s="133"/>
-      <c r="R67" s="133"/>
-      <c r="S67" s="133"/>
-      <c r="T67" s="133"/>
-      <c r="U67" s="133"/>
-      <c r="V67" s="133"/>
-      <c r="W67" s="133"/>
-      <c r="X67" s="133"/>
-      <c r="Y67" s="133"/>
-      <c r="Z67" s="133"/>
-      <c r="AA67" s="133"/>
-      <c r="AB67" s="133"/>
     </row>
     <row r="68" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C68" s="34"/>
     </row>
-    <row r="69" spans="3:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C69" s="34"/>
+    <row r="69" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="C69" s="30" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="71" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D71" s="30" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="73" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D73" s="55" t="s">
+        <v>305</v>
+      </c>
+      <c r="E73" s="67" t="s">
+        <v>397</v>
+      </c>
+      <c r="F73" s="68"/>
+      <c r="G73" s="68"/>
+      <c r="H73" s="68"/>
+      <c r="I73" s="67" t="s">
+        <v>376</v>
+      </c>
+      <c r="J73" s="69"/>
+      <c r="K73" s="68"/>
+      <c r="L73" s="68"/>
+      <c r="M73" s="68"/>
+      <c r="N73" s="68"/>
+      <c r="O73" s="68"/>
+      <c r="P73" s="68"/>
+      <c r="Q73" s="68"/>
+      <c r="R73" s="68"/>
+      <c r="S73" s="68"/>
+      <c r="T73" s="69"/>
+      <c r="U73" s="73"/>
+      <c r="V73" s="74"/>
+      <c r="W73" s="74"/>
+      <c r="X73" s="74"/>
+      <c r="Y73" s="74"/>
+      <c r="Z73" s="74"/>
+      <c r="AA73" s="74"/>
+      <c r="AB73" s="74"/>
+    </row>
+    <row r="74" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D74" s="64">
+        <v>1</v>
+      </c>
+      <c r="E74" s="64" t="s">
+        <v>358</v>
+      </c>
+      <c r="F74" s="65"/>
+      <c r="G74" s="65"/>
+      <c r="H74" s="65"/>
+      <c r="I74" s="70" t="s">
+        <v>377</v>
+      </c>
+      <c r="J74" s="66"/>
+      <c r="K74" s="65"/>
+      <c r="L74" s="65"/>
+      <c r="M74" s="65"/>
+      <c r="N74" s="65"/>
+      <c r="O74" s="65"/>
+      <c r="P74" s="65"/>
+      <c r="Q74" s="65"/>
+      <c r="R74" s="65"/>
+      <c r="S74" s="65"/>
+      <c r="T74" s="66"/>
+      <c r="U74" s="71"/>
+      <c r="V74" s="72"/>
+      <c r="W74" s="72"/>
+      <c r="X74" s="72"/>
+      <c r="Y74" s="72"/>
+      <c r="Z74" s="72"/>
+      <c r="AA74" s="72"/>
+      <c r="AB74" s="72"/>
+    </row>
+    <row r="75" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D75" s="64">
+        <v>2</v>
+      </c>
+      <c r="E75" s="64" t="s">
+        <v>359</v>
+      </c>
+      <c r="F75" s="65"/>
+      <c r="G75" s="65"/>
+      <c r="H75" s="65"/>
+      <c r="I75" s="70" t="s">
+        <v>378</v>
+      </c>
+      <c r="J75" s="66"/>
+      <c r="K75" s="65"/>
+      <c r="L75" s="65"/>
+      <c r="M75" s="65"/>
+      <c r="N75" s="65"/>
+      <c r="O75" s="65"/>
+      <c r="P75" s="65"/>
+      <c r="Q75" s="65"/>
+      <c r="R75" s="65"/>
+      <c r="S75" s="65"/>
+      <c r="T75" s="66"/>
+      <c r="U75" s="71"/>
+      <c r="V75" s="72"/>
+      <c r="W75" s="72"/>
+      <c r="X75" s="72"/>
+      <c r="Y75" s="72"/>
+      <c r="Z75" s="72"/>
+      <c r="AA75" s="72"/>
+      <c r="AB75" s="72"/>
+    </row>
+    <row r="76" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D76" s="64">
+        <v>3</v>
+      </c>
+      <c r="E76" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="F76" s="65"/>
+      <c r="G76" s="65"/>
+      <c r="H76" s="65"/>
+      <c r="I76" s="70" t="s">
+        <v>379</v>
+      </c>
+      <c r="J76" s="66"/>
+      <c r="K76" s="65"/>
+      <c r="L76" s="65"/>
+      <c r="M76" s="65"/>
+      <c r="N76" s="65"/>
+      <c r="O76" s="65"/>
+      <c r="P76" s="65"/>
+      <c r="Q76" s="65"/>
+      <c r="R76" s="65"/>
+      <c r="S76" s="65"/>
+      <c r="T76" s="66"/>
+      <c r="U76" s="71"/>
+      <c r="V76" s="72"/>
+      <c r="W76" s="72"/>
+      <c r="X76" s="72"/>
+      <c r="Y76" s="72"/>
+      <c r="Z76" s="72"/>
+      <c r="AA76" s="72"/>
+      <c r="AB76" s="72"/>
+    </row>
+    <row r="77" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D77" s="64">
+        <v>4</v>
+      </c>
+      <c r="E77" s="64" t="s">
+        <v>361</v>
+      </c>
+      <c r="F77" s="65"/>
+      <c r="G77" s="65"/>
+      <c r="H77" s="65"/>
+      <c r="I77" s="70" t="s">
+        <v>380</v>
+      </c>
+      <c r="J77" s="66"/>
+      <c r="K77" s="65"/>
+      <c r="L77" s="65"/>
+      <c r="M77" s="65"/>
+      <c r="N77" s="65"/>
+      <c r="O77" s="65"/>
+      <c r="P77" s="65"/>
+      <c r="Q77" s="65"/>
+      <c r="R77" s="65"/>
+      <c r="S77" s="65"/>
+      <c r="T77" s="66"/>
+      <c r="U77" s="71"/>
+      <c r="V77" s="72"/>
+      <c r="W77" s="72"/>
+      <c r="X77" s="72"/>
+      <c r="Y77" s="72"/>
+      <c r="Z77" s="72"/>
+      <c r="AA77" s="72"/>
+      <c r="AB77" s="72"/>
+    </row>
+    <row r="78" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D78" s="64">
+        <v>5</v>
+      </c>
+      <c r="E78" s="64" t="s">
+        <v>362</v>
+      </c>
+      <c r="F78" s="65"/>
+      <c r="G78" s="65"/>
+      <c r="H78" s="65"/>
+      <c r="I78" s="70" t="s">
+        <v>381</v>
+      </c>
+      <c r="J78" s="66"/>
+      <c r="K78" s="65"/>
+      <c r="L78" s="65"/>
+      <c r="M78" s="65"/>
+      <c r="N78" s="65"/>
+      <c r="O78" s="65"/>
+      <c r="P78" s="65"/>
+      <c r="Q78" s="65"/>
+      <c r="R78" s="65"/>
+      <c r="S78" s="65"/>
+      <c r="T78" s="66"/>
+      <c r="U78" s="71"/>
+      <c r="V78" s="72"/>
+      <c r="W78" s="72"/>
+      <c r="X78" s="72"/>
+      <c r="Y78" s="72"/>
+      <c r="Z78" s="72"/>
+      <c r="AA78" s="72"/>
+      <c r="AB78" s="72"/>
+    </row>
+    <row r="79" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D79" s="64">
+        <v>6</v>
+      </c>
+      <c r="E79" s="64" t="s">
+        <v>363</v>
+      </c>
+      <c r="F79" s="65"/>
+      <c r="G79" s="65"/>
+      <c r="H79" s="65"/>
+      <c r="I79" s="70" t="s">
+        <v>382</v>
+      </c>
+      <c r="J79" s="66"/>
+      <c r="K79" s="65"/>
+      <c r="L79" s="65"/>
+      <c r="M79" s="65"/>
+      <c r="N79" s="65"/>
+      <c r="O79" s="65"/>
+      <c r="P79" s="65"/>
+      <c r="Q79" s="65"/>
+      <c r="R79" s="65"/>
+      <c r="S79" s="65"/>
+      <c r="T79" s="66"/>
+      <c r="U79" s="71"/>
+      <c r="V79" s="72"/>
+      <c r="W79" s="72"/>
+      <c r="X79" s="72"/>
+      <c r="Y79" s="72"/>
+      <c r="Z79" s="72"/>
+      <c r="AA79" s="72"/>
+      <c r="AB79" s="72"/>
+    </row>
+    <row r="80" spans="3:28" x14ac:dyDescent="0.15">
+      <c r="D80" s="64">
+        <v>7</v>
+      </c>
+      <c r="E80" s="64" t="s">
+        <v>408</v>
+      </c>
+      <c r="F80" s="65"/>
+      <c r="G80" s="65"/>
+      <c r="H80" s="65"/>
+      <c r="I80" s="70" t="s">
+        <v>383</v>
+      </c>
+      <c r="J80" s="66"/>
+      <c r="K80" s="65"/>
+      <c r="L80" s="65"/>
+      <c r="M80" s="65"/>
+      <c r="N80" s="65"/>
+      <c r="O80" s="65"/>
+      <c r="P80" s="65"/>
+      <c r="Q80" s="65"/>
+      <c r="R80" s="65"/>
+      <c r="S80" s="65"/>
+      <c r="T80" s="66"/>
+      <c r="U80" s="71"/>
+      <c r="V80" s="72"/>
+      <c r="W80" s="72"/>
+      <c r="X80" s="72"/>
+      <c r="Y80" s="72"/>
+      <c r="Z80" s="72"/>
+      <c r="AA80" s="72"/>
+      <c r="AB80" s="72"/>
+    </row>
+    <row r="81" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D81" s="64">
+        <v>8</v>
+      </c>
+      <c r="E81" s="64" t="s">
+        <v>364</v>
+      </c>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="70" t="s">
+        <v>384</v>
+      </c>
+      <c r="J81" s="66"/>
+      <c r="K81" s="65"/>
+      <c r="L81" s="65"/>
+      <c r="M81" s="65"/>
+      <c r="N81" s="65"/>
+      <c r="O81" s="65"/>
+      <c r="P81" s="65"/>
+      <c r="Q81" s="65"/>
+      <c r="R81" s="65"/>
+      <c r="S81" s="65"/>
+      <c r="T81" s="66"/>
+      <c r="U81" s="71"/>
+      <c r="V81" s="72"/>
+      <c r="W81" s="72"/>
+      <c r="X81" s="72"/>
+      <c r="Y81" s="72"/>
+      <c r="Z81" s="72"/>
+      <c r="AA81" s="72"/>
+      <c r="AB81" s="72"/>
+    </row>
+    <row r="82" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D82" s="64">
+        <v>9</v>
+      </c>
+      <c r="E82" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="F82" s="65"/>
+      <c r="G82" s="65"/>
+      <c r="H82" s="65"/>
+      <c r="I82" s="70" t="s">
+        <v>385</v>
+      </c>
+      <c r="J82" s="66"/>
+      <c r="K82" s="65"/>
+      <c r="L82" s="65"/>
+      <c r="M82" s="65"/>
+      <c r="N82" s="65"/>
+      <c r="O82" s="65"/>
+      <c r="P82" s="65"/>
+      <c r="Q82" s="65"/>
+      <c r="R82" s="65"/>
+      <c r="S82" s="65"/>
+      <c r="T82" s="66"/>
+      <c r="U82" s="71"/>
+      <c r="V82" s="72"/>
+      <c r="W82" s="72"/>
+      <c r="X82" s="72"/>
+      <c r="Y82" s="72"/>
+      <c r="Z82" s="72"/>
+      <c r="AA82" s="72"/>
+      <c r="AB82" s="72"/>
+    </row>
+    <row r="83" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D83" s="64">
+        <v>10</v>
+      </c>
+      <c r="E83" s="64" t="s">
+        <v>366</v>
+      </c>
+      <c r="F83" s="65"/>
+      <c r="G83" s="65"/>
+      <c r="H83" s="65"/>
+      <c r="I83" s="70" t="s">
+        <v>386</v>
+      </c>
+      <c r="J83" s="66"/>
+      <c r="K83" s="65"/>
+      <c r="L83" s="65"/>
+      <c r="M83" s="65"/>
+      <c r="N83" s="65"/>
+      <c r="O83" s="65"/>
+      <c r="P83" s="65"/>
+      <c r="Q83" s="65"/>
+      <c r="R83" s="65"/>
+      <c r="S83" s="65"/>
+      <c r="T83" s="66"/>
+      <c r="U83" s="71"/>
+      <c r="V83" s="72"/>
+      <c r="W83" s="72"/>
+      <c r="X83" s="72"/>
+      <c r="Y83" s="72"/>
+      <c r="Z83" s="72"/>
+      <c r="AA83" s="72"/>
+      <c r="AB83" s="72"/>
+    </row>
+    <row r="84" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D84" s="64">
+        <v>11</v>
+      </c>
+      <c r="E84" s="64" t="s">
+        <v>367</v>
+      </c>
+      <c r="F84" s="65"/>
+      <c r="G84" s="65"/>
+      <c r="H84" s="65"/>
+      <c r="I84" s="70" t="s">
+        <v>387</v>
+      </c>
+      <c r="J84" s="66"/>
+      <c r="K84" s="65"/>
+      <c r="L84" s="65"/>
+      <c r="M84" s="65"/>
+      <c r="N84" s="65"/>
+      <c r="O84" s="65"/>
+      <c r="P84" s="65"/>
+      <c r="Q84" s="65"/>
+      <c r="R84" s="65"/>
+      <c r="S84" s="65"/>
+      <c r="T84" s="66"/>
+      <c r="U84" s="71"/>
+      <c r="V84" s="72"/>
+      <c r="W84" s="72"/>
+      <c r="X84" s="72"/>
+      <c r="Y84" s="72"/>
+      <c r="Z84" s="72"/>
+      <c r="AA84" s="72"/>
+      <c r="AB84" s="72"/>
+    </row>
+    <row r="85" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D85" s="64">
+        <v>12</v>
+      </c>
+      <c r="E85" s="64" t="s">
+        <v>368</v>
+      </c>
+      <c r="F85" s="65"/>
+      <c r="G85" s="65"/>
+      <c r="H85" s="65"/>
+      <c r="I85" s="70" t="s">
+        <v>388</v>
+      </c>
+      <c r="J85" s="66"/>
+      <c r="K85" s="65"/>
+      <c r="L85" s="65"/>
+      <c r="M85" s="65"/>
+      <c r="N85" s="65"/>
+      <c r="O85" s="65"/>
+      <c r="P85" s="65"/>
+      <c r="Q85" s="65"/>
+      <c r="R85" s="65"/>
+      <c r="S85" s="65"/>
+      <c r="T85" s="66"/>
+      <c r="U85" s="71"/>
+      <c r="V85" s="72"/>
+      <c r="W85" s="72"/>
+      <c r="X85" s="72"/>
+      <c r="Y85" s="72"/>
+      <c r="Z85" s="72"/>
+      <c r="AA85" s="72"/>
+      <c r="AB85" s="72"/>
+    </row>
+    <row r="86" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D86" s="64">
+        <v>13</v>
+      </c>
+      <c r="E86" s="64" t="s">
+        <v>369</v>
+      </c>
+      <c r="F86" s="65"/>
+      <c r="G86" s="65"/>
+      <c r="H86" s="65"/>
+      <c r="I86" s="70" t="s">
+        <v>389</v>
+      </c>
+      <c r="J86" s="66"/>
+      <c r="K86" s="65"/>
+      <c r="L86" s="65"/>
+      <c r="M86" s="65"/>
+      <c r="N86" s="65"/>
+      <c r="O86" s="65"/>
+      <c r="P86" s="65"/>
+      <c r="Q86" s="65"/>
+      <c r="R86" s="65"/>
+      <c r="S86" s="65"/>
+      <c r="T86" s="66"/>
+      <c r="U86" s="71"/>
+      <c r="V86" s="72"/>
+      <c r="W86" s="72"/>
+      <c r="X86" s="72"/>
+      <c r="Y86" s="72"/>
+      <c r="Z86" s="72"/>
+      <c r="AA86" s="72"/>
+      <c r="AB86" s="72"/>
+    </row>
+    <row r="87" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D87" s="64">
+        <v>14</v>
+      </c>
+      <c r="E87" s="64" t="s">
+        <v>370</v>
+      </c>
+      <c r="F87" s="65"/>
+      <c r="G87" s="65"/>
+      <c r="H87" s="65"/>
+      <c r="I87" s="70" t="s">
+        <v>390</v>
+      </c>
+      <c r="J87" s="66"/>
+      <c r="K87" s="65"/>
+      <c r="L87" s="65"/>
+      <c r="M87" s="65"/>
+      <c r="N87" s="65"/>
+      <c r="O87" s="65"/>
+      <c r="P87" s="65"/>
+      <c r="Q87" s="65"/>
+      <c r="R87" s="65"/>
+      <c r="S87" s="65"/>
+      <c r="T87" s="66"/>
+      <c r="U87" s="71"/>
+      <c r="V87" s="72"/>
+      <c r="W87" s="72"/>
+      <c r="X87" s="72"/>
+      <c r="Y87" s="72"/>
+      <c r="Z87" s="72"/>
+      <c r="AA87" s="72"/>
+      <c r="AB87" s="72"/>
+    </row>
+    <row r="88" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D88" s="64">
+        <v>15</v>
+      </c>
+      <c r="E88" s="64" t="s">
+        <v>371</v>
+      </c>
+      <c r="F88" s="65"/>
+      <c r="G88" s="65"/>
+      <c r="H88" s="65"/>
+      <c r="I88" s="70" t="s">
+        <v>391</v>
+      </c>
+      <c r="J88" s="66"/>
+      <c r="K88" s="65"/>
+      <c r="L88" s="65"/>
+      <c r="M88" s="65"/>
+      <c r="N88" s="65"/>
+      <c r="O88" s="65"/>
+      <c r="P88" s="65"/>
+      <c r="Q88" s="65"/>
+      <c r="R88" s="65"/>
+      <c r="S88" s="65"/>
+      <c r="T88" s="66"/>
+      <c r="U88" s="71"/>
+      <c r="V88" s="72"/>
+      <c r="W88" s="72"/>
+      <c r="X88" s="72"/>
+      <c r="Y88" s="72"/>
+      <c r="Z88" s="72"/>
+      <c r="AA88" s="72"/>
+      <c r="AB88" s="72"/>
+    </row>
+    <row r="89" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D89" s="64">
+        <v>16</v>
+      </c>
+      <c r="E89" s="64" t="s">
+        <v>372</v>
+      </c>
+      <c r="F89" s="65"/>
+      <c r="G89" s="65"/>
+      <c r="H89" s="65"/>
+      <c r="I89" s="70" t="s">
+        <v>392</v>
+      </c>
+      <c r="J89" s="66"/>
+      <c r="K89" s="65"/>
+      <c r="L89" s="65"/>
+      <c r="M89" s="65"/>
+      <c r="N89" s="65"/>
+      <c r="O89" s="65"/>
+      <c r="P89" s="65"/>
+      <c r="Q89" s="65"/>
+      <c r="R89" s="65"/>
+      <c r="S89" s="65"/>
+      <c r="T89" s="66"/>
+      <c r="U89" s="71"/>
+      <c r="V89" s="72"/>
+      <c r="W89" s="72"/>
+      <c r="X89" s="72"/>
+      <c r="Y89" s="72"/>
+      <c r="Z89" s="72"/>
+      <c r="AA89" s="72"/>
+      <c r="AB89" s="72"/>
+    </row>
+    <row r="90" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D90" s="64">
+        <v>17</v>
+      </c>
+      <c r="E90" s="64" t="s">
+        <v>373</v>
+      </c>
+      <c r="F90" s="65"/>
+      <c r="G90" s="65"/>
+      <c r="H90" s="65"/>
+      <c r="I90" s="70" t="s">
+        <v>393</v>
+      </c>
+      <c r="J90" s="66"/>
+      <c r="K90" s="65"/>
+      <c r="L90" s="65"/>
+      <c r="M90" s="65"/>
+      <c r="N90" s="65"/>
+      <c r="O90" s="65"/>
+      <c r="P90" s="65"/>
+      <c r="Q90" s="65"/>
+      <c r="R90" s="65"/>
+      <c r="S90" s="65"/>
+      <c r="T90" s="66"/>
+      <c r="U90" s="71"/>
+      <c r="V90" s="72"/>
+      <c r="W90" s="72"/>
+      <c r="X90" s="72"/>
+      <c r="Y90" s="72"/>
+      <c r="Z90" s="72"/>
+      <c r="AA90" s="72"/>
+      <c r="AB90" s="72"/>
+    </row>
+    <row r="91" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D91" s="64">
+        <v>18</v>
+      </c>
+      <c r="E91" s="64" t="s">
+        <v>374</v>
+      </c>
+      <c r="F91" s="65"/>
+      <c r="G91" s="65"/>
+      <c r="H91" s="65"/>
+      <c r="I91" s="70" t="s">
+        <v>394</v>
+      </c>
+      <c r="J91" s="66"/>
+      <c r="K91" s="65"/>
+      <c r="L91" s="65"/>
+      <c r="M91" s="65"/>
+      <c r="N91" s="65"/>
+      <c r="O91" s="65"/>
+      <c r="P91" s="65"/>
+      <c r="Q91" s="65"/>
+      <c r="R91" s="65"/>
+      <c r="S91" s="65"/>
+      <c r="T91" s="66"/>
+      <c r="U91" s="71"/>
+      <c r="V91" s="72"/>
+      <c r="W91" s="72"/>
+      <c r="X91" s="72"/>
+      <c r="Y91" s="72"/>
+      <c r="Z91" s="72"/>
+      <c r="AA91" s="72"/>
+      <c r="AB91" s="72"/>
+    </row>
+    <row r="92" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D92" s="64">
+        <v>19</v>
+      </c>
+      <c r="E92" s="64" t="s">
+        <v>375</v>
+      </c>
+      <c r="F92" s="65"/>
+      <c r="G92" s="65"/>
+      <c r="H92" s="65"/>
+      <c r="I92" s="70" t="s">
+        <v>395</v>
+      </c>
+      <c r="J92" s="66"/>
+      <c r="K92" s="65"/>
+      <c r="L92" s="65"/>
+      <c r="M92" s="65"/>
+      <c r="N92" s="65"/>
+      <c r="O92" s="65"/>
+      <c r="P92" s="65"/>
+      <c r="Q92" s="65"/>
+      <c r="R92" s="65"/>
+      <c r="S92" s="65"/>
+      <c r="T92" s="66"/>
+      <c r="U92" s="71"/>
+      <c r="V92" s="72"/>
+      <c r="W92" s="72"/>
+      <c r="X92" s="72"/>
+      <c r="Y92" s="72"/>
+      <c r="Z92" s="72"/>
+      <c r="AA92" s="72"/>
+      <c r="AB92" s="72"/>
+    </row>
+    <row r="94" spans="4:28" x14ac:dyDescent="0.15">
+      <c r="D94" s="72"/>
+      <c r="E94" s="72"/>
+      <c r="F94" s="72"/>
+      <c r="G94" s="72"/>
+      <c r="H94" s="72"/>
+      <c r="I94" s="72"/>
+      <c r="J94" s="72"/>
+      <c r="K94" s="72"/>
+      <c r="L94" s="72"/>
+      <c r="M94" s="72"/>
+      <c r="N94" s="72"/>
+      <c r="O94" s="75"/>
+      <c r="P94" s="72"/>
+      <c r="Q94" s="72"/>
+      <c r="R94" s="72"/>
+      <c r="S94" s="72"/>
+      <c r="T94" s="72"/>
+      <c r="U94" s="72"/>
+      <c r="V94" s="72"/>
+      <c r="W94" s="72"/>
+      <c r="X94" s="72"/>
+      <c r="Y94" s="72"/>
+      <c r="Z94" s="72"/>
+      <c r="AA94" s="72"/>
+      <c r="AB94" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="E60:J60"/>
-    <mergeCell ref="K60:AB60"/>
+    <mergeCell ref="E59:J59"/>
+    <mergeCell ref="K59:AB59"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
@@ -11252,38 +12201,60 @@
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="E57:J57"/>
+    <mergeCell ref="K57:AB57"/>
     <mergeCell ref="E58:J58"/>
     <mergeCell ref="K58:AB58"/>
-    <mergeCell ref="E59:J59"/>
-    <mergeCell ref="K59:AB59"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="E60:J60"/>
+    <mergeCell ref="K60:AB60"/>
     <mergeCell ref="E61:J61"/>
     <mergeCell ref="K61:AB61"/>
     <mergeCell ref="E62:J62"/>
     <mergeCell ref="K62:AB62"/>
+    <mergeCell ref="E66:J66"/>
+    <mergeCell ref="K66:AB66"/>
     <mergeCell ref="E63:J63"/>
     <mergeCell ref="K63:AB63"/>
-    <mergeCell ref="E67:J67"/>
-    <mergeCell ref="K67:AB67"/>
     <mergeCell ref="E64:J64"/>
     <mergeCell ref="K64:AB64"/>
     <mergeCell ref="E65:J65"/>
     <mergeCell ref="K65:AB65"/>
-    <mergeCell ref="E66:J66"/>
-    <mergeCell ref="K66:AB66"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
+  <hyperlinks>
+    <hyperlink ref="AB74" r:id="rId1" display="https://jakarta.ee/specifications/faces/" xr:uid="{072C18AF-609F-4653-9808-3595E12CDA8B}"/>
+    <hyperlink ref="AB75" r:id="rId2" display="https://jakarta.ee/specifications/authentication/" xr:uid="{0A797D20-605F-46BB-ADCC-B14FE0BAE9E6}"/>
+    <hyperlink ref="AB76" r:id="rId3" display="https://jakarta.ee/specifications/authorization/" xr:uid="{DEEA3D02-1151-4A12-AE68-04AD5A22943B}"/>
+    <hyperlink ref="AB77" r:id="rId4" display="https://jakarta.ee/specifications/messaging/" xr:uid="{D8FBB6FF-C55B-4709-82BA-8B942F0EE8F3}"/>
+    <hyperlink ref="AB78" r:id="rId5" display="https://jakarta.ee/specifications/persistence/" xr:uid="{2B13828B-C59E-461B-BDE8-DF64D4AA2EBD}"/>
+    <hyperlink ref="AB79" r:id="rId6" display="https://jakarta.ee/specifications/transactions/" xr:uid="{4B4DFC95-691A-43EF-9BA6-3F253F48DED8}"/>
+    <hyperlink ref="AB80" r:id="rId7" display="https://jakarta.ee/specifications/batch/" xr:uid="{BDBD61B2-5A98-4723-9582-4D624CD9BC90}"/>
+    <hyperlink ref="AB81" r:id="rId8" display="https://jakarta.ee/specifications/connectors/" xr:uid="{63C049C0-B50F-4413-8D9E-D92B11C0DCB8}"/>
+    <hyperlink ref="AB82" r:id="rId9" display="https://jakarta.ee/specifications/activation/" xr:uid="{AB9F409E-AB6B-4558-A403-A228A8ABDA31}"/>
+    <hyperlink ref="AB83" r:id="rId10" display="https://jakarta.ee/specifications/expression-language/" xr:uid="{F62A3EF1-C282-4BCC-98A5-A6CA71C650B4}"/>
+    <hyperlink ref="AB84" r:id="rId11" display="https://jakarta.ee/specifications/enterprise-beans/" xr:uid="{704C23F0-9669-4135-B37D-FF9FAF28013A}"/>
+    <hyperlink ref="AB85" r:id="rId12" display="https://jakarta.ee/specifications/xml-binding/" xr:uid="{72A38165-5E11-4AE4-A696-C0EDB438F3FC}"/>
+    <hyperlink ref="AB86" r:id="rId13" display="https://jakarta.ee/specifications/jsonb/" xr:uid="{0C3AD5D6-3AFC-4F21-8554-C2193029568C}"/>
+    <hyperlink ref="AB87" r:id="rId14" display="https://jakarta.ee/specifications/jsonp/" xr:uid="{C91A89E6-4BB2-4045-AAFF-4A88EACA4FE5}"/>
+    <hyperlink ref="AB88" r:id="rId15" display="https://jakarta.ee/specifications/pages/" xr:uid="{E897019C-0949-48DE-8AA1-C7CAA399C7DE}"/>
+    <hyperlink ref="AB89" r:id="rId16" display="https://jakarta.ee/specifications/xml-web-services/" xr:uid="{BEBFEE85-BD91-44D7-BB2A-683DD7731328}"/>
+    <hyperlink ref="AB90" r:id="rId17" display="https://jakarta.ee/specifications/restful-ws/" xr:uid="{02390528-EB8B-4E6A-B1E9-9B563A6E8657}"/>
+    <hyperlink ref="AB91" r:id="rId18" display="https://jakarta.ee/specifications/tags/" xr:uid="{429F9649-389A-4EB4-A123-299AE69673C7}"/>
+    <hyperlink ref="AB92" r:id="rId19" display="https://jakarta.ee/specifications/cdi/" xr:uid="{0CBA927F-33E0-472C-B599-04E03CFEE5F6}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId20"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;C- &amp;P -</oddFooter>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="48" max="34" man="1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="47" max="34" man="1"/>
+    <brk id="67" max="34" man="1"/>
   </rowBreaks>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId21"/>
 </worksheet>
 </file>
 
@@ -11293,7 +12264,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K49"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4.375" style="10" customWidth="1"/>
     <col min="2" max="2" width="21.75" style="10" customWidth="1"/>
@@ -11309,44 +12280,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="169" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="169" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="170" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="146" t="s">
+      <c r="D1" s="169" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="146" t="s">
+      <c r="E1" s="169" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="146" t="s">
+      <c r="F1" s="169" t="s">
         <v>231</v>
       </c>
-      <c r="G1" s="146" t="s">
+      <c r="G1" s="169" t="s">
         <v>224</v>
       </c>
-      <c r="H1" s="146" t="s">
+      <c r="H1" s="169" t="s">
         <v>102</v>
       </c>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146" t="s">
+      <c r="I1" s="169"/>
+      <c r="J1" s="169"/>
+      <c r="K1" s="169" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A2" s="146"/>
-      <c r="B2" s="146"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="148"/>
+      <c r="A2" s="169"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="171"/>
       <c r="H2" s="63" t="s">
         <v>218</v>
       </c>
@@ -11356,7 +12327,7 @@
       <c r="J2" s="63" t="s">
         <v>220</v>
       </c>
-      <c r="K2" s="146"/>
+      <c r="K2" s="169"/>
     </row>
     <row r="3" spans="1:11" ht="101.25" x14ac:dyDescent="0.15">
       <c r="A3" s="57" t="s">
@@ -11372,23 +12343,23 @@
         <v>210</v>
       </c>
       <c r="E3" s="57" t="s">
+        <v>247</v>
+      </c>
+      <c r="F3" s="58" t="s">
         <v>248</v>
-      </c>
-      <c r="F3" s="58" t="s">
-        <v>249</v>
       </c>
       <c r="G3" s="57"/>
       <c r="H3" s="59" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I3" s="59" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J3" s="59" t="s">
         <v>115</v>
       </c>
       <c r="K3" s="57" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="191.25" x14ac:dyDescent="0.15">
@@ -11421,7 +12392,7 @@
         <v>114</v>
       </c>
       <c r="K4" s="57" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.15">
@@ -11438,17 +12409,17 @@
         <v>129</v>
       </c>
       <c r="E5" s="57" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I5" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J5" s="59" t="s">
         <v>115</v>
@@ -11471,17 +12442,17 @@
         <v>158</v>
       </c>
       <c r="E6" s="57" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F6" s="58" t="s">
         <v>53</v>
       </c>
       <c r="G6" s="57"/>
       <c r="H6" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J6" s="59" t="s">
         <v>126</v>
@@ -11493,13 +12464,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C7" s="61" t="s">
         <v>100</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E7" s="57" t="s">
         <v>82</v>
@@ -11508,7 +12479,7 @@
         <v>47</v>
       </c>
       <c r="G7" s="57" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H7" s="59" t="s">
         <v>123</v>
@@ -11520,7 +12491,7 @@
         <v>123</v>
       </c>
       <c r="K7" s="57" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="56.25" x14ac:dyDescent="0.15">
@@ -11549,10 +12520,10 @@
         <v>113</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J8" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K8" s="57" t="s">
         <v>6</v>
@@ -11563,13 +12534,13 @@
         <v>31</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C9" s="61" t="s">
         <v>36</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E9" s="57" t="s">
         <v>73</v>
@@ -11584,13 +12555,13 @@
         <v>113</v>
       </c>
       <c r="I9" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J9" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K9" s="57" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.15">
@@ -11607,10 +12578,10 @@
         <v>161</v>
       </c>
       <c r="E10" s="57" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G10" s="57" t="s">
         <v>51</v>
@@ -11619,13 +12590,13 @@
         <v>114</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J10" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K10" s="57" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="337.5" x14ac:dyDescent="0.15">
@@ -11642,23 +12613,23 @@
         <v>165</v>
       </c>
       <c r="E11" s="57" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G11" s="57"/>
       <c r="H11" s="59" t="s">
         <v>112</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J11" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K11" s="57" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -11675,23 +12646,23 @@
         <v>165</v>
       </c>
       <c r="E12" s="57" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G12" s="57"/>
       <c r="H12" s="59" t="s">
         <v>112</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J12" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K12" s="57" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.15">
@@ -11702,23 +12673,23 @@
         <v>128</v>
       </c>
       <c r="C13" s="61" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D13" s="57" t="s">
         <v>5</v>
       </c>
       <c r="E13" s="57" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F13" s="58" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G13" s="57"/>
       <c r="H13" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I13" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J13" s="59" t="s">
         <v>116</v>
@@ -11736,7 +12707,7 @@
         <v>40</v>
       </c>
       <c r="D14" s="57" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E14" s="57" t="s">
         <v>74</v>
@@ -11746,10 +12717,10 @@
       </c>
       <c r="G14" s="57"/>
       <c r="H14" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J14" s="59" t="s">
         <v>118</v>
@@ -11773,20 +12744,20 @@
         <v>7</v>
       </c>
       <c r="F15" s="58" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G15" s="57"/>
       <c r="H15" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I15" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J15" s="59" t="s">
         <v>115</v>
       </c>
       <c r="K15" s="57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="78.75" x14ac:dyDescent="0.15">
@@ -11797,23 +12768,23 @@
         <v>150</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D16" s="57" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E16" s="57" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G16" s="57"/>
       <c r="H16" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I16" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J16" s="59" t="s">
         <v>126</v>
@@ -11831,53 +12802,51 @@
         <v>78</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E17" s="57" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G17" s="57"/>
       <c r="H17" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I17" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J17" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="K17" s="57" t="s">
-        <v>232</v>
-      </c>
+      <c r="K17" s="57"/>
     </row>
     <row r="18" spans="1:11" ht="157.5" x14ac:dyDescent="0.15">
       <c r="A18" s="57" t="s">
         <v>32</v>
       </c>
       <c r="B18" s="57" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C18" s="61" t="s">
         <v>79</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E18" s="57" t="s">
         <v>8</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G18" s="57"/>
       <c r="H18" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I18" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J18" s="59" t="s">
         <v>119</v>
@@ -11891,26 +12860,26 @@
         <v>32</v>
       </c>
       <c r="B19" s="57" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C19" s="61" t="s">
         <v>77</v>
       </c>
       <c r="D19" s="57" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E19" s="57" t="s">
         <v>9</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G19" s="57"/>
       <c r="H19" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I19" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J19" s="59" t="s">
         <v>119</v>
@@ -11930,20 +12899,20 @@
         <v>1</v>
       </c>
       <c r="D20" s="57" t="s">
+        <v>250</v>
+      </c>
+      <c r="E20" s="57" t="s">
         <v>251</v>
       </c>
-      <c r="E20" s="57" t="s">
-        <v>252</v>
-      </c>
       <c r="F20" s="58" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G20" s="57"/>
       <c r="H20" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I20" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J20" s="59" t="s">
         <v>116</v>
@@ -11973,10 +12942,10 @@
         <v>141</v>
       </c>
       <c r="H21" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I21" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J21" s="59" t="s">
         <v>115</v>
@@ -11994,7 +12963,7 @@
         <v>176</v>
       </c>
       <c r="D22" s="57" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E22" s="57" t="s">
         <v>191</v>
@@ -12009,10 +12978,10 @@
         <v>113</v>
       </c>
       <c r="I22" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J22" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K22" s="57" t="s">
         <v>177</v>
@@ -12041,13 +13010,13 @@
         <v>55</v>
       </c>
       <c r="H23" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I23" s="59" t="s">
         <v>56</v>
       </c>
       <c r="J23" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K23" s="57" t="s">
         <v>144</v>
@@ -12076,10 +13045,10 @@
         <v>59</v>
       </c>
       <c r="H24" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I24" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J24" s="59" t="s">
         <v>117</v>
@@ -12111,10 +13080,10 @@
         <v>62</v>
       </c>
       <c r="H25" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I25" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J25" s="59" t="s">
         <v>130</v>
@@ -12134,7 +13103,7 @@
         <v>28</v>
       </c>
       <c r="D26" s="57" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E26" s="57" t="s">
         <v>29</v>
@@ -12146,10 +13115,10 @@
         <v>122</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I26" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J26" s="59" t="s">
         <v>121</v>
@@ -12172,19 +13141,19 @@
         <v>168</v>
       </c>
       <c r="E27" s="57" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F27" s="60" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G27" s="57" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H27" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I27" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J27" s="59" t="s">
         <v>123</v>
@@ -12202,28 +13171,28 @@
         <v>83</v>
       </c>
       <c r="D28" s="57" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E28" s="57" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F28" s="60" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G28" s="57" t="s">
-        <v>277</v>
+        <v>396</v>
       </c>
       <c r="H28" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I28" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J28" s="59" t="s">
         <v>113</v>
       </c>
       <c r="K28" s="57" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="281.25" x14ac:dyDescent="0.15">
@@ -12237,22 +13206,22 @@
         <v>85</v>
       </c>
       <c r="D29" s="57" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E29" s="57" t="s">
+        <v>274</v>
+      </c>
+      <c r="F29" s="60" t="s">
+        <v>334</v>
+      </c>
+      <c r="G29" s="57" t="s">
         <v>275</v>
       </c>
-      <c r="F29" s="60" t="s">
-        <v>336</v>
-      </c>
-      <c r="G29" s="57" t="s">
-        <v>276</v>
-      </c>
       <c r="H29" s="59" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I29" s="59" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J29" s="59" t="s">
         <v>123</v>
@@ -12270,22 +13239,22 @@
         <v>84</v>
       </c>
       <c r="D30" s="57" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E30" s="57" t="s">
         <v>227</v>
       </c>
       <c r="F30" s="60" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G30" s="57" t="s">
         <v>229</v>
       </c>
       <c r="H30" s="59" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I30" s="59" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J30" s="59" t="s">
         <v>123</v>
@@ -12300,23 +13269,23 @@
         <v>135</v>
       </c>
       <c r="C31" s="61" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D31" s="57" t="s">
         <v>154</v>
       </c>
       <c r="E31" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F31" s="58" t="s">
         <v>64</v>
       </c>
       <c r="G31" s="57"/>
       <c r="H31" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I31" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J31" s="59" t="s">
         <v>115</v>
@@ -12334,7 +13303,7 @@
         <v>91</v>
       </c>
       <c r="D32" s="57" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E32" s="57" t="s">
         <v>136</v>
@@ -12344,10 +13313,10 @@
       </c>
       <c r="G32" s="57"/>
       <c r="H32" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I32" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J32" s="59" t="s">
         <v>116</v>
@@ -12371,7 +13340,7 @@
         <v>12</v>
       </c>
       <c r="F33" s="60" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G33" s="57" t="s">
         <v>138</v>
@@ -12380,13 +13349,13 @@
         <v>113</v>
       </c>
       <c r="I33" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J33" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K33" s="57" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="135" x14ac:dyDescent="0.15">
@@ -12394,13 +13363,13 @@
         <v>194</v>
       </c>
       <c r="B34" s="57" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C34" s="61" t="s">
         <v>124</v>
       </c>
       <c r="D34" s="57" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E34" s="57" t="s">
         <v>89</v>
@@ -12413,13 +13382,13 @@
         <v>113</v>
       </c>
       <c r="I34" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J34" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K34" s="57" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="112.5" x14ac:dyDescent="0.15">
@@ -12427,13 +13396,13 @@
         <v>111</v>
       </c>
       <c r="B35" s="57" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C35" s="61" t="s">
         <v>226</v>
       </c>
       <c r="D35" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E35" s="57" t="s">
         <v>228</v>
@@ -12443,10 +13412,10 @@
       </c>
       <c r="G35" s="57"/>
       <c r="H35" s="62" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I35" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J35" s="59" t="s">
         <v>127</v>
@@ -12458,7 +13427,7 @@
         <v>195</v>
       </c>
       <c r="B36" s="57" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C36" s="61" t="s">
         <v>35</v>
@@ -12474,10 +13443,10 @@
       </c>
       <c r="G36" s="57"/>
       <c r="H36" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I36" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J36" s="59" t="s">
         <v>116</v>
@@ -12489,26 +13458,26 @@
         <v>111</v>
       </c>
       <c r="B37" s="57" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C37" s="61" t="s">
         <v>90</v>
       </c>
       <c r="D37" s="57" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E37" s="57" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F37" s="58" t="s">
         <v>64</v>
       </c>
       <c r="G37" s="57"/>
       <c r="H37" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I37" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J37" s="59" t="s">
         <v>112</v>
@@ -12532,7 +13501,7 @@
         <v>12</v>
       </c>
       <c r="F38" s="60" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G38" s="57" t="s">
         <v>138</v>
@@ -12541,10 +13510,10 @@
         <v>113</v>
       </c>
       <c r="I38" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J38" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K38" s="57" t="s">
         <v>14</v>
@@ -12561,7 +13530,7 @@
         <v>124</v>
       </c>
       <c r="D39" s="57" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E39" s="57" t="s">
         <v>89</v>
@@ -12574,13 +13543,13 @@
         <v>113</v>
       </c>
       <c r="I39" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J39" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K39" s="57" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="45" x14ac:dyDescent="0.15">
@@ -12604,10 +13573,10 @@
       </c>
       <c r="G40" s="57"/>
       <c r="H40" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I40" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J40" s="59" t="s">
         <v>115</v>
@@ -12631,7 +13600,7 @@
         <v>13</v>
       </c>
       <c r="F41" s="60" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G41" s="57" t="s">
         <v>138</v>
@@ -12640,10 +13609,10 @@
         <v>130</v>
       </c>
       <c r="I41" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J41" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K41" s="57" t="s">
         <v>15</v>
@@ -12654,13 +13623,13 @@
         <v>33</v>
       </c>
       <c r="B42" s="57" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C42" s="61" t="s">
         <v>198</v>
       </c>
       <c r="D42" s="57" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E42" s="57" t="s">
         <v>89</v>
@@ -12673,13 +13642,13 @@
         <v>126</v>
       </c>
       <c r="I42" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J42" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K42" s="57" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="56.25" x14ac:dyDescent="0.15">
@@ -12703,13 +13672,13 @@
       </c>
       <c r="G43" s="57"/>
       <c r="H43" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I43" s="59" t="s">
         <v>120</v>
       </c>
       <c r="J43" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K43" s="57" t="s">
         <v>159</v>
@@ -12736,13 +13705,13 @@
       </c>
       <c r="G44" s="57"/>
       <c r="H44" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I44" s="59" t="s">
         <v>119</v>
       </c>
       <c r="J44" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K44" s="57" t="s">
         <v>149</v>
@@ -12753,19 +13722,19 @@
         <v>99</v>
       </c>
       <c r="B45" s="57" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C45" s="61" t="s">
         <v>88</v>
       </c>
       <c r="D45" s="57" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E45" s="57" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F45" s="58" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G45" s="57"/>
       <c r="H45" s="59" t="s">
@@ -12775,10 +13744,10 @@
         <v>53</v>
       </c>
       <c r="J45" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K45" s="57" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="135" x14ac:dyDescent="0.15">
@@ -12810,7 +13779,7 @@
         <v>113</v>
       </c>
       <c r="J46" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K46" s="57" t="s">
         <v>181</v>
@@ -12821,19 +13790,19 @@
         <v>99</v>
       </c>
       <c r="B47" s="57" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C47" s="61" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D47" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="E47" s="57" t="s">
         <v>264</v>
       </c>
-      <c r="E47" s="57" t="s">
-        <v>265</v>
-      </c>
       <c r="F47" s="60" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G47" s="57"/>
       <c r="H47" s="59" t="s">
@@ -12843,7 +13812,7 @@
         <v>119</v>
       </c>
       <c r="J47" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K47" s="57" t="s">
         <v>180</v>
@@ -12860,10 +13829,10 @@
         <v>148</v>
       </c>
       <c r="D48" s="57" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E48" s="57" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F48" s="60" t="s">
         <v>71</v>
@@ -12876,7 +13845,7 @@
         <v>113</v>
       </c>
       <c r="J48" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K48" s="57" t="s">
         <v>179</v>
@@ -12893,13 +13862,13 @@
         <v>137</v>
       </c>
       <c r="D49" s="57" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E49" s="57" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F49" s="60" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G49" s="57"/>
       <c r="H49" s="59" t="s">
@@ -12909,7 +13878,7 @@
         <v>119</v>
       </c>
       <c r="J49" s="59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K49" s="57" t="s">
         <v>179</v>
@@ -12930,7 +13899,7 @@
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="8" scale="68" fitToHeight="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="71" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;C- &amp;P -</oddFooter>
   </headerFooter>
